--- a/all_grants.xlsx
+++ b/all_grants.xlsx
@@ -489,191 +489,37 @@
       <c r="B2" s="1" t="inlineStr"/>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>RFP - for Website Maintenance and Hosting</t>
+          <t>RFQ - Construction of Grey water treatment, Water tank, New Borewell, Toil...</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>MAMTA Health Institute for Mother and Child (MAMTA) | India
-International Development - RFP - for Website Maintenance and Hosting, MAMTA Health Institute for Mother and Child (MAMTA), India - DevNetJobsIndia.org
+          <t>WaterAid India | Raichur District, Karnataka
+International Development - RFQ - Construction of Grey water treatment, Water tank, New Borewell, Toilet Retrofitting, Rainwater Harvesting in 6 Gram panchayats..., WaterAid India, Karnataka - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
 Register
 Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search ... Read More</t>
+Value M ... Read More</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>• 2. Scope of Work
-Website
-Hosting
-Host Mamta’s website,
-www.mamtahimc.in.
-Website hosting must be isolated from
-any
-other
-websites
-or
-applications
-not
-related
-to
-the
-website.
-Designated
-Mamta
-staff
-should
-have
-full
-access permissions
-to
-the
-hosting
-environment.
-The
-hosting
-environment
-must
-have
-monitoring
-and
-threat
-protection
-systems
-in place to monitor for unusual activity and activity patterns and prevent unauthorized access attempts.
-The
-website
-should
-only
-be
-accessible
-through
-HTTPS
-connection
-using
-an
-auto- renewing SSL (TLS) certificate. The certificate must be maintained by the
-Vendor.
-Website
-Maintenance
-Provide
-ongoing
-website
-maintenance,
-including:
-Regular
-updates
-of
-the
-server
-and
-the
-website
-software
-as
-verified
-updates
-and security patches become available.
-Upgrades
-must
-be
-deployed
-to
-Vendor’s
-test
-servers
-and
-tested
-prior
-to
-production
-release.
-Ongoing
-performance
-and
-security
-monitoring.
-Upon
-discovery
-of
-any
-performance
-and/or
-security
-issue,
-notifications must be sent to Client. Performance and security issues are treated as high priority/urgent, and Client is immediately notified by email.
-Routine maintenance of the server and application software, licensing, including third-party integrations such as Single Sign-On, ADP, Google Tag Manager and Analytics,
-and
-other
-third-party
-systems
-as
-applicable
-to
-ensure
-website’s
-optimal and secure performance.
-Daily
-backups.
-User
-Support
-Provide
-ongoing
-website
-user
-support,
-including
-but
-not
-limited
-to:
-Requests
-to
-modify
-or
-update
-content,
-imagery
-and
-templates.
-Add or modify pages, banners, photographs, graphics
-Password
-reset
-assistance.
-Submission of Proposals
-The deadline for submission of proposals is
-2 March, 2026
-. Submissions
-must
-be forwarded in electronic
-format
-only (either
-PDF or
-Microsoft Word and Excel) to
-rfp@mamtahimc.in.
-Offerors must not submit zipped files or drive links. The technical proposal and cost proposal must be sent as separate attachments. Please mention RFP Name in the e-mail subject line. Offerors are responsible for
-ensuring that
-their
-offers are received in
-accordance with
-the
-instructions stated herein.
-For detailed information, please check the complete version of the RFP attached below.
+          <t>• Terms and Conditions:
+Selected vendor will be received the bidding confirmation within 10 days from the last day of RFQ (last day of quotation submission date) and the other vendors can consider the bidding has been closed and work assignment has been completed; no specified mails will be sent about selection of vendors.
+Quotation should send to
+waiprocurementbengaluru@wateraid.org.
+For detailed information, please check the complete version of the RFQ attached below.
 • Job Email ID:
-rfp(at)mamtahimc.in
+waiprocurementbengaluru(at)wateraid.org
 Download Attachment:
-Request for Proposal for Website_19022026.doc
+Tender Notice for open tendering_WRC - RAICHUR.pdf
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
 Apply by:
-02 Mar 2026
+03 Mar 2026
 Access all the jobs and get ahead!
 Subscribe to Value Membership Now!
 Subscribe
@@ -735,54 +581,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Project) Health &amp; Nutrition
-Bal Raksha Bharat (BRB)
-Location:
-Rajasthan
+RFP - Requirement of Agency for Creating High Qua...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Delhi
+Apply by:
+20 Mar 2026
+Programme officers (Education &amp; Life Skills Educa...
+Butterflies NGO
+Location:
+Delhi
+Apply by:
+15 Mar 2026
+RFQ: Construction of New gated check dams, De-sil...
+WaterAid India
+Location:
+Telangana
 Apply by:
 08 Mar 2026
-Regional Coordinator - North
-Intas Foundation
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Monitoring Coordinator
-Intas Foundation
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Individual Consultant – Technical support on Foun...
-UNICEF
-Location:
-Rajasthan
-Apply by:
-09 Mar 2026
-Multiple Vacancies
-AIDENT Social Welfare Organisation (ASWO)
-Location:
-Uttar Pradesh
-Apply by:
-16 Mar 2026
-Head of Accounts &amp; Finance
-Watershed Organization Trust (WOTR)
+Regional Coordinator
+Bharat Rural Livelihoods Foundation (BRLF)
 Location:
 Maharashtra
 Apply by:
-01 Apr 2026
-Sr. Manager/Manager-Sustainable Cotton Programmes
-Aga Khan Rural Support Programme India (AKRSP Ind...
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Project Manager – Vocational and Skill Development
-White Lotus Trust
-Location:
-Delhi
-Apply by:
-01 Apr 2026
+18 Mar 2026
+Project Nurse 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Project Technical Support 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Block Academic Coordinator
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
+District Program Manager
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
 Jobseekers
 Register
 Login
@@ -812,12 +658,12 @@
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>Learning, Safety</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>02-03-2026</t>
+          <t>03-03-2026</t>
         </is>
       </c>
       <c r="H2" s="1" t="n">
@@ -825,7 +671,7 @@
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287390</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287688</t>
         </is>
       </c>
     </row>
@@ -838,603 +684,10 @@
       <c r="B3" s="1" t="inlineStr"/>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>RFP - Hiring Agency/Organisation for the implementation of biosecurity at ...</t>
+          <t>RFP – EOI for the Establishment of Recharge Shaft</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Jhpiego | India
-International Development - RFP - Hiring Agency/Organisation for the implementation of biosecurity at human – Animal interfaces, Jhpiego, India - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Login ... Read More</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>• Section 4 - Scope of Work
-Section 5 –
-Vendor Information Form– Standard   Template
-Section 6 - Standard   Template of Technical Service Contract
-For detailed information, please check the complete version of the RFP attached below.
-• Job Email ID:
-jhpin.procurement(at)jhpiego.org
-Download Attachment:
-RFP - Hiring agency for the implementation of biosecurity.pdf
-Download Attachment:
-MOM - Pre-bid.doc
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-02 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-Assistant Manager (Project) Health &amp; Nutrition
-Bal Raksha Bharat (BRB)
-Location:
-Rajasthan
-Apply by:
-08 Mar 2026
-Regional Coordinator - North
-Intas Foundation
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Monitoring Coordinator
-Intas Foundation
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Individual Consultant – Technical support on Foun...
-UNICEF
-Location:
-Rajasthan
-Apply by:
-09 Mar 2026
-Multiple Vacancies
-AIDENT Social Welfare Organisation (ASWO)
-Location:
-Uttar Pradesh
-Apply by:
-16 Mar 2026
-Head of Accounts &amp; Finance
-Watershed Organization Trust (WOTR)
-Location:
-Maharashtra
-Apply by:
-01 Apr 2026
-Sr. Manager/Manager-Sustainable Cotton Programmes
-Aga Khan Rural Support Programme India (AKRSP Ind...
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Project Manager – Vocational and Skill Development
-White Lotus Trust
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>02-03-2026</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287080</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr"/>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Evaluation of Centre for Catalyzing Change’s Program at Scale of Co...</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Centre for Catalyzing Change (C3) | India
-International Development - RFP - Evaluation of Centre for Catalyzing Change’s Program at Scale of  Completion of Education and Delayed marriage of Adolescents Girls, Centre for Catalyzing Change (C3), India - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Registe ... Read More</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>• b. Proposal Submission Guidelines
-The applicant should submit the Technical and Financial Proposal in two separate pdf documents
-Each proposal (Technical and Financial) should be saved in a separate pdf file marked as &lt;Agency name&gt;_&lt;proposal type&gt;_C3_Education Initiative Evaluation e.g. the technical proposal of X agency well be will be saved as
-X_Technical Proposal_C3_Education initiatives_ Evaluation.pdf
-All the proposals to be zipped together in one folder named &lt;Agency name&gt;_C3_Education initiative Evaluation should be emailed to
-procument@c3india.org
-on or before the proposal submission time
-The email containing the proposal should quote &lt;Agency name&gt;_Proposal_C3_Education initiative Evaluation in the subject line
-For detailed information, please check the complete version of the RFP attached below.
-Download Attachment:
-RFP for education initiatives_C3.pdf
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-02 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-Assistant Manager (Project) Health &amp; Nutrition
-Bal Raksha Bharat (BRB)
-Location:
-Rajasthan
-Apply by:
-08 Mar 2026
-Regional Coordinator - North
-Intas Foundation
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Monitoring Coordinator
-Intas Foundation
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Individual Consultant – Technical support on Foun...
-UNICEF
-Location:
-Rajasthan
-Apply by:
-09 Mar 2026
-Multiple Vacancies
-AIDENT Social Welfare Organisation (ASWO)
-Location:
-Uttar Pradesh
-Apply by:
-16 Mar 2026
-Head of Accounts &amp; Finance
-Watershed Organization Trust (WOTR)
-Location:
-Maharashtra
-Apply by:
-01 Apr 2026
-Sr. Manager/Manager-Sustainable Cotton Programmes
-Aga Khan Rural Support Programme India (AKRSP Ind...
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Project Manager – Vocational and Skill Development
-White Lotus Trust
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>02-03-2026</t>
-        </is>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=285557</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr"/>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>RFQ - Construction of Grey water treatment, Water tank, New Borewell, Toil...</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>WaterAid India | Raichur District, Karnataka
-International Development - RFQ - Construction of Grey water treatment, Water tank, New Borewell, Toilet Retrofitting, Rainwater Harvesting in 6 Gram panchayats..., WaterAid India, Karnataka - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value M ... Read More</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>• Terms and Conditions:
-Selected vendor will be received the bidding confirmation within 10 days from the last day of RFQ (last day of quotation submission date) and the other vendors can consider the bidding has been closed and work assignment has been completed; no specified mails will be sent about selection of vendors.
-Quotation should send to
-waiprocurementbengaluru@wateraid.org.
-For detailed information, please check the complete version of the RFQ attached below.
-• Job Email ID:
-waiprocurementbengaluru(at)wateraid.org
-Download Attachment:
-Tender Notice for open tendering_WRC - RAICHUR.pdf
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-03 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-Assistant Manager (Project) Health &amp; Nutrition
-Bal Raksha Bharat (BRB)
-Location:
-Rajasthan
-Apply by:
-08 Mar 2026
-Regional Coordinator - North
-Intas Foundation
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Monitoring Coordinator
-Intas Foundation
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Individual Consultant – Technical support on Foun...
-UNICEF
-Location:
-Rajasthan
-Apply by:
-09 Mar 2026
-Multiple Vacancies
-AIDENT Social Welfare Organisation (ASWO)
-Location:
-Uttar Pradesh
-Apply by:
-16 Mar 2026
-Head of Accounts &amp; Finance
-Watershed Organization Trust (WOTR)
-Location:
-Maharashtra
-Apply by:
-01 Apr 2026
-Sr. Manager/Manager-Sustainable Cotton Programmes
-Aga Khan Rural Support Programme India (AKRSP Ind...
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Project Manager – Vocational and Skill Development
-White Lotus Trust
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G5" s="1" t="inlineStr">
-        <is>
-          <t>03-03-2026</t>
-        </is>
-      </c>
-      <c r="H5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287688</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr"/>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>RFP – EOI for the Establishment of Recharge Shaft</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>PHD Rural Development Foundation | Alwar and Jaipur districts, Rajasthan
 International Development - RFP – EOI for the Establishment of Recharge Shaft, PHD Rural Development Foundation, Rajasthan - DevNetJobsIndia.org
@@ -1448,7 +701,7 @@
 RFPs/Tenders ... Read More</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>• Only those firms that qualify in the technical bid will be considered for the price bid. The price bid will have to be submitted separately in a sealed envelope later, based on the scope of work, which will be shared with the successful technical bidders.
 Therefore, experienced vendors are invited to submit the technical bid as follows. The technical bid must include the following relevant documents (items (i) to (xi):
@@ -1543,54 +796,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Project) Health &amp; Nutrition
-Bal Raksha Bharat (BRB)
-Location:
-Rajasthan
+RFP - Requirement of Agency for Creating High Qua...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Delhi
+Apply by:
+20 Mar 2026
+Programme officers (Education &amp; Life Skills Educa...
+Butterflies NGO
+Location:
+Delhi
+Apply by:
+15 Mar 2026
+RFQ: Construction of New gated check dams, De-sil...
+WaterAid India
+Location:
+Telangana
 Apply by:
 08 Mar 2026
-Regional Coordinator - North
-Intas Foundation
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Monitoring Coordinator
-Intas Foundation
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Individual Consultant – Technical support on Foun...
-UNICEF
-Location:
-Rajasthan
-Apply by:
-09 Mar 2026
-Multiple Vacancies
-AIDENT Social Welfare Organisation (ASWO)
-Location:
-Uttar Pradesh
-Apply by:
-16 Mar 2026
-Head of Accounts &amp; Finance
-Watershed Organization Trust (WOTR)
+Regional Coordinator
+Bharat Rural Livelihoods Foundation (BRLF)
 Location:
 Maharashtra
 Apply by:
-01 Apr 2026
-Sr. Manager/Manager-Sustainable Cotton Programmes
-Aga Khan Rural Support Programme India (AKRSP Ind...
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Project Manager – Vocational and Skill Development
-White Lotus Trust
-Location:
-Delhi
-Apply by:
-01 Apr 2026
+18 Mar 2026
+Project Nurse 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Project Technical Support 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Block Academic Coordinator
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
+District Program Manager
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
 Jobseekers
 Register
 Login
@@ -1618,38 +871,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F6" s="1" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G6" s="1" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>03-03-2026</t>
         </is>
       </c>
-      <c r="H6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="1" t="inlineStr">
+      <c r="H3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287598</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr"/>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr"/>
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>RFP- for Hiring a Resource Person/Agency Development of MEAL Questionnaire...</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Parmarth Samaj Sevi Sansthan | Jhansi, Uttar Pradesh
 International Development - RFP- for Hiring a Resource Person/Agency Development of MEAL Questionnaires and Processes for CommCare Tool, Parmarth Samaj Sevi Sansthan, Uttar Pradesh - DevNetJobsIndia.org
@@ -1661,7 +914,7 @@
 Value Mem ... Read More</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>• Introduction and context:
 Parmarth Samaj Sevi Sansthan
@@ -1838,54 +1091,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Project) Health &amp; Nutrition
-Bal Raksha Bharat (BRB)
-Location:
-Rajasthan
+RFP - Requirement of Agency for Creating High Qua...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Delhi
+Apply by:
+20 Mar 2026
+Programme officers (Education &amp; Life Skills Educa...
+Butterflies NGO
+Location:
+Delhi
+Apply by:
+15 Mar 2026
+RFQ: Construction of New gated check dams, De-sil...
+WaterAid India
+Location:
+Telangana
 Apply by:
 08 Mar 2026
-Regional Coordinator - North
-Intas Foundation
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Monitoring Coordinator
-Intas Foundation
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Individual Consultant – Technical support on Foun...
-UNICEF
-Location:
-Rajasthan
-Apply by:
-09 Mar 2026
-Multiple Vacancies
-AIDENT Social Welfare Organisation (ASWO)
-Location:
-Uttar Pradesh
-Apply by:
-16 Mar 2026
-Head of Accounts &amp; Finance
-Watershed Organization Trust (WOTR)
+Regional Coordinator
+Bharat Rural Livelihoods Foundation (BRLF)
 Location:
 Maharashtra
 Apply by:
-01 Apr 2026
-Sr. Manager/Manager-Sustainable Cotton Programmes
-Aga Khan Rural Support Programme India (AKRSP Ind...
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Project Manager – Vocational and Skill Development
-White Lotus Trust
-Location:
-Delhi
-Apply by:
-01 Apr 2026
+18 Mar 2026
+Project Nurse 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Project Technical Support 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Block Academic Coordinator
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
+District Program Manager
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
 Jobseekers
 Register
 Login
@@ -1913,38 +1166,240 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F7" s="1" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G7" s="1" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>03-03-2026</t>
         </is>
       </c>
-      <c r="H7" s="1" t="n">
+      <c r="H4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287368</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr"/>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>EoI - Construction &amp; Infrastructure Works – Schools Of Pali And Jodhpur D...</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Ashray Foundation | Pali And Jodhpur Districts, Rajasthan
+International Development - EoI -  Construction &amp; Infrastructure Works – Schools Of Pali And Jodhpur Districts, Rajasthan, Ashray Foundation, Rajasthan - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume ... Read More</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>• Scope of Work:
+Construction of Tin Sheds (12) and Additional Classrooms (15) in Govt. Schools, Upgradation of Sports Stadium (2)
+• Eligibility Criteria:
+Interested agencies must meet the following requirements:
+Valid statutory registrations (GST, PAN, etc.).
+Minimum relevant experience of 3 years in same activity is mandatory
+Demonstrated capacity and team to execute projects within strict timelines and quality
+• Submission Details:
+Interested agencies are requested to submit their EOI along with: Company Profile, Details of Relevant Project Experience, Copies of Necessary Registration &amp; Compliance Documents and Geo-tagged Photographs of the work undertaken, if any
+Last Date for Submission &amp; mail id for submission:
+04/03/2026 and
+tenders@ashrayfoundation.org
+Note: Ashray Foundation reserves the right to accept or reject any or all proposals without assigning any reason.
+• Job Email ID:
+tenders(at)ashrayfoundation.org
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+04 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Associate (Programme Management)
+Indian Institute For Human Settlements (Iihs)
+Location:
+Karnataka
+Apply by:
+07 Mar 2026
+Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+RFP - Requirement of Agency for Creating High Qua...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Delhi
+Apply by:
+20 Mar 2026
+Programme officers (Education &amp; Life Skills Educa...
+Butterflies NGO
+Location:
+Delhi
+Apply by:
+15 Mar 2026
+RFQ: Construction of New gated check dams, De-sil...
+WaterAid India
+Location:
+Telangana
+Apply by:
+08 Mar 2026
+Regional Coordinator
+Bharat Rural Livelihoods Foundation (BRLF)
+Location:
+Maharashtra
+Apply by:
+18 Mar 2026
+Project Nurse 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Project Technical Support 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Block Academic Coordinator
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
+District Program Manager
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>04-03-2026</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287368</t>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287610</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr"/>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="B6" s="1" t="inlineStr"/>
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>EoI - Mobile Cancer Screening Project – Ut Of Andaman &amp; Nicobar Islands</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Ashray Foundation | Sri Vijaya Puram (Port Blair), Andaman and Nicobar Islands
 International Development - EoI - Mobile Cancer Screening Project – Ut Of Andaman &amp; Nicobar Islands, Ashray Foundation, Andaman and Nicobar Islands - DevNetJobsIndia.org
@@ -1956,7 +1411,7 @@
 Value Membership ... Read More</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>• Scope of Work:
 Requirement of Vehicle:
@@ -2047,54 +1502,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Project) Health &amp; Nutrition
-Bal Raksha Bharat (BRB)
-Location:
-Rajasthan
+RFP - Requirement of Agency for Creating High Qua...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Delhi
+Apply by:
+20 Mar 2026
+Programme officers (Education &amp; Life Skills Educa...
+Butterflies NGO
+Location:
+Delhi
+Apply by:
+15 Mar 2026
+RFQ: Construction of New gated check dams, De-sil...
+WaterAid India
+Location:
+Telangana
 Apply by:
 08 Mar 2026
-Regional Coordinator - North
-Intas Foundation
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Monitoring Coordinator
-Intas Foundation
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Individual Consultant – Technical support on Foun...
-UNICEF
-Location:
-Rajasthan
-Apply by:
-09 Mar 2026
-Multiple Vacancies
-AIDENT Social Welfare Organisation (ASWO)
-Location:
-Uttar Pradesh
-Apply by:
-16 Mar 2026
-Head of Accounts &amp; Finance
-Watershed Organization Trust (WOTR)
+Regional Coordinator
+Bharat Rural Livelihoods Foundation (BRLF)
 Location:
 Maharashtra
 Apply by:
-01 Apr 2026
-Sr. Manager/Manager-Sustainable Cotton Programmes
-Aga Khan Rural Support Programme India (AKRSP Ind...
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Project Manager – Vocational and Skill Development
-White Lotus Trust
-Location:
-Delhi
-Apply by:
-01 Apr 2026
+18 Mar 2026
+Project Nurse 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Project Technical Support 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Block Academic Coordinator
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
+District Program Manager
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
 Jobseekers
 Register
 Login
@@ -2122,38 +1577,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F8" s="1" t="inlineStr">
+      <c r="F6" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G8" s="1" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>04-03-2026</t>
         </is>
       </c>
-      <c r="H8" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I8" s="1" t="inlineStr">
+      <c r="H6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287612</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr"/>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>RFQ - for Case Study</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>MAMTA Health Institute for Mother and Child (MAMTA) | India
 International Development - RFQ - for Case Study, MAMTA Health Institute for Mother and Child (MAMTA), India - DevNetJobsIndia.org
@@ -2170,7 +1625,7 @@
 Jobseeke ... Read More</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>• Scope of Work
 Mamta–HIMC
@@ -2302,54 +1757,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Project) Health &amp; Nutrition
-Bal Raksha Bharat (BRB)
-Location:
-Rajasthan
+RFP - Requirement of Agency for Creating High Qua...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Delhi
+Apply by:
+20 Mar 2026
+Programme officers (Education &amp; Life Skills Educa...
+Butterflies NGO
+Location:
+Delhi
+Apply by:
+15 Mar 2026
+RFQ: Construction of New gated check dams, De-sil...
+WaterAid India
+Location:
+Telangana
 Apply by:
 08 Mar 2026
-Regional Coordinator - North
-Intas Foundation
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Monitoring Coordinator
-Intas Foundation
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Individual Consultant – Technical support on Foun...
-UNICEF
-Location:
-Rajasthan
-Apply by:
-09 Mar 2026
-Multiple Vacancies
-AIDENT Social Welfare Organisation (ASWO)
-Location:
-Uttar Pradesh
-Apply by:
-16 Mar 2026
-Head of Accounts &amp; Finance
-Watershed Organization Trust (WOTR)
+Regional Coordinator
+Bharat Rural Livelihoods Foundation (BRLF)
 Location:
 Maharashtra
 Apply by:
-01 Apr 2026
-Sr. Manager/Manager-Sustainable Cotton Programmes
-Aga Khan Rural Support Programme India (AKRSP Ind...
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Project Manager – Vocational and Skill Development
-White Lotus Trust
-Location:
-Delhi
-Apply by:
-01 Apr 2026
+18 Mar 2026
+Project Nurse 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Project Technical Support 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Block Academic Coordinator
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
+District Program Manager
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
 Jobseekers
 Register
 Login
@@ -2377,722 +1832,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F9" s="1" t="inlineStr">
+      <c r="F7" s="1" t="inlineStr">
         <is>
           <t>Safety</t>
         </is>
       </c>
-      <c r="G9" s="1" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>04-03-2026</t>
         </is>
       </c>
-      <c r="H9" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" s="1" t="inlineStr">
+      <c r="H7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287442</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr"/>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>EoI - Construction &amp; Infrastructure Works – Schools Of Pali And Jodhpur D...</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Ashray Foundation | Pali And Jodhpur Districts, Rajasthan
-International Development - EoI -  Construction &amp; Infrastructure Works – Schools Of Pali And Jodhpur Districts, Rajasthan, Ashray Foundation, Rajasthan - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume ... Read More</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>• Scope of Work:
-Construction of Tin Sheds (12) and Additional Classrooms (15) in Govt. Schools, Upgradation of Sports Stadium (2)
-• Eligibility Criteria:
-Interested agencies must meet the following requirements:
-Valid statutory registrations (GST, PAN, etc.).
-Minimum relevant experience of 3 years in same activity is mandatory
-Demonstrated capacity and team to execute projects within strict timelines and quality
-• Submission Details:
-Interested agencies are requested to submit their EOI along with: Company Profile, Details of Relevant Project Experience, Copies of Necessary Registration &amp; Compliance Documents and Geo-tagged Photographs of the work undertaken, if any
-Last Date for Submission &amp; mail id for submission:
-04/03/2026 and
-tenders@ashrayfoundation.org
-Note: Ashray Foundation reserves the right to accept or reject any or all proposals without assigning any reason.
-• Job Email ID:
-tenders(at)ashrayfoundation.org
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-04 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-Assistant Manager (Project) Health &amp; Nutrition
-Bal Raksha Bharat (BRB)
-Location:
-Rajasthan
-Apply by:
-08 Mar 2026
-Regional Coordinator - North
-Intas Foundation
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Monitoring Coordinator
-Intas Foundation
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Individual Consultant – Technical support on Foun...
-UNICEF
-Location:
-Rajasthan
-Apply by:
-09 Mar 2026
-Multiple Vacancies
-AIDENT Social Welfare Organisation (ASWO)
-Location:
-Uttar Pradesh
-Apply by:
-16 Mar 2026
-Head of Accounts &amp; Finance
-Watershed Organization Trust (WOTR)
-Location:
-Maharashtra
-Apply by:
-01 Apr 2026
-Sr. Manager/Manager-Sustainable Cotton Programmes
-Aga Khan Rural Support Programme India (AKRSP Ind...
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Project Manager – Vocational and Skill Development
-White Lotus Trust
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G10" s="1" t="inlineStr">
-        <is>
-          <t>04-03-2026</t>
-        </is>
-      </c>
-      <c r="H10" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287610</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="inlineStr"/>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>ToR - State And National Level Consolidation Study On Government Schemes, ...</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Life Education And Development Support (Leads) And Ghoghardiha Prakhand Swarajya Vikas Sangh (GPSVS) | Jharkhand, Bihar
-International Development - ToR - State And National Level Consolidation Study On Government Schemes, Labour Rights &amp; Grievance Mechanisms - Safe Employment Guidebooks..., Life Ed ... Read More</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>• 3. Scope of Work
-The consultant/agency will adopt a policy-research and systems-analysis approach encompassing the following components:
-3.1 State &amp; National Policy Mapping
-Review relevant government schemes, labour laws, operational guidelines, and institutional mandates.
-Conduct comparative analysis of state and national policy frameworks affecting migrant and unorganised workers.
-Map implementation pathways, departmental roles, and convergence structures.
-3.2 Access Pathway &amp; Exclusion Analysis
-• Examine eligibility criteria, documentation requirements, approval timelines, and rejection points.
-Identify systemic barriers affecting migrant access to entitlements and services.
-Analyse exclusion patterns linked to migration vulnerability and livelihood insecurity.
-3.3 Review of Grievance Redressal Mechanisms
-Map complaint systems, escalation hierarchies, and response timelines at state and national levels.
-Assess field-level effectiveness, accessibility, and usability.
-Identify gaps between policy provisions and implementation realities.
-3.4 Development of Safe Employment Guidebook
-Consolidate state and national provisions into structured, user-friendly knowledge.
-Develop two comprehensive Safe Employment Guidebooks (Hindi &amp; English) covering:
-safe migration processes and precautions,
-labour rights, entitlements, and protections,
-access to government schemes and grievance systems,
-contextual chapters on Jharkhand and Bihar.
-3.5 Validation and Finalisation
-Present draft outputs to LEADS, GPSVS, and WHH for technical review.
-Incorporate feedback and revisions.
-Submit final research report and two complete Safe Employment Guidebooks.
-4. Expected Deliverables
-Inception report with methodology and detailed work plan
-State and national policy mapping document
-Draft analytical research report
-Draft Safe Employment Guidebooks (Hindi &amp; English)
-Final Safe Employment Guidebooks in Hindi and English including Jharkhand &amp; Bihar chapters
-Final validated research report.
-5. Duration and Level of Effort
-The assignment is expected to be completed within 10 weeks from contract signing, with clearly defined review milestones and iterative consultation with programme stakeholders.
-6. Profile of the Consultant / Agency
-Essential
-Demonstrated experience in policy research, migration, labour rights, or social protection.
-Similar assignments with NGOs, CSOs, research institutions, or development agencies.
-Strong analytical writing, documentation, and publication development capacity.
-Desirable
-Experience with EU or internationally funded development programmes.
-Familiarity with migration contexts in Bihar, Jharkhand, or eastern India.
-Ability to produce high-quality bilingual (Hindi &amp; English) knowledge resources.
-7. Application Process
-Interested applicants should submit:
-Technical Proposal
-Understanding of the assignment
-Proposed methodology, timeline, and work plan
-Team composition and relevant experience
-Samples of previous research or publication work
-Financial Proposal
-Detailed professional fee structure
-Applicable taxes clearly indicated
-Validity of quotation (minimum 60 days)
-• 8. Submission Details
-Submission Email:
-amangpsvs@gmail.com
-,
-manishleadsjh@gmail.com
-and
-aparna.lall@welthungerhilfe.de
-CC:
-leadsindiajh@gmail.com
-;
-gpsvsjp@gmail.com
-; and
-renita.rajora@welthungerhilfe.de
-Subject
-: Application – State &amp; National Consolidation Study (IND 1389)
-Locations
-: Jharkhand: Khunti, Simdega, Ramgarh, Bihar: Madhubani, Supaul, Darbhanga
-Deadline
-: 5th March 2026
-9. Budget
-The budget for this assignment is INR 5,00,000 (Rupees Five Lakh only) inclusive all taxes.
-• 10. Selection Process
-Proposals will be assessed through a technical and financial evaluation process conducted by the procurement committee.
-Shortlisted applicants may be invited for clarification or presentation prior to final selection. The decision of the committee shall be final and binding.
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-05 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-Assistant Manager (Project) Health &amp; Nutrition
-Bal Raksha Bharat (BRB)
-Location:
-Rajasthan
-Apply by:
-08 Mar 2026
-Regional Coordinator - North
-Intas Foundation
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Monitoring Coordinator
-Intas Foundation
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Individual Consultant – Technical support on Foun...
-UNICEF
-Location:
-Rajasthan
-Apply by:
-09 Mar 2026
-Multiple Vacancies
-AIDENT Social Welfare Organisation (ASWO)
-Location:
-Uttar Pradesh
-Apply by:
-16 Mar 2026
-Head of Accounts &amp; Finance
-Watershed Organization Trust (WOTR)
-Location:
-Maharashtra
-Apply by:
-01 Apr 2026
-Sr. Manager/Manager-Sustainable Cotton Programmes
-Aga Khan Rural Support Programme India (AKRSP Ind...
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Project Manager – Vocational and Skill Development
-White Lotus Trust
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>Governance, Learning</t>
-        </is>
-      </c>
-      <c r="G11" s="1" t="inlineStr">
-        <is>
-          <t>05-03-2026</t>
-        </is>
-      </c>
-      <c r="H11" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="I11" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287504</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="inlineStr"/>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>RFQ - for Report Designing</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>MAMTA Health Institute for Mother and Child (MAMTA) | India
-International Development - RFQ - for Report Designing, MAMTA Health Institute for Mother and Child (MAMTA), India - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jo ... Read More</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>• Scope of Work
-This is to bring to your kind attention that we want to hire an agency to design Report the total no. of pages in the report are 300 maximum (including cover page and back cover) and document size are A4. The topic of report would be on maternal health, environment, community health, etc.
-The Terms of Reference are as follows:
-Kindly provide the quotations for each of the above items separately, including GST by 5th March 2026.
-Kindly provide separate quotations for report design per page.
-Work must be completed in 2 months from the date of this order accepted by the vendor.
-MAMTA will pay the amounts to the vendor after verification application files by MAMTA and submission of the original invoice.
-The taxes will be deducted as per the relevant rules of the Govt. of India.
-Others
-MAMTA HIMC reserves the right to reject all or any quotation(s), wholly or partly, without assigning any reason whatsoever.
-MAMTA HIMC team reserves the right to request the top 3 quotations for an in-person discussion.
-MAMTA reserves the right, in its sole discretion, to conduct negotiations in accordance with MAMTA and/donor’s policies and procedures and to request additional information from prospective Bidders to supplement or clarify any aspect of the proposal documents if such revisions will be in the interest of our programs
-Only shortlisted agencies will be contacted.
-You must pay all sub-vendor payments before submitting the hard copy of the final bills and supporting documents to MAMTA HIMC.
-MAMTA shall not be legally bound by any award notice issued for this RFQ until an Agreement is duly signed and executed with the winning bidder(s).
-Further details will be shared with shortlisted agencies.
-Application Process –
-All applicants (company/agency/institutional/individual) if applicable, should follow the Government of India guidelines/policy for the Prevention of Sexual Harassment (PoSH) at the workplace. As part of the application process, you are required to share the status of the Internal Complaints Committee (ICC). If the committee is not incorporated, then under what criteria is it not enacted?
-Interested agencies/organizations/individuals must submit the proposal for the
-report designing
-highlighting the process, portfolio of past work, financial proposal and the timeline for the project. The technical and financial quotations should be sent in soft copy over email at
-rfp@mamtahimc.in
-by
-5
-th
-March 2026 With the subject line: “Quotation for Report Designing”.
-• The quotations should be made separately for the event and states. We encourage local vendors to apply. Incomplete applications and applications received after the deadline will not be considered for the selection process.
-The selection team will only contact applicants who have been shortlisted for the process.
-• Mamta HIMC has a policy of erasing all confidential information, ideas/concepts submitted in proposals/applications after the selection process is completed.
-"Confidentiality of Applicants"
-Mamta shall not be liable to share the list of shortlisted applicants with any party outside the organization. The organization takes all necessary measures to protect the confidentiality of applicants, and shall not disclose any personal information, process, and data related to the application, except as required by law.
-• Job Email ID:
-rfp(at)mamtahimc.in
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-05 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-Assistant Manager (Project) Health &amp; Nutrition
-Bal Raksha Bharat (BRB)
-Location:
-Rajasthan
-Apply by:
-08 Mar 2026
-Regional Coordinator - North
-Intas Foundation
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Monitoring Coordinator
-Intas Foundation
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Individual Consultant – Technical support on Foun...
-UNICEF
-Location:
-Rajasthan
-Apply by:
-09 Mar 2026
-Multiple Vacancies
-AIDENT Social Welfare Organisation (ASWO)
-Location:
-Uttar Pradesh
-Apply by:
-16 Mar 2026
-Head of Accounts &amp; Finance
-Watershed Organization Trust (WOTR)
-Location:
-Maharashtra
-Apply by:
-01 Apr 2026
-Sr. Manager/Manager-Sustainable Cotton Programmes
-Aga Khan Rural Support Programme India (AKRSP Ind...
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Project Manager – Vocational and Skill Development
-White Lotus Trust
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="G12" s="1" t="inlineStr">
-        <is>
-          <t>05-03-2026</t>
-        </is>
-      </c>
-      <c r="H12" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="I12" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287643</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="inlineStr"/>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr"/>
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>RFP - Training of Volunteers &amp; Help Desk Operators</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Ghoghardiha Prakhand Swarajya Vikas Sangh (GPSVS) | Bihar, Jharkhand
 International Development - RFP - Training of Volunteers &amp; Help Desk Operators, Ghoghardiha Prakhand Swarajya Vikas Sangh (GPSVS), Bihar, Jharkhand - DevNetJobsIndia.org
@@ -3105,7 +1876,7 @@
 Broadcast ... Read More</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>• 3. Scope of Work
 The selected agency/consultant will undertake the following:
@@ -3323,54 +2094,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Project) Health &amp; Nutrition
-Bal Raksha Bharat (BRB)
-Location:
-Rajasthan
+RFP - Requirement of Agency for Creating High Qua...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Delhi
+Apply by:
+20 Mar 2026
+Programme officers (Education &amp; Life Skills Educa...
+Butterflies NGO
+Location:
+Delhi
+Apply by:
+15 Mar 2026
+RFQ: Construction of New gated check dams, De-sil...
+WaterAid India
+Location:
+Telangana
 Apply by:
 08 Mar 2026
-Regional Coordinator - North
-Intas Foundation
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Monitoring Coordinator
-Intas Foundation
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Individual Consultant – Technical support on Foun...
-UNICEF
-Location:
-Rajasthan
-Apply by:
-09 Mar 2026
-Multiple Vacancies
-AIDENT Social Welfare Organisation (ASWO)
-Location:
-Uttar Pradesh
-Apply by:
-16 Mar 2026
-Head of Accounts &amp; Finance
-Watershed Organization Trust (WOTR)
+Regional Coordinator
+Bharat Rural Livelihoods Foundation (BRLF)
 Location:
 Maharashtra
 Apply by:
-01 Apr 2026
-Sr. Manager/Manager-Sustainable Cotton Programmes
-Aga Khan Rural Support Programme India (AKRSP Ind...
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Project Manager – Vocational and Skill Development
-White Lotus Trust
-Location:
-Delhi
-Apply by:
-01 Apr 2026
+18 Mar 2026
+Project Nurse 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Project Technical Support 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Block Academic Coordinator
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
+District Program Manager
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
 Jobseekers
 Register
 Login
@@ -3398,66 +2169,64 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F13" s="1" t="inlineStr">
+      <c r="F8" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G13" s="1" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>05-03-2026</t>
         </is>
       </c>
-      <c r="H13" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="I13" s="1" t="inlineStr">
+      <c r="H8" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287444</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr"/>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>RFP- #2026-IN-01- Agency for economic Impact Analysis</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>PATH | Delhi
-International Development - RFP- #2026-IN-01- Agency for economic Impact Analysis, PATH, Delhi - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Login
-|
-Register
-Jobseekers Login
-Jobseekers Register
-Job ... Read More</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>• Job Email ID:
-rfpindia(at)path.org
+      <c r="B9" s="1" t="inlineStr"/>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>RFP - Hiring an Agency to Conduct Evidence Synthesis, Co-Design Key Interv...</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Project Concern International India (PCI India) | India
+International Development - RFP - Hiring an Agency to Conduct Evidence Synthesis, Co-Design Key Intervention Components, and Develop a Scalable and Operational Implementation, Project Concern International India (PCI India), India - DevNetJobs ... Read More</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>• Last   Date for Submission of bids
+05
+th
+March 2026
+Proposals   to be submitted at
+procdelhi@pciglobal.in
+Receipt of Proposals
+Technical and Financial   proposals should be submitted as separate attachments
+and to be submitted
+in a single email
+attachments.
+NOTE
+:
+(a) The agencies registered under the Societies/Trust/Foreign Contribution (Regulation) Act, 2010, are not required to submit applications. Proposals from these agencies will not be considered.
+For detailed information, please check the complete version of the RFP attached below.
+• Job Email ID:
+procdelhi(at)pciglobal.in
 Download Attachment:
-Request for Proposal - RFP#2026-IN-01- Agency for economic Impact Analysis.doc
+RFP-AGENCY TO CONDUCT EVIDENCE SYNTHESIS, CO-DESIGN KEY INTERVENTION ..........doc
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
@@ -3524,54 +2293,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Project) Health &amp; Nutrition
-Bal Raksha Bharat (BRB)
-Location:
-Rajasthan
+RFP - Requirement of Agency for Creating High Qua...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Delhi
+Apply by:
+20 Mar 2026
+Programme officers (Education &amp; Life Skills Educa...
+Butterflies NGO
+Location:
+Delhi
+Apply by:
+15 Mar 2026
+RFQ: Construction of New gated check dams, De-sil...
+WaterAid India
+Location:
+Telangana
 Apply by:
 08 Mar 2026
-Regional Coordinator - North
-Intas Foundation
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Monitoring Coordinator
-Intas Foundation
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Individual Consultant – Technical support on Foun...
-UNICEF
-Location:
-Rajasthan
-Apply by:
-09 Mar 2026
-Multiple Vacancies
-AIDENT Social Welfare Organisation (ASWO)
-Location:
-Uttar Pradesh
-Apply by:
-16 Mar 2026
-Head of Accounts &amp; Finance
-Watershed Organization Trust (WOTR)
+Regional Coordinator
+Bharat Rural Livelihoods Foundation (BRLF)
 Location:
 Maharashtra
 Apply by:
-01 Apr 2026
-Sr. Manager/Manager-Sustainable Cotton Programmes
-Aga Khan Rural Support Programme India (AKRSP Ind...
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Project Manager – Vocational and Skill Development
-White Lotus Trust
-Location:
-Delhi
-Apply by:
-01 Apr 2026
+18 Mar 2026
+Project Nurse 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Project Technical Support 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Block Academic Coordinator
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
+District Program Manager
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
 Jobseekers
 Register
 Login
@@ -3599,38 +2368,750 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F14" s="1" t="inlineStr">
-        <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G14" s="1" t="inlineStr">
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>05-03-2026</t>
         </is>
       </c>
-      <c r="H14" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="I14" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287460</t>
+      <c r="H9" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287312</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr"/>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="B10" s="1" t="inlineStr"/>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>RFQ - for the Supply of Seeds</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>MAMTA Health Institute for Mother and Child (MAMTA) | India
+International Development - RFQ -  for the Supply of Seeds, MAMTA Health Institute for Mother and Child (MAMTA), India - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Event ... Read More</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>• The terms and conditions for the purchase of seed:
+Provide seed percentage certificate of all Germination
+The seed must be supplied within 20 days from the date of order placement. Prices should be inclusive of GST and transportation charges.
+Seeds must be resistant to downy and powdery mildew.
+In case seeds fafulfillfulfil the supplier of the above-prescribed standard must guarantee the replacement of seeds.
+Genetic purity should not be less than 90%
+Germination (minimum): 85%
+Inert matter (maximum): 3%
+Weed seed (max.) = 20 no./kg
+Other crops seed (max.) = 20 no./ kg
+Packed: within 6 months
+Validity: at least 12 months
+Tax deductions will be done as per the relevant rules of the Government of India.
+Share the quotation on letterhead
+inclusive of GST (Otherwise the quotation will not be considered).
+Others
+MAMTA HIMC reserves the right to reject all or any quotation(s), wholly or partly, without assigning any reason whatsoever.
+MAMTA HIMC team reserves the right to request the top 3 quotations for an in-person discussion.
+MAMTA reserves the right, in its sole discretion, to conduct negotiations in accordance with MAMTA and/donor’s policies and procedures and to request additional information from prospective Bidders to supplement or clarify any aspect of the proposal documents if such revisions will be in the interest of our programs
+Only shortlisted agencies will be contacted.
+You must pay all sub-vendor payments before submitting the hard copy of the final bills and supporting documents to MAMTA HIMC.
+MAMTA shall not be legally bound by any award notice issued for this RFQ until an Agreement is duly signed and executed with the winning bidder(s).
+Further details will be shared with shortlisted agencies.
+Application Process –
+All applicants (company/agency/institutional) if applicable, should follow the Government of India guidelines/policy for the Prevention of Sexual Harassment (PoSH) at the workplace. As part of the application process, you are required to share the status of the Internal Complaints Committee (ICC). If the committee is not incorporated, then under what criteria is it not enacted?
+Interested agencies/organizations/individuals must submit the proposal for the
+Seeds
+highlighting the process, portfolio of past work, financial proposal and the timeline for the project. The technical and financial quotations should be sent in soft copy over email at
+rfp@mamtahimc.in
+by
+5
+th
+March 2026 With the subject line: “Quotation for Supply of Certified Seasonal Vegetable Seeds”. The
+• quotations should be made separately for the event and states. We encourage local vendors to apply. Incomplete applications and applications received after the deadline will not be considered for the selection process.
+The selection team will only contact applicants who have been shortlisted for the process.
+• Mamta HIMC has a policy of erasing all confidential information, ideas/concepts submitted in proposals/applications after the selection process is completed.
+"Confidentiality of Applicants"
+Mamta shall not be liable to share the list of shortlisted applicants with any party outside the organization. The organization takes all necessary measures to protect the confidentiality of applicants, and shall not disclose any personal information, process, and data related to the application, except as required by law.
+• Job Email ID:
+rfp(at)mamtahimc.in
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+05 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Associate (Programme Management)
+Indian Institute For Human Settlements (Iihs)
+Location:
+Karnataka
+Apply by:
+07 Mar 2026
+Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+RFP - Requirement of Agency for Creating High Qua...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Delhi
+Apply by:
+20 Mar 2026
+Programme officers (Education &amp; Life Skills Educa...
+Butterflies NGO
+Location:
+Delhi
+Apply by:
+15 Mar 2026
+RFQ: Construction of New gated check dams, De-sil...
+WaterAid India
+Location:
+Telangana
+Apply by:
+08 Mar 2026
+Regional Coordinator
+Bharat Rural Livelihoods Foundation (BRLF)
+Location:
+Maharashtra
+Apply by:
+18 Mar 2026
+Project Nurse 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Project Technical Support 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Block Academic Coordinator
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
+District Program Manager
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>05-03-2026</t>
+        </is>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287641</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr"/>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>RFQ - for Report Designing</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>MAMTA Health Institute for Mother and Child (MAMTA) | India
+International Development - RFQ - for Report Designing, MAMTA Health Institute for Mother and Child (MAMTA), India - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jo ... Read More</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>• Scope of Work
+This is to bring to your kind attention that we want to hire an agency to design Report the total no. of pages in the report are 300 maximum (including cover page and back cover) and document size are A4. The topic of report would be on maternal health, environment, community health, etc.
+The Terms of Reference are as follows:
+Kindly provide the quotations for each of the above items separately, including GST by 5th March 2026.
+Kindly provide separate quotations for report design per page.
+Work must be completed in 2 months from the date of this order accepted by the vendor.
+MAMTA will pay the amounts to the vendor after verification application files by MAMTA and submission of the original invoice.
+The taxes will be deducted as per the relevant rules of the Govt. of India.
+Others
+MAMTA HIMC reserves the right to reject all or any quotation(s), wholly or partly, without assigning any reason whatsoever.
+MAMTA HIMC team reserves the right to request the top 3 quotations for an in-person discussion.
+MAMTA reserves the right, in its sole discretion, to conduct negotiations in accordance with MAMTA and/donor’s policies and procedures and to request additional information from prospective Bidders to supplement or clarify any aspect of the proposal documents if such revisions will be in the interest of our programs
+Only shortlisted agencies will be contacted.
+You must pay all sub-vendor payments before submitting the hard copy of the final bills and supporting documents to MAMTA HIMC.
+MAMTA shall not be legally bound by any award notice issued for this RFQ until an Agreement is duly signed and executed with the winning bidder(s).
+Further details will be shared with shortlisted agencies.
+Application Process –
+All applicants (company/agency/institutional/individual) if applicable, should follow the Government of India guidelines/policy for the Prevention of Sexual Harassment (PoSH) at the workplace. As part of the application process, you are required to share the status of the Internal Complaints Committee (ICC). If the committee is not incorporated, then under what criteria is it not enacted?
+Interested agencies/organizations/individuals must submit the proposal for the
+report designing
+highlighting the process, portfolio of past work, financial proposal and the timeline for the project. The technical and financial quotations should be sent in soft copy over email at
+rfp@mamtahimc.in
+by
+5
+th
+March 2026 With the subject line: “Quotation for Report Designing”.
+• The quotations should be made separately for the event and states. We encourage local vendors to apply. Incomplete applications and applications received after the deadline will not be considered for the selection process.
+The selection team will only contact applicants who have been shortlisted for the process.
+• Mamta HIMC has a policy of erasing all confidential information, ideas/concepts submitted in proposals/applications after the selection process is completed.
+"Confidentiality of Applicants"
+Mamta shall not be liable to share the list of shortlisted applicants with any party outside the organization. The organization takes all necessary measures to protect the confidentiality of applicants, and shall not disclose any personal information, process, and data related to the application, except as required by law.
+• Job Email ID:
+rfp(at)mamtahimc.in
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+05 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Associate (Programme Management)
+Indian Institute For Human Settlements (Iihs)
+Location:
+Karnataka
+Apply by:
+07 Mar 2026
+Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+RFP - Requirement of Agency for Creating High Qua...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Delhi
+Apply by:
+20 Mar 2026
+Programme officers (Education &amp; Life Skills Educa...
+Butterflies NGO
+Location:
+Delhi
+Apply by:
+15 Mar 2026
+RFQ: Construction of New gated check dams, De-sil...
+WaterAid India
+Location:
+Telangana
+Apply by:
+08 Mar 2026
+Regional Coordinator
+Bharat Rural Livelihoods Foundation (BRLF)
+Location:
+Maharashtra
+Apply by:
+18 Mar 2026
+Project Nurse 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Project Technical Support 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Block Academic Coordinator
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
+District Program Manager
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t>05-03-2026</t>
+        </is>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287643</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr"/>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>ToR - State And National Level Consolidation Study On Government Schemes, ...</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Life Education And Development Support (Leads) And Ghoghardiha Prakhand Swarajya Vikas Sangh (GPSVS) | Jharkhand, Bihar
+International Development - ToR - State And National Level Consolidation Study On Government Schemes, Labour Rights &amp; Grievance Mechanisms - Safe Employment Guidebooks..., Life Ed ... Read More</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>• 3. Scope of Work
+The consultant/agency will adopt a policy-research and systems-analysis approach encompassing the following components:
+3.1 State &amp; National Policy Mapping
+Review relevant government schemes, labour laws, operational guidelines, and institutional mandates.
+Conduct comparative analysis of state and national policy frameworks affecting migrant and unorganised workers.
+Map implementation pathways, departmental roles, and convergence structures.
+3.2 Access Pathway &amp; Exclusion Analysis
+• Examine eligibility criteria, documentation requirements, approval timelines, and rejection points.
+Identify systemic barriers affecting migrant access to entitlements and services.
+Analyse exclusion patterns linked to migration vulnerability and livelihood insecurity.
+3.3 Review of Grievance Redressal Mechanisms
+Map complaint systems, escalation hierarchies, and response timelines at state and national levels.
+Assess field-level effectiveness, accessibility, and usability.
+Identify gaps between policy provisions and implementation realities.
+3.4 Development of Safe Employment Guidebook
+Consolidate state and national provisions into structured, user-friendly knowledge.
+Develop two comprehensive Safe Employment Guidebooks (Hindi &amp; English) covering:
+safe migration processes and precautions,
+labour rights, entitlements, and protections,
+access to government schemes and grievance systems,
+contextual chapters on Jharkhand and Bihar.
+3.5 Validation and Finalisation
+Present draft outputs to LEADS, GPSVS, and WHH for technical review.
+Incorporate feedback and revisions.
+Submit final research report and two complete Safe Employment Guidebooks.
+4. Expected Deliverables
+Inception report with methodology and detailed work plan
+State and national policy mapping document
+Draft analytical research report
+Draft Safe Employment Guidebooks (Hindi &amp; English)
+Final Safe Employment Guidebooks in Hindi and English including Jharkhand &amp; Bihar chapters
+Final validated research report.
+5. Duration and Level of Effort
+The assignment is expected to be completed within 10 weeks from contract signing, with clearly defined review milestones and iterative consultation with programme stakeholders.
+6. Profile of the Consultant / Agency
+Essential
+Demonstrated experience in policy research, migration, labour rights, or social protection.
+Similar assignments with NGOs, CSOs, research institutions, or development agencies.
+Strong analytical writing, documentation, and publication development capacity.
+Desirable
+Experience with EU or internationally funded development programmes.
+Familiarity with migration contexts in Bihar, Jharkhand, or eastern India.
+Ability to produce high-quality bilingual (Hindi &amp; English) knowledge resources.
+7. Application Process
+Interested applicants should submit:
+Technical Proposal
+Understanding of the assignment
+Proposed methodology, timeline, and work plan
+Team composition and relevant experience
+Samples of previous research or publication work
+Financial Proposal
+Detailed professional fee structure
+Applicable taxes clearly indicated
+Validity of quotation (minimum 60 days)
+• 8. Submission Details
+Submission Email:
+amangpsvs@gmail.com
+,
+manishleadsjh@gmail.com
+and
+aparna.lall@welthungerhilfe.de
+CC:
+leadsindiajh@gmail.com
+;
+gpsvsjp@gmail.com
+; and
+renita.rajora@welthungerhilfe.de
+Subject
+: Application – State &amp; National Consolidation Study (IND 1389)
+Locations
+: Jharkhand: Khunti, Simdega, Ramgarh, Bihar: Madhubani, Supaul, Darbhanga
+Deadline
+: 5th March 2026
+9. Budget
+The budget for this assignment is INR 5,00,000 (Rupees Five Lakh only) inclusive all taxes.
+• 10. Selection Process
+Proposals will be assessed through a technical and financial evaluation process conducted by the procurement committee.
+Shortlisted applicants may be invited for clarification or presentation prior to final selection. The decision of the committee shall be final and binding.
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+05 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Associate (Programme Management)
+Indian Institute For Human Settlements (Iihs)
+Location:
+Karnataka
+Apply by:
+07 Mar 2026
+Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+RFP - Requirement of Agency for Creating High Qua...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Delhi
+Apply by:
+20 Mar 2026
+Programme officers (Education &amp; Life Skills Educa...
+Butterflies NGO
+Location:
+Delhi
+Apply by:
+15 Mar 2026
+RFQ: Construction of New gated check dams, De-sil...
+WaterAid India
+Location:
+Telangana
+Apply by:
+08 Mar 2026
+Regional Coordinator
+Bharat Rural Livelihoods Foundation (BRLF)
+Location:
+Maharashtra
+Apply by:
+18 Mar 2026
+Project Nurse 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Project Technical Support 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Block Academic Coordinator
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
+District Program Manager
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>Governance, Learning</t>
+        </is>
+      </c>
+      <c r="G12" s="1" t="inlineStr">
+        <is>
+          <t>05-03-2026</t>
+        </is>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287504</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr"/>
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>Request for Quotation for Case Study</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Institute for Global Development (IGD) | Uttar Pradesh, Andhra Pradesh, Telangana, Karnataka
 International Development - Request for Quotation for Case Study, Institute for Global Development (IGD), Andhra Pradesh, Telangana, Karnataka - DevNetJobsIndia.org
@@ -3642,7 +3123,7 @@
 Value M ... Read More</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>• Scope of Work
 IGD invites quotations from qualified individuals or agencies to develop case studies documenting key program activities. The case studies will be developed focusing on some campaign components
@@ -3763,54 +3244,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Project) Health &amp; Nutrition
-Bal Raksha Bharat (BRB)
-Location:
-Rajasthan
+RFP - Requirement of Agency for Creating High Qua...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Delhi
+Apply by:
+20 Mar 2026
+Programme officers (Education &amp; Life Skills Educa...
+Butterflies NGO
+Location:
+Delhi
+Apply by:
+15 Mar 2026
+RFQ: Construction of New gated check dams, De-sil...
+WaterAid India
+Location:
+Telangana
 Apply by:
 08 Mar 2026
-Regional Coordinator - North
-Intas Foundation
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Monitoring Coordinator
-Intas Foundation
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Individual Consultant – Technical support on Foun...
-UNICEF
-Location:
-Rajasthan
-Apply by:
-09 Mar 2026
-Multiple Vacancies
-AIDENT Social Welfare Organisation (ASWO)
-Location:
-Uttar Pradesh
-Apply by:
-16 Mar 2026
-Head of Accounts &amp; Finance
-Watershed Organization Trust (WOTR)
+Regional Coordinator
+Bharat Rural Livelihoods Foundation (BRLF)
 Location:
 Maharashtra
 Apply by:
-01 Apr 2026
-Sr. Manager/Manager-Sustainable Cotton Programmes
-Aga Khan Rural Support Programme India (AKRSP Ind...
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Project Manager – Vocational and Skill Development
-White Lotus Trust
-Location:
-Delhi
-Apply by:
-01 Apr 2026
+18 Mar 2026
+Project Nurse 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Project Technical Support 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Block Academic Coordinator
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
+District Program Manager
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
 Jobseekers
 Register
 Login
@@ -3838,100 +3319,112 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F15" s="1" t="inlineStr">
+      <c r="F13" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G15" s="1" t="inlineStr">
+      <c r="G13" s="1" t="inlineStr">
         <is>
           <t>05-03-2026</t>
         </is>
       </c>
-      <c r="H15" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="I15" s="1" t="inlineStr">
+      <c r="H13" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287670</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr"/>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>RFQ - for the Supply of Seeds</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>MAMTA Health Institute for Mother and Child (MAMTA) | India
-International Development - RFQ -  for the Supply of Seeds, MAMTA Health Institute for Mother and Child (MAMTA), India - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Event ... Read More</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>• The terms and conditions for the purchase of seed:
-Provide seed percentage certificate of all Germination
-The seed must be supplied within 20 days from the date of order placement. Prices should be inclusive of GST and transportation charges.
-Seeds must be resistant to downy and powdery mildew.
-In case seeds fafulfillfulfil the supplier of the above-prescribed standard must guarantee the replacement of seeds.
-Genetic purity should not be less than 90%
-Germination (minimum): 85%
-Inert matter (maximum): 3%
-Weed seed (max.) = 20 no./kg
-Other crops seed (max.) = 20 no./ kg
-Packed: within 6 months
-Validity: at least 12 months
-Tax deductions will be done as per the relevant rules of the Government of India.
-Share the quotation on letterhead
-inclusive of GST (Otherwise the quotation will not be considered).
-Others
-MAMTA HIMC reserves the right to reject all or any quotation(s), wholly or partly, without assigning any reason whatsoever.
-MAMTA HIMC team reserves the right to request the top 3 quotations for an in-person discussion.
-MAMTA reserves the right, in its sole discretion, to conduct negotiations in accordance with MAMTA and/donor’s policies and procedures and to request additional information from prospective Bidders to supplement or clarify any aspect of the proposal documents if such revisions will be in the interest of our programs
-Only shortlisted agencies will be contacted.
-You must pay all sub-vendor payments before submitting the hard copy of the final bills and supporting documents to MAMTA HIMC.
-MAMTA shall not be legally bound by any award notice issued for this RFQ until an Agreement is duly signed and executed with the winning bidder(s).
-Further details will be shared with shortlisted agencies.
-Application Process –
-All applicants (company/agency/institutional) if applicable, should follow the Government of India guidelines/policy for the Prevention of Sexual Harassment (PoSH) at the workplace. As part of the application process, you are required to share the status of the Internal Complaints Committee (ICC). If the committee is not incorporated, then under what criteria is it not enacted?
-Interested agencies/organizations/individuals must submit the proposal for the
-Seeds
-highlighting the process, portfolio of past work, financial proposal and the timeline for the project. The technical and financial quotations should be sent in soft copy over email at
-rfp@mamtahimc.in
-by
-5
-th
-March 2026 With the subject line: “Quotation for Supply of Certified Seasonal Vegetable Seeds”. The
-• quotations should be made separately for the event and states. We encourage local vendors to apply. Incomplete applications and applications received after the deadline will not be considered for the selection process.
-The selection team will only contact applicants who have been shortlisted for the process.
-• Mamta HIMC has a policy of erasing all confidential information, ideas/concepts submitted in proposals/applications after the selection process is completed.
-"Confidentiality of Applicants"
-Mamta shall not be liable to share the list of shortlisted applicants with any party outside the organization. The organization takes all necessary measures to protect the confidentiality of applicants, and shall not disclose any personal information, process, and data related to the application, except as required by law.
-• Job Email ID:
-rfp(at)mamtahimc.in
+      <c r="B14" s="1" t="inlineStr"/>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>EoI - For Empanelment of agencies for Impact Assessment/ Evaluation Servic...</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Small Industries Development Bank of India (SIDBI) | India
+International Development - EoI - For Empanelment of agencies for Impact Assessment/ Evaluation Services under Programmes for Development and Impact, Small Industries Development Bank of India (SIDBI), India - DevNetJobsIndia.org
+Jobseekers ... Read More</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>• Please      note that all the information required as per the documents required for      responding to EOI needs to be provided. Incomplete information in these      areas may lead to non-selection.
+Modification      And/ Or Withdrawal of documents:
+Documents once submitted will      be treated as final and no further correspondence will be entertained. No      document shall be modified after the deadline for submission of documents      in response to the EOI. Also, no Respondent shall be allowed to withdraw      any document, if the Respondent happens to be a successful      Respondent.
+SIDBI      has the right to reject any or all documents received without assigning      any reason whatsoever.
+NOTE:
+SIDBI SHALL NOT BE RESPONSIBLE FOR NON-RECEIPT / NON-DELIVERY OF THE DOCUMENTS DUE TO ANY REASON, WHATSOEVER.
+Critical Information
+Events
+Particular / Date and Time
+Tender No
+SIDBI/REOI/68279
+Tender Issue Date
+13/02/2026
+Last date for seeking Clarification on EOI document
+20/02/2026
+All queries relating to the EoI must be in writing only   and to be sent via
+email on.
+pdi@sidbi.in
+and
+mayankp@sidbi.in
+Pre EOI meeting
+25/02/2026
+The meeting shall be virtual / online over MS Teams Call.   Meeting Link will be shared separately to all the bidder
+Last date for submission of EoI
+06/03/2026
+Bids to submitted through email only at:
+pdi@sidbi.in
+and
+mayankp@sidbi.in
+Independent External Monitor
+Shri Sanjay Kumar Srivastava, IAS (Retd.),
+Apartment T-6 B,
+Windsor Court, DLF Phase-IV
+Gurgaon-122009
+Mobile No-9910059472
+E-mail:
+sksrivastava7854@rediffmail.com
+Dr. Parvez Hayat, IPS (Retd.),
+B-4/69- A, Safdarjung Enclave
+New Delhi-110029
+Mobile-9810134469
+E-Mail:
+phayatips@gmail.com
+• Contact details of SIDBI officials
+Shri Mohammed Adil Ahsan
+Asst. General Manager,
+Programmes for Development &amp; Impact [PDI]
+SIDBI Tower, 15, Ashok Marg, Lucknow – 226001
+Ph: 0522-4261631
+Email:
+mdadil@sidbi.in
+Shri Mayank Prakash
+Theme Leader – Monitoring &amp; Evaluation
+Programmes for Development &amp; Impact [PDI]
+SIDBI Tower, 15, Ashok Marg, Lucknow – 226001
+Ph: 0522 - 4259 626
+Email
+mayankp@sidbi.in
+For detailed information, please check the complete version of the EoI attached below.
+Download Attachment:
+EOI for empanelment of Imapact assesment agencies_1202026.pdf
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
 Apply by:
-05 Mar 2026
+06 Mar 2026
 Access all the jobs and get ahead!
 Subscribe to Value Membership Now!
 Subscribe
@@ -3993,54 +3486,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Project) Health &amp; Nutrition
-Bal Raksha Bharat (BRB)
-Location:
-Rajasthan
+RFP - Requirement of Agency for Creating High Qua...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Delhi
+Apply by:
+20 Mar 2026
+Programme officers (Education &amp; Life Skills Educa...
+Butterflies NGO
+Location:
+Delhi
+Apply by:
+15 Mar 2026
+RFQ: Construction of New gated check dams, De-sil...
+WaterAid India
+Location:
+Telangana
 Apply by:
 08 Mar 2026
-Regional Coordinator - North
-Intas Foundation
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Monitoring Coordinator
-Intas Foundation
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Individual Consultant – Technical support on Foun...
-UNICEF
-Location:
-Rajasthan
-Apply by:
-09 Mar 2026
-Multiple Vacancies
-AIDENT Social Welfare Organisation (ASWO)
-Location:
-Uttar Pradesh
-Apply by:
-16 Mar 2026
-Head of Accounts &amp; Finance
-Watershed Organization Trust (WOTR)
+Regional Coordinator
+Bharat Rural Livelihoods Foundation (BRLF)
 Location:
 Maharashtra
 Apply by:
-01 Apr 2026
-Sr. Manager/Manager-Sustainable Cotton Programmes
-Aga Khan Rural Support Programme India (AKRSP Ind...
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Project Manager – Vocational and Skill Development
-White Lotus Trust
-Location:
-Delhi
-Apply by:
-01 Apr 2026
+18 Mar 2026
+Project Nurse 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Project Technical Support 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Block Academic Coordinator
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
+District Program Manager
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
 Jobseekers
 Register
 Login
@@ -4068,69 +3561,71 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="G16" s="1" t="inlineStr">
-        <is>
-          <t>05-03-2026</t>
-        </is>
-      </c>
-      <c r="H16" s="1" t="n">
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t>Governance, Learning</t>
+        </is>
+      </c>
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t>06-03-2026</t>
+        </is>
+      </c>
+      <c r="H14" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I16" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287641</t>
+      <c r="I14" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287084</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr"/>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Hiring an Agency to Conduct Evidence Synthesis, Co-Design Key Interv...</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Project Concern International India (PCI India) | India
-International Development - RFP - Hiring an Agency to Conduct Evidence Synthesis, Co-Design Key Intervention Components, and Develop a Scalable and Operational Implementation, Project Concern International India (PCI India), India - DevNetJobs ... Read More</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>• Last   Date for Submission of bids
-05
-th
-March 2026
-Proposals   to be submitted at
-procdelhi@pciglobal.in
-Receipt of Proposals
-Technical and Financial   proposals should be submitted as separate attachments
-and to be submitted
-in a single email
-attachments.
-NOTE
-:
-(a) The agencies registered under the Societies/Trust/Foreign Contribution (Regulation) Act, 2010, are not required to submit applications. Proposals from these agencies will not be considered.
-For detailed information, please check the complete version of the RFP attached below.
-• Job Email ID:
-procdelhi(at)pciglobal.in
+      <c r="B15" s="1" t="inlineStr"/>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>RFP- #2026-IN-01- Agency for economic Impact Analysis</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>PATH | Delhi
+International Development - RFP- #2026-IN-01- Agency for economic Impact Analysis, PATH, Delhi - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers:
+Login
+|
+Register
+Jobseekers Login
+Jobseekers Register
+Job ... Read More</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>• Job Email ID:
+rfpindia(at)path.org
 Download Attachment:
-RFP-AGENCY TO CONDUCT EVIDENCE SYNTHESIS, CO-DESIGN KEY INTERVENTION ..........doc
+Request for Proposal - RFP#2026-IN-01- Agency for economic Impact Analysis.doc
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
 Apply by:
-05 Mar 2026
+07 Mar 2026
 Access all the jobs and get ahead!
 Subscribe to Value Membership Now!
 Subscribe
@@ -4192,54 +3687,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Project) Health &amp; Nutrition
-Bal Raksha Bharat (BRB)
-Location:
-Rajasthan
+RFP - Requirement of Agency for Creating High Qua...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Delhi
+Apply by:
+20 Mar 2026
+Programme officers (Education &amp; Life Skills Educa...
+Butterflies NGO
+Location:
+Delhi
+Apply by:
+15 Mar 2026
+RFQ: Construction of New gated check dams, De-sil...
+WaterAid India
+Location:
+Telangana
 Apply by:
 08 Mar 2026
-Regional Coordinator - North
-Intas Foundation
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Monitoring Coordinator
-Intas Foundation
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Individual Consultant – Technical support on Foun...
-UNICEF
-Location:
-Rajasthan
-Apply by:
-09 Mar 2026
-Multiple Vacancies
-AIDENT Social Welfare Organisation (ASWO)
-Location:
-Uttar Pradesh
-Apply by:
-16 Mar 2026
-Head of Accounts &amp; Finance
-Watershed Organization Trust (WOTR)
+Regional Coordinator
+Bharat Rural Livelihoods Foundation (BRLF)
 Location:
 Maharashtra
 Apply by:
-01 Apr 2026
-Sr. Manager/Manager-Sustainable Cotton Programmes
-Aga Khan Rural Support Programme India (AKRSP Ind...
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Project Manager – Vocational and Skill Development
-White Lotus Trust
-Location:
-Delhi
-Apply by:
-01 Apr 2026
+18 Mar 2026
+Project Nurse 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Project Technical Support 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Block Academic Coordinator
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
+District Program Manager
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
 Jobseekers
 Register
 Login
@@ -4267,38 +3762,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="G17" s="1" t="inlineStr">
-        <is>
-          <t>05-03-2026</t>
-        </is>
-      </c>
-      <c r="H17" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="I17" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287312</t>
+      <c r="F15" s="1" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G15" s="1" t="inlineStr">
+        <is>
+          <t>07-03-2026</t>
+        </is>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I15" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287460</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B18" s="1" t="inlineStr"/>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="B16" s="1" t="inlineStr"/>
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>RFP - Onboarding Agency for Revamping Assam LMIS Dashboard</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>PATH | Assam
 International Development - RFP - Onboarding Agency for Revamping Assam LMIS Dashboard, PATH, Assam - DevNetJobsIndia.org
@@ -4320,7 +3815,7 @@
 Jobseekers Registe ... Read More</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>• 3.2. Commercial contracting terms and conditions will be negotiated with the successful supplier at the end of the selection process.
 3.3. By submitting a proposal, the supplier confirms their agreement to abide by the RFP terms and PATH policies, including the
@@ -4407,7 +3902,7 @@
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
 Apply by:
-06 Mar 2026
+07 Mar 2026
 Access all the jobs and get ahead!
 Subscribe to Value Membership Now!
 Subscribe
@@ -4469,54 +3964,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Project) Health &amp; Nutrition
-Bal Raksha Bharat (BRB)
-Location:
-Rajasthan
+RFP - Requirement of Agency for Creating High Qua...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Delhi
+Apply by:
+20 Mar 2026
+Programme officers (Education &amp; Life Skills Educa...
+Butterflies NGO
+Location:
+Delhi
+Apply by:
+15 Mar 2026
+RFQ: Construction of New gated check dams, De-sil...
+WaterAid India
+Location:
+Telangana
 Apply by:
 08 Mar 2026
-Regional Coordinator - North
-Intas Foundation
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Monitoring Coordinator
-Intas Foundation
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Individual Consultant – Technical support on Foun...
-UNICEF
-Location:
-Rajasthan
-Apply by:
-09 Mar 2026
-Multiple Vacancies
-AIDENT Social Welfare Organisation (ASWO)
-Location:
-Uttar Pradesh
-Apply by:
-16 Mar 2026
-Head of Accounts &amp; Finance
-Watershed Organization Trust (WOTR)
+Regional Coordinator
+Bharat Rural Livelihoods Foundation (BRLF)
 Location:
 Maharashtra
 Apply by:
-01 Apr 2026
-Sr. Manager/Manager-Sustainable Cotton Programmes
-Aga Khan Rural Support Programme India (AKRSP Ind...
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Project Manager – Vocational and Skill Development
-White Lotus Trust
-Location:
-Delhi
-Apply by:
-01 Apr 2026
+18 Mar 2026
+Project Nurse 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Project Technical Support 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Block Academic Coordinator
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
+District Program Manager
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
 Jobseekers
 Register
 Login
@@ -4544,112 +4039,75 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F18" s="1" t="inlineStr">
+      <c r="F16" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G18" s="1" t="inlineStr">
-        <is>
-          <t>06-03-2026</t>
-        </is>
-      </c>
-      <c r="H18" s="1" t="n">
+      <c r="G16" s="1" t="inlineStr">
+        <is>
+          <t>07-03-2026</t>
+        </is>
+      </c>
+      <c r="H16" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="I18" s="1" t="inlineStr">
+      <c r="I16" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287335</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr"/>
-      <c r="C19" s="1" t="inlineStr">
-        <is>
-          <t>EoI - For Empanelment of agencies for Impact Assessment/ Evaluation Servic...</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Small Industries Development Bank of India (SIDBI) | India
-International Development - EoI - For Empanelment of agencies for Impact Assessment/ Evaluation Services under Programmes for Development and Impact, Small Industries Development Bank of India (SIDBI), India - DevNetJobsIndia.org
-Jobseekers ... Read More</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>• Please      note that all the information required as per the documents required for      responding to EOI needs to be provided. Incomplete information in these      areas may lead to non-selection.
-Modification      And/ Or Withdrawal of documents:
-Documents once submitted will      be treated as final and no further correspondence will be entertained. No      document shall be modified after the deadline for submission of documents      in response to the EOI. Also, no Respondent shall be allowed to withdraw      any document, if the Respondent happens to be a successful      Respondent.
-SIDBI      has the right to reject any or all documents received without assigning      any reason whatsoever.
-NOTE:
-SIDBI SHALL NOT BE RESPONSIBLE FOR NON-RECEIPT / NON-DELIVERY OF THE DOCUMENTS DUE TO ANY REASON, WHATSOEVER.
-Critical Information
-Events
-Particular / Date and Time
-Tender No
-SIDBI/REOI/68279
-Tender Issue Date
-13/02/2026
-Last date for seeking Clarification on EOI document
-20/02/2026
-All queries relating to the EoI must be in writing only   and to be sent via
-email on.
-pdi@sidbi.in
-and
-mayankp@sidbi.in
-Pre EOI meeting
-25/02/2026
-The meeting shall be virtual / online over MS Teams Call.   Meeting Link will be shared separately to all the bidder
-Last date for submission of EoI
-06/03/2026
-Bids to submitted through email only at:
-pdi@sidbi.in
-and
-mayankp@sidbi.in
-Independent External Monitor
-Shri Sanjay Kumar Srivastava, IAS (Retd.),
-Apartment T-6 B,
-Windsor Court, DLF Phase-IV
-Gurgaon-122009
-Mobile No-9910059472
-E-mail:
-sksrivastava7854@rediffmail.com
-Dr. Parvez Hayat, IPS (Retd.),
-B-4/69- A, Safdarjung Enclave
-New Delhi-110029
-Mobile-9810134469
-E-Mail:
-phayatips@gmail.com
-• Contact details of SIDBI officials
-Shri Mohammed Adil Ahsan
-Asst. General Manager,
-Programmes for Development &amp; Impact [PDI]
-SIDBI Tower, 15, Ashok Marg, Lucknow – 226001
-Ph: 0522-4261631
-Email:
-mdadil@sidbi.in
-Shri Mayank Prakash
-Theme Leader – Monitoring &amp; Evaluation
-Programmes for Development &amp; Impact [PDI]
-SIDBI Tower, 15, Ashok Marg, Lucknow – 226001
-Ph: 0522 - 4259 626
-Email
-mayankp@sidbi.in
-For detailed information, please check the complete version of the EoI attached below.
+      <c r="B17" s="1" t="inlineStr"/>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>Associate (Programme Management)</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Indian Institute For Human Settlements (Iihs) | Karnataka
+International Development - Associate (Programme Management), Indian Institute For Human Settlements (Iihs), Karnataka - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events ... Read More</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>• IIHS is an equal opportunity employer that encourages women, people with disabilities and those from economically and socially excluded communities with the requisite skills and qualifications to apply for positions.
+• To apply
+If you are interested in exploring this opportunity with us, please fill the online
+application form
+by clicking here. (You can also click on the “
+Apply Now
+” button at the end of the Job Description displayed on the website).
+Contact
+Please write to us at
+hr@iihs.co.in
+if you need any clarifications while filling the online application form.
+• Job Email ID:
+hr(at)iihs.co.in
 Download Attachment:
-EOI for empanelment of Imapact assesment agencies_1202026.pdf
+Associate-Programme-Management-–-ASSURE-Lighthouse-Projects.pdf
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
 Apply by:
-06 Mar 2026
+07 Mar 2026
 Access all the jobs and get ahead!
 Subscribe to Value Membership Now!
 Subscribe
@@ -4711,54 +4169,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Project) Health &amp; Nutrition
-Bal Raksha Bharat (BRB)
-Location:
-Rajasthan
+RFP - Requirement of Agency for Creating High Qua...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Delhi
+Apply by:
+20 Mar 2026
+Programme officers (Education &amp; Life Skills Educa...
+Butterflies NGO
+Location:
+Delhi
+Apply by:
+15 Mar 2026
+RFQ: Construction of New gated check dams, De-sil...
+WaterAid India
+Location:
+Telangana
 Apply by:
 08 Mar 2026
-Regional Coordinator - North
-Intas Foundation
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Monitoring Coordinator
-Intas Foundation
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Individual Consultant – Technical support on Foun...
-UNICEF
-Location:
-Rajasthan
-Apply by:
-09 Mar 2026
-Multiple Vacancies
-AIDENT Social Welfare Organisation (ASWO)
-Location:
-Uttar Pradesh
-Apply by:
-16 Mar 2026
-Head of Accounts &amp; Finance
-Watershed Organization Trust (WOTR)
+Regional Coordinator
+Bharat Rural Livelihoods Foundation (BRLF)
 Location:
 Maharashtra
 Apply by:
-01 Apr 2026
-Sr. Manager/Manager-Sustainable Cotton Programmes
-Aga Khan Rural Support Programme India (AKRSP Ind...
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Project Manager – Vocational and Skill Development
-White Lotus Trust
-Location:
-Delhi
-Apply by:
-01 Apr 2026
+18 Mar 2026
+Project Nurse 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Project Technical Support 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Block Academic Coordinator
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
+District Program Manager
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
 Jobseekers
 Register
 Login
@@ -4786,243 +4244,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F19" s="1" t="inlineStr">
-        <is>
-          <t>Governance, Learning</t>
-        </is>
-      </c>
-      <c r="G19" s="1" t="inlineStr">
-        <is>
-          <t>06-03-2026</t>
-        </is>
-      </c>
-      <c r="H19" s="1" t="n">
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G17" s="1" t="inlineStr">
+        <is>
+          <t>07-03-2026</t>
+        </is>
+      </c>
+      <c r="H17" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="I19" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287084</t>
+      <c r="I17" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=285747</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr"/>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>Associate (Programme Management)</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Indian Institute For Human Settlements (Iihs) | Karnataka
-International Development - Associate (Programme Management), Indian Institute For Human Settlements (Iihs), Karnataka - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events ... Read More</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>• IIHS is an equal opportunity employer that encourages women, people with disabilities and those from economically and socially excluded communities with the requisite skills and qualifications to apply for positions.
-• To apply
-If you are interested in exploring this opportunity with us, please fill the online
-application form
-by clicking here. (You can also click on the “
-Apply Now
-” button at the end of the Job Description displayed on the website).
-Contact
-Please write to us at
-hr@iihs.co.in
-if you need any clarifications while filling the online application form.
-• Job Email ID:
-hr(at)iihs.co.in
-Download Attachment:
-Associate-Programme-Management-–-ASSURE-Lighthouse-Projects.pdf
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-07 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-Assistant Manager (Project) Health &amp; Nutrition
-Bal Raksha Bharat (BRB)
-Location:
-Rajasthan
-Apply by:
-08 Mar 2026
-Regional Coordinator - North
-Intas Foundation
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Monitoring Coordinator
-Intas Foundation
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Individual Consultant – Technical support on Foun...
-UNICEF
-Location:
-Rajasthan
-Apply by:
-09 Mar 2026
-Multiple Vacancies
-AIDENT Social Welfare Organisation (ASWO)
-Location:
-Uttar Pradesh
-Apply by:
-16 Mar 2026
-Head of Accounts &amp; Finance
-Watershed Organization Trust (WOTR)
-Location:
-Maharashtra
-Apply by:
-01 Apr 2026
-Sr. Manager/Manager-Sustainable Cotton Programmes
-Aga Khan Rural Support Programme India (AKRSP Ind...
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Project Manager – Vocational and Skill Development
-White Lotus Trust
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>07-03-2026</t>
-        </is>
-      </c>
-      <c r="H20" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="I20" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=285747</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B21" s="1" t="inlineStr"/>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="B18" s="1" t="inlineStr"/>
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>RFP - Final Evaluation of the Bhoomi Ka Programme</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Deutsche Welthungerhilfe | India
 International Development - RFP - Final Evaluation of the Bhoomi Ka Programme, Deutsche Welthungerhilfe, India - DevNetJobsIndia.org
@@ -5043,7 +4296,7 @@
 Jobs ... Read More</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>• INTRODUCTION AND CONTEXT
 Country:
@@ -5167,54 +4420,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Project) Health &amp; Nutrition
-Bal Raksha Bharat (BRB)
-Location:
-Rajasthan
+RFP - Requirement of Agency for Creating High Qua...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Delhi
+Apply by:
+20 Mar 2026
+Programme officers (Education &amp; Life Skills Educa...
+Butterflies NGO
+Location:
+Delhi
+Apply by:
+15 Mar 2026
+RFQ: Construction of New gated check dams, De-sil...
+WaterAid India
+Location:
+Telangana
 Apply by:
 08 Mar 2026
-Regional Coordinator - North
-Intas Foundation
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Monitoring Coordinator
-Intas Foundation
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Individual Consultant – Technical support on Foun...
-UNICEF
-Location:
-Rajasthan
-Apply by:
-09 Mar 2026
-Multiple Vacancies
-AIDENT Social Welfare Organisation (ASWO)
-Location:
-Uttar Pradesh
-Apply by:
-16 Mar 2026
-Head of Accounts &amp; Finance
-Watershed Organization Trust (WOTR)
+Regional Coordinator
+Bharat Rural Livelihoods Foundation (BRLF)
 Location:
 Maharashtra
 Apply by:
-01 Apr 2026
-Sr. Manager/Manager-Sustainable Cotton Programmes
-Aga Khan Rural Support Programme India (AKRSP Ind...
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Project Manager – Vocational and Skill Development
-White Lotus Trust
-Location:
-Delhi
-Apply by:
-01 Apr 2026
+18 Mar 2026
+Project Nurse 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Project Technical Support 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Block Academic Coordinator
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
+District Program Manager
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
 Jobseekers
 Register
 Login
@@ -5242,66 +4495,64 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F21" s="1" t="inlineStr">
+      <c r="F18" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G21" s="1" t="inlineStr">
+      <c r="G18" s="1" t="inlineStr">
         <is>
           <t>08-03-2026</t>
         </is>
       </c>
-      <c r="H21" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I21" s="1" t="inlineStr">
+      <c r="H18" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I18" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287384</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr"/>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>RFP For The Contractors To Procure, Build, Install, Supply Chlorine Tablet...</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>EAII Advisors Pvt Ltd | Andhra Pradesh
-International Development - RFP For The Contractors To Procure, Build, Install, Supply Chlorine Tablets, Operate And Maintain Tablet-Based In Line Chlorination Devices, EAII Advisors Pvt Ltd, Andhra Pradesh - DevNetJobsIndia.org
+      <c r="B19" s="1" t="inlineStr"/>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>RFQ: Construction of New gated check dams, De-siltation, and retrofitting ...</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>WaterAid India | Telangana
+International Development - RFQ: Construction of New gated check dams, De-siltation, and retrofitting of check dam in 6 villages, WaterAid India, Telangana - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
 Register
-Ho ... Read More</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>• Proposal Requirements
-1. Company Background and Details
-A. Company Profile
-Overview of the firm or firms submitting the bid, including a brief history, information about organizational structure, relevant company financials, location of offices, number of employees, relevant certifications, or any other information that could be pertinent.
-Supplier Response:
-Kindly fill in the column “Bidder Response”. The current inputs are guiding inputs or choices for answers. Kindly fill in accordingly.
-For detailed information, please check the complete version of the RFP attached below.
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+E ... Read More</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>• Job Email ID:
+WAIProcurementAP(at)wateraid.org
 Download Attachment:
-Standalone IC RFP Technical Evaluation Response Template.docx
-Download Attachment:
-Telugu_Standalone IC RFP Technical Evaluation Response Template.docx
+Tender Notice-15 check dams-Jalsankalp-19.02.26_compressed.pdf
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
 Apply by:
-09 Mar 2026
+08 Mar 2026
 Access all the jobs and get ahead!
 Subscribe to Value Membership Now!
 Subscribe
@@ -5363,54 +4614,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Project) Health &amp; Nutrition
-Bal Raksha Bharat (BRB)
-Location:
-Rajasthan
+RFP - Requirement of Agency for Creating High Qua...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Delhi
+Apply by:
+20 Mar 2026
+Programme officers (Education &amp; Life Skills Educa...
+Butterflies NGO
+Location:
+Delhi
+Apply by:
+15 Mar 2026
+RFQ: Construction of New gated check dams, De-sil...
+WaterAid India
+Location:
+Telangana
 Apply by:
 08 Mar 2026
-Regional Coordinator - North
-Intas Foundation
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Monitoring Coordinator
-Intas Foundation
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Individual Consultant – Technical support on Foun...
-UNICEF
-Location:
-Rajasthan
-Apply by:
-09 Mar 2026
-Multiple Vacancies
-AIDENT Social Welfare Organisation (ASWO)
-Location:
-Uttar Pradesh
-Apply by:
-16 Mar 2026
-Head of Accounts &amp; Finance
-Watershed Organization Trust (WOTR)
+Regional Coordinator
+Bharat Rural Livelihoods Foundation (BRLF)
 Location:
 Maharashtra
 Apply by:
-01 Apr 2026
-Sr. Manager/Manager-Sustainable Cotton Programmes
-Aga Khan Rural Support Programme India (AKRSP Ind...
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Project Manager – Vocational and Skill Development
-White Lotus Trust
-Location:
-Delhi
-Apply by:
-01 Apr 2026
+18 Mar 2026
+Project Nurse 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Project Technical Support 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Block Academic Coordinator
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
+District Program Manager
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
 Jobseekers
 Register
 Login
@@ -5438,57 +4689,61 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F22" s="1" t="inlineStr">
+      <c r="F19" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G22" s="1" t="inlineStr">
-        <is>
-          <t>09-03-2026</t>
-        </is>
-      </c>
-      <c r="H22" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="I22" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=285949</t>
+      <c r="G19" s="1" t="inlineStr">
+        <is>
+          <t>08-03-2026</t>
+        </is>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I19" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287784</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr"/>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Hiring of an International Audit Firm</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Coalition for Disaster Resilient Infrastructure (CDRI) | India
-International Development - RFP - Hiring of an International Audit Firm, Coalition for Disaster Resilient Infrastructure (CDRI), India - DevNetJobsIndia.org
+      <c r="B20" s="1" t="inlineStr"/>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>RFP For The Contractors To Procure, Build, Install, Supply Chlorine Tablet...</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>EAII Advisors Pvt Ltd | Andhra Pradesh
+International Development - RFP For The Contractors To Procure, Build, Install, Supply Chlorine Tablets, Operate And Maintain Tablet-Based In Line Chlorination Devices, EAII Advisors Pvt Ltd, Andhra Pradesh - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
 Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tender ... Read More</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>• Job Email ID:
-tender.projects(at)cdri.world
+Ho ... Read More</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>• Proposal Requirements
+1. Company Background and Details
+A. Company Profile
+Overview of the firm or firms submitting the bid, including a brief history, information about organizational structure, relevant company financials, location of offices, number of employees, relevant certifications, or any other information that could be pertinent.
+Supplier Response:
+Kindly fill in the column “Bidder Response”. The current inputs are guiding inputs or choices for answers. Kindly fill in accordingly.
+For detailed information, please check the complete version of the RFP attached below.
 Download Attachment:
-RFP-Hiring International Audit Firm-20 Feb'26.pdf
+Standalone IC RFP Technical Evaluation Response Template.docx
+Download Attachment:
+Telugu_Standalone IC RFP Technical Evaluation Response Template.docx
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
@@ -5555,54 +4810,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Project) Health &amp; Nutrition
-Bal Raksha Bharat (BRB)
-Location:
-Rajasthan
+RFP - Requirement of Agency for Creating High Qua...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Delhi
+Apply by:
+20 Mar 2026
+Programme officers (Education &amp; Life Skills Educa...
+Butterflies NGO
+Location:
+Delhi
+Apply by:
+15 Mar 2026
+RFQ: Construction of New gated check dams, De-sil...
+WaterAid India
+Location:
+Telangana
 Apply by:
 08 Mar 2026
-Regional Coordinator - North
-Intas Foundation
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Monitoring Coordinator
-Intas Foundation
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Individual Consultant – Technical support on Foun...
-UNICEF
-Location:
-Rajasthan
-Apply by:
-09 Mar 2026
-Multiple Vacancies
-AIDENT Social Welfare Organisation (ASWO)
-Location:
-Uttar Pradesh
-Apply by:
-16 Mar 2026
-Head of Accounts &amp; Finance
-Watershed Organization Trust (WOTR)
+Regional Coordinator
+Bharat Rural Livelihoods Foundation (BRLF)
 Location:
 Maharashtra
 Apply by:
-01 Apr 2026
-Sr. Manager/Manager-Sustainable Cotton Programmes
-Aga Khan Rural Support Programme India (AKRSP Ind...
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Project Manager – Vocational and Skill Development
-White Lotus Trust
-Location:
-Delhi
-Apply by:
-01 Apr 2026
+18 Mar 2026
+Project Nurse 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Project Technical Support 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Block Academic Coordinator
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
+District Program Manager
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
 Jobseekers
 Register
 Login
@@ -5630,88 +4885,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F23" s="1" t="inlineStr">
-        <is>
-          <t>Climate</t>
-        </is>
-      </c>
-      <c r="G23" s="1" t="inlineStr">
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G20" s="1" t="inlineStr">
         <is>
           <t>09-03-2026</t>
         </is>
       </c>
-      <c r="H23" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="I23" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287382</t>
+      <c r="H20" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=285949</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr"/>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Early-Stage Impact Assessment-CDRI SWP 23-26</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Coalition for Disaster Resilient Infrastructure (CDRI) | India
-International Development - RFP - Early-Stage Impact Assessment-CDRI SWP 23-26, Coalition for Disaster Resilient Infrastructure (CDRI), India - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs ... Read More</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F24" s="1" t="inlineStr">
-        <is>
-          <t>Climate, Governance</t>
-        </is>
-      </c>
-      <c r="G24" s="1" t="inlineStr">
-        <is>
-          <t>09-03-2026</t>
-        </is>
-      </c>
-      <c r="H24" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="I24" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287093</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B25" s="1" t="inlineStr"/>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="B21" s="1" t="inlineStr"/>
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>RFP For Selection of an Implementation Support Agency (Isa) For Capacity B...</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>EAII Advisors Pvt Ltd | Andhra Pradesh
 International Development - RFP For Selection of an Implementation Support Agency (Isa) For Capacity Building Of Community Leaders To Conduct Community Engagement Activities, EAII Advisors Pvt Ltd, Andhra Pradesh - DevNetJobsIndia.org
@@ -5721,7 +4926,7 @@
 Regis ... Read More</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>• Proposal Requirements
 1. Company Background and Details
@@ -5800,54 +5005,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Project) Health &amp; Nutrition
-Bal Raksha Bharat (BRB)
-Location:
-Rajasthan
+RFP - Requirement of Agency for Creating High Qua...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Delhi
+Apply by:
+20 Mar 2026
+Programme officers (Education &amp; Life Skills Educa...
+Butterflies NGO
+Location:
+Delhi
+Apply by:
+15 Mar 2026
+RFQ: Construction of New gated check dams, De-sil...
+WaterAid India
+Location:
+Telangana
 Apply by:
 08 Mar 2026
-Regional Coordinator - North
-Intas Foundation
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Monitoring Coordinator
-Intas Foundation
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Individual Consultant – Technical support on Foun...
-UNICEF
-Location:
-Rajasthan
-Apply by:
-09 Mar 2026
-Multiple Vacancies
-AIDENT Social Welfare Organisation (ASWO)
-Location:
-Uttar Pradesh
-Apply by:
-16 Mar 2026
-Head of Accounts &amp; Finance
-Watershed Organization Trust (WOTR)
+Regional Coordinator
+Bharat Rural Livelihoods Foundation (BRLF)
 Location:
 Maharashtra
 Apply by:
-01 Apr 2026
-Sr. Manager/Manager-Sustainable Cotton Programmes
-Aga Khan Rural Support Programme India (AKRSP Ind...
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Project Manager – Vocational and Skill Development
-White Lotus Trust
-Location:
-Delhi
-Apply by:
-01 Apr 2026
+18 Mar 2026
+Project Nurse 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Project Technical Support 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Block Academic Coordinator
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
+District Program Manager
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
 Jobseekers
 Register
 Login
@@ -5875,38 +5080,280 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F25" s="1" t="inlineStr">
+      <c r="F21" s="1" t="inlineStr">
         <is>
           <t>Governance, Learning</t>
         </is>
       </c>
-      <c r="G25" s="1" t="inlineStr">
+      <c r="G21" s="1" t="inlineStr">
         <is>
           <t>09-03-2026</t>
         </is>
       </c>
-      <c r="H25" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="I25" s="1" t="inlineStr">
+      <c r="H21" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I21" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=285950</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr"/>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="B22" s="1" t="inlineStr"/>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>RFP - Hiring of an International Audit Firm</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Coalition for Disaster Resilient Infrastructure (CDRI) | India
+International Development - RFP - Hiring of an International Audit Firm, Coalition for Disaster Resilient Infrastructure (CDRI), India - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tender ... Read More</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>• Job Email ID:
+tender.projects(at)cdri.world
+Download Attachment:
+RFP-Hiring International Audit Firm-20 Feb'26.pdf
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+09 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Associate (Programme Management)
+Indian Institute For Human Settlements (Iihs)
+Location:
+Karnataka
+Apply by:
+07 Mar 2026
+Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+RFP - Requirement of Agency for Creating High Qua...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Delhi
+Apply by:
+20 Mar 2026
+Programme officers (Education &amp; Life Skills Educa...
+Butterflies NGO
+Location:
+Delhi
+Apply by:
+15 Mar 2026
+RFQ: Construction of New gated check dams, De-sil...
+WaterAid India
+Location:
+Telangana
+Apply by:
+08 Mar 2026
+Regional Coordinator
+Bharat Rural Livelihoods Foundation (BRLF)
+Location:
+Maharashtra
+Apply by:
+18 Mar 2026
+Project Nurse 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Project Technical Support 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Block Academic Coordinator
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
+District Program Manager
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F22" s="1" t="inlineStr">
+        <is>
+          <t>Climate</t>
+        </is>
+      </c>
+      <c r="G22" s="1" t="inlineStr">
+        <is>
+          <t>09-03-2026</t>
+        </is>
+      </c>
+      <c r="H22" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I22" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287382</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr"/>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>RFP - Early-Stage Impact Assessment-CDRI SWP 23-26</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Coalition for Disaster Resilient Infrastructure (CDRI) | India
+International Development - RFP - Early-Stage Impact Assessment-CDRI SWP 23-26, Coalition for Disaster Resilient Infrastructure (CDRI), India - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs ... Read More</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F23" s="1" t="inlineStr">
+        <is>
+          <t>Climate, Governance</t>
+        </is>
+      </c>
+      <c r="G23" s="1" t="inlineStr">
+        <is>
+          <t>09-03-2026</t>
+        </is>
+      </c>
+      <c r="H23" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I23" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287093</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="inlineStr"/>
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>RFP - for Supply of Skill Lab Items</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>TeamLease Foundation | India
 International Development - RFP - for Supply of Skill Lab Items, TeamLease Foundation, India - DevNetJobsIndia.org
@@ -5928,7 +5375,7 @@
 Jobseeker ... Read More</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>• Technical Bid Submission Link-
 https://forms.gle/V9iy35ddb4kWEb468
@@ -6029,54 +5476,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Project) Health &amp; Nutrition
-Bal Raksha Bharat (BRB)
-Location:
-Rajasthan
+RFP - Requirement of Agency for Creating High Qua...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Delhi
+Apply by:
+20 Mar 2026
+Programme officers (Education &amp; Life Skills Educa...
+Butterflies NGO
+Location:
+Delhi
+Apply by:
+15 Mar 2026
+RFQ: Construction of New gated check dams, De-sil...
+WaterAid India
+Location:
+Telangana
 Apply by:
 08 Mar 2026
-Regional Coordinator - North
-Intas Foundation
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Monitoring Coordinator
-Intas Foundation
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Individual Consultant – Technical support on Foun...
-UNICEF
-Location:
-Rajasthan
-Apply by:
-09 Mar 2026
-Multiple Vacancies
-AIDENT Social Welfare Organisation (ASWO)
-Location:
-Uttar Pradesh
-Apply by:
-16 Mar 2026
-Head of Accounts &amp; Finance
-Watershed Organization Trust (WOTR)
+Regional Coordinator
+Bharat Rural Livelihoods Foundation (BRLF)
 Location:
 Maharashtra
 Apply by:
-01 Apr 2026
-Sr. Manager/Manager-Sustainable Cotton Programmes
-Aga Khan Rural Support Programme India (AKRSP Ind...
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Project Manager – Vocational and Skill Development
-White Lotus Trust
-Location:
-Delhi
-Apply by:
-01 Apr 2026
+18 Mar 2026
+Project Nurse 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Project Technical Support 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Block Academic Coordinator
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
+District Program Manager
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
 Jobseekers
 Register
 Login
@@ -6104,44 +5551,44 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F26" s="1" t="inlineStr">
+      <c r="F24" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G26" s="1" t="inlineStr">
+      <c r="G24" s="1" t="inlineStr">
         <is>
           <t>11-03-2026</t>
         </is>
       </c>
-      <c r="H26" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="I26" s="1" t="inlineStr">
+      <c r="H24" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="I24" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287613</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr"/>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="B25" s="1" t="inlineStr"/>
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>RFP - Study On SC-DMPA In Rajasthan- Clients And Providers Perspectives On...</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Centre For Community Economics And Development Consultants Society- CECOEDECON | Jaipur, Rajasthan
 International Development - RFP - Study On SC-DMPA In Rajasthan- Clients And Providers Perspectives On SC-DMPA In Rajasthan, Centre For Community Economics And Development Consultants Society- CECOEDE ... Read More</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>• Despite India’s achievement of replacement-level fertility, unmet need for contraception—particularly for spacing methods—remains substantial, with modern contraceptive use at 56.4% (2019–21), highlighting persistent gaps in access and choice, especially among vulnerable populations. Expanding the contraceptive method mix through innovative, user-centred approaches is therefore essential to meeting national commitments under FP2030 and the Sustainable Development Goals. In this context, the Government of India’s introduction of subcutaneous DMPA (DMPA-SC) as a self-care option under the National Family Planning Programme in 2023 represents a strategic step toward enhancing women’s autonomy, privacy, and convenience in contraceptive use. Global and national evidence indicates strong feasibility and acceptability of self-administered DMPA-SC among both users and providers; however, successful implementation requires an in-depth understanding of user experiences and health system readiness. This study, to be conducted in Jaipur-1, Jaisalmer and Sawai Madhopur districts of Rajasthan, aims to examine the perspectives &amp; experience of current SC-DMPA users and explore healthcare providers’ views on enabling and generating actionable evidence to inform effective scale-up of SC-DMPA within India’s public health system.
 CECOEDECON, with support from UNFPA, is implementing the roll-out of subcutaneous DMPA (SC-DMPA) in selected pilot districts of Rajasthan in the public health facilities, in collaboration with the Department of Health &amp; Family Welfare, Government of Rajasthan.
@@ -6270,54 +5717,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Project) Health &amp; Nutrition
-Bal Raksha Bharat (BRB)
-Location:
-Rajasthan
+RFP - Requirement of Agency for Creating High Qua...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Delhi
+Apply by:
+20 Mar 2026
+Programme officers (Education &amp; Life Skills Educa...
+Butterflies NGO
+Location:
+Delhi
+Apply by:
+15 Mar 2026
+RFQ: Construction of New gated check dams, De-sil...
+WaterAid India
+Location:
+Telangana
 Apply by:
 08 Mar 2026
-Regional Coordinator - North
-Intas Foundation
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Monitoring Coordinator
-Intas Foundation
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Individual Consultant – Technical support on Foun...
-UNICEF
-Location:
-Rajasthan
-Apply by:
-09 Mar 2026
-Multiple Vacancies
-AIDENT Social Welfare Organisation (ASWO)
-Location:
-Uttar Pradesh
-Apply by:
-16 Mar 2026
-Head of Accounts &amp; Finance
-Watershed Organization Trust (WOTR)
+Regional Coordinator
+Bharat Rural Livelihoods Foundation (BRLF)
 Location:
 Maharashtra
 Apply by:
-01 Apr 2026
-Sr. Manager/Manager-Sustainable Cotton Programmes
-Aga Khan Rural Support Programme India (AKRSP Ind...
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Project Manager – Vocational and Skill Development
-White Lotus Trust
-Location:
-Delhi
-Apply by:
-01 Apr 2026
+18 Mar 2026
+Project Nurse 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Project Technical Support 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Block Academic Coordinator
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
+District Program Manager
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
 Jobseekers
 Register
 Login
@@ -6345,38 +5792,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F27" s="1" t="inlineStr">
+      <c r="F25" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G27" s="1" t="inlineStr">
+      <c r="G25" s="1" t="inlineStr">
         <is>
           <t>11-03-2026</t>
         </is>
       </c>
-      <c r="H27" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="I27" s="1" t="inlineStr">
+      <c r="H25" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="I25" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287322</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr"/>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="B26" s="1" t="inlineStr"/>
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>SOW - Engagement of a Public Relations (PR) Agency on Retainer</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Room to Read India | India
 International Development - SOW - Engagement of a Public Relations (PR) Agency on Retainer, Room to Read India, India - DevNetJobsIndia.org
@@ -6397,7 +5844,7 @@
 Job ... Read More</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>• Scope of Work (SOW)
 Engagement of a Public Relations (PR) Agency on Retainer
@@ -6521,54 +5968,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Project) Health &amp; Nutrition
-Bal Raksha Bharat (BRB)
-Location:
-Rajasthan
+RFP - Requirement of Agency for Creating High Qua...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Delhi
+Apply by:
+20 Mar 2026
+Programme officers (Education &amp; Life Skills Educa...
+Butterflies NGO
+Location:
+Delhi
+Apply by:
+15 Mar 2026
+RFQ: Construction of New gated check dams, De-sil...
+WaterAid India
+Location:
+Telangana
 Apply by:
 08 Mar 2026
-Regional Coordinator - North
-Intas Foundation
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Monitoring Coordinator
-Intas Foundation
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Individual Consultant – Technical support on Foun...
-UNICEF
-Location:
-Rajasthan
-Apply by:
-09 Mar 2026
-Multiple Vacancies
-AIDENT Social Welfare Organisation (ASWO)
-Location:
-Uttar Pradesh
-Apply by:
-16 Mar 2026
-Head of Accounts &amp; Finance
-Watershed Organization Trust (WOTR)
+Regional Coordinator
+Bharat Rural Livelihoods Foundation (BRLF)
 Location:
 Maharashtra
 Apply by:
-01 Apr 2026
-Sr. Manager/Manager-Sustainable Cotton Programmes
-Aga Khan Rural Support Programme India (AKRSP Ind...
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Project Manager – Vocational and Skill Development
-White Lotus Trust
-Location:
-Delhi
-Apply by:
-01 Apr 2026
+18 Mar 2026
+Project Nurse 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Project Technical Support 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Block Academic Coordinator
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
+District Program Manager
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
 Jobseekers
 Register
 Login
@@ -6596,38 +6043,245 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F28" s="1" t="inlineStr">
+      <c r="F26" s="1" t="inlineStr">
         <is>
           <t>Governance, Learning</t>
         </is>
       </c>
-      <c r="G28" s="1" t="inlineStr">
+      <c r="G26" s="1" t="inlineStr">
         <is>
           <t>12-03-2026</t>
         </is>
       </c>
-      <c r="H28" s="1" t="n">
+      <c r="H26" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="I26" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287648</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="inlineStr"/>
+      <c r="C27" s="1" t="inlineStr">
+        <is>
+          <t>RFP - for Internal Audit</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>India HIV/AIDS Alliance (Alliance India) | Delhi
+International Development - RFP - for Internal Audit, India HIV/AIDS Alliance (Alliance India), Delhi - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers:
+Login
+|
+Regist ... Read More</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>• Alliance India reserves the right to reject applications that do not meet eligibility or application submission requirements (as detailed above) without further notice to the applicant. Issuance of this RFP does not constitute an award commitment or a guarantee of business on the part of Alliance India, nor does it commit Alliance India to pay for the costs incurred in submitting the application. Further, Alliance India reserves the right to reject any or all applications received and negotiate separately with an applicant if such action is considered in the best interest of Alliance India/ project.
+iii.
+Queries, Response and Submission
+Queries regarding this RFP will be sent only to procurement@allianceindia.org by March 07, 2026. Alliance India shall collaborate and respond to all meaningful queries from prospective applicants by March 10, 2026. Responses to questions shall be compiled and sent to all the applicants who raised the queries through email only. ALLIANCE INDIA is under no obligation to consider or respond to questions that are not received on time.
+iv.
+• Submission of bids
+The bid has to be submitted in the prescribed format on or before March 13, 2026 by 5 p.m. Indian Standard Time to
+procurement@allianceindia.org
+For the detailed version of the Request for Proposal, please refer to the RFP attached.
+• Job Email ID:
+procurement(at)allianceindia.org
+Download Attachment:
+RFP for Internal Audit - FY 2025-26.doc
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+13 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Associate (Programme Management)
+Indian Institute For Human Settlements (Iihs)
+Location:
+Karnataka
+Apply by:
+07 Mar 2026
+Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+RFP - Requirement of Agency for Creating High Qua...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Delhi
+Apply by:
+20 Mar 2026
+Programme officers (Education &amp; Life Skills Educa...
+Butterflies NGO
+Location:
+Delhi
+Apply by:
+15 Mar 2026
+RFQ: Construction of New gated check dams, De-sil...
+WaterAid India
+Location:
+Telangana
+Apply by:
+08 Mar 2026
+Regional Coordinator
+Bharat Rural Livelihoods Foundation (BRLF)
+Location:
+Maharashtra
+Apply by:
+18 Mar 2026
+Project Nurse 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Project Technical Support 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Block Academic Coordinator
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
+District Program Manager
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F27" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G27" s="1" t="inlineStr">
+        <is>
+          <t>13-03-2026</t>
+        </is>
+      </c>
+      <c r="H27" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="I28" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287648</t>
+      <c r="I27" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287765</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr"/>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="B28" s="1" t="inlineStr"/>
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>Specialist – Financial Management and Compliance</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Financial Management Service Foundation (FMSF) | Uttar Pradesh
 International Development - Specialist – Financial Management and Compliance, Financial Management Service Foundation (FMSF), Uttar Pradesh - DevNetJobsIndia.org
@@ -6641,7 +6295,7 @@
 RFPs/T ... Read More</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>• will play a vital role in a program which seeks to strengthen the internal capacities of non-profit organizations in India across three building blocks of institutional functioning: governance, financial management, and compliance. These areas are deeply interconnected and together determine how effectively an organization operates, delivers programs and meets the expectations of its stakeholders. This position demands expertise in specific areas related to governance, compliance, and financial management, contributing essential guidance and support to strengthen the capabilities of participating organizations.
 Job Responsibilities:
@@ -6748,54 +6402,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Project) Health &amp; Nutrition
-Bal Raksha Bharat (BRB)
-Location:
-Rajasthan
+RFP - Requirement of Agency for Creating High Qua...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Delhi
+Apply by:
+20 Mar 2026
+Programme officers (Education &amp; Life Skills Educa...
+Butterflies NGO
+Location:
+Delhi
+Apply by:
+15 Mar 2026
+RFQ: Construction of New gated check dams, De-sil...
+WaterAid India
+Location:
+Telangana
 Apply by:
 08 Mar 2026
-Regional Coordinator - North
-Intas Foundation
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Monitoring Coordinator
-Intas Foundation
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Individual Consultant – Technical support on Foun...
-UNICEF
-Location:
-Rajasthan
-Apply by:
-09 Mar 2026
-Multiple Vacancies
-AIDENT Social Welfare Organisation (ASWO)
-Location:
-Uttar Pradesh
-Apply by:
-16 Mar 2026
-Head of Accounts &amp; Finance
-Watershed Organization Trust (WOTR)
+Regional Coordinator
+Bharat Rural Livelihoods Foundation (BRLF)
 Location:
 Maharashtra
 Apply by:
-01 Apr 2026
-Sr. Manager/Manager-Sustainable Cotton Programmes
-Aga Khan Rural Support Programme India (AKRSP Ind...
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Project Manager – Vocational and Skill Development
-White Lotus Trust
-Location:
-Delhi
-Apply by:
-01 Apr 2026
+18 Mar 2026
+Project Nurse 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Project Technical Support 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Block Academic Coordinator
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
+District Program Manager
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
 Jobseekers
 Register
 Login
@@ -6823,22 +6477,71 @@
 Recruitment Exchange</t>
         </is>
       </c>
+      <c r="F28" s="1" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G28" s="1" t="inlineStr">
+        <is>
+          <t>13-03-2026</t>
+        </is>
+      </c>
+      <c r="H28" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="I28" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287015</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="inlineStr"/>
+      <c r="C29" s="1" t="inlineStr">
+        <is>
+          <t>RFP - for Empanelment of Knowledge Partners for Grooming of students for ...</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>TeamLease Foundation | India
+International Development - RFP - for  Empanelment of Knowledge Partners for Grooming of students for competitive examination (through partner) Super 30 Model, TeamLease Foundation, India - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast ... Read More</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
-          <t>13-03-2026</t>
+          <t>15-03-2026</t>
         </is>
       </c>
       <c r="H29" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I29" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287015</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287763</t>
         </is>
       </c>
     </row>
@@ -7005,54 +6708,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Project) Health &amp; Nutrition
-Bal Raksha Bharat (BRB)
-Location:
-Rajasthan
+RFP - Requirement of Agency for Creating High Qua...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Delhi
+Apply by:
+20 Mar 2026
+Programme officers (Education &amp; Life Skills Educa...
+Butterflies NGO
+Location:
+Delhi
+Apply by:
+15 Mar 2026
+RFQ: Construction of New gated check dams, De-sil...
+WaterAid India
+Location:
+Telangana
 Apply by:
 08 Mar 2026
-Regional Coordinator - North
-Intas Foundation
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Monitoring Coordinator
-Intas Foundation
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Individual Consultant – Technical support on Foun...
-UNICEF
-Location:
-Rajasthan
-Apply by:
-09 Mar 2026
-Multiple Vacancies
-AIDENT Social Welfare Organisation (ASWO)
-Location:
-Uttar Pradesh
-Apply by:
-16 Mar 2026
-Head of Accounts &amp; Finance
-Watershed Organization Trust (WOTR)
+Regional Coordinator
+Bharat Rural Livelihoods Foundation (BRLF)
 Location:
 Maharashtra
 Apply by:
-01 Apr 2026
-Sr. Manager/Manager-Sustainable Cotton Programmes
-Aga Khan Rural Support Programme India (AKRSP Ind...
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Project Manager – Vocational and Skill Development
-White Lotus Trust
-Location:
-Delhi
-Apply by:
-01 Apr 2026
+18 Mar 2026
+Project Nurse 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Project Technical Support 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Block Academic Coordinator
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
+District Program Manager
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
 Jobseekers
 Register
 Login
@@ -7091,7 +6794,7 @@
         </is>
       </c>
       <c r="H30" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I30" s="1" t="inlineStr">
         <is>
@@ -7223,54 +6926,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Project) Health &amp; Nutrition
-Bal Raksha Bharat (BRB)
-Location:
-Rajasthan
+RFP - Requirement of Agency for Creating High Qua...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Delhi
+Apply by:
+20 Mar 2026
+Programme officers (Education &amp; Life Skills Educa...
+Butterflies NGO
+Location:
+Delhi
+Apply by:
+15 Mar 2026
+RFQ: Construction of New gated check dams, De-sil...
+WaterAid India
+Location:
+Telangana
 Apply by:
 08 Mar 2026
-Regional Coordinator - North
-Intas Foundation
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Monitoring Coordinator
-Intas Foundation
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Individual Consultant – Technical support on Foun...
-UNICEF
-Location:
-Rajasthan
-Apply by:
-09 Mar 2026
-Multiple Vacancies
-AIDENT Social Welfare Organisation (ASWO)
-Location:
-Uttar Pradesh
-Apply by:
-16 Mar 2026
-Head of Accounts &amp; Finance
-Watershed Organization Trust (WOTR)
+Regional Coordinator
+Bharat Rural Livelihoods Foundation (BRLF)
 Location:
 Maharashtra
 Apply by:
-01 Apr 2026
-Sr. Manager/Manager-Sustainable Cotton Programmes
-Aga Khan Rural Support Programme India (AKRSP Ind...
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Project Manager – Vocational and Skill Development
-White Lotus Trust
-Location:
-Delhi
-Apply by:
-01 Apr 2026
+18 Mar 2026
+Project Nurse 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Project Technical Support 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Block Academic Coordinator
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
+District Program Manager
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
 Jobseekers
 Register
 Login
@@ -7309,7 +7012,7 @@
         </is>
       </c>
       <c r="H31" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I31" s="1" t="inlineStr">
         <is>
@@ -7423,54 +7126,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Project) Health &amp; Nutrition
-Bal Raksha Bharat (BRB)
-Location:
-Rajasthan
+RFP - Requirement of Agency for Creating High Qua...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Delhi
+Apply by:
+20 Mar 2026
+Programme officers (Education &amp; Life Skills Educa...
+Butterflies NGO
+Location:
+Delhi
+Apply by:
+15 Mar 2026
+RFQ: Construction of New gated check dams, De-sil...
+WaterAid India
+Location:
+Telangana
 Apply by:
 08 Mar 2026
-Regional Coordinator - North
-Intas Foundation
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Monitoring Coordinator
-Intas Foundation
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Individual Consultant – Technical support on Foun...
-UNICEF
-Location:
-Rajasthan
-Apply by:
-09 Mar 2026
-Multiple Vacancies
-AIDENT Social Welfare Organisation (ASWO)
-Location:
-Uttar Pradesh
-Apply by:
-16 Mar 2026
-Head of Accounts &amp; Finance
-Watershed Organization Trust (WOTR)
+Regional Coordinator
+Bharat Rural Livelihoods Foundation (BRLF)
 Location:
 Maharashtra
 Apply by:
-01 Apr 2026
-Sr. Manager/Manager-Sustainable Cotton Programmes
-Aga Khan Rural Support Programme India (AKRSP Ind...
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Project Manager – Vocational and Skill Development
-White Lotus Trust
-Location:
-Delhi
-Apply by:
-01 Apr 2026
+18 Mar 2026
+Project Nurse 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Project Technical Support 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Block Academic Coordinator
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
+District Program Manager
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
 Jobseekers
 Register
 Login
@@ -7509,7 +7212,7 @@
         </is>
       </c>
       <c r="H32" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I32" s="1" t="inlineStr">
         <is>
@@ -7624,54 +7327,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Project) Health &amp; Nutrition
-Bal Raksha Bharat (BRB)
-Location:
-Rajasthan
+RFP - Requirement of Agency for Creating High Qua...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Delhi
+Apply by:
+20 Mar 2026
+Programme officers (Education &amp; Life Skills Educa...
+Butterflies NGO
+Location:
+Delhi
+Apply by:
+15 Mar 2026
+RFQ: Construction of New gated check dams, De-sil...
+WaterAid India
+Location:
+Telangana
 Apply by:
 08 Mar 2026
-Regional Coordinator - North
-Intas Foundation
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Monitoring Coordinator
-Intas Foundation
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Individual Consultant – Technical support on Foun...
-UNICEF
-Location:
-Rajasthan
-Apply by:
-09 Mar 2026
-Multiple Vacancies
-AIDENT Social Welfare Organisation (ASWO)
-Location:
-Uttar Pradesh
-Apply by:
-16 Mar 2026
-Head of Accounts &amp; Finance
-Watershed Organization Trust (WOTR)
+Regional Coordinator
+Bharat Rural Livelihoods Foundation (BRLF)
 Location:
 Maharashtra
 Apply by:
-01 Apr 2026
-Sr. Manager/Manager-Sustainable Cotton Programmes
-Aga Khan Rural Support Programme India (AKRSP Ind...
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Project Manager – Vocational and Skill Development
-White Lotus Trust
-Location:
-Delhi
-Apply by:
-01 Apr 2026
+18 Mar 2026
+Project Nurse 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Project Technical Support 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Block Academic Coordinator
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
+District Program Manager
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
 Jobseekers
 Register
 Login
@@ -7710,7 +7413,7 @@
         </is>
       </c>
       <c r="H33" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I33" s="1" t="inlineStr">
         <is>
@@ -7826,54 +7529,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Project) Health &amp; Nutrition
-Bal Raksha Bharat (BRB)
-Location:
-Rajasthan
+RFP - Requirement of Agency for Creating High Qua...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Delhi
+Apply by:
+20 Mar 2026
+Programme officers (Education &amp; Life Skills Educa...
+Butterflies NGO
+Location:
+Delhi
+Apply by:
+15 Mar 2026
+RFQ: Construction of New gated check dams, De-sil...
+WaterAid India
+Location:
+Telangana
 Apply by:
 08 Mar 2026
-Regional Coordinator - North
-Intas Foundation
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Monitoring Coordinator
-Intas Foundation
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Individual Consultant – Technical support on Foun...
-UNICEF
-Location:
-Rajasthan
-Apply by:
-09 Mar 2026
-Multiple Vacancies
-AIDENT Social Welfare Organisation (ASWO)
-Location:
-Uttar Pradesh
-Apply by:
-16 Mar 2026
-Head of Accounts &amp; Finance
-Watershed Organization Trust (WOTR)
+Regional Coordinator
+Bharat Rural Livelihoods Foundation (BRLF)
 Location:
 Maharashtra
 Apply by:
-01 Apr 2026
-Sr. Manager/Manager-Sustainable Cotton Programmes
-Aga Khan Rural Support Programme India (AKRSP Ind...
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Project Manager – Vocational and Skill Development
-White Lotus Trust
-Location:
-Delhi
-Apply by:
-01 Apr 2026
+18 Mar 2026
+Project Nurse 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Project Technical Support 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Block Academic Coordinator
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
+District Program Manager
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
 Jobseekers
 Register
 Login
@@ -7912,7 +7615,7 @@
         </is>
       </c>
       <c r="H34" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I34" s="1" t="inlineStr">
         <is>
@@ -7978,8 +7681,7 @@
 Application for Junior Research Technician (IRRI Project Deployment)
 .
 Only shortlisted candidates who complete the required documentation will be considered for subsequent stages of selection.
-Selection will be done on a first-come-first-served basis.
-Applications received up to Thursday each week will be reviewed, and interviews will be conducted in the following week.
+Selection will be done on a first-come-first-served basis. Applications received up to Thursday each week will be reviewed, and interviews will be conducted in the following week. As soon as we shall finish all recruitment, we will take the advertisement off.
 • Job Email ID:
 communications(at)starshieldsolution.com
 Download Attachment:
@@ -8050,54 +7752,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Project) Health &amp; Nutrition
-Bal Raksha Bharat (BRB)
-Location:
-Rajasthan
+RFP - Requirement of Agency for Creating High Qua...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Delhi
+Apply by:
+20 Mar 2026
+Programme officers (Education &amp; Life Skills Educa...
+Butterflies NGO
+Location:
+Delhi
+Apply by:
+15 Mar 2026
+RFQ: Construction of New gated check dams, De-sil...
+WaterAid India
+Location:
+Telangana
 Apply by:
 08 Mar 2026
-Regional Coordinator - North
-Intas Foundation
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Monitoring Coordinator
-Intas Foundation
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Individual Consultant – Technical support on Foun...
-UNICEF
-Location:
-Rajasthan
-Apply by:
-09 Mar 2026
-Multiple Vacancies
-AIDENT Social Welfare Organisation (ASWO)
-Location:
-Uttar Pradesh
-Apply by:
-16 Mar 2026
-Head of Accounts &amp; Finance
-Watershed Organization Trust (WOTR)
+Regional Coordinator
+Bharat Rural Livelihoods Foundation (BRLF)
 Location:
 Maharashtra
 Apply by:
-01 Apr 2026
-Sr. Manager/Manager-Sustainable Cotton Programmes
-Aga Khan Rural Support Programme India (AKRSP Ind...
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Project Manager – Vocational and Skill Development
-White Lotus Trust
-Location:
-Delhi
-Apply by:
-01 Apr 2026
+18 Mar 2026
+Project Nurse 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Project Technical Support 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Block Academic Coordinator
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
+District Program Manager
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
 Jobseekers
 Register
 Login
@@ -8136,7 +7838,7 @@
         </is>
       </c>
       <c r="H35" s="1" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I35" s="1" t="inlineStr">
         <is>
@@ -8202,8 +7904,7 @@
 Application for Agriculture Research Development Officer (IRRI Project Deployment)
 .
 Only shortlisted candidates who complete the required documentation will be considered for subsequent stages of selection.
-Selection will be done on a first-come-first-served basis.
-Applications received up to Thursday each week will be reviewed, and interviews will be conducted in the following week.
+Selection will be done on a first-come-first-served basis. Applications received up to Thursday each week will be reviewed, and interviews will be conducted in the following week. As soon as we shall finish all recruitment, we will take the advertisement off.
 • Job Email ID:
 communications(at)starshieldsolution.com
 Download Attachment:
@@ -8274,54 +7975,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Project) Health &amp; Nutrition
-Bal Raksha Bharat (BRB)
-Location:
-Rajasthan
+RFP - Requirement of Agency for Creating High Qua...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Delhi
+Apply by:
+20 Mar 2026
+Programme officers (Education &amp; Life Skills Educa...
+Butterflies NGO
+Location:
+Delhi
+Apply by:
+15 Mar 2026
+RFQ: Construction of New gated check dams, De-sil...
+WaterAid India
+Location:
+Telangana
 Apply by:
 08 Mar 2026
-Regional Coordinator - North
-Intas Foundation
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Monitoring Coordinator
-Intas Foundation
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Individual Consultant – Technical support on Foun...
-UNICEF
-Location:
-Rajasthan
-Apply by:
-09 Mar 2026
-Multiple Vacancies
-AIDENT Social Welfare Organisation (ASWO)
-Location:
-Uttar Pradesh
-Apply by:
-16 Mar 2026
-Head of Accounts &amp; Finance
-Watershed Organization Trust (WOTR)
+Regional Coordinator
+Bharat Rural Livelihoods Foundation (BRLF)
 Location:
 Maharashtra
 Apply by:
-01 Apr 2026
-Sr. Manager/Manager-Sustainable Cotton Programmes
-Aga Khan Rural Support Programme India (AKRSP Ind...
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Project Manager – Vocational and Skill Development
-White Lotus Trust
-Location:
-Delhi
-Apply by:
-01 Apr 2026
+18 Mar 2026
+Project Nurse 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Project Technical Support 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Block Academic Coordinator
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
+District Program Manager
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
 Jobseekers
 Register
 Login
@@ -8360,7 +8061,7 @@
         </is>
       </c>
       <c r="H36" s="1" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I36" s="1" t="inlineStr">
         <is>
@@ -8491,54 +8192,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Project) Health &amp; Nutrition
-Bal Raksha Bharat (BRB)
-Location:
-Rajasthan
+RFP - Requirement of Agency for Creating High Qua...
+Nature Conservancy India Solutions Private Limite...
+Location:
+Delhi
+Apply by:
+20 Mar 2026
+Programme officers (Education &amp; Life Skills Educa...
+Butterflies NGO
+Location:
+Delhi
+Apply by:
+15 Mar 2026
+RFQ: Construction of New gated check dams, De-sil...
+WaterAid India
+Location:
+Telangana
 Apply by:
 08 Mar 2026
-Regional Coordinator - North
-Intas Foundation
-Location:
-Delhi
-Apply by:
-01 Apr 2026
-Monitoring Coordinator
-Intas Foundation
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Individual Consultant – Technical support on Foun...
-UNICEF
-Location:
-Rajasthan
-Apply by:
-09 Mar 2026
-Multiple Vacancies
-AIDENT Social Welfare Organisation (ASWO)
-Location:
-Uttar Pradesh
-Apply by:
-16 Mar 2026
-Head of Accounts &amp; Finance
-Watershed Organization Trust (WOTR)
+Regional Coordinator
+Bharat Rural Livelihoods Foundation (BRLF)
 Location:
 Maharashtra
 Apply by:
-01 Apr 2026
-Sr. Manager/Manager-Sustainable Cotton Programmes
-Aga Khan Rural Support Programme India (AKRSP Ind...
-Location:
-Gujarat
-Apply by:
-01 Apr 2026
-Project Manager – Vocational and Skill Development
-White Lotus Trust
-Location:
-Delhi
-Apply by:
-01 Apr 2026
+18 Mar 2026
+Project Nurse 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Project Technical Support 1
+Centre for Chronic Disease Control (CCDC)
+Location:
+India
+Apply by:
+15 Mar 2026
+Block Academic Coordinator
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
+District Program Manager
+Language and Learning Foundation (LLF)
+Location:
+Chhattisgarh
+Apply by:
+02 Apr 2026
 Jobseekers
 Register
 Login
@@ -8577,7 +8278,7 @@
         </is>
       </c>
       <c r="H37" s="1" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I37" s="1" t="inlineStr">
         <is>

--- a/all_grants.xlsx
+++ b/all_grants.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I86"/>
+  <dimension ref="A1:I83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -489,42 +489,55 @@
       <c r="B2" s="1" t="inlineStr"/>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>RFQ - Construction of Grey water treatment, Water tank, New Borewell, Toil...</t>
+          <t>EoI - Construction &amp; Infrastructure Works – Schools Of Pali And Jodhpur D...</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>WaterAid India | Raichur District, Karnataka
-International Development - RFQ - Construction of Grey water treatment, Water tank, New Borewell, Toilet Retrofitting, Rainwater Harvesting in 6 Gram panchayats..., WaterAid India, Karnataka - DevNetJobsIndia.org
+          <t>Ashray Foundation | Pali And Jodhpur Districts, Rajasthan
+International Development - EoI -  Construction &amp; Infrastructure Works – Schools Of Pali And Jodhpur Districts, Rajasthan, Ashray Foundation, Rajasthan - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
 Register
 Home
-Value M ... Read More</t>
+Value Membership
+Broadcast Resume ... Read More</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>• Terms and Conditions:
-Selected vendor will be received the bidding confirmation within 10 days from the last day of RFQ (last day of quotation submission date) and the other vendors can consider the bidding has been closed and work assignment has been completed; no specified mails will be sent about selection of vendors.
-Quotation should send to
-waiprocurementbengaluru@wateraid.org.
-For detailed information, please check the complete version of the RFQ attached below.
+          <t>• Scope of Work:
+Construction of Tin Sheds (12) and Additional Classrooms (15) in Govt. Schools, Upgradation of Sports Stadium (2)
+• Eligibility Criteria:
+Interested agencies must meet the following requirements:
+Valid statutory registrations (GST, PAN, etc.).
+Minimum relevant experience of 3 years in same activity is mandatory
+Demonstrated capacity and team to execute projects within strict timelines and quality
+• Submission Details:
+Interested agencies are requested to submit their EOI along with: Company Profile, Details of Relevant Project Experience, Copies of Necessary Registration &amp; Compliance Documents and Geo-tagged Photographs of the work undertaken, if any
+Last Date for Submission &amp; mail id for submission:
+04/03/2026 and
+tenders@ashrayfoundation.org
+Note: Ashray Foundation reserves the right to accept or reject any or all proposals without assigning any reason.
 • Job Email ID:
-waiprocurementbengaluru(at)wateraid.org
-Download Attachment:
-Tender Notice for open tendering_WRC - RAICHUR.pdf
+tenders(at)ashrayfoundation.org
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
 Apply by:
-03 Mar 2026
+04 Mar 2026
 Access all the jobs and get ahead!
 Subscribe to Value Membership Now!
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -581,54 +594,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFP - Requirement of Agency for Creating High Qua...
-Nature Conservancy India Solutions Private Limite...
-Location:
-Delhi
-Apply by:
-20 Mar 2026
-Programme officers (Education &amp; Life Skills Educa...
-Butterflies NGO
-Location:
-Delhi
+Documentation / Program Officer
+Pragati Path Foundation
+Location:
+Uttar Pradesh
+Apply by:
+25 Mar 2026
+Accounts Officer
+Jana Kalayana Samakhya
+Location:
+Odisha
+Apply by:
+30 Mar 2026
+Manager - Accounts &amp; Finance
+(Value Members only)
+Location:
+Rajasthan
+Apply by:
+13 Mar 2026
+Project Coordinator
+Asra Samajik Lok Kalyan Samiti
+Location:
+Madhya Pradesh
+Apply by:
+30 Mar 2026
+Account Manager
+(Value Members only)
+Location:
+Odisha
+Apply by:
+10 Mar 2026
+Resource Person, Teacher Support – Ashram School ...
+Kavana Charitable Trust
+Location:
+Karnataka
+Apply by:
+02 Apr 2026
+Teach Manager, Child Development Team (Dual Role)
+U&amp;I Trust
+Location:
+India
+Apply by:
+31 Mar 2026
+Rural India Fellowship
+Katakhali Swapnopuron Welfare Society
+Location:
+West Bengal
 Apply by:
 15 Mar 2026
-RFQ: Construction of New gated check dams, De-sil...
-WaterAid India
-Location:
-Telangana
-Apply by:
-08 Mar 2026
-Regional Coordinator
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-Maharashtra
-Apply by:
-18 Mar 2026
-Project Nurse 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Project Technical Support 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Block Academic Coordinator
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-District Program Manager
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
 Jobseekers
 Register
 Login
@@ -663,7 +676,7 @@
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>03-03-2026</t>
+          <t>04-03-2026</t>
         </is>
       </c>
       <c r="H2" s="1" t="n">
@@ -671,7 +684,7 @@
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287688</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287610</t>
         </is>
       </c>
     </row>
@@ -684,722 +697,10 @@
       <c r="B3" s="1" t="inlineStr"/>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>RFP – EOI for the Establishment of Recharge Shaft</t>
+          <t>EoI - Mobile Cancer Screening Project – Ut Of Andaman &amp; Nicobar Islands</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>PHD Rural Development Foundation | Alwar and Jaipur districts, Rajasthan
-International Development - RFP – EOI for the Establishment of Recharge Shaft, PHD Rural Development Foundation, Rajasthan - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders ... Read More</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>• Only those firms that qualify in the technical bid will be considered for the price bid. The price bid will have to be submitted separately in a sealed envelope later, based on the scope of work, which will be shared with the successful technical bidders.
-Therefore, experienced vendors are invited to submit the technical bid as follows. The technical bid must include the following relevant documents (items (i) to (xi):
-Technical criteria required to be submitted by the bidder:
-a. The vendor must have relevant work experience.
-b. The vendor must have experience of successful completion of at least one similar project/work order of a minimum value of Rs. 2-5.0 lakhs during the last 2 years.
-The bidder must submit the following documents:
-Company Profile/List of projects completed in the last 3 years
-GST Certificate
-PAN Card
-Aadhaar Card
-Certified Balance Sheet/Turnover
-MSME Registration Certificate (In case of non-registration, please share a declaration)
-PF Registration (In case of non-registration, please share a declaration)
-ESIC Registration (In case of non-registration, please share a declaration)
-Registration under the Contract Labour (Regulation and Abolition) Act, 1970
-Whether the firm has any legal suit/criminal case pending against it for violation of EPF/ESI, Minimum Wages Act or other laws (provide details). The bidder must attach a certificate (in the technical bid) stating that no criminal/legal case is pending or under consideration against them.
-Work orders/Purchase orders/Relevant documents for experience in similar/relevant work (Minimum 3 work orders should be shared for the last 2 years only, at least one work order should be of a minimum value of Rs. 2-5.0 lakhs)
-• How to apply:
-• Send all relevant documents to the email ID:
-rdf@phdcci.in
-Note:
-Last date for submission of documents is on or before 3
-rd
-March , 2026
-The successful bidder will have to enter into a detailed contract agreement with PHDRDF on a non-judicial stamp paper of Rs. (in figures) (in words) for each work.
-• Job Email ID:
-rdf(at)phdcci.in
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-03 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-RFP - Requirement of Agency for Creating High Qua...
-Nature Conservancy India Solutions Private Limite...
-Location:
-Delhi
-Apply by:
-20 Mar 2026
-Programme officers (Education &amp; Life Skills Educa...
-Butterflies NGO
-Location:
-Delhi
-Apply by:
-15 Mar 2026
-RFQ: Construction of New gated check dams, De-sil...
-WaterAid India
-Location:
-Telangana
-Apply by:
-08 Mar 2026
-Regional Coordinator
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-Maharashtra
-Apply by:
-18 Mar 2026
-Project Nurse 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Project Technical Support 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Block Academic Coordinator
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-District Program Manager
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>03-03-2026</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287598</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr"/>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>RFP- for Hiring a Resource Person/Agency Development of MEAL Questionnaire...</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Parmarth Samaj Sevi Sansthan | Jhansi, Uttar Pradesh
-International Development - RFP- for Hiring a Resource Person/Agency Development of MEAL Questionnaires and Processes for CommCare Tool, Parmarth Samaj Sevi Sansthan, Uttar Pradesh - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Mem ... Read More</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>• Introduction and context:
-Parmarth Samaj Sevi Sansthan
-is a grassroots organization dedicated to water crisis mitigation in the water-stressed Bundelkhand region of UP &amp; MP since 1996 intending to bring qualitative improvement and changes in the lives of the vulnerable people. Parmarth’s strength is its strong community connection and its commitment to the betterment of downtrodden society. Parmarth works with various stakeholders; institutions, corporate entities, the government, local communities, and individuals to provide timely interventions in water conservation, environment protection, village development, sustainable agriculture, river rejuvenation, sanitation &amp; and waste management, women empowerment, education, and skill development.
-About the project, including project duration
-The project
-Women 4 Water
-Welthungerhilfe
-(WHH) and BMZ
-(Germany). Along with India, it is being implemented by  Parmarth in UP.
-Objective-
-Women's participation and influence in water governance and management will be strengthened, improving access to clean water and more equitable distribution of water resources for rural populations in India.
-Outcome-
-In selected districts of Uttar Pradesh, Bihar and Jharkhand of Selected Blocks, gender equality is being integrated and institutionalized into local self-governance institutions and public water management programs.
-Project area details-
-We are working within  222-gram panchayats across Three state Uttar Pradesh, Bihar, Jharkahnd. The majority of the population in these areas belongs to underprivileged communities, with agriculture being their primary source of livelihood. Our efforts are focused on improving the women's socio-economic conditions of these communities by addressing their unique challenges and needs.
-1-     Background of the Assignment-
-We are implementing development programs focused on community empowerment, water security, gender equality, and governance strengthening. To strengthen Monitoring, Evaluation, Accountability, and Learning (MEAL) systems, the organization seeks to develop standardized digital questionnaires and processes aligned with the approved Monitoring Framework (2023–2027) and integrate them into the CommCare platform.
-2-     Objectives of the assignment
-The primary objective of this assignment is:
-To develop a comprehensive set of structured questionnaires aligned with the approved MEAL indicators.
-To design a standardized Mentoring process framework, including case management for digital data collection using the CommCare tool.
-To ensure indicator-wise data flow, reporting structure, and dashboard readiness.
-Handholding support for data collection.
-• 3. Scope of Work
-The selected Resource Person/Agency will be responsible for the following:
-3.1 Review and Alignment
-Review the existing Monitoring Framework (2023–2027).
-Map all output, outcome, and impact indicators.
-Identify data collection frequency, sources, and verification mechanisms.
-3.2 Questionnaire Development
-Analysis of baseline questionnaire and monitoring format to develop questionnaire
-Ensure questionnaires are: Indicator-linked , Logically sequenced, Gender-sensitive and inclusive ,Compatible with digital platforms (CommCare-ready structure)
-3.3 CommCare Tool Structuring
-Convert questionnaires into CommCare-compatible formats.
-A section on Case Management and follow-up:
-a case-based tracking system in CommCare for:
-EWRs / Jal Sahelis / VWSCs / Community leaders (as relevant); Household-level follow-up (if required)
-*Case lifecycle stages (opened → verified → action → resolved → closed)
-*Registration and follow-up forms. - Linkage between cases and events/trainings/meetings
-Define:
-Skip logic, Validation rules, Data constraints, Mandatory fields, Ensure user-friendly data entry structure.
-3.4 MEAL Process Development
-Develop a clear data flow mechanism from field to dashboard.
-Define roles and responsibilities for:
-Data collection, Data verification, Data validation, Data reporting
-Develop a guideline for data collection and quality assurance.
-3.5 Capacity Building
-Conduct orientation/training (online/offline)
-for staff on
-:
-Use of tools, Indicator understanding, Form navigation.
-4.  METHODOLOGY
-Review of MEAL framework, logframe, and indicators for tool finalisation.
-5. Deliverables
-The Resource Person/Agency is expected to submit:
-Inception Report (with work plan and methodology)
-Review the existing document and standardise the questionnaire
-Develop a data flow matrix for Commcare.
-Develop guidelines for field data collection.
-Filed testing through CommCare and synchronise functionality.
-Assignment completion report.
-6. Duration of Assignment
-The assignment is expected to be completed within 30–45 days from the date of contract signing.
-A detailed timeline with milestones should be proposed by the applicant.
-• 7. Eligibility Criteria
-Interested applicants must:
-Have proven experience in MEAL system development.
-Have experience working with digital data collection tools (preferably CommCare).
-Demonstrate experience in development sector programs (Water, Governance, Gender, Livelihood, etc.).
-Have at least 5+ years of relevant experience.
-Provide samples of similar assignments completed.
-Proposal Submission Process
-Offers will be accepted by individual consultants, commercial companies, NGOs and academics until the fill-in date.
-Applicants have to provide
-a technical and financial offer
-The
-technical part
-of the offer should include reference to the perceived feasibility of the ToR. It should also include a brief description of the overall design and methodology of the evaluation and a workplan/adaptations to the timeline at hand (maximum 4 pages).
-The Consultant’s choice of country/countries for tendering must be clearly mentioned in the proposal
-.
-The
-financial part
-includes a proposed budget for the complete evaluation. It should state the fees per working day (plus the respective
-GST
-, if applicable), the number of working days proposed and other costs. Proof of professional registration and taxation is also required (e.g. by providing the evaluator(s) tax number).
-• Selection Criteria
-Financial proposal (40%)
-Technical proposal (60%) incl. (a) survey design, (b) experience and track record of the consultant engaging in similar assignments, and (c) knowledge of the region.
-Timeline
-Assignment Fees &amp; Reimbursement of Costs:
-20% upon submission of Inception Report
-30% upon submission of Draft Tools &amp; CommCare Structure
-50% upon final approval and submission of all deliverables
-Terms of Payments:
-As per the payment schedule, payment will be transferred through NEFT and cheque. TDS will be conducted as per income tax norms.
-Confidentiality
-- The parties will treat all discussions and documents relating to this TOR as confidential. Any document, tools, templates, pictures, video clips, etc. developed through this assignment is the property of Parmarth and will have sole ownership of it.
-Note- For more information , please see the annexure.
-Contact Information
-:
-helpdesk.parmarth@parmarthsanstha.in
-copy to
-pssshrjhansi@gmail.com
-Deadline for Submission
-: 03 March, 2026
-• Job Email ID:
-helpdesk.parmarth(at)parmarthsanstha.in
-Download Attachment:
-Annexure.docx
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-03 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-RFP - Requirement of Agency for Creating High Qua...
-Nature Conservancy India Solutions Private Limite...
-Location:
-Delhi
-Apply by:
-20 Mar 2026
-Programme officers (Education &amp; Life Skills Educa...
-Butterflies NGO
-Location:
-Delhi
-Apply by:
-15 Mar 2026
-RFQ: Construction of New gated check dams, De-sil...
-WaterAid India
-Location:
-Telangana
-Apply by:
-08 Mar 2026
-Regional Coordinator
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-Maharashtra
-Apply by:
-18 Mar 2026
-Project Nurse 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Project Technical Support 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Block Academic Coordinator
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-District Program Manager
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>03-03-2026</t>
-        </is>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287368</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr"/>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>EoI - Construction &amp; Infrastructure Works – Schools Of Pali And Jodhpur D...</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Ashray Foundation | Pali And Jodhpur Districts, Rajasthan
-International Development - EoI -  Construction &amp; Infrastructure Works – Schools Of Pali And Jodhpur Districts, Rajasthan, Ashray Foundation, Rajasthan - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume ... Read More</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>• Scope of Work:
-Construction of Tin Sheds (12) and Additional Classrooms (15) in Govt. Schools, Upgradation of Sports Stadium (2)
-• Eligibility Criteria:
-Interested agencies must meet the following requirements:
-Valid statutory registrations (GST, PAN, etc.).
-Minimum relevant experience of 3 years in same activity is mandatory
-Demonstrated capacity and team to execute projects within strict timelines and quality
-• Submission Details:
-Interested agencies are requested to submit their EOI along with: Company Profile, Details of Relevant Project Experience, Copies of Necessary Registration &amp; Compliance Documents and Geo-tagged Photographs of the work undertaken, if any
-Last Date for Submission &amp; mail id for submission:
-04/03/2026 and
-tenders@ashrayfoundation.org
-Note: Ashray Foundation reserves the right to accept or reject any or all proposals without assigning any reason.
-• Job Email ID:
-tenders(at)ashrayfoundation.org
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-04 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-RFP - Requirement of Agency for Creating High Qua...
-Nature Conservancy India Solutions Private Limite...
-Location:
-Delhi
-Apply by:
-20 Mar 2026
-Programme officers (Education &amp; Life Skills Educa...
-Butterflies NGO
-Location:
-Delhi
-Apply by:
-15 Mar 2026
-RFQ: Construction of New gated check dams, De-sil...
-WaterAid India
-Location:
-Telangana
-Apply by:
-08 Mar 2026
-Regional Coordinator
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-Maharashtra
-Apply by:
-18 Mar 2026
-Project Nurse 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Project Technical Support 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Block Academic Coordinator
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-District Program Manager
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G5" s="1" t="inlineStr">
-        <is>
-          <t>04-03-2026</t>
-        </is>
-      </c>
-      <c r="H5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287610</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr"/>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>EoI - Mobile Cancer Screening Project – Ut Of Andaman &amp; Nicobar Islands</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Ashray Foundation | Sri Vijaya Puram (Port Blair), Andaman and Nicobar Islands
 International Development - EoI - Mobile Cancer Screening Project – Ut Of Andaman &amp; Nicobar Islands, Ashray Foundation, Andaman and Nicobar Islands - DevNetJobsIndia.org
@@ -1411,7 +712,7 @@
 Value Membership ... Read More</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>• Scope of Work:
 Requirement of Vehicle:
@@ -1446,6 +747,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -1502,54 +809,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFP - Requirement of Agency for Creating High Qua...
-Nature Conservancy India Solutions Private Limite...
-Location:
-Delhi
-Apply by:
-20 Mar 2026
-Programme officers (Education &amp; Life Skills Educa...
-Butterflies NGO
-Location:
-Delhi
+Documentation / Program Officer
+Pragati Path Foundation
+Location:
+Uttar Pradesh
+Apply by:
+25 Mar 2026
+Accounts Officer
+Jana Kalayana Samakhya
+Location:
+Odisha
+Apply by:
+30 Mar 2026
+Manager - Accounts &amp; Finance
+(Value Members only)
+Location:
+Rajasthan
+Apply by:
+13 Mar 2026
+Project Coordinator
+Asra Samajik Lok Kalyan Samiti
+Location:
+Madhya Pradesh
+Apply by:
+30 Mar 2026
+Account Manager
+(Value Members only)
+Location:
+Odisha
+Apply by:
+10 Mar 2026
+Resource Person, Teacher Support – Ashram School ...
+Kavana Charitable Trust
+Location:
+Karnataka
+Apply by:
+02 Apr 2026
+Teach Manager, Child Development Team (Dual Role)
+U&amp;I Trust
+Location:
+India
+Apply by:
+31 Mar 2026
+Rural India Fellowship
+Katakhali Swapnopuron Welfare Society
+Location:
+West Bengal
 Apply by:
 15 Mar 2026
-RFQ: Construction of New gated check dams, De-sil...
-WaterAid India
-Location:
-Telangana
-Apply by:
-08 Mar 2026
-Regional Coordinator
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-Maharashtra
-Apply by:
-18 Mar 2026
-Project Nurse 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Project Technical Support 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Block Academic Coordinator
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-District Program Manager
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
 Jobseekers
 Register
 Login
@@ -1577,38 +884,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F6" s="1" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G6" s="1" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>04-03-2026</t>
         </is>
       </c>
-      <c r="H6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="1" t="inlineStr">
+      <c r="H3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287612</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr"/>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr"/>
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>RFQ - for Case Study</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>MAMTA Health Institute for Mother and Child (MAMTA) | India
 International Development - RFQ - for Case Study, MAMTA Health Institute for Mother and Child (MAMTA), India - DevNetJobsIndia.org
@@ -1625,7 +932,7 @@
 Jobseeke ... Read More</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>• Scope of Work
 Mamta–HIMC
@@ -1701,6 +1008,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -1757,54 +1070,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFP - Requirement of Agency for Creating High Qua...
-Nature Conservancy India Solutions Private Limite...
-Location:
-Delhi
-Apply by:
-20 Mar 2026
-Programme officers (Education &amp; Life Skills Educa...
-Butterflies NGO
-Location:
-Delhi
+Documentation / Program Officer
+Pragati Path Foundation
+Location:
+Uttar Pradesh
+Apply by:
+25 Mar 2026
+Accounts Officer
+Jana Kalayana Samakhya
+Location:
+Odisha
+Apply by:
+30 Mar 2026
+Manager - Accounts &amp; Finance
+(Value Members only)
+Location:
+Rajasthan
+Apply by:
+13 Mar 2026
+Project Coordinator
+Asra Samajik Lok Kalyan Samiti
+Location:
+Madhya Pradesh
+Apply by:
+30 Mar 2026
+Account Manager
+(Value Members only)
+Location:
+Odisha
+Apply by:
+10 Mar 2026
+Resource Person, Teacher Support – Ashram School ...
+Kavana Charitable Trust
+Location:
+Karnataka
+Apply by:
+02 Apr 2026
+Teach Manager, Child Development Team (Dual Role)
+U&amp;I Trust
+Location:
+India
+Apply by:
+31 Mar 2026
+Rural India Fellowship
+Katakhali Swapnopuron Welfare Society
+Location:
+West Bengal
 Apply by:
 15 Mar 2026
-RFQ: Construction of New gated check dams, De-sil...
-WaterAid India
-Location:
-Telangana
-Apply by:
-08 Mar 2026
-Regional Coordinator
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-Maharashtra
-Apply by:
-18 Mar 2026
-Project Nurse 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Project Technical Support 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Block Academic Coordinator
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-District Program Manager
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
 Jobseekers
 Register
 Login
@@ -1832,38 +1145,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F7" s="1" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>Safety</t>
         </is>
       </c>
-      <c r="G7" s="1" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>04-03-2026</t>
         </is>
       </c>
-      <c r="H7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" s="1" t="inlineStr">
+      <c r="H4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287442</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr"/>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr"/>
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>RFP - Training of Volunteers &amp; Help Desk Operators</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Ghoghardiha Prakhand Swarajya Vikas Sangh (GPSVS) | Bihar, Jharkhand
 International Development - RFP - Training of Volunteers &amp; Help Desk Operators, Ghoghardiha Prakhand Swarajya Vikas Sangh (GPSVS), Bihar, Jharkhand - DevNetJobsIndia.org
@@ -1876,7 +1189,7 @@
 Broadcast ... Read More</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>• 3. Scope of Work
 The selected agency/consultant will undertake the following:
@@ -2038,6 +1351,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -2094,54 +1413,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFP - Requirement of Agency for Creating High Qua...
-Nature Conservancy India Solutions Private Limite...
-Location:
-Delhi
-Apply by:
-20 Mar 2026
-Programme officers (Education &amp; Life Skills Educa...
-Butterflies NGO
-Location:
-Delhi
+Documentation / Program Officer
+Pragati Path Foundation
+Location:
+Uttar Pradesh
+Apply by:
+25 Mar 2026
+Accounts Officer
+Jana Kalayana Samakhya
+Location:
+Odisha
+Apply by:
+30 Mar 2026
+Manager - Accounts &amp; Finance
+(Value Members only)
+Location:
+Rajasthan
+Apply by:
+13 Mar 2026
+Project Coordinator
+Asra Samajik Lok Kalyan Samiti
+Location:
+Madhya Pradesh
+Apply by:
+30 Mar 2026
+Account Manager
+(Value Members only)
+Location:
+Odisha
+Apply by:
+10 Mar 2026
+Resource Person, Teacher Support – Ashram School ...
+Kavana Charitable Trust
+Location:
+Karnataka
+Apply by:
+02 Apr 2026
+Teach Manager, Child Development Team (Dual Role)
+U&amp;I Trust
+Location:
+India
+Apply by:
+31 Mar 2026
+Rural India Fellowship
+Katakhali Swapnopuron Welfare Society
+Location:
+West Bengal
 Apply by:
 15 Mar 2026
-RFQ: Construction of New gated check dams, De-sil...
-WaterAid India
-Location:
-Telangana
-Apply by:
-08 Mar 2026
-Regional Coordinator
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-Maharashtra
-Apply by:
-18 Mar 2026
-Project Nurse 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Project Technical Support 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Block Academic Coordinator
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-District Program Manager
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
 Jobseekers
 Register
 Login
@@ -2169,64 +1488,89 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F8" s="1" t="inlineStr">
+      <c r="F5" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G8" s="1" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>05-03-2026</t>
         </is>
       </c>
-      <c r="H8" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I8" s="1" t="inlineStr">
+      <c r="H5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287444</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr"/>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Hiring an Agency to Conduct Evidence Synthesis, Co-Design Key Interv...</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Project Concern International India (PCI India) | India
-International Development - RFP - Hiring an Agency to Conduct Evidence Synthesis, Co-Design Key Intervention Components, and Develop a Scalable and Operational Implementation, Project Concern International India (PCI India), India - DevNetJobs ... Read More</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>• Last   Date for Submission of bids
-05
+      <c r="B6" s="1" t="inlineStr"/>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>RFQ - for Report Designing</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>MAMTA Health Institute for Mother and Child (MAMTA) | India
+International Development - RFQ - for Report Designing, MAMTA Health Institute for Mother and Child (MAMTA), India - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jo ... Read More</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>• Scope of Work
+This is to bring to your kind attention that we want to hire an agency to design Report the total no. of pages in the report are 300 maximum (including cover page and back cover) and document size are A4. The topic of report would be on maternal health, environment, community health, etc.
+The Terms of Reference are as follows:
+Kindly provide the quotations for each of the above items separately, including GST by 5th March 2026.
+Kindly provide separate quotations for report design per page.
+Work must be completed in 2 months from the date of this order accepted by the vendor.
+MAMTA will pay the amounts to the vendor after verification application files by MAMTA and submission of the original invoice.
+The taxes will be deducted as per the relevant rules of the Govt. of India.
+Others
+MAMTA HIMC reserves the right to reject all or any quotation(s), wholly or partly, without assigning any reason whatsoever.
+MAMTA HIMC team reserves the right to request the top 3 quotations for an in-person discussion.
+MAMTA reserves the right, in its sole discretion, to conduct negotiations in accordance with MAMTA and/donor’s policies and procedures and to request additional information from prospective Bidders to supplement or clarify any aspect of the proposal documents if such revisions will be in the interest of our programs
+Only shortlisted agencies will be contacted.
+You must pay all sub-vendor payments before submitting the hard copy of the final bills and supporting documents to MAMTA HIMC.
+MAMTA shall not be legally bound by any award notice issued for this RFQ until an Agreement is duly signed and executed with the winning bidder(s).
+Further details will be shared with shortlisted agencies.
+Application Process –
+All applicants (company/agency/institutional/individual) if applicable, should follow the Government of India guidelines/policy for the Prevention of Sexual Harassment (PoSH) at the workplace. As part of the application process, you are required to share the status of the Internal Complaints Committee (ICC). If the committee is not incorporated, then under what criteria is it not enacted?
+Interested agencies/organizations/individuals must submit the proposal for the
+report designing
+highlighting the process, portfolio of past work, financial proposal and the timeline for the project. The technical and financial quotations should be sent in soft copy over email at
+rfp@mamtahimc.in
+by
+5
 th
-March 2026
-Proposals   to be submitted at
-procdelhi@pciglobal.in
-Receipt of Proposals
-Technical and Financial   proposals should be submitted as separate attachments
-and to be submitted
-in a single email
-attachments.
-NOTE
-:
-(a) The agencies registered under the Societies/Trust/Foreign Contribution (Regulation) Act, 2010, are not required to submit applications. Proposals from these agencies will not be considered.
-For detailed information, please check the complete version of the RFP attached below.
+March 2026 With the subject line: “Quotation for Report Designing”.
+• The quotations should be made separately for the event and states. We encourage local vendors to apply. Incomplete applications and applications received after the deadline will not be considered for the selection process.
+The selection team will only contact applicants who have been shortlisted for the process.
+• Mamta HIMC has a policy of erasing all confidential information, ideas/concepts submitted in proposals/applications after the selection process is completed.
+"Confidentiality of Applicants"
+Mamta shall not be liable to share the list of shortlisted applicants with any party outside the organization. The organization takes all necessary measures to protect the confidentiality of applicants, and shall not disclose any personal information, process, and data related to the application, except as required by law.
 • Job Email ID:
-procdelhi(at)pciglobal.in
-Download Attachment:
-RFP-AGENCY TO CONDUCT EVIDENCE SYNTHESIS, CO-DESIGN KEY INTERVENTION ..........doc
+rfp(at)mamtahimc.in
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
@@ -2237,6 +1581,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -2293,54 +1643,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFP - Requirement of Agency for Creating High Qua...
-Nature Conservancy India Solutions Private Limite...
-Location:
-Delhi
-Apply by:
-20 Mar 2026
-Programme officers (Education &amp; Life Skills Educa...
-Butterflies NGO
-Location:
-Delhi
+Documentation / Program Officer
+Pragati Path Foundation
+Location:
+Uttar Pradesh
+Apply by:
+25 Mar 2026
+Accounts Officer
+Jana Kalayana Samakhya
+Location:
+Odisha
+Apply by:
+30 Mar 2026
+Manager - Accounts &amp; Finance
+(Value Members only)
+Location:
+Rajasthan
+Apply by:
+13 Mar 2026
+Project Coordinator
+Asra Samajik Lok Kalyan Samiti
+Location:
+Madhya Pradesh
+Apply by:
+30 Mar 2026
+Account Manager
+(Value Members only)
+Location:
+Odisha
+Apply by:
+10 Mar 2026
+Resource Person, Teacher Support – Ashram School ...
+Kavana Charitable Trust
+Location:
+Karnataka
+Apply by:
+02 Apr 2026
+Teach Manager, Child Development Team (Dual Role)
+U&amp;I Trust
+Location:
+India
+Apply by:
+31 Mar 2026
+Rural India Fellowship
+Katakhali Swapnopuron Welfare Society
+Location:
+West Bengal
 Apply by:
 15 Mar 2026
-RFQ: Construction of New gated check dams, De-sil...
-WaterAid India
-Location:
-Telangana
-Apply by:
-08 Mar 2026
-Regional Coordinator
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-Maharashtra
-Apply by:
-18 Mar 2026
-Project Nurse 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Project Technical Support 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Block Academic Coordinator
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-District Program Manager
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
 Jobseekers
 Register
 Login
@@ -2368,38 +1718,488 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F9" s="1" t="inlineStr">
+      <c r="F6" s="1" t="inlineStr">
         <is>
           <t>Safety</t>
         </is>
       </c>
-      <c r="G9" s="1" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>05-03-2026</t>
         </is>
       </c>
-      <c r="H9" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" s="1" t="inlineStr">
+      <c r="H6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287643</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>Request for Quotation for Case Study</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Institute for Global Development (IGD) | Uttar Pradesh, Andhra Pradesh, Telangana, Karnataka
+International Development - Request for Quotation for Case Study, Institute for Global Development (IGD), Andhra Pradesh, Telangana, Karnataka - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value M ... Read More</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>• Scope of Work
+IGD invites quotations from qualified individuals or agencies to develop case studies documenting key program activities. The case studies will be developed focusing on some campaign components
+The selected individual/agency will be required to work across 8-9 districts, with case study selection across seven states/districts as follows:
+Three in Uttar Pradesh (Bahraich, Chandauli, and Gorakhpur)
+Two districts in Andhra Pradesh
+Two districts in Telangana
+Two districts in Karnataka
+The case studies will focus on documenting the activities listed above, highlighting implementation processes, key achievements, challenges, and best practices.
+Terms of Reference
+Develop
+4 case studies per Districts
+across each of the 8–9 selected districts.
+Quotations must include a
+breakdown of costs
+for each item (including food, transport, accommodation, and GST).
+The assignment must be
+completed within two months
+from the date of contract acceptance.
+Payment will be released
+upon submission of original documentation
+and
+invoice verification
+.
+Applicable
+tax deductions
+will be made in accordance with Government of India regulations.
+Others
+IGD reserves the right to reject all or any quotation(s), wholly or partly, without assigning any reason whatsoever.
+IGD team reserves the right to request the top 3 quotations for an in-person discussion.
+IGD reserves the right, in its sole discretion, to conduct negotiations in accordance with IGD and/donor’s policies and procedures and to request additional information from prospective Bidders to supplement or clarify any aspect of the proposal documents if such revisions will be in the interest of our programs
+Only shortlisted agencies will be contacted.
+IGD shall not be legally bound by any award notice issued for this RFQ until an Agreement is duly signed and executed with the winning bidder(s).
+Further details will be shared with shortlisted agencies.
+Application Process –
+All applicants (company/agency/institutional) if applicable, should follow the Government of India guidelines/policy for the Prevention of Sexual Harassment (PoSH) at the workplace. As part of the application process, you are required to share the status of the Internal Complaints Committee (ICC). If the committee is not incorporated, then under what criteria is it not enacted?
+Interested agencies/organizations/individuals must submit the proposal for the
+Case Study
+, highlighting the process, portfolio of past work, financial proposal and the timeline for the project. The technical and financial quotations should be sent in soft copy over email at
+jobs@igdindia.org
+by
+5
+th
+March 2026 with subject line “Quotation for
+Case Study
+Development for Campaign Activities
+”.
+• We encourage local vendors to apply. Incomplete applications and applications received after the deadline will not be considered for the selection process.
+The selection team will only contact applicants who have been shortlisted for the process.
+• IGD has a policy of erasing all confidential information, ideas/concepts submitted in proposals/applications after the selection process is completed.
+"Confidentiality of Applicants"
+IGD shall not be liable to share the list of shortlisted applicants with any party outside the organization. The organization takes all necessary measures to protect the confidentiality of applicants, and shall not disclose any personal information, process, and data related to the application, except as required by law.
+• Job Email ID:
+jobs(at)igdindia.org
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+05 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Associate (Programme Management)
+Indian Institute For Human Settlements (Iihs)
+Location:
+Karnataka
+Apply by:
+07 Mar 2026
+Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+Documentation / Program Officer
+Pragati Path Foundation
+Location:
+Uttar Pradesh
+Apply by:
+25 Mar 2026
+Accounts Officer
+Jana Kalayana Samakhya
+Location:
+Odisha
+Apply by:
+30 Mar 2026
+Manager - Accounts &amp; Finance
+(Value Members only)
+Location:
+Rajasthan
+Apply by:
+13 Mar 2026
+Project Coordinator
+Asra Samajik Lok Kalyan Samiti
+Location:
+Madhya Pradesh
+Apply by:
+30 Mar 2026
+Account Manager
+(Value Members only)
+Location:
+Odisha
+Apply by:
+10 Mar 2026
+Resource Person, Teacher Support – Ashram School ...
+Kavana Charitable Trust
+Location:
+Karnataka
+Apply by:
+02 Apr 2026
+Teach Manager, Child Development Team (Dual Role)
+U&amp;I Trust
+Location:
+India
+Apply by:
+31 Mar 2026
+Rural India Fellowship
+Katakhali Swapnopuron Welfare Society
+Location:
+West Bengal
+Apply by:
+15 Mar 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>05-03-2026</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287670</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr"/>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>RFP - Hiring an Agency to Conduct Evidence Synthesis, Co-Design Key Interv...</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Project Concern International India (PCI India) | India
+International Development - RFP - Hiring an Agency to Conduct Evidence Synthesis, Co-Design Key Intervention Components, and Develop a Scalable and Operational Implementation, Project Concern International India (PCI India), India - DevNetJobs ... Read More</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>• Last   Date for Submission of bids
+05
+th
+March 2026
+Proposals   to be submitted at
+procdelhi@pciglobal.in
+Receipt of Proposals
+Technical and Financial   proposals should be submitted as separate attachments
+and to be submitted
+in a single email
+attachments.
+NOTE
+:
+(a) The agencies registered under the Societies/Trust/Foreign Contribution (Regulation) Act, 2010, are not required to submit applications. Proposals from these agencies will not be considered.
+For detailed information, please check the complete version of the RFP attached below.
+• Job Email ID:
+procdelhi(at)pciglobal.in
+Download Attachment:
+RFP-AGENCY TO CONDUCT EVIDENCE SYNTHESIS, CO-DESIGN KEY INTERVENTION ..........doc
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+05 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Associate (Programme Management)
+Indian Institute For Human Settlements (Iihs)
+Location:
+Karnataka
+Apply by:
+07 Mar 2026
+Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+Documentation / Program Officer
+Pragati Path Foundation
+Location:
+Uttar Pradesh
+Apply by:
+25 Mar 2026
+Accounts Officer
+Jana Kalayana Samakhya
+Location:
+Odisha
+Apply by:
+30 Mar 2026
+Manager - Accounts &amp; Finance
+(Value Members only)
+Location:
+Rajasthan
+Apply by:
+13 Mar 2026
+Project Coordinator
+Asra Samajik Lok Kalyan Samiti
+Location:
+Madhya Pradesh
+Apply by:
+30 Mar 2026
+Account Manager
+(Value Members only)
+Location:
+Odisha
+Apply by:
+10 Mar 2026
+Resource Person, Teacher Support – Ashram School ...
+Kavana Charitable Trust
+Location:
+Karnataka
+Apply by:
+02 Apr 2026
+Teach Manager, Child Development Team (Dual Role)
+U&amp;I Trust
+Location:
+India
+Apply by:
+31 Mar 2026
+Rural India Fellowship
+Katakhali Swapnopuron Welfare Society
+Location:
+West Bengal
+Apply by:
+15 Mar 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>05-03-2026</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287312</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr"/>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="B9" s="1" t="inlineStr"/>
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>RFQ - for the Supply of Seeds</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>MAMTA Health Institute for Mother and Child (MAMTA) | India
 International Development - RFQ -  for the Supply of Seeds, MAMTA Health Institute for Mother and Child (MAMTA), India - DevNetJobsIndia.org
@@ -2415,7 +2215,7 @@
 Event ... Read More</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>• The terms and conditions for the purchase of seed:
 Provide seed percentage certificate of all Germination
@@ -2467,6 +2267,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -2523,54 +2329,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFP - Requirement of Agency for Creating High Qua...
-Nature Conservancy India Solutions Private Limite...
-Location:
-Delhi
-Apply by:
-20 Mar 2026
-Programme officers (Education &amp; Life Skills Educa...
-Butterflies NGO
-Location:
-Delhi
+Documentation / Program Officer
+Pragati Path Foundation
+Location:
+Uttar Pradesh
+Apply by:
+25 Mar 2026
+Accounts Officer
+Jana Kalayana Samakhya
+Location:
+Odisha
+Apply by:
+30 Mar 2026
+Manager - Accounts &amp; Finance
+(Value Members only)
+Location:
+Rajasthan
+Apply by:
+13 Mar 2026
+Project Coordinator
+Asra Samajik Lok Kalyan Samiti
+Location:
+Madhya Pradesh
+Apply by:
+30 Mar 2026
+Account Manager
+(Value Members only)
+Location:
+Odisha
+Apply by:
+10 Mar 2026
+Resource Person, Teacher Support – Ashram School ...
+Kavana Charitable Trust
+Location:
+Karnataka
+Apply by:
+02 Apr 2026
+Teach Manager, Child Development Team (Dual Role)
+U&amp;I Trust
+Location:
+India
+Apply by:
+31 Mar 2026
+Rural India Fellowship
+Katakhali Swapnopuron Welfare Society
+Location:
+West Bengal
 Apply by:
 15 Mar 2026
-RFQ: Construction of New gated check dams, De-sil...
-WaterAid India
-Location:
-Telangana
-Apply by:
-08 Mar 2026
-Regional Coordinator
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-Maharashtra
-Apply by:
-18 Mar 2026
-Project Nurse 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Project Technical Support 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Block Academic Coordinator
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-District Program Manager
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
 Jobseekers
 Register
 Login
@@ -2598,268 +2404,44 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F10" s="1" t="inlineStr">
+      <c r="F9" s="1" t="inlineStr">
         <is>
           <t>Safety</t>
         </is>
       </c>
-      <c r="G10" s="1" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>05-03-2026</t>
         </is>
       </c>
-      <c r="H10" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" s="1" t="inlineStr">
+      <c r="H9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287641</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr"/>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>RFQ - for Report Designing</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>MAMTA Health Institute for Mother and Child (MAMTA) | India
-International Development - RFQ - for Report Designing, MAMTA Health Institute for Mother and Child (MAMTA), India - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jo ... Read More</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>• Scope of Work
-This is to bring to your kind attention that we want to hire an agency to design Report the total no. of pages in the report are 300 maximum (including cover page and back cover) and document size are A4. The topic of report would be on maternal health, environment, community health, etc.
-The Terms of Reference are as follows:
-Kindly provide the quotations for each of the above items separately, including GST by 5th March 2026.
-Kindly provide separate quotations for report design per page.
-Work must be completed in 2 months from the date of this order accepted by the vendor.
-MAMTA will pay the amounts to the vendor after verification application files by MAMTA and submission of the original invoice.
-The taxes will be deducted as per the relevant rules of the Govt. of India.
-Others
-MAMTA HIMC reserves the right to reject all or any quotation(s), wholly or partly, without assigning any reason whatsoever.
-MAMTA HIMC team reserves the right to request the top 3 quotations for an in-person discussion.
-MAMTA reserves the right, in its sole discretion, to conduct negotiations in accordance with MAMTA and/donor’s policies and procedures and to request additional information from prospective Bidders to supplement or clarify any aspect of the proposal documents if such revisions will be in the interest of our programs
-Only shortlisted agencies will be contacted.
-You must pay all sub-vendor payments before submitting the hard copy of the final bills and supporting documents to MAMTA HIMC.
-MAMTA shall not be legally bound by any award notice issued for this RFQ until an Agreement is duly signed and executed with the winning bidder(s).
-Further details will be shared with shortlisted agencies.
-Application Process –
-All applicants (company/agency/institutional/individual) if applicable, should follow the Government of India guidelines/policy for the Prevention of Sexual Harassment (PoSH) at the workplace. As part of the application process, you are required to share the status of the Internal Complaints Committee (ICC). If the committee is not incorporated, then under what criteria is it not enacted?
-Interested agencies/organizations/individuals must submit the proposal for the
-report designing
-highlighting the process, portfolio of past work, financial proposal and the timeline for the project. The technical and financial quotations should be sent in soft copy over email at
-rfp@mamtahimc.in
-by
-5
-th
-March 2026 With the subject line: “Quotation for Report Designing”.
-• The quotations should be made separately for the event and states. We encourage local vendors to apply. Incomplete applications and applications received after the deadline will not be considered for the selection process.
-The selection team will only contact applicants who have been shortlisted for the process.
-• Mamta HIMC has a policy of erasing all confidential information, ideas/concepts submitted in proposals/applications after the selection process is completed.
-"Confidentiality of Applicants"
-Mamta shall not be liable to share the list of shortlisted applicants with any party outside the organization. The organization takes all necessary measures to protect the confidentiality of applicants, and shall not disclose any personal information, process, and data related to the application, except as required by law.
-• Job Email ID:
-rfp(at)mamtahimc.in
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-05 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-RFP - Requirement of Agency for Creating High Qua...
-Nature Conservancy India Solutions Private Limite...
-Location:
-Delhi
-Apply by:
-20 Mar 2026
-Programme officers (Education &amp; Life Skills Educa...
-Butterflies NGO
-Location:
-Delhi
-Apply by:
-15 Mar 2026
-RFQ: Construction of New gated check dams, De-sil...
-WaterAid India
-Location:
-Telangana
-Apply by:
-08 Mar 2026
-Regional Coordinator
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-Maharashtra
-Apply by:
-18 Mar 2026
-Project Nurse 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Project Technical Support 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Block Academic Coordinator
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-District Program Manager
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="G11" s="1" t="inlineStr">
-        <is>
-          <t>05-03-2026</t>
-        </is>
-      </c>
-      <c r="H11" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I11" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287643</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="inlineStr"/>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="B10" s="1" t="inlineStr"/>
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>ToR - State And National Level Consolidation Study On Government Schemes, ...</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Life Education And Development Support (Leads) And Ghoghardiha Prakhand Swarajya Vikas Sangh (GPSVS) | Jharkhand, Bihar
 International Development - ToR - State And National Level Consolidation Study On Government Schemes, Labour Rights &amp; Grievance Mechanisms - Safe Employment Guidebooks..., Life Ed ... Read More</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>• 3. Scope of Work
 The consultant/agency will adopt a policy-research and systems-analysis approach encompassing the following components:
@@ -2949,6 +2531,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -3005,54 +2593,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFP - Requirement of Agency for Creating High Qua...
-Nature Conservancy India Solutions Private Limite...
-Location:
-Delhi
-Apply by:
-20 Mar 2026
-Programme officers (Education &amp; Life Skills Educa...
-Butterflies NGO
-Location:
-Delhi
+Documentation / Program Officer
+Pragati Path Foundation
+Location:
+Uttar Pradesh
+Apply by:
+25 Mar 2026
+Accounts Officer
+Jana Kalayana Samakhya
+Location:
+Odisha
+Apply by:
+30 Mar 2026
+Manager - Accounts &amp; Finance
+(Value Members only)
+Location:
+Rajasthan
+Apply by:
+13 Mar 2026
+Project Coordinator
+Asra Samajik Lok Kalyan Samiti
+Location:
+Madhya Pradesh
+Apply by:
+30 Mar 2026
+Account Manager
+(Value Members only)
+Location:
+Odisha
+Apply by:
+10 Mar 2026
+Resource Person, Teacher Support – Ashram School ...
+Kavana Charitable Trust
+Location:
+Karnataka
+Apply by:
+02 Apr 2026
+Teach Manager, Child Development Team (Dual Role)
+U&amp;I Trust
+Location:
+India
+Apply by:
+31 Mar 2026
+Rural India Fellowship
+Katakhali Swapnopuron Welfare Society
+Location:
+West Bengal
 Apply by:
 15 Mar 2026
-RFQ: Construction of New gated check dams, De-sil...
-WaterAid India
-Location:
-Telangana
-Apply by:
-08 Mar 2026
-Regional Coordinator
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-Maharashtra
-Apply by:
-18 Mar 2026
-Project Nurse 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Project Technical Support 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Block Academic Coordinator
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-District Program Manager
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
 Jobseekers
 Register
 Login
@@ -3080,284 +2668,45 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F12" s="1" t="inlineStr">
+      <c r="F10" s="1" t="inlineStr">
         <is>
           <t>Governance, Learning</t>
         </is>
       </c>
-      <c r="G12" s="1" t="inlineStr">
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>05-03-2026</t>
         </is>
       </c>
-      <c r="H12" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I12" s="1" t="inlineStr">
+      <c r="H10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287504</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr"/>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>Request for Quotation for Case Study</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Institute for Global Development (IGD) | Uttar Pradesh, Andhra Pradesh, Telangana, Karnataka
-International Development - Request for Quotation for Case Study, Institute for Global Development (IGD), Andhra Pradesh, Telangana, Karnataka - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value M ... Read More</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>• Scope of Work
-IGD invites quotations from qualified individuals or agencies to develop case studies documenting key program activities. The case studies will be developed focusing on some campaign components
-The selected individual/agency will be required to work across 8-9 districts, with case study selection across seven states/districts as follows:
-Three in Uttar Pradesh (Bahraich, Chandauli, and Gorakhpur)
-Two districts in Andhra Pradesh
-Two districts in Telangana
-Two districts in Karnataka
-The case studies will focus on documenting the activities listed above, highlighting implementation processes, key achievements, challenges, and best practices.
-Terms of Reference
-Develop
-4 case studies per Districts
-across each of the 8–9 selected districts.
-Quotations must include a
-breakdown of costs
-for each item (including food, transport, accommodation, and GST).
-The assignment must be
-completed within two months
-from the date of contract acceptance.
-Payment will be released
-upon submission of original documentation
-and
-invoice verification
-.
-Applicable
-tax deductions
-will be made in accordance with Government of India regulations.
-Others
-IGD reserves the right to reject all or any quotation(s), wholly or partly, without assigning any reason whatsoever.
-IGD team reserves the right to request the top 3 quotations for an in-person discussion.
-IGD reserves the right, in its sole discretion, to conduct negotiations in accordance with IGD and/donor’s policies and procedures and to request additional information from prospective Bidders to supplement or clarify any aspect of the proposal documents if such revisions will be in the interest of our programs
-Only shortlisted agencies will be contacted.
-IGD shall not be legally bound by any award notice issued for this RFQ until an Agreement is duly signed and executed with the winning bidder(s).
-Further details will be shared with shortlisted agencies.
-Application Process –
-All applicants (company/agency/institutional) if applicable, should follow the Government of India guidelines/policy for the Prevention of Sexual Harassment (PoSH) at the workplace. As part of the application process, you are required to share the status of the Internal Complaints Committee (ICC). If the committee is not incorporated, then under what criteria is it not enacted?
-Interested agencies/organizations/individuals must submit the proposal for the
-Case Study
-, highlighting the process, portfolio of past work, financial proposal and the timeline for the project. The technical and financial quotations should be sent in soft copy over email at
-jobs@igdindia.org
-by
-5
-th
-March 2026 with subject line “Quotation for
-Case Study
-Development for Campaign Activities
-”.
-• We encourage local vendors to apply. Incomplete applications and applications received after the deadline will not be considered for the selection process.
-The selection team will only contact applicants who have been shortlisted for the process.
-• IGD has a policy of erasing all confidential information, ideas/concepts submitted in proposals/applications after the selection process is completed.
-"Confidentiality of Applicants"
-IGD shall not be liable to share the list of shortlisted applicants with any party outside the organization. The organization takes all necessary measures to protect the confidentiality of applicants, and shall not disclose any personal information, process, and data related to the application, except as required by law.
-• Job Email ID:
-jobs(at)igdindia.org
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-05 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-RFP - Requirement of Agency for Creating High Qua...
-Nature Conservancy India Solutions Private Limite...
-Location:
-Delhi
-Apply by:
-20 Mar 2026
-Programme officers (Education &amp; Life Skills Educa...
-Butterflies NGO
-Location:
-Delhi
-Apply by:
-15 Mar 2026
-RFQ: Construction of New gated check dams, De-sil...
-WaterAid India
-Location:
-Telangana
-Apply by:
-08 Mar 2026
-Regional Coordinator
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-Maharashtra
-Apply by:
-18 Mar 2026
-Project Nurse 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Project Technical Support 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Block Academic Coordinator
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-District Program Manager
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G13" s="1" t="inlineStr">
-        <is>
-          <t>05-03-2026</t>
-        </is>
-      </c>
-      <c r="H13" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I13" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287670</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="inlineStr"/>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr"/>
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>EoI - For Empanelment of agencies for Impact Assessment/ Evaluation Servic...</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Small Industries Development Bank of India (SIDBI) | India
 International Development - EoI - For Empanelment of agencies for Impact Assessment/ Evaluation Services under Programmes for Development and Impact, Small Industries Development Bank of India (SIDBI), India - DevNetJobsIndia.org
 Jobseekers ... Read More</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>• Please      note that all the information required as per the documents required for      responding to EOI needs to be provided. Incomplete information in these      areas may lead to non-selection.
 Modification      And/ Or Withdrawal of documents:
@@ -3430,6 +2779,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -3486,54 +2841,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFP - Requirement of Agency for Creating High Qua...
-Nature Conservancy India Solutions Private Limite...
-Location:
-Delhi
-Apply by:
-20 Mar 2026
-Programme officers (Education &amp; Life Skills Educa...
-Butterflies NGO
-Location:
-Delhi
+Documentation / Program Officer
+Pragati Path Foundation
+Location:
+Uttar Pradesh
+Apply by:
+25 Mar 2026
+Accounts Officer
+Jana Kalayana Samakhya
+Location:
+Odisha
+Apply by:
+30 Mar 2026
+Manager - Accounts &amp; Finance
+(Value Members only)
+Location:
+Rajasthan
+Apply by:
+13 Mar 2026
+Project Coordinator
+Asra Samajik Lok Kalyan Samiti
+Location:
+Madhya Pradesh
+Apply by:
+30 Mar 2026
+Account Manager
+(Value Members only)
+Location:
+Odisha
+Apply by:
+10 Mar 2026
+Resource Person, Teacher Support – Ashram School ...
+Kavana Charitable Trust
+Location:
+Karnataka
+Apply by:
+02 Apr 2026
+Teach Manager, Child Development Team (Dual Role)
+U&amp;I Trust
+Location:
+India
+Apply by:
+31 Mar 2026
+Rural India Fellowship
+Katakhali Swapnopuron Welfare Society
+Location:
+West Bengal
 Apply by:
 15 Mar 2026
-RFQ: Construction of New gated check dams, De-sil...
-WaterAid India
-Location:
-Telangana
-Apply by:
-08 Mar 2026
-Regional Coordinator
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-Maharashtra
-Apply by:
-18 Mar 2026
-Project Nurse 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Project Technical Support 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Block Academic Coordinator
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-District Program Manager
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
 Jobseekers
 Register
 Login
@@ -3561,239 +2916,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F14" s="1" t="inlineStr">
+      <c r="F11" s="1" t="inlineStr">
         <is>
           <t>Governance, Learning</t>
         </is>
       </c>
-      <c r="G14" s="1" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>06-03-2026</t>
         </is>
       </c>
-      <c r="H14" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="I14" s="1" t="inlineStr">
+      <c r="H11" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287084</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr"/>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>RFP- #2026-IN-01- Agency for economic Impact Analysis</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>PATH | Delhi
-International Development - RFP- #2026-IN-01- Agency for economic Impact Analysis, PATH, Delhi - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Login
-|
-Register
-Jobseekers Login
-Jobseekers Register
-Job ... Read More</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>• Job Email ID:
-rfpindia(at)path.org
-Download Attachment:
-Request for Proposal - RFP#2026-IN-01- Agency for economic Impact Analysis.doc
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-07 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-RFP - Requirement of Agency for Creating High Qua...
-Nature Conservancy India Solutions Private Limite...
-Location:
-Delhi
-Apply by:
-20 Mar 2026
-Programme officers (Education &amp; Life Skills Educa...
-Butterflies NGO
-Location:
-Delhi
-Apply by:
-15 Mar 2026
-RFQ: Construction of New gated check dams, De-sil...
-WaterAid India
-Location:
-Telangana
-Apply by:
-08 Mar 2026
-Regional Coordinator
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-Maharashtra
-Apply by:
-18 Mar 2026
-Project Nurse 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Project Technical Support 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Block Academic Coordinator
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-District Program Manager
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F15" s="1" t="inlineStr">
-        <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G15" s="1" t="inlineStr">
-        <is>
-          <t>07-03-2026</t>
-        </is>
-      </c>
-      <c r="H15" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I15" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287460</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B16" s="1" t="inlineStr"/>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="B12" s="1" t="inlineStr"/>
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>RFP - Onboarding Agency for Revamping Assam LMIS Dashboard</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>PATH | Assam
 International Development - RFP - Onboarding Agency for Revamping Assam LMIS Dashboard, PATH, Assam - DevNetJobsIndia.org
@@ -3815,7 +2969,7 @@
 Jobseekers Registe ... Read More</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>• 3.2. Commercial contracting terms and conditions will be negotiated with the successful supplier at the end of the selection process.
 3.3. By submitting a proposal, the supplier confirms their agreement to abide by the RFP terms and PATH policies, including the
@@ -3908,6 +3062,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -3964,54 +3124,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFP - Requirement of Agency for Creating High Qua...
-Nature Conservancy India Solutions Private Limite...
-Location:
-Delhi
-Apply by:
-20 Mar 2026
-Programme officers (Education &amp; Life Skills Educa...
-Butterflies NGO
-Location:
-Delhi
+Documentation / Program Officer
+Pragati Path Foundation
+Location:
+Uttar Pradesh
+Apply by:
+25 Mar 2026
+Accounts Officer
+Jana Kalayana Samakhya
+Location:
+Odisha
+Apply by:
+30 Mar 2026
+Manager - Accounts &amp; Finance
+(Value Members only)
+Location:
+Rajasthan
+Apply by:
+13 Mar 2026
+Project Coordinator
+Asra Samajik Lok Kalyan Samiti
+Location:
+Madhya Pradesh
+Apply by:
+30 Mar 2026
+Account Manager
+(Value Members only)
+Location:
+Odisha
+Apply by:
+10 Mar 2026
+Resource Person, Teacher Support – Ashram School ...
+Kavana Charitable Trust
+Location:
+Karnataka
+Apply by:
+02 Apr 2026
+Teach Manager, Child Development Team (Dual Role)
+U&amp;I Trust
+Location:
+India
+Apply by:
+31 Mar 2026
+Rural India Fellowship
+Katakhali Swapnopuron Welfare Society
+Location:
+West Bengal
 Apply by:
 15 Mar 2026
-RFQ: Construction of New gated check dams, De-sil...
-WaterAid India
-Location:
-Telangana
-Apply by:
-08 Mar 2026
-Regional Coordinator
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-Maharashtra
-Apply by:
-18 Mar 2026
-Project Nurse 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Project Technical Support 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Block Academic Coordinator
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-District Program Manager
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
 Jobseekers
 Register
 Login
@@ -4039,41 +3199,41 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F16" s="1" t="inlineStr">
+      <c r="F12" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G16" s="1" t="inlineStr">
+      <c r="G12" s="1" t="inlineStr">
         <is>
           <t>07-03-2026</t>
         </is>
       </c>
-      <c r="H16" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I16" s="1" t="inlineStr">
+      <c r="H12" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287335</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr"/>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>Associate (Programme Management)</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Indian Institute For Human Settlements (Iihs) | Karnataka
-International Development - Associate (Programme Management), Indian Institute For Human Settlements (Iihs), Karnataka - DevNetJobsIndia.org
+      <c r="B13" s="1" t="inlineStr"/>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>RFP- #2026-IN-01- Agency for economic Impact Analysis</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>PATH | Delhi
+International Development - RFP- #2026-IN-01- Agency for economic Impact Analysis, PATH, Delhi - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
@@ -4083,26 +3243,22 @@
 Broadcast Resume
 RFPs/Tenders
 Search Jobs
-Events ... Read More</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>• IIHS is an equal opportunity employer that encourages women, people with disabilities and those from economically and socially excluded communities with the requisite skills and qualifications to apply for positions.
-• To apply
-If you are interested in exploring this opportunity with us, please fill the online
-application form
-by clicking here. (You can also click on the “
-Apply Now
-” button at the end of the Job Description displayed on the website).
-Contact
-Please write to us at
-hr@iihs.co.in
-if you need any clarifications while filling the online application form.
-• Job Email ID:
-hr(at)iihs.co.in
+Events
+Jobseekers:
+Login
+|
+Register
+Jobseekers Login
+Jobseekers Register
+Job ... Read More</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>• Job Email ID:
+rfpindia(at)path.org
 Download Attachment:
-Associate-Programme-Management-–-ASSURE-Lighthouse-Projects.pdf
+Request for Proposal - RFP#2026-IN-01- Agency for economic Impact Analysis.doc
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
@@ -4113,6 +3269,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -4169,54 +3331,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFP - Requirement of Agency for Creating High Qua...
-Nature Conservancy India Solutions Private Limite...
-Location:
-Delhi
-Apply by:
-20 Mar 2026
-Programme officers (Education &amp; Life Skills Educa...
-Butterflies NGO
-Location:
-Delhi
+Documentation / Program Officer
+Pragati Path Foundation
+Location:
+Uttar Pradesh
+Apply by:
+25 Mar 2026
+Accounts Officer
+Jana Kalayana Samakhya
+Location:
+Odisha
+Apply by:
+30 Mar 2026
+Manager - Accounts &amp; Finance
+(Value Members only)
+Location:
+Rajasthan
+Apply by:
+13 Mar 2026
+Project Coordinator
+Asra Samajik Lok Kalyan Samiti
+Location:
+Madhya Pradesh
+Apply by:
+30 Mar 2026
+Account Manager
+(Value Members only)
+Location:
+Odisha
+Apply by:
+10 Mar 2026
+Resource Person, Teacher Support – Ashram School ...
+Kavana Charitable Trust
+Location:
+Karnataka
+Apply by:
+02 Apr 2026
+Teach Manager, Child Development Team (Dual Role)
+U&amp;I Trust
+Location:
+India
+Apply by:
+31 Mar 2026
+Rural India Fellowship
+Katakhali Swapnopuron Welfare Society
+Location:
+West Bengal
 Apply by:
 15 Mar 2026
-RFQ: Construction of New gated check dams, De-sil...
-WaterAid India
-Location:
-Telangana
-Apply by:
-08 Mar 2026
-Regional Coordinator
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-Maharashtra
-Apply by:
-18 Mar 2026
-Project Nurse 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Project Technical Support 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Block Academic Coordinator
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-District Program Manager
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
 Jobseekers
 Register
 Login
@@ -4244,38 +3406,249 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F17" s="1" t="inlineStr">
+      <c r="F13" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G17" s="1" t="inlineStr">
+      <c r="G13" s="1" t="inlineStr">
         <is>
           <t>07-03-2026</t>
         </is>
       </c>
-      <c r="H17" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I17" s="1" t="inlineStr">
+      <c r="H13" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287460</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr"/>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>Associate (Programme Management)</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Indian Institute For Human Settlements (Iihs) | Karnataka
+International Development - Associate (Programme Management), Indian Institute For Human Settlements (Iihs), Karnataka - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events ... Read More</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>• IIHS is an equal opportunity employer that encourages women, people with disabilities and those from economically and socially excluded communities with the requisite skills and qualifications to apply for positions.
+• To apply
+If you are interested in exploring this opportunity with us, please fill the online
+application form
+by clicking here. (You can also click on the “
+Apply Now
+” button at the end of the Job Description displayed on the website).
+Contact
+Please write to us at
+hr@iihs.co.in
+if you need any clarifications while filling the online application form.
+• Job Email ID:
+hr(at)iihs.co.in
+Download Attachment:
+Associate-Programme-Management-–-ASSURE-Lighthouse-Projects.pdf
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+07 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Associate (Programme Management)
+Indian Institute For Human Settlements (Iihs)
+Location:
+Karnataka
+Apply by:
+07 Mar 2026
+Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+Documentation / Program Officer
+Pragati Path Foundation
+Location:
+Uttar Pradesh
+Apply by:
+25 Mar 2026
+Accounts Officer
+Jana Kalayana Samakhya
+Location:
+Odisha
+Apply by:
+30 Mar 2026
+Manager - Accounts &amp; Finance
+(Value Members only)
+Location:
+Rajasthan
+Apply by:
+13 Mar 2026
+Project Coordinator
+Asra Samajik Lok Kalyan Samiti
+Location:
+Madhya Pradesh
+Apply by:
+30 Mar 2026
+Account Manager
+(Value Members only)
+Location:
+Odisha
+Apply by:
+10 Mar 2026
+Resource Person, Teacher Support – Ashram School ...
+Kavana Charitable Trust
+Location:
+Karnataka
+Apply by:
+02 Apr 2026
+Teach Manager, Child Development Team (Dual Role)
+U&amp;I Trust
+Location:
+India
+Apply by:
+31 Mar 2026
+Rural India Fellowship
+Katakhali Swapnopuron Welfare Society
+Location:
+West Bengal
+Apply by:
+15 Mar 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t>07-03-2026</t>
+        </is>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=285747</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B18" s="1" t="inlineStr"/>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="B15" s="1" t="inlineStr"/>
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>RFP - Final Evaluation of the Bhoomi Ka Programme</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Deutsche Welthungerhilfe | India
 International Development - RFP - Final Evaluation of the Bhoomi Ka Programme, Deutsche Welthungerhilfe, India - DevNetJobsIndia.org
@@ -4296,7 +3669,7 @@
 Jobs ... Read More</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>• INTRODUCTION AND CONTEXT
 Country:
@@ -4364,6 +3737,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -4420,54 +3799,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFP - Requirement of Agency for Creating High Qua...
-Nature Conservancy India Solutions Private Limite...
-Location:
-Delhi
-Apply by:
-20 Mar 2026
-Programme officers (Education &amp; Life Skills Educa...
-Butterflies NGO
-Location:
-Delhi
+Documentation / Program Officer
+Pragati Path Foundation
+Location:
+Uttar Pradesh
+Apply by:
+25 Mar 2026
+Accounts Officer
+Jana Kalayana Samakhya
+Location:
+Odisha
+Apply by:
+30 Mar 2026
+Manager - Accounts &amp; Finance
+(Value Members only)
+Location:
+Rajasthan
+Apply by:
+13 Mar 2026
+Project Coordinator
+Asra Samajik Lok Kalyan Samiti
+Location:
+Madhya Pradesh
+Apply by:
+30 Mar 2026
+Account Manager
+(Value Members only)
+Location:
+Odisha
+Apply by:
+10 Mar 2026
+Resource Person, Teacher Support – Ashram School ...
+Kavana Charitable Trust
+Location:
+Karnataka
+Apply by:
+02 Apr 2026
+Teach Manager, Child Development Team (Dual Role)
+U&amp;I Trust
+Location:
+India
+Apply by:
+31 Mar 2026
+Rural India Fellowship
+Katakhali Swapnopuron Welfare Society
+Location:
+West Bengal
 Apply by:
 15 Mar 2026
-RFQ: Construction of New gated check dams, De-sil...
-WaterAid India
-Location:
-Telangana
-Apply by:
-08 Mar 2026
-Regional Coordinator
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-Maharashtra
-Apply by:
-18 Mar 2026
-Project Nurse 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Project Technical Support 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Block Academic Coordinator
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-District Program Manager
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
 Jobseekers
 Register
 Login
@@ -4495,38 +3874,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F18" s="1" t="inlineStr">
+      <c r="F15" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G18" s="1" t="inlineStr">
+      <c r="G15" s="1" t="inlineStr">
         <is>
           <t>08-03-2026</t>
         </is>
       </c>
-      <c r="H18" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="I18" s="1" t="inlineStr">
+      <c r="H15" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I15" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287384</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr"/>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="B16" s="1" t="inlineStr"/>
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>RFQ: Construction of New gated check dams, De-siltation, and retrofitting ...</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>WaterAid India | Telangana
 International Development - RFQ: Construction of New gated check dams, De-siltation, and retrofitting of check dam in 6 villages, WaterAid India, Telangana - DevNetJobsIndia.org
@@ -4542,7 +3921,7 @@
 E ... Read More</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>• Job Email ID:
 WAIProcurementAP(at)wateraid.org
@@ -4558,6 +3937,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -4614,54 +3999,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFP - Requirement of Agency for Creating High Qua...
-Nature Conservancy India Solutions Private Limite...
-Location:
-Delhi
-Apply by:
-20 Mar 2026
-Programme officers (Education &amp; Life Skills Educa...
-Butterflies NGO
-Location:
-Delhi
+Documentation / Program Officer
+Pragati Path Foundation
+Location:
+Uttar Pradesh
+Apply by:
+25 Mar 2026
+Accounts Officer
+Jana Kalayana Samakhya
+Location:
+Odisha
+Apply by:
+30 Mar 2026
+Manager - Accounts &amp; Finance
+(Value Members only)
+Location:
+Rajasthan
+Apply by:
+13 Mar 2026
+Project Coordinator
+Asra Samajik Lok Kalyan Samiti
+Location:
+Madhya Pradesh
+Apply by:
+30 Mar 2026
+Account Manager
+(Value Members only)
+Location:
+Odisha
+Apply by:
+10 Mar 2026
+Resource Person, Teacher Support – Ashram School ...
+Kavana Charitable Trust
+Location:
+Karnataka
+Apply by:
+02 Apr 2026
+Teach Manager, Child Development Team (Dual Role)
+U&amp;I Trust
+Location:
+India
+Apply by:
+31 Mar 2026
+Rural India Fellowship
+Katakhali Swapnopuron Welfare Society
+Location:
+West Bengal
 Apply by:
 15 Mar 2026
-RFQ: Construction of New gated check dams, De-sil...
-WaterAid India
-Location:
-Telangana
-Apply by:
-08 Mar 2026
-Regional Coordinator
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-Maharashtra
-Apply by:
-18 Mar 2026
-Project Nurse 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Project Technical Support 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Block Academic Coordinator
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-District Program Manager
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
 Jobseekers
 Register
 Login
@@ -4689,61 +4074,57 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F19" s="1" t="inlineStr">
+      <c r="F16" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G19" s="1" t="inlineStr">
+      <c r="G16" s="1" t="inlineStr">
         <is>
           <t>08-03-2026</t>
         </is>
       </c>
-      <c r="H19" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="I19" s="1" t="inlineStr">
+      <c r="H16" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287784</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr"/>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>RFP For The Contractors To Procure, Build, Install, Supply Chlorine Tablet...</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>EAII Advisors Pvt Ltd | Andhra Pradesh
-International Development - RFP For The Contractors To Procure, Build, Install, Supply Chlorine Tablets, Operate And Maintain Tablet-Based In Line Chlorination Devices, EAII Advisors Pvt Ltd, Andhra Pradesh - DevNetJobsIndia.org
+      <c r="B17" s="1" t="inlineStr"/>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>RFP - Hiring of an International Audit Firm</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Coalition for Disaster Resilient Infrastructure (CDRI) | India
+International Development - RFP - Hiring of an International Audit Firm, Coalition for Disaster Resilient Infrastructure (CDRI), India - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
 Register
-Ho ... Read More</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>• Proposal Requirements
-1. Company Background and Details
-A. Company Profile
-Overview of the firm or firms submitting the bid, including a brief history, information about organizational structure, relevant company financials, location of offices, number of employees, relevant certifications, or any other information that could be pertinent.
-Supplier Response:
-Kindly fill in the column “Bidder Response”. The current inputs are guiding inputs or choices for answers. Kindly fill in accordingly.
-For detailed information, please check the complete version of the RFP attached below.
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tender ... Read More</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>• Job Email ID:
+tender.projects(at)cdri.world
 Download Attachment:
-Standalone IC RFP Technical Evaluation Response Template.docx
-Download Attachment:
-Telugu_Standalone IC RFP Technical Evaluation Response Template.docx
+RFP-Hiring International Audit Firm-20 Feb'26.pdf
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
@@ -4754,6 +4135,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -4810,54 +4197,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFP - Requirement of Agency for Creating High Qua...
-Nature Conservancy India Solutions Private Limite...
-Location:
-Delhi
-Apply by:
-20 Mar 2026
-Programme officers (Education &amp; Life Skills Educa...
-Butterflies NGO
-Location:
-Delhi
+Documentation / Program Officer
+Pragati Path Foundation
+Location:
+Uttar Pradesh
+Apply by:
+25 Mar 2026
+Accounts Officer
+Jana Kalayana Samakhya
+Location:
+Odisha
+Apply by:
+30 Mar 2026
+Manager - Accounts &amp; Finance
+(Value Members only)
+Location:
+Rajasthan
+Apply by:
+13 Mar 2026
+Project Coordinator
+Asra Samajik Lok Kalyan Samiti
+Location:
+Madhya Pradesh
+Apply by:
+30 Mar 2026
+Account Manager
+(Value Members only)
+Location:
+Odisha
+Apply by:
+10 Mar 2026
+Resource Person, Teacher Support – Ashram School ...
+Kavana Charitable Trust
+Location:
+Karnataka
+Apply by:
+02 Apr 2026
+Teach Manager, Child Development Team (Dual Role)
+U&amp;I Trust
+Location:
+India
+Apply by:
+31 Mar 2026
+Rural India Fellowship
+Katakhali Swapnopuron Welfare Society
+Location:
+West Bengal
 Apply by:
 15 Mar 2026
-RFQ: Construction of New gated check dams, De-sil...
-WaterAid India
-Location:
-Telangana
-Apply by:
-08 Mar 2026
-Regional Coordinator
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-Maharashtra
-Apply by:
-18 Mar 2026
-Project Nurse 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Project Technical Support 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Block Academic Coordinator
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-District Program Manager
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
 Jobseekers
 Register
 Login
@@ -4885,38 +4272,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G20" s="1" t="inlineStr">
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>Climate</t>
+        </is>
+      </c>
+      <c r="G17" s="1" t="inlineStr">
         <is>
           <t>09-03-2026</t>
         </is>
       </c>
-      <c r="H20" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I20" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=285949</t>
+      <c r="H17" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I17" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287382</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr"/>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="B18" s="1" t="inlineStr"/>
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>RFP For Selection of an Implementation Support Agency (Isa) For Capacity B...</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>EAII Advisors Pvt Ltd | Andhra Pradesh
 International Development - RFP For Selection of an Implementation Support Agency (Isa) For Capacity Building Of Community Leaders To Conduct Community Engagement Activities, EAII Advisors Pvt Ltd, Andhra Pradesh - DevNetJobsIndia.org
@@ -4926,7 +4313,7 @@
 Regis ... Read More</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>• Proposal Requirements
 1. Company Background and Details
@@ -4949,6 +4336,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -5005,54 +4398,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFP - Requirement of Agency for Creating High Qua...
-Nature Conservancy India Solutions Private Limite...
-Location:
-Delhi
-Apply by:
-20 Mar 2026
-Programme officers (Education &amp; Life Skills Educa...
-Butterflies NGO
-Location:
-Delhi
+Documentation / Program Officer
+Pragati Path Foundation
+Location:
+Uttar Pradesh
+Apply by:
+25 Mar 2026
+Accounts Officer
+Jana Kalayana Samakhya
+Location:
+Odisha
+Apply by:
+30 Mar 2026
+Manager - Accounts &amp; Finance
+(Value Members only)
+Location:
+Rajasthan
+Apply by:
+13 Mar 2026
+Project Coordinator
+Asra Samajik Lok Kalyan Samiti
+Location:
+Madhya Pradesh
+Apply by:
+30 Mar 2026
+Account Manager
+(Value Members only)
+Location:
+Odisha
+Apply by:
+10 Mar 2026
+Resource Person, Teacher Support – Ashram School ...
+Kavana Charitable Trust
+Location:
+Karnataka
+Apply by:
+02 Apr 2026
+Teach Manager, Child Development Team (Dual Role)
+U&amp;I Trust
+Location:
+India
+Apply by:
+31 Mar 2026
+Rural India Fellowship
+Katakhali Swapnopuron Welfare Society
+Location:
+West Bengal
 Apply by:
 15 Mar 2026
-RFQ: Construction of New gated check dams, De-sil...
-WaterAid India
-Location:
-Telangana
-Apply by:
-08 Mar 2026
-Regional Coordinator
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-Maharashtra
-Apply by:
-18 Mar 2026
-Project Nurse 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Project Technical Support 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Block Academic Coordinator
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-District Program Manager
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
 Jobseekers
 Register
 Login
@@ -5080,41 +4473,41 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F21" s="1" t="inlineStr">
+      <c r="F18" s="1" t="inlineStr">
         <is>
           <t>Governance, Learning</t>
         </is>
       </c>
-      <c r="G21" s="1" t="inlineStr">
+      <c r="G18" s="1" t="inlineStr">
         <is>
           <t>09-03-2026</t>
         </is>
       </c>
-      <c r="H21" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I21" s="1" t="inlineStr">
+      <c r="H18" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I18" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=285950</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr"/>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Hiring of an International Audit Firm</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="B19" s="1" t="inlineStr"/>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>RFP - Early-Stage Impact Assessment-CDRI SWP 23-26</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Coalition for Disaster Resilient Infrastructure (CDRI) | India
-International Development - RFP - Hiring of an International Audit Firm, Coalition for Disaster Resilient Infrastructure (CDRI), India - DevNetJobsIndia.org
+International Development - RFP - Early-Stage Impact Assessment-CDRI SWP 23-26, Coalition for Disaster Resilient Infrastructure (CDRI), India - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
@@ -5122,15 +4515,69 @@
 Home
 Value Membership
 Broadcast Resume
-RFPs/Tender ... Read More</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>• Job Email ID:
-tender.projects(at)cdri.world
+RFPs ... Read More</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="inlineStr">
+        <is>
+          <t>Climate, Governance</t>
+        </is>
+      </c>
+      <c r="G19" s="1" t="inlineStr">
+        <is>
+          <t>09-03-2026</t>
+        </is>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I19" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287093</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr"/>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>RFP For The Contractors To Procure, Build, Install, Supply Chlorine Tablet...</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>EAII Advisors Pvt Ltd | Andhra Pradesh
+International Development - RFP For The Contractors To Procure, Build, Install, Supply Chlorine Tablets, Operate And Maintain Tablet-Based In Line Chlorination Devices, EAII Advisors Pvt Ltd, Andhra Pradesh - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Ho ... Read More</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>• Proposal Requirements
+1. Company Background and Details
+A. Company Profile
+Overview of the firm or firms submitting the bid, including a brief history, information about organizational structure, relevant company financials, location of offices, number of employees, relevant certifications, or any other information that could be pertinent.
+Supplier Response:
+Kindly fill in the column “Bidder Response”. The current inputs are guiding inputs or choices for answers. Kindly fill in accordingly.
+For detailed information, please check the complete version of the RFP attached below.
 Download Attachment:
-RFP-Hiring International Audit Firm-20 Feb'26.pdf
+Standalone IC RFP Technical Evaluation Response Template.docx
+Download Attachment:
+Telugu_Standalone IC RFP Technical Evaluation Response Template.docx
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
@@ -5141,6 +4588,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -5197,54 +4650,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFP - Requirement of Agency for Creating High Qua...
-Nature Conservancy India Solutions Private Limite...
-Location:
-Delhi
-Apply by:
-20 Mar 2026
-Programme officers (Education &amp; Life Skills Educa...
-Butterflies NGO
-Location:
-Delhi
+Documentation / Program Officer
+Pragati Path Foundation
+Location:
+Uttar Pradesh
+Apply by:
+25 Mar 2026
+Accounts Officer
+Jana Kalayana Samakhya
+Location:
+Odisha
+Apply by:
+30 Mar 2026
+Manager - Accounts &amp; Finance
+(Value Members only)
+Location:
+Rajasthan
+Apply by:
+13 Mar 2026
+Project Coordinator
+Asra Samajik Lok Kalyan Samiti
+Location:
+Madhya Pradesh
+Apply by:
+30 Mar 2026
+Account Manager
+(Value Members only)
+Location:
+Odisha
+Apply by:
+10 Mar 2026
+Resource Person, Teacher Support – Ashram School ...
+Kavana Charitable Trust
+Location:
+Karnataka
+Apply by:
+02 Apr 2026
+Teach Manager, Child Development Team (Dual Role)
+U&amp;I Trust
+Location:
+India
+Apply by:
+31 Mar 2026
+Rural India Fellowship
+Katakhali Swapnopuron Welfare Society
+Location:
+West Bengal
 Apply by:
 15 Mar 2026
-RFQ: Construction of New gated check dams, De-sil...
-WaterAid India
-Location:
-Telangana
-Apply by:
-08 Mar 2026
-Regional Coordinator
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-Maharashtra
-Apply by:
-18 Mar 2026
-Project Nurse 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Project Technical Support 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Block Academic Coordinator
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-District Program Manager
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
 Jobseekers
 Register
 Login
@@ -5272,88 +4725,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F22" s="1" t="inlineStr">
-        <is>
-          <t>Climate</t>
-        </is>
-      </c>
-      <c r="G22" s="1" t="inlineStr">
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G20" s="1" t="inlineStr">
         <is>
           <t>09-03-2026</t>
         </is>
       </c>
-      <c r="H22" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I22" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287382</t>
+      <c r="H20" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=285949</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr"/>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Early-Stage Impact Assessment-CDRI SWP 23-26</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Coalition for Disaster Resilient Infrastructure (CDRI) | India
-International Development - RFP - Early-Stage Impact Assessment-CDRI SWP 23-26, Coalition for Disaster Resilient Infrastructure (CDRI), India - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs ... Read More</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F23" s="1" t="inlineStr">
-        <is>
-          <t>Climate, Governance</t>
-        </is>
-      </c>
-      <c r="G23" s="1" t="inlineStr">
-        <is>
-          <t>09-03-2026</t>
-        </is>
-      </c>
-      <c r="H23" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I23" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287093</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B24" s="1" t="inlineStr"/>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="B21" s="1" t="inlineStr"/>
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>RFP - for Supply of Skill Lab Items</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>TeamLease Foundation | India
 International Development - RFP - for Supply of Skill Lab Items, TeamLease Foundation, India - DevNetJobsIndia.org
@@ -5375,7 +4778,7 @@
 Jobseeker ... Read More</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>• Technical Bid Submission Link-
 https://forms.gle/V9iy35ddb4kWEb468
@@ -5420,6 +4823,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -5476,54 +4885,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFP - Requirement of Agency for Creating High Qua...
-Nature Conservancy India Solutions Private Limite...
-Location:
-Delhi
-Apply by:
-20 Mar 2026
-Programme officers (Education &amp; Life Skills Educa...
-Butterflies NGO
-Location:
-Delhi
+Documentation / Program Officer
+Pragati Path Foundation
+Location:
+Uttar Pradesh
+Apply by:
+25 Mar 2026
+Accounts Officer
+Jana Kalayana Samakhya
+Location:
+Odisha
+Apply by:
+30 Mar 2026
+Manager - Accounts &amp; Finance
+(Value Members only)
+Location:
+Rajasthan
+Apply by:
+13 Mar 2026
+Project Coordinator
+Asra Samajik Lok Kalyan Samiti
+Location:
+Madhya Pradesh
+Apply by:
+30 Mar 2026
+Account Manager
+(Value Members only)
+Location:
+Odisha
+Apply by:
+10 Mar 2026
+Resource Person, Teacher Support – Ashram School ...
+Kavana Charitable Trust
+Location:
+Karnataka
+Apply by:
+02 Apr 2026
+Teach Manager, Child Development Team (Dual Role)
+U&amp;I Trust
+Location:
+India
+Apply by:
+31 Mar 2026
+Rural India Fellowship
+Katakhali Swapnopuron Welfare Society
+Location:
+West Bengal
 Apply by:
 15 Mar 2026
-RFQ: Construction of New gated check dams, De-sil...
-WaterAid India
-Location:
-Telangana
-Apply by:
-08 Mar 2026
-Regional Coordinator
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-Maharashtra
-Apply by:
-18 Mar 2026
-Project Nurse 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Project Technical Support 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Block Academic Coordinator
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-District Program Manager
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
 Jobseekers
 Register
 Login
@@ -5551,44 +4960,44 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F24" s="1" t="inlineStr">
+      <c r="F21" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G24" s="1" t="inlineStr">
+      <c r="G21" s="1" t="inlineStr">
         <is>
           <t>11-03-2026</t>
         </is>
       </c>
-      <c r="H24" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="I24" s="1" t="inlineStr">
+      <c r="H21" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I21" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287613</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr"/>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="B22" s="1" t="inlineStr"/>
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>RFP - Study On SC-DMPA In Rajasthan- Clients And Providers Perspectives On...</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Centre For Community Economics And Development Consultants Society- CECOEDECON | Jaipur, Rajasthan
 International Development - RFP - Study On SC-DMPA In Rajasthan- Clients And Providers Perspectives On SC-DMPA In Rajasthan, Centre For Community Economics And Development Consultants Society- CECOEDE ... Read More</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>• Despite India’s achievement of replacement-level fertility, unmet need for contraception—particularly for spacing methods—remains substantial, with modern contraceptive use at 56.4% (2019–21), highlighting persistent gaps in access and choice, especially among vulnerable populations. Expanding the contraceptive method mix through innovative, user-centred approaches is therefore essential to meeting national commitments under FP2030 and the Sustainable Development Goals. In this context, the Government of India’s introduction of subcutaneous DMPA (DMPA-SC) as a self-care option under the National Family Planning Programme in 2023 represents a strategic step toward enhancing women’s autonomy, privacy, and convenience in contraceptive use. Global and national evidence indicates strong feasibility and acceptability of self-administered DMPA-SC among both users and providers; however, successful implementation requires an in-depth understanding of user experiences and health system readiness. This study, to be conducted in Jaipur-1, Jaisalmer and Sawai Madhopur districts of Rajasthan, aims to examine the perspectives &amp; experience of current SC-DMPA users and explore healthcare providers’ views on enabling and generating actionable evidence to inform effective scale-up of SC-DMPA within India’s public health system.
 CECOEDECON, with support from UNFPA, is implementing the roll-out of subcutaneous DMPA (SC-DMPA) in selected pilot districts of Rajasthan in the public health facilities, in collaboration with the Department of Health &amp; Family Welfare, Government of Rajasthan.
@@ -5661,6 +5070,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -5717,54 +5132,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFP - Requirement of Agency for Creating High Qua...
-Nature Conservancy India Solutions Private Limite...
-Location:
-Delhi
-Apply by:
-20 Mar 2026
-Programme officers (Education &amp; Life Skills Educa...
-Butterflies NGO
-Location:
-Delhi
+Documentation / Program Officer
+Pragati Path Foundation
+Location:
+Uttar Pradesh
+Apply by:
+25 Mar 2026
+Accounts Officer
+Jana Kalayana Samakhya
+Location:
+Odisha
+Apply by:
+30 Mar 2026
+Manager - Accounts &amp; Finance
+(Value Members only)
+Location:
+Rajasthan
+Apply by:
+13 Mar 2026
+Project Coordinator
+Asra Samajik Lok Kalyan Samiti
+Location:
+Madhya Pradesh
+Apply by:
+30 Mar 2026
+Account Manager
+(Value Members only)
+Location:
+Odisha
+Apply by:
+10 Mar 2026
+Resource Person, Teacher Support – Ashram School ...
+Kavana Charitable Trust
+Location:
+Karnataka
+Apply by:
+02 Apr 2026
+Teach Manager, Child Development Team (Dual Role)
+U&amp;I Trust
+Location:
+India
+Apply by:
+31 Mar 2026
+Rural India Fellowship
+Katakhali Swapnopuron Welfare Society
+Location:
+West Bengal
 Apply by:
 15 Mar 2026
-RFQ: Construction of New gated check dams, De-sil...
-WaterAid India
-Location:
-Telangana
-Apply by:
-08 Mar 2026
-Regional Coordinator
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-Maharashtra
-Apply by:
-18 Mar 2026
-Project Nurse 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Project Technical Support 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Block Academic Coordinator
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-District Program Manager
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
 Jobseekers
 Register
 Login
@@ -5792,38 +5207,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F25" s="1" t="inlineStr">
+      <c r="F22" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G25" s="1" t="inlineStr">
+      <c r="G22" s="1" t="inlineStr">
         <is>
           <t>11-03-2026</t>
         </is>
       </c>
-      <c r="H25" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="I25" s="1" t="inlineStr">
+      <c r="H22" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I22" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287322</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr"/>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="B23" s="1" t="inlineStr"/>
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>SOW - Engagement of a Public Relations (PR) Agency on Retainer</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Room to Read India | India
 International Development - SOW - Engagement of a Public Relations (PR) Agency on Retainer, Room to Read India, India - DevNetJobsIndia.org
@@ -5844,7 +5259,7 @@
 Job ... Read More</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>• Scope of Work (SOW)
 Engagement of a Public Relations (PR) Agency on Retainer
@@ -5912,6 +5327,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -5968,54 +5389,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFP - Requirement of Agency for Creating High Qua...
-Nature Conservancy India Solutions Private Limite...
-Location:
-Delhi
-Apply by:
-20 Mar 2026
-Programme officers (Education &amp; Life Skills Educa...
-Butterflies NGO
-Location:
-Delhi
+Documentation / Program Officer
+Pragati Path Foundation
+Location:
+Uttar Pradesh
+Apply by:
+25 Mar 2026
+Accounts Officer
+Jana Kalayana Samakhya
+Location:
+Odisha
+Apply by:
+30 Mar 2026
+Manager - Accounts &amp; Finance
+(Value Members only)
+Location:
+Rajasthan
+Apply by:
+13 Mar 2026
+Project Coordinator
+Asra Samajik Lok Kalyan Samiti
+Location:
+Madhya Pradesh
+Apply by:
+30 Mar 2026
+Account Manager
+(Value Members only)
+Location:
+Odisha
+Apply by:
+10 Mar 2026
+Resource Person, Teacher Support – Ashram School ...
+Kavana Charitable Trust
+Location:
+Karnataka
+Apply by:
+02 Apr 2026
+Teach Manager, Child Development Team (Dual Role)
+U&amp;I Trust
+Location:
+India
+Apply by:
+31 Mar 2026
+Rural India Fellowship
+Katakhali Swapnopuron Welfare Society
+Location:
+West Bengal
 Apply by:
 15 Mar 2026
-RFQ: Construction of New gated check dams, De-sil...
-WaterAid India
-Location:
-Telangana
-Apply by:
-08 Mar 2026
-Regional Coordinator
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-Maharashtra
-Apply by:
-18 Mar 2026
-Project Nurse 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Project Technical Support 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Block Academic Coordinator
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-District Program Manager
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
 Jobseekers
 Register
 Login
@@ -6043,38 +5464,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F26" s="1" t="inlineStr">
+      <c r="F23" s="1" t="inlineStr">
         <is>
           <t>Governance, Learning</t>
         </is>
       </c>
-      <c r="G26" s="1" t="inlineStr">
+      <c r="G23" s="1" t="inlineStr">
         <is>
           <t>12-03-2026</t>
         </is>
       </c>
-      <c r="H26" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="I26" s="1" t="inlineStr">
+      <c r="H23" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="I23" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287648</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr"/>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="B24" s="1" t="inlineStr"/>
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>RFP - for Internal Audit</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>India HIV/AIDS Alliance (Alliance India) | Delhi
 International Development - RFP - for Internal Audit, India HIV/AIDS Alliance (Alliance India), Delhi - DevNetJobsIndia.org
@@ -6094,7 +5515,7 @@
 Regist ... Read More</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>• Alliance India reserves the right to reject applications that do not meet eligibility or application submission requirements (as detailed above) without further notice to the applicant. Issuance of this RFP does not constitute an award commitment or a guarantee of business on the part of Alliance India, nor does it commit Alliance India to pay for the costs incurred in submitting the application. Further, Alliance India reserves the right to reject any or all applications received and negotiate separately with an applicant if such action is considered in the best interest of Alliance India/ project.
 iii.
@@ -6119,6 +5540,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -6175,54 +5602,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFP - Requirement of Agency for Creating High Qua...
-Nature Conservancy India Solutions Private Limite...
-Location:
-Delhi
-Apply by:
-20 Mar 2026
-Programme officers (Education &amp; Life Skills Educa...
-Butterflies NGO
-Location:
-Delhi
+Documentation / Program Officer
+Pragati Path Foundation
+Location:
+Uttar Pradesh
+Apply by:
+25 Mar 2026
+Accounts Officer
+Jana Kalayana Samakhya
+Location:
+Odisha
+Apply by:
+30 Mar 2026
+Manager - Accounts &amp; Finance
+(Value Members only)
+Location:
+Rajasthan
+Apply by:
+13 Mar 2026
+Project Coordinator
+Asra Samajik Lok Kalyan Samiti
+Location:
+Madhya Pradesh
+Apply by:
+30 Mar 2026
+Account Manager
+(Value Members only)
+Location:
+Odisha
+Apply by:
+10 Mar 2026
+Resource Person, Teacher Support – Ashram School ...
+Kavana Charitable Trust
+Location:
+Karnataka
+Apply by:
+02 Apr 2026
+Teach Manager, Child Development Team (Dual Role)
+U&amp;I Trust
+Location:
+India
+Apply by:
+31 Mar 2026
+Rural India Fellowship
+Katakhali Swapnopuron Welfare Society
+Location:
+West Bengal
 Apply by:
 15 Mar 2026
-RFQ: Construction of New gated check dams, De-sil...
-WaterAid India
-Location:
-Telangana
-Apply by:
-08 Mar 2026
-Regional Coordinator
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-Maharashtra
-Apply by:
-18 Mar 2026
-Project Nurse 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Project Technical Support 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Block Academic Coordinator
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-District Program Manager
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
 Jobseekers
 Register
 Login
@@ -6250,38 +5677,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F27" s="1" t="inlineStr">
+      <c r="F24" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G27" s="1" t="inlineStr">
+      <c r="G24" s="1" t="inlineStr">
         <is>
           <t>13-03-2026</t>
         </is>
       </c>
-      <c r="H27" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="I27" s="1" t="inlineStr">
+      <c r="H24" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="I24" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287765</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr"/>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="B25" s="1" t="inlineStr"/>
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>Specialist – Financial Management and Compliance</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Financial Management Service Foundation (FMSF) | Uttar Pradesh
 International Development - Specialist – Financial Management and Compliance, Financial Management Service Foundation (FMSF), Uttar Pradesh - DevNetJobsIndia.org
@@ -6295,7 +5722,7 @@
 RFPs/T ... Read More</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>• will play a vital role in a program which seeks to strengthen the internal capacities of non-profit organizations in India across three building blocks of institutional functioning: governance, financial management, and compliance. These areas are deeply interconnected and together determine how effectively an organization operates, delivers programs and meets the expectations of its stakeholders. This position demands expertise in specific areas related to governance, compliance, and financial management, contributing essential guidance and support to strengthen the capabilities of participating organizations.
 Job Responsibilities:
@@ -6346,6 +5773,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -6402,54 +5835,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFP - Requirement of Agency for Creating High Qua...
-Nature Conservancy India Solutions Private Limite...
-Location:
-Delhi
-Apply by:
-20 Mar 2026
-Programme officers (Education &amp; Life Skills Educa...
-Butterflies NGO
-Location:
-Delhi
+Documentation / Program Officer
+Pragati Path Foundation
+Location:
+Uttar Pradesh
+Apply by:
+25 Mar 2026
+Accounts Officer
+Jana Kalayana Samakhya
+Location:
+Odisha
+Apply by:
+30 Mar 2026
+Manager - Accounts &amp; Finance
+(Value Members only)
+Location:
+Rajasthan
+Apply by:
+13 Mar 2026
+Project Coordinator
+Asra Samajik Lok Kalyan Samiti
+Location:
+Madhya Pradesh
+Apply by:
+30 Mar 2026
+Account Manager
+(Value Members only)
+Location:
+Odisha
+Apply by:
+10 Mar 2026
+Resource Person, Teacher Support – Ashram School ...
+Kavana Charitable Trust
+Location:
+Karnataka
+Apply by:
+02 Apr 2026
+Teach Manager, Child Development Team (Dual Role)
+U&amp;I Trust
+Location:
+India
+Apply by:
+31 Mar 2026
+Rural India Fellowship
+Katakhali Swapnopuron Welfare Society
+Location:
+West Bengal
 Apply by:
 15 Mar 2026
-RFQ: Construction of New gated check dams, De-sil...
-WaterAid India
-Location:
-Telangana
-Apply by:
-08 Mar 2026
-Regional Coordinator
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-Maharashtra
-Apply by:
-18 Mar 2026
-Project Nurse 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Project Technical Support 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Block Academic Coordinator
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-District Program Manager
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
 Jobseekers
 Register
 Login
@@ -6477,87 +5910,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F28" s="1" t="inlineStr">
+      <c r="F25" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G28" s="1" t="inlineStr">
+      <c r="G25" s="1" t="inlineStr">
         <is>
           <t>13-03-2026</t>
         </is>
       </c>
-      <c r="H28" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="I28" s="1" t="inlineStr">
+      <c r="H25" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="I25" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287015</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr"/>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>RFP - for Empanelment of Knowledge Partners for Grooming of students for ...</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>TeamLease Foundation | India
-International Development - RFP - for  Empanelment of Knowledge Partners for Grooming of students for competitive examination (through partner) Super 30 Model, TeamLease Foundation, India - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast ... Read More</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F29" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G29" s="1" t="inlineStr">
-        <is>
-          <t>15-03-2026</t>
-        </is>
-      </c>
-      <c r="H29" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="I29" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287763</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B30" s="1" t="inlineStr"/>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="B26" s="1" t="inlineStr"/>
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>RFP - External organization/agency to undertake documentation and process ...</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>India Health Action Trust (IHAT) | India
 International Development - RFP - External organization/agency to undertake documentation and process evaluation of the Gen Equal Fellowship Programme, India Health Action Trust (IHAT), India - DevNetJobsIndia.org
@@ -6569,7 +5953,7 @@
 Value Memb ... Read More</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>• 3A. Scope of Work
 Time Period
@@ -6652,6 +6036,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -6708,54 +6098,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFP - Requirement of Agency for Creating High Qua...
-Nature Conservancy India Solutions Private Limite...
-Location:
-Delhi
-Apply by:
-20 Mar 2026
-Programme officers (Education &amp; Life Skills Educa...
-Butterflies NGO
-Location:
-Delhi
+Documentation / Program Officer
+Pragati Path Foundation
+Location:
+Uttar Pradesh
+Apply by:
+25 Mar 2026
+Accounts Officer
+Jana Kalayana Samakhya
+Location:
+Odisha
+Apply by:
+30 Mar 2026
+Manager - Accounts &amp; Finance
+(Value Members only)
+Location:
+Rajasthan
+Apply by:
+13 Mar 2026
+Project Coordinator
+Asra Samajik Lok Kalyan Samiti
+Location:
+Madhya Pradesh
+Apply by:
+30 Mar 2026
+Account Manager
+(Value Members only)
+Location:
+Odisha
+Apply by:
+10 Mar 2026
+Resource Person, Teacher Support – Ashram School ...
+Kavana Charitable Trust
+Location:
+Karnataka
+Apply by:
+02 Apr 2026
+Teach Manager, Child Development Team (Dual Role)
+U&amp;I Trust
+Location:
+India
+Apply by:
+31 Mar 2026
+Rural India Fellowship
+Katakhali Swapnopuron Welfare Society
+Location:
+West Bengal
 Apply by:
 15 Mar 2026
-RFQ: Construction of New gated check dams, De-sil...
-WaterAid India
-Location:
-Telangana
-Apply by:
-08 Mar 2026
-Regional Coordinator
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-Maharashtra
-Apply by:
-18 Mar 2026
-Project Nurse 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Project Technical Support 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Block Academic Coordinator
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-District Program Manager
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
 Jobseekers
 Register
 Login
@@ -6783,38 +6173,87 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F30" s="1" t="inlineStr">
+      <c r="F26" s="1" t="inlineStr">
         <is>
           <t>Safety</t>
         </is>
       </c>
-      <c r="G30" s="1" t="inlineStr">
+      <c r="G26" s="1" t="inlineStr">
         <is>
           <t>15-03-2026</t>
         </is>
       </c>
-      <c r="H30" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="I30" s="1" t="inlineStr">
+      <c r="H26" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="I26" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287645</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr"/>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="B27" s="1" t="inlineStr"/>
+      <c r="C27" s="1" t="inlineStr">
+        <is>
+          <t>RFP - for Empanelment of Knowledge Partners for Grooming of students for ...</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>TeamLease Foundation | India
+International Development - RFP - for  Empanelment of Knowledge Partners for Grooming of students for competitive examination (through partner) Super 30 Model, TeamLease Foundation, India - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast ... Read More</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F27" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G27" s="1" t="inlineStr">
+        <is>
+          <t>15-03-2026</t>
+        </is>
+      </c>
+      <c r="H27" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="I27" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287763</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr"/>
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>RFP - Big IC+ISA RFP - Selection of a Service Provider for Supply, Instal...</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>EAII Advisors Pvt Ltd | Andhra Pradesh
 International Development - RFP - Big IC+ISA RFP -  Selection of a Service Provider for Supply, Installation and Operation &amp; Maintenance of 150 ILC Devices and Capacity Building., EAII Advisors Pvt Ltd, Andhra Pradesh - DevNetJobsIndia.org
@@ -6823,7 +6262,7 @@
 | ... Read More</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>• 2. Purpose of the RFP:
 2.1  EAII is soliciting bids for:
@@ -6870,6 +6309,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -6926,54 +6371,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFP - Requirement of Agency for Creating High Qua...
-Nature Conservancy India Solutions Private Limite...
-Location:
-Delhi
-Apply by:
-20 Mar 2026
-Programme officers (Education &amp; Life Skills Educa...
-Butterflies NGO
-Location:
-Delhi
+Documentation / Program Officer
+Pragati Path Foundation
+Location:
+Uttar Pradesh
+Apply by:
+25 Mar 2026
+Accounts Officer
+Jana Kalayana Samakhya
+Location:
+Odisha
+Apply by:
+30 Mar 2026
+Manager - Accounts &amp; Finance
+(Value Members only)
+Location:
+Rajasthan
+Apply by:
+13 Mar 2026
+Project Coordinator
+Asra Samajik Lok Kalyan Samiti
+Location:
+Madhya Pradesh
+Apply by:
+30 Mar 2026
+Account Manager
+(Value Members only)
+Location:
+Odisha
+Apply by:
+10 Mar 2026
+Resource Person, Teacher Support – Ashram School ...
+Kavana Charitable Trust
+Location:
+Karnataka
+Apply by:
+02 Apr 2026
+Teach Manager, Child Development Team (Dual Role)
+U&amp;I Trust
+Location:
+India
+Apply by:
+31 Mar 2026
+Rural India Fellowship
+Katakhali Swapnopuron Welfare Society
+Location:
+West Bengal
 Apply by:
 15 Mar 2026
-RFQ: Construction of New gated check dams, De-sil...
-WaterAid India
-Location:
-Telangana
-Apply by:
-08 Mar 2026
-Regional Coordinator
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-Maharashtra
-Apply by:
-18 Mar 2026
-Project Nurse 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Project Technical Support 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Block Academic Coordinator
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-District Program Manager
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
 Jobseekers
 Register
 Login
@@ -7001,38 +6446,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F31" s="1" t="inlineStr">
+      <c r="F28" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G31" s="1" t="inlineStr">
+      <c r="G28" s="1" t="inlineStr">
         <is>
           <t>16-03-2026</t>
         </is>
       </c>
-      <c r="H31" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="I31" s="1" t="inlineStr">
+      <c r="H28" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="I28" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287172</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B32" s="1" t="inlineStr"/>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="B29" s="1" t="inlineStr"/>
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>Specialist – Communication</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Financial Management Service Foundation (FMSF) | Uttar Pradesh
 International Development - Specialist – Communication, Financial Management Service Foundation (FMSF), Uttar Pradesh - DevNetJobsIndia.org
@@ -7048,7 +6493,7 @@
 Eve ... Read More</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>• Joining FMSF means becoming part of a passionate team dedicated to making a positive impact. We offer competitive compensation, opportunities for professional development, and a supportive work environment where your contributions are valued and recognized. If you are committed to driving positive change, promoting accountability and strengthening the development sector, we encourage you to apply for the position of Specialist – Communication at FMSF.
 • How to Apply:
@@ -7070,6 +6515,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -7126,54 +6577,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFP - Requirement of Agency for Creating High Qua...
-Nature Conservancy India Solutions Private Limite...
-Location:
-Delhi
-Apply by:
-20 Mar 2026
-Programme officers (Education &amp; Life Skills Educa...
-Butterflies NGO
-Location:
-Delhi
+Documentation / Program Officer
+Pragati Path Foundation
+Location:
+Uttar Pradesh
+Apply by:
+25 Mar 2026
+Accounts Officer
+Jana Kalayana Samakhya
+Location:
+Odisha
+Apply by:
+30 Mar 2026
+Manager - Accounts &amp; Finance
+(Value Members only)
+Location:
+Rajasthan
+Apply by:
+13 Mar 2026
+Project Coordinator
+Asra Samajik Lok Kalyan Samiti
+Location:
+Madhya Pradesh
+Apply by:
+30 Mar 2026
+Account Manager
+(Value Members only)
+Location:
+Odisha
+Apply by:
+10 Mar 2026
+Resource Person, Teacher Support – Ashram School ...
+Kavana Charitable Trust
+Location:
+Karnataka
+Apply by:
+02 Apr 2026
+Teach Manager, Child Development Team (Dual Role)
+U&amp;I Trust
+Location:
+India
+Apply by:
+31 Mar 2026
+Rural India Fellowship
+Katakhali Swapnopuron Welfare Society
+Location:
+West Bengal
 Apply by:
 15 Mar 2026
-RFQ: Construction of New gated check dams, De-sil...
-WaterAid India
-Location:
-Telangana
-Apply by:
-08 Mar 2026
-Regional Coordinator
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-Maharashtra
-Apply by:
-18 Mar 2026
-Project Nurse 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Project Technical Support 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Block Academic Coordinator
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-District Program Manager
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
 Jobseekers
 Register
 Login
@@ -7201,38 +6652,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F32" s="1" t="inlineStr">
+      <c r="F29" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G32" s="1" t="inlineStr">
+      <c r="G29" s="1" t="inlineStr">
         <is>
           <t>19-03-2026</t>
         </is>
       </c>
-      <c r="H32" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="I32" s="1" t="inlineStr">
+      <c r="H29" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="I29" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287207</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B33" s="1" t="inlineStr"/>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="B30" s="1" t="inlineStr"/>
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>Specialist - Grants</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Financial Management Service Foundation (FMSF) | Uttar Pradesh
 International Development - Specialist - Grants, Financial Management Service Foundation (FMSF), Uttar Pradesh - DevNetJobsIndia.org
@@ -7249,7 +6700,7 @@
 Job ... Read More</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>• Joining FMSF means becoming part of a passionate team dedicated to making a positive impact. We offer competitive compensation, opportunities for professional development, and a supportive work environment where your contributions are valued and recognized. If you are committed to driving positive change, promoting accountability and strengthening the development sector, we encourage you to apply for the position of Specialist - Grants at FMSF.
 You’re Resume to be accompanied with:
@@ -7271,6 +6722,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -7327,54 +6784,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFP - Requirement of Agency for Creating High Qua...
-Nature Conservancy India Solutions Private Limite...
-Location:
-Delhi
-Apply by:
-20 Mar 2026
-Programme officers (Education &amp; Life Skills Educa...
-Butterflies NGO
-Location:
-Delhi
+Documentation / Program Officer
+Pragati Path Foundation
+Location:
+Uttar Pradesh
+Apply by:
+25 Mar 2026
+Accounts Officer
+Jana Kalayana Samakhya
+Location:
+Odisha
+Apply by:
+30 Mar 2026
+Manager - Accounts &amp; Finance
+(Value Members only)
+Location:
+Rajasthan
+Apply by:
+13 Mar 2026
+Project Coordinator
+Asra Samajik Lok Kalyan Samiti
+Location:
+Madhya Pradesh
+Apply by:
+30 Mar 2026
+Account Manager
+(Value Members only)
+Location:
+Odisha
+Apply by:
+10 Mar 2026
+Resource Person, Teacher Support – Ashram School ...
+Kavana Charitable Trust
+Location:
+Karnataka
+Apply by:
+02 Apr 2026
+Teach Manager, Child Development Team (Dual Role)
+U&amp;I Trust
+Location:
+India
+Apply by:
+31 Mar 2026
+Rural India Fellowship
+Katakhali Swapnopuron Welfare Society
+Location:
+West Bengal
 Apply by:
 15 Mar 2026
-RFQ: Construction of New gated check dams, De-sil...
-WaterAid India
-Location:
-Telangana
-Apply by:
-08 Mar 2026
-Regional Coordinator
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-Maharashtra
-Apply by:
-18 Mar 2026
-Project Nurse 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Project Technical Support 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Block Academic Coordinator
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-District Program Manager
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
 Jobseekers
 Register
 Login
@@ -7402,38 +6859,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F33" s="1" t="inlineStr">
+      <c r="F30" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G33" s="1" t="inlineStr">
+      <c r="G30" s="1" t="inlineStr">
         <is>
           <t>21-03-2026</t>
         </is>
       </c>
-      <c r="H33" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="I33" s="1" t="inlineStr">
+      <c r="H30" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="I30" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287318</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr"/>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="B31" s="1" t="inlineStr"/>
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>EoI – Mobile Medical Units, Ai-Enabled Tb Screening &amp; Supply Of Medical An...</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Ashray Foundation | Korba, Chattisgarh (Delivery Location), Gujarat
 International Development - EoI – Mobile Medical Units, Ai-Enabled Tb Screening &amp; Supply Of Medical And Nutritional Support, Ashray Foundation, Gujarat - DevNetJobsIndia.org
@@ -7446,7 +6903,7 @@
 Broadc ... Read More</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>• Ashray Foundation invites eligible and experienced agencies to submit their Expression of Interest / for the following scope of work:
 Fabrication of Mobile Medical Units (MMUs) – 2 Units
@@ -7473,6 +6930,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -7529,54 +6992,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFP - Requirement of Agency for Creating High Qua...
-Nature Conservancy India Solutions Private Limite...
-Location:
-Delhi
-Apply by:
-20 Mar 2026
-Programme officers (Education &amp; Life Skills Educa...
-Butterflies NGO
-Location:
-Delhi
+Documentation / Program Officer
+Pragati Path Foundation
+Location:
+Uttar Pradesh
+Apply by:
+25 Mar 2026
+Accounts Officer
+Jana Kalayana Samakhya
+Location:
+Odisha
+Apply by:
+30 Mar 2026
+Manager - Accounts &amp; Finance
+(Value Members only)
+Location:
+Rajasthan
+Apply by:
+13 Mar 2026
+Project Coordinator
+Asra Samajik Lok Kalyan Samiti
+Location:
+Madhya Pradesh
+Apply by:
+30 Mar 2026
+Account Manager
+(Value Members only)
+Location:
+Odisha
+Apply by:
+10 Mar 2026
+Resource Person, Teacher Support – Ashram School ...
+Kavana Charitable Trust
+Location:
+Karnataka
+Apply by:
+02 Apr 2026
+Teach Manager, Child Development Team (Dual Role)
+U&amp;I Trust
+Location:
+India
+Apply by:
+31 Mar 2026
+Rural India Fellowship
+Katakhali Swapnopuron Welfare Society
+Location:
+West Bengal
 Apply by:
 15 Mar 2026
-RFQ: Construction of New gated check dams, De-sil...
-WaterAid India
-Location:
-Telangana
-Apply by:
-08 Mar 2026
-Regional Coordinator
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-Maharashtra
-Apply by:
-18 Mar 2026
-Project Nurse 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Project Technical Support 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Block Academic Coordinator
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-District Program Manager
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
 Jobseekers
 Register
 Login
@@ -7604,261 +7067,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F34" s="1" t="inlineStr">
+      <c r="F31" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G34" s="1" t="inlineStr">
+      <c r="G31" s="1" t="inlineStr">
         <is>
           <t>24-03-2026</t>
         </is>
       </c>
-      <c r="H34" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="I34" s="1" t="inlineStr">
+      <c r="H31" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="I31" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287319</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr"/>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>Junior Research Technicians / Senior Project Asso...</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>Starshield Security Solution Pvt.Ltd | Uttar Pradesh
-International Development - Junior Research Technicians / Senior Project Associate, Starshield Security Solution Pvt.Ltd, Uttar Pradesh - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search ... Read More</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>• Eligibility Criteria
-Qualification
-:
-Intermediate with 2–3 years of relevant experience
-OR
-Graduate with 1–2 years of relevant experience
-Skills &amp; Experience (Mandatory):
-Experience in agriculture field operations and data collection
-Basic knowledge of MS Office (Word &amp; Excel)
-Experience in rice-wheat cropping system production preferred
-Good coordination and communication skills
-Willingness to travel and work in field conditions
-Knowledge of smart mobile apps for data survey and data recording
-Knowledge on agri machinery
-Community mobilization and Work with Farmers group/FPCs
-The applicants must have a two-wheeler vehicle and license with them
-Key Performance Indicators
-Timely support to demonstrations, trainings, and field activities
-Accurate data collection and documentation
-Proper maintenance of equipment and field sites
-Positive feedback from farmers and stakeholders
-Creation of new service providers
-Application Details
-Interested candidates are requested to fill-out the shared application form and submit their updated CV via email to
-communications@starshieldsolution.com
-with the subject line:
-Application for Junior Research Technician (IRRI Project Deployment)
-.
-Only shortlisted candidates who complete the required documentation will be considered for subsequent stages of selection.
-Selection will be done on a first-come-first-served basis. Applications received up to Thursday each week will be reviewed, and interviews will be conducted in the following week. As soon as we shall finish all recruitment, we will take the advertisement off.
-• Job Email ID:
-communications(at)starshieldsolution.com
-Download Attachment:
-Application Proforma_Junior Research Technicians -  Senior Project Associate.doc
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-30 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-RFP - Requirement of Agency for Creating High Qua...
-Nature Conservancy India Solutions Private Limite...
-Location:
-Delhi
-Apply by:
-20 Mar 2026
-Programme officers (Education &amp; Life Skills Educa...
-Butterflies NGO
-Location:
-Delhi
-Apply by:
-15 Mar 2026
-RFQ: Construction of New gated check dams, De-sil...
-WaterAid India
-Location:
-Telangana
-Apply by:
-08 Mar 2026
-Regional Coordinator
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-Maharashtra
-Apply by:
-18 Mar 2026
-Project Nurse 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Project Technical Support 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Block Academic Coordinator
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-District Program Manager
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F35" s="1" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="G35" s="1" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="H35" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="I35" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287635</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="inlineStr"/>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="B32" s="1" t="inlineStr"/>
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>Agriculture Research Development Officer / Projec...</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Starshield Security Solution Pvt.Ltd | Uttar Pradesh
 International Development - Agriculture Research Development Officer / Project Scientist III, Starshield Security Solution Pvt.Ltd, Uttar Pradesh - DevNetJobsIndia.org
@@ -7872,7 +7112,7 @@
 RFPs/Tende ... Read More</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>• Eligibility Criteria
 Qualification:
@@ -7919,6 +7159,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -7975,54 +7221,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFP - Requirement of Agency for Creating High Qua...
-Nature Conservancy India Solutions Private Limite...
-Location:
-Delhi
-Apply by:
-20 Mar 2026
-Programme officers (Education &amp; Life Skills Educa...
-Butterflies NGO
-Location:
-Delhi
+Documentation / Program Officer
+Pragati Path Foundation
+Location:
+Uttar Pradesh
+Apply by:
+25 Mar 2026
+Accounts Officer
+Jana Kalayana Samakhya
+Location:
+Odisha
+Apply by:
+30 Mar 2026
+Manager - Accounts &amp; Finance
+(Value Members only)
+Location:
+Rajasthan
+Apply by:
+13 Mar 2026
+Project Coordinator
+Asra Samajik Lok Kalyan Samiti
+Location:
+Madhya Pradesh
+Apply by:
+30 Mar 2026
+Account Manager
+(Value Members only)
+Location:
+Odisha
+Apply by:
+10 Mar 2026
+Resource Person, Teacher Support – Ashram School ...
+Kavana Charitable Trust
+Location:
+Karnataka
+Apply by:
+02 Apr 2026
+Teach Manager, Child Development Team (Dual Role)
+U&amp;I Trust
+Location:
+India
+Apply by:
+31 Mar 2026
+Rural India Fellowship
+Katakhali Swapnopuron Welfare Society
+Location:
+West Bengal
 Apply by:
 15 Mar 2026
-RFQ: Construction of New gated check dams, De-sil...
-WaterAid India
-Location:
-Telangana
-Apply by:
-08 Mar 2026
-Regional Coordinator
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-Maharashtra
-Apply by:
-18 Mar 2026
-Project Nurse 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Project Technical Support 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Block Academic Coordinator
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-District Program Manager
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
 Jobseekers
 Register
 Login
@@ -8050,38 +7296,267 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F36" s="1" t="inlineStr">
+      <c r="F32" s="1" t="inlineStr">
         <is>
           <t>Learning, Safety</t>
         </is>
       </c>
-      <c r="G36" s="1" t="inlineStr">
+      <c r="G32" s="1" t="inlineStr">
         <is>
           <t>30-03-2026</t>
         </is>
       </c>
-      <c r="H36" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="I36" s="1" t="inlineStr">
+      <c r="H32" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="I32" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287636</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr"/>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="B33" s="1" t="inlineStr"/>
+      <c r="C33" s="1" t="inlineStr">
+        <is>
+          <t>Junior Research Technicians / Senior Project Asso...</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Starshield Security Solution Pvt.Ltd | Uttar Pradesh
+International Development - Junior Research Technicians / Senior Project Associate, Starshield Security Solution Pvt.Ltd, Uttar Pradesh - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search ... Read More</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>• Eligibility Criteria
+Qualification
+:
+Intermediate with 2–3 years of relevant experience
+OR
+Graduate with 1–2 years of relevant experience
+Skills &amp; Experience (Mandatory):
+Experience in agriculture field operations and data collection
+Basic knowledge of MS Office (Word &amp; Excel)
+Experience in rice-wheat cropping system production preferred
+Good coordination and communication skills
+Willingness to travel and work in field conditions
+Knowledge of smart mobile apps for data survey and data recording
+Knowledge on agri machinery
+Community mobilization and Work with Farmers group/FPCs
+The applicants must have a two-wheeler vehicle and license with them
+Key Performance Indicators
+Timely support to demonstrations, trainings, and field activities
+Accurate data collection and documentation
+Proper maintenance of equipment and field sites
+Positive feedback from farmers and stakeholders
+Creation of new service providers
+Application Details
+Interested candidates are requested to fill-out the shared application form and submit their updated CV via email to
+communications@starshieldsolution.com
+with the subject line:
+Application for Junior Research Technician (IRRI Project Deployment)
+.
+Only shortlisted candidates who complete the required documentation will be considered for subsequent stages of selection.
+Selection will be done on a first-come-first-served basis. Applications received up to Thursday each week will be reviewed, and interviews will be conducted in the following week. As soon as we shall finish all recruitment, we will take the advertisement off.
+• Job Email ID:
+communications(at)starshieldsolution.com
+Download Attachment:
+Application Proforma_Junior Research Technicians -  Senior Project Associate.doc
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+30 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Associate (Programme Management)
+Indian Institute For Human Settlements (Iihs)
+Location:
+Karnataka
+Apply by:
+07 Mar 2026
+Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+Documentation / Program Officer
+Pragati Path Foundation
+Location:
+Uttar Pradesh
+Apply by:
+25 Mar 2026
+Accounts Officer
+Jana Kalayana Samakhya
+Location:
+Odisha
+Apply by:
+30 Mar 2026
+Manager - Accounts &amp; Finance
+(Value Members only)
+Location:
+Rajasthan
+Apply by:
+13 Mar 2026
+Project Coordinator
+Asra Samajik Lok Kalyan Samiti
+Location:
+Madhya Pradesh
+Apply by:
+30 Mar 2026
+Account Manager
+(Value Members only)
+Location:
+Odisha
+Apply by:
+10 Mar 2026
+Resource Person, Teacher Support – Ashram School ...
+Kavana Charitable Trust
+Location:
+Karnataka
+Apply by:
+02 Apr 2026
+Teach Manager, Child Development Team (Dual Role)
+U&amp;I Trust
+Location:
+India
+Apply by:
+31 Mar 2026
+Rural India Fellowship
+Katakhali Swapnopuron Welfare Society
+Location:
+West Bengal
+Apply by:
+15 Mar 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F33" s="1" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="G33" s="1" t="inlineStr">
+        <is>
+          <t>30-03-2026</t>
+        </is>
+      </c>
+      <c r="H33" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="I33" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287635</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="inlineStr"/>
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>Sector Experts</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Academy of Management Studies (AMS) | India
 International Development - Sector Experts, Academy of Management Studies (AMS), India - DevNetJobsIndia.org
@@ -8102,7 +7577,7 @@
 Jobseekers Login ... Read More</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>• Eligibility
 Postgraduate degree / Ph.D. in relevant or allied disciplines
@@ -8136,6 +7611,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -8192,54 +7673,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFP - Requirement of Agency for Creating High Qua...
-Nature Conservancy India Solutions Private Limite...
-Location:
-Delhi
-Apply by:
-20 Mar 2026
-Programme officers (Education &amp; Life Skills Educa...
-Butterflies NGO
-Location:
-Delhi
+Documentation / Program Officer
+Pragati Path Foundation
+Location:
+Uttar Pradesh
+Apply by:
+25 Mar 2026
+Accounts Officer
+Jana Kalayana Samakhya
+Location:
+Odisha
+Apply by:
+30 Mar 2026
+Manager - Accounts &amp; Finance
+(Value Members only)
+Location:
+Rajasthan
+Apply by:
+13 Mar 2026
+Project Coordinator
+Asra Samajik Lok Kalyan Samiti
+Location:
+Madhya Pradesh
+Apply by:
+30 Mar 2026
+Account Manager
+(Value Members only)
+Location:
+Odisha
+Apply by:
+10 Mar 2026
+Resource Person, Teacher Support – Ashram School ...
+Kavana Charitable Trust
+Location:
+Karnataka
+Apply by:
+02 Apr 2026
+Teach Manager, Child Development Team (Dual Role)
+U&amp;I Trust
+Location:
+India
+Apply by:
+31 Mar 2026
+Rural India Fellowship
+Katakhali Swapnopuron Welfare Society
+Location:
+West Bengal
 Apply by:
 15 Mar 2026
-RFQ: Construction of New gated check dams, De-sil...
-WaterAid India
-Location:
-Telangana
-Apply by:
-08 Mar 2026
-Regional Coordinator
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-Maharashtra
-Apply by:
-18 Mar 2026
-Project Nurse 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Project Technical Support 1
-Centre for Chronic Disease Control (CCDC)
-Location:
-India
-Apply by:
-15 Mar 2026
-Block Academic Coordinator
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
-District Program Manager
-Language and Learning Foundation (LLF)
-Location:
-Chhattisgarh
-Apply by:
-02 Apr 2026
 Jobseekers
 Register
 Login
@@ -8267,22 +7748,103 @@
 Recruitment Exchange</t>
         </is>
       </c>
+      <c r="F34" s="1" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G34" s="1" t="inlineStr">
+        <is>
+          <t>31-03-2026</t>
+        </is>
+      </c>
+      <c r="H34" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="I34" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287726</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="inlineStr"/>
+      <c r="C35" s="1" t="inlineStr">
+        <is>
+          <t>RFP for Endline Evaluation Study - HSBC GCC Women Entrepreneurship Program - Click here</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr"/>
+      <c r="E35" s="2" t="inlineStr"/>
+      <c r="F35" s="1" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G35" s="1" t="inlineStr"/>
+      <c r="H35" s="1" t="inlineStr"/>
+      <c r="I35" s="1" t="inlineStr">
+        <is>
+          <t>https://www.nasscomfoundation.org/pdf/endline-evaluation-study-hsbc-gcc-women-entrepreneurship-program.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="inlineStr"/>
+      <c r="C36" s="1" t="inlineStr">
+        <is>
+          <t>Travel &amp; Transportation Services for Trainer Mobility - IBM SkillBuild Bootcamps - Click here</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G36" s="1" t="inlineStr"/>
+      <c r="H36" s="1" t="inlineStr"/>
+      <c r="I36" s="1" t="inlineStr">
+        <is>
+          <t>https://www.nasscomfoundation.org/pdf/travel-and-transportation-services-for-trainer-mobility-ibm-skillbuild-bootcamps.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="inlineStr"/>
+      <c r="C37" s="1" t="inlineStr">
+        <is>
+          <t>Baseline and End-line Evaluation of the HSBC Neurodivergent Digital Annotator Skilling Program - Click here | Click here</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr"/>
+      <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G37" s="1" t="inlineStr">
-        <is>
-          <t>31-03-2026</t>
-        </is>
-      </c>
-      <c r="H37" s="1" t="n">
-        <v>28</v>
-      </c>
+      <c r="G37" s="1" t="inlineStr"/>
+      <c r="H37" s="1" t="inlineStr"/>
       <c r="I37" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287726</t>
+          <t>https://www.nasscomfoundation.org/pdf/baseline-and-end-line-evaluation-of-hsbc-neurodivergent-digital-annotator-skilling-program.pdf</t>
         </is>
       </c>
     </row>
@@ -8295,21 +7857,21 @@
       <c r="B38" s="1" t="inlineStr"/>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>RFP for Endline Evaluation Study - HSBC GCC Women Entrepreneurship Program - Click here</t>
+          <t>RFP for Catering Vendor - IBM Skillbuild Bootcamps - Click here</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr"/>
       <c r="H38" s="1" t="inlineStr"/>
       <c r="I38" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/endline-evaluation-study-hsbc-gcc-women-entrepreneurship-program.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/rfp-for-catering-vendor-ibm-skillbuild-bootcamps.pdf</t>
         </is>
       </c>
     </row>
@@ -8322,21 +7884,21 @@
       <c r="B39" s="1" t="inlineStr"/>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>Travel &amp; Transportation Services for Trainer Mobility - IBM SkillBuild Bootcamps - Click here</t>
+          <t>Organization-wide Management Information System (MIS) for Nasscom Foundation - Click here</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G39" s="1" t="inlineStr"/>
       <c r="H39" s="1" t="inlineStr"/>
       <c r="I39" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/travel-and-transportation-services-for-trainer-mobility-ibm-skillbuild-bootcamps.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/organization-wide-management-information-system-for-nasscom-foundation.pdf</t>
         </is>
       </c>
     </row>
@@ -8349,7 +7911,7 @@
       <c r="B40" s="1" t="inlineStr"/>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>Baseline and End-line Evaluation of the HSBC Neurodivergent Digital Annotator Skilling Program - Click here | Click here</t>
+          <t>Request for Proposal (RFP) for Social Media Management Services - Click here</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr"/>
@@ -8363,7 +7925,7 @@
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/baseline-and-end-line-evaluation-of-hsbc-neurodivergent-digital-annotator-skilling-program.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/request-for-proposal-for-social-media-management-services.pdf</t>
         </is>
       </c>
     </row>
@@ -8376,21 +7938,21 @@
       <c r="B41" s="1" t="inlineStr"/>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>RFP for Catering Vendor - IBM Skillbuild Bootcamps - Click here</t>
+          <t>RFP - TechForSociety - Evaluation Study - Click here</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr"/>
       <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G41" s="1" t="inlineStr"/>
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/rfp-for-catering-vendor-ibm-skillbuild-bootcamps.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/techforsociety-evaluation-study.pdf</t>
         </is>
       </c>
     </row>
@@ -8403,7 +7965,7 @@
       <c r="B42" s="1" t="inlineStr"/>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>Organization-wide Management Information System (MIS) for Nasscom Foundation - Click here</t>
+          <t>Base-line and End-line evaluation for Digital Literacy Project in 4 States - Click here</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr"/>
@@ -8417,7 +7979,7 @@
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/organization-wide-management-information-system-for-nasscom-foundation.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/base-line-and-end-line-evaluation-for-digital-literacy-project-in-4-states.pdf</t>
         </is>
       </c>
     </row>
@@ -8430,21 +7992,21 @@
       <c r="B43" s="1" t="inlineStr"/>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>Request for Proposal (RFP) for Social Media Management Services - Click here</t>
+          <t>IP Selection - Scholarship Support to students from Economically Weaker Section pursuing higher education in STEM courses - Click here</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
       <c r="E43" s="2" t="inlineStr"/>
       <c r="F43" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G43" s="1" t="inlineStr"/>
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/request-for-proposal-for-social-media-management-services.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/scholarship-support-for-economically-weaker-section-students-in-stem-higher-education.pdf</t>
         </is>
       </c>
     </row>
@@ -8457,21 +8019,21 @@
       <c r="B44" s="1" t="inlineStr"/>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>RFP - TechForSociety - Evaluation Study - Click here</t>
+          <t>Digital Upskilling of Farmer Producer Organizations (FPOs) through Technology - Click here</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
       <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G44" s="1" t="inlineStr"/>
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/techforsociety-evaluation-study.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/baseline-endline-study-digital-upskilling-fpos-technology.pdf</t>
         </is>
       </c>
     </row>
@@ -8484,21 +8046,21 @@
       <c r="B45" s="1" t="inlineStr"/>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>Base-line and End-line evaluation for Digital Literacy Project in 4 States - Click here</t>
+          <t>Project - Accelerating 100 Women Micro Entrepreneurs of Northeastern States - Click here</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
       <c r="E45" s="2" t="inlineStr"/>
       <c r="F45" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G45" s="1" t="inlineStr"/>
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/base-line-and-end-line-evaluation-for-digital-literacy-project-in-4-states.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/project-accelerating-100-women-micro-entrepreneurs-of-northeastern-states.pdf</t>
         </is>
       </c>
     </row>
@@ -8511,21 +8073,21 @@
       <c r="B46" s="1" t="inlineStr"/>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>IP Selection - Scholarship Support to students from Economically Weaker Section pursuing higher education in STEM courses - Click here</t>
+          <t>Agency for Developing Training Modules and Conducting Training of Trainers (ToT) for MSMEs on IPR and Financial Management - Click here</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G46" s="1" t="inlineStr"/>
       <c r="H46" s="1" t="inlineStr"/>
       <c r="I46" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/scholarship-support-for-economically-weaker-section-students-in-stem-higher-education.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/agency-for-developing-training-modules-and-conducting-ToT-for-MSMEs-on-IPR-and-financial-management.pdf</t>
         </is>
       </c>
     </row>
@@ -8538,7 +8100,7 @@
       <c r="B47" s="1" t="inlineStr"/>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>Digital Upskilling of Farmer Producer Organizations (FPOs) through Technology - Click here</t>
+          <t>RFP for WISE - Women in Innovation, Skills &amp; Entrepreneurship - Click here</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
@@ -8552,7 +8114,7 @@
       <c r="H47" s="1" t="inlineStr"/>
       <c r="I47" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/baseline-endline-study-digital-upskilling-fpos-technology.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/women-in-Innovation-skills-and-entrepreneurship.pdf</t>
         </is>
       </c>
     </row>
@@ -8565,7 +8127,7 @@
       <c r="B48" s="1" t="inlineStr"/>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>Project - Accelerating 100 Women Micro Entrepreneurs of Northeastern States - Click here</t>
+          <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - English  - Click here</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
@@ -8579,7 +8141,7 @@
       <c r="H48" s="1" t="inlineStr"/>
       <c r="I48" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/project-accelerating-100-women-micro-entrepreneurs-of-northeastern-states.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-English.pdf</t>
         </is>
       </c>
     </row>
@@ -8592,21 +8154,21 @@
       <c r="B49" s="1" t="inlineStr"/>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>Agency for Developing Training Modules and Conducting Training of Trainers (ToT) for MSMEs on IPR and Financial Management - Click here</t>
+          <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - Kannada - Click here</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
       <c r="E49" s="2" t="inlineStr"/>
       <c r="F49" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G49" s="1" t="inlineStr"/>
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/agency-for-developing-training-modules-and-conducting-ToT-for-MSMEs-on-IPR-and-financial-management.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-Kannada.pdf</t>
         </is>
       </c>
     </row>
@@ -8619,7 +8181,7 @@
       <c r="B50" s="1" t="inlineStr"/>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>RFP for WISE - Women in Innovation, Skills &amp; Entrepreneurship - Click here</t>
+          <t>RFP - Trainer for Nano Women Entrepreneurs in Karnataka - Click here</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
@@ -8633,7 +8195,7 @@
       <c r="H50" s="1" t="inlineStr"/>
       <c r="I50" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/women-in-Innovation-skills-and-entrepreneurship.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/trainer-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
         </is>
       </c>
     </row>
@@ -8646,7 +8208,7 @@
       <c r="B51" s="1" t="inlineStr"/>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - English  - Click here</t>
+          <t>RFP - Training Agency with Content and Trainers for Nano Women Entrepreneurs in Karnataka - Click here</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
@@ -8660,7 +8222,7 @@
       <c r="H51" s="1" t="inlineStr"/>
       <c r="I51" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-English.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/training-agency-with-content-and-trainers-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
         </is>
       </c>
     </row>
@@ -8673,21 +8235,21 @@
       <c r="B52" s="1" t="inlineStr"/>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - Kannada - Click here</t>
+          <t>Access to E-Governance and Livelihood in PVTG Communities in Aspirational Blocks - Click here</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
       <c r="E52" s="2" t="inlineStr"/>
       <c r="F52" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G52" s="1" t="inlineStr"/>
       <c r="H52" s="1" t="inlineStr"/>
       <c r="I52" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-Kannada.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/access-to-e-governance-and-livelihood-in-pvtg-communities-in-aspirational-blocks.pdf</t>
         </is>
       </c>
     </row>
@@ -8700,7 +8262,7 @@
       <c r="B53" s="1" t="inlineStr"/>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>RFP - Trainer for Nano Women Entrepreneurs in Karnataka - Click here</t>
+          <t>thingQbator Portal Enhancement and Maintenance Proposal - Click here</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
@@ -8714,74 +8276,94 @@
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/trainer-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/thingQbator-portal-enhancement-and-maintenance-proposal.pdf</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B54" s="1" t="inlineStr"/>
+          <t>HCL Foundation</t>
+        </is>
+      </c>
+      <c r="B54" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>RFP - Training Agency with Content and Trainers for Nano Women Entrepreneurs in Karnataka - Click here</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards Biodiversity monitoring for Pan-India Afforestation sites</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
       <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G54" s="1" t="inlineStr"/>
+          <t>Climate</t>
+        </is>
+      </c>
+      <c r="G54" s="1" t="inlineStr">
+        <is>
+          <t>10th Feb, 2026</t>
+        </is>
+      </c>
       <c r="H54" s="1" t="inlineStr"/>
       <c r="I54" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/training-agency-with-content-and-trainers-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Biodiversity%20monitoring%20for%20Pan-India%20Afforestation%20sites%202-DSB.pdf</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B55" s="1" t="inlineStr"/>
+          <t>HCL Foundation</t>
+        </is>
+      </c>
+      <c r="B55" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>Access to E-Governance and Livelihood in PVTG Communities in Aspirational Blocks - Click here</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards soil profiling and assessment from the restored and rejuvenated Harit sites.</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr"/>
       <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G55" s="1" t="inlineStr"/>
+          <t>Climate</t>
+        </is>
+      </c>
+      <c r="G55" s="1" t="inlineStr">
+        <is>
+          <t>10th Feb, 2026</t>
+        </is>
+      </c>
       <c r="H55" s="1" t="inlineStr"/>
       <c r="I55" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/access-to-e-governance-and-livelihood-in-pvtg-communities-in-aspirational-blocks.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Soil%20assessment-v1%20RKS-DSB_0.pdf</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B56" s="1" t="inlineStr"/>
+          <t>HCL Foundation</t>
+        </is>
+      </c>
+      <c r="B56" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>thingQbator Portal Enhancement and Maintenance Proposal - Click here</t>
+          <t>HCLFoundation invites proposals from NGOs/CSR implementing agencies for ‘Operating a Social Enterprise Cafe” under the flagship urban development programme - Uday</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
@@ -8791,11 +8373,15 @@
           <t>Learning</t>
         </is>
       </c>
-      <c r="G56" s="1" t="inlineStr"/>
+      <c r="G56" s="1" t="inlineStr">
+        <is>
+          <t>15th Dec, 2025</t>
+        </is>
+      </c>
       <c r="H56" s="1" t="inlineStr"/>
       <c r="I56" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/thingQbator-portal-enhancement-and-maintenance-proposal.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-11/RfP_Social%20Enterprise%20Cafe_UDAY.docx</t>
         </is>
       </c>
     </row>
@@ -8812,25 +8398,25 @@
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards Biodiversity monitoring for Pan-India Afforestation sites</t>
+          <t>Programme Officer/Senior Programme Officer – Environment Education</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr"/>
       <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="1" t="inlineStr">
         <is>
-          <t>Climate</t>
+          <t>Learning, Climate</t>
         </is>
       </c>
       <c r="G57" s="1" t="inlineStr">
         <is>
-          <t>10th Feb, 2026</t>
+          <t>10th Nov, 2025</t>
         </is>
       </c>
       <c r="H57" s="1" t="inlineStr"/>
       <c r="I57" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Biodiversity%20monitoring%20for%20Pan-India%20Afforestation%20sites%202-DSB.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-10/Harit_POSPO_EEA_Multilocation_Oct%202025.pdf</t>
         </is>
       </c>
     </row>
@@ -8847,25 +8433,25 @@
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards soil profiling and assessment from the restored and rejuvenated Harit sites.</t>
+          <t>HCLFoundation invites applications for the PO/SPO position under its flagship programme Harit by HCLFoundation</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr"/>
       <c r="E58" s="2" t="inlineStr"/>
       <c r="F58" s="1" t="inlineStr">
         <is>
-          <t>Climate</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G58" s="1" t="inlineStr">
         <is>
-          <t>10th Feb, 2026</t>
+          <t>31st Oct, 2025</t>
         </is>
       </c>
       <c r="H58" s="1" t="inlineStr"/>
       <c r="I58" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Soil%20assessment-v1%20RKS-DSB_0.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-10/JD_Water%20Conservation_SPO%20V4.pdf</t>
         </is>
       </c>
     </row>
@@ -8882,25 +8468,25 @@
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites proposals from NGOs/CSR implementing agencies for ‘Operating a Social Enterprise Cafe” under the flagship urban development programme - Uday</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit by HCLFoundation, invites RFP from NGOs / CSR organizations working in Water Conservation for the development of Water Structures etc.</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr"/>
       <c r="E59" s="2" t="inlineStr"/>
       <c r="F59" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Learning, Climate</t>
         </is>
       </c>
       <c r="G59" s="1" t="inlineStr">
         <is>
-          <t>15th Dec, 2025</t>
+          <t>21st May, 2025</t>
         </is>
       </c>
       <c r="H59" s="1" t="inlineStr"/>
       <c r="I59" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-11/RfP_Social%20Enterprise%20Cafe_UDAY.docx</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/Final_RFP%20for%20water%20structure%20rejuvenation%20.docx</t>
         </is>
       </c>
     </row>
@@ -8917,25 +8503,25 @@
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>Programme Officer/Senior Programme Officer – Environment Education</t>
+          <t>HCLFoundation invites technical application abstracts for the developing technology drive source code model mobile applications and web portals for addressing human-animal interactions under the Animal Welfare thematic of  Harit by HCLFoundation</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr"/>
       <c r="E60" s="2" t="inlineStr"/>
       <c r="F60" s="1" t="inlineStr">
         <is>
-          <t>Learning, Climate</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G60" s="1" t="inlineStr">
         <is>
-          <t>10th Nov, 2025</t>
+          <t>15th May, 2025</t>
         </is>
       </c>
       <c r="H60" s="1" t="inlineStr"/>
       <c r="I60" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-10/Harit_POSPO_EEA_Multilocation_Oct%202025.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_AW%20Tech%20Based%20Source%20Code%20Model_V1%20%281%29.docx</t>
         </is>
       </c>
     </row>
@@ -8952,25 +8538,25 @@
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites applications for the PO/SPO position under its flagship programme Harit by HCLFoundation</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit invites RFP from NGOs/CSR organizations working in the field of environment for project on the restoration of various degraded and natural habitats</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr"/>
       <c r="E61" s="2" t="inlineStr"/>
       <c r="F61" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Climate</t>
         </is>
       </c>
       <c r="G61" s="1" t="inlineStr">
         <is>
-          <t>31st Oct, 2025</t>
+          <t>15th May, 2025</t>
         </is>
       </c>
       <c r="H61" s="1" t="inlineStr"/>
       <c r="I61" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-10/JD_Water%20Conservation_SPO%20V4.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/Harit_A%20HR_RFP%20.docx</t>
         </is>
       </c>
     </row>
@@ -8987,25 +8573,25 @@
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit by HCLFoundation, invites RFP from NGOs / CSR organizations working in Water Conservation for the development of Water Structures etc.</t>
+          <t>HCLFoundation invites EOI for conducting holistic and comprehensive Impact Assessments of environmental projects supported under Harit by HCLFoundation</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr"/>
       <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="1" t="inlineStr">
         <is>
-          <t>Learning, Climate</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G62" s="1" t="inlineStr">
         <is>
-          <t>21st May, 2025</t>
+          <t>15th May, 2025</t>
         </is>
       </c>
       <c r="H62" s="1" t="inlineStr"/>
       <c r="I62" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/Final_RFP%20for%20water%20structure%20rejuvenation%20.docx</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_Harit%20Impact%20Assessments.docx</t>
         </is>
       </c>
     </row>
@@ -9022,14 +8608,14 @@
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites technical application abstracts for the developing technology drive source code model mobile applications and web portals for addressing human-animal interactions under the Animal Welfare thematic of  Harit by HCLFoundation</t>
+          <t>HCLFoundation invites technical application abstracts for the conducting technical and highly engaging environment awareness and sustainability workshops under Harit by HCLFoundation</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr"/>
       <c r="E63" s="2" t="inlineStr"/>
       <c r="F63" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Climate</t>
         </is>
       </c>
       <c r="G63" s="1" t="inlineStr">
@@ -9040,112 +8626,88 @@
       <c r="H63" s="1" t="inlineStr"/>
       <c r="I63" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_AW%20Tech%20Based%20Source%20Code%20Model_V1%20%281%29.docx</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_EEA_Env%20%20Sus%20awareness%20workshops_FY%2025-26%20%281%29.docx</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>HCL Foundation</t>
+          <t>NIUA</t>
         </is>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Tender</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit invites RFP from NGOs/CSR organizations working in the field of environment for project on the restoration of various degraded and natural habitats</t>
+          <t>Quotation_for_Rate_Contrac_Vehicle_Hiring_for_NCR_or_Outstation..pdf</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr"/>
       <c r="E64" s="2" t="inlineStr"/>
-      <c r="F64" s="1" t="inlineStr">
-        <is>
-          <t>Climate</t>
-        </is>
-      </c>
-      <c r="G64" s="1" t="inlineStr">
-        <is>
-          <t>15th May, 2025</t>
-        </is>
-      </c>
+      <c r="F64" s="1" t="inlineStr"/>
+      <c r="G64" s="1" t="inlineStr"/>
       <c r="H64" s="1" t="inlineStr"/>
       <c r="I64" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/Harit_A%20HR_RFP%20.docx</t>
+          <t>https://niua.in/sites/default/files/tenders/Quotation_for_Rate_Contrac_Vehicle_Hiring_for_NCR_or_Outstation..pdf</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>HCL Foundation</t>
+          <t>NIUA</t>
         </is>
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Tender</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites EOI for conducting holistic and comprehensive Impact Assessments of environmental projects supported under Harit by HCLFoundation</t>
+          <t>Final_RfP_UrbanShift_Preparation_of_Integrated_Green_Mobility_Plan_for_Pune.pdf</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr"/>
       <c r="E65" s="2" t="inlineStr"/>
-      <c r="F65" s="1" t="inlineStr">
-        <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G65" s="1" t="inlineStr">
-        <is>
-          <t>15th May, 2025</t>
-        </is>
-      </c>
+      <c r="F65" s="1" t="inlineStr"/>
+      <c r="G65" s="1" t="inlineStr"/>
       <c r="H65" s="1" t="inlineStr"/>
       <c r="I65" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_Harit%20Impact%20Assessments.docx</t>
+          <t>https://niua.in/sites/default/files/tenders/Final_RfP_UrbanShift_Preparation_of_Integrated_Green_Mobility_Plan_for_Pune.pdf</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>HCL Foundation</t>
+          <t>NIUA</t>
         </is>
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Tender</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites technical application abstracts for the conducting technical and highly engaging environment awareness and sustainability workshops under Harit by HCLFoundation</t>
+          <t>RfP_IGMP_Response to Pre-Bid Queries_200226.pdf</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
       <c r="E66" s="2" t="inlineStr"/>
-      <c r="F66" s="1" t="inlineStr">
-        <is>
-          <t>Climate</t>
-        </is>
-      </c>
-      <c r="G66" s="1" t="inlineStr">
-        <is>
-          <t>15th May, 2025</t>
-        </is>
-      </c>
+      <c r="F66" s="1" t="inlineStr"/>
+      <c r="G66" s="1" t="inlineStr"/>
       <c r="H66" s="1" t="inlineStr"/>
       <c r="I66" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_EEA_Env%20%20Sus%20awareness%20workshops_FY%2025-26%20%281%29.docx</t>
+          <t>https://niua.in/sites/default/files/tenders/RfP_IGMP_Response%20to%20Pre-Bid%20Queries_200226.pdf</t>
         </is>
       </c>
     </row>
@@ -9162,7 +8724,7 @@
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>Quotation_for_Rate_Contrac_Vehicle_Hiring_for_NCR_or_Outstation..pdf</t>
+          <t>Corrigendum_1_RfP_IGMP.pdf</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr"/>
@@ -9172,7 +8734,7 @@
       <c r="H67" s="1" t="inlineStr"/>
       <c r="I67" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Quotation_for_Rate_Contrac_Vehicle_Hiring_for_NCR_or_Outstation..pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/Corrigendum_1_RfP_IGMP.pdf</t>
         </is>
       </c>
     </row>
@@ -9189,7 +8751,7 @@
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>Final_RfP_UrbanShift_Preparation_of_Integrated_Green_Mobility_Plan_for_Pune.pdf</t>
+          <t>Corrigendum 2_IGMP.pdf</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr"/>
@@ -9199,7 +8761,7 @@
       <c r="H68" s="1" t="inlineStr"/>
       <c r="I68" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Final_RfP_UrbanShift_Preparation_of_Integrated_Green_Mobility_Plan_for_Pune.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/Corrigendum%202_IGMP.pdf</t>
         </is>
       </c>
     </row>
@@ -9216,7 +8778,7 @@
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>RfP_IGMP_Response to Pre-Bid Queries_200226.pdf</t>
+          <t>RFP_Engagement of GIS Expert_SCBP_2026.pdf</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr"/>
@@ -9226,7 +8788,7 @@
       <c r="H69" s="1" t="inlineStr"/>
       <c r="I69" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/RfP_IGMP_Response%20to%20Pre-Bid%20Queries_200226.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/RFP_Engagement%20of%20GIS%20Expert_SCBP_2026.pdf</t>
         </is>
       </c>
     </row>
@@ -9243,7 +8805,7 @@
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>Corrigendum_1_RfP_IGMP.pdf</t>
+          <t>Response_to_Queries_Engagement_of_GIS_Expert_Agency.pdf</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr"/>
@@ -9253,7 +8815,7 @@
       <c r="H70" s="1" t="inlineStr"/>
       <c r="I70" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Corrigendum_1_RfP_IGMP.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/Response_to_Queries_Engagement_of_GIS_Expert_Agency.pdf</t>
         </is>
       </c>
     </row>
@@ -9270,7 +8832,7 @@
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>Corrigendum 2_IGMP.pdf</t>
+          <t>RfP_SRTW.pdf</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr"/>
@@ -9280,7 +8842,7 @@
       <c r="H71" s="1" t="inlineStr"/>
       <c r="I71" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Corrigendum%202_IGMP.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/RfP_SRTW.pdf</t>
         </is>
       </c>
     </row>
@@ -9297,7 +8859,7 @@
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>RFP_Engagement of GIS Expert_SCBP_2026.pdf</t>
+          <t>Response to Pre-Bid Queries_SRTW_for Uploading.pdf</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr"/>
@@ -9307,7 +8869,7 @@
       <c r="H72" s="1" t="inlineStr"/>
       <c r="I72" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/RFP_Engagement%20of%20GIS%20Expert_SCBP_2026.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/Response%20to%20Pre-Bid%20Queries_SRTW_for%20Uploading.pdf</t>
         </is>
       </c>
     </row>
@@ -9324,7 +8886,7 @@
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>Response_to_Queries_Engagement_of_GIS_Expert_Agency.pdf</t>
+          <t>EOI_TECHNICAL_ASSISTANCE_UNDER_CITIIS_2.0_PROGRAM_DOMESTIC_POOL_OF_EXPERTS.pdf</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr"/>
@@ -9334,7 +8896,7 @@
       <c r="H73" s="1" t="inlineStr"/>
       <c r="I73" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Response_to_Queries_Engagement_of_GIS_Expert_Agency.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/EOI_TECHNICAL_ASSISTANCE_UNDER_CITIIS_2.0_PROGRAM_DOMESTIC_POOL_OF_EXPERTS.pdf</t>
         </is>
       </c>
     </row>
@@ -9351,7 +8913,7 @@
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>RfP_SRTW.pdf</t>
+          <t>Reply to Pre- Bid Queries - EOI for DE's under CITIIS 2.0.pdf</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr"/>
@@ -9361,7 +8923,7 @@
       <c r="H74" s="1" t="inlineStr"/>
       <c r="I74" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/RfP_SRTW.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/Reply%20to%20Pre-%20Bid%20Queries%20-%20EOI%20for%20DE%27s%20under%20CITIIS%202.0.pdf</t>
         </is>
       </c>
     </row>
@@ -9378,7 +8940,7 @@
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>Response to Pre-Bid Queries_SRTW_for Uploading.pdf</t>
+          <t>GeM-Bidding-8666471.pdf</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr"/>
@@ -9388,7 +8950,7 @@
       <c r="H75" s="1" t="inlineStr"/>
       <c r="I75" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Response%20to%20Pre-Bid%20Queries_SRTW_for%20Uploading.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-8666471.pdf</t>
         </is>
       </c>
     </row>
@@ -9405,7 +8967,7 @@
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>EOI_TECHNICAL_ASSISTANCE_UNDER_CITIIS_2.0_PROGRAM_DOMESTIC_POOL_OF_EXPERTS.pdf</t>
+          <t>corgaudt1.pdf</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr"/>
@@ -9415,7 +8977,7 @@
       <c r="H76" s="1" t="inlineStr"/>
       <c r="I76" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/EOI_TECHNICAL_ASSISTANCE_UNDER_CITIIS_2.0_PROGRAM_DOMESTIC_POOL_OF_EXPERTS.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/corgaudt1.pdf</t>
         </is>
       </c>
     </row>
@@ -9432,7 +8994,7 @@
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>Reply to Pre- Bid Queries - EOI for DE's under CITIIS 2.0.pdf</t>
+          <t>Corrigendum6959493.pdf</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr"/>
@@ -9442,7 +9004,7 @@
       <c r="H77" s="1" t="inlineStr"/>
       <c r="I77" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Reply%20to%20Pre-%20Bid%20Queries%20-%20EOI%20for%20DE%27s%20under%20CITIIS%202.0.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/Corrigendum6959493.pdf</t>
         </is>
       </c>
     </row>
@@ -9459,7 +9021,7 @@
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>GeM-Bidding-8666471.pdf</t>
+          <t>ADDENDUM6959493.pdf</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr"/>
@@ -9469,7 +9031,7 @@
       <c r="H78" s="1" t="inlineStr"/>
       <c r="I78" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-8666471.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/ADDENDUM6959493.pdf</t>
         </is>
       </c>
     </row>
@@ -9486,7 +9048,7 @@
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>corgaudt1.pdf</t>
+          <t>RfP CJ&amp;IP Package 03_UrbanShift.pdf</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr"/>
@@ -9496,7 +9058,7 @@
       <c r="H79" s="1" t="inlineStr"/>
       <c r="I79" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/corgaudt1.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/RfP%20CJ%26IP%20Package%2003_UrbanShift.pdf</t>
         </is>
       </c>
     </row>
@@ -9513,7 +9075,7 @@
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>Corrigendum6959493.pdf</t>
+          <t>Prebid reply Cj&amp;IP package 3_18.12.2025.pdf</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr"/>
@@ -9523,7 +9085,7 @@
       <c r="H80" s="1" t="inlineStr"/>
       <c r="I80" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Corrigendum6959493.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/Prebid%20reply%20Cj%26IP%20package%203_18.12.2025.pdf</t>
         </is>
       </c>
     </row>
@@ -9540,7 +9102,7 @@
       </c>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>ADDENDUM6959493.pdf</t>
+          <t>GeM-Bidding-8478801.pdf</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr"/>
@@ -9550,7 +9112,7 @@
       <c r="H81" s="1" t="inlineStr"/>
       <c r="I81" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/ADDENDUM6959493.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-8478801.pdf</t>
         </is>
       </c>
     </row>
@@ -9567,7 +9129,7 @@
       </c>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>RfP CJ&amp;IP Package 03_UrbanShift.pdf</t>
+          <t>GeM-Bidding-8476974.pdf</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr"/>
@@ -9577,7 +9139,7 @@
       <c r="H82" s="1" t="inlineStr"/>
       <c r="I82" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/RfP%20CJ%26IP%20Package%2003_UrbanShift.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-8476974.pdf</t>
         </is>
       </c>
     </row>
@@ -9594,7 +9156,7 @@
       </c>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>Prebid reply Cj&amp;IP package 3_18.12.2025.pdf</t>
+          <t>GeM-Bidding-8497150.pdf</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr"/>
@@ -9604,87 +9166,6 @@
       <c r="H83" s="1" t="inlineStr"/>
       <c r="I83" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Prebid%20reply%20Cj%26IP%20package%203_18.12.2025.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>GeM-Bidding-8478801.pdf</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr"/>
-      <c r="E84" s="2" t="inlineStr"/>
-      <c r="F84" s="1" t="inlineStr"/>
-      <c r="G84" s="1" t="inlineStr"/>
-      <c r="H84" s="1" t="inlineStr"/>
-      <c r="I84" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-8478801.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>GeM-Bidding-8476974.pdf</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr"/>
-      <c r="E85" s="2" t="inlineStr"/>
-      <c r="F85" s="1" t="inlineStr"/>
-      <c r="G85" s="1" t="inlineStr"/>
-      <c r="H85" s="1" t="inlineStr"/>
-      <c r="I85" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-8476974.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B86" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C86" s="1" t="inlineStr">
-        <is>
-          <t>GeM-Bidding-8497150.pdf</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr"/>
-      <c r="E86" s="2" t="inlineStr"/>
-      <c r="F86" s="1" t="inlineStr"/>
-      <c r="G86" s="1" t="inlineStr"/>
-      <c r="H86" s="1" t="inlineStr"/>
-      <c r="I86" s="1" t="inlineStr">
-        <is>
           <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-8497150.pdf</t>
         </is>
       </c>

--- a/all_grants.xlsx
+++ b/all_grants.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -489,44 +489,72 @@
       <c r="B2" s="1" t="inlineStr"/>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>EoI - Construction &amp; Infrastructure Works – Schools Of Pali And Jodhpur D...</t>
+          <t>RFQ - for the Supply of Seeds</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Ashray Foundation | Pali And Jodhpur Districts, Rajasthan
-International Development - EoI -  Construction &amp; Infrastructure Works – Schools Of Pali And Jodhpur Districts, Rajasthan, Ashray Foundation, Rajasthan - DevNetJobsIndia.org
+          <t>MAMTA Health Institute for Mother and Child (MAMTA) | India
+International Development - RFQ -  for the Supply of Seeds, MAMTA Health Institute for Mother and Child (MAMTA), India - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
 Register
 Home
 Value Membership
-Broadcast Resume ... Read More</t>
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Event ... Read More</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>• Scope of Work:
-Construction of Tin Sheds (12) and Additional Classrooms (15) in Govt. Schools, Upgradation of Sports Stadium (2)
-• Eligibility Criteria:
-Interested agencies must meet the following requirements:
-Valid statutory registrations (GST, PAN, etc.).
-Minimum relevant experience of 3 years in same activity is mandatory
-Demonstrated capacity and team to execute projects within strict timelines and quality
-• Submission Details:
-Interested agencies are requested to submit their EOI along with: Company Profile, Details of Relevant Project Experience, Copies of Necessary Registration &amp; Compliance Documents and Geo-tagged Photographs of the work undertaken, if any
-Last Date for Submission &amp; mail id for submission:
-04/03/2026 and
-tenders@ashrayfoundation.org
-Note: Ashray Foundation reserves the right to accept or reject any or all proposals without assigning any reason.
+          <t>• The terms and conditions for the purchase of seed:
+Provide seed percentage certificate of all Germination
+The seed must be supplied within 20 days from the date of order placement. Prices should be inclusive of GST and transportation charges.
+Seeds must be resistant to downy and powdery mildew.
+In case seeds fafulfillfulfil the supplier of the above-prescribed standard must guarantee the replacement of seeds.
+Genetic purity should not be less than 90%
+Germination (minimum): 85%
+Inert matter (maximum): 3%
+Weed seed (max.) = 20 no./kg
+Other crops seed (max.) = 20 no./ kg
+Packed: within 6 months
+Validity: at least 12 months
+Tax deductions will be done as per the relevant rules of the Government of India.
+Share the quotation on letterhead
+inclusive of GST (Otherwise the quotation will not be considered).
+Others
+MAMTA HIMC reserves the right to reject all or any quotation(s), wholly or partly, without assigning any reason whatsoever.
+MAMTA HIMC team reserves the right to request the top 3 quotations for an in-person discussion.
+MAMTA reserves the right, in its sole discretion, to conduct negotiations in accordance with MAMTA and/donor’s policies and procedures and to request additional information from prospective Bidders to supplement or clarify any aspect of the proposal documents if such revisions will be in the interest of our programs
+Only shortlisted agencies will be contacted.
+You must pay all sub-vendor payments before submitting the hard copy of the final bills and supporting documents to MAMTA HIMC.
+MAMTA shall not be legally bound by any award notice issued for this RFQ until an Agreement is duly signed and executed with the winning bidder(s).
+Further details will be shared with shortlisted agencies.
+Application Process –
+All applicants (company/agency/institutional) if applicable, should follow the Government of India guidelines/policy for the Prevention of Sexual Harassment (PoSH) at the workplace. As part of the application process, you are required to share the status of the Internal Complaints Committee (ICC). If the committee is not incorporated, then under what criteria is it not enacted?
+Interested agencies/organizations/individuals must submit the proposal for the
+Seeds
+highlighting the process, portfolio of past work, financial proposal and the timeline for the project. The technical and financial quotations should be sent in soft copy over email at
+rfp@mamtahimc.in
+by
+5
+th
+March 2026 With the subject line: “Quotation for Supply of Certified Seasonal Vegetable Seeds”. The
+• quotations should be made separately for the event and states. We encourage local vendors to apply. Incomplete applications and applications received after the deadline will not be considered for the selection process.
+The selection team will only contact applicants who have been shortlisted for the process.
+• Mamta HIMC has a policy of erasing all confidential information, ideas/concepts submitted in proposals/applications after the selection process is completed.
+"Confidentiality of Applicants"
+Mamta shall not be liable to share the list of shortlisted applicants with any party outside the organization. The organization takes all necessary measures to protect the confidentiality of applicants, and shall not disclose any personal information, process, and data related to the application, except as required by law.
 • Job Email ID:
-tenders(at)ashrayfoundation.org
+rfp(at)mamtahimc.in
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
 Apply by:
-04 Mar 2026
+05 Mar 2026
 Access all the jobs and get ahead!
 Subscribe to Value Membership Now!
 Subscribe
@@ -594,54 +622,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Documentation / Program Officer
-Pragati Path Foundation
-Location:
-Uttar Pradesh
-Apply by:
-25 Mar 2026
-Accounts Officer
-Jana Kalayana Samakhya
-Location:
-Odisha
-Apply by:
-30 Mar 2026
-Manager - Accounts &amp; Finance
-(Value Members only)
-Location:
-Rajasthan
-Apply by:
-13 Mar 2026
+Computer Science Trainer (School)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Computer Science Trainer (College)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Nursing Aid
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Driver
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Medical Officer
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Nurse
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Physiotherapist
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Project Coordinator
-Asra Samajik Lok Kalyan Samiti
-Location:
-Madhya Pradesh
-Apply by:
-30 Mar 2026
-Account Manager
-(Value Members only)
-Location:
-Odisha
-Apply by:
-10 Mar 2026
-Resource Person, Teacher Support – Ashram School ...
-Kavana Charitable Trust
-Location:
-Karnataka
-Apply by:
-02 Apr 2026
-Teach Manager, Child Development Team (Dual Role)
-U&amp;I Trust
-Location:
-India
-Apply by:
-31 Mar 2026
-Rural India Fellowship
-Katakhali Swapnopuron Welfare Society
-Location:
-West Bengal
-Apply by:
-15 Mar 2026
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Jobseekers
 Register
 Login
@@ -671,12 +699,12 @@
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>04-03-2026</t>
+          <t>05-03-2026</t>
         </is>
       </c>
       <c r="H2" s="1" t="n">
@@ -684,7 +712,7 @@
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287610</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287641</t>
         </is>
       </c>
     </row>
@@ -697,51 +725,66 @@
       <c r="B3" s="1" t="inlineStr"/>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>EoI - Mobile Cancer Screening Project – Ut Of Andaman &amp; Nicobar Islands</t>
+          <t>RFQ - for Report Designing</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Ashray Foundation | Sri Vijaya Puram (Port Blair), Andaman and Nicobar Islands
-International Development - EoI - Mobile Cancer Screening Project – Ut Of Andaman &amp; Nicobar Islands, Ashray Foundation, Andaman and Nicobar Islands - DevNetJobsIndia.org
+          <t>MAMTA Health Institute for Mother and Child (MAMTA) | India
+International Development - RFQ - for Report Designing, MAMTA Health Institute for Mother and Child (MAMTA), India - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
 Register
 Home
-Value Membership ... Read More</t>
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jo ... Read More</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>• Scope of Work:
-Requirement of Vehicle:
-Isuzu DMAX Ambulance AIS-125 Type C Ambulance- 2 units
-Fabrication for Mobile Screening Unit -2 units
-Portable Screening Devices:
-a) Breast Cancer- IBE or Niram AI
-b) Cervical Cancer- Colposcope, HPV DNA Kits, Thermal Abiation
-c)Oral Cancer- Sascan Device
-Diagnostic Kits for HPV, Oral Cytology, etc.
-• Eligibility:
-Dealer Authorisation letter
-Valid GST Certificate, PAN &amp; statutory registrations, Licenses
-Minimum 3–years of relevant experience in Fabrication of MSUs
-• Submission details:
-Interested agencies are requested to submit their interest on EOI along with: Company profile, Details of Project Experience, Copies of Necessary Documents, Licenses and Compliance Documents, Previous work orders and
-photographs.
-Last date for submission and mail id for submission :
-04/03/2026 and
-tenders@ashrayfoundation.org
-Note:
-Ashray Foundation reserves the right to accept or reject any proposal without assigning any reason.
+          <t>• Scope of Work
+This is to bring to your kind attention that we want to hire an agency to design Report the total no. of pages in the report are 300 maximum (including cover page and back cover) and document size are A4. The topic of report would be on maternal health, environment, community health, etc.
+The Terms of Reference are as follows:
+Kindly provide the quotations for each of the above items separately, including GST by 5th March 2026.
+Kindly provide separate quotations for report design per page.
+Work must be completed in 2 months from the date of this order accepted by the vendor.
+MAMTA will pay the amounts to the vendor after verification application files by MAMTA and submission of the original invoice.
+The taxes will be deducted as per the relevant rules of the Govt. of India.
+Others
+MAMTA HIMC reserves the right to reject all or any quotation(s), wholly or partly, without assigning any reason whatsoever.
+MAMTA HIMC team reserves the right to request the top 3 quotations for an in-person discussion.
+MAMTA reserves the right, in its sole discretion, to conduct negotiations in accordance with MAMTA and/donor’s policies and procedures and to request additional information from prospective Bidders to supplement or clarify any aspect of the proposal documents if such revisions will be in the interest of our programs
+Only shortlisted agencies will be contacted.
+You must pay all sub-vendor payments before submitting the hard copy of the final bills and supporting documents to MAMTA HIMC.
+MAMTA shall not be legally bound by any award notice issued for this RFQ until an Agreement is duly signed and executed with the winning bidder(s).
+Further details will be shared with shortlisted agencies.
+Application Process –
+All applicants (company/agency/institutional/individual) if applicable, should follow the Government of India guidelines/policy for the Prevention of Sexual Harassment (PoSH) at the workplace. As part of the application process, you are required to share the status of the Internal Complaints Committee (ICC). If the committee is not incorporated, then under what criteria is it not enacted?
+Interested agencies/organizations/individuals must submit the proposal for the
+report designing
+highlighting the process, portfolio of past work, financial proposal and the timeline for the project. The technical and financial quotations should be sent in soft copy over email at
+rfp@mamtahimc.in
+by
+5
+th
+March 2026 With the subject line: “Quotation for Report Designing”.
+• The quotations should be made separately for the event and states. We encourage local vendors to apply. Incomplete applications and applications received after the deadline will not be considered for the selection process.
+The selection team will only contact applicants who have been shortlisted for the process.
+• Mamta HIMC has a policy of erasing all confidential information, ideas/concepts submitted in proposals/applications after the selection process is completed.
+"Confidentiality of Applicants"
+Mamta shall not be liable to share the list of shortlisted applicants with any party outside the organization. The organization takes all necessary measures to protect the confidentiality of applicants, and shall not disclose any personal information, process, and data related to the application, except as required by law.
 • Job Email ID:
-tenders(at)ashrayfoundation.org
+rfp(at)mamtahimc.in
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
 Apply by:
-04 Mar 2026
+05 Mar 2026
 Access all the jobs and get ahead!
 Subscribe to Value Membership Now!
 Subscribe
@@ -809,54 +852,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Documentation / Program Officer
-Pragati Path Foundation
-Location:
-Uttar Pradesh
-Apply by:
-25 Mar 2026
-Accounts Officer
-Jana Kalayana Samakhya
-Location:
-Odisha
-Apply by:
-30 Mar 2026
-Manager - Accounts &amp; Finance
-(Value Members only)
-Location:
-Rajasthan
-Apply by:
-13 Mar 2026
+Computer Science Trainer (School)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Computer Science Trainer (College)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Nursing Aid
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Driver
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Medical Officer
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Nurse
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Physiotherapist
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Project Coordinator
-Asra Samajik Lok Kalyan Samiti
-Location:
-Madhya Pradesh
-Apply by:
-30 Mar 2026
-Account Manager
-(Value Members only)
-Location:
-Odisha
-Apply by:
-10 Mar 2026
-Resource Person, Teacher Support – Ashram School ...
-Kavana Charitable Trust
-Location:
-Karnataka
-Apply by:
-02 Apr 2026
-Teach Manager, Child Development Team (Dual Role)
-U&amp;I Trust
-Location:
-India
-Apply by:
-31 Mar 2026
-Rural India Fellowship
-Katakhali Swapnopuron Welfare Society
-Location:
-West Bengal
-Apply by:
-15 Mar 2026
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Jobseekers
 Register
 Login
@@ -886,12 +929,12 @@
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
-          <t>04-03-2026</t>
+          <t>05-03-2026</t>
         </is>
       </c>
       <c r="H3" s="1" t="n">
@@ -899,7 +942,7 @@
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287612</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287643</t>
         </is>
       </c>
     </row>
@@ -912,97 +955,41 @@
       <c r="B4" s="1" t="inlineStr"/>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>RFQ - for Case Study</t>
+          <t>RFP - Hiring an Agency to Conduct Evidence Synthesis, Co-Design Key Interv...</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>MAMTA Health Institute for Mother and Child (MAMTA) | India
-International Development - RFQ - for Case Study, MAMTA Health Institute for Mother and Child (MAMTA), India - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseeke ... Read More</t>
+          <t>Project Concern International India (PCI India) | India
+International Development - RFP - Hiring an Agency to Conduct Evidence Synthesis, Co-Design Key Intervention Components, and Develop a Scalable and Operational Implementation, Project Concern International India (PCI India), India - DevNetJobs ... Read More</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>• Scope of Work
-Mamta–HIMC
-invites quotations from qualified individuals or agencies to develop case studies documenting key program activities. The case studies will be developed focusing on the following components:
-Munni Campaign
-AJJA Campaign
-Pari Campaign
-K4 Campaign
-SJSM
-Routine Sessions
-Breastfeeding
-The selected individual/agency will be required to work across 8–10 districts, with case study selection across seven states/districts as follows:
-One in Uttar Pradesh (UP)
-One in Himachal Pradesh
-One in Rajasthan
-One in Bihar
-One in Assam
-One in Gadchiroli (Maharashtra)
-One in Odisha
-The case studies will focus on documenting the activities listed above, highlighting implementation processes, key achievements, challenges, and best practices.
-Terms of Reference
-Develop
-7 case studies per event
-across each of the 8–10 selected districts.
-Quotations must include a
-breakdown of costs
-for each item (including food, transport, accommodation, and GST).
-The assignment must be
-completed within two months
-from the date of contract acceptance.
-Payment will be released
-upon submission of original documentation
-and
-invoice verification
-.
-Applicable
-tax deductions
-will be made in accordance with Government of India regulations.
-Others
-MAMTA HIMC reserves the right to reject all or any quotation(s), wholly or partly, without assigning any reason whatsoever.
-MAMTA HIMC team reserves the right to request the top 3 quotations for an in-person discussion.
-MAMTA reserves the right, in its sole discretion, to conduct negotiations in accordance with MAMTA and/donor’s policies and procedures and to request additional information from prospective Bidders to supplement or clarify any aspect of the proposal documents if such revisions will be in the interest of our programs
-Only shortlisted agencies will be contacted.
-MAMTA shall not be legally bound by any award notice issued for this RFQ until an Agreement is duly signed and executed with the winning bidder(s).
-Further details will be shared with shortlisted agencies.
-Application Process –
-All applicants (company/agency/institutional) if applicable, should follow the Government of India guidelines/policy for the Prevention of Sexual Harassment (PoSH) at the workplace. As part of the application process, you are required to share the status of the Internal Complaints Committee (ICC). If the committee is not incorporated, then under what criteria is it not enacted?
-Interested agencies/organizations/individuals must submit the proposal for the
-Case Study
-, highlighting the process, portfolio of past work, financial proposal and the timeline for the project. The technical and financial quotations should be sent in soft copy over email at
-rfp@mamtahimc.in
-by
-4
+          <t>• Last   Date for Submission of bids
+05
 th
-March 2026 with subject line “Quotation for
-Case Study
-Development for Campaign Activities
-”.
-• The quotations should be made separately for the state of Uttar Pradesh, Rajasthan, Maharashtra, Delhi, Odisha, Himachal Pradesh, Bihar and Jharkhand. We encourage local vendors to apply. Incomplete applications and applications received after the deadline will not be considered for the selection process.
-The selection team will only contact applicants who have been shortlisted for the process.
-• Mamta HIMC has a policy of erasing all confidential information, ideas/concepts submitted in proposals/applications after the selection process is completed.
-"Confidentiality of Applicants"
-Mamta shall not be liable to share the list of shortlisted applicants with any party outside the organization. The organization takes all necessary measures to protect the confidentiality of applicants, and shall not disclose any personal information, process, and data related to the application, except as required by law.
+March 2026
+Proposals   to be submitted at
+procdelhi@pciglobal.in
+Receipt of Proposals
+Technical and Financial   proposals should be submitted as separate attachments
+and to be submitted
+in a single email
+attachments.
+NOTE
+:
+(a) The agencies registered under the Societies/Trust/Foreign Contribution (Regulation) Act, 2010, are not required to submit applications. Proposals from these agencies will not be considered.
+For detailed information, please check the complete version of the RFP attached below.
 • Job Email ID:
-rfp(at)mamtahimc.in
+procdelhi(at)pciglobal.in
+Download Attachment:
+RFP-AGENCY TO CONDUCT EVIDENCE SYNTHESIS, CO-DESIGN KEY INTERVENTION ..........doc
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
 Apply by:
-04 Mar 2026
+05 Mar 2026
 Access all the jobs and get ahead!
 Subscribe to Value Membership Now!
 Subscribe
@@ -1070,54 +1057,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Documentation / Program Officer
-Pragati Path Foundation
-Location:
-Uttar Pradesh
-Apply by:
-25 Mar 2026
-Accounts Officer
-Jana Kalayana Samakhya
-Location:
-Odisha
-Apply by:
-30 Mar 2026
-Manager - Accounts &amp; Finance
-(Value Members only)
-Location:
-Rajasthan
-Apply by:
-13 Mar 2026
+Computer Science Trainer (School)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Computer Science Trainer (College)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Nursing Aid
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Driver
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Medical Officer
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Nurse
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Physiotherapist
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Project Coordinator
-Asra Samajik Lok Kalyan Samiti
-Location:
-Madhya Pradesh
-Apply by:
-30 Mar 2026
-Account Manager
-(Value Members only)
-Location:
-Odisha
-Apply by:
-10 Mar 2026
-Resource Person, Teacher Support – Ashram School ...
-Kavana Charitable Trust
-Location:
-Karnataka
-Apply by:
-02 Apr 2026
-Teach Manager, Child Development Team (Dual Role)
-U&amp;I Trust
-Location:
-India
-Apply by:
-31 Mar 2026
-Rural India Fellowship
-Katakhali Swapnopuron Welfare Society
-Location:
-West Bengal
-Apply by:
-15 Mar 2026
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Jobseekers
 Register
 Login
@@ -1152,7 +1139,7 @@
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
-          <t>04-03-2026</t>
+          <t>05-03-2026</t>
         </is>
       </c>
       <c r="H4" s="1" t="n">
@@ -1160,7 +1147,7 @@
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287442</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287312</t>
         </is>
       </c>
     </row>
@@ -1413,54 +1400,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Documentation / Program Officer
-Pragati Path Foundation
-Location:
-Uttar Pradesh
-Apply by:
-25 Mar 2026
-Accounts Officer
-Jana Kalayana Samakhya
-Location:
-Odisha
-Apply by:
-30 Mar 2026
-Manager - Accounts &amp; Finance
-(Value Members only)
-Location:
-Rajasthan
-Apply by:
-13 Mar 2026
+Computer Science Trainer (School)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Computer Science Trainer (College)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Nursing Aid
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Driver
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Medical Officer
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Nurse
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Physiotherapist
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Project Coordinator
-Asra Samajik Lok Kalyan Samiti
-Location:
-Madhya Pradesh
-Apply by:
-30 Mar 2026
-Account Manager
-(Value Members only)
-Location:
-Odisha
-Apply by:
-10 Mar 2026
-Resource Person, Teacher Support – Ashram School ...
-Kavana Charitable Trust
-Location:
-Karnataka
-Apply by:
-02 Apr 2026
-Teach Manager, Child Development Team (Dual Role)
-U&amp;I Trust
-Location:
-India
-Apply by:
-31 Mar 2026
-Rural India Fellowship
-Katakhali Swapnopuron Welfare Society
-Location:
-West Bengal
-Apply by:
-15 Mar 2026
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Jobseekers
 Register
 Login
@@ -1499,7 +1486,7 @@
         </is>
       </c>
       <c r="H5" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" s="1" t="inlineStr">
         <is>
@@ -1516,240 +1503,10 @@
       <c r="B6" s="1" t="inlineStr"/>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>RFQ - for Report Designing</t>
+          <t>Request for Quotation for Case Study</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>MAMTA Health Institute for Mother and Child (MAMTA) | India
-International Development - RFQ - for Report Designing, MAMTA Health Institute for Mother and Child (MAMTA), India - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jo ... Read More</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>• Scope of Work
-This is to bring to your kind attention that we want to hire an agency to design Report the total no. of pages in the report are 300 maximum (including cover page and back cover) and document size are A4. The topic of report would be on maternal health, environment, community health, etc.
-The Terms of Reference are as follows:
-Kindly provide the quotations for each of the above items separately, including GST by 5th March 2026.
-Kindly provide separate quotations for report design per page.
-Work must be completed in 2 months from the date of this order accepted by the vendor.
-MAMTA will pay the amounts to the vendor after verification application files by MAMTA and submission of the original invoice.
-The taxes will be deducted as per the relevant rules of the Govt. of India.
-Others
-MAMTA HIMC reserves the right to reject all or any quotation(s), wholly or partly, without assigning any reason whatsoever.
-MAMTA HIMC team reserves the right to request the top 3 quotations for an in-person discussion.
-MAMTA reserves the right, in its sole discretion, to conduct negotiations in accordance with MAMTA and/donor’s policies and procedures and to request additional information from prospective Bidders to supplement or clarify any aspect of the proposal documents if such revisions will be in the interest of our programs
-Only shortlisted agencies will be contacted.
-You must pay all sub-vendor payments before submitting the hard copy of the final bills and supporting documents to MAMTA HIMC.
-MAMTA shall not be legally bound by any award notice issued for this RFQ until an Agreement is duly signed and executed with the winning bidder(s).
-Further details will be shared with shortlisted agencies.
-Application Process –
-All applicants (company/agency/institutional/individual) if applicable, should follow the Government of India guidelines/policy for the Prevention of Sexual Harassment (PoSH) at the workplace. As part of the application process, you are required to share the status of the Internal Complaints Committee (ICC). If the committee is not incorporated, then under what criteria is it not enacted?
-Interested agencies/organizations/individuals must submit the proposal for the
-report designing
-highlighting the process, portfolio of past work, financial proposal and the timeline for the project. The technical and financial quotations should be sent in soft copy over email at
-rfp@mamtahimc.in
-by
-5
-th
-March 2026 With the subject line: “Quotation for Report Designing”.
-• The quotations should be made separately for the event and states. We encourage local vendors to apply. Incomplete applications and applications received after the deadline will not be considered for the selection process.
-The selection team will only contact applicants who have been shortlisted for the process.
-• Mamta HIMC has a policy of erasing all confidential information, ideas/concepts submitted in proposals/applications after the selection process is completed.
-"Confidentiality of Applicants"
-Mamta shall not be liable to share the list of shortlisted applicants with any party outside the organization. The organization takes all necessary measures to protect the confidentiality of applicants, and shall not disclose any personal information, process, and data related to the application, except as required by law.
-• Job Email ID:
-rfp(at)mamtahimc.in
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-05 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-Documentation / Program Officer
-Pragati Path Foundation
-Location:
-Uttar Pradesh
-Apply by:
-25 Mar 2026
-Accounts Officer
-Jana Kalayana Samakhya
-Location:
-Odisha
-Apply by:
-30 Mar 2026
-Manager - Accounts &amp; Finance
-(Value Members only)
-Location:
-Rajasthan
-Apply by:
-13 Mar 2026
-Project Coordinator
-Asra Samajik Lok Kalyan Samiti
-Location:
-Madhya Pradesh
-Apply by:
-30 Mar 2026
-Account Manager
-(Value Members only)
-Location:
-Odisha
-Apply by:
-10 Mar 2026
-Resource Person, Teacher Support – Ashram School ...
-Kavana Charitable Trust
-Location:
-Karnataka
-Apply by:
-02 Apr 2026
-Teach Manager, Child Development Team (Dual Role)
-U&amp;I Trust
-Location:
-India
-Apply by:
-31 Mar 2026
-Rural India Fellowship
-Katakhali Swapnopuron Welfare Society
-Location:
-West Bengal
-Apply by:
-15 Mar 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="G6" s="1" t="inlineStr">
-        <is>
-          <t>05-03-2026</t>
-        </is>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287643</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr"/>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>Request for Quotation for Case Study</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Institute for Global Development (IGD) | Uttar Pradesh, Andhra Pradesh, Telangana, Karnataka
 International Development - Request for Quotation for Case Study, Institute for Global Development (IGD), Andhra Pradesh, Telangana, Karnataka - DevNetJobsIndia.org
@@ -1761,7 +1518,7 @@
 Value M ... Read More</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>• Scope of Work
 IGD invites quotations from qualified individuals or agencies to develop case studies documenting key program activities. The case studies will be developed focusing on some campaign components
@@ -1888,54 +1645,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Documentation / Program Officer
-Pragati Path Foundation
-Location:
-Uttar Pradesh
-Apply by:
-25 Mar 2026
-Accounts Officer
-Jana Kalayana Samakhya
-Location:
-Odisha
-Apply by:
-30 Mar 2026
-Manager - Accounts &amp; Finance
-(Value Members only)
-Location:
-Rajasthan
-Apply by:
-13 Mar 2026
+Computer Science Trainer (School)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Computer Science Trainer (College)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Nursing Aid
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Driver
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Medical Officer
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Nurse
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Physiotherapist
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Project Coordinator
-Asra Samajik Lok Kalyan Samiti
-Location:
-Madhya Pradesh
-Apply by:
-30 Mar 2026
-Account Manager
-(Value Members only)
-Location:
-Odisha
-Apply by:
-10 Mar 2026
-Resource Person, Teacher Support – Ashram School ...
-Kavana Charitable Trust
-Location:
-Karnataka
-Apply by:
-02 Apr 2026
-Teach Manager, Child Development Team (Dual Role)
-U&amp;I Trust
-Location:
-India
-Apply by:
-31 Mar 2026
-Rural India Fellowship
-Katakhali Swapnopuron Welfare Society
-Location:
-West Bengal
-Apply by:
-15 Mar 2026
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Jobseekers
 Register
 Login
@@ -1963,485 +1720,44 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F7" s="1" t="inlineStr">
+      <c r="F6" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G7" s="1" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>05-03-2026</t>
         </is>
       </c>
-      <c r="H7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" s="1" t="inlineStr">
+      <c r="H6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287670</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr"/>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Hiring an Agency to Conduct Evidence Synthesis, Co-Design Key Interv...</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Project Concern International India (PCI India) | India
-International Development - RFP - Hiring an Agency to Conduct Evidence Synthesis, Co-Design Key Intervention Components, and Develop a Scalable and Operational Implementation, Project Concern International India (PCI India), India - DevNetJobs ... Read More</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>• Last   Date for Submission of bids
-05
-th
-March 2026
-Proposals   to be submitted at
-procdelhi@pciglobal.in
-Receipt of Proposals
-Technical and Financial   proposals should be submitted as separate attachments
-and to be submitted
-in a single email
-attachments.
-NOTE
-:
-(a) The agencies registered under the Societies/Trust/Foreign Contribution (Regulation) Act, 2010, are not required to submit applications. Proposals from these agencies will not be considered.
-For detailed information, please check the complete version of the RFP attached below.
-• Job Email ID:
-procdelhi(at)pciglobal.in
-Download Attachment:
-RFP-AGENCY TO CONDUCT EVIDENCE SYNTHESIS, CO-DESIGN KEY INTERVENTION ..........doc
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-05 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-Documentation / Program Officer
-Pragati Path Foundation
-Location:
-Uttar Pradesh
-Apply by:
-25 Mar 2026
-Accounts Officer
-Jana Kalayana Samakhya
-Location:
-Odisha
-Apply by:
-30 Mar 2026
-Manager - Accounts &amp; Finance
-(Value Members only)
-Location:
-Rajasthan
-Apply by:
-13 Mar 2026
-Project Coordinator
-Asra Samajik Lok Kalyan Samiti
-Location:
-Madhya Pradesh
-Apply by:
-30 Mar 2026
-Account Manager
-(Value Members only)
-Location:
-Odisha
-Apply by:
-10 Mar 2026
-Resource Person, Teacher Support – Ashram School ...
-Kavana Charitable Trust
-Location:
-Karnataka
-Apply by:
-02 Apr 2026
-Teach Manager, Child Development Team (Dual Role)
-U&amp;I Trust
-Location:
-India
-Apply by:
-31 Mar 2026
-Rural India Fellowship
-Katakhali Swapnopuron Welfare Society
-Location:
-West Bengal
-Apply by:
-15 Mar 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="G8" s="1" t="inlineStr">
-        <is>
-          <t>05-03-2026</t>
-        </is>
-      </c>
-      <c r="H8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287312</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="inlineStr"/>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>RFQ - for the Supply of Seeds</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>MAMTA Health Institute for Mother and Child (MAMTA) | India
-International Development - RFQ -  for the Supply of Seeds, MAMTA Health Institute for Mother and Child (MAMTA), India - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Event ... Read More</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>• The terms and conditions for the purchase of seed:
-Provide seed percentage certificate of all Germination
-The seed must be supplied within 20 days from the date of order placement. Prices should be inclusive of GST and transportation charges.
-Seeds must be resistant to downy and powdery mildew.
-In case seeds fafulfillfulfil the supplier of the above-prescribed standard must guarantee the replacement of seeds.
-Genetic purity should not be less than 90%
-Germination (minimum): 85%
-Inert matter (maximum): 3%
-Weed seed (max.) = 20 no./kg
-Other crops seed (max.) = 20 no./ kg
-Packed: within 6 months
-Validity: at least 12 months
-Tax deductions will be done as per the relevant rules of the Government of India.
-Share the quotation on letterhead
-inclusive of GST (Otherwise the quotation will not be considered).
-Others
-MAMTA HIMC reserves the right to reject all or any quotation(s), wholly or partly, without assigning any reason whatsoever.
-MAMTA HIMC team reserves the right to request the top 3 quotations for an in-person discussion.
-MAMTA reserves the right, in its sole discretion, to conduct negotiations in accordance with MAMTA and/donor’s policies and procedures and to request additional information from prospective Bidders to supplement or clarify any aspect of the proposal documents if such revisions will be in the interest of our programs
-Only shortlisted agencies will be contacted.
-You must pay all sub-vendor payments before submitting the hard copy of the final bills and supporting documents to MAMTA HIMC.
-MAMTA shall not be legally bound by any award notice issued for this RFQ until an Agreement is duly signed and executed with the winning bidder(s).
-Further details will be shared with shortlisted agencies.
-Application Process –
-All applicants (company/agency/institutional) if applicable, should follow the Government of India guidelines/policy for the Prevention of Sexual Harassment (PoSH) at the workplace. As part of the application process, you are required to share the status of the Internal Complaints Committee (ICC). If the committee is not incorporated, then under what criteria is it not enacted?
-Interested agencies/organizations/individuals must submit the proposal for the
-Seeds
-highlighting the process, portfolio of past work, financial proposal and the timeline for the project. The technical and financial quotations should be sent in soft copy over email at
-rfp@mamtahimc.in
-by
-5
-th
-March 2026 With the subject line: “Quotation for Supply of Certified Seasonal Vegetable Seeds”. The
-• quotations should be made separately for the event and states. We encourage local vendors to apply. Incomplete applications and applications received after the deadline will not be considered for the selection process.
-The selection team will only contact applicants who have been shortlisted for the process.
-• Mamta HIMC has a policy of erasing all confidential information, ideas/concepts submitted in proposals/applications after the selection process is completed.
-"Confidentiality of Applicants"
-Mamta shall not be liable to share the list of shortlisted applicants with any party outside the organization. The organization takes all necessary measures to protect the confidentiality of applicants, and shall not disclose any personal information, process, and data related to the application, except as required by law.
-• Job Email ID:
-rfp(at)mamtahimc.in
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-05 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-Documentation / Program Officer
-Pragati Path Foundation
-Location:
-Uttar Pradesh
-Apply by:
-25 Mar 2026
-Accounts Officer
-Jana Kalayana Samakhya
-Location:
-Odisha
-Apply by:
-30 Mar 2026
-Manager - Accounts &amp; Finance
-(Value Members only)
-Location:
-Rajasthan
-Apply by:
-13 Mar 2026
-Project Coordinator
-Asra Samajik Lok Kalyan Samiti
-Location:
-Madhya Pradesh
-Apply by:
-30 Mar 2026
-Account Manager
-(Value Members only)
-Location:
-Odisha
-Apply by:
-10 Mar 2026
-Resource Person, Teacher Support – Ashram School ...
-Kavana Charitable Trust
-Location:
-Karnataka
-Apply by:
-02 Apr 2026
-Teach Manager, Child Development Team (Dual Role)
-U&amp;I Trust
-Location:
-India
-Apply by:
-31 Mar 2026
-Rural India Fellowship
-Katakhali Swapnopuron Welfare Society
-Location:
-West Bengal
-Apply by:
-15 Mar 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
-          <t>05-03-2026</t>
-        </is>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287641</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="inlineStr"/>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>ToR - State And National Level Consolidation Study On Government Schemes, ...</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Life Education And Development Support (Leads) And Ghoghardiha Prakhand Swarajya Vikas Sangh (GPSVS) | Jharkhand, Bihar
 International Development - ToR - State And National Level Consolidation Study On Government Schemes, Labour Rights &amp; Grievance Mechanisms - Safe Employment Guidebooks..., Life Ed ... Read More</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>• 3. Scope of Work
 The consultant/agency will adopt a policy-research and systems-analysis approach encompassing the following components:
@@ -2593,54 +1909,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Documentation / Program Officer
-Pragati Path Foundation
-Location:
-Uttar Pradesh
-Apply by:
-25 Mar 2026
-Accounts Officer
-Jana Kalayana Samakhya
-Location:
-Odisha
-Apply by:
-30 Mar 2026
-Manager - Accounts &amp; Finance
-(Value Members only)
-Location:
-Rajasthan
-Apply by:
-13 Mar 2026
+Computer Science Trainer (School)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Computer Science Trainer (College)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Nursing Aid
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Driver
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Medical Officer
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Nurse
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Physiotherapist
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Project Coordinator
-Asra Samajik Lok Kalyan Samiti
-Location:
-Madhya Pradesh
-Apply by:
-30 Mar 2026
-Account Manager
-(Value Members only)
-Location:
-Odisha
-Apply by:
-10 Mar 2026
-Resource Person, Teacher Support – Ashram School ...
-Kavana Charitable Trust
-Location:
-Karnataka
-Apply by:
-02 Apr 2026
-Teach Manager, Child Development Team (Dual Role)
-U&amp;I Trust
-Location:
-India
-Apply by:
-31 Mar 2026
-Rural India Fellowship
-Katakhali Swapnopuron Welfare Society
-Location:
-West Bengal
-Apply by:
-15 Mar 2026
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Jobseekers
 Register
 Login
@@ -2668,45 +1984,45 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F10" s="1" t="inlineStr">
+      <c r="F7" s="1" t="inlineStr">
         <is>
           <t>Governance, Learning</t>
         </is>
       </c>
-      <c r="G10" s="1" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>05-03-2026</t>
         </is>
       </c>
-      <c r="H10" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" s="1" t="inlineStr">
+      <c r="H7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287504</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr"/>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr"/>
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>EoI - For Empanelment of agencies for Impact Assessment/ Evaluation Servic...</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Small Industries Development Bank of India (SIDBI) | India
 International Development - EoI - For Empanelment of agencies for Impact Assessment/ Evaluation Services under Programmes for Development and Impact, Small Industries Development Bank of India (SIDBI), India - DevNetJobsIndia.org
 Jobseekers ... Read More</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>• Please      note that all the information required as per the documents required for      responding to EOI needs to be provided. Incomplete information in these      areas may lead to non-selection.
 Modification      And/ Or Withdrawal of documents:
@@ -2841,54 +2157,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Documentation / Program Officer
-Pragati Path Foundation
-Location:
-Uttar Pradesh
-Apply by:
-25 Mar 2026
-Accounts Officer
-Jana Kalayana Samakhya
-Location:
-Odisha
-Apply by:
-30 Mar 2026
-Manager - Accounts &amp; Finance
-(Value Members only)
-Location:
-Rajasthan
-Apply by:
-13 Mar 2026
+Computer Science Trainer (School)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Computer Science Trainer (College)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Nursing Aid
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Driver
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Medical Officer
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Nurse
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Physiotherapist
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Project Coordinator
-Asra Samajik Lok Kalyan Samiti
-Location:
-Madhya Pradesh
-Apply by:
-30 Mar 2026
-Account Manager
-(Value Members only)
-Location:
-Odisha
-Apply by:
-10 Mar 2026
-Resource Person, Teacher Support – Ashram School ...
-Kavana Charitable Trust
-Location:
-Karnataka
-Apply by:
-02 Apr 2026
-Teach Manager, Child Development Team (Dual Role)
-U&amp;I Trust
-Location:
-India
-Apply by:
-31 Mar 2026
-Rural India Fellowship
-Katakhali Swapnopuron Welfare Society
-Location:
-West Bengal
-Apply by:
-15 Mar 2026
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Jobseekers
 Register
 Login
@@ -2916,38 +2232,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F11" s="1" t="inlineStr">
+      <c r="F8" s="1" t="inlineStr">
         <is>
           <t>Governance, Learning</t>
         </is>
       </c>
-      <c r="G11" s="1" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>06-03-2026</t>
         </is>
       </c>
-      <c r="H11" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I11" s="1" t="inlineStr">
+      <c r="H8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287084</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr"/>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="B9" s="1" t="inlineStr"/>
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>RFP - Onboarding Agency for Revamping Assam LMIS Dashboard</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>PATH | Assam
 International Development - RFP - Onboarding Agency for Revamping Assam LMIS Dashboard, PATH, Assam - DevNetJobsIndia.org
@@ -2969,7 +2285,7 @@
 Jobseekers Registe ... Read More</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>• 3.2. Commercial contracting terms and conditions will be negotiated with the successful supplier at the end of the selection process.
 3.3. By submitting a proposal, the supplier confirms their agreement to abide by the RFP terms and PATH policies, including the
@@ -3124,54 +2440,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Documentation / Program Officer
-Pragati Path Foundation
-Location:
-Uttar Pradesh
-Apply by:
-25 Mar 2026
-Accounts Officer
-Jana Kalayana Samakhya
-Location:
-Odisha
-Apply by:
-30 Mar 2026
-Manager - Accounts &amp; Finance
-(Value Members only)
-Location:
-Rajasthan
-Apply by:
-13 Mar 2026
+Computer Science Trainer (School)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Computer Science Trainer (College)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Nursing Aid
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Driver
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Medical Officer
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Nurse
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Physiotherapist
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Project Coordinator
-Asra Samajik Lok Kalyan Samiti
-Location:
-Madhya Pradesh
-Apply by:
-30 Mar 2026
-Account Manager
-(Value Members only)
-Location:
-Odisha
-Apply by:
-10 Mar 2026
-Resource Person, Teacher Support – Ashram School ...
-Kavana Charitable Trust
-Location:
-Karnataka
-Apply by:
-02 Apr 2026
-Teach Manager, Child Development Team (Dual Role)
-U&amp;I Trust
-Location:
-India
-Apply by:
-31 Mar 2026
-Rural India Fellowship
-Katakhali Swapnopuron Welfare Society
-Location:
-West Bengal
-Apply by:
-15 Mar 2026
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Jobseekers
 Register
 Login
@@ -3199,38 +2515,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F12" s="1" t="inlineStr">
+      <c r="F9" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G12" s="1" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>07-03-2026</t>
         </is>
       </c>
-      <c r="H12" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="I12" s="1" t="inlineStr">
+      <c r="H9" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287335</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr"/>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="B10" s="1" t="inlineStr"/>
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>RFP- #2026-IN-01- Agency for economic Impact Analysis</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>PATH | Delhi
 International Development - RFP- #2026-IN-01- Agency for economic Impact Analysis, PATH, Delhi - DevNetJobsIndia.org
@@ -3253,7 +2569,7 @@
 Job ... Read More</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>• Job Email ID:
 rfpindia(at)path.org
@@ -3331,54 +2647,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Documentation / Program Officer
-Pragati Path Foundation
-Location:
-Uttar Pradesh
-Apply by:
-25 Mar 2026
-Accounts Officer
-Jana Kalayana Samakhya
-Location:
-Odisha
-Apply by:
-30 Mar 2026
-Manager - Accounts &amp; Finance
-(Value Members only)
-Location:
-Rajasthan
-Apply by:
-13 Mar 2026
+Computer Science Trainer (School)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Computer Science Trainer (College)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Nursing Aid
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Driver
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Medical Officer
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Nurse
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Physiotherapist
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Project Coordinator
-Asra Samajik Lok Kalyan Samiti
-Location:
-Madhya Pradesh
-Apply by:
-30 Mar 2026
-Account Manager
-(Value Members only)
-Location:
-Odisha
-Apply by:
-10 Mar 2026
-Resource Person, Teacher Support – Ashram School ...
-Kavana Charitable Trust
-Location:
-Karnataka
-Apply by:
-02 Apr 2026
-Teach Manager, Child Development Team (Dual Role)
-U&amp;I Trust
-Location:
-India
-Apply by:
-31 Mar 2026
-Rural India Fellowship
-Katakhali Swapnopuron Welfare Society
-Location:
-West Bengal
-Apply by:
-15 Mar 2026
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Jobseekers
 Register
 Login
@@ -3406,38 +2722,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F13" s="1" t="inlineStr">
+      <c r="F10" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G13" s="1" t="inlineStr">
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>07-03-2026</t>
         </is>
       </c>
-      <c r="H13" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="I13" s="1" t="inlineStr">
+      <c r="H10" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287460</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr"/>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr"/>
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>Associate (Programme Management)</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Indian Institute For Human Settlements (Iihs) | Karnataka
 International Development - Associate (Programme Management), Indian Institute For Human Settlements (Iihs), Karnataka - DevNetJobsIndia.org
@@ -3453,7 +2769,7 @@
 Events ... Read More</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>• IIHS is an equal opportunity employer that encourages women, people with disabilities and those from economically and socially excluded communities with the requisite skills and qualifications to apply for positions.
 • To apply
@@ -3542,54 +2858,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Documentation / Program Officer
-Pragati Path Foundation
-Location:
-Uttar Pradesh
-Apply by:
-25 Mar 2026
-Accounts Officer
-Jana Kalayana Samakhya
-Location:
-Odisha
-Apply by:
-30 Mar 2026
-Manager - Accounts &amp; Finance
-(Value Members only)
-Location:
-Rajasthan
-Apply by:
-13 Mar 2026
+Computer Science Trainer (School)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Computer Science Trainer (College)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Nursing Aid
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Driver
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Medical Officer
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Nurse
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Physiotherapist
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Project Coordinator
-Asra Samajik Lok Kalyan Samiti
-Location:
-Madhya Pradesh
-Apply by:
-30 Mar 2026
-Account Manager
-(Value Members only)
-Location:
-Odisha
-Apply by:
-10 Mar 2026
-Resource Person, Teacher Support – Ashram School ...
-Kavana Charitable Trust
-Location:
-Karnataka
-Apply by:
-02 Apr 2026
-Teach Manager, Child Development Team (Dual Role)
-U&amp;I Trust
-Location:
-India
-Apply by:
-31 Mar 2026
-Rural India Fellowship
-Katakhali Swapnopuron Welfare Society
-Location:
-West Bengal
-Apply by:
-15 Mar 2026
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Jobseekers
 Register
 Login
@@ -3617,38 +2933,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F14" s="1" t="inlineStr">
+      <c r="F11" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G14" s="1" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>07-03-2026</t>
         </is>
       </c>
-      <c r="H14" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="I14" s="1" t="inlineStr">
+      <c r="H11" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=285747</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr"/>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="B12" s="1" t="inlineStr"/>
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>RFP - Final Evaluation of the Bhoomi Ka Programme</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Deutsche Welthungerhilfe | India
 International Development - RFP - Final Evaluation of the Bhoomi Ka Programme, Deutsche Welthungerhilfe, India - DevNetJobsIndia.org
@@ -3669,7 +2985,7 @@
 Jobs ... Read More</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>• INTRODUCTION AND CONTEXT
 Country:
@@ -3799,54 +3115,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Documentation / Program Officer
-Pragati Path Foundation
-Location:
-Uttar Pradesh
-Apply by:
-25 Mar 2026
-Accounts Officer
-Jana Kalayana Samakhya
-Location:
-Odisha
-Apply by:
-30 Mar 2026
-Manager - Accounts &amp; Finance
-(Value Members only)
-Location:
-Rajasthan
-Apply by:
-13 Mar 2026
+Computer Science Trainer (School)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Computer Science Trainer (College)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Nursing Aid
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Driver
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Medical Officer
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Nurse
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Physiotherapist
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Project Coordinator
-Asra Samajik Lok Kalyan Samiti
-Location:
-Madhya Pradesh
-Apply by:
-30 Mar 2026
-Account Manager
-(Value Members only)
-Location:
-Odisha
-Apply by:
-10 Mar 2026
-Resource Person, Teacher Support – Ashram School ...
-Kavana Charitable Trust
-Location:
-Karnataka
-Apply by:
-02 Apr 2026
-Teach Manager, Child Development Team (Dual Role)
-U&amp;I Trust
-Location:
-India
-Apply by:
-31 Mar 2026
-Rural India Fellowship
-Katakhali Swapnopuron Welfare Society
-Location:
-West Bengal
-Apply by:
-15 Mar 2026
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Jobseekers
 Register
 Login
@@ -3874,38 +3190,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F15" s="1" t="inlineStr">
+      <c r="F12" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G15" s="1" t="inlineStr">
+      <c r="G12" s="1" t="inlineStr">
         <is>
           <t>08-03-2026</t>
         </is>
       </c>
-      <c r="H15" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I15" s="1" t="inlineStr">
+      <c r="H12" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287384</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr"/>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="B13" s="1" t="inlineStr"/>
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>RFQ: Construction of New gated check dams, De-siltation, and retrofitting ...</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>WaterAid India | Telangana
 International Development - RFQ: Construction of New gated check dams, De-siltation, and retrofitting of check dam in 6 villages, WaterAid India, Telangana - DevNetJobsIndia.org
@@ -3921,7 +3237,7 @@
 E ... Read More</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>• Job Email ID:
 WAIProcurementAP(at)wateraid.org
@@ -3999,54 +3315,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Documentation / Program Officer
-Pragati Path Foundation
-Location:
-Uttar Pradesh
-Apply by:
-25 Mar 2026
-Accounts Officer
-Jana Kalayana Samakhya
-Location:
-Odisha
-Apply by:
-30 Mar 2026
-Manager - Accounts &amp; Finance
-(Value Members only)
-Location:
-Rajasthan
-Apply by:
-13 Mar 2026
+Computer Science Trainer (School)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Computer Science Trainer (College)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Nursing Aid
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Driver
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Medical Officer
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Nurse
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Physiotherapist
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Project Coordinator
-Asra Samajik Lok Kalyan Samiti
-Location:
-Madhya Pradesh
-Apply by:
-30 Mar 2026
-Account Manager
-(Value Members only)
-Location:
-Odisha
-Apply by:
-10 Mar 2026
-Resource Person, Teacher Support – Ashram School ...
-Kavana Charitable Trust
-Location:
-Karnataka
-Apply by:
-02 Apr 2026
-Teach Manager, Child Development Team (Dual Role)
-U&amp;I Trust
-Location:
-India
-Apply by:
-31 Mar 2026
-Rural India Fellowship
-Katakhali Swapnopuron Welfare Society
-Location:
-West Bengal
-Apply by:
-15 Mar 2026
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Jobseekers
 Register
 Login
@@ -4074,38 +3390,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F16" s="1" t="inlineStr">
+      <c r="F13" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G16" s="1" t="inlineStr">
+      <c r="G13" s="1" t="inlineStr">
         <is>
           <t>08-03-2026</t>
         </is>
       </c>
-      <c r="H16" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I16" s="1" t="inlineStr">
+      <c r="H13" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287784</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr"/>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="B14" s="1" t="inlineStr"/>
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>RFP - Hiring of an International Audit Firm</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Coalition for Disaster Resilient Infrastructure (CDRI) | India
 International Development - RFP - Hiring of an International Audit Firm, Coalition for Disaster Resilient Infrastructure (CDRI), India - DevNetJobsIndia.org
@@ -4119,7 +3435,7 @@
 RFPs/Tender ... Read More</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>• Job Email ID:
 tender.projects(at)cdri.world
@@ -4197,54 +3513,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Documentation / Program Officer
-Pragati Path Foundation
-Location:
-Uttar Pradesh
-Apply by:
-25 Mar 2026
-Accounts Officer
-Jana Kalayana Samakhya
-Location:
-Odisha
-Apply by:
-30 Mar 2026
-Manager - Accounts &amp; Finance
-(Value Members only)
-Location:
-Rajasthan
-Apply by:
-13 Mar 2026
+Computer Science Trainer (School)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Computer Science Trainer (College)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Nursing Aid
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Driver
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Medical Officer
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Nurse
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Physiotherapist
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Project Coordinator
-Asra Samajik Lok Kalyan Samiti
-Location:
-Madhya Pradesh
-Apply by:
-30 Mar 2026
-Account Manager
-(Value Members only)
-Location:
-Odisha
-Apply by:
-10 Mar 2026
-Resource Person, Teacher Support – Ashram School ...
-Kavana Charitable Trust
-Location:
-Karnataka
-Apply by:
-02 Apr 2026
-Teach Manager, Child Development Team (Dual Role)
-U&amp;I Trust
-Location:
-India
-Apply by:
-31 Mar 2026
-Rural India Fellowship
-Katakhali Swapnopuron Welfare Society
-Location:
-West Bengal
-Apply by:
-15 Mar 2026
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Jobseekers
 Register
 Login
@@ -4272,48 +3588,99 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F17" s="1" t="inlineStr">
+      <c r="F14" s="1" t="inlineStr">
         <is>
           <t>Climate</t>
         </is>
       </c>
-      <c r="G17" s="1" t="inlineStr">
+      <c r="G14" s="1" t="inlineStr">
         <is>
           <t>09-03-2026</t>
         </is>
       </c>
-      <c r="H17" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="I17" s="1" t="inlineStr">
+      <c r="H14" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I14" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287382</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B18" s="1" t="inlineStr"/>
-      <c r="C18" s="1" t="inlineStr">
-        <is>
-          <t>RFP For Selection of an Implementation Support Agency (Isa) For Capacity B...</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>EAII Advisors Pvt Ltd | Andhra Pradesh
-International Development - RFP For Selection of an Implementation Support Agency (Isa) For Capacity Building Of Community Leaders To Conduct Community Engagement Activities, EAII Advisors Pvt Ltd, Andhra Pradesh - DevNetJobsIndia.org
+      <c r="B15" s="1" t="inlineStr"/>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>RFP - Early-Stage Impact Assessment-CDRI SWP 23-26</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Coalition for Disaster Resilient Infrastructure (CDRI) | India
+International Development - RFP - Early-Stage Impact Assessment-CDRI SWP 23-26, Coalition for Disaster Resilient Infrastructure (CDRI), India - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
-Regis ... Read More</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs ... Read More</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F15" s="1" t="inlineStr">
+        <is>
+          <t>Climate, Governance</t>
+        </is>
+      </c>
+      <c r="G15" s="1" t="inlineStr">
+        <is>
+          <t>09-03-2026</t>
+        </is>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I15" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287093</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr"/>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>RFP For The Contractors To Procure, Build, Install, Supply Chlorine Tablet...</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>EAII Advisors Pvt Ltd | Andhra Pradesh
+International Development - RFP For The Contractors To Procure, Build, Install, Supply Chlorine Tablets, Operate And Maintain Tablet-Based In Line Chlorination Devices, EAII Advisors Pvt Ltd, Andhra Pradesh - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Ho ... Read More</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>• Proposal Requirements
 1. Company Background and Details
@@ -4323,9 +3690,9 @@
 Kindly fill in the column “Bidder Response”. The current inputs are guiding inputs or choices for answers. Kindly fill in accordingly.
 For detailed information, please check the complete version of the RFP attached below.
 Download Attachment:
-Standalone ISA RFP Technical Evaluation Response Template (1).docx
+Standalone IC RFP Technical Evaluation Response Template.docx
 Download Attachment:
-Telugu_Standalone ISA RFP Technical Evaluation Response Template.docx
+Telugu_Standalone IC RFP Technical Evaluation Response Template.docx
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
@@ -4398,54 +3765,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Documentation / Program Officer
-Pragati Path Foundation
-Location:
-Uttar Pradesh
-Apply by:
-25 Mar 2026
-Accounts Officer
-Jana Kalayana Samakhya
-Location:
-Odisha
-Apply by:
-30 Mar 2026
-Manager - Accounts &amp; Finance
-(Value Members only)
-Location:
-Rajasthan
-Apply by:
-13 Mar 2026
+Computer Science Trainer (School)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Computer Science Trainer (College)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Nursing Aid
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Driver
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Medical Officer
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Nurse
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Physiotherapist
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Project Coordinator
-Asra Samajik Lok Kalyan Samiti
-Location:
-Madhya Pradesh
-Apply by:
-30 Mar 2026
-Account Manager
-(Value Members only)
-Location:
-Odisha
-Apply by:
-10 Mar 2026
-Resource Person, Teacher Support – Ashram School ...
-Kavana Charitable Trust
-Location:
-Karnataka
-Apply by:
-02 Apr 2026
-Teach Manager, Child Development Team (Dual Role)
-U&amp;I Trust
-Location:
-India
-Apply by:
-31 Mar 2026
-Rural India Fellowship
-Katakhali Swapnopuron Welfare Society
-Location:
-West Bengal
-Apply by:
-15 Mar 2026
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Jobseekers
 Register
 Login
@@ -4473,99 +3840,48 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F18" s="1" t="inlineStr">
-        <is>
-          <t>Governance, Learning</t>
-        </is>
-      </c>
-      <c r="G18" s="1" t="inlineStr">
+      <c r="F16" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G16" s="1" t="inlineStr">
         <is>
           <t>09-03-2026</t>
         </is>
       </c>
-      <c r="H18" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="I18" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=285950</t>
+      <c r="H16" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=285949</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr"/>
-      <c r="C19" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Early-Stage Impact Assessment-CDRI SWP 23-26</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Coalition for Disaster Resilient Infrastructure (CDRI) | India
-International Development - RFP - Early-Stage Impact Assessment-CDRI SWP 23-26, Coalition for Disaster Resilient Infrastructure (CDRI), India - DevNetJobsIndia.org
+      <c r="B17" s="1" t="inlineStr"/>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>RFP For Selection of an Implementation Support Agency (Isa) For Capacity B...</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>EAII Advisors Pvt Ltd | Andhra Pradesh
+International Development - RFP For Selection of an Implementation Support Agency (Isa) For Capacity Building Of Community Leaders To Conduct Community Engagement Activities, EAII Advisors Pvt Ltd, Andhra Pradesh - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs ... Read More</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F19" s="1" t="inlineStr">
-        <is>
-          <t>Climate, Governance</t>
-        </is>
-      </c>
-      <c r="G19" s="1" t="inlineStr">
-        <is>
-          <t>09-03-2026</t>
-        </is>
-      </c>
-      <c r="H19" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="I19" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287093</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B20" s="1" t="inlineStr"/>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>RFP For The Contractors To Procure, Build, Install, Supply Chlorine Tablet...</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>EAII Advisors Pvt Ltd | Andhra Pradesh
-International Development - RFP For The Contractors To Procure, Build, Install, Supply Chlorine Tablets, Operate And Maintain Tablet-Based In Line Chlorination Devices, EAII Advisors Pvt Ltd, Andhra Pradesh - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Ho ... Read More</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
+Regis ... Read More</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>• Proposal Requirements
 1. Company Background and Details
@@ -4575,9 +3891,9 @@
 Kindly fill in the column “Bidder Response”. The current inputs are guiding inputs or choices for answers. Kindly fill in accordingly.
 For detailed information, please check the complete version of the RFP attached below.
 Download Attachment:
-Standalone IC RFP Technical Evaluation Response Template.docx
+Standalone ISA RFP Technical Evaluation Response Template (1).docx
 Download Attachment:
-Telugu_Standalone IC RFP Technical Evaluation Response Template.docx
+Telugu_Standalone ISA RFP Technical Evaluation Response Template.docx
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
@@ -4650,54 +3966,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Documentation / Program Officer
-Pragati Path Foundation
-Location:
-Uttar Pradesh
-Apply by:
-25 Mar 2026
-Accounts Officer
-Jana Kalayana Samakhya
-Location:
-Odisha
-Apply by:
-30 Mar 2026
-Manager - Accounts &amp; Finance
-(Value Members only)
-Location:
-Rajasthan
-Apply by:
-13 Mar 2026
+Computer Science Trainer (School)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Computer Science Trainer (College)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Nursing Aid
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Driver
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Medical Officer
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Nurse
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Physiotherapist
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Project Coordinator
-Asra Samajik Lok Kalyan Samiti
-Location:
-Madhya Pradesh
-Apply by:
-30 Mar 2026
-Account Manager
-(Value Members only)
-Location:
-Odisha
-Apply by:
-10 Mar 2026
-Resource Person, Teacher Support – Ashram School ...
-Kavana Charitable Trust
-Location:
-Karnataka
-Apply by:
-02 Apr 2026
-Teach Manager, Child Development Team (Dual Role)
-U&amp;I Trust
-Location:
-India
-Apply by:
-31 Mar 2026
-Rural India Fellowship
-Katakhali Swapnopuron Welfare Society
-Location:
-West Bengal
-Apply by:
-15 Mar 2026
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Jobseekers
 Register
 Login
@@ -4725,279 +4041,44 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G20" s="1" t="inlineStr">
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>Governance, Learning</t>
+        </is>
+      </c>
+      <c r="G17" s="1" t="inlineStr">
         <is>
           <t>09-03-2026</t>
         </is>
       </c>
-      <c r="H20" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="I20" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=285949</t>
+      <c r="H17" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=285950</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr"/>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>RFP - for Supply of Skill Lab Items</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>TeamLease Foundation | India
-International Development - RFP - for Supply of Skill Lab Items, TeamLease Foundation, India - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Login
-|
-Register
-Jobseekers Login
-Jobseeker ... Read More</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>• Technical Bid Submission Link-
-https://forms.gle/V9iy35ddb4kWEb468
-• Financial Bid Submission Link-
-https://forms.gle/LozobuuuMh55Ea2G8
-Note
-: Technical bid and financial bid are to be submitted separately in separate links.
-Following points are to be kept in mind while submitting the bids-
-All Bid must contain the complete address of firm, including contact number/ email ID of the person who is authorized to submit the bid under their signatures.
-All bids must be signed on all pages by the bidder. Unsigned bids shall not be entertained/ accepted.
-All pages of the bid being submitted must be signed and sequentially numbered by the bidder irrespective of the nature of content of the documents.
-Bids not submitted as per the specified format and nomenclature or ambiguous in nature will be liable to be rejected.
-• The interested bidders may submit their bid to TLF on or before the date mentioned in this RFP Documents. Any bid received by TLF after the prescribed deadline for submission of bids will be rejected and no further correspondence in this regard will be entertained.
-Financial bid should be prepared as per Annexure II given in the RFP Documents. Same is also to be uploaded in google forms too.
-Bidders shall indicate their rates in clear/ visible figures as well as in words. In case of a mismatch, the rates written in words will prevail.
-• At any time prior to the last date for submission of bids, TLF, may, for any reason, whether at its own initiative or in response to a clarification requested by a prospective bidder, modify the RFP Documents by an amendment and publish the revised version of the RFP.
-The contract panel may consist of maximum three vendors for each item. However, TLF reserves the right to review the performance of the panel of vendors and terminate the contract of such vendors whose performance is not found satisfactory. The decision of TLF will be final in this regard.
-TLF will issue Purchase Order(s) (PO) during the period up to 31-March-2026. as per the required quantities and as per the rates and other terms of the Purchase Order.
-TLF may issue separate Purchase Order(s) PO based on its actual requirements to the Successful Bidder(s) for providing Product(s) and / or Service(s) and there is no minimum or prior commitment for such orders under this RFP.
-The successful bidder will be expected to provide all the necessary support for delivery of the items, warranty and required support during the warranty period.
-Delivery of the Kits specified in this RFP should be by 20
-th
-December 2025 from the PO date
-Successful bidder will ensure delivery, installation and operationalization of all products /components under the contract before acceptance testing / examination, and the Warranty period will commence only on acceptance of the products
-If, during the warranty period, any system as a whole or any subsystem has any failure on two or more occasions in a period of 3 months, it shall be replaced by equivalent new equipment by the Vendor at no cost to TLF
-The successful bidder shall be fully responsible for the manufacturer’s warranty for all equipment, accessories, spare parts etc. against any defects arising from design, material, manufacturing, workmanship, or any act or omission of the manufacturer / vendor or any defect that may develop under normal use of supplied equipment during the warranty period
-In case of any deviations, specific exemption may be sought on case-to-case basis from the respective Departments placing the Service Request
-• Printed terms and conditions of the bidders will not be considered as forming part of their bid. In case terms and conditions as given in the RFP Documents are not acceptable to any bidder, they should clearly specify the deviations in their bids.
-Bids complete in all respects along with supporting documents, must be submitted as per the RFP requirements. No physical document is to be submitted by the bidders.
-NO conditional or partial Bid will be entertained and will be rejected.
-• Parallel Contracts - TLF may also execute parallel contracts with more than one firm on the lowest approved rates on the same terms and conditions. These parallel contracts will be utilized if the original L1 substantially technically qualified bidder is not in a position to supply material as per TLFs requirement within the time frame indicated in the bid.
-For detailed information, please check the complete version of the RFP attached below.
-Download Attachment:
-RFP for procurement Skill Lab Items under RIST Mansi_250226.pdf
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-11 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-Documentation / Program Officer
-Pragati Path Foundation
-Location:
-Uttar Pradesh
-Apply by:
-25 Mar 2026
-Accounts Officer
-Jana Kalayana Samakhya
-Location:
-Odisha
-Apply by:
-30 Mar 2026
-Manager - Accounts &amp; Finance
-(Value Members only)
-Location:
-Rajasthan
-Apply by:
-13 Mar 2026
-Project Coordinator
-Asra Samajik Lok Kalyan Samiti
-Location:
-Madhya Pradesh
-Apply by:
-30 Mar 2026
-Account Manager
-(Value Members only)
-Location:
-Odisha
-Apply by:
-10 Mar 2026
-Resource Person, Teacher Support – Ashram School ...
-Kavana Charitable Trust
-Location:
-Karnataka
-Apply by:
-02 Apr 2026
-Teach Manager, Child Development Team (Dual Role)
-U&amp;I Trust
-Location:
-India
-Apply by:
-31 Mar 2026
-Rural India Fellowship
-Katakhali Swapnopuron Welfare Society
-Location:
-West Bengal
-Apply by:
-15 Mar 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F21" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G21" s="1" t="inlineStr">
-        <is>
-          <t>11-03-2026</t>
-        </is>
-      </c>
-      <c r="H21" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="I21" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287613</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B22" s="1" t="inlineStr"/>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="B18" s="1" t="inlineStr"/>
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>RFP - Study On SC-DMPA In Rajasthan- Clients And Providers Perspectives On...</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Centre For Community Economics And Development Consultants Society- CECOEDECON | Jaipur, Rajasthan
 International Development - RFP - Study On SC-DMPA In Rajasthan- Clients And Providers Perspectives On SC-DMPA In Rajasthan, Centre For Community Economics And Development Consultants Society- CECOEDE ... Read More</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>• Despite India’s achievement of replacement-level fertility, unmet need for contraception—particularly for spacing methods—remains substantial, with modern contraceptive use at 56.4% (2019–21), highlighting persistent gaps in access and choice, especially among vulnerable populations. Expanding the contraceptive method mix through innovative, user-centred approaches is therefore essential to meeting national commitments under FP2030 and the Sustainable Development Goals. In this context, the Government of India’s introduction of subcutaneous DMPA (DMPA-SC) as a self-care option under the National Family Planning Programme in 2023 represents a strategic step toward enhancing women’s autonomy, privacy, and convenience in contraceptive use. Global and national evidence indicates strong feasibility and acceptability of self-administered DMPA-SC among both users and providers; however, successful implementation requires an in-depth understanding of user experiences and health system readiness. This study, to be conducted in Jaipur-1, Jaisalmer and Sawai Madhopur districts of Rajasthan, aims to examine the perspectives &amp; experience of current SC-DMPA users and explore healthcare providers’ views on enabling and generating actionable evidence to inform effective scale-up of SC-DMPA within India’s public health system.
 CECOEDECON, with support from UNFPA, is implementing the roll-out of subcutaneous DMPA (SC-DMPA) in selected pilot districts of Rajasthan in the public health facilities, in collaboration with the Department of Health &amp; Family Welfare, Government of Rajasthan.
@@ -5132,54 +4213,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Documentation / Program Officer
-Pragati Path Foundation
-Location:
-Uttar Pradesh
-Apply by:
-25 Mar 2026
-Accounts Officer
-Jana Kalayana Samakhya
-Location:
-Odisha
-Apply by:
-30 Mar 2026
-Manager - Accounts &amp; Finance
-(Value Members only)
-Location:
-Rajasthan
-Apply by:
-13 Mar 2026
+Computer Science Trainer (School)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Computer Science Trainer (College)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Nursing Aid
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Driver
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Medical Officer
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Nurse
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Physiotherapist
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Project Coordinator
-Asra Samajik Lok Kalyan Samiti
-Location:
-Madhya Pradesh
-Apply by:
-30 Mar 2026
-Account Manager
-(Value Members only)
-Location:
-Odisha
-Apply by:
-10 Mar 2026
-Resource Person, Teacher Support – Ashram School ...
-Kavana Charitable Trust
-Location:
-Karnataka
-Apply by:
-02 Apr 2026
-Teach Manager, Child Development Team (Dual Role)
-U&amp;I Trust
-Location:
-India
-Apply by:
-31 Mar 2026
-Rural India Fellowship
-Katakhali Swapnopuron Welfare Society
-Location:
-West Bengal
-Apply by:
-15 Mar 2026
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Jobseekers
 Register
 Login
@@ -5207,38 +4288,273 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F22" s="1" t="inlineStr">
+      <c r="F18" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G22" s="1" t="inlineStr">
+      <c r="G18" s="1" t="inlineStr">
         <is>
           <t>11-03-2026</t>
         </is>
       </c>
-      <c r="H22" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="I22" s="1" t="inlineStr">
+      <c r="H18" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I18" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287322</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr"/>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="B19" s="1" t="inlineStr"/>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>RFP - for Supply of Skill Lab Items</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>TeamLease Foundation | India
+International Development - RFP - for Supply of Skill Lab Items, TeamLease Foundation, India - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers:
+Login
+|
+Register
+Jobseekers Login
+Jobseeker ... Read More</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>• Technical Bid Submission Link-
+https://forms.gle/V9iy35ddb4kWEb468
+• Financial Bid Submission Link-
+https://forms.gle/LozobuuuMh55Ea2G8
+Note
+: Technical bid and financial bid are to be submitted separately in separate links.
+Following points are to be kept in mind while submitting the bids-
+All Bid must contain the complete address of firm, including contact number/ email ID of the person who is authorized to submit the bid under their signatures.
+All bids must be signed on all pages by the bidder. Unsigned bids shall not be entertained/ accepted.
+All pages of the bid being submitted must be signed and sequentially numbered by the bidder irrespective of the nature of content of the documents.
+Bids not submitted as per the specified format and nomenclature or ambiguous in nature will be liable to be rejected.
+• The interested bidders may submit their bid to TLF on or before the date mentioned in this RFP Documents. Any bid received by TLF after the prescribed deadline for submission of bids will be rejected and no further correspondence in this regard will be entertained.
+Financial bid should be prepared as per Annexure II given in the RFP Documents. Same is also to be uploaded in google forms too.
+Bidders shall indicate their rates in clear/ visible figures as well as in words. In case of a mismatch, the rates written in words will prevail.
+• At any time prior to the last date for submission of bids, TLF, may, for any reason, whether at its own initiative or in response to a clarification requested by a prospective bidder, modify the RFP Documents by an amendment and publish the revised version of the RFP.
+The contract panel may consist of maximum three vendors for each item. However, TLF reserves the right to review the performance of the panel of vendors and terminate the contract of such vendors whose performance is not found satisfactory. The decision of TLF will be final in this regard.
+TLF will issue Purchase Order(s) (PO) during the period up to 31-March-2026. as per the required quantities and as per the rates and other terms of the Purchase Order.
+TLF may issue separate Purchase Order(s) PO based on its actual requirements to the Successful Bidder(s) for providing Product(s) and / or Service(s) and there is no minimum or prior commitment for such orders under this RFP.
+The successful bidder will be expected to provide all the necessary support for delivery of the items, warranty and required support during the warranty period.
+Delivery of the Kits specified in this RFP should be by 20
+th
+December 2025 from the PO date
+Successful bidder will ensure delivery, installation and operationalization of all products /components under the contract before acceptance testing / examination, and the Warranty period will commence only on acceptance of the products
+If, during the warranty period, any system as a whole or any subsystem has any failure on two or more occasions in a period of 3 months, it shall be replaced by equivalent new equipment by the Vendor at no cost to TLF
+The successful bidder shall be fully responsible for the manufacturer’s warranty for all equipment, accessories, spare parts etc. against any defects arising from design, material, manufacturing, workmanship, or any act or omission of the manufacturer / vendor or any defect that may develop under normal use of supplied equipment during the warranty period
+In case of any deviations, specific exemption may be sought on case-to-case basis from the respective Departments placing the Service Request
+• Printed terms and conditions of the bidders will not be considered as forming part of their bid. In case terms and conditions as given in the RFP Documents are not acceptable to any bidder, they should clearly specify the deviations in their bids.
+Bids complete in all respects along with supporting documents, must be submitted as per the RFP requirements. No physical document is to be submitted by the bidders.
+NO conditional or partial Bid will be entertained and will be rejected.
+• Parallel Contracts - TLF may also execute parallel contracts with more than one firm on the lowest approved rates on the same terms and conditions. These parallel contracts will be utilized if the original L1 substantially technically qualified bidder is not in a position to supply material as per TLFs requirement within the time frame indicated in the bid.
+For detailed information, please check the complete version of the RFP attached below.
+Download Attachment:
+RFP for procurement Skill Lab Items under RIST Mansi_250226.pdf
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+11 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Associate (Programme Management)
+Indian Institute For Human Settlements (Iihs)
+Location:
+Karnataka
+Apply by:
+07 Mar 2026
+Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+Computer Science Trainer (School)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Computer Science Trainer (College)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Nursing Aid
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Driver
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Medical Officer
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Nurse
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Physiotherapist
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Project Coordinator
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G19" s="1" t="inlineStr">
+        <is>
+          <t>11-03-2026</t>
+        </is>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I19" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287613</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr"/>
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>SOW - Engagement of a Public Relations (PR) Agency on Retainer</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Room to Read India | India
 International Development - SOW - Engagement of a Public Relations (PR) Agency on Retainer, Room to Read India, India - DevNetJobsIndia.org
@@ -5259,7 +4575,7 @@
 Job ... Read More</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>• Scope of Work (SOW)
 Engagement of a Public Relations (PR) Agency on Retainer
@@ -5389,54 +4705,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Documentation / Program Officer
-Pragati Path Foundation
-Location:
-Uttar Pradesh
-Apply by:
-25 Mar 2026
-Accounts Officer
-Jana Kalayana Samakhya
-Location:
-Odisha
-Apply by:
-30 Mar 2026
-Manager - Accounts &amp; Finance
-(Value Members only)
-Location:
-Rajasthan
-Apply by:
-13 Mar 2026
+Computer Science Trainer (School)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Computer Science Trainer (College)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Nursing Aid
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Driver
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Medical Officer
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Nurse
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Physiotherapist
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Project Coordinator
-Asra Samajik Lok Kalyan Samiti
-Location:
-Madhya Pradesh
-Apply by:
-30 Mar 2026
-Account Manager
-(Value Members only)
-Location:
-Odisha
-Apply by:
-10 Mar 2026
-Resource Person, Teacher Support – Ashram School ...
-Kavana Charitable Trust
-Location:
-Karnataka
-Apply by:
-02 Apr 2026
-Teach Manager, Child Development Team (Dual Role)
-U&amp;I Trust
-Location:
-India
-Apply by:
-31 Mar 2026
-Rural India Fellowship
-Katakhali Swapnopuron Welfare Society
-Location:
-West Bengal
-Apply by:
-15 Mar 2026
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Jobseekers
 Register
 Login
@@ -5464,38 +4780,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F23" s="1" t="inlineStr">
+      <c r="F20" s="1" t="inlineStr">
         <is>
           <t>Governance, Learning</t>
         </is>
       </c>
-      <c r="G23" s="1" t="inlineStr">
+      <c r="G20" s="1" t="inlineStr">
         <is>
           <t>12-03-2026</t>
         </is>
       </c>
-      <c r="H23" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="I23" s="1" t="inlineStr">
+      <c r="H20" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I20" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287648</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr"/>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="B21" s="1" t="inlineStr"/>
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>RFP - for Internal Audit</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>India HIV/AIDS Alliance (Alliance India) | Delhi
 International Development - RFP - for Internal Audit, India HIV/AIDS Alliance (Alliance India), Delhi - DevNetJobsIndia.org
@@ -5515,7 +4831,7 @@
 Regist ... Read More</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>• Alliance India reserves the right to reject applications that do not meet eligibility or application submission requirements (as detailed above) without further notice to the applicant. Issuance of this RFP does not constitute an award commitment or a guarantee of business on the part of Alliance India, nor does it commit Alliance India to pay for the costs incurred in submitting the application. Further, Alliance India reserves the right to reject any or all applications received and negotiate separately with an applicant if such action is considered in the best interest of Alliance India/ project.
 iii.
@@ -5602,54 +4918,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Documentation / Program Officer
-Pragati Path Foundation
-Location:
-Uttar Pradesh
-Apply by:
-25 Mar 2026
-Accounts Officer
-Jana Kalayana Samakhya
-Location:
-Odisha
-Apply by:
-30 Mar 2026
-Manager - Accounts &amp; Finance
-(Value Members only)
-Location:
-Rajasthan
-Apply by:
-13 Mar 2026
+Computer Science Trainer (School)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Computer Science Trainer (College)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Nursing Aid
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Driver
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Medical Officer
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Nurse
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Physiotherapist
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Project Coordinator
-Asra Samajik Lok Kalyan Samiti
-Location:
-Madhya Pradesh
-Apply by:
-30 Mar 2026
-Account Manager
-(Value Members only)
-Location:
-Odisha
-Apply by:
-10 Mar 2026
-Resource Person, Teacher Support – Ashram School ...
-Kavana Charitable Trust
-Location:
-Karnataka
-Apply by:
-02 Apr 2026
-Teach Manager, Child Development Team (Dual Role)
-U&amp;I Trust
-Location:
-India
-Apply by:
-31 Mar 2026
-Rural India Fellowship
-Katakhali Swapnopuron Welfare Society
-Location:
-West Bengal
-Apply by:
-15 Mar 2026
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Jobseekers
 Register
 Login
@@ -5677,38 +4993,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F24" s="1" t="inlineStr">
+      <c r="F21" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G24" s="1" t="inlineStr">
+      <c r="G21" s="1" t="inlineStr">
         <is>
           <t>13-03-2026</t>
         </is>
       </c>
-      <c r="H24" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="I24" s="1" t="inlineStr">
+      <c r="H21" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="I21" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287765</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr"/>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="B22" s="1" t="inlineStr"/>
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>Specialist – Financial Management and Compliance</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Financial Management Service Foundation (FMSF) | Uttar Pradesh
 International Development - Specialist – Financial Management and Compliance, Financial Management Service Foundation (FMSF), Uttar Pradesh - DevNetJobsIndia.org
@@ -5722,7 +5038,7 @@
 RFPs/T ... Read More</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>• will play a vital role in a program which seeks to strengthen the internal capacities of non-profit organizations in India across three building blocks of institutional functioning: governance, financial management, and compliance. These areas are deeply interconnected and together determine how effectively an organization operates, delivers programs and meets the expectations of its stakeholders. This position demands expertise in specific areas related to governance, compliance, and financial management, contributing essential guidance and support to strengthen the capabilities of participating organizations.
 Job Responsibilities:
@@ -5835,54 +5151,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Documentation / Program Officer
-Pragati Path Foundation
-Location:
-Uttar Pradesh
-Apply by:
-25 Mar 2026
-Accounts Officer
-Jana Kalayana Samakhya
-Location:
-Odisha
-Apply by:
-30 Mar 2026
-Manager - Accounts &amp; Finance
-(Value Members only)
-Location:
-Rajasthan
-Apply by:
-13 Mar 2026
+Computer Science Trainer (School)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Computer Science Trainer (College)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Nursing Aid
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Driver
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Medical Officer
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Nurse
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Physiotherapist
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Project Coordinator
-Asra Samajik Lok Kalyan Samiti
-Location:
-Madhya Pradesh
-Apply by:
-30 Mar 2026
-Account Manager
-(Value Members only)
-Location:
-Odisha
-Apply by:
-10 Mar 2026
-Resource Person, Teacher Support – Ashram School ...
-Kavana Charitable Trust
-Location:
-Karnataka
-Apply by:
-02 Apr 2026
-Teach Manager, Child Development Team (Dual Role)
-U&amp;I Trust
-Location:
-India
-Apply by:
-31 Mar 2026
-Rural India Fellowship
-Katakhali Swapnopuron Welfare Society
-Location:
-West Bengal
-Apply by:
-15 Mar 2026
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Jobseekers
 Register
 Login
@@ -5910,38 +5226,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F25" s="1" t="inlineStr">
+      <c r="F22" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G25" s="1" t="inlineStr">
+      <c r="G22" s="1" t="inlineStr">
         <is>
           <t>13-03-2026</t>
         </is>
       </c>
-      <c r="H25" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="I25" s="1" t="inlineStr">
+      <c r="H22" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="I22" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287015</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr"/>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="B23" s="1" t="inlineStr"/>
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>RFP - External organization/agency to undertake documentation and process ...</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>India Health Action Trust (IHAT) | India
 International Development - RFP - External organization/agency to undertake documentation and process evaluation of the Gen Equal Fellowship Programme, India Health Action Trust (IHAT), India - DevNetJobsIndia.org
@@ -5953,7 +5269,7 @@
 Value Memb ... Read More</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>• 3A. Scope of Work
 Time Period
@@ -6098,54 +5414,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Documentation / Program Officer
-Pragati Path Foundation
-Location:
-Uttar Pradesh
-Apply by:
-25 Mar 2026
-Accounts Officer
-Jana Kalayana Samakhya
-Location:
-Odisha
-Apply by:
-30 Mar 2026
-Manager - Accounts &amp; Finance
-(Value Members only)
-Location:
-Rajasthan
-Apply by:
-13 Mar 2026
+Computer Science Trainer (School)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Computer Science Trainer (College)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Nursing Aid
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Driver
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Medical Officer
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Nurse
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Physiotherapist
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Project Coordinator
-Asra Samajik Lok Kalyan Samiti
-Location:
-Madhya Pradesh
-Apply by:
-30 Mar 2026
-Account Manager
-(Value Members only)
-Location:
-Odisha
-Apply by:
-10 Mar 2026
-Resource Person, Teacher Support – Ashram School ...
-Kavana Charitable Trust
-Location:
-Karnataka
-Apply by:
-02 Apr 2026
-Teach Manager, Child Development Team (Dual Role)
-U&amp;I Trust
-Location:
-India
-Apply by:
-31 Mar 2026
-Rural India Fellowship
-Katakhali Swapnopuron Welfare Society
-Location:
-West Bengal
-Apply by:
-15 Mar 2026
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Jobseekers
 Register
 Login
@@ -6173,38 +5489,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F26" s="1" t="inlineStr">
+      <c r="F23" s="1" t="inlineStr">
         <is>
           <t>Safety</t>
         </is>
       </c>
-      <c r="G26" s="1" t="inlineStr">
+      <c r="G23" s="1" t="inlineStr">
         <is>
           <t>15-03-2026</t>
         </is>
       </c>
-      <c r="H26" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="I26" s="1" t="inlineStr">
+      <c r="H23" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="I23" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287645</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr"/>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="B24" s="1" t="inlineStr"/>
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>RFP - for Empanelment of Knowledge Partners for Grooming of students for ...</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>TeamLease Foundation | India
 International Development - RFP - for  Empanelment of Knowledge Partners for Grooming of students for competitive examination (through partner) Super 30 Model, TeamLease Foundation, India - DevNetJobsIndia.org
@@ -6217,43 +5533,43 @@
 Broadcast ... Read More</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F27" s="1" t="inlineStr">
+      <c r="F24" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G27" s="1" t="inlineStr">
+      <c r="G24" s="1" t="inlineStr">
         <is>
           <t>15-03-2026</t>
         </is>
       </c>
-      <c r="H27" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="I27" s="1" t="inlineStr">
+      <c r="H24" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="I24" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287763</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr"/>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="B25" s="1" t="inlineStr"/>
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>RFP - Big IC+ISA RFP - Selection of a Service Provider for Supply, Instal...</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>EAII Advisors Pvt Ltd | Andhra Pradesh
 International Development - RFP - Big IC+ISA RFP -  Selection of a Service Provider for Supply, Installation and Operation &amp; Maintenance of 150 ILC Devices and Capacity Building., EAII Advisors Pvt Ltd, Andhra Pradesh - DevNetJobsIndia.org
@@ -6262,7 +5578,7 @@
 | ... Read More</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>• 2. Purpose of the RFP:
 2.1  EAII is soliciting bids for:
@@ -6371,54 +5687,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Documentation / Program Officer
-Pragati Path Foundation
-Location:
-Uttar Pradesh
-Apply by:
-25 Mar 2026
-Accounts Officer
-Jana Kalayana Samakhya
-Location:
-Odisha
-Apply by:
-30 Mar 2026
-Manager - Accounts &amp; Finance
-(Value Members only)
-Location:
-Rajasthan
-Apply by:
-13 Mar 2026
+Computer Science Trainer (School)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Computer Science Trainer (College)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Nursing Aid
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Driver
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Medical Officer
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Nurse
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Physiotherapist
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Project Coordinator
-Asra Samajik Lok Kalyan Samiti
-Location:
-Madhya Pradesh
-Apply by:
-30 Mar 2026
-Account Manager
-(Value Members only)
-Location:
-Odisha
-Apply by:
-10 Mar 2026
-Resource Person, Teacher Support – Ashram School ...
-Kavana Charitable Trust
-Location:
-Karnataka
-Apply by:
-02 Apr 2026
-Teach Manager, Child Development Team (Dual Role)
-U&amp;I Trust
-Location:
-India
-Apply by:
-31 Mar 2026
-Rural India Fellowship
-Katakhali Swapnopuron Welfare Society
-Location:
-West Bengal
-Apply by:
-15 Mar 2026
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Jobseekers
 Register
 Login
@@ -6446,38 +5762,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F28" s="1" t="inlineStr">
+      <c r="F25" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G28" s="1" t="inlineStr">
+      <c r="G25" s="1" t="inlineStr">
         <is>
           <t>16-03-2026</t>
         </is>
       </c>
-      <c r="H28" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="I28" s="1" t="inlineStr">
+      <c r="H25" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="I25" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287172</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr"/>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="B26" s="1" t="inlineStr"/>
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>Specialist – Communication</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Financial Management Service Foundation (FMSF) | Uttar Pradesh
 International Development - Specialist – Communication, Financial Management Service Foundation (FMSF), Uttar Pradesh - DevNetJobsIndia.org
@@ -6493,7 +5809,7 @@
 Eve ... Read More</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>• Joining FMSF means becoming part of a passionate team dedicated to making a positive impact. We offer competitive compensation, opportunities for professional development, and a supportive work environment where your contributions are valued and recognized. If you are committed to driving positive change, promoting accountability and strengthening the development sector, we encourage you to apply for the position of Specialist – Communication at FMSF.
 • How to Apply:
@@ -6577,54 +5893,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Documentation / Program Officer
-Pragati Path Foundation
-Location:
-Uttar Pradesh
-Apply by:
-25 Mar 2026
-Accounts Officer
-Jana Kalayana Samakhya
-Location:
-Odisha
-Apply by:
-30 Mar 2026
-Manager - Accounts &amp; Finance
-(Value Members only)
-Location:
-Rajasthan
-Apply by:
-13 Mar 2026
+Computer Science Trainer (School)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Computer Science Trainer (College)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Nursing Aid
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Driver
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Medical Officer
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Nurse
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Physiotherapist
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Project Coordinator
-Asra Samajik Lok Kalyan Samiti
-Location:
-Madhya Pradesh
-Apply by:
-30 Mar 2026
-Account Manager
-(Value Members only)
-Location:
-Odisha
-Apply by:
-10 Mar 2026
-Resource Person, Teacher Support – Ashram School ...
-Kavana Charitable Trust
-Location:
-Karnataka
-Apply by:
-02 Apr 2026
-Teach Manager, Child Development Team (Dual Role)
-U&amp;I Trust
-Location:
-India
-Apply by:
-31 Mar 2026
-Rural India Fellowship
-Katakhali Swapnopuron Welfare Society
-Location:
-West Bengal
-Apply by:
-15 Mar 2026
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Jobseekers
 Register
 Login
@@ -6652,38 +5968,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F29" s="1" t="inlineStr">
+      <c r="F26" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G29" s="1" t="inlineStr">
+      <c r="G26" s="1" t="inlineStr">
         <is>
           <t>19-03-2026</t>
         </is>
       </c>
-      <c r="H29" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="I29" s="1" t="inlineStr">
+      <c r="H26" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="I26" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287207</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B30" s="1" t="inlineStr"/>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="B27" s="1" t="inlineStr"/>
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>Specialist - Grants</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Financial Management Service Foundation (FMSF) | Uttar Pradesh
 International Development - Specialist - Grants, Financial Management Service Foundation (FMSF), Uttar Pradesh - DevNetJobsIndia.org
@@ -6700,7 +6016,7 @@
 Job ... Read More</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>• Joining FMSF means becoming part of a passionate team dedicated to making a positive impact. We offer competitive compensation, opportunities for professional development, and a supportive work environment where your contributions are valued and recognized. If you are committed to driving positive change, promoting accountability and strengthening the development sector, we encourage you to apply for the position of Specialist - Grants at FMSF.
 You’re Resume to be accompanied with:
@@ -6784,54 +6100,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Documentation / Program Officer
-Pragati Path Foundation
-Location:
-Uttar Pradesh
-Apply by:
-25 Mar 2026
-Accounts Officer
-Jana Kalayana Samakhya
-Location:
-Odisha
-Apply by:
-30 Mar 2026
-Manager - Accounts &amp; Finance
-(Value Members only)
-Location:
-Rajasthan
-Apply by:
-13 Mar 2026
+Computer Science Trainer (School)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Computer Science Trainer (College)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Nursing Aid
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Driver
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Medical Officer
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Nurse
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Physiotherapist
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Project Coordinator
-Asra Samajik Lok Kalyan Samiti
-Location:
-Madhya Pradesh
-Apply by:
-30 Mar 2026
-Account Manager
-(Value Members only)
-Location:
-Odisha
-Apply by:
-10 Mar 2026
-Resource Person, Teacher Support – Ashram School ...
-Kavana Charitable Trust
-Location:
-Karnataka
-Apply by:
-02 Apr 2026
-Teach Manager, Child Development Team (Dual Role)
-U&amp;I Trust
-Location:
-India
-Apply by:
-31 Mar 2026
-Rural India Fellowship
-Katakhali Swapnopuron Welfare Society
-Location:
-West Bengal
-Apply by:
-15 Mar 2026
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Jobseekers
 Register
 Login
@@ -6859,38 +6175,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F30" s="1" t="inlineStr">
+      <c r="F27" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G30" s="1" t="inlineStr">
+      <c r="G27" s="1" t="inlineStr">
         <is>
           <t>21-03-2026</t>
         </is>
       </c>
-      <c r="H30" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="I30" s="1" t="inlineStr">
+      <c r="H27" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="I27" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287318</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr"/>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="B28" s="1" t="inlineStr"/>
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>EoI – Mobile Medical Units, Ai-Enabled Tb Screening &amp; Supply Of Medical An...</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Ashray Foundation | Korba, Chattisgarh (Delivery Location), Gujarat
 International Development - EoI – Mobile Medical Units, Ai-Enabled Tb Screening &amp; Supply Of Medical And Nutritional Support, Ashray Foundation, Gujarat - DevNetJobsIndia.org
@@ -6903,7 +6219,7 @@
 Broadc ... Read More</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>• Ashray Foundation invites eligible and experienced agencies to submit their Expression of Interest / for the following scope of work:
 Fabrication of Mobile Medical Units (MMUs) – 2 Units
@@ -6992,54 +6308,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Documentation / Program Officer
-Pragati Path Foundation
-Location:
-Uttar Pradesh
-Apply by:
-25 Mar 2026
-Accounts Officer
-Jana Kalayana Samakhya
-Location:
-Odisha
-Apply by:
-30 Mar 2026
-Manager - Accounts &amp; Finance
-(Value Members only)
-Location:
-Rajasthan
-Apply by:
-13 Mar 2026
+Computer Science Trainer (School)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Computer Science Trainer (College)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Nursing Aid
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Driver
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Medical Officer
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Nurse
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Physiotherapist
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Project Coordinator
-Asra Samajik Lok Kalyan Samiti
-Location:
-Madhya Pradesh
-Apply by:
-30 Mar 2026
-Account Manager
-(Value Members only)
-Location:
-Odisha
-Apply by:
-10 Mar 2026
-Resource Person, Teacher Support – Ashram School ...
-Kavana Charitable Trust
-Location:
-Karnataka
-Apply by:
-02 Apr 2026
-Teach Manager, Child Development Team (Dual Role)
-U&amp;I Trust
-Location:
-India
-Apply by:
-31 Mar 2026
-Rural India Fellowship
-Katakhali Swapnopuron Welfare Society
-Location:
-West Bengal
-Apply by:
-15 Mar 2026
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Jobseekers
 Register
 Login
@@ -7067,38 +6383,267 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F31" s="1" t="inlineStr">
+      <c r="F28" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G31" s="1" t="inlineStr">
+      <c r="G28" s="1" t="inlineStr">
         <is>
           <t>24-03-2026</t>
         </is>
       </c>
-      <c r="H31" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="I31" s="1" t="inlineStr">
+      <c r="H28" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="I28" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287319</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B32" s="1" t="inlineStr"/>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="B29" s="1" t="inlineStr"/>
+      <c r="C29" s="1" t="inlineStr">
+        <is>
+          <t>Junior Research Technicians / Senior Project Asso...</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Starshield Security Solution Pvt.Ltd | Uttar Pradesh
+International Development - Junior Research Technicians / Senior Project Associate, Starshield Security Solution Pvt.Ltd, Uttar Pradesh - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search ... Read More</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>• Eligibility Criteria
+Qualification
+:
+Intermediate with 2–3 years of relevant experience
+OR
+Graduate with 1–2 years of relevant experience
+Skills &amp; Experience (Mandatory):
+Experience in agriculture field operations and data collection
+Basic knowledge of MS Office (Word &amp; Excel)
+Experience in rice-wheat cropping system production preferred
+Good coordination and communication skills
+Willingness to travel and work in field conditions
+Knowledge of smart mobile apps for data survey and data recording
+Knowledge on agri machinery
+Community mobilization and Work with Farmers group/FPCs
+The applicants must have a two-wheeler vehicle and license with them
+Key Performance Indicators
+Timely support to demonstrations, trainings, and field activities
+Accurate data collection and documentation
+Proper maintenance of equipment and field sites
+Positive feedback from farmers and stakeholders
+Creation of new service providers
+Application Details
+Interested candidates are requested to fill-out the shared application form and submit their updated CV via email to
+communications@starshieldsolution.com
+with the subject line:
+Application for Junior Research Technician (IRRI Project Deployment)
+.
+Only shortlisted candidates who complete the required documentation will be considered for subsequent stages of selection.
+Selection will be done on a first-come-first-served basis. Applications received up to Thursday each week will be reviewed, and interviews will be conducted in the following week. As soon as we shall finish all recruitment, we will take the advertisement off.
+• Job Email ID:
+communications(at)starshieldsolution.com
+Download Attachment:
+Application Proforma_Junior Research Technicians -  Senior Project Associate.doc
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+30 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Associate (Programme Management)
+Indian Institute For Human Settlements (Iihs)
+Location:
+Karnataka
+Apply by:
+07 Mar 2026
+Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+Computer Science Trainer (School)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Computer Science Trainer (College)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Nursing Aid
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Driver
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Medical Officer
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Nurse
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Physiotherapist
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Project Coordinator
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F29" s="1" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="G29" s="1" t="inlineStr">
+        <is>
+          <t>30-03-2026</t>
+        </is>
+      </c>
+      <c r="H29" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="I29" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287635</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr"/>
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>Agriculture Research Development Officer / Projec...</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Starshield Security Solution Pvt.Ltd | Uttar Pradesh
 International Development - Agriculture Research Development Officer / Project Scientist III, Starshield Security Solution Pvt.Ltd, Uttar Pradesh - DevNetJobsIndia.org
@@ -7112,7 +6657,7 @@
 RFPs/Tende ... Read More</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>• Eligibility Criteria
 Qualification:
@@ -7221,54 +6766,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Documentation / Program Officer
-Pragati Path Foundation
-Location:
-Uttar Pradesh
-Apply by:
-25 Mar 2026
-Accounts Officer
-Jana Kalayana Samakhya
-Location:
-Odisha
-Apply by:
-30 Mar 2026
-Manager - Accounts &amp; Finance
-(Value Members only)
-Location:
-Rajasthan
-Apply by:
-13 Mar 2026
+Computer Science Trainer (School)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Computer Science Trainer (College)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Nursing Aid
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Driver
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Medical Officer
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Nurse
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Physiotherapist
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Project Coordinator
-Asra Samajik Lok Kalyan Samiti
-Location:
-Madhya Pradesh
-Apply by:
-30 Mar 2026
-Account Manager
-(Value Members only)
-Location:
-Odisha
-Apply by:
-10 Mar 2026
-Resource Person, Teacher Support – Ashram School ...
-Kavana Charitable Trust
-Location:
-Karnataka
-Apply by:
-02 Apr 2026
-Teach Manager, Child Development Team (Dual Role)
-U&amp;I Trust
-Location:
-India
-Apply by:
-31 Mar 2026
-Rural India Fellowship
-Katakhali Swapnopuron Welfare Society
-Location:
-West Bengal
-Apply by:
-15 Mar 2026
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Jobseekers
 Register
 Login
@@ -7296,41 +6841,41 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F32" s="1" t="inlineStr">
+      <c r="F30" s="1" t="inlineStr">
         <is>
           <t>Learning, Safety</t>
         </is>
       </c>
-      <c r="G32" s="1" t="inlineStr">
+      <c r="G30" s="1" t="inlineStr">
         <is>
           <t>30-03-2026</t>
         </is>
       </c>
-      <c r="H32" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="I32" s="1" t="inlineStr">
+      <c r="H30" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="I30" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287636</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B33" s="1" t="inlineStr"/>
-      <c r="C33" s="1" t="inlineStr">
-        <is>
-          <t>Junior Research Technicians / Senior Project Asso...</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Starshield Security Solution Pvt.Ltd | Uttar Pradesh
-International Development - Junior Research Technicians / Senior Project Associate, Starshield Security Solution Pvt.Ltd, Uttar Pradesh - DevNetJobsIndia.org
+      <c r="B31" s="1" t="inlineStr"/>
+      <c r="C31" s="1" t="inlineStr">
+        <is>
+          <t>Sector Experts</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Academy of Management Studies (AMS) | India
+International Development - Sector Experts, Academy of Management Studies (AMS), India - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
@@ -7339,50 +6884,44 @@
 Value Membership
 Broadcast Resume
 RFPs/Tenders
-Search ... Read More</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>• Eligibility Criteria
-Qualification
-:
-Intermediate with 2–3 years of relevant experience
-OR
-Graduate with 1–2 years of relevant experience
-Skills &amp; Experience (Mandatory):
-Experience in agriculture field operations and data collection
-Basic knowledge of MS Office (Word &amp; Excel)
-Experience in rice-wheat cropping system production preferred
-Good coordination and communication skills
-Willingness to travel and work in field conditions
-Knowledge of smart mobile apps for data survey and data recording
-Knowledge on agri machinery
-Community mobilization and Work with Farmers group/FPCs
-The applicants must have a two-wheeler vehicle and license with them
-Key Performance Indicators
-Timely support to demonstrations, trainings, and field activities
-Accurate data collection and documentation
-Proper maintenance of equipment and field sites
-Positive feedback from farmers and stakeholders
-Creation of new service providers
-Application Details
-Interested candidates are requested to fill-out the shared application form and submit their updated CV via email to
-communications@starshieldsolution.com
-with the subject line:
-Application for Junior Research Technician (IRRI Project Deployment)
-.
-Only shortlisted candidates who complete the required documentation will be considered for subsequent stages of selection.
-Selection will be done on a first-come-first-served basis. Applications received up to Thursday each week will be reviewed, and interviews will be conducted in the following week. As soon as we shall finish all recruitment, we will take the advertisement off.
+Search Jobs
+Events
+Jobseekers:
+Login
+|
+Register
+Jobseekers Login ... Read More</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>• Eligibility
+Postgraduate degree / Ph.D. in relevant or allied disciplines
+Minimum 5 years of relevant experience
+Experience of working with Government Departments / International Agencies preferred
+Demonstrated experience in research, monitoring &amp; evaluation, or technical advisory role
+Engagement Terms
+Shortlisted Experts shall be empaneled for a duration of 1 year which is extendable based on mutual agreement. Experts shall be engaged in short-term project-based assignments that organization undertakes in relevant sectors. The duration of engagement, project-specific roles and responsibilities, and remuneration will be decided as per project requirements and expertise level.
+• How to Apply
+Interested candidates may mail their detailed CV along with a recent photograph by
+31st March, 2026
+to
+hrd@amsindia.org
+mentioning“
+Sector Experts – Sector Name
+” in the subject line. The applicants must also mention in their emails the following details:
+Area(s) of specialization
+Current status of Employment
+Expected professional fee (daily/monthly)
 • Job Email ID:
-communications(at)starshieldsolution.com
+hrd(at)amsindia.org
 Download Attachment:
-Application Proforma_Junior Research Technicians -  Senior Project Associate.doc
+Empanelment of Experts.pdf
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
 Apply by:
-30 Mar 2026
+31 Mar 2026
 Access all the jobs and get ahead!
 Subscribe to Value Membership Now!
 Subscribe
@@ -7450,54 +6989,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Documentation / Program Officer
-Pragati Path Foundation
-Location:
-Uttar Pradesh
-Apply by:
-25 Mar 2026
-Accounts Officer
-Jana Kalayana Samakhya
-Location:
-Odisha
-Apply by:
-30 Mar 2026
-Manager - Accounts &amp; Finance
-(Value Members only)
-Location:
-Rajasthan
-Apply by:
-13 Mar 2026
+Computer Science Trainer (School)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Computer Science Trainer (College)
+Raspberry Pi Foundation
+Location:
+Telangana
+Apply by:
+04 Apr 2026
+Nursing Aid
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Driver
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Medical Officer
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Nurse
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
+Physiotherapist
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Project Coordinator
-Asra Samajik Lok Kalyan Samiti
-Location:
-Madhya Pradesh
-Apply by:
-30 Mar 2026
-Account Manager
-(Value Members only)
-Location:
-Odisha
-Apply by:
-10 Mar 2026
-Resource Person, Teacher Support – Ashram School ...
-Kavana Charitable Trust
-Location:
-Karnataka
-Apply by:
-02 Apr 2026
-Teach Manager, Child Development Team (Dual Role)
-U&amp;I Trust
-Location:
-India
-Apply by:
-31 Mar 2026
-Rural India Fellowship
-Katakhali Swapnopuron Welfare Society
-Location:
-West Bengal
-Apply by:
-15 Mar 2026
+The Catholic Health Association of India (CHAI)
+Location:
+Telangana
+Apply by:
+11 Mar 2026
 Jobseekers
 Register
 Login
@@ -7525,245 +7064,103 @@
 Recruitment Exchange</t>
         </is>
       </c>
+      <c r="F31" s="1" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G31" s="1" t="inlineStr">
+        <is>
+          <t>31-03-2026</t>
+        </is>
+      </c>
+      <c r="H31" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="I31" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287726</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr"/>
+      <c r="C32" s="1" t="inlineStr">
+        <is>
+          <t>RFP for Endline Evaluation Study - HSBC GCC Women Entrepreneurship Program - Click here</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="1" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G32" s="1" t="inlineStr"/>
+      <c r="H32" s="1" t="inlineStr"/>
+      <c r="I32" s="1" t="inlineStr">
+        <is>
+          <t>https://www.nasscomfoundation.org/pdf/endline-evaluation-study-hsbc-gcc-women-entrepreneurship-program.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="inlineStr"/>
+      <c r="C33" s="1" t="inlineStr">
+        <is>
+          <t>Travel &amp; Transportation Services for Trainer Mobility - IBM SkillBuild Bootcamps - Click here</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr"/>
+      <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="1" t="inlineStr">
         <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="G33" s="1" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="H33" s="1" t="n">
-        <v>26</v>
-      </c>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G33" s="1" t="inlineStr"/>
+      <c r="H33" s="1" t="inlineStr"/>
       <c r="I33" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287635</t>
+          <t>https://www.nasscomfoundation.org/pdf/travel-and-transportation-services-for-trainer-mobility-ibm-skillbuild-bootcamps.pdf</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>DevNetJobsIndia</t>
+          <t>Nasscom</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr"/>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>Sector Experts</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Academy of Management Studies (AMS) | India
-International Development - Sector Experts, Academy of Management Studies (AMS), India - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Login
-|
-Register
-Jobseekers Login ... Read More</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>• Eligibility
-Postgraduate degree / Ph.D. in relevant or allied disciplines
-Minimum 5 years of relevant experience
-Experience of working with Government Departments / International Agencies preferred
-Demonstrated experience in research, monitoring &amp; evaluation, or technical advisory role
-Engagement Terms
-Shortlisted Experts shall be empaneled for a duration of 1 year which is extendable based on mutual agreement. Experts shall be engaged in short-term project-based assignments that organization undertakes in relevant sectors. The duration of engagement, project-specific roles and responsibilities, and remuneration will be decided as per project requirements and expertise level.
-• How to Apply
-Interested candidates may mail their detailed CV along with a recent photograph by
-31st March, 2026
-to
-hrd@amsindia.org
-mentioning“
-Sector Experts – Sector Name
-” in the subject line. The applicants must also mention in their emails the following details:
-Area(s) of specialization
-Current status of Employment
-Expected professional fee (daily/monthly)
-• Job Email ID:
-hrd(at)amsindia.org
-Download Attachment:
-Empanelment of Experts.pdf
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-31 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-Documentation / Program Officer
-Pragati Path Foundation
-Location:
-Uttar Pradesh
-Apply by:
-25 Mar 2026
-Accounts Officer
-Jana Kalayana Samakhya
-Location:
-Odisha
-Apply by:
-30 Mar 2026
-Manager - Accounts &amp; Finance
-(Value Members only)
-Location:
-Rajasthan
-Apply by:
-13 Mar 2026
-Project Coordinator
-Asra Samajik Lok Kalyan Samiti
-Location:
-Madhya Pradesh
-Apply by:
-30 Mar 2026
-Account Manager
-(Value Members only)
-Location:
-Odisha
-Apply by:
-10 Mar 2026
-Resource Person, Teacher Support – Ashram School ...
-Kavana Charitable Trust
-Location:
-Karnataka
-Apply by:
-02 Apr 2026
-Teach Manager, Child Development Team (Dual Role)
-U&amp;I Trust
-Location:
-India
-Apply by:
-31 Mar 2026
-Rural India Fellowship
-Katakhali Swapnopuron Welfare Society
-Location:
-West Bengal
-Apply by:
-15 Mar 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
+          <t>Baseline and End-line Evaluation of the HSBC Neurodivergent Digital Annotator Skilling Program - Click here | Click here</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G34" s="1" t="inlineStr">
-        <is>
-          <t>31-03-2026</t>
-        </is>
-      </c>
-      <c r="H34" s="1" t="n">
-        <v>27</v>
-      </c>
+      <c r="G34" s="1" t="inlineStr"/>
+      <c r="H34" s="1" t="inlineStr"/>
       <c r="I34" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287726</t>
+          <t>https://www.nasscomfoundation.org/pdf/baseline-and-end-line-evaluation-of-hsbc-neurodivergent-digital-annotator-skilling-program.pdf</t>
         </is>
       </c>
     </row>
@@ -7776,21 +7173,21 @@
       <c r="B35" s="1" t="inlineStr"/>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>RFP for Endline Evaluation Study - HSBC GCC Women Entrepreneurship Program - Click here</t>
+          <t>RFP for Catering Vendor - IBM Skillbuild Bootcamps - Click here</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G35" s="1" t="inlineStr"/>
       <c r="H35" s="1" t="inlineStr"/>
       <c r="I35" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/endline-evaluation-study-hsbc-gcc-women-entrepreneurship-program.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/rfp-for-catering-vendor-ibm-skillbuild-bootcamps.pdf</t>
         </is>
       </c>
     </row>
@@ -7803,21 +7200,21 @@
       <c r="B36" s="1" t="inlineStr"/>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>Travel &amp; Transportation Services for Trainer Mobility - IBM SkillBuild Bootcamps - Click here</t>
+          <t>Organization-wide Management Information System (MIS) for Nasscom Foundation - Click here</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G36" s="1" t="inlineStr"/>
       <c r="H36" s="1" t="inlineStr"/>
       <c r="I36" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/travel-and-transportation-services-for-trainer-mobility-ibm-skillbuild-bootcamps.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/organization-wide-management-information-system-for-nasscom-foundation.pdf</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7227,7 @@
       <c r="B37" s="1" t="inlineStr"/>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>Baseline and End-line Evaluation of the HSBC Neurodivergent Digital Annotator Skilling Program - Click here | Click here</t>
+          <t>Request for Proposal (RFP) for Social Media Management Services - Click here</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr"/>
@@ -7844,7 +7241,7 @@
       <c r="H37" s="1" t="inlineStr"/>
       <c r="I37" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/baseline-and-end-line-evaluation-of-hsbc-neurodivergent-digital-annotator-skilling-program.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/request-for-proposal-for-social-media-management-services.pdf</t>
         </is>
       </c>
     </row>
@@ -7857,21 +7254,21 @@
       <c r="B38" s="1" t="inlineStr"/>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>RFP for Catering Vendor - IBM Skillbuild Bootcamps - Click here</t>
+          <t>RFP - TechForSociety - Evaluation Study - Click here</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr"/>
       <c r="H38" s="1" t="inlineStr"/>
       <c r="I38" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/rfp-for-catering-vendor-ibm-skillbuild-bootcamps.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/techforsociety-evaluation-study.pdf</t>
         </is>
       </c>
     </row>
@@ -7884,7 +7281,7 @@
       <c r="B39" s="1" t="inlineStr"/>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>Organization-wide Management Information System (MIS) for Nasscom Foundation - Click here</t>
+          <t>Base-line and End-line evaluation for Digital Literacy Project in 4 States - Click here</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr"/>
@@ -7898,7 +7295,7 @@
       <c r="H39" s="1" t="inlineStr"/>
       <c r="I39" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/organization-wide-management-information-system-for-nasscom-foundation.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/base-line-and-end-line-evaluation-for-digital-literacy-project-in-4-states.pdf</t>
         </is>
       </c>
     </row>
@@ -7911,21 +7308,21 @@
       <c r="B40" s="1" t="inlineStr"/>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>Request for Proposal (RFP) for Social Media Management Services - Click here</t>
+          <t>IP Selection - Scholarship Support to students from Economically Weaker Section pursuing higher education in STEM courses - Click here</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G40" s="1" t="inlineStr"/>
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/request-for-proposal-for-social-media-management-services.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/scholarship-support-for-economically-weaker-section-students-in-stem-higher-education.pdf</t>
         </is>
       </c>
     </row>
@@ -7938,21 +7335,21 @@
       <c r="B41" s="1" t="inlineStr"/>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>RFP - TechForSociety - Evaluation Study - Click here</t>
+          <t>Digital Upskilling of Farmer Producer Organizations (FPOs) through Technology - Click here</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr"/>
       <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G41" s="1" t="inlineStr"/>
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/techforsociety-evaluation-study.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/baseline-endline-study-digital-upskilling-fpos-technology.pdf</t>
         </is>
       </c>
     </row>
@@ -7965,21 +7362,21 @@
       <c r="B42" s="1" t="inlineStr"/>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>Base-line and End-line evaluation for Digital Literacy Project in 4 States - Click here</t>
+          <t>Project - Accelerating 100 Women Micro Entrepreneurs of Northeastern States - Click here</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr"/>
       <c r="F42" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G42" s="1" t="inlineStr"/>
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/base-line-and-end-line-evaluation-for-digital-literacy-project-in-4-states.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/project-accelerating-100-women-micro-entrepreneurs-of-northeastern-states.pdf</t>
         </is>
       </c>
     </row>
@@ -7992,21 +7389,21 @@
       <c r="B43" s="1" t="inlineStr"/>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>IP Selection - Scholarship Support to students from Economically Weaker Section pursuing higher education in STEM courses - Click here</t>
+          <t>Agency for Developing Training Modules and Conducting Training of Trainers (ToT) for MSMEs on IPR and Financial Management - Click here</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
       <c r="E43" s="2" t="inlineStr"/>
       <c r="F43" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G43" s="1" t="inlineStr"/>
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/scholarship-support-for-economically-weaker-section-students-in-stem-higher-education.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/agency-for-developing-training-modules-and-conducting-ToT-for-MSMEs-on-IPR-and-financial-management.pdf</t>
         </is>
       </c>
     </row>
@@ -8019,7 +7416,7 @@
       <c r="B44" s="1" t="inlineStr"/>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>Digital Upskilling of Farmer Producer Organizations (FPOs) through Technology - Click here</t>
+          <t>RFP for WISE - Women in Innovation, Skills &amp; Entrepreneurship - Click here</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
@@ -8033,7 +7430,7 @@
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/baseline-endline-study-digital-upskilling-fpos-technology.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/women-in-Innovation-skills-and-entrepreneurship.pdf</t>
         </is>
       </c>
     </row>
@@ -8046,7 +7443,7 @@
       <c r="B45" s="1" t="inlineStr"/>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>Project - Accelerating 100 Women Micro Entrepreneurs of Northeastern States - Click here</t>
+          <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - English  - Click here</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
@@ -8060,7 +7457,7 @@
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/project-accelerating-100-women-micro-entrepreneurs-of-northeastern-states.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-English.pdf</t>
         </is>
       </c>
     </row>
@@ -8073,21 +7470,21 @@
       <c r="B46" s="1" t="inlineStr"/>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>Agency for Developing Training Modules and Conducting Training of Trainers (ToT) for MSMEs on IPR and Financial Management - Click here</t>
+          <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - Kannada - Click here</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G46" s="1" t="inlineStr"/>
       <c r="H46" s="1" t="inlineStr"/>
       <c r="I46" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/agency-for-developing-training-modules-and-conducting-ToT-for-MSMEs-on-IPR-and-financial-management.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-Kannada.pdf</t>
         </is>
       </c>
     </row>
@@ -8100,7 +7497,7 @@
       <c r="B47" s="1" t="inlineStr"/>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>RFP for WISE - Women in Innovation, Skills &amp; Entrepreneurship - Click here</t>
+          <t>RFP - Trainer for Nano Women Entrepreneurs in Karnataka - Click here</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
@@ -8114,7 +7511,7 @@
       <c r="H47" s="1" t="inlineStr"/>
       <c r="I47" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/women-in-Innovation-skills-and-entrepreneurship.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/trainer-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
         </is>
       </c>
     </row>
@@ -8127,7 +7524,7 @@
       <c r="B48" s="1" t="inlineStr"/>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - English  - Click here</t>
+          <t>RFP - Training Agency with Content and Trainers for Nano Women Entrepreneurs in Karnataka - Click here</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
@@ -8141,7 +7538,7 @@
       <c r="H48" s="1" t="inlineStr"/>
       <c r="I48" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-English.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/training-agency-with-content-and-trainers-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
         </is>
       </c>
     </row>
@@ -8154,21 +7551,21 @@
       <c r="B49" s="1" t="inlineStr"/>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - Kannada - Click here</t>
+          <t>Access to E-Governance and Livelihood in PVTG Communities in Aspirational Blocks - Click here</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
       <c r="E49" s="2" t="inlineStr"/>
       <c r="F49" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G49" s="1" t="inlineStr"/>
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-Kannada.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/access-to-e-governance-and-livelihood-in-pvtg-communities-in-aspirational-blocks.pdf</t>
         </is>
       </c>
     </row>
@@ -8181,7 +7578,7 @@
       <c r="B50" s="1" t="inlineStr"/>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>RFP - Trainer for Nano Women Entrepreneurs in Karnataka - Click here</t>
+          <t>thingQbator Portal Enhancement and Maintenance Proposal - Click here</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
@@ -8195,74 +7592,94 @@
       <c r="H50" s="1" t="inlineStr"/>
       <c r="I50" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/trainer-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/thingQbator-portal-enhancement-and-maintenance-proposal.pdf</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B51" s="1" t="inlineStr"/>
+          <t>HCL Foundation</t>
+        </is>
+      </c>
+      <c r="B51" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>RFP - Training Agency with Content and Trainers for Nano Women Entrepreneurs in Karnataka - Click here</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards Biodiversity monitoring for Pan-India Afforestation sites</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
       <c r="E51" s="2" t="inlineStr"/>
       <c r="F51" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G51" s="1" t="inlineStr"/>
+          <t>Climate</t>
+        </is>
+      </c>
+      <c r="G51" s="1" t="inlineStr">
+        <is>
+          <t>10th Feb, 2026</t>
+        </is>
+      </c>
       <c r="H51" s="1" t="inlineStr"/>
       <c r="I51" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/training-agency-with-content-and-trainers-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Biodiversity%20monitoring%20for%20Pan-India%20Afforestation%20sites%202-DSB.pdf</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B52" s="1" t="inlineStr"/>
+          <t>HCL Foundation</t>
+        </is>
+      </c>
+      <c r="B52" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>Access to E-Governance and Livelihood in PVTG Communities in Aspirational Blocks - Click here</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards soil profiling and assessment from the restored and rejuvenated Harit sites.</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
       <c r="E52" s="2" t="inlineStr"/>
       <c r="F52" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G52" s="1" t="inlineStr"/>
+          <t>Climate</t>
+        </is>
+      </c>
+      <c r="G52" s="1" t="inlineStr">
+        <is>
+          <t>10th Feb, 2026</t>
+        </is>
+      </c>
       <c r="H52" s="1" t="inlineStr"/>
       <c r="I52" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/access-to-e-governance-and-livelihood-in-pvtg-communities-in-aspirational-blocks.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Soil%20assessment-v1%20RKS-DSB_0.pdf</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B53" s="1" t="inlineStr"/>
+          <t>HCL Foundation</t>
+        </is>
+      </c>
+      <c r="B53" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>thingQbator Portal Enhancement and Maintenance Proposal - Click here</t>
+          <t>HCLFoundation invites proposals from NGOs/CSR implementing agencies for ‘Operating a Social Enterprise Cafe” under the flagship urban development programme - Uday</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
@@ -8272,11 +7689,15 @@
           <t>Learning</t>
         </is>
       </c>
-      <c r="G53" s="1" t="inlineStr"/>
+      <c r="G53" s="1" t="inlineStr">
+        <is>
+          <t>15th Dec, 2025</t>
+        </is>
+      </c>
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/thingQbator-portal-enhancement-and-maintenance-proposal.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-11/RfP_Social%20Enterprise%20Cafe_UDAY.docx</t>
         </is>
       </c>
     </row>
@@ -8293,25 +7714,25 @@
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards Biodiversity monitoring for Pan-India Afforestation sites</t>
+          <t>Programme Officer/Senior Programme Officer – Environment Education</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
       <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="1" t="inlineStr">
         <is>
-          <t>Climate</t>
+          <t>Learning, Climate</t>
         </is>
       </c>
       <c r="G54" s="1" t="inlineStr">
         <is>
-          <t>10th Feb, 2026</t>
+          <t>10th Nov, 2025</t>
         </is>
       </c>
       <c r="H54" s="1" t="inlineStr"/>
       <c r="I54" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Biodiversity%20monitoring%20for%20Pan-India%20Afforestation%20sites%202-DSB.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-10/Harit_POSPO_EEA_Multilocation_Oct%202025.pdf</t>
         </is>
       </c>
     </row>
@@ -8328,25 +7749,25 @@
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards soil profiling and assessment from the restored and rejuvenated Harit sites.</t>
+          <t>HCLFoundation invites applications for the PO/SPO position under its flagship programme Harit by HCLFoundation</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr"/>
       <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="1" t="inlineStr">
         <is>
-          <t>Climate</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G55" s="1" t="inlineStr">
         <is>
-          <t>10th Feb, 2026</t>
+          <t>31st Oct, 2025</t>
         </is>
       </c>
       <c r="H55" s="1" t="inlineStr"/>
       <c r="I55" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Soil%20assessment-v1%20RKS-DSB_0.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-10/JD_Water%20Conservation_SPO%20V4.pdf</t>
         </is>
       </c>
     </row>
@@ -8363,25 +7784,25 @@
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites proposals from NGOs/CSR implementing agencies for ‘Operating a Social Enterprise Cafe” under the flagship urban development programme - Uday</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit by HCLFoundation, invites RFP from NGOs / CSR organizations working in Water Conservation for the development of Water Structures etc.</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Learning, Climate</t>
         </is>
       </c>
       <c r="G56" s="1" t="inlineStr">
         <is>
-          <t>15th Dec, 2025</t>
+          <t>21st May, 2025</t>
         </is>
       </c>
       <c r="H56" s="1" t="inlineStr"/>
       <c r="I56" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-11/RfP_Social%20Enterprise%20Cafe_UDAY.docx</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/Final_RFP%20for%20water%20structure%20rejuvenation%20.docx</t>
         </is>
       </c>
     </row>
@@ -8398,25 +7819,25 @@
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>Programme Officer/Senior Programme Officer – Environment Education</t>
+          <t>HCLFoundation invites technical application abstracts for the developing technology drive source code model mobile applications and web portals for addressing human-animal interactions under the Animal Welfare thematic of  Harit by HCLFoundation</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr"/>
       <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="1" t="inlineStr">
         <is>
-          <t>Learning, Climate</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G57" s="1" t="inlineStr">
         <is>
-          <t>10th Nov, 2025</t>
+          <t>15th May, 2025</t>
         </is>
       </c>
       <c r="H57" s="1" t="inlineStr"/>
       <c r="I57" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-10/Harit_POSPO_EEA_Multilocation_Oct%202025.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_AW%20Tech%20Based%20Source%20Code%20Model_V1%20%281%29.docx</t>
         </is>
       </c>
     </row>
@@ -8433,25 +7854,25 @@
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites applications for the PO/SPO position under its flagship programme Harit by HCLFoundation</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit invites RFP from NGOs/CSR organizations working in the field of environment for project on the restoration of various degraded and natural habitats</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr"/>
       <c r="E58" s="2" t="inlineStr"/>
       <c r="F58" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Climate</t>
         </is>
       </c>
       <c r="G58" s="1" t="inlineStr">
         <is>
-          <t>31st Oct, 2025</t>
+          <t>15th May, 2025</t>
         </is>
       </c>
       <c r="H58" s="1" t="inlineStr"/>
       <c r="I58" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-10/JD_Water%20Conservation_SPO%20V4.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/Harit_A%20HR_RFP%20.docx</t>
         </is>
       </c>
     </row>
@@ -8468,25 +7889,25 @@
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit by HCLFoundation, invites RFP from NGOs / CSR organizations working in Water Conservation for the development of Water Structures etc.</t>
+          <t>HCLFoundation invites EOI for conducting holistic and comprehensive Impact Assessments of environmental projects supported under Harit by HCLFoundation</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr"/>
       <c r="E59" s="2" t="inlineStr"/>
       <c r="F59" s="1" t="inlineStr">
         <is>
-          <t>Learning, Climate</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G59" s="1" t="inlineStr">
         <is>
-          <t>21st May, 2025</t>
+          <t>15th May, 2025</t>
         </is>
       </c>
       <c r="H59" s="1" t="inlineStr"/>
       <c r="I59" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/Final_RFP%20for%20water%20structure%20rejuvenation%20.docx</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_Harit%20Impact%20Assessments.docx</t>
         </is>
       </c>
     </row>
@@ -8503,14 +7924,14 @@
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites technical application abstracts for the developing technology drive source code model mobile applications and web portals for addressing human-animal interactions under the Animal Welfare thematic of  Harit by HCLFoundation</t>
+          <t>HCLFoundation invites technical application abstracts for the conducting technical and highly engaging environment awareness and sustainability workshops under Harit by HCLFoundation</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr"/>
       <c r="E60" s="2" t="inlineStr"/>
       <c r="F60" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Climate</t>
         </is>
       </c>
       <c r="G60" s="1" t="inlineStr">
@@ -8521,652 +7942,7 @@
       <c r="H60" s="1" t="inlineStr"/>
       <c r="I60" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_AW%20Tech%20Based%20Source%20Code%20Model_V1%20%281%29.docx</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="1" t="inlineStr">
-        <is>
-          <t>HCL Foundation</t>
-        </is>
-      </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit invites RFP from NGOs/CSR organizations working in the field of environment for project on the restoration of various degraded and natural habitats</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr"/>
-      <c r="E61" s="2" t="inlineStr"/>
-      <c r="F61" s="1" t="inlineStr">
-        <is>
-          <t>Climate</t>
-        </is>
-      </c>
-      <c r="G61" s="1" t="inlineStr">
-        <is>
-          <t>15th May, 2025</t>
-        </is>
-      </c>
-      <c r="H61" s="1" t="inlineStr"/>
-      <c r="I61" s="1" t="inlineStr">
-        <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/Harit_A%20HR_RFP%20.docx</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="1" t="inlineStr">
-        <is>
-          <t>HCL Foundation</t>
-        </is>
-      </c>
-      <c r="B62" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C62" s="1" t="inlineStr">
-        <is>
-          <t>HCLFoundation invites EOI for conducting holistic and comprehensive Impact Assessments of environmental projects supported under Harit by HCLFoundation</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr"/>
-      <c r="E62" s="2" t="inlineStr"/>
-      <c r="F62" s="1" t="inlineStr">
-        <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G62" s="1" t="inlineStr">
-        <is>
-          <t>15th May, 2025</t>
-        </is>
-      </c>
-      <c r="H62" s="1" t="inlineStr"/>
-      <c r="I62" s="1" t="inlineStr">
-        <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_Harit%20Impact%20Assessments.docx</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="1" t="inlineStr">
-        <is>
-          <t>HCL Foundation</t>
-        </is>
-      </c>
-      <c r="B63" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C63" s="1" t="inlineStr">
-        <is>
-          <t>HCLFoundation invites technical application abstracts for the conducting technical and highly engaging environment awareness and sustainability workshops under Harit by HCLFoundation</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr"/>
-      <c r="E63" s="2" t="inlineStr"/>
-      <c r="F63" s="1" t="inlineStr">
-        <is>
-          <t>Climate</t>
-        </is>
-      </c>
-      <c r="G63" s="1" t="inlineStr">
-        <is>
-          <t>15th May, 2025</t>
-        </is>
-      </c>
-      <c r="H63" s="1" t="inlineStr"/>
-      <c r="I63" s="1" t="inlineStr">
-        <is>
           <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_EEA_Env%20%20Sus%20awareness%20workshops_FY%2025-26%20%281%29.docx</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>Quotation_for_Rate_Contrac_Vehicle_Hiring_for_NCR_or_Outstation..pdf</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr"/>
-      <c r="E64" s="2" t="inlineStr"/>
-      <c r="F64" s="1" t="inlineStr"/>
-      <c r="G64" s="1" t="inlineStr"/>
-      <c r="H64" s="1" t="inlineStr"/>
-      <c r="I64" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/Quotation_for_Rate_Contrac_Vehicle_Hiring_for_NCR_or_Outstation..pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>Final_RfP_UrbanShift_Preparation_of_Integrated_Green_Mobility_Plan_for_Pune.pdf</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr"/>
-      <c r="E65" s="2" t="inlineStr"/>
-      <c r="F65" s="1" t="inlineStr"/>
-      <c r="G65" s="1" t="inlineStr"/>
-      <c r="H65" s="1" t="inlineStr"/>
-      <c r="I65" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/Final_RfP_UrbanShift_Preparation_of_Integrated_Green_Mobility_Plan_for_Pune.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>RfP_IGMP_Response to Pre-Bid Queries_200226.pdf</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr"/>
-      <c r="E66" s="2" t="inlineStr"/>
-      <c r="F66" s="1" t="inlineStr"/>
-      <c r="G66" s="1" t="inlineStr"/>
-      <c r="H66" s="1" t="inlineStr"/>
-      <c r="I66" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/RfP_IGMP_Response%20to%20Pre-Bid%20Queries_200226.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>Corrigendum_1_RfP_IGMP.pdf</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr"/>
-      <c r="E67" s="2" t="inlineStr"/>
-      <c r="F67" s="1" t="inlineStr"/>
-      <c r="G67" s="1" t="inlineStr"/>
-      <c r="H67" s="1" t="inlineStr"/>
-      <c r="I67" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/Corrigendum_1_RfP_IGMP.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C68" s="1" t="inlineStr">
-        <is>
-          <t>Corrigendum 2_IGMP.pdf</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr"/>
-      <c r="E68" s="2" t="inlineStr"/>
-      <c r="F68" s="1" t="inlineStr"/>
-      <c r="G68" s="1" t="inlineStr"/>
-      <c r="H68" s="1" t="inlineStr"/>
-      <c r="I68" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/Corrigendum%202_IGMP.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>RFP_Engagement of GIS Expert_SCBP_2026.pdf</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr"/>
-      <c r="E69" s="2" t="inlineStr"/>
-      <c r="F69" s="1" t="inlineStr"/>
-      <c r="G69" s="1" t="inlineStr"/>
-      <c r="H69" s="1" t="inlineStr"/>
-      <c r="I69" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/RFP_Engagement%20of%20GIS%20Expert_SCBP_2026.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>Response_to_Queries_Engagement_of_GIS_Expert_Agency.pdf</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr"/>
-      <c r="E70" s="2" t="inlineStr"/>
-      <c r="F70" s="1" t="inlineStr"/>
-      <c r="G70" s="1" t="inlineStr"/>
-      <c r="H70" s="1" t="inlineStr"/>
-      <c r="I70" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/Response_to_Queries_Engagement_of_GIS_Expert_Agency.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>RfP_SRTW.pdf</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr"/>
-      <c r="E71" s="2" t="inlineStr"/>
-      <c r="F71" s="1" t="inlineStr"/>
-      <c r="G71" s="1" t="inlineStr"/>
-      <c r="H71" s="1" t="inlineStr"/>
-      <c r="I71" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/RfP_SRTW.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>Response to Pre-Bid Queries_SRTW_for Uploading.pdf</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr"/>
-      <c r="E72" s="2" t="inlineStr"/>
-      <c r="F72" s="1" t="inlineStr"/>
-      <c r="G72" s="1" t="inlineStr"/>
-      <c r="H72" s="1" t="inlineStr"/>
-      <c r="I72" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/Response%20to%20Pre-Bid%20Queries_SRTW_for%20Uploading.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>EOI_TECHNICAL_ASSISTANCE_UNDER_CITIIS_2.0_PROGRAM_DOMESTIC_POOL_OF_EXPERTS.pdf</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr"/>
-      <c r="E73" s="2" t="inlineStr"/>
-      <c r="F73" s="1" t="inlineStr"/>
-      <c r="G73" s="1" t="inlineStr"/>
-      <c r="H73" s="1" t="inlineStr"/>
-      <c r="I73" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/EOI_TECHNICAL_ASSISTANCE_UNDER_CITIIS_2.0_PROGRAM_DOMESTIC_POOL_OF_EXPERTS.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>Reply to Pre- Bid Queries - EOI for DE's under CITIIS 2.0.pdf</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr"/>
-      <c r="E74" s="2" t="inlineStr"/>
-      <c r="F74" s="1" t="inlineStr"/>
-      <c r="G74" s="1" t="inlineStr"/>
-      <c r="H74" s="1" t="inlineStr"/>
-      <c r="I74" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/Reply%20to%20Pre-%20Bid%20Queries%20-%20EOI%20for%20DE%27s%20under%20CITIIS%202.0.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>GeM-Bidding-8666471.pdf</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr"/>
-      <c r="E75" s="2" t="inlineStr"/>
-      <c r="F75" s="1" t="inlineStr"/>
-      <c r="G75" s="1" t="inlineStr"/>
-      <c r="H75" s="1" t="inlineStr"/>
-      <c r="I75" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-8666471.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B76" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C76" s="1" t="inlineStr">
-        <is>
-          <t>corgaudt1.pdf</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr"/>
-      <c r="E76" s="2" t="inlineStr"/>
-      <c r="F76" s="1" t="inlineStr"/>
-      <c r="G76" s="1" t="inlineStr"/>
-      <c r="H76" s="1" t="inlineStr"/>
-      <c r="I76" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/corgaudt1.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>Corrigendum6959493.pdf</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr"/>
-      <c r="E77" s="2" t="inlineStr"/>
-      <c r="F77" s="1" t="inlineStr"/>
-      <c r="G77" s="1" t="inlineStr"/>
-      <c r="H77" s="1" t="inlineStr"/>
-      <c r="I77" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/Corrigendum6959493.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>ADDENDUM6959493.pdf</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr"/>
-      <c r="E78" s="2" t="inlineStr"/>
-      <c r="F78" s="1" t="inlineStr"/>
-      <c r="G78" s="1" t="inlineStr"/>
-      <c r="H78" s="1" t="inlineStr"/>
-      <c r="I78" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/ADDENDUM6959493.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>RfP CJ&amp;IP Package 03_UrbanShift.pdf</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr"/>
-      <c r="E79" s="2" t="inlineStr"/>
-      <c r="F79" s="1" t="inlineStr"/>
-      <c r="G79" s="1" t="inlineStr"/>
-      <c r="H79" s="1" t="inlineStr"/>
-      <c r="I79" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/RfP%20CJ%26IP%20Package%2003_UrbanShift.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>Prebid reply Cj&amp;IP package 3_18.12.2025.pdf</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr"/>
-      <c r="E80" s="2" t="inlineStr"/>
-      <c r="F80" s="1" t="inlineStr"/>
-      <c r="G80" s="1" t="inlineStr"/>
-      <c r="H80" s="1" t="inlineStr"/>
-      <c r="I80" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/Prebid%20reply%20Cj%26IP%20package%203_18.12.2025.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>GeM-Bidding-8478801.pdf</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr"/>
-      <c r="E81" s="2" t="inlineStr"/>
-      <c r="F81" s="1" t="inlineStr"/>
-      <c r="G81" s="1" t="inlineStr"/>
-      <c r="H81" s="1" t="inlineStr"/>
-      <c r="I81" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-8478801.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>GeM-Bidding-8476974.pdf</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr"/>
-      <c r="E82" s="2" t="inlineStr"/>
-      <c r="F82" s="1" t="inlineStr"/>
-      <c r="G82" s="1" t="inlineStr"/>
-      <c r="H82" s="1" t="inlineStr"/>
-      <c r="I82" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-8476974.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>GeM-Bidding-8497150.pdf</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr"/>
-      <c r="E83" s="2" t="inlineStr"/>
-      <c r="F83" s="1" t="inlineStr"/>
-      <c r="G83" s="1" t="inlineStr"/>
-      <c r="H83" s="1" t="inlineStr"/>
-      <c r="I83" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-8497150.pdf</t>
         </is>
       </c>
     </row>

--- a/all_grants.xlsx
+++ b/all_grants.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -489,1540 +489,17 @@
       <c r="B2" s="1" t="inlineStr"/>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>RFQ - for the Supply of Seeds</t>
+          <t>EoI - For Empanelment of agencies for Impact Assessment/ Evaluation Servic...</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>MAMTA Health Institute for Mother and Child (MAMTA) | India
-International Development - RFQ -  for the Supply of Seeds, MAMTA Health Institute for Mother and Child (MAMTA), India - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Event ... Read More</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>• The terms and conditions for the purchase of seed:
-Provide seed percentage certificate of all Germination
-The seed must be supplied within 20 days from the date of order placement. Prices should be inclusive of GST and transportation charges.
-Seeds must be resistant to downy and powdery mildew.
-In case seeds fafulfillfulfil the supplier of the above-prescribed standard must guarantee the replacement of seeds.
-Genetic purity should not be less than 90%
-Germination (minimum): 85%
-Inert matter (maximum): 3%
-Weed seed (max.) = 20 no./kg
-Other crops seed (max.) = 20 no./ kg
-Packed: within 6 months
-Validity: at least 12 months
-Tax deductions will be done as per the relevant rules of the Government of India.
-Share the quotation on letterhead
-inclusive of GST (Otherwise the quotation will not be considered).
-Others
-MAMTA HIMC reserves the right to reject all or any quotation(s), wholly or partly, without assigning any reason whatsoever.
-MAMTA HIMC team reserves the right to request the top 3 quotations for an in-person discussion.
-MAMTA reserves the right, in its sole discretion, to conduct negotiations in accordance with MAMTA and/donor’s policies and procedures and to request additional information from prospective Bidders to supplement or clarify any aspect of the proposal documents if such revisions will be in the interest of our programs
-Only shortlisted agencies will be contacted.
-You must pay all sub-vendor payments before submitting the hard copy of the final bills and supporting documents to MAMTA HIMC.
-MAMTA shall not be legally bound by any award notice issued for this RFQ until an Agreement is duly signed and executed with the winning bidder(s).
-Further details will be shared with shortlisted agencies.
-Application Process –
-All applicants (company/agency/institutional) if applicable, should follow the Government of India guidelines/policy for the Prevention of Sexual Harassment (PoSH) at the workplace. As part of the application process, you are required to share the status of the Internal Complaints Committee (ICC). If the committee is not incorporated, then under what criteria is it not enacted?
-Interested agencies/organizations/individuals must submit the proposal for the
-Seeds
-highlighting the process, portfolio of past work, financial proposal and the timeline for the project. The technical and financial quotations should be sent in soft copy over email at
-rfp@mamtahimc.in
-by
-5
-th
-March 2026 With the subject line: “Quotation for Supply of Certified Seasonal Vegetable Seeds”. The
-• quotations should be made separately for the event and states. We encourage local vendors to apply. Incomplete applications and applications received after the deadline will not be considered for the selection process.
-The selection team will only contact applicants who have been shortlisted for the process.
-• Mamta HIMC has a policy of erasing all confidential information, ideas/concepts submitted in proposals/applications after the selection process is completed.
-"Confidentiality of Applicants"
-Mamta shall not be liable to share the list of shortlisted applicants with any party outside the organization. The organization takes all necessary measures to protect the confidentiality of applicants, and shall not disclose any personal information, process, and data related to the application, except as required by law.
-• Job Email ID:
-rfp(at)mamtahimc.in
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-05 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-Computer Science Trainer (School)
-Raspberry Pi Foundation
-Location:
-Telangana
-Apply by:
-04 Apr 2026
-Computer Science Trainer (College)
-Raspberry Pi Foundation
-Location:
-Telangana
-Apply by:
-04 Apr 2026
-Nursing Aid
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Driver
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Medical Officer
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Nurse
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Physiotherapist
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Project Coordinator
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>05-03-2026</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287641</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr"/>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>RFQ - for Report Designing</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>MAMTA Health Institute for Mother and Child (MAMTA) | India
-International Development - RFQ - for Report Designing, MAMTA Health Institute for Mother and Child (MAMTA), India - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jo ... Read More</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>• Scope of Work
-This is to bring to your kind attention that we want to hire an agency to design Report the total no. of pages in the report are 300 maximum (including cover page and back cover) and document size are A4. The topic of report would be on maternal health, environment, community health, etc.
-The Terms of Reference are as follows:
-Kindly provide the quotations for each of the above items separately, including GST by 5th March 2026.
-Kindly provide separate quotations for report design per page.
-Work must be completed in 2 months from the date of this order accepted by the vendor.
-MAMTA will pay the amounts to the vendor after verification application files by MAMTA and submission of the original invoice.
-The taxes will be deducted as per the relevant rules of the Govt. of India.
-Others
-MAMTA HIMC reserves the right to reject all or any quotation(s), wholly or partly, without assigning any reason whatsoever.
-MAMTA HIMC team reserves the right to request the top 3 quotations for an in-person discussion.
-MAMTA reserves the right, in its sole discretion, to conduct negotiations in accordance with MAMTA and/donor’s policies and procedures and to request additional information from prospective Bidders to supplement or clarify any aspect of the proposal documents if such revisions will be in the interest of our programs
-Only shortlisted agencies will be contacted.
-You must pay all sub-vendor payments before submitting the hard copy of the final bills and supporting documents to MAMTA HIMC.
-MAMTA shall not be legally bound by any award notice issued for this RFQ until an Agreement is duly signed and executed with the winning bidder(s).
-Further details will be shared with shortlisted agencies.
-Application Process –
-All applicants (company/agency/institutional/individual) if applicable, should follow the Government of India guidelines/policy for the Prevention of Sexual Harassment (PoSH) at the workplace. As part of the application process, you are required to share the status of the Internal Complaints Committee (ICC). If the committee is not incorporated, then under what criteria is it not enacted?
-Interested agencies/organizations/individuals must submit the proposal for the
-report designing
-highlighting the process, portfolio of past work, financial proposal and the timeline for the project. The technical and financial quotations should be sent in soft copy over email at
-rfp@mamtahimc.in
-by
-5
-th
-March 2026 With the subject line: “Quotation for Report Designing”.
-• The quotations should be made separately for the event and states. We encourage local vendors to apply. Incomplete applications and applications received after the deadline will not be considered for the selection process.
-The selection team will only contact applicants who have been shortlisted for the process.
-• Mamta HIMC has a policy of erasing all confidential information, ideas/concepts submitted in proposals/applications after the selection process is completed.
-"Confidentiality of Applicants"
-Mamta shall not be liable to share the list of shortlisted applicants with any party outside the organization. The organization takes all necessary measures to protect the confidentiality of applicants, and shall not disclose any personal information, process, and data related to the application, except as required by law.
-• Job Email ID:
-rfp(at)mamtahimc.in
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-05 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-Computer Science Trainer (School)
-Raspberry Pi Foundation
-Location:
-Telangana
-Apply by:
-04 Apr 2026
-Computer Science Trainer (College)
-Raspberry Pi Foundation
-Location:
-Telangana
-Apply by:
-04 Apr 2026
-Nursing Aid
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Driver
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Medical Officer
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Nurse
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Physiotherapist
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Project Coordinator
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>05-03-2026</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287643</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr"/>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Hiring an Agency to Conduct Evidence Synthesis, Co-Design Key Interv...</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Project Concern International India (PCI India) | India
-International Development - RFP - Hiring an Agency to Conduct Evidence Synthesis, Co-Design Key Intervention Components, and Develop a Scalable and Operational Implementation, Project Concern International India (PCI India), India - DevNetJobs ... Read More</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>• Last   Date for Submission of bids
-05
-th
-March 2026
-Proposals   to be submitted at
-procdelhi@pciglobal.in
-Receipt of Proposals
-Technical and Financial   proposals should be submitted as separate attachments
-and to be submitted
-in a single email
-attachments.
-NOTE
-:
-(a) The agencies registered under the Societies/Trust/Foreign Contribution (Regulation) Act, 2010, are not required to submit applications. Proposals from these agencies will not be considered.
-For detailed information, please check the complete version of the RFP attached below.
-• Job Email ID:
-procdelhi(at)pciglobal.in
-Download Attachment:
-RFP-AGENCY TO CONDUCT EVIDENCE SYNTHESIS, CO-DESIGN KEY INTERVENTION ..........doc
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-05 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-Computer Science Trainer (School)
-Raspberry Pi Foundation
-Location:
-Telangana
-Apply by:
-04 Apr 2026
-Computer Science Trainer (College)
-Raspberry Pi Foundation
-Location:
-Telangana
-Apply by:
-04 Apr 2026
-Nursing Aid
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Driver
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Medical Officer
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Nurse
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Physiotherapist
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Project Coordinator
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>05-03-2026</t>
-        </is>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287312</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr"/>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Training of Volunteers &amp; Help Desk Operators</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Ghoghardiha Prakhand Swarajya Vikas Sangh (GPSVS) | Bihar, Jharkhand
-International Development - RFP - Training of Volunteers &amp; Help Desk Operators, Ghoghardiha Prakhand Swarajya Vikas Sangh (GPSVS), Bihar, Jharkhand - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast ... Read More</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>• 3. Scope of Work
-The selected agency/consultant will undertake the following:
-3.1 Training Needs Refinement &amp; Curriculum Design
-Review project documents, volunteer roles, and Help Desk functions in
-Bihar context
-.
-Finalise
-training framework, modules, session plans, and learning outcomes
-in consultation with
-GPSVS
-.
-Prepare
-bilingual training materials (Hindi &amp; English where required)
-.
-3.2 Multi-Phase Training Delivery
-The assignment will include
-three structured training phases
-:
-Phase 1 – Orientation &amp; Capacity Building Training
-Foundation-level training for selected volunteers and Help Desk Operators.
-Coverage of:
-government schemes and social protection,
-labour rights and safe migration,
-grievance redressal systems,
-documentation and facilitation processes,
-communication and community mobilisation skills.
-Phase 2 – Refresher Training
-Conducted after initial field implementation.
-Focus on:
-problem solving from real case experiences,
-strengthening facilitation quality and reporting,
-addressing field-level gaps,
-reinforcing convergence with departments and institutions in Bihar.
-Phase 3 – Final Training on Sustainability &amp; Institutionalisation
-Focus on
-long-term sustainability of volunteer and Help Desk systems
-.
-Coverage of:
-strengthening community ownership,
-institutional linkages and referral pathways,
-documentation, data use, and accountability,
-continuation of services beyond the project duration.
-3.3 Mentorship &amp; Handholding Support
-Provide
-structured post-training mentorship
-to volunteers and Help Desk Operators in Bihar.
-Support trainees in:
-resolving real beneficiary cases,
-improving documentation and reporting quality,
-strengthening Help Desk service delivery,
-ensuring sustained application of training learning.
-Submit
-mentorship progress notes and final mentorship report
-.
-3.4 Documentation &amp; Reporting
-The agency will submit:
-training reports with attendance, photographs, and session summaries,
-participant learning assessment results,
-mentorship documentation, and
-a
-final consolidated completion report
-with key learnings and recommendations for Bihar.
-4. Key Deliverables
-Inception note with
-training design, modules, and schedule
-Finalised
-training curriculum and materials
-Completion of:
-Orientation &amp; Capacity Building Training
-Refresher Training
-Final Sustainability Training
-Mentorship implementation and report
-Final
-training completion and learning report
-5. Duration of the Assignment
-Total expected duration:
-6–7 months
-, including:
-preparation and curriculum development,
-delivery of three training phases, and
-mentorship and reporting.
-6. Budget
-The
-budget for this assignment is INR 3,00,000 (Rupees Three Lakh only)
-, aligned with current market standards for professional
-training design, delivery, mentorship, and documentation
-.
-• 7. Eligibility Criteria
-Essential
-Demonstrated experience in
-capacity building, training delivery, or community institution strengthening
-.
-Similar assignments
-with NGOs, CSOs, government programmes, or development agencies.
-Expertise in:
-government schemes and entitlements,
-labour rights / migration, and
-community facilitation systems.
-Desirable
-Familiarity with
-Bihar socio-economic and migration context
-.
-Availability of
-qualified trainers and field mentors
-.
-• 8. Proposal Submission Requirements
-Technical Proposal
-Understanding of the assignment
-Proposed
-training methodology, phased plan, and timeline
-Team composition and trainer/mentor profiles
-Relevant past experience and sample work
-Financial Proposal
-Detailed
-cost breakup within INR 3,00,000
-Taxes clearly indicated
-Quotation validity of
-minimum 60 days
-• 9. Submission Details
-Submission Email:
-amangpsvs@gmail.com
-and
-aparna.lall@welthungerhilfe.de
-CC:
-gpsvsjp@gmail.com
-and
-renita.rajora@welthungerhilfe.de
-Subject Line:
-Application – Training of Volunteers &amp; Help Desk Operators (IND 1389 – Bihar)
-Deadline:
-5
-th
-March 2026
-Only
-shortlisted applicants
-will be contacted.
-• 10. Selection Process
-Proposals will be evaluated through a
-technical and financial assessment
-conducted by the
-procurement committee of GPSVS
-, in alignment with
-donor procurement guidelines
-.
-Shortlisted applicants may be invited for
-clarification or presentation
-prior to final selection.
-The decision of GPSVS will be
-final and binding
-.
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-05 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-Computer Science Trainer (School)
-Raspberry Pi Foundation
-Location:
-Telangana
-Apply by:
-04 Apr 2026
-Computer Science Trainer (College)
-Raspberry Pi Foundation
-Location:
-Telangana
-Apply by:
-04 Apr 2026
-Nursing Aid
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Driver
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Medical Officer
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Nurse
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Physiotherapist
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Project Coordinator
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G5" s="1" t="inlineStr">
-        <is>
-          <t>05-03-2026</t>
-        </is>
-      </c>
-      <c r="H5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287444</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr"/>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>Request for Quotation for Case Study</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Institute for Global Development (IGD) | Uttar Pradesh, Andhra Pradesh, Telangana, Karnataka
-International Development - Request for Quotation for Case Study, Institute for Global Development (IGD), Andhra Pradesh, Telangana, Karnataka - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value M ... Read More</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>• Scope of Work
-IGD invites quotations from qualified individuals or agencies to develop case studies documenting key program activities. The case studies will be developed focusing on some campaign components
-The selected individual/agency will be required to work across 8-9 districts, with case study selection across seven states/districts as follows:
-Three in Uttar Pradesh (Bahraich, Chandauli, and Gorakhpur)
-Two districts in Andhra Pradesh
-Two districts in Telangana
-Two districts in Karnataka
-The case studies will focus on documenting the activities listed above, highlighting implementation processes, key achievements, challenges, and best practices.
-Terms of Reference
-Develop
-4 case studies per Districts
-across each of the 8–9 selected districts.
-Quotations must include a
-breakdown of costs
-for each item (including food, transport, accommodation, and GST).
-The assignment must be
-completed within two months
-from the date of contract acceptance.
-Payment will be released
-upon submission of original documentation
-and
-invoice verification
-.
-Applicable
-tax deductions
-will be made in accordance with Government of India regulations.
-Others
-IGD reserves the right to reject all or any quotation(s), wholly or partly, without assigning any reason whatsoever.
-IGD team reserves the right to request the top 3 quotations for an in-person discussion.
-IGD reserves the right, in its sole discretion, to conduct negotiations in accordance with IGD and/donor’s policies and procedures and to request additional information from prospective Bidders to supplement or clarify any aspect of the proposal documents if such revisions will be in the interest of our programs
-Only shortlisted agencies will be contacted.
-IGD shall not be legally bound by any award notice issued for this RFQ until an Agreement is duly signed and executed with the winning bidder(s).
-Further details will be shared with shortlisted agencies.
-Application Process –
-All applicants (company/agency/institutional) if applicable, should follow the Government of India guidelines/policy for the Prevention of Sexual Harassment (PoSH) at the workplace. As part of the application process, you are required to share the status of the Internal Complaints Committee (ICC). If the committee is not incorporated, then under what criteria is it not enacted?
-Interested agencies/organizations/individuals must submit the proposal for the
-Case Study
-, highlighting the process, portfolio of past work, financial proposal and the timeline for the project. The technical and financial quotations should be sent in soft copy over email at
-jobs@igdindia.org
-by
-5
-th
-March 2026 with subject line “Quotation for
-Case Study
-Development for Campaign Activities
-”.
-• We encourage local vendors to apply. Incomplete applications and applications received after the deadline will not be considered for the selection process.
-The selection team will only contact applicants who have been shortlisted for the process.
-• IGD has a policy of erasing all confidential information, ideas/concepts submitted in proposals/applications after the selection process is completed.
-"Confidentiality of Applicants"
-IGD shall not be liable to share the list of shortlisted applicants with any party outside the organization. The organization takes all necessary measures to protect the confidentiality of applicants, and shall not disclose any personal information, process, and data related to the application, except as required by law.
-• Job Email ID:
-jobs(at)igdindia.org
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-05 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-Computer Science Trainer (School)
-Raspberry Pi Foundation
-Location:
-Telangana
-Apply by:
-04 Apr 2026
-Computer Science Trainer (College)
-Raspberry Pi Foundation
-Location:
-Telangana
-Apply by:
-04 Apr 2026
-Nursing Aid
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Driver
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Medical Officer
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Nurse
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Physiotherapist
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Project Coordinator
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G6" s="1" t="inlineStr">
-        <is>
-          <t>05-03-2026</t>
-        </is>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287670</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr"/>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>ToR - State And National Level Consolidation Study On Government Schemes, ...</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Life Education And Development Support (Leads) And Ghoghardiha Prakhand Swarajya Vikas Sangh (GPSVS) | Jharkhand, Bihar
-International Development - ToR - State And National Level Consolidation Study On Government Schemes, Labour Rights &amp; Grievance Mechanisms - Safe Employment Guidebooks..., Life Ed ... Read More</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>• 3. Scope of Work
-The consultant/agency will adopt a policy-research and systems-analysis approach encompassing the following components:
-3.1 State &amp; National Policy Mapping
-Review relevant government schemes, labour laws, operational guidelines, and institutional mandates.
-Conduct comparative analysis of state and national policy frameworks affecting migrant and unorganised workers.
-Map implementation pathways, departmental roles, and convergence structures.
-3.2 Access Pathway &amp; Exclusion Analysis
-• Examine eligibility criteria, documentation requirements, approval timelines, and rejection points.
-Identify systemic barriers affecting migrant access to entitlements and services.
-Analyse exclusion patterns linked to migration vulnerability and livelihood insecurity.
-3.3 Review of Grievance Redressal Mechanisms
-Map complaint systems, escalation hierarchies, and response timelines at state and national levels.
-Assess field-level effectiveness, accessibility, and usability.
-Identify gaps between policy provisions and implementation realities.
-3.4 Development of Safe Employment Guidebook
-Consolidate state and national provisions into structured, user-friendly knowledge.
-Develop two comprehensive Safe Employment Guidebooks (Hindi &amp; English) covering:
-safe migration processes and precautions,
-labour rights, entitlements, and protections,
-access to government schemes and grievance systems,
-contextual chapters on Jharkhand and Bihar.
-3.5 Validation and Finalisation
-Present draft outputs to LEADS, GPSVS, and WHH for technical review.
-Incorporate feedback and revisions.
-Submit final research report and two complete Safe Employment Guidebooks.
-4. Expected Deliverables
-Inception report with methodology and detailed work plan
-State and national policy mapping document
-Draft analytical research report
-Draft Safe Employment Guidebooks (Hindi &amp; English)
-Final Safe Employment Guidebooks in Hindi and English including Jharkhand &amp; Bihar chapters
-Final validated research report.
-5. Duration and Level of Effort
-The assignment is expected to be completed within 10 weeks from contract signing, with clearly defined review milestones and iterative consultation with programme stakeholders.
-6. Profile of the Consultant / Agency
-Essential
-Demonstrated experience in policy research, migration, labour rights, or social protection.
-Similar assignments with NGOs, CSOs, research institutions, or development agencies.
-Strong analytical writing, documentation, and publication development capacity.
-Desirable
-Experience with EU or internationally funded development programmes.
-Familiarity with migration contexts in Bihar, Jharkhand, or eastern India.
-Ability to produce high-quality bilingual (Hindi &amp; English) knowledge resources.
-7. Application Process
-Interested applicants should submit:
-Technical Proposal
-Understanding of the assignment
-Proposed methodology, timeline, and work plan
-Team composition and relevant experience
-Samples of previous research or publication work
-Financial Proposal
-Detailed professional fee structure
-Applicable taxes clearly indicated
-Validity of quotation (minimum 60 days)
-• 8. Submission Details
-Submission Email:
-amangpsvs@gmail.com
-,
-manishleadsjh@gmail.com
-and
-aparna.lall@welthungerhilfe.de
-CC:
-leadsindiajh@gmail.com
-;
-gpsvsjp@gmail.com
-; and
-renita.rajora@welthungerhilfe.de
-Subject
-: Application – State &amp; National Consolidation Study (IND 1389)
-Locations
-: Jharkhand: Khunti, Simdega, Ramgarh, Bihar: Madhubani, Supaul, Darbhanga
-Deadline
-: 5th March 2026
-9. Budget
-The budget for this assignment is INR 5,00,000 (Rupees Five Lakh only) inclusive all taxes.
-• 10. Selection Process
-Proposals will be assessed through a technical and financial evaluation process conducted by the procurement committee.
-Shortlisted applicants may be invited for clarification or presentation prior to final selection. The decision of the committee shall be final and binding.
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-05 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-Computer Science Trainer (School)
-Raspberry Pi Foundation
-Location:
-Telangana
-Apply by:
-04 Apr 2026
-Computer Science Trainer (College)
-Raspberry Pi Foundation
-Location:
-Telangana
-Apply by:
-04 Apr 2026
-Nursing Aid
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Driver
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Medical Officer
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Nurse
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Physiotherapist
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Project Coordinator
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>Governance, Learning</t>
-        </is>
-      </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>05-03-2026</t>
-        </is>
-      </c>
-      <c r="H7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287504</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="inlineStr"/>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>EoI - For Empanelment of agencies for Impact Assessment/ Evaluation Servic...</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Small Industries Development Bank of India (SIDBI) | India
 International Development - EoI - For Empanelment of agencies for Impact Assessment/ Evaluation Services under Programmes for Development and Impact, Small Industries Development Bank of India (SIDBI), India - DevNetJobsIndia.org
 Jobseekers ... Read More</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>• Please      note that all the information required as per the documents required for      responding to EOI needs to be provided. Incomplete information in these      areas may lead to non-selection.
 Modification      And/ Or Withdrawal of documents:
@@ -2095,6 +572,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
 Lead-Finance &amp; Compliance
 Marathwada Navnirman Lokayat (Manavlok)
 Location:
@@ -2149,62 +632,56 @@
 Bihar
 Apply by:
 11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Computer Science Trainer (School)
-Raspberry Pi Foundation
+Design and Readiness Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Program Manager – AI Skilling Initiative
+SwaTaleem Foundation
+Location:
+Haryana
+Apply by:
+05 Apr 2026
+Communications Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Director of International Programmes Impact And P...
+Confidential
 Location:
 Telangana
 Apply by:
+08 Apr 2026
+Organizational Development (OD) Manager
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Manager – Monitoring &amp; Evaluation
+Family Planning Association of India (FPA India)
+Location:
+Maharashtra
+Apply by:
 04 Apr 2026
-Computer Science Trainer (College)
-Raspberry Pi Foundation
-Location:
-Telangana
-Apply by:
-04 Apr 2026
-Nursing Aid
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Driver
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Medical Officer
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Nurse
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Physiotherapist
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Project Coordinator
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
+Officer – Instructional Design and Technical Supp...
+Room to Read India
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+RFP UNW-IND-2026-00002 for Hiring resource agency...
+UN Women
+Location:
+India
+Apply by:
+23 Mar 2026
 Jobseekers
 Register
 Login
@@ -2232,38 +709,456 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F8" s="1" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>Governance, Learning</t>
         </is>
       </c>
-      <c r="G8" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>06-03-2026</t>
         </is>
       </c>
-      <c r="H8" s="1" t="n">
+      <c r="H2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287084</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr"/>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>RFP- #2026-IN-01- Agency for economic Impact Analysis</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>PATH | Delhi
+International Development - RFP- #2026-IN-01- Agency for economic Impact Analysis, PATH, Delhi - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers:
+Login
+|
+Register
+Jobseekers Login
+Jobseekers Register
+Job ... Read More</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>• Job Email ID:
+rfpindia(at)path.org
+Download Attachment:
+Request for Proposal - RFP#2026-IN-01- Agency for economic Impact Analysis.doc
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+07 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Associate (Programme Management)
+Indian Institute For Human Settlements (Iihs)
+Location:
+Karnataka
+Apply by:
+07 Mar 2026
+Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+Design and Readiness Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Program Manager – AI Skilling Initiative
+SwaTaleem Foundation
+Location:
+Haryana
+Apply by:
+05 Apr 2026
+Communications Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Director of International Programmes Impact And P...
+Confidential
+Location:
+Telangana
+Apply by:
+08 Apr 2026
+Organizational Development (OD) Manager
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Manager – Monitoring &amp; Evaluation
+Family Planning Association of India (FPA India)
+Location:
+Maharashtra
+Apply by:
+04 Apr 2026
+Officer – Instructional Design and Technical Supp...
+Room to Read India
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+RFP UNW-IND-2026-00002 for Hiring resource agency...
+UN Women
+Location:
+India
+Apply by:
+23 Mar 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>07-03-2026</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287084</t>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287460</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr"/>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr"/>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Associate (Programme Management)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Indian Institute For Human Settlements (Iihs) | Karnataka
+International Development - Associate (Programme Management), Indian Institute For Human Settlements (Iihs), Karnataka - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events ... Read More</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>• IIHS is an equal opportunity employer that encourages women, people with disabilities and those from economically and socially excluded communities with the requisite skills and qualifications to apply for positions.
+• To apply
+If you are interested in exploring this opportunity with us, please fill the online
+application form
+by clicking here. (You can also click on the “
+Apply Now
+” button at the end of the Job Description displayed on the website).
+Contact
+Please write to us at
+hr@iihs.co.in
+if you need any clarifications while filling the online application form.
+• Job Email ID:
+hr(at)iihs.co.in
+Download Attachment:
+Associate-Programme-Management-–-ASSURE-Lighthouse-Projects.pdf
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+07 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Associate (Programme Management)
+Indian Institute For Human Settlements (Iihs)
+Location:
+Karnataka
+Apply by:
+07 Mar 2026
+Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+Design and Readiness Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Program Manager – AI Skilling Initiative
+SwaTaleem Foundation
+Location:
+Haryana
+Apply by:
+05 Apr 2026
+Communications Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Director of International Programmes Impact And P...
+Confidential
+Location:
+Telangana
+Apply by:
+08 Apr 2026
+Organizational Development (OD) Manager
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Manager – Monitoring &amp; Evaluation
+Family Planning Association of India (FPA India)
+Location:
+Maharashtra
+Apply by:
+04 Apr 2026
+Officer – Instructional Design and Technical Supp...
+Room to Read India
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+RFP UNW-IND-2026-00002 for Hiring resource agency...
+UN Women
+Location:
+India
+Apply by:
+23 Mar 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>07-03-2026</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=285747</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr"/>
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>RFP - Onboarding Agency for Revamping Assam LMIS Dashboard</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>PATH | Assam
 International Development - RFP - Onboarding Agency for Revamping Assam LMIS Dashboard, PATH, Assam - DevNetJobsIndia.org
@@ -2285,7 +1180,7 @@
 Jobseekers Registe ... Read More</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>• 3.2. Commercial contracting terms and conditions will be negotiated with the successful supplier at the end of the selection process.
 3.3. By submitting a proposal, the supplier confirms their agreement to abide by the RFP terms and PATH policies, including the
@@ -2378,6 +1273,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
 Lead-Finance &amp; Compliance
 Marathwada Navnirman Lokayat (Manavlok)
 Location:
@@ -2432,62 +1333,56 @@
 Bihar
 Apply by:
 11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Computer Science Trainer (School)
-Raspberry Pi Foundation
+Design and Readiness Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Program Manager – AI Skilling Initiative
+SwaTaleem Foundation
+Location:
+Haryana
+Apply by:
+05 Apr 2026
+Communications Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Director of International Programmes Impact And P...
+Confidential
 Location:
 Telangana
 Apply by:
+08 Apr 2026
+Organizational Development (OD) Manager
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Manager – Monitoring &amp; Evaluation
+Family Planning Association of India (FPA India)
+Location:
+Maharashtra
+Apply by:
 04 Apr 2026
-Computer Science Trainer (College)
-Raspberry Pi Foundation
-Location:
-Telangana
-Apply by:
-04 Apr 2026
-Nursing Aid
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Driver
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Medical Officer
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Nurse
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Physiotherapist
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Project Coordinator
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
+Officer – Instructional Design and Technical Supp...
+Room to Read India
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+RFP UNW-IND-2026-00002 for Hiring resource agency...
+UN Women
+Location:
+India
+Apply by:
+23 Mar 2026
 Jobseekers
 Register
 Login
@@ -2515,41 +1410,41 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F9" s="1" t="inlineStr">
+      <c r="F5" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G9" s="1" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>07-03-2026</t>
         </is>
       </c>
-      <c r="H9" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" s="1" t="inlineStr">
+      <c r="H5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287335</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr"/>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>RFP- #2026-IN-01- Agency for economic Impact Analysis</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>PATH | Delhi
-International Development - RFP- #2026-IN-01- Agency for economic Impact Analysis, PATH, Delhi - DevNetJobsIndia.org
+      <c r="B6" s="1" t="inlineStr"/>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>RFQ: Construction of New gated check dams, De-siltation, and retrofitting ...</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>WaterAid India | Telangana
+International Development - RFQ: Construction of New gated check dams, De-siltation, and retrofitting of check dam in 6 villages, WaterAid India, Telangana - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
@@ -2559,32 +1454,31 @@
 Broadcast Resume
 RFPs/Tenders
 Search Jobs
-Events
-Jobseekers:
-Login
-|
-Register
-Jobseekers Login
-Jobseekers Register
-Job ... Read More</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+E ... Read More</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>• Job Email ID:
-rfpindia(at)path.org
+WAIProcurementAP(at)wateraid.org
 Download Attachment:
-Request for Proposal - RFP#2026-IN-01- Agency for economic Impact Analysis.doc
+Tender Notice-15 check dams-Jalsankalp-19.02.26_compressed.pdf
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
 Apply by:
-07 Mar 2026
+08 Mar 2026
 Access all the jobs and get ahead!
 Subscribe to Value Membership Now!
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
 Lead-Finance &amp; Compliance
 Marathwada Navnirman Lokayat (Manavlok)
 Location:
@@ -2639,62 +1533,56 @@
 Bihar
 Apply by:
 11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Computer Science Trainer (School)
-Raspberry Pi Foundation
+Design and Readiness Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Program Manager – AI Skilling Initiative
+SwaTaleem Foundation
+Location:
+Haryana
+Apply by:
+05 Apr 2026
+Communications Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Director of International Programmes Impact And P...
+Confidential
 Location:
 Telangana
 Apply by:
+08 Apr 2026
+Organizational Development (OD) Manager
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Manager – Monitoring &amp; Evaluation
+Family Planning Association of India (FPA India)
+Location:
+Maharashtra
+Apply by:
 04 Apr 2026
-Computer Science Trainer (College)
-Raspberry Pi Foundation
-Location:
-Telangana
-Apply by:
-04 Apr 2026
-Nursing Aid
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Driver
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Medical Officer
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Nurse
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Physiotherapist
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Project Coordinator
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
+Officer – Instructional Design and Technical Supp...
+Room to Read India
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+RFP UNW-IND-2026-00002 for Hiring resource agency...
+UN Women
+Location:
+India
+Apply by:
+23 Mar 2026
 Jobseekers
 Register
 Login
@@ -2722,249 +1610,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G10" s="1" t="inlineStr">
-        <is>
-          <t>07-03-2026</t>
-        </is>
-      </c>
-      <c r="H10" s="1" t="n">
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>08-03-2026</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I10" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287460</t>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287784</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr"/>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>Associate (Programme Management)</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Indian Institute For Human Settlements (Iihs) | Karnataka
-International Development - Associate (Programme Management), Indian Institute For Human Settlements (Iihs), Karnataka - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events ... Read More</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>• IIHS is an equal opportunity employer that encourages women, people with disabilities and those from economically and socially excluded communities with the requisite skills and qualifications to apply for positions.
-• To apply
-If you are interested in exploring this opportunity with us, please fill the online
-application form
-by clicking here. (You can also click on the “
-Apply Now
-” button at the end of the Job Description displayed on the website).
-Contact
-Please write to us at
-hr@iihs.co.in
-if you need any clarifications while filling the online application form.
-• Job Email ID:
-hr(at)iihs.co.in
-Download Attachment:
-Associate-Programme-Management-–-ASSURE-Lighthouse-Projects.pdf
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-07 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-Computer Science Trainer (School)
-Raspberry Pi Foundation
-Location:
-Telangana
-Apply by:
-04 Apr 2026
-Computer Science Trainer (College)
-Raspberry Pi Foundation
-Location:
-Telangana
-Apply by:
-04 Apr 2026
-Nursing Aid
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Driver
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Medical Officer
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Nurse
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Physiotherapist
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Project Coordinator
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G11" s="1" t="inlineStr">
-        <is>
-          <t>07-03-2026</t>
-        </is>
-      </c>
-      <c r="H11" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I11" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=285747</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="inlineStr"/>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>RFP - Final Evaluation of the Bhoomi Ka Programme</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Deutsche Welthungerhilfe | India
 International Development - RFP - Final Evaluation of the Bhoomi Ka Programme, Deutsche Welthungerhilfe, India - DevNetJobsIndia.org
@@ -2985,7 +1662,7 @@
 Jobs ... Read More</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>• INTRODUCTION AND CONTEXT
 Country:
@@ -3053,6 +1730,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
 Lead-Finance &amp; Compliance
 Marathwada Navnirman Lokayat (Manavlok)
 Location:
@@ -3107,62 +1790,56 @@
 Bihar
 Apply by:
 11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Computer Science Trainer (School)
-Raspberry Pi Foundation
+Design and Readiness Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Program Manager – AI Skilling Initiative
+SwaTaleem Foundation
+Location:
+Haryana
+Apply by:
+05 Apr 2026
+Communications Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Director of International Programmes Impact And P...
+Confidential
 Location:
 Telangana
 Apply by:
+08 Apr 2026
+Organizational Development (OD) Manager
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Manager – Monitoring &amp; Evaluation
+Family Planning Association of India (FPA India)
+Location:
+Maharashtra
+Apply by:
 04 Apr 2026
-Computer Science Trainer (College)
-Raspberry Pi Foundation
-Location:
-Telangana
-Apply by:
-04 Apr 2026
-Nursing Aid
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Driver
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Medical Officer
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Nurse
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Physiotherapist
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Project Coordinator
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
+Officer – Instructional Design and Technical Supp...
+Room to Read India
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+RFP UNW-IND-2026-00002 for Hiring resource agency...
+UN Women
+Location:
+India
+Apply by:
+23 Mar 2026
 Jobseekers
 Register
 Login
@@ -3190,69 +1867,77 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F12" s="1" t="inlineStr">
+      <c r="F7" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G12" s="1" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>08-03-2026</t>
         </is>
       </c>
-      <c r="H12" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="I12" s="1" t="inlineStr">
+      <c r="H7" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287384</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr"/>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>RFQ: Construction of New gated check dams, De-siltation, and retrofitting ...</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>WaterAid India | Telangana
-International Development - RFQ: Construction of New gated check dams, De-siltation, and retrofitting of check dam in 6 villages, WaterAid India, Telangana - DevNetJobsIndia.org
+      <c r="B8" s="1" t="inlineStr"/>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>RFP For The Contractors To Procure, Build, Install, Supply Chlorine Tablet...</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>EAII Advisors Pvt Ltd | Andhra Pradesh
+International Development - RFP For The Contractors To Procure, Build, Install, Supply Chlorine Tablets, Operate And Maintain Tablet-Based In Line Chlorination Devices, EAII Advisors Pvt Ltd, Andhra Pradesh - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
 Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-E ... Read More</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>• Job Email ID:
-WAIProcurementAP(at)wateraid.org
+Ho ... Read More</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>• Proposal Requirements
+1. Company Background and Details
+A. Company Profile
+Overview of the firm or firms submitting the bid, including a brief history, information about organizational structure, relevant company financials, location of offices, number of employees, relevant certifications, or any other information that could be pertinent.
+Supplier Response:
+Kindly fill in the column “Bidder Response”. The current inputs are guiding inputs or choices for answers. Kindly fill in accordingly.
+For detailed information, please check the complete version of the RFP attached below.
 Download Attachment:
-Tender Notice-15 check dams-Jalsankalp-19.02.26_compressed.pdf
+Standalone IC RFP Technical Evaluation Response Template.docx
+Download Attachment:
+Telugu_Standalone IC RFP Technical Evaluation Response Template.docx
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
 Apply by:
-08 Mar 2026
+09 Mar 2026
 Access all the jobs and get ahead!
 Subscribe to Value Membership Now!
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
 Lead-Finance &amp; Compliance
 Marathwada Navnirman Lokayat (Manavlok)
 Location:
@@ -3307,62 +1992,56 @@
 Bihar
 Apply by:
 11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Computer Science Trainer (School)
-Raspberry Pi Foundation
+Design and Readiness Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Program Manager – AI Skilling Initiative
+SwaTaleem Foundation
+Location:
+Haryana
+Apply by:
+05 Apr 2026
+Communications Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Director of International Programmes Impact And P...
+Confidential
 Location:
 Telangana
 Apply by:
+08 Apr 2026
+Organizational Development (OD) Manager
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Manager – Monitoring &amp; Evaluation
+Family Planning Association of India (FPA India)
+Location:
+Maharashtra
+Apply by:
 04 Apr 2026
-Computer Science Trainer (College)
-Raspberry Pi Foundation
-Location:
-Telangana
-Apply by:
-04 Apr 2026
-Nursing Aid
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Driver
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Medical Officer
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Nurse
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Physiotherapist
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Project Coordinator
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
+Officer – Instructional Design and Technical Supp...
+Room to Read India
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+RFP UNW-IND-2026-00002 for Hiring resource agency...
+UN Women
+Location:
+India
+Apply by:
+23 Mar 2026
 Jobseekers
 Register
 Login
@@ -3390,38 +2069,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F13" s="1" t="inlineStr">
+      <c r="F8" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G13" s="1" t="inlineStr">
-        <is>
-          <t>08-03-2026</t>
-        </is>
-      </c>
-      <c r="H13" s="1" t="n">
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>09-03-2026</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I13" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287784</t>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=285949</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr"/>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="B9" s="1" t="inlineStr"/>
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>RFP - Hiring of an International Audit Firm</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Coalition for Disaster Resilient Infrastructure (CDRI) | India
 International Development - RFP - Hiring of an International Audit Firm, Coalition for Disaster Resilient Infrastructure (CDRI), India - DevNetJobsIndia.org
@@ -3435,7 +2114,7 @@
 RFPs/Tender ... Read More</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>• Job Email ID:
 tender.projects(at)cdri.world
@@ -3451,6 +2130,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
 Lead-Finance &amp; Compliance
 Marathwada Navnirman Lokayat (Manavlok)
 Location:
@@ -3505,62 +2190,56 @@
 Bihar
 Apply by:
 11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Computer Science Trainer (School)
-Raspberry Pi Foundation
+Design and Readiness Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Program Manager – AI Skilling Initiative
+SwaTaleem Foundation
+Location:
+Haryana
+Apply by:
+05 Apr 2026
+Communications Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Director of International Programmes Impact And P...
+Confidential
 Location:
 Telangana
 Apply by:
+08 Apr 2026
+Organizational Development (OD) Manager
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Manager – Monitoring &amp; Evaluation
+Family Planning Association of India (FPA India)
+Location:
+Maharashtra
+Apply by:
 04 Apr 2026
-Computer Science Trainer (College)
-Raspberry Pi Foundation
-Location:
-Telangana
-Apply by:
-04 Apr 2026
-Nursing Aid
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Driver
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Medical Officer
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Nurse
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Physiotherapist
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Project Coordinator
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
+Officer – Instructional Design and Technical Supp...
+Room to Read India
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+RFP UNW-IND-2026-00002 for Hiring resource agency...
+UN Women
+Location:
+India
+Apply by:
+23 Mar 2026
 Jobseekers
 Register
 Login
@@ -3588,38 +2267,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F14" s="1" t="inlineStr">
+      <c r="F9" s="1" t="inlineStr">
         <is>
           <t>Climate</t>
         </is>
       </c>
-      <c r="G14" s="1" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>09-03-2026</t>
         </is>
       </c>
-      <c r="H14" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I14" s="1" t="inlineStr">
+      <c r="H9" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287382</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr"/>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="B10" s="1" t="inlineStr"/>
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>RFP - Early-Stage Impact Assessment-CDRI SWP 23-26</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Coalition for Disaster Resilient Infrastructure (CDRI) | India
 International Development - RFP - Early-Stage Impact Assessment-CDRI SWP 23-26, Coalition for Disaster Resilient Infrastructure (CDRI), India - DevNetJobsIndia.org
@@ -3633,54 +2312,53 @@
 RFPs ... Read More</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F15" s="1" t="inlineStr">
+      <c r="F10" s="1" t="inlineStr">
         <is>
           <t>Climate, Governance</t>
         </is>
       </c>
-      <c r="G15" s="1" t="inlineStr">
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>09-03-2026</t>
         </is>
       </c>
-      <c r="H15" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I15" s="1" t="inlineStr">
+      <c r="H10" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287093</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr"/>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>RFP For The Contractors To Procure, Build, Install, Supply Chlorine Tablet...</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr"/>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>RFP For Selection of an Implementation Support Agency (Isa) For Capacity B...</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>EAII Advisors Pvt Ltd | Andhra Pradesh
-International Development - RFP For The Contractors To Procure, Build, Install, Supply Chlorine Tablets, Operate And Maintain Tablet-Based In Line Chlorination Devices, EAII Advisors Pvt Ltd, Andhra Pradesh - DevNetJobsIndia.org
+International Development - RFP For Selection of an Implementation Support Agency (Isa) For Capacity Building Of Community Leaders To Conduct Community Engagement Activities, EAII Advisors Pvt Ltd, Andhra Pradesh - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
-Register
-Ho ... Read More</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+Regis ... Read More</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>• Proposal Requirements
 1. Company Background and Details
@@ -3690,9 +2368,9 @@
 Kindly fill in the column “Bidder Response”. The current inputs are guiding inputs or choices for answers. Kindly fill in accordingly.
 For detailed information, please check the complete version of the RFP attached below.
 Download Attachment:
-Standalone IC RFP Technical Evaluation Response Template.docx
+Standalone ISA RFP Technical Evaluation Response Template (1).docx
 Download Attachment:
-Telugu_Standalone IC RFP Technical Evaluation Response Template.docx
+Telugu_Standalone ISA RFP Technical Evaluation Response Template.docx
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
@@ -3703,6 +2381,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
 Lead-Finance &amp; Compliance
 Marathwada Navnirman Lokayat (Manavlok)
 Location:
@@ -3757,62 +2441,56 @@
 Bihar
 Apply by:
 11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Computer Science Trainer (School)
-Raspberry Pi Foundation
+Design and Readiness Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Program Manager – AI Skilling Initiative
+SwaTaleem Foundation
+Location:
+Haryana
+Apply by:
+05 Apr 2026
+Communications Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Director of International Programmes Impact And P...
+Confidential
 Location:
 Telangana
 Apply by:
+08 Apr 2026
+Organizational Development (OD) Manager
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Manager – Monitoring &amp; Evaluation
+Family Planning Association of India (FPA India)
+Location:
+Maharashtra
+Apply by:
 04 Apr 2026
-Computer Science Trainer (College)
-Raspberry Pi Foundation
-Location:
-Telangana
-Apply by:
-04 Apr 2026
-Nursing Aid
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Driver
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Medical Officer
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Nurse
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Physiotherapist
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Project Coordinator
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
+Officer – Instructional Design and Technical Supp...
+Room to Read India
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+RFP UNW-IND-2026-00002 for Hiring resource agency...
+UN Women
+Location:
+India
+Apply by:
+23 Mar 2026
 Jobseekers
 Register
 Login
@@ -3840,70 +2518,110 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G16" s="1" t="inlineStr">
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>Governance, Learning</t>
+        </is>
+      </c>
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>09-03-2026</t>
         </is>
       </c>
-      <c r="H16" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I16" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=285949</t>
+      <c r="H11" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=285950</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr"/>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>RFP For Selection of an Implementation Support Agency (Isa) For Capacity B...</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>EAII Advisors Pvt Ltd | Andhra Pradesh
-International Development - RFP For Selection of an Implementation Support Agency (Isa) For Capacity Building Of Community Leaders To Conduct Community Engagement Activities, EAII Advisors Pvt Ltd, Andhra Pradesh - DevNetJobsIndia.org
+      <c r="B12" s="1" t="inlineStr"/>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>RFP - for Supply of Skill Lab Items</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>TeamLease Foundation | India
+International Development - RFP - for Supply of Skill Lab Items, TeamLease Foundation, India - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
-Regis ... Read More</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>• Proposal Requirements
-1. Company Background and Details
-A. Company Profile
-Overview of the firm or firms submitting the bid, including a brief history, information about organizational structure, relevant company financials, location of offices, number of employees, relevant certifications, or any other information that could be pertinent.
-Supplier Response:
-Kindly fill in the column “Bidder Response”. The current inputs are guiding inputs or choices for answers. Kindly fill in accordingly.
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers:
+Login
+|
+Register
+Jobseekers Login
+Jobseeker ... Read More</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>• Technical Bid Submission Link-
+https://forms.gle/V9iy35ddb4kWEb468
+• Financial Bid Submission Link-
+https://forms.gle/LozobuuuMh55Ea2G8
+Note
+: Technical bid and financial bid are to be submitted separately in separate links.
+Following points are to be kept in mind while submitting the bids-
+All Bid must contain the complete address of firm, including contact number/ email ID of the person who is authorized to submit the bid under their signatures.
+All bids must be signed on all pages by the bidder. Unsigned bids shall not be entertained/ accepted.
+All pages of the bid being submitted must be signed and sequentially numbered by the bidder irrespective of the nature of content of the documents.
+Bids not submitted as per the specified format and nomenclature or ambiguous in nature will be liable to be rejected.
+• The interested bidders may submit their bid to TLF on or before the date mentioned in this RFP Documents. Any bid received by TLF after the prescribed deadline for submission of bids will be rejected and no further correspondence in this regard will be entertained.
+Financial bid should be prepared as per Annexure II given in the RFP Documents. Same is also to be uploaded in google forms too.
+Bidders shall indicate their rates in clear/ visible figures as well as in words. In case of a mismatch, the rates written in words will prevail.
+• At any time prior to the last date for submission of bids, TLF, may, for any reason, whether at its own initiative or in response to a clarification requested by a prospective bidder, modify the RFP Documents by an amendment and publish the revised version of the RFP.
+The contract panel may consist of maximum three vendors for each item. However, TLF reserves the right to review the performance of the panel of vendors and terminate the contract of such vendors whose performance is not found satisfactory. The decision of TLF will be final in this regard.
+TLF will issue Purchase Order(s) (PO) during the period up to 31-March-2026. as per the required quantities and as per the rates and other terms of the Purchase Order.
+TLF may issue separate Purchase Order(s) PO based on its actual requirements to the Successful Bidder(s) for providing Product(s) and / or Service(s) and there is no minimum or prior commitment for such orders under this RFP.
+The successful bidder will be expected to provide all the necessary support for delivery of the items, warranty and required support during the warranty period.
+Delivery of the Kits specified in this RFP should be by 20
+th
+December 2025 from the PO date
+Successful bidder will ensure delivery, installation and operationalization of all products /components under the contract before acceptance testing / examination, and the Warranty period will commence only on acceptance of the products
+If, during the warranty period, any system as a whole or any subsystem has any failure on two or more occasions in a period of 3 months, it shall be replaced by equivalent new equipment by the Vendor at no cost to TLF
+The successful bidder shall be fully responsible for the manufacturer’s warranty for all equipment, accessories, spare parts etc. against any defects arising from design, material, manufacturing, workmanship, or any act or omission of the manufacturer / vendor or any defect that may develop under normal use of supplied equipment during the warranty period
+In case of any deviations, specific exemption may be sought on case-to-case basis from the respective Departments placing the Service Request
+• Printed terms and conditions of the bidders will not be considered as forming part of their bid. In case terms and conditions as given in the RFP Documents are not acceptable to any bidder, they should clearly specify the deviations in their bids.
+Bids complete in all respects along with supporting documents, must be submitted as per the RFP requirements. No physical document is to be submitted by the bidders.
+NO conditional or partial Bid will be entertained and will be rejected.
+• Parallel Contracts - TLF may also execute parallel contracts with more than one firm on the lowest approved rates on the same terms and conditions. These parallel contracts will be utilized if the original L1 substantially technically qualified bidder is not in a position to supply material as per TLFs requirement within the time frame indicated in the bid.
 For detailed information, please check the complete version of the RFP attached below.
 Download Attachment:
-Standalone ISA RFP Technical Evaluation Response Template (1).docx
-Download Attachment:
-Telugu_Standalone ISA RFP Technical Evaluation Response Template.docx
+RFP for procurement Skill Lab Items under RIST Mansi_250226.pdf
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
 Apply by:
-09 Mar 2026
+11 Mar 2026
 Access all the jobs and get ahead!
 Subscribe to Value Membership Now!
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
 Lead-Finance &amp; Compliance
 Marathwada Navnirman Lokayat (Manavlok)
 Location:
@@ -3958,62 +2676,56 @@
 Bihar
 Apply by:
 11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Computer Science Trainer (School)
-Raspberry Pi Foundation
+Design and Readiness Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Program Manager – AI Skilling Initiative
+SwaTaleem Foundation
+Location:
+Haryana
+Apply by:
+05 Apr 2026
+Communications Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Director of International Programmes Impact And P...
+Confidential
 Location:
 Telangana
 Apply by:
+08 Apr 2026
+Organizational Development (OD) Manager
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Manager – Monitoring &amp; Evaluation
+Family Planning Association of India (FPA India)
+Location:
+Maharashtra
+Apply by:
 04 Apr 2026
-Computer Science Trainer (College)
-Raspberry Pi Foundation
-Location:
-Telangana
-Apply by:
-04 Apr 2026
-Nursing Aid
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Driver
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Medical Officer
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Nurse
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Physiotherapist
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Project Coordinator
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
+Officer – Instructional Design and Technical Supp...
+Room to Read India
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+RFP UNW-IND-2026-00002 for Hiring resource agency...
+UN Women
+Location:
+India
+Apply by:
+23 Mar 2026
 Jobseekers
 Register
 Login
@@ -4041,44 +2753,44 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t>Governance, Learning</t>
-        </is>
-      </c>
-      <c r="G17" s="1" t="inlineStr">
-        <is>
-          <t>09-03-2026</t>
-        </is>
-      </c>
-      <c r="H17" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I17" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=285950</t>
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G12" s="1" t="inlineStr">
+        <is>
+          <t>11-03-2026</t>
+        </is>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I12" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287613</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B18" s="1" t="inlineStr"/>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="B13" s="1" t="inlineStr"/>
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>RFP - Study On SC-DMPA In Rajasthan- Clients And Providers Perspectives On...</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Centre For Community Economics And Development Consultants Society- CECOEDECON | Jaipur, Rajasthan
 International Development - RFP - Study On SC-DMPA In Rajasthan- Clients And Providers Perspectives On SC-DMPA In Rajasthan, Centre For Community Economics And Development Consultants Society- CECOEDE ... Read More</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>• Despite India’s achievement of replacement-level fertility, unmet need for contraception—particularly for spacing methods—remains substantial, with modern contraceptive use at 56.4% (2019–21), highlighting persistent gaps in access and choice, especially among vulnerable populations. Expanding the contraceptive method mix through innovative, user-centred approaches is therefore essential to meeting national commitments under FP2030 and the Sustainable Development Goals. In this context, the Government of India’s introduction of subcutaneous DMPA (DMPA-SC) as a self-care option under the National Family Planning Programme in 2023 represents a strategic step toward enhancing women’s autonomy, privacy, and convenience in contraceptive use. Global and national evidence indicates strong feasibility and acceptability of self-administered DMPA-SC among both users and providers; however, successful implementation requires an in-depth understanding of user experiences and health system readiness. This study, to be conducted in Jaipur-1, Jaisalmer and Sawai Madhopur districts of Rajasthan, aims to examine the perspectives &amp; experience of current SC-DMPA users and explore healthcare providers’ views on enabling and generating actionable evidence to inform effective scale-up of SC-DMPA within India’s public health system.
 CECOEDECON, with support from UNFPA, is implementing the roll-out of subcutaneous DMPA (SC-DMPA) in selected pilot districts of Rajasthan in the public health facilities, in collaboration with the Department of Health &amp; Family Welfare, Government of Rajasthan.
@@ -4151,6 +2863,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
 Lead-Finance &amp; Compliance
 Marathwada Navnirman Lokayat (Manavlok)
 Location:
@@ -4205,62 +2923,56 @@
 Bihar
 Apply by:
 11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Computer Science Trainer (School)
-Raspberry Pi Foundation
+Design and Readiness Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Program Manager – AI Skilling Initiative
+SwaTaleem Foundation
+Location:
+Haryana
+Apply by:
+05 Apr 2026
+Communications Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Director of International Programmes Impact And P...
+Confidential
 Location:
 Telangana
 Apply by:
+08 Apr 2026
+Organizational Development (OD) Manager
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Manager – Monitoring &amp; Evaluation
+Family Planning Association of India (FPA India)
+Location:
+Maharashtra
+Apply by:
 04 Apr 2026
-Computer Science Trainer (College)
-Raspberry Pi Foundation
-Location:
-Telangana
-Apply by:
-04 Apr 2026
-Nursing Aid
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Driver
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Medical Officer
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Nurse
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Physiotherapist
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Project Coordinator
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
+Officer – Instructional Design and Technical Supp...
+Room to Read India
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+RFP UNW-IND-2026-00002 for Hiring resource agency...
+UN Women
+Location:
+India
+Apply by:
+23 Mar 2026
 Jobseekers
 Register
 Login
@@ -4288,273 +3000,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F18" s="1" t="inlineStr">
+      <c r="F13" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G18" s="1" t="inlineStr">
+      <c r="G13" s="1" t="inlineStr">
         <is>
           <t>11-03-2026</t>
         </is>
       </c>
-      <c r="H18" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I18" s="1" t="inlineStr">
+      <c r="H13" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I13" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287322</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr"/>
-      <c r="C19" s="1" t="inlineStr">
-        <is>
-          <t>RFP - for Supply of Skill Lab Items</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>TeamLease Foundation | India
-International Development - RFP - for Supply of Skill Lab Items, TeamLease Foundation, India - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Login
-|
-Register
-Jobseekers Login
-Jobseeker ... Read More</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>• Technical Bid Submission Link-
-https://forms.gle/V9iy35ddb4kWEb468
-• Financial Bid Submission Link-
-https://forms.gle/LozobuuuMh55Ea2G8
-Note
-: Technical bid and financial bid are to be submitted separately in separate links.
-Following points are to be kept in mind while submitting the bids-
-All Bid must contain the complete address of firm, including contact number/ email ID of the person who is authorized to submit the bid under their signatures.
-All bids must be signed on all pages by the bidder. Unsigned bids shall not be entertained/ accepted.
-All pages of the bid being submitted must be signed and sequentially numbered by the bidder irrespective of the nature of content of the documents.
-Bids not submitted as per the specified format and nomenclature or ambiguous in nature will be liable to be rejected.
-• The interested bidders may submit their bid to TLF on or before the date mentioned in this RFP Documents. Any bid received by TLF after the prescribed deadline for submission of bids will be rejected and no further correspondence in this regard will be entertained.
-Financial bid should be prepared as per Annexure II given in the RFP Documents. Same is also to be uploaded in google forms too.
-Bidders shall indicate their rates in clear/ visible figures as well as in words. In case of a mismatch, the rates written in words will prevail.
-• At any time prior to the last date for submission of bids, TLF, may, for any reason, whether at its own initiative or in response to a clarification requested by a prospective bidder, modify the RFP Documents by an amendment and publish the revised version of the RFP.
-The contract panel may consist of maximum three vendors for each item. However, TLF reserves the right to review the performance of the panel of vendors and terminate the contract of such vendors whose performance is not found satisfactory. The decision of TLF will be final in this regard.
-TLF will issue Purchase Order(s) (PO) during the period up to 31-March-2026. as per the required quantities and as per the rates and other terms of the Purchase Order.
-TLF may issue separate Purchase Order(s) PO based on its actual requirements to the Successful Bidder(s) for providing Product(s) and / or Service(s) and there is no minimum or prior commitment for such orders under this RFP.
-The successful bidder will be expected to provide all the necessary support for delivery of the items, warranty and required support during the warranty period.
-Delivery of the Kits specified in this RFP should be by 20
-th
-December 2025 from the PO date
-Successful bidder will ensure delivery, installation and operationalization of all products /components under the contract before acceptance testing / examination, and the Warranty period will commence only on acceptance of the products
-If, during the warranty period, any system as a whole or any subsystem has any failure on two or more occasions in a period of 3 months, it shall be replaced by equivalent new equipment by the Vendor at no cost to TLF
-The successful bidder shall be fully responsible for the manufacturer’s warranty for all equipment, accessories, spare parts etc. against any defects arising from design, material, manufacturing, workmanship, or any act or omission of the manufacturer / vendor or any defect that may develop under normal use of supplied equipment during the warranty period
-In case of any deviations, specific exemption may be sought on case-to-case basis from the respective Departments placing the Service Request
-• Printed terms and conditions of the bidders will not be considered as forming part of their bid. In case terms and conditions as given in the RFP Documents are not acceptable to any bidder, they should clearly specify the deviations in their bids.
-Bids complete in all respects along with supporting documents, must be submitted as per the RFP requirements. No physical document is to be submitted by the bidders.
-NO conditional or partial Bid will be entertained and will be rejected.
-• Parallel Contracts - TLF may also execute parallel contracts with more than one firm on the lowest approved rates on the same terms and conditions. These parallel contracts will be utilized if the original L1 substantially technically qualified bidder is not in a position to supply material as per TLFs requirement within the time frame indicated in the bid.
-For detailed information, please check the complete version of the RFP attached below.
-Download Attachment:
-RFP for procurement Skill Lab Items under RIST Mansi_250226.pdf
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-11 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-Computer Science Trainer (School)
-Raspberry Pi Foundation
-Location:
-Telangana
-Apply by:
-04 Apr 2026
-Computer Science Trainer (College)
-Raspberry Pi Foundation
-Location:
-Telangana
-Apply by:
-04 Apr 2026
-Nursing Aid
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Driver
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Medical Officer
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Nurse
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Physiotherapist
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Project Coordinator
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F19" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G19" s="1" t="inlineStr">
-        <is>
-          <t>11-03-2026</t>
-        </is>
-      </c>
-      <c r="H19" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I19" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287613</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B20" s="1" t="inlineStr"/>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="B14" s="1" t="inlineStr"/>
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>SOW - Engagement of a Public Relations (PR) Agency on Retainer</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Room to Read India | India
 International Development - SOW - Engagement of a Public Relations (PR) Agency on Retainer, Room to Read India, India - DevNetJobsIndia.org
@@ -4575,7 +3052,7 @@
 Job ... Read More</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>• Scope of Work (SOW)
 Engagement of a Public Relations (PR) Agency on Retainer
@@ -4643,6 +3120,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
 Lead-Finance &amp; Compliance
 Marathwada Navnirman Lokayat (Manavlok)
 Location:
@@ -4697,62 +3180,56 @@
 Bihar
 Apply by:
 11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Computer Science Trainer (School)
-Raspberry Pi Foundation
+Design and Readiness Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Program Manager – AI Skilling Initiative
+SwaTaleem Foundation
+Location:
+Haryana
+Apply by:
+05 Apr 2026
+Communications Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Director of International Programmes Impact And P...
+Confidential
 Location:
 Telangana
 Apply by:
+08 Apr 2026
+Organizational Development (OD) Manager
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Manager – Monitoring &amp; Evaluation
+Family Planning Association of India (FPA India)
+Location:
+Maharashtra
+Apply by:
 04 Apr 2026
-Computer Science Trainer (College)
-Raspberry Pi Foundation
-Location:
-Telangana
-Apply by:
-04 Apr 2026
-Nursing Aid
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Driver
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Medical Officer
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Nurse
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Physiotherapist
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Project Coordinator
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
+Officer – Instructional Design and Technical Supp...
+Room to Read India
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+RFP UNW-IND-2026-00002 for Hiring resource agency...
+UN Women
+Location:
+India
+Apply by:
+23 Mar 2026
 Jobseekers
 Register
 Login
@@ -4780,251 +3257,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F20" s="1" t="inlineStr">
+      <c r="F14" s="1" t="inlineStr">
         <is>
           <t>Governance, Learning</t>
         </is>
       </c>
-      <c r="G20" s="1" t="inlineStr">
+      <c r="G14" s="1" t="inlineStr">
         <is>
           <t>12-03-2026</t>
         </is>
       </c>
-      <c r="H20" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="I20" s="1" t="inlineStr">
+      <c r="H14" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I14" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287648</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr"/>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>RFP - for Internal Audit</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>India HIV/AIDS Alliance (Alliance India) | Delhi
-International Development - RFP - for Internal Audit, India HIV/AIDS Alliance (Alliance India), Delhi - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Login
-|
-Regist ... Read More</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>• Alliance India reserves the right to reject applications that do not meet eligibility or application submission requirements (as detailed above) without further notice to the applicant. Issuance of this RFP does not constitute an award commitment or a guarantee of business on the part of Alliance India, nor does it commit Alliance India to pay for the costs incurred in submitting the application. Further, Alliance India reserves the right to reject any or all applications received and negotiate separately with an applicant if such action is considered in the best interest of Alliance India/ project.
-iii.
-Queries, Response and Submission
-Queries regarding this RFP will be sent only to procurement@allianceindia.org by March 07, 2026. Alliance India shall collaborate and respond to all meaningful queries from prospective applicants by March 10, 2026. Responses to questions shall be compiled and sent to all the applicants who raised the queries through email only. ALLIANCE INDIA is under no obligation to consider or respond to questions that are not received on time.
-iv.
-• Submission of bids
-The bid has to be submitted in the prescribed format on or before March 13, 2026 by 5 p.m. Indian Standard Time to
-procurement@allianceindia.org
-For the detailed version of the Request for Proposal, please refer to the RFP attached.
-• Job Email ID:
-procurement(at)allianceindia.org
-Download Attachment:
-RFP for Internal Audit - FY 2025-26.doc
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-13 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-Computer Science Trainer (School)
-Raspberry Pi Foundation
-Location:
-Telangana
-Apply by:
-04 Apr 2026
-Computer Science Trainer (College)
-Raspberry Pi Foundation
-Location:
-Telangana
-Apply by:
-04 Apr 2026
-Nursing Aid
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Driver
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Medical Officer
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Nurse
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Physiotherapist
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Project Coordinator
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F21" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G21" s="1" t="inlineStr">
-        <is>
-          <t>13-03-2026</t>
-        </is>
-      </c>
-      <c r="H21" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="I21" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287765</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B22" s="1" t="inlineStr"/>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="B15" s="1" t="inlineStr"/>
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>Specialist – Financial Management and Compliance</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Financial Management Service Foundation (FMSF) | Uttar Pradesh
 International Development - Specialist – Financial Management and Compliance, Financial Management Service Foundation (FMSF), Uttar Pradesh - DevNetJobsIndia.org
@@ -5038,7 +3302,7 @@
 RFPs/T ... Read More</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>• will play a vital role in a program which seeks to strengthen the internal capacities of non-profit organizations in India across three building blocks of institutional functioning: governance, financial management, and compliance. These areas are deeply interconnected and together determine how effectively an organization operates, delivers programs and meets the expectations of its stakeholders. This position demands expertise in specific areas related to governance, compliance, and financial management, contributing essential guidance and support to strengthen the capabilities of participating organizations.
 Job Responsibilities:
@@ -5089,6 +3353,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
 Lead-Finance &amp; Compliance
 Marathwada Navnirman Lokayat (Manavlok)
 Location:
@@ -5143,62 +3413,56 @@
 Bihar
 Apply by:
 11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Computer Science Trainer (School)
-Raspberry Pi Foundation
+Design and Readiness Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Program Manager – AI Skilling Initiative
+SwaTaleem Foundation
+Location:
+Haryana
+Apply by:
+05 Apr 2026
+Communications Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Director of International Programmes Impact And P...
+Confidential
 Location:
 Telangana
 Apply by:
+08 Apr 2026
+Organizational Development (OD) Manager
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Manager – Monitoring &amp; Evaluation
+Family Planning Association of India (FPA India)
+Location:
+Maharashtra
+Apply by:
 04 Apr 2026
-Computer Science Trainer (College)
-Raspberry Pi Foundation
-Location:
-Telangana
-Apply by:
-04 Apr 2026
-Nursing Aid
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Driver
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Medical Officer
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Nurse
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Physiotherapist
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Project Coordinator
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
+Officer – Instructional Design and Technical Supp...
+Room to Read India
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+RFP UNW-IND-2026-00002 for Hiring resource agency...
+UN Women
+Location:
+India
+Apply by:
+23 Mar 2026
 Jobseekers
 Register
 Login
@@ -5226,38 +3490,455 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F22" s="1" t="inlineStr">
+      <c r="F15" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G22" s="1" t="inlineStr">
+      <c r="G15" s="1" t="inlineStr">
         <is>
           <t>13-03-2026</t>
         </is>
       </c>
-      <c r="H22" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="I22" s="1" t="inlineStr">
+      <c r="H15" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I15" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287015</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr"/>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="B16" s="1" t="inlineStr"/>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>RFP - for Internal Audit</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>India HIV/AIDS Alliance (Alliance India) | Delhi
+International Development - RFP - for Internal Audit, India HIV/AIDS Alliance (Alliance India), Delhi - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers:
+Login
+|
+Regist ... Read More</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>• Alliance India reserves the right to reject applications that do not meet eligibility or application submission requirements (as detailed above) without further notice to the applicant. Issuance of this RFP does not constitute an award commitment or a guarantee of business on the part of Alliance India, nor does it commit Alliance India to pay for the costs incurred in submitting the application. Further, Alliance India reserves the right to reject any or all applications received and negotiate separately with an applicant if such action is considered in the best interest of Alliance India/ project.
+iii.
+Queries, Response and Submission
+Queries regarding this RFP will be sent only to procurement@allianceindia.org by March 07, 2026. Alliance India shall collaborate and respond to all meaningful queries from prospective applicants by March 10, 2026. Responses to questions shall be compiled and sent to all the applicants who raised the queries through email only. ALLIANCE INDIA is under no obligation to consider or respond to questions that are not received on time.
+iv.
+• Submission of bids
+The bid has to be submitted in the prescribed format on or before March 13, 2026 by 5 p.m. Indian Standard Time to
+procurement@allianceindia.org
+For the detailed version of the Request for Proposal, please refer to the RFP attached.
+• Job Email ID:
+procurement(at)allianceindia.org
+Download Attachment:
+RFP for Internal Audit - FY 2025-26.doc
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+13 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Associate (Programme Management)
+Indian Institute For Human Settlements (Iihs)
+Location:
+Karnataka
+Apply by:
+07 Mar 2026
+Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+Design and Readiness Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Program Manager – AI Skilling Initiative
+SwaTaleem Foundation
+Location:
+Haryana
+Apply by:
+05 Apr 2026
+Communications Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Director of International Programmes Impact And P...
+Confidential
+Location:
+Telangana
+Apply by:
+08 Apr 2026
+Organizational Development (OD) Manager
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Manager – Monitoring &amp; Evaluation
+Family Planning Association of India (FPA India)
+Location:
+Maharashtra
+Apply by:
+04 Apr 2026
+Officer – Instructional Design and Technical Supp...
+Room to Read India
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+RFP UNW-IND-2026-00002 for Hiring resource agency...
+UN Women
+Location:
+India
+Apply by:
+23 Mar 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G16" s="1" t="inlineStr">
+        <is>
+          <t>13-03-2026</t>
+        </is>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I16" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287765</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr"/>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>ToR - Strategic Review and Forward-Looking Education Strategy Development</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>ChildFund India | India
+International Development - ToR - Strategic Review and Forward-Looking Education Strategy Development, ChildFund India, India - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers:
+Login
+|
+Registe ... Read More</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>• Job Email ID:
+centralpurchase2(at)childfundindia.org
+Download Attachment:
+ToR for Education.doc
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+15 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Associate (Programme Management)
+Indian Institute For Human Settlements (Iihs)
+Location:
+Karnataka
+Apply by:
+07 Mar 2026
+Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+Design and Readiness Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Program Manager – AI Skilling Initiative
+SwaTaleem Foundation
+Location:
+Haryana
+Apply by:
+05 Apr 2026
+Communications Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Director of International Programmes Impact And P...
+Confidential
+Location:
+Telangana
+Apply by:
+08 Apr 2026
+Organizational Development (OD) Manager
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Manager – Monitoring &amp; Evaluation
+Family Planning Association of India (FPA India)
+Location:
+Maharashtra
+Apply by:
+04 Apr 2026
+Officer – Instructional Design and Technical Supp...
+Room to Read India
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+RFP UNW-IND-2026-00002 for Hiring resource agency...
+UN Women
+Location:
+India
+Apply by:
+23 Mar 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>Learning, Safety</t>
+        </is>
+      </c>
+      <c r="G17" s="1" t="inlineStr">
+        <is>
+          <t>15-03-2026</t>
+        </is>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="I17" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287902</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr"/>
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>RFP - External organization/agency to undertake documentation and process ...</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>India Health Action Trust (IHAT) | India
 International Development - RFP - External organization/agency to undertake documentation and process evaluation of the Gen Equal Fellowship Programme, India Health Action Trust (IHAT), India - DevNetJobsIndia.org
@@ -5269,7 +3950,7 @@
 Value Memb ... Read More</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>• 3A. Scope of Work
 Time Period
@@ -5352,6 +4033,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
 Lead-Finance &amp; Compliance
 Marathwada Navnirman Lokayat (Manavlok)
 Location:
@@ -5406,62 +4093,56 @@
 Bihar
 Apply by:
 11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Computer Science Trainer (School)
-Raspberry Pi Foundation
+Design and Readiness Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Program Manager – AI Skilling Initiative
+SwaTaleem Foundation
+Location:
+Haryana
+Apply by:
+05 Apr 2026
+Communications Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Director of International Programmes Impact And P...
+Confidential
 Location:
 Telangana
 Apply by:
+08 Apr 2026
+Organizational Development (OD) Manager
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Manager – Monitoring &amp; Evaluation
+Family Planning Association of India (FPA India)
+Location:
+Maharashtra
+Apply by:
 04 Apr 2026
-Computer Science Trainer (College)
-Raspberry Pi Foundation
-Location:
-Telangana
-Apply by:
-04 Apr 2026
-Nursing Aid
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Driver
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Medical Officer
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Nurse
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Physiotherapist
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Project Coordinator
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
+Officer – Instructional Design and Technical Supp...
+Room to Read India
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+RFP UNW-IND-2026-00002 for Hiring resource agency...
+UN Women
+Location:
+India
+Apply by:
+23 Mar 2026
 Jobseekers
 Register
 Login
@@ -5489,38 +4170,465 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F23" s="1" t="inlineStr">
+      <c r="F18" s="1" t="inlineStr">
         <is>
           <t>Safety</t>
         </is>
       </c>
-      <c r="G23" s="1" t="inlineStr">
+      <c r="G18" s="1" t="inlineStr">
         <is>
           <t>15-03-2026</t>
         </is>
       </c>
-      <c r="H23" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="I23" s="1" t="inlineStr">
+      <c r="H18" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="I18" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287645</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr"/>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="B19" s="1" t="inlineStr"/>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>ToR - Livelihoods Strategy Review and Future Direction Roadmap</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>ChildFund India | India
+International Development - ToR - Livelihoods Strategy Review and Future Direction Roadmap, ChildFund India, India - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers:
+Login
+|
+Register
+Jobseeker ... Read More</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>• To determine the relevance, alignment, and coherence of the Livelihood Program under CSP 2022–2027 with national priorities, donor expectations, and organizational mandate.
+To assess the extent to which planned outputs and outcomes have been achieved and to evaluate the quality and impact of program interventions.
+Identify achievements, innovations, good practices, and enabling factors across Livelihood program interventions.
+Document gaps, challenges, and areas for strengthening
+To examine the sustainability of program outcomes and the institutional readiness of ChildFund India for long-term resilience and growth.
+Facilitate reflection through workshops involving staff, partners, and selected beneficiaries and provide recommendations for strategic direction, scalability, and future program priorities.
+Proposal Submission
+Interested evaluators/agencies are invited to submit:
+Technical proposal outlining approach and methodology
+Team composition and relevant experience
+Financial proposal with a detailed budget
+Sample of previous qualitative evaluation work
+Interested evaluators/agencies are requested to submit their technical and financial proposals to
+centralpurchase2@childfundindia.org
+by 15 March 2026.
+Reference No:- PRA/CFI/DEL/2025-26/053
+ChildFund India reserves the right to modify this ToR based on programmatic and contextual requirements.
+For detailed information, please check the complete version of the advert attached below.
+• Job Email ID:
+centralpurchase2(at)childfundindia.org
+Download Attachment:
+ToR Livelihood Portfolio-6.3.2026.doc
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+15 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Associate (Programme Management)
+Indian Institute For Human Settlements (Iihs)
+Location:
+Karnataka
+Apply by:
+07 Mar 2026
+Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+Design and Readiness Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Program Manager – AI Skilling Initiative
+SwaTaleem Foundation
+Location:
+Haryana
+Apply by:
+05 Apr 2026
+Communications Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Director of International Programmes Impact And P...
+Confidential
+Location:
+Telangana
+Apply by:
+08 Apr 2026
+Organizational Development (OD) Manager
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Manager – Monitoring &amp; Evaluation
+Family Planning Association of India (FPA India)
+Location:
+Maharashtra
+Apply by:
+04 Apr 2026
+Officer – Instructional Design and Technical Supp...
+Room to Read India
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+RFP UNW-IND-2026-00002 for Hiring resource agency...
+UN Women
+Location:
+India
+Apply by:
+23 Mar 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="G19" s="1" t="inlineStr">
+        <is>
+          <t>15-03-2026</t>
+        </is>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="I19" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287910</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr"/>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>ToR - Portfolio-Wide Learning Exercise cum review for the Health Domain</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>ChildFund India | India
+International Development - ToR - Portfolio-Wide Learning Exercise cum review for the Health Domain, ChildFund India, India - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers:
+Login
+|
+Register ... Read More</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>• Job Email ID:
+centralpurchase2(at)childfundindia.org
+Download Attachment:
+TOR  Health Portfolio_23.2.2026.doc
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+15 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Associate (Programme Management)
+Indian Institute For Human Settlements (Iihs)
+Location:
+Karnataka
+Apply by:
+07 Mar 2026
+Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+Design and Readiness Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Program Manager – AI Skilling Initiative
+SwaTaleem Foundation
+Location:
+Haryana
+Apply by:
+05 Apr 2026
+Communications Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Director of International Programmes Impact And P...
+Confidential
+Location:
+Telangana
+Apply by:
+08 Apr 2026
+Organizational Development (OD) Manager
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Manager – Monitoring &amp; Evaluation
+Family Planning Association of India (FPA India)
+Location:
+Maharashtra
+Apply by:
+04 Apr 2026
+Officer – Instructional Design and Technical Supp...
+Room to Read India
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+RFP UNW-IND-2026-00002 for Hiring resource agency...
+UN Women
+Location:
+India
+Apply by:
+23 Mar 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t>Learning, Safety</t>
+        </is>
+      </c>
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t>15-03-2026</t>
+        </is>
+      </c>
+      <c r="H20" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287901</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr"/>
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>RFP - for Empanelment of Knowledge Partners for Grooming of students for ...</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>TeamLease Foundation | India
 International Development - RFP - for  Empanelment of Knowledge Partners for Grooming of students for competitive examination (through partner) Super 30 Model, TeamLease Foundation, India - DevNetJobsIndia.org
@@ -5533,43 +4641,43 @@
 Broadcast ... Read More</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F24" s="1" t="inlineStr">
+      <c r="F21" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G24" s="1" t="inlineStr">
+      <c r="G21" s="1" t="inlineStr">
         <is>
           <t>15-03-2026</t>
         </is>
       </c>
-      <c r="H24" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="I24" s="1" t="inlineStr">
+      <c r="H21" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="I21" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287763</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr"/>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="B22" s="1" t="inlineStr"/>
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>RFP - Big IC+ISA RFP - Selection of a Service Provider for Supply, Instal...</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>EAII Advisors Pvt Ltd | Andhra Pradesh
 International Development - RFP - Big IC+ISA RFP -  Selection of a Service Provider for Supply, Installation and Operation &amp; Maintenance of 150 ILC Devices and Capacity Building., EAII Advisors Pvt Ltd, Andhra Pradesh - DevNetJobsIndia.org
@@ -5578,7 +4686,7 @@
 | ... Read More</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>• 2. Purpose of the RFP:
 2.1  EAII is soliciting bids for:
@@ -5625,6 +4733,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
 Lead-Finance &amp; Compliance
 Marathwada Navnirman Lokayat (Manavlok)
 Location:
@@ -5679,62 +4793,56 @@
 Bihar
 Apply by:
 11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Computer Science Trainer (School)
-Raspberry Pi Foundation
+Design and Readiness Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Program Manager – AI Skilling Initiative
+SwaTaleem Foundation
+Location:
+Haryana
+Apply by:
+05 Apr 2026
+Communications Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Director of International Programmes Impact And P...
+Confidential
 Location:
 Telangana
 Apply by:
+08 Apr 2026
+Organizational Development (OD) Manager
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Manager – Monitoring &amp; Evaluation
+Family Planning Association of India (FPA India)
+Location:
+Maharashtra
+Apply by:
 04 Apr 2026
-Computer Science Trainer (College)
-Raspberry Pi Foundation
-Location:
-Telangana
-Apply by:
-04 Apr 2026
-Nursing Aid
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Driver
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Medical Officer
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Nurse
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Physiotherapist
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Project Coordinator
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
+Officer – Instructional Design and Technical Supp...
+Room to Read India
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+RFP UNW-IND-2026-00002 for Hiring resource agency...
+UN Women
+Location:
+India
+Apply by:
+23 Mar 2026
 Jobseekers
 Register
 Login
@@ -5762,38 +4870,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F25" s="1" t="inlineStr">
+      <c r="F22" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G25" s="1" t="inlineStr">
+      <c r="G22" s="1" t="inlineStr">
         <is>
           <t>16-03-2026</t>
         </is>
       </c>
-      <c r="H25" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="I25" s="1" t="inlineStr">
+      <c r="H22" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="I22" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287172</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr"/>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="B23" s="1" t="inlineStr"/>
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>Specialist – Communication</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Financial Management Service Foundation (FMSF) | Uttar Pradesh
 International Development - Specialist – Communication, Financial Management Service Foundation (FMSF), Uttar Pradesh - DevNetJobsIndia.org
@@ -5809,7 +4917,7 @@
 Eve ... Read More</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>• Joining FMSF means becoming part of a passionate team dedicated to making a positive impact. We offer competitive compensation, opportunities for professional development, and a supportive work environment where your contributions are valued and recognized. If you are committed to driving positive change, promoting accountability and strengthening the development sector, we encourage you to apply for the position of Specialist – Communication at FMSF.
 • How to Apply:
@@ -5831,6 +4939,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
 Lead-Finance &amp; Compliance
 Marathwada Navnirman Lokayat (Manavlok)
 Location:
@@ -5885,62 +4999,56 @@
 Bihar
 Apply by:
 11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Computer Science Trainer (School)
-Raspberry Pi Foundation
+Design and Readiness Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Program Manager – AI Skilling Initiative
+SwaTaleem Foundation
+Location:
+Haryana
+Apply by:
+05 Apr 2026
+Communications Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Director of International Programmes Impact And P...
+Confidential
 Location:
 Telangana
 Apply by:
+08 Apr 2026
+Organizational Development (OD) Manager
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Manager – Monitoring &amp; Evaluation
+Family Planning Association of India (FPA India)
+Location:
+Maharashtra
+Apply by:
 04 Apr 2026
-Computer Science Trainer (College)
-Raspberry Pi Foundation
-Location:
-Telangana
-Apply by:
-04 Apr 2026
-Nursing Aid
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Driver
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Medical Officer
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Nurse
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Physiotherapist
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Project Coordinator
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
+Officer – Instructional Design and Technical Supp...
+Room to Read India
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+RFP UNW-IND-2026-00002 for Hiring resource agency...
+UN Women
+Location:
+India
+Apply by:
+23 Mar 2026
 Jobseekers
 Register
 Login
@@ -5968,66 +5076,64 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F26" s="1" t="inlineStr">
+      <c r="F23" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G26" s="1" t="inlineStr">
+      <c r="G23" s="1" t="inlineStr">
         <is>
           <t>19-03-2026</t>
         </is>
       </c>
-      <c r="H26" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="I26" s="1" t="inlineStr">
+      <c r="H23" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="I23" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287207</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr"/>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>Specialist - Grants</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Financial Management Service Foundation (FMSF) | Uttar Pradesh
-International Development - Specialist - Grants, Financial Management Service Foundation (FMSF), Uttar Pradesh - DevNetJobsIndia.org
+      <c r="B24" s="1" t="inlineStr"/>
+      <c r="C24" s="1" t="inlineStr">
+        <is>
+          <t>RFP - Consultancy for development of descriptive documentation of Ashiyana...</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Prerana | Mumbai, Maharashtra
+International Development - RFP - Consultancy for development of descriptive documentation of Ashiyana Implementation &amp; Practice Framework, and produce a replication-ready, Prerana, Maharashtra - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
 Register
 Home
 Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Job ... Read More</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>• Joining FMSF means becoming part of a passionate team dedicated to making a positive impact. We offer competitive compensation, opportunities for professional development, and a supportive work environment where your contributions are valued and recognized. If you are committed to driving positive change, promoting accountability and strengthening the development sector, we encourage you to apply for the position of Specialist - Grants at FMSF.
-You’re Resume to be accompanied with:
-Motivational letter justifying suitability for the position – role fitment based on present &amp; past work experience
-Current/last drawn compensation &amp; expected compensation
-CVs without Motivational Letter will not be considered
-• How to Apply:
-Apply online by clicking on the link
-https://www.fmsfindia.org.in/apply-now/specialist-grants
-FMSF is an Equal Opportunity Employer.
-Please note that only the shortlisted candidates will be contacted.
+Br ... Read More</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>• Submission Details
+Proposals must be submitted by email to:
+rashmi@preranaantitrafficking.org
+Subject line:
+Proposal – Aashiyana Implementation &amp; Practice Framework
+Deadline:
+21-03-26
+For detailed information, please check the complete version of the RFP attached below.
+• Job Email ID:
+rashmi(at)preranaantitrafficking.org
+Download Attachment:
+Aashiyana- Framework Documentation- RFP- v2.doc
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
@@ -6038,6 +5144,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
 Lead-Finance &amp; Compliance
 Marathwada Navnirman Lokayat (Manavlok)
 Location:
@@ -6092,62 +5204,56 @@
 Bihar
 Apply by:
 11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Computer Science Trainer (School)
-Raspberry Pi Foundation
+Design and Readiness Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Program Manager – AI Skilling Initiative
+SwaTaleem Foundation
+Location:
+Haryana
+Apply by:
+05 Apr 2026
+Communications Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Director of International Programmes Impact And P...
+Confidential
 Location:
 Telangana
 Apply by:
+08 Apr 2026
+Organizational Development (OD) Manager
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Manager – Monitoring &amp; Evaluation
+Family Planning Association of India (FPA India)
+Location:
+Maharashtra
+Apply by:
 04 Apr 2026
-Computer Science Trainer (College)
-Raspberry Pi Foundation
-Location:
-Telangana
-Apply by:
-04 Apr 2026
-Nursing Aid
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Driver
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Medical Officer
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Nurse
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Physiotherapist
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Project Coordinator
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
+Officer – Instructional Design and Technical Supp...
+Room to Read India
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+RFP UNW-IND-2026-00002 for Hiring resource agency...
+UN Women
+Location:
+India
+Apply by:
+23 Mar 2026
 Jobseekers
 Register
 Login
@@ -6175,77 +5281,82 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F27" s="1" t="inlineStr">
-        <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G27" s="1" t="inlineStr">
+      <c r="F24" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G24" s="1" t="inlineStr">
         <is>
           <t>21-03-2026</t>
         </is>
       </c>
-      <c r="H27" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="I27" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287318</t>
+      <c r="H24" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="I24" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287890</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr"/>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>EoI – Mobile Medical Units, Ai-Enabled Tb Screening &amp; Supply Of Medical An...</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Ashray Foundation | Korba, Chattisgarh (Delivery Location), Gujarat
-International Development - EoI – Mobile Medical Units, Ai-Enabled Tb Screening &amp; Supply Of Medical And Nutritional Support, Ashray Foundation, Gujarat - DevNetJobsIndia.org
+      <c r="B25" s="1" t="inlineStr"/>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>Specialist - Grants</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Financial Management Service Foundation (FMSF) | Uttar Pradesh
+International Development - Specialist - Grants, Financial Management Service Foundation (FMSF), Uttar Pradesh - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
 Register
 Home
 Value Membership
-Broadc ... Read More</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>• Ashray Foundation invites eligible and experienced agencies to submit their Expression of Interest / for the following scope of work:
-Fabrication of Mobile Medical Units (MMUs) – 2 Units
-AI Integration &amp; Medical Equipment for TB screening (Portable X-ray) – 2 Units
-Supply of Hygiene Kits for TB support treatment on a monthly basis.
-Supply of Nutritional Kits
-Supply of Medicines (on actuals)
-Interested agencies are requested to submit their company profile along with the following mandatory documents such as Registration Certificate of the firm, PAN Card, GST Registration Certificate, Udyam Registration Certificate (if available), Bank details (Cancelled Cheque), Relevant work experience in the above-mentioned areas, supported by photographs.
-For agencies applying for the supply of medicines, hygiene kits, and nutritional kits, submission of valid registration required for medical supply
-and statutory licenses and registration required for medical supply,
-necessary approvals are mandatory. The last date for submission of the company profile and required documents is 24 February 2026.
-All documents should be sent via email to:
-tenders@ashrayfoundation.org
-. Note: Incomplete submissions or unclear copies will lead to rejection.
-• Job Email ID:
-tenders(at)ashrayfoundation.org
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Job ... Read More</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>• Joining FMSF means becoming part of a passionate team dedicated to making a positive impact. We offer competitive compensation, opportunities for professional development, and a supportive work environment where your contributions are valued and recognized. If you are committed to driving positive change, promoting accountability and strengthening the development sector, we encourage you to apply for the position of Specialist - Grants at FMSF.
+You’re Resume to be accompanied with:
+Motivational letter justifying suitability for the position – role fitment based on present &amp; past work experience
+Current/last drawn compensation &amp; expected compensation
+CVs without Motivational Letter will not be considered
+• How to Apply:
+Apply online by clicking on the link
+https://www.fmsfindia.org.in/apply-now/specialist-grants
+FMSF is an Equal Opportunity Employer.
+Please note that only the shortlisted candidates will be contacted.
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
 Apply by:
-24 Mar 2026
+21 Mar 2026
 Access all the jobs and get ahead!
 Subscribe to Value Membership Now!
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
 Lead-Finance &amp; Compliance
 Marathwada Navnirman Lokayat (Manavlok)
 Location:
@@ -6300,62 +5411,56 @@
 Bihar
 Apply by:
 11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Computer Science Trainer (School)
-Raspberry Pi Foundation
+Design and Readiness Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Program Manager – AI Skilling Initiative
+SwaTaleem Foundation
+Location:
+Haryana
+Apply by:
+05 Apr 2026
+Communications Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Director of International Programmes Impact And P...
+Confidential
 Location:
 Telangana
 Apply by:
+08 Apr 2026
+Organizational Development (OD) Manager
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Manager – Monitoring &amp; Evaluation
+Family Planning Association of India (FPA India)
+Location:
+Maharashtra
+Apply by:
 04 Apr 2026
-Computer Science Trainer (College)
-Raspberry Pi Foundation
-Location:
-Telangana
-Apply by:
-04 Apr 2026
-Nursing Aid
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Driver
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Medical Officer
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Nurse
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Physiotherapist
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Project Coordinator
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
+Officer – Instructional Design and Technical Supp...
+Room to Read India
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+RFP UNW-IND-2026-00002 for Hiring resource agency...
+UN Women
+Location:
+India
+Apply by:
+23 Mar 2026
 Jobseekers
 Register
 Login
@@ -6383,38 +5488,475 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F28" s="1" t="inlineStr">
+      <c r="F25" s="1" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G25" s="1" t="inlineStr">
+        <is>
+          <t>21-03-2026</t>
+        </is>
+      </c>
+      <c r="H25" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="I25" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287318</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr"/>
+      <c r="C26" s="1" t="inlineStr">
+        <is>
+          <t>EoI – Mobile Medical Units, Ai-Enabled Tb Screening &amp; Supply Of Medical An...</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Ashray Foundation | Korba, Chattisgarh (Delivery Location), Gujarat
+International Development - EoI – Mobile Medical Units, Ai-Enabled Tb Screening &amp; Supply Of Medical And Nutritional Support, Ashray Foundation, Gujarat - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadc ... Read More</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>• Ashray Foundation invites eligible and experienced agencies to submit their Expression of Interest / for the following scope of work:
+Fabrication of Mobile Medical Units (MMUs) – 2 Units
+AI Integration &amp; Medical Equipment for TB screening (Portable X-ray) – 2 Units
+Supply of Hygiene Kits for TB support treatment on a monthly basis.
+Supply of Nutritional Kits
+Supply of Medicines (on actuals)
+Interested agencies are requested to submit their company profile along with the following mandatory documents such as Registration Certificate of the firm, PAN Card, GST Registration Certificate, Udyam Registration Certificate (if available), Bank details (Cancelled Cheque), Relevant work experience in the above-mentioned areas, supported by photographs.
+For agencies applying for the supply of medicines, hygiene kits, and nutritional kits, submission of valid registration required for medical supply
+and statutory licenses and registration required for medical supply,
+necessary approvals are mandatory. The last date for submission of the company profile and required documents is 24 February 2026.
+All documents should be sent via email to:
+tenders@ashrayfoundation.org
+. Note: Incomplete submissions or unclear copies will lead to rejection.
+• Job Email ID:
+tenders(at)ashrayfoundation.org
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+24 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Associate (Programme Management)
+Indian Institute For Human Settlements (Iihs)
+Location:
+Karnataka
+Apply by:
+07 Mar 2026
+Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+Design and Readiness Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Program Manager – AI Skilling Initiative
+SwaTaleem Foundation
+Location:
+Haryana
+Apply by:
+05 Apr 2026
+Communications Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Director of International Programmes Impact And P...
+Confidential
+Location:
+Telangana
+Apply by:
+08 Apr 2026
+Organizational Development (OD) Manager
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Manager – Monitoring &amp; Evaluation
+Family Planning Association of India (FPA India)
+Location:
+Maharashtra
+Apply by:
+04 Apr 2026
+Officer – Instructional Design and Technical Supp...
+Room to Read India
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+RFP UNW-IND-2026-00002 for Hiring resource agency...
+UN Women
+Location:
+India
+Apply by:
+23 Mar 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F26" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G28" s="1" t="inlineStr">
+      <c r="G26" s="1" t="inlineStr">
         <is>
           <t>24-03-2026</t>
         </is>
       </c>
-      <c r="H28" s="1" t="n">
+      <c r="H26" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="I26" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287319</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="inlineStr"/>
+      <c r="C27" s="1" t="inlineStr">
+        <is>
+          <t>RFP - End of Program Evaluation Accelerating Access to Safe Water and San...</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Water.org | Bangladesh, Cambodia, India
+International Development - RFP - End of Program Evaluation  Accelerating Access to Safe Water and Sanitation, Financing, Water.org, India - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Event ... Read More</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>• The evaluation will require the firm to facilitate and coordinate with Water.org staff and partners. The program requires the firm to submit the deliverables outlined in section 2 Scope of Work.
+C.
+Water.org is not liable for any expenditure incurred by responding firms prior to issuance of an executed contract with Water.org.
+D.
+Submissions must be typed and submitted only by email and must follow the format of the requests for information in Section 5: Submissions Requirements. Unless agreed upon with Water.org, no changes or corrections to a response will be allowed after the deadline. The proposals must be submitted by email to Ms. Heather Arney (
+harney@water.org
+) and Diwakar Das (
+ddas@water.org
+). The proposal must contain a technical proposal and a financial bid using Water.org’s budgeting format.
+E.
+Proposed schedule:
+25 March 2026 – request for proposal submission due
+6 April 2026 – results announced
+27 April – engagement begins
+10 December – contract ends
+• 2. Scope of work
+A. Overview
+For 35 years, Water.org has been at the forefront of developing and delivering sustainable solutions to the global water crisis. Water.org pioneers innovative, community-driven and marketbased solutions to provide universal access to safe water and sanitation, giving women hope, children health and communities a future. To date, Water.org has positively transformed millions of lives around the world, ensuring a better life for generations ahead. More details can be found on the organization’s
+website
+.
+About the evaluation
+Water.org is concluding a nearly three
+?
+year initiative, launched in 2024, to expand its WaterCredit activities and reach more than 850,000 people in Bangladesh, Cambodia, and India with access to safe water and/or sanitation. The initiative has been implemented through two primary channels:
+WaterCredit
+: WaterCredit facilitates access to small, affordable loans for household water and sanitation solutions. Water.org provides financial and technical assistance to local financial institutions, strengthening their capacity to offer affordable water and sanitation (WSS) financing to customers at the base of the economic pyramid.
+WaterCredit via Associations
+: An evolution of the WaterCredit model, this approach engages directly with Private Water Operators (PWOs) and with associations to work with their member financial institutions and Private Water Operators (PWOs). Through these partnerships, Water.org supports the development, rollout, and scaling of WaterCredit loan products tailored for both households and PWOs.
+For detailed information, please check the complete version of the RFP attached below.
+Download Attachment:
+Water.org Project Budget - template.xls
+Download Attachment:
+Request for proposal_evaluation March 2026.pdf
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+25 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Associate (Programme Management)
+Indian Institute For Human Settlements (Iihs)
+Location:
+Karnataka
+Apply by:
+07 Mar 2026
+Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+Design and Readiness Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Program Manager – AI Skilling Initiative
+SwaTaleem Foundation
+Location:
+Haryana
+Apply by:
+05 Apr 2026
+Communications Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Director of International Programmes Impact And P...
+Confidential
+Location:
+Telangana
+Apply by:
+08 Apr 2026
+Organizational Development (OD) Manager
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Manager – Monitoring &amp; Evaluation
+Family Planning Association of India (FPA India)
+Location:
+Maharashtra
+Apply by:
+04 Apr 2026
+Officer – Instructional Design and Technical Supp...
+Room to Read India
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+RFP UNW-IND-2026-00002 for Hiring resource agency...
+UN Women
+Location:
+India
+Apply by:
+23 Mar 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F27" s="1" t="inlineStr">
+        <is>
+          <t>Governance, Safety</t>
+        </is>
+      </c>
+      <c r="G27" s="1" t="inlineStr">
+        <is>
+          <t>25-03-2026</t>
+        </is>
+      </c>
+      <c r="H27" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="I28" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287319</t>
+      <c r="I27" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287835</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr"/>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="B28" s="1" t="inlineStr"/>
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>Junior Research Technicians / Senior Project Asso...</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Starshield Security Solution Pvt.Ltd | Uttar Pradesh
 International Development - Junior Research Technicians / Senior Project Associate, Starshield Security Solution Pvt.Ltd, Uttar Pradesh - DevNetJobsIndia.org
@@ -6429,7 +5971,7 @@
 Search ... Read More</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>• Eligibility Criteria
 Qualification
@@ -6475,6 +6017,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
 Lead-Finance &amp; Compliance
 Marathwada Navnirman Lokayat (Manavlok)
 Location:
@@ -6529,62 +6077,56 @@
 Bihar
 Apply by:
 11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Computer Science Trainer (School)
-Raspberry Pi Foundation
+Design and Readiness Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Program Manager – AI Skilling Initiative
+SwaTaleem Foundation
+Location:
+Haryana
+Apply by:
+05 Apr 2026
+Communications Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Director of International Programmes Impact And P...
+Confidential
 Location:
 Telangana
 Apply by:
+08 Apr 2026
+Organizational Development (OD) Manager
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Manager – Monitoring &amp; Evaluation
+Family Planning Association of India (FPA India)
+Location:
+Maharashtra
+Apply by:
 04 Apr 2026
-Computer Science Trainer (College)
-Raspberry Pi Foundation
-Location:
-Telangana
-Apply by:
-04 Apr 2026
-Nursing Aid
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Driver
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Medical Officer
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Nurse
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Physiotherapist
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Project Coordinator
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
+Officer – Instructional Design and Technical Supp...
+Room to Read India
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+RFP UNW-IND-2026-00002 for Hiring resource agency...
+UN Women
+Location:
+India
+Apply by:
+23 Mar 2026
 Jobseekers
 Register
 Login
@@ -6612,38 +6154,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F29" s="1" t="inlineStr">
+      <c r="F28" s="1" t="inlineStr">
         <is>
           <t>Safety</t>
         </is>
       </c>
-      <c r="G29" s="1" t="inlineStr">
+      <c r="G28" s="1" t="inlineStr">
         <is>
           <t>30-03-2026</t>
         </is>
       </c>
-      <c r="H29" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="I29" s="1" t="inlineStr">
+      <c r="H28" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="I28" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287635</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B30" s="1" t="inlineStr"/>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="B29" s="1" t="inlineStr"/>
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>Agriculture Research Development Officer / Projec...</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Starshield Security Solution Pvt.Ltd | Uttar Pradesh
 International Development - Agriculture Research Development Officer / Project Scientist III, Starshield Security Solution Pvt.Ltd, Uttar Pradesh - DevNetJobsIndia.org
@@ -6657,7 +6199,7 @@
 RFPs/Tende ... Read More</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>• Eligibility Criteria
 Qualification:
@@ -6704,6 +6246,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
 Lead-Finance &amp; Compliance
 Marathwada Navnirman Lokayat (Manavlok)
 Location:
@@ -6758,62 +6306,56 @@
 Bihar
 Apply by:
 11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Computer Science Trainer (School)
-Raspberry Pi Foundation
+Design and Readiness Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Program Manager – AI Skilling Initiative
+SwaTaleem Foundation
+Location:
+Haryana
+Apply by:
+05 Apr 2026
+Communications Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Director of International Programmes Impact And P...
+Confidential
 Location:
 Telangana
 Apply by:
+08 Apr 2026
+Organizational Development (OD) Manager
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Manager – Monitoring &amp; Evaluation
+Family Planning Association of India (FPA India)
+Location:
+Maharashtra
+Apply by:
 04 Apr 2026
-Computer Science Trainer (College)
-Raspberry Pi Foundation
-Location:
-Telangana
-Apply by:
-04 Apr 2026
-Nursing Aid
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Driver
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Medical Officer
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Nurse
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Physiotherapist
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Project Coordinator
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
+Officer – Instructional Design and Technical Supp...
+Room to Read India
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+RFP UNW-IND-2026-00002 for Hiring resource agency...
+UN Women
+Location:
+India
+Apply by:
+23 Mar 2026
 Jobseekers
 Register
 Login
@@ -6841,38 +6383,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F30" s="1" t="inlineStr">
+      <c r="F29" s="1" t="inlineStr">
         <is>
           <t>Learning, Safety</t>
         </is>
       </c>
-      <c r="G30" s="1" t="inlineStr">
+      <c r="G29" s="1" t="inlineStr">
         <is>
           <t>30-03-2026</t>
         </is>
       </c>
-      <c r="H30" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="I30" s="1" t="inlineStr">
+      <c r="H29" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="I29" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287636</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr"/>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="B30" s="1" t="inlineStr"/>
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>Sector Experts</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Academy of Management Studies (AMS) | India
 International Development - Sector Experts, Academy of Management Studies (AMS), India - DevNetJobsIndia.org
@@ -6893,7 +6435,7 @@
 Jobseekers Login ... Read More</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>• Eligibility
 Postgraduate degree / Ph.D. in relevant or allied disciplines
@@ -6927,6 +6469,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
 Lead-Finance &amp; Compliance
 Marathwada Navnirman Lokayat (Manavlok)
 Location:
@@ -6981,62 +6529,56 @@
 Bihar
 Apply by:
 11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Computer Science Trainer (School)
-Raspberry Pi Foundation
+Design and Readiness Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Program Manager – AI Skilling Initiative
+SwaTaleem Foundation
+Location:
+Haryana
+Apply by:
+05 Apr 2026
+Communications Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Director of International Programmes Impact And P...
+Confidential
 Location:
 Telangana
 Apply by:
+08 Apr 2026
+Organizational Development (OD) Manager
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Manager – Monitoring &amp; Evaluation
+Family Planning Association of India (FPA India)
+Location:
+Maharashtra
+Apply by:
 04 Apr 2026
-Computer Science Trainer (College)
-Raspberry Pi Foundation
-Location:
-Telangana
-Apply by:
-04 Apr 2026
-Nursing Aid
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Driver
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Medical Officer
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Nurse
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Physiotherapist
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
-Project Coordinator
-The Catholic Health Association of India (CHAI)
-Location:
-Telangana
-Apply by:
-11 Mar 2026
+Officer – Instructional Design and Technical Supp...
+Room to Read India
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+RFP UNW-IND-2026-00002 for Hiring resource agency...
+UN Women
+Location:
+India
+Apply by:
+23 Mar 2026
 Jobseekers
 Register
 Login
@@ -7064,6 +6606,211 @@
 Recruitment Exchange</t>
         </is>
       </c>
+      <c r="F30" s="1" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G30" s="1" t="inlineStr">
+        <is>
+          <t>31-03-2026</t>
+        </is>
+      </c>
+      <c r="H30" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="I30" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287726</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="inlineStr"/>
+      <c r="C31" s="1" t="inlineStr">
+        <is>
+          <t>Associate – Finance and Operations</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Financial Management Service Foundation (FMSF) | Uttar Pradesh
+International Development - Associate – Finance and Operations, Financial Management Service Foundation (FMSF), Uttar Pradesh - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search ... Read More</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>• Joining FMSF means becoming part of a passionate team dedicated to making a positive impact. We offer competitive compensation, opportunities for professional development, and a supportive work environment where your contributions are valued and recognized. If you are committed to driving positive change, promoting accountability and strengthening the development sector, we encourage you to apply for the position of
+Associate – Finance and Operations
+at FMSF.
+You’re Resume to be accompanied with:
+Motivational letter justifying suitability for the position – role fitment based on present &amp; past work experience
+Current/last drawn compensation &amp; expected compensation
+CVs without Motivational Letter will not be considered
+FMSF is an Equal Opportunity Employer.
+Please note that only the shortlisted candidates will be contacted
+Apply Here
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+05 Apr 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Associate (Programme Management)
+Indian Institute For Human Settlements (Iihs)
+Location:
+Karnataka
+Apply by:
+07 Mar 2026
+Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+Design and Readiness Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Program Manager – AI Skilling Initiative
+SwaTaleem Foundation
+Location:
+Haryana
+Apply by:
+05 Apr 2026
+Communications Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Director of International Programmes Impact And P...
+Confidential
+Location:
+Telangana
+Apply by:
+08 Apr 2026
+Organizational Development (OD) Manager
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Manager – Monitoring &amp; Evaluation
+Family Planning Association of India (FPA India)
+Location:
+Maharashtra
+Apply by:
+04 Apr 2026
+Officer – Instructional Design and Technical Supp...
+Room to Read India
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+RFP UNW-IND-2026-00002 for Hiring resource agency...
+UN Women
+Location:
+India
+Apply by:
+23 Mar 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
       <c r="F31" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
@@ -7071,15 +6818,15 @@
       </c>
       <c r="G31" s="1" t="inlineStr">
         <is>
-          <t>31-03-2026</t>
+          <t>05-04-2026</t>
         </is>
       </c>
       <c r="H31" s="1" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I31" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287726</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287913</t>
         </is>
       </c>
     </row>
@@ -7943,6 +7690,546 @@
       <c r="I60" s="1" t="inlineStr">
         <is>
           <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_EEA_Env%20%20Sus%20awareness%20workshops_FY%2025-26%20%281%29.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>NIUA</t>
+        </is>
+      </c>
+      <c r="B61" s="1" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C61" s="1" t="inlineStr">
+        <is>
+          <t>Supply_of_Unskilled_Manpower.pdf</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr"/>
+      <c r="E61" s="2" t="inlineStr"/>
+      <c r="F61" s="1" t="inlineStr"/>
+      <c r="G61" s="1" t="inlineStr"/>
+      <c r="H61" s="1" t="inlineStr"/>
+      <c r="I61" s="1" t="inlineStr">
+        <is>
+          <t>https://niua.in/sites/default/files/tenders/Supply_of_Unskilled_Manpower.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>NIUA</t>
+        </is>
+      </c>
+      <c r="B62" s="1" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C62" s="1" t="inlineStr">
+        <is>
+          <t>Quotation_for_Rate_Contrac_Vehicle_Hiring_for_NCR_or_Outstation..pdf</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr"/>
+      <c r="E62" s="2" t="inlineStr"/>
+      <c r="F62" s="1" t="inlineStr"/>
+      <c r="G62" s="1" t="inlineStr"/>
+      <c r="H62" s="1" t="inlineStr"/>
+      <c r="I62" s="1" t="inlineStr">
+        <is>
+          <t>https://niua.in/sites/default/files/tenders/Quotation_for_Rate_Contrac_Vehicle_Hiring_for_NCR_or_Outstation..pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>NIUA</t>
+        </is>
+      </c>
+      <c r="B63" s="1" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="inlineStr">
+        <is>
+          <t>Final_RfP_UrbanShift_Preparation_of_Integrated_Green_Mobility_Plan_for_Pune.pdf</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr"/>
+      <c r="E63" s="2" t="inlineStr"/>
+      <c r="F63" s="1" t="inlineStr"/>
+      <c r="G63" s="1" t="inlineStr"/>
+      <c r="H63" s="1" t="inlineStr"/>
+      <c r="I63" s="1" t="inlineStr">
+        <is>
+          <t>https://niua.in/sites/default/files/tenders/Final_RfP_UrbanShift_Preparation_of_Integrated_Green_Mobility_Plan_for_Pune.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>NIUA</t>
+        </is>
+      </c>
+      <c r="B64" s="1" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C64" s="1" t="inlineStr">
+        <is>
+          <t>RfP_IGMP_Response to Pre-Bid Queries_200226.pdf</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr"/>
+      <c r="E64" s="2" t="inlineStr"/>
+      <c r="F64" s="1" t="inlineStr"/>
+      <c r="G64" s="1" t="inlineStr"/>
+      <c r="H64" s="1" t="inlineStr"/>
+      <c r="I64" s="1" t="inlineStr">
+        <is>
+          <t>https://niua.in/sites/default/files/tenders/RfP_IGMP_Response%20to%20Pre-Bid%20Queries_200226.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>NIUA</t>
+        </is>
+      </c>
+      <c r="B65" s="1" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="inlineStr">
+        <is>
+          <t>Corrigendum_1_RfP_IGMP.pdf</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr"/>
+      <c r="E65" s="2" t="inlineStr"/>
+      <c r="F65" s="1" t="inlineStr"/>
+      <c r="G65" s="1" t="inlineStr"/>
+      <c r="H65" s="1" t="inlineStr"/>
+      <c r="I65" s="1" t="inlineStr">
+        <is>
+          <t>https://niua.in/sites/default/files/tenders/Corrigendum_1_RfP_IGMP.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>NIUA</t>
+        </is>
+      </c>
+      <c r="B66" s="1" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="inlineStr">
+        <is>
+          <t>Corrigendum 2_IGMP.pdf</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr"/>
+      <c r="E66" s="2" t="inlineStr"/>
+      <c r="F66" s="1" t="inlineStr"/>
+      <c r="G66" s="1" t="inlineStr"/>
+      <c r="H66" s="1" t="inlineStr"/>
+      <c r="I66" s="1" t="inlineStr">
+        <is>
+          <t>https://niua.in/sites/default/files/tenders/Corrigendum%202_IGMP.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>NIUA</t>
+        </is>
+      </c>
+      <c r="B67" s="1" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C67" s="1" t="inlineStr">
+        <is>
+          <t>RFP_Engagement of GIS Expert_SCBP_2026.pdf</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr"/>
+      <c r="E67" s="2" t="inlineStr"/>
+      <c r="F67" s="1" t="inlineStr"/>
+      <c r="G67" s="1" t="inlineStr"/>
+      <c r="H67" s="1" t="inlineStr"/>
+      <c r="I67" s="1" t="inlineStr">
+        <is>
+          <t>https://niua.in/sites/default/files/tenders/RFP_Engagement%20of%20GIS%20Expert_SCBP_2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>NIUA</t>
+        </is>
+      </c>
+      <c r="B68" s="1" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C68" s="1" t="inlineStr">
+        <is>
+          <t>Response_to_Queries_Engagement_of_GIS_Expert_Agency.pdf</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr"/>
+      <c r="E68" s="2" t="inlineStr"/>
+      <c r="F68" s="1" t="inlineStr"/>
+      <c r="G68" s="1" t="inlineStr"/>
+      <c r="H68" s="1" t="inlineStr"/>
+      <c r="I68" s="1" t="inlineStr">
+        <is>
+          <t>https://niua.in/sites/default/files/tenders/Response_to_Queries_Engagement_of_GIS_Expert_Agency.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>NIUA</t>
+        </is>
+      </c>
+      <c r="B69" s="1" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C69" s="1" t="inlineStr">
+        <is>
+          <t>RfP_SRTW.pdf</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr"/>
+      <c r="E69" s="2" t="inlineStr"/>
+      <c r="F69" s="1" t="inlineStr"/>
+      <c r="G69" s="1" t="inlineStr"/>
+      <c r="H69" s="1" t="inlineStr"/>
+      <c r="I69" s="1" t="inlineStr">
+        <is>
+          <t>https://niua.in/sites/default/files/tenders/RfP_SRTW.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>NIUA</t>
+        </is>
+      </c>
+      <c r="B70" s="1" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C70" s="1" t="inlineStr">
+        <is>
+          <t>Response to Pre-Bid Queries_SRTW_for Uploading.pdf</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr"/>
+      <c r="E70" s="2" t="inlineStr"/>
+      <c r="F70" s="1" t="inlineStr"/>
+      <c r="G70" s="1" t="inlineStr"/>
+      <c r="H70" s="1" t="inlineStr"/>
+      <c r="I70" s="1" t="inlineStr">
+        <is>
+          <t>https://niua.in/sites/default/files/tenders/Response%20to%20Pre-Bid%20Queries_SRTW_for%20Uploading.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>NIUA</t>
+        </is>
+      </c>
+      <c r="B71" s="1" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C71" s="1" t="inlineStr">
+        <is>
+          <t>EOI_TECHNICAL_ASSISTANCE_UNDER_CITIIS_2.0_PROGRAM_DOMESTIC_POOL_OF_EXPERTS.pdf</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr"/>
+      <c r="E71" s="2" t="inlineStr"/>
+      <c r="F71" s="1" t="inlineStr"/>
+      <c r="G71" s="1" t="inlineStr"/>
+      <c r="H71" s="1" t="inlineStr"/>
+      <c r="I71" s="1" t="inlineStr">
+        <is>
+          <t>https://niua.in/sites/default/files/tenders/EOI_TECHNICAL_ASSISTANCE_UNDER_CITIIS_2.0_PROGRAM_DOMESTIC_POOL_OF_EXPERTS.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t>NIUA</t>
+        </is>
+      </c>
+      <c r="B72" s="1" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="inlineStr">
+        <is>
+          <t>Reply to Pre- Bid Queries - EOI for DE's under CITIIS 2.0.pdf</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr"/>
+      <c r="E72" s="2" t="inlineStr"/>
+      <c r="F72" s="1" t="inlineStr"/>
+      <c r="G72" s="1" t="inlineStr"/>
+      <c r="H72" s="1" t="inlineStr"/>
+      <c r="I72" s="1" t="inlineStr">
+        <is>
+          <t>https://niua.in/sites/default/files/tenders/Reply%20to%20Pre-%20Bid%20Queries%20-%20EOI%20for%20DE%27s%20under%20CITIIS%202.0.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>NIUA</t>
+        </is>
+      </c>
+      <c r="B73" s="1" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C73" s="1" t="inlineStr">
+        <is>
+          <t>GeM-Bidding-8666471.pdf</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr"/>
+      <c r="E73" s="2" t="inlineStr"/>
+      <c r="F73" s="1" t="inlineStr"/>
+      <c r="G73" s="1" t="inlineStr"/>
+      <c r="H73" s="1" t="inlineStr"/>
+      <c r="I73" s="1" t="inlineStr">
+        <is>
+          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-8666471.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>NIUA</t>
+        </is>
+      </c>
+      <c r="B74" s="1" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C74" s="1" t="inlineStr">
+        <is>
+          <t>corgaudt1.pdf</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr"/>
+      <c r="E74" s="2" t="inlineStr"/>
+      <c r="F74" s="1" t="inlineStr"/>
+      <c r="G74" s="1" t="inlineStr"/>
+      <c r="H74" s="1" t="inlineStr"/>
+      <c r="I74" s="1" t="inlineStr">
+        <is>
+          <t>https://niua.in/sites/default/files/tenders/corgaudt1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="inlineStr">
+        <is>
+          <t>NIUA</t>
+        </is>
+      </c>
+      <c r="B75" s="1" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C75" s="1" t="inlineStr">
+        <is>
+          <t>Corrigendum6959493.pdf</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr"/>
+      <c r="E75" s="2" t="inlineStr"/>
+      <c r="F75" s="1" t="inlineStr"/>
+      <c r="G75" s="1" t="inlineStr"/>
+      <c r="H75" s="1" t="inlineStr"/>
+      <c r="I75" s="1" t="inlineStr">
+        <is>
+          <t>https://niua.in/sites/default/files/tenders/Corrigendum6959493.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>NIUA</t>
+        </is>
+      </c>
+      <c r="B76" s="1" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C76" s="1" t="inlineStr">
+        <is>
+          <t>ADDENDUM6959493.pdf</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr"/>
+      <c r="E76" s="2" t="inlineStr"/>
+      <c r="F76" s="1" t="inlineStr"/>
+      <c r="G76" s="1" t="inlineStr"/>
+      <c r="H76" s="1" t="inlineStr"/>
+      <c r="I76" s="1" t="inlineStr">
+        <is>
+          <t>https://niua.in/sites/default/files/tenders/ADDENDUM6959493.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>NIUA</t>
+        </is>
+      </c>
+      <c r="B77" s="1" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C77" s="1" t="inlineStr">
+        <is>
+          <t>RfP CJ&amp;IP Package 03_UrbanShift.pdf</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr"/>
+      <c r="E77" s="2" t="inlineStr"/>
+      <c r="F77" s="1" t="inlineStr"/>
+      <c r="G77" s="1" t="inlineStr"/>
+      <c r="H77" s="1" t="inlineStr"/>
+      <c r="I77" s="1" t="inlineStr">
+        <is>
+          <t>https://niua.in/sites/default/files/tenders/RfP%20CJ%26IP%20Package%2003_UrbanShift.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>NIUA</t>
+        </is>
+      </c>
+      <c r="B78" s="1" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C78" s="1" t="inlineStr">
+        <is>
+          <t>Prebid reply Cj&amp;IP package 3_18.12.2025.pdf</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr"/>
+      <c r="E78" s="2" t="inlineStr"/>
+      <c r="F78" s="1" t="inlineStr"/>
+      <c r="G78" s="1" t="inlineStr"/>
+      <c r="H78" s="1" t="inlineStr"/>
+      <c r="I78" s="1" t="inlineStr">
+        <is>
+          <t>https://niua.in/sites/default/files/tenders/Prebid%20reply%20Cj%26IP%20package%203_18.12.2025.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr">
+        <is>
+          <t>NIUA</t>
+        </is>
+      </c>
+      <c r="B79" s="1" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C79" s="1" t="inlineStr">
+        <is>
+          <t>GeM-Bidding-8478801.pdf</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr"/>
+      <c r="E79" s="2" t="inlineStr"/>
+      <c r="F79" s="1" t="inlineStr"/>
+      <c r="G79" s="1" t="inlineStr"/>
+      <c r="H79" s="1" t="inlineStr"/>
+      <c r="I79" s="1" t="inlineStr">
+        <is>
+          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-8478801.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>NIUA</t>
+        </is>
+      </c>
+      <c r="B80" s="1" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C80" s="1" t="inlineStr">
+        <is>
+          <t>GeM-Bidding-8476974.pdf</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr"/>
+      <c r="E80" s="2" t="inlineStr"/>
+      <c r="F80" s="1" t="inlineStr"/>
+      <c r="G80" s="1" t="inlineStr"/>
+      <c r="H80" s="1" t="inlineStr"/>
+      <c r="I80" s="1" t="inlineStr">
+        <is>
+          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-8476974.pdf</t>
         </is>
       </c>
     </row>

--- a/all_grants.xlsx
+++ b/all_grants.xlsx
@@ -489,676 +489,10 @@
       <c r="B2" s="1" t="inlineStr"/>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>EoI - For Empanelment of agencies for Impact Assessment/ Evaluation Servic...</t>
+          <t>RFP - Onboarding Agency for Revamping Assam LMIS Dashboard</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Small Industries Development Bank of India (SIDBI) | India
-International Development - EoI - For Empanelment of agencies for Impact Assessment/ Evaluation Services under Programmes for Development and Impact, Small Industries Development Bank of India (SIDBI), India - DevNetJobsIndia.org
-Jobseekers ... Read More</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>• Please      note that all the information required as per the documents required for      responding to EOI needs to be provided. Incomplete information in these      areas may lead to non-selection.
-Modification      And/ Or Withdrawal of documents:
-Documents once submitted will      be treated as final and no further correspondence will be entertained. No      document shall be modified after the deadline for submission of documents      in response to the EOI. Also, no Respondent shall be allowed to withdraw      any document, if the Respondent happens to be a successful      Respondent.
-SIDBI      has the right to reject any or all documents received without assigning      any reason whatsoever.
-NOTE:
-SIDBI SHALL NOT BE RESPONSIBLE FOR NON-RECEIPT / NON-DELIVERY OF THE DOCUMENTS DUE TO ANY REASON, WHATSOEVER.
-Critical Information
-Events
-Particular / Date and Time
-Tender No
-SIDBI/REOI/68279
-Tender Issue Date
-13/02/2026
-Last date for seeking Clarification on EOI document
-20/02/2026
-All queries relating to the EoI must be in writing only   and to be sent via
-email on.
-pdi@sidbi.in
-and
-mayankp@sidbi.in
-Pre EOI meeting
-25/02/2026
-The meeting shall be virtual / online over MS Teams Call.   Meeting Link will be shared separately to all the bidder
-Last date for submission of EoI
-06/03/2026
-Bids to submitted through email only at:
-pdi@sidbi.in
-and
-mayankp@sidbi.in
-Independent External Monitor
-Shri Sanjay Kumar Srivastava, IAS (Retd.),
-Apartment T-6 B,
-Windsor Court, DLF Phase-IV
-Gurgaon-122009
-Mobile No-9910059472
-E-mail:
-sksrivastava7854@rediffmail.com
-Dr. Parvez Hayat, IPS (Retd.),
-B-4/69- A, Safdarjung Enclave
-New Delhi-110029
-Mobile-9810134469
-E-Mail:
-phayatips@gmail.com
-• Contact details of SIDBI officials
-Shri Mohammed Adil Ahsan
-Asst. General Manager,
-Programmes for Development &amp; Impact [PDI]
-SIDBI Tower, 15, Ashok Marg, Lucknow – 226001
-Ph: 0522-4261631
-Email:
-mdadil@sidbi.in
-Shri Mayank Prakash
-Theme Leader – Monitoring &amp; Evaluation
-Programmes for Development &amp; Impact [PDI]
-SIDBI Tower, 15, Ashok Marg, Lucknow – 226001
-Ph: 0522 - 4259 626
-Email
-mayankp@sidbi.in
-For detailed information, please check the complete version of the EoI attached below.
-Download Attachment:
-EOI for empanelment of Imapact assesment agencies_1202026.pdf
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-06 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Associate – Finance and Operations
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-Design and Readiness Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Program Manager – AI Skilling Initiative
-SwaTaleem Foundation
-Location:
-Haryana
-Apply by:
-05 Apr 2026
-Communications Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Director of International Programmes Impact And P...
-Confidential
-Location:
-Telangana
-Apply by:
-08 Apr 2026
-Organizational Development (OD) Manager
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Manager – Monitoring &amp; Evaluation
-Family Planning Association of India (FPA India)
-Location:
-Maharashtra
-Apply by:
-04 Apr 2026
-Officer – Instructional Design and Technical Supp...
-Room to Read India
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-RFP UNW-IND-2026-00002 for Hiring resource agency...
-UN Women
-Location:
-India
-Apply by:
-23 Mar 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>Governance, Learning</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>06-03-2026</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287084</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr"/>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>RFP- #2026-IN-01- Agency for economic Impact Analysis</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>PATH | Delhi
-International Development - RFP- #2026-IN-01- Agency for economic Impact Analysis, PATH, Delhi - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Login
-|
-Register
-Jobseekers Login
-Jobseekers Register
-Job ... Read More</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>• Job Email ID:
-rfpindia(at)path.org
-Download Attachment:
-Request for Proposal - RFP#2026-IN-01- Agency for economic Impact Analysis.doc
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-07 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Associate – Finance and Operations
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-Design and Readiness Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Program Manager – AI Skilling Initiative
-SwaTaleem Foundation
-Location:
-Haryana
-Apply by:
-05 Apr 2026
-Communications Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Director of International Programmes Impact And P...
-Confidential
-Location:
-Telangana
-Apply by:
-08 Apr 2026
-Organizational Development (OD) Manager
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Manager – Monitoring &amp; Evaluation
-Family Planning Association of India (FPA India)
-Location:
-Maharashtra
-Apply by:
-04 Apr 2026
-Officer – Instructional Design and Technical Supp...
-Room to Read India
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-RFP UNW-IND-2026-00002 for Hiring resource agency...
-UN Women
-Location:
-India
-Apply by:
-23 Mar 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>07-03-2026</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287460</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr"/>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>Associate (Programme Management)</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Indian Institute For Human Settlements (Iihs) | Karnataka
-International Development - Associate (Programme Management), Indian Institute For Human Settlements (Iihs), Karnataka - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events ... Read More</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>• IIHS is an equal opportunity employer that encourages women, people with disabilities and those from economically and socially excluded communities with the requisite skills and qualifications to apply for positions.
-• To apply
-If you are interested in exploring this opportunity with us, please fill the online
-application form
-by clicking here. (You can also click on the “
-Apply Now
-” button at the end of the Job Description displayed on the website).
-Contact
-Please write to us at
-hr@iihs.co.in
-if you need any clarifications while filling the online application form.
-• Job Email ID:
-hr(at)iihs.co.in
-Download Attachment:
-Associate-Programme-Management-–-ASSURE-Lighthouse-Projects.pdf
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-07 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Associate – Finance and Operations
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-Design and Readiness Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Program Manager – AI Skilling Initiative
-SwaTaleem Foundation
-Location:
-Haryana
-Apply by:
-05 Apr 2026
-Communications Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Director of International Programmes Impact And P...
-Confidential
-Location:
-Telangana
-Apply by:
-08 Apr 2026
-Organizational Development (OD) Manager
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Manager – Monitoring &amp; Evaluation
-Family Planning Association of India (FPA India)
-Location:
-Maharashtra
-Apply by:
-04 Apr 2026
-Officer – Instructional Design and Technical Supp...
-Room to Read India
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-RFP UNW-IND-2026-00002 for Hiring resource agency...
-UN Women
-Location:
-India
-Apply by:
-23 Mar 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>07-03-2026</t>
-        </is>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=285747</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr"/>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Onboarding Agency for Revamping Assam LMIS Dashboard</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>PATH | Assam
 International Development - RFP - Onboarding Agency for Revamping Assam LMIS Dashboard, PATH, Assam - DevNetJobsIndia.org
@@ -1180,7 +514,7 @@
 Jobseekers Registe ... Read More</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>• 3.2. Commercial contracting terms and conditions will be negotiated with the successful supplier at the end of the selection process.
 3.3. By submitting a proposal, the supplier confirms their agreement to abide by the RFP terms and PATH policies, including the
@@ -1335,6 +669,36 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+RFP for Data Collection for Foundational Reading ...
+Lords Education and Health Society (LEHS)
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Research Scientist – I (Non Medical)
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Technical Support - III
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Program Lead- Governance and Gender Justice
+Society for Women's Action and Training Initiativ...
+Location:
+Gujarat
+Apply by:
+25 Mar 2026
+Senior Field Officer Certification Management
+Fairtrade India Project - CSM
+Location:
+Andhra Pradesh
+Apply by:
+15 Mar 2026
 Design and Readiness Lead
 SwaTaleem Foundation
 Location:
@@ -1353,36 +717,6 @@
 Delhi
 Apply by:
 05 Apr 2026
-Director of International Programmes Impact And P...
-Confidential
-Location:
-Telangana
-Apply by:
-08 Apr 2026
-Organizational Development (OD) Manager
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Manager – Monitoring &amp; Evaluation
-Family Planning Association of India (FPA India)
-Location:
-Maharashtra
-Apply by:
-04 Apr 2026
-Officer – Instructional Design and Technical Supp...
-Room to Read India
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-RFP UNW-IND-2026-00002 for Hiring resource agency...
-UN Women
-Location:
-India
-Apply by:
-23 Mar 2026
 Jobseekers
 Register
 Login
@@ -1410,41 +744,41 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F5" s="1" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G5" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>07-03-2026</t>
         </is>
       </c>
-      <c r="H5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="1" t="inlineStr">
+      <c r="H2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287335</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr"/>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>RFQ: Construction of New gated check dams, De-siltation, and retrofitting ...</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>WaterAid India | Telangana
-International Development - RFQ: Construction of New gated check dams, De-siltation, and retrofitting of check dam in 6 villages, WaterAid India, Telangana - DevNetJobsIndia.org
+      <c r="B3" s="1" t="inlineStr"/>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>RFP- #2026-IN-01- Agency for economic Impact Analysis</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>PATH | Delhi
+International Development - RFP- #2026-IN-01- Agency for economic Impact Analysis, PATH, Delhi - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
@@ -1454,20 +788,27 @@
 Broadcast Resume
 RFPs/Tenders
 Search Jobs
-E ... Read More</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+Events
+Jobseekers:
+Login
+|
+Register
+Jobseekers Login
+Jobseekers Register
+Job ... Read More</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>• Job Email ID:
-WAIProcurementAP(at)wateraid.org
+rfpindia(at)path.org
 Download Attachment:
-Tender Notice-15 check dams-Jalsankalp-19.02.26_compressed.pdf
+Request for Proposal - RFP#2026-IN-01- Agency for economic Impact Analysis.doc
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
 Apply by:
-08 Mar 2026
+07 Mar 2026
 Access all the jobs and get ahead!
 Subscribe to Value Membership Now!
 Subscribe
@@ -1535,6 +876,36 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+RFP for Data Collection for Foundational Reading ...
+Lords Education and Health Society (LEHS)
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Research Scientist – I (Non Medical)
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Technical Support - III
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Program Lead- Governance and Gender Justice
+Society for Women's Action and Training Initiativ...
+Location:
+Gujarat
+Apply by:
+25 Mar 2026
+Senior Field Officer Certification Management
+Fairtrade India Project - CSM
+Location:
+Andhra Pradesh
+Apply by:
+15 Mar 2026
 Design and Readiness Lead
 SwaTaleem Foundation
 Location:
@@ -1553,36 +924,6 @@
 Delhi
 Apply by:
 05 Apr 2026
-Director of International Programmes Impact And P...
-Confidential
-Location:
-Telangana
-Apply by:
-08 Apr 2026
-Organizational Development (OD) Manager
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Manager – Monitoring &amp; Evaluation
-Family Planning Association of India (FPA India)
-Location:
-Maharashtra
-Apply by:
-04 Apr 2026
-Officer – Instructional Design and Technical Supp...
-Room to Read India
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-RFP UNW-IND-2026-00002 for Hiring resource agency...
-UN Women
-Location:
-India
-Apply by:
-23 Mar 2026
 Jobseekers
 Register
 Login
@@ -1610,38 +951,449 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F6" s="1" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>07-03-2026</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287460</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr"/>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Associate (Programme Management)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Indian Institute For Human Settlements (Iihs) | Karnataka
+International Development - Associate (Programme Management), Indian Institute For Human Settlements (Iihs), Karnataka - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events ... Read More</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>• IIHS is an equal opportunity employer that encourages women, people with disabilities and those from economically and socially excluded communities with the requisite skills and qualifications to apply for positions.
+• To apply
+If you are interested in exploring this opportunity with us, please fill the online
+application form
+by clicking here. (You can also click on the “
+Apply Now
+” button at the end of the Job Description displayed on the website).
+Contact
+Please write to us at
+hr@iihs.co.in
+if you need any clarifications while filling the online application form.
+• Job Email ID:
+hr(at)iihs.co.in
+Download Attachment:
+Associate-Programme-Management-–-ASSURE-Lighthouse-Projects.pdf
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+07 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Associate (Programme Management)
+Indian Institute For Human Settlements (Iihs)
+Location:
+Karnataka
+Apply by:
+07 Mar 2026
+Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+RFP for Data Collection for Foundational Reading ...
+Lords Education and Health Society (LEHS)
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Research Scientist – I (Non Medical)
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Technical Support - III
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Program Lead- Governance and Gender Justice
+Society for Women's Action and Training Initiativ...
+Location:
+Gujarat
+Apply by:
+25 Mar 2026
+Senior Field Officer Certification Management
+Fairtrade India Project - CSM
+Location:
+Andhra Pradesh
+Apply by:
+15 Mar 2026
+Design and Readiness Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Program Manager – AI Skilling Initiative
+SwaTaleem Foundation
+Location:
+Haryana
+Apply by:
+05 Apr 2026
+Communications Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>07-03-2026</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=285747</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr"/>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>RFQ: Construction of New gated check dams, De-siltation, and retrofitting ...</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>WaterAid India | Telangana
+International Development - RFQ: Construction of New gated check dams, De-siltation, and retrofitting of check dam in 6 villages, WaterAid India, Telangana - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+E ... Read More</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>• Job Email ID:
+WAIProcurementAP(at)wateraid.org
+Download Attachment:
+Tender Notice-15 check dams-Jalsankalp-19.02.26_compressed.pdf
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+08 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Associate (Programme Management)
+Indian Institute For Human Settlements (Iihs)
+Location:
+Karnataka
+Apply by:
+07 Mar 2026
+Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+RFP for Data Collection for Foundational Reading ...
+Lords Education and Health Society (LEHS)
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Research Scientist – I (Non Medical)
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Technical Support - III
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Program Lead- Governance and Gender Justice
+Society for Women's Action and Training Initiativ...
+Location:
+Gujarat
+Apply by:
+25 Mar 2026
+Senior Field Officer Certification Management
+Fairtrade India Project - CSM
+Location:
+Andhra Pradesh
+Apply by:
+15 Mar 2026
+Design and Readiness Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Program Manager – AI Skilling Initiative
+SwaTaleem Foundation
+Location:
+Haryana
+Apply by:
+05 Apr 2026
+Communications Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G6" s="1" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>08-03-2026</t>
         </is>
       </c>
-      <c r="H6" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I6" s="1" t="inlineStr">
+      <c r="H5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287784</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr"/>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="B6" s="1" t="inlineStr"/>
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>RFP - Final Evaluation of the Bhoomi Ka Programme</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Deutsche Welthungerhilfe | India
 International Development - RFP - Final Evaluation of the Bhoomi Ka Programme, Deutsche Welthungerhilfe, India - DevNetJobsIndia.org
@@ -1662,7 +1414,7 @@
 Jobs ... Read More</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>• INTRODUCTION AND CONTEXT
 Country:
@@ -1792,6 +1544,36 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+RFP for Data Collection for Foundational Reading ...
+Lords Education and Health Society (LEHS)
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Research Scientist – I (Non Medical)
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Technical Support - III
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Program Lead- Governance and Gender Justice
+Society for Women's Action and Training Initiativ...
+Location:
+Gujarat
+Apply by:
+25 Mar 2026
+Senior Field Officer Certification Management
+Fairtrade India Project - CSM
+Location:
+Andhra Pradesh
+Apply by:
+15 Mar 2026
 Design and Readiness Lead
 SwaTaleem Foundation
 Location:
@@ -1810,36 +1592,6 @@
 Delhi
 Apply by:
 05 Apr 2026
-Director of International Programmes Impact And P...
-Confidential
-Location:
-Telangana
-Apply by:
-08 Apr 2026
-Organizational Development (OD) Manager
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Manager – Monitoring &amp; Evaluation
-Family Planning Association of India (FPA India)
-Location:
-Maharashtra
-Apply by:
-04 Apr 2026
-Officer – Instructional Design and Technical Supp...
-Room to Read India
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-RFP UNW-IND-2026-00002 for Hiring resource agency...
-UN Women
-Location:
-India
-Apply by:
-23 Mar 2026
 Jobseekers
 Register
 Login
@@ -1867,49 +1619,48 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F7" s="1" t="inlineStr">
+      <c r="F6" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G7" s="1" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>08-03-2026</t>
         </is>
       </c>
-      <c r="H7" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I7" s="1" t="inlineStr">
+      <c r="H6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287384</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr"/>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>RFP For The Contractors To Procure, Build, Install, Supply Chlorine Tablet...</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>RFP For Selection of an Implementation Support Agency (Isa) For Capacity B...</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>EAII Advisors Pvt Ltd | Andhra Pradesh
-International Development - RFP For The Contractors To Procure, Build, Install, Supply Chlorine Tablets, Operate And Maintain Tablet-Based In Line Chlorination Devices, EAII Advisors Pvt Ltd, Andhra Pradesh - DevNetJobsIndia.org
+International Development - RFP For Selection of an Implementation Support Agency (Isa) For Capacity Building Of Community Leaders To Conduct Community Engagement Activities, EAII Advisors Pvt Ltd, Andhra Pradesh - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
-Register
-Ho ... Read More</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+Regis ... Read More</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>• Proposal Requirements
 1. Company Background and Details
@@ -1919,9 +1670,9 @@
 Kindly fill in the column “Bidder Response”. The current inputs are guiding inputs or choices for answers. Kindly fill in accordingly.
 For detailed information, please check the complete version of the RFP attached below.
 Download Attachment:
-Standalone IC RFP Technical Evaluation Response Template.docx
+Standalone ISA RFP Technical Evaluation Response Template (1).docx
 Download Attachment:
-Telugu_Standalone IC RFP Technical Evaluation Response Template.docx
+Telugu_Standalone ISA RFP Technical Evaluation Response Template.docx
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
@@ -1994,6 +1745,36 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+RFP for Data Collection for Foundational Reading ...
+Lords Education and Health Society (LEHS)
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Research Scientist – I (Non Medical)
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Technical Support - III
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Program Lead- Governance and Gender Justice
+Society for Women's Action and Training Initiativ...
+Location:
+Gujarat
+Apply by:
+25 Mar 2026
+Senior Field Officer Certification Management
+Fairtrade India Project - CSM
+Location:
+Andhra Pradesh
+Apply by:
+15 Mar 2026
 Design and Readiness Lead
 SwaTaleem Foundation
 Location:
@@ -2012,36 +1793,6 @@
 Delhi
 Apply by:
 05 Apr 2026
-Director of International Programmes Impact And P...
-Confidential
-Location:
-Telangana
-Apply by:
-08 Apr 2026
-Organizational Development (OD) Manager
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Manager – Monitoring &amp; Evaluation
-Family Planning Association of India (FPA India)
-Location:
-Maharashtra
-Apply by:
-04 Apr 2026
-Officer – Instructional Design and Technical Supp...
-Room to Read India
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-RFP UNW-IND-2026-00002 for Hiring resource agency...
-UN Women
-Location:
-India
-Apply by:
-23 Mar 2026
 Jobseekers
 Register
 Login
@@ -2069,9 +1820,59 @@
 Recruitment Exchange</t>
         </is>
       </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>Governance, Learning</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>09-03-2026</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=285950</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr"/>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>RFP - Early-Stage Impact Assessment-CDRI SWP 23-26</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Coalition for Disaster Resilient Infrastructure (CDRI) | India
+International Development - RFP - Early-Stage Impact Assessment-CDRI SWP 23-26, Coalition for Disaster Resilient Infrastructure (CDRI), India - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs ... Read More</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="F8" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Climate, Governance</t>
         </is>
       </c>
       <c r="G8" s="1" t="inlineStr">
@@ -2080,11 +1881,11 @@
         </is>
       </c>
       <c r="H8" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I8" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=285949</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287093</t>
         </is>
       </c>
     </row>
@@ -2192,6 +1993,36 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+RFP for Data Collection for Foundational Reading ...
+Lords Education and Health Society (LEHS)
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Research Scientist – I (Non Medical)
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Technical Support - III
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Program Lead- Governance and Gender Justice
+Society for Women's Action and Training Initiativ...
+Location:
+Gujarat
+Apply by:
+25 Mar 2026
+Senior Field Officer Certification Management
+Fairtrade India Project - CSM
+Location:
+Andhra Pradesh
+Apply by:
+15 Mar 2026
 Design and Readiness Lead
 SwaTaleem Foundation
 Location:
@@ -2210,36 +2041,6 @@
 Delhi
 Apply by:
 05 Apr 2026
-Director of International Programmes Impact And P...
-Confidential
-Location:
-Telangana
-Apply by:
-08 Apr 2026
-Organizational Development (OD) Manager
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Manager – Monitoring &amp; Evaluation
-Family Planning Association of India (FPA India)
-Location:
-Maharashtra
-Apply by:
-04 Apr 2026
-Officer – Instructional Design and Technical Supp...
-Room to Read India
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-RFP UNW-IND-2026-00002 for Hiring resource agency...
-UN Women
-Location:
-India
-Apply by:
-23 Mar 2026
 Jobseekers
 Register
 Login
@@ -2278,7 +2079,7 @@
         </is>
       </c>
       <c r="H9" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I9" s="1" t="inlineStr">
         <is>
@@ -2295,70 +2096,21 @@
       <c r="B10" s="1" t="inlineStr"/>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>RFP - Early-Stage Impact Assessment-CDRI SWP 23-26</t>
+          <t>RFP For The Contractors To Procure, Build, Install, Supply Chlorine Tablet...</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Coalition for Disaster Resilient Infrastructure (CDRI) | India
-International Development - RFP - Early-Stage Impact Assessment-CDRI SWP 23-26, Coalition for Disaster Resilient Infrastructure (CDRI), India - DevNetJobsIndia.org
+          <t>EAII Advisors Pvt Ltd | Andhra Pradesh
+International Development - RFP For The Contractors To Procure, Build, Install, Supply Chlorine Tablets, Operate And Maintain Tablet-Based In Line Chlorination Devices, EAII Advisors Pvt Ltd, Andhra Pradesh - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
 Register
-Home
-Value Membership
-Broadcast Resume
-RFPs ... Read More</t>
+Ho ... Read More</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>Climate, Governance</t>
-        </is>
-      </c>
-      <c r="G10" s="1" t="inlineStr">
-        <is>
-          <t>09-03-2026</t>
-        </is>
-      </c>
-      <c r="H10" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="I10" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287093</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="inlineStr"/>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>RFP For Selection of an Implementation Support Agency (Isa) For Capacity B...</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>EAII Advisors Pvt Ltd | Andhra Pradesh
-International Development - RFP For Selection of an Implementation Support Agency (Isa) For Capacity Building Of Community Leaders To Conduct Community Engagement Activities, EAII Advisors Pvt Ltd, Andhra Pradesh - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Regis ... Read More</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>• Proposal Requirements
 1. Company Background and Details
@@ -2368,9 +2120,9 @@
 Kindly fill in the column “Bidder Response”. The current inputs are guiding inputs or choices for answers. Kindly fill in accordingly.
 For detailed information, please check the complete version of the RFP attached below.
 Download Attachment:
-Standalone ISA RFP Technical Evaluation Response Template (1).docx
+Standalone IC RFP Technical Evaluation Response Template.docx
 Download Attachment:
-Telugu_Standalone ISA RFP Technical Evaluation Response Template.docx
+Telugu_Standalone IC RFP Technical Evaluation Response Template.docx
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
@@ -2443,6 +2195,36 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+RFP for Data Collection for Foundational Reading ...
+Lords Education and Health Society (LEHS)
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Research Scientist – I (Non Medical)
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Technical Support - III
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Program Lead- Governance and Gender Justice
+Society for Women's Action and Training Initiativ...
+Location:
+Gujarat
+Apply by:
+25 Mar 2026
+Senior Field Officer Certification Management
+Fairtrade India Project - CSM
+Location:
+Andhra Pradesh
+Apply by:
+15 Mar 2026
 Design and Readiness Lead
 SwaTaleem Foundation
 Location:
@@ -2461,36 +2243,6 @@
 Delhi
 Apply by:
 05 Apr 2026
-Director of International Programmes Impact And P...
-Confidential
-Location:
-Telangana
-Apply by:
-08 Apr 2026
-Organizational Development (OD) Manager
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Manager – Monitoring &amp; Evaluation
-Family Planning Association of India (FPA India)
-Location:
-Maharashtra
-Apply by:
-04 Apr 2026
-Officer – Instructional Design and Technical Supp...
-Room to Read India
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-RFP UNW-IND-2026-00002 for Hiring resource agency...
-UN Women
-Location:
-India
-Apply by:
-23 Mar 2026
 Jobseekers
 Register
 Login
@@ -2518,38 +2270,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>Governance, Learning</t>
-        </is>
-      </c>
-      <c r="G11" s="1" t="inlineStr">
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>09-03-2026</t>
         </is>
       </c>
-      <c r="H11" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="I11" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=285950</t>
+      <c r="H10" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=285949</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr"/>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr"/>
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>RFP - for Supply of Skill Lab Items</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>TeamLease Foundation | India
 International Development - RFP - for Supply of Skill Lab Items, TeamLease Foundation, India - DevNetJobsIndia.org
@@ -2571,7 +2323,7 @@
 Jobseeker ... Read More</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>• Technical Bid Submission Link-
 https://forms.gle/V9iy35ddb4kWEb468
@@ -2678,6 +2430,36 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+RFP for Data Collection for Foundational Reading ...
+Lords Education and Health Society (LEHS)
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Research Scientist – I (Non Medical)
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Technical Support - III
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Program Lead- Governance and Gender Justice
+Society for Women's Action and Training Initiativ...
+Location:
+Gujarat
+Apply by:
+25 Mar 2026
+Senior Field Officer Certification Management
+Fairtrade India Project - CSM
+Location:
+Andhra Pradesh
+Apply by:
+15 Mar 2026
 Design and Readiness Lead
 SwaTaleem Foundation
 Location:
@@ -2696,36 +2478,6 @@
 Delhi
 Apply by:
 05 Apr 2026
-Director of International Programmes Impact And P...
-Confidential
-Location:
-Telangana
-Apply by:
-08 Apr 2026
-Organizational Development (OD) Manager
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Manager – Monitoring &amp; Evaluation
-Family Planning Association of India (FPA India)
-Location:
-Maharashtra
-Apply by:
-04 Apr 2026
-Officer – Instructional Design and Technical Supp...
-Room to Read India
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-RFP UNW-IND-2026-00002 for Hiring resource agency...
-UN Women
-Location:
-India
-Apply by:
-23 Mar 2026
 Jobseekers
 Register
 Login
@@ -2753,44 +2505,44 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F12" s="1" t="inlineStr">
+      <c r="F11" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G12" s="1" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>11-03-2026</t>
         </is>
       </c>
-      <c r="H12" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="I12" s="1" t="inlineStr">
+      <c r="H11" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287613</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr"/>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="B12" s="1" t="inlineStr"/>
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>RFP - Study On SC-DMPA In Rajasthan- Clients And Providers Perspectives On...</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Centre For Community Economics And Development Consultants Society- CECOEDECON | Jaipur, Rajasthan
 International Development - RFP - Study On SC-DMPA In Rajasthan- Clients And Providers Perspectives On SC-DMPA In Rajasthan, Centre For Community Economics And Development Consultants Society- CECOEDE ... Read More</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>• Despite India’s achievement of replacement-level fertility, unmet need for contraception—particularly for spacing methods—remains substantial, with modern contraceptive use at 56.4% (2019–21), highlighting persistent gaps in access and choice, especially among vulnerable populations. Expanding the contraceptive method mix through innovative, user-centred approaches is therefore essential to meeting national commitments under FP2030 and the Sustainable Development Goals. In this context, the Government of India’s introduction of subcutaneous DMPA (DMPA-SC) as a self-care option under the National Family Planning Programme in 2023 represents a strategic step toward enhancing women’s autonomy, privacy, and convenience in contraceptive use. Global and national evidence indicates strong feasibility and acceptability of self-administered DMPA-SC among both users and providers; however, successful implementation requires an in-depth understanding of user experiences and health system readiness. This study, to be conducted in Jaipur-1, Jaisalmer and Sawai Madhopur districts of Rajasthan, aims to examine the perspectives &amp; experience of current SC-DMPA users and explore healthcare providers’ views on enabling and generating actionable evidence to inform effective scale-up of SC-DMPA within India’s public health system.
 CECOEDECON, with support from UNFPA, is implementing the roll-out of subcutaneous DMPA (SC-DMPA) in selected pilot districts of Rajasthan in the public health facilities, in collaboration with the Department of Health &amp; Family Welfare, Government of Rajasthan.
@@ -2925,6 +2677,36 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+RFP for Data Collection for Foundational Reading ...
+Lords Education and Health Society (LEHS)
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Research Scientist – I (Non Medical)
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Technical Support - III
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Program Lead- Governance and Gender Justice
+Society for Women's Action and Training Initiativ...
+Location:
+Gujarat
+Apply by:
+25 Mar 2026
+Senior Field Officer Certification Management
+Fairtrade India Project - CSM
+Location:
+Andhra Pradesh
+Apply by:
+15 Mar 2026
 Design and Readiness Lead
 SwaTaleem Foundation
 Location:
@@ -2943,36 +2725,6 @@
 Delhi
 Apply by:
 05 Apr 2026
-Director of International Programmes Impact And P...
-Confidential
-Location:
-Telangana
-Apply by:
-08 Apr 2026
-Organizational Development (OD) Manager
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Manager – Monitoring &amp; Evaluation
-Family Planning Association of India (FPA India)
-Location:
-Maharashtra
-Apply by:
-04 Apr 2026
-Officer – Instructional Design and Technical Supp...
-Room to Read India
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-RFP UNW-IND-2026-00002 for Hiring resource agency...
-UN Women
-Location:
-India
-Apply by:
-23 Mar 2026
 Jobseekers
 Register
 Login
@@ -3000,38 +2752,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F13" s="1" t="inlineStr">
+      <c r="F12" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G13" s="1" t="inlineStr">
+      <c r="G12" s="1" t="inlineStr">
         <is>
           <t>11-03-2026</t>
         </is>
       </c>
-      <c r="H13" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="I13" s="1" t="inlineStr">
+      <c r="H12" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287322</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr"/>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="B13" s="1" t="inlineStr"/>
+      <c r="C13" s="1" t="inlineStr">
         <is>
           <t>SOW - Engagement of a Public Relations (PR) Agency on Retainer</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Room to Read India | India
 International Development - SOW - Engagement of a Public Relations (PR) Agency on Retainer, Room to Read India, India - DevNetJobsIndia.org
@@ -3052,7 +2804,7 @@
 Job ... Read More</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>• Scope of Work (SOW)
 Engagement of a Public Relations (PR) Agency on Retainer
@@ -3182,6 +2934,36 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+RFP for Data Collection for Foundational Reading ...
+Lords Education and Health Society (LEHS)
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Research Scientist – I (Non Medical)
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Technical Support - III
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Program Lead- Governance and Gender Justice
+Society for Women's Action and Training Initiativ...
+Location:
+Gujarat
+Apply by:
+25 Mar 2026
+Senior Field Officer Certification Management
+Fairtrade India Project - CSM
+Location:
+Andhra Pradesh
+Apply by:
+15 Mar 2026
 Design and Readiness Lead
 SwaTaleem Foundation
 Location:
@@ -3200,36 +2982,6 @@
 Delhi
 Apply by:
 05 Apr 2026
-Director of International Programmes Impact And P...
-Confidential
-Location:
-Telangana
-Apply by:
-08 Apr 2026
-Organizational Development (OD) Manager
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Manager – Monitoring &amp; Evaluation
-Family Planning Association of India (FPA India)
-Location:
-Maharashtra
-Apply by:
-04 Apr 2026
-Officer – Instructional Design and Technical Supp...
-Room to Read India
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-RFP UNW-IND-2026-00002 for Hiring resource agency...
-UN Women
-Location:
-India
-Apply by:
-23 Mar 2026
 Jobseekers
 Register
 Login
@@ -3257,14 +3009,227 @@
 Recruitment Exchange</t>
         </is>
       </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>Governance, Learning</t>
+        </is>
+      </c>
+      <c r="G13" s="1" t="inlineStr">
+        <is>
+          <t>12-03-2026</t>
+        </is>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I13" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287648</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr"/>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>RFP - for Internal Audit</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>India HIV/AIDS Alliance (Alliance India) | Delhi
+International Development - RFP - for Internal Audit, India HIV/AIDS Alliance (Alliance India), Delhi - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers:
+Login
+|
+Regist ... Read More</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>• Alliance India reserves the right to reject applications that do not meet eligibility or application submission requirements (as detailed above) without further notice to the applicant. Issuance of this RFP does not constitute an award commitment or a guarantee of business on the part of Alliance India, nor does it commit Alliance India to pay for the costs incurred in submitting the application. Further, Alliance India reserves the right to reject any or all applications received and negotiate separately with an applicant if such action is considered in the best interest of Alliance India/ project.
+iii.
+Queries, Response and Submission
+Queries regarding this RFP will be sent only to procurement@allianceindia.org by March 07, 2026. Alliance India shall collaborate and respond to all meaningful queries from prospective applicants by March 10, 2026. Responses to questions shall be compiled and sent to all the applicants who raised the queries through email only. ALLIANCE INDIA is under no obligation to consider or respond to questions that are not received on time.
+iv.
+• Submission of bids
+The bid has to be submitted in the prescribed format on or before March 13, 2026 by 5 p.m. Indian Standard Time to
+procurement@allianceindia.org
+For the detailed version of the Request for Proposal, please refer to the RFP attached.
+• Job Email ID:
+procurement(at)allianceindia.org
+Download Attachment:
+RFP for Internal Audit - FY 2025-26.doc
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+13 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Associate (Programme Management)
+Indian Institute For Human Settlements (Iihs)
+Location:
+Karnataka
+Apply by:
+07 Mar 2026
+Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+RFP for Data Collection for Foundational Reading ...
+Lords Education and Health Society (LEHS)
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Research Scientist – I (Non Medical)
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Technical Support - III
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Program Lead- Governance and Gender Justice
+Society for Women's Action and Training Initiativ...
+Location:
+Gujarat
+Apply by:
+25 Mar 2026
+Senior Field Officer Certification Management
+Fairtrade India Project - CSM
+Location:
+Andhra Pradesh
+Apply by:
+15 Mar 2026
+Design and Readiness Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Program Manager – AI Skilling Initiative
+SwaTaleem Foundation
+Location:
+Haryana
+Apply by:
+05 Apr 2026
+Communications Lead
+SwaTaleem Foundation
+Location:
+Delhi
+Apply by:
+05 Apr 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
       <c r="F14" s="1" t="inlineStr">
         <is>
-          <t>Governance, Learning</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G14" s="1" t="inlineStr">
         <is>
-          <t>12-03-2026</t>
+          <t>13-03-2026</t>
         </is>
       </c>
       <c r="H14" s="1" t="n">
@@ -3272,7 +3237,7 @@
       </c>
       <c r="I14" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287648</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287765</t>
         </is>
       </c>
     </row>
@@ -3415,6 +3380,36 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+RFP for Data Collection for Foundational Reading ...
+Lords Education and Health Society (LEHS)
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Research Scientist – I (Non Medical)
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Technical Support - III
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Program Lead- Governance and Gender Justice
+Society for Women's Action and Training Initiativ...
+Location:
+Gujarat
+Apply by:
+25 Mar 2026
+Senior Field Officer Certification Management
+Fairtrade India Project - CSM
+Location:
+Andhra Pradesh
+Apply by:
+15 Mar 2026
 Design and Readiness Lead
 SwaTaleem Foundation
 Location:
@@ -3433,36 +3428,6 @@
 Delhi
 Apply by:
 05 Apr 2026
-Director of International Programmes Impact And P...
-Confidential
-Location:
-Telangana
-Apply by:
-08 Apr 2026
-Organizational Development (OD) Manager
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Manager – Monitoring &amp; Evaluation
-Family Planning Association of India (FPA India)
-Location:
-Maharashtra
-Apply by:
-04 Apr 2026
-Officer – Instructional Design and Technical Supp...
-Room to Read India
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-RFP UNW-IND-2026-00002 for Hiring resource agency...
-UN Women
-Location:
-India
-Apply by:
-23 Mar 2026
 Jobseekers
 Register
 Login
@@ -3501,7 +3466,7 @@
         </is>
       </c>
       <c r="H15" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I15" s="1" t="inlineStr">
         <is>
@@ -3518,13 +3483,13 @@
       <c r="B16" s="1" t="inlineStr"/>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>RFP - for Internal Audit</t>
+          <t>ToR - Portfolio-Wide Learning Exercise cum review for the Health Domain</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>India HIV/AIDS Alliance (Alliance India) | Delhi
-International Development - RFP - for Internal Audit, India HIV/AIDS Alliance (Alliance India), Delhi - DevNetJobsIndia.org
+          <t>ChildFund India | India
+International Development - ToR - Portfolio-Wide Learning Exercise cum review for the Health Domain, ChildFund India, India - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
@@ -3538,29 +3503,20 @@
 Jobseekers:
 Login
 |
-Regist ... Read More</t>
+Register ... Read More</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>• Alliance India reserves the right to reject applications that do not meet eligibility or application submission requirements (as detailed above) without further notice to the applicant. Issuance of this RFP does not constitute an award commitment or a guarantee of business on the part of Alliance India, nor does it commit Alliance India to pay for the costs incurred in submitting the application. Further, Alliance India reserves the right to reject any or all applications received and negotiate separately with an applicant if such action is considered in the best interest of Alliance India/ project.
-iii.
-Queries, Response and Submission
-Queries regarding this RFP will be sent only to procurement@allianceindia.org by March 07, 2026. Alliance India shall collaborate and respond to all meaningful queries from prospective applicants by March 10, 2026. Responses to questions shall be compiled and sent to all the applicants who raised the queries through email only. ALLIANCE INDIA is under no obligation to consider or respond to questions that are not received on time.
-iv.
-• Submission of bids
-The bid has to be submitted in the prescribed format on or before March 13, 2026 by 5 p.m. Indian Standard Time to
-procurement@allianceindia.org
-For the detailed version of the Request for Proposal, please refer to the RFP attached.
-• Job Email ID:
-procurement(at)allianceindia.org
+          <t>• Job Email ID:
+centralpurchase2(at)childfundindia.org
 Download Attachment:
-RFP for Internal Audit - FY 2025-26.doc
+TOR  Health Portfolio_23.2.2026.doc
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
 Apply by:
-13 Mar 2026
+15 Mar 2026
 Access all the jobs and get ahead!
 Subscribe to Value Membership Now!
 Subscribe
@@ -3628,6 +3584,36 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+RFP for Data Collection for Foundational Reading ...
+Lords Education and Health Society (LEHS)
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Research Scientist – I (Non Medical)
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Technical Support - III
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Program Lead- Governance and Gender Justice
+Society for Women's Action and Training Initiativ...
+Location:
+Gujarat
+Apply by:
+25 Mar 2026
+Senior Field Officer Certification Management
+Fairtrade India Project - CSM
+Location:
+Andhra Pradesh
+Apply by:
+15 Mar 2026
 Design and Readiness Lead
 SwaTaleem Foundation
 Location:
@@ -3646,36 +3632,6 @@
 Delhi
 Apply by:
 05 Apr 2026
-Director of International Programmes Impact And P...
-Confidential
-Location:
-Telangana
-Apply by:
-08 Apr 2026
-Organizational Development (OD) Manager
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Manager – Monitoring &amp; Evaluation
-Family Planning Association of India (FPA India)
-Location:
-Maharashtra
-Apply by:
-04 Apr 2026
-Officer – Instructional Design and Technical Supp...
-Room to Read India
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-RFP UNW-IND-2026-00002 for Hiring resource agency...
-UN Women
-Location:
-India
-Apply by:
-23 Mar 2026
 Jobseekers
 Register
 Login
@@ -3705,20 +3661,20 @@
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Learning, Safety</t>
         </is>
       </c>
       <c r="G16" s="1" t="inlineStr">
         <is>
-          <t>13-03-2026</t>
+          <t>15-03-2026</t>
         </is>
       </c>
       <c r="H16" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I16" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287765</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287901</t>
         </is>
       </c>
     </row>
@@ -3731,13 +3687,13 @@
       <c r="B17" s="1" t="inlineStr"/>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>ToR - Strategic Review and Forward-Looking Education Strategy Development</t>
+          <t>RFP for Data Collection for Foundational Reading Tool in Odisha</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>ChildFund India | India
-International Development - ToR - Strategic Review and Forward-Looking Education Strategy Development, ChildFund India, India - DevNetJobsIndia.org
+          <t>Lords Education and Health Society (LEHS) | Odisha
+International Development - RFP for Data Collection for Foundational Reading Tool in Odisha, Lords Education and Health Society (LEHS), Odisha - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
@@ -3746,20 +3702,36 @@
 Value Membership
 Broadcast Resume
 RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Login
-|
-Registe ... Read More</t>
+Se ... Read More</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>• Job Email ID:
-centralpurchase2(at)childfundindia.org
+          <t>• 4. SCOPE OF WORK
+Summary of Activities
+S.No
+Activity   Description
+Timelines
+1
+Data   Collection: students' reading of textual items   (letters/words/non-words/paragraphs) in Odia &amp; English languages for   Grades 1-8.
+Data       Collection should be completed in   April 2026
+Details of the Activity Below:
+Data Collection: Collect audio data of students reading texts in Odia &amp; English from Grade 1-8
+Total Number of Hours to be collected: ~360 hours for the Odia language
+Total Number of Hours to be collected: ~115 hours for the English language
+• Submission Details
+All proposals to this RFP must be received no later than &lt;15th March 2026&gt;
+.
+The proposal should be submitted only through e-mail in PDF format addressed to the Procurement Team at:
+rfp.lehs@wadhwaniai.org
+. The email's subject line must contain the reference number and title of the RFP: Data Collection for Foundational Reading
+Tool in Odisha  (Name of Partner)
+Any proposals received by Wadhwani-AI after the deadline prescribed in the timeline of this document are liable to be rejected.
+For detailed information, please check the complete version of the RFP attached below
+• Job Email ID:
+rfp.lehs(at)wadhwaniai.org
 Download Attachment:
-ToR for Education.doc
+RFP for Data Collection for Foundational Reading Tool in Odisha.pdf
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
@@ -3832,6 +3804,36 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+RFP for Data Collection for Foundational Reading ...
+Lords Education and Health Society (LEHS)
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Research Scientist – I (Non Medical)
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Technical Support - III
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Program Lead- Governance and Gender Justice
+Society for Women's Action and Training Initiativ...
+Location:
+Gujarat
+Apply by:
+25 Mar 2026
+Senior Field Officer Certification Management
+Fairtrade India Project - CSM
+Location:
+Andhra Pradesh
+Apply by:
+15 Mar 2026
 Design and Readiness Lead
 SwaTaleem Foundation
 Location:
@@ -3850,36 +3852,6 @@
 Delhi
 Apply by:
 05 Apr 2026
-Director of International Programmes Impact And P...
-Confidential
-Location:
-Telangana
-Apply by:
-08 Apr 2026
-Organizational Development (OD) Manager
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Manager – Monitoring &amp; Evaluation
-Family Planning Association of India (FPA India)
-Location:
-Maharashtra
-Apply by:
-04 Apr 2026
-Officer – Instructional Design and Technical Supp...
-Room to Read India
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-RFP UNW-IND-2026-00002 for Hiring resource agency...
-UN Women
-Location:
-India
-Apply by:
-23 Mar 2026
 Jobseekers
 Register
 Login
@@ -3909,7 +3881,7 @@
       </c>
       <c r="F17" s="1" t="inlineStr">
         <is>
-          <t>Learning, Safety</t>
+          <t>Governance, Learning, Safety</t>
         </is>
       </c>
       <c r="G17" s="1" t="inlineStr">
@@ -3918,11 +3890,11 @@
         </is>
       </c>
       <c r="H17" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I17" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287902</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287936</t>
         </is>
       </c>
     </row>
@@ -4095,6 +4067,36 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+RFP for Data Collection for Foundational Reading ...
+Lords Education and Health Society (LEHS)
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Research Scientist – I (Non Medical)
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Technical Support - III
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Program Lead- Governance and Gender Justice
+Society for Women's Action and Training Initiativ...
+Location:
+Gujarat
+Apply by:
+25 Mar 2026
+Senior Field Officer Certification Management
+Fairtrade India Project - CSM
+Location:
+Andhra Pradesh
+Apply by:
+15 Mar 2026
 Design and Readiness Lead
 SwaTaleem Foundation
 Location:
@@ -4113,36 +4115,6 @@
 Delhi
 Apply by:
 05 Apr 2026
-Director of International Programmes Impact And P...
-Confidential
-Location:
-Telangana
-Apply by:
-08 Apr 2026
-Organizational Development (OD) Manager
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Manager – Monitoring &amp; Evaluation
-Family Planning Association of India (FPA India)
-Location:
-Maharashtra
-Apply by:
-04 Apr 2026
-Officer – Instructional Design and Technical Supp...
-Room to Read India
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-RFP UNW-IND-2026-00002 for Hiring resource agency...
-UN Women
-Location:
-India
-Apply by:
-23 Mar 2026
 Jobseekers
 Register
 Login
@@ -4181,7 +4153,7 @@
         </is>
       </c>
       <c r="H18" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I18" s="1" t="inlineStr">
         <is>
@@ -4318,6 +4290,36 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+RFP for Data Collection for Foundational Reading ...
+Lords Education and Health Society (LEHS)
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Research Scientist – I (Non Medical)
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Technical Support - III
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Program Lead- Governance and Gender Justice
+Society for Women's Action and Training Initiativ...
+Location:
+Gujarat
+Apply by:
+25 Mar 2026
+Senior Field Officer Certification Management
+Fairtrade India Project - CSM
+Location:
+Andhra Pradesh
+Apply by:
+15 Mar 2026
 Design and Readiness Lead
 SwaTaleem Foundation
 Location:
@@ -4336,36 +4338,6 @@
 Delhi
 Apply by:
 05 Apr 2026
-Director of International Programmes Impact And P...
-Confidential
-Location:
-Telangana
-Apply by:
-08 Apr 2026
-Organizational Development (OD) Manager
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Manager – Monitoring &amp; Evaluation
-Family Planning Association of India (FPA India)
-Location:
-Maharashtra
-Apply by:
-04 Apr 2026
-Officer – Instructional Design and Technical Supp...
-Room to Read India
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-RFP UNW-IND-2026-00002 for Hiring resource agency...
-UN Women
-Location:
-India
-Apply by:
-23 Mar 2026
 Jobseekers
 Register
 Login
@@ -4404,7 +4376,7 @@
         </is>
       </c>
       <c r="H19" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I19" s="1" t="inlineStr">
         <is>
@@ -4421,13 +4393,13 @@
       <c r="B20" s="1" t="inlineStr"/>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>ToR - Portfolio-Wide Learning Exercise cum review for the Health Domain</t>
+          <t>ToR - Strategic Review and Forward-Looking Education Strategy Development</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
           <t>ChildFund India | India
-International Development - ToR - Portfolio-Wide Learning Exercise cum review for the Health Domain, ChildFund India, India - DevNetJobsIndia.org
+International Development - ToR - Strategic Review and Forward-Looking Education Strategy Development, ChildFund India, India - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
@@ -4441,7 +4413,7 @@
 Jobseekers:
 Login
 |
-Register ... Read More</t>
+Registe ... Read More</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -4449,7 +4421,7 @@
           <t>• Job Email ID:
 centralpurchase2(at)childfundindia.org
 Download Attachment:
-TOR  Health Portfolio_23.2.2026.doc
+ToR for Education.doc
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
@@ -4522,6 +4494,36 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+RFP for Data Collection for Foundational Reading ...
+Lords Education and Health Society (LEHS)
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Research Scientist – I (Non Medical)
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Technical Support - III
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Program Lead- Governance and Gender Justice
+Society for Women's Action and Training Initiativ...
+Location:
+Gujarat
+Apply by:
+25 Mar 2026
+Senior Field Officer Certification Management
+Fairtrade India Project - CSM
+Location:
+Andhra Pradesh
+Apply by:
+15 Mar 2026
 Design and Readiness Lead
 SwaTaleem Foundation
 Location:
@@ -4540,36 +4542,6 @@
 Delhi
 Apply by:
 05 Apr 2026
-Director of International Programmes Impact And P...
-Confidential
-Location:
-Telangana
-Apply by:
-08 Apr 2026
-Organizational Development (OD) Manager
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Manager – Monitoring &amp; Evaluation
-Family Planning Association of India (FPA India)
-Location:
-Maharashtra
-Apply by:
-04 Apr 2026
-Officer – Instructional Design and Technical Supp...
-Room to Read India
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-RFP UNW-IND-2026-00002 for Hiring resource agency...
-UN Women
-Location:
-India
-Apply by:
-23 Mar 2026
 Jobseekers
 Register
 Login
@@ -4608,11 +4580,11 @@
         </is>
       </c>
       <c r="H20" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I20" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287901</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287902</t>
         </is>
       </c>
     </row>
@@ -4657,7 +4629,7 @@
         </is>
       </c>
       <c r="H21" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I21" s="1" t="inlineStr">
         <is>
@@ -4795,6 +4767,36 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+RFP for Data Collection for Foundational Reading ...
+Lords Education and Health Society (LEHS)
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Research Scientist – I (Non Medical)
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Technical Support - III
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Program Lead- Governance and Gender Justice
+Society for Women's Action and Training Initiativ...
+Location:
+Gujarat
+Apply by:
+25 Mar 2026
+Senior Field Officer Certification Management
+Fairtrade India Project - CSM
+Location:
+Andhra Pradesh
+Apply by:
+15 Mar 2026
 Design and Readiness Lead
 SwaTaleem Foundation
 Location:
@@ -4813,36 +4815,6 @@
 Delhi
 Apply by:
 05 Apr 2026
-Director of International Programmes Impact And P...
-Confidential
-Location:
-Telangana
-Apply by:
-08 Apr 2026
-Organizational Development (OD) Manager
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Manager – Monitoring &amp; Evaluation
-Family Planning Association of India (FPA India)
-Location:
-Maharashtra
-Apply by:
-04 Apr 2026
-Officer – Instructional Design and Technical Supp...
-Room to Read India
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-RFP UNW-IND-2026-00002 for Hiring resource agency...
-UN Women
-Location:
-India
-Apply by:
-23 Mar 2026
 Jobseekers
 Register
 Login
@@ -4881,7 +4853,7 @@
         </is>
       </c>
       <c r="H22" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I22" s="1" t="inlineStr">
         <is>
@@ -5001,6 +4973,36 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+RFP for Data Collection for Foundational Reading ...
+Lords Education and Health Society (LEHS)
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Research Scientist – I (Non Medical)
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Technical Support - III
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Program Lead- Governance and Gender Justice
+Society for Women's Action and Training Initiativ...
+Location:
+Gujarat
+Apply by:
+25 Mar 2026
+Senior Field Officer Certification Management
+Fairtrade India Project - CSM
+Location:
+Andhra Pradesh
+Apply by:
+15 Mar 2026
 Design and Readiness Lead
 SwaTaleem Foundation
 Location:
@@ -5019,36 +5021,6 @@
 Delhi
 Apply by:
 05 Apr 2026
-Director of International Programmes Impact And P...
-Confidential
-Location:
-Telangana
-Apply by:
-08 Apr 2026
-Organizational Development (OD) Manager
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Manager – Monitoring &amp; Evaluation
-Family Planning Association of India (FPA India)
-Location:
-Maharashtra
-Apply by:
-04 Apr 2026
-Officer – Instructional Design and Technical Supp...
-Room to Read India
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-RFP UNW-IND-2026-00002 for Hiring resource agency...
-UN Women
-Location:
-India
-Apply by:
-23 Mar 2026
 Jobseekers
 Register
 Login
@@ -5087,7 +5059,7 @@
         </is>
       </c>
       <c r="H23" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I23" s="1" t="inlineStr">
         <is>
@@ -5206,6 +5178,36 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+RFP for Data Collection for Foundational Reading ...
+Lords Education and Health Society (LEHS)
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Research Scientist – I (Non Medical)
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Technical Support - III
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Program Lead- Governance and Gender Justice
+Society for Women's Action and Training Initiativ...
+Location:
+Gujarat
+Apply by:
+25 Mar 2026
+Senior Field Officer Certification Management
+Fairtrade India Project - CSM
+Location:
+Andhra Pradesh
+Apply by:
+15 Mar 2026
 Design and Readiness Lead
 SwaTaleem Foundation
 Location:
@@ -5224,36 +5226,6 @@
 Delhi
 Apply by:
 05 Apr 2026
-Director of International Programmes Impact And P...
-Confidential
-Location:
-Telangana
-Apply by:
-08 Apr 2026
-Organizational Development (OD) Manager
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Manager – Monitoring &amp; Evaluation
-Family Planning Association of India (FPA India)
-Location:
-Maharashtra
-Apply by:
-04 Apr 2026
-Officer – Instructional Design and Technical Supp...
-Room to Read India
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-RFP UNW-IND-2026-00002 for Hiring resource agency...
-UN Women
-Location:
-India
-Apply by:
-23 Mar 2026
 Jobseekers
 Register
 Login
@@ -5292,7 +5264,7 @@
         </is>
       </c>
       <c r="H24" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I24" s="1" t="inlineStr">
         <is>
@@ -5413,6 +5385,36 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+RFP for Data Collection for Foundational Reading ...
+Lords Education and Health Society (LEHS)
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Research Scientist – I (Non Medical)
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Technical Support - III
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Program Lead- Governance and Gender Justice
+Society for Women's Action and Training Initiativ...
+Location:
+Gujarat
+Apply by:
+25 Mar 2026
+Senior Field Officer Certification Management
+Fairtrade India Project - CSM
+Location:
+Andhra Pradesh
+Apply by:
+15 Mar 2026
 Design and Readiness Lead
 SwaTaleem Foundation
 Location:
@@ -5431,36 +5433,6 @@
 Delhi
 Apply by:
 05 Apr 2026
-Director of International Programmes Impact And P...
-Confidential
-Location:
-Telangana
-Apply by:
-08 Apr 2026
-Organizational Development (OD) Manager
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Manager – Monitoring &amp; Evaluation
-Family Planning Association of India (FPA India)
-Location:
-Maharashtra
-Apply by:
-04 Apr 2026
-Officer – Instructional Design and Technical Supp...
-Room to Read India
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-RFP UNW-IND-2026-00002 for Hiring resource agency...
-UN Women
-Location:
-India
-Apply by:
-23 Mar 2026
 Jobseekers
 Register
 Login
@@ -5499,7 +5471,7 @@
         </is>
       </c>
       <c r="H25" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I25" s="1" t="inlineStr">
         <is>
@@ -5621,6 +5593,36 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+RFP for Data Collection for Foundational Reading ...
+Lords Education and Health Society (LEHS)
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Research Scientist – I (Non Medical)
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Technical Support - III
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Program Lead- Governance and Gender Justice
+Society for Women's Action and Training Initiativ...
+Location:
+Gujarat
+Apply by:
+25 Mar 2026
+Senior Field Officer Certification Management
+Fairtrade India Project - CSM
+Location:
+Andhra Pradesh
+Apply by:
+15 Mar 2026
 Design and Readiness Lead
 SwaTaleem Foundation
 Location:
@@ -5639,36 +5641,6 @@
 Delhi
 Apply by:
 05 Apr 2026
-Director of International Programmes Impact And P...
-Confidential
-Location:
-Telangana
-Apply by:
-08 Apr 2026
-Organizational Development (OD) Manager
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Manager – Monitoring &amp; Evaluation
-Family Planning Association of India (FPA India)
-Location:
-Maharashtra
-Apply by:
-04 Apr 2026
-Officer – Instructional Design and Technical Supp...
-Room to Read India
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-RFP UNW-IND-2026-00002 for Hiring resource agency...
-UN Women
-Location:
-India
-Apply by:
-23 Mar 2026
 Jobseekers
 Register
 Login
@@ -5707,7 +5679,7 @@
         </is>
       </c>
       <c r="H26" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
@@ -5850,6 +5822,36 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+RFP for Data Collection for Foundational Reading ...
+Lords Education and Health Society (LEHS)
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Research Scientist – I (Non Medical)
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Technical Support - III
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Program Lead- Governance and Gender Justice
+Society for Women's Action and Training Initiativ...
+Location:
+Gujarat
+Apply by:
+25 Mar 2026
+Senior Field Officer Certification Management
+Fairtrade India Project - CSM
+Location:
+Andhra Pradesh
+Apply by:
+15 Mar 2026
 Design and Readiness Lead
 SwaTaleem Foundation
 Location:
@@ -5868,36 +5870,6 @@
 Delhi
 Apply by:
 05 Apr 2026
-Director of International Programmes Impact And P...
-Confidential
-Location:
-Telangana
-Apply by:
-08 Apr 2026
-Organizational Development (OD) Manager
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Manager – Monitoring &amp; Evaluation
-Family Planning Association of India (FPA India)
-Location:
-Maharashtra
-Apply by:
-04 Apr 2026
-Officer – Instructional Design and Technical Supp...
-Room to Read India
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-RFP UNW-IND-2026-00002 for Hiring resource agency...
-UN Women
-Location:
-India
-Apply by:
-23 Mar 2026
 Jobseekers
 Register
 Login
@@ -5936,7 +5908,7 @@
         </is>
       </c>
       <c r="H27" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
@@ -6079,6 +6051,36 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+RFP for Data Collection for Foundational Reading ...
+Lords Education and Health Society (LEHS)
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Research Scientist – I (Non Medical)
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Technical Support - III
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Program Lead- Governance and Gender Justice
+Society for Women's Action and Training Initiativ...
+Location:
+Gujarat
+Apply by:
+25 Mar 2026
+Senior Field Officer Certification Management
+Fairtrade India Project - CSM
+Location:
+Andhra Pradesh
+Apply by:
+15 Mar 2026
 Design and Readiness Lead
 SwaTaleem Foundation
 Location:
@@ -6097,36 +6099,6 @@
 Delhi
 Apply by:
 05 Apr 2026
-Director of International Programmes Impact And P...
-Confidential
-Location:
-Telangana
-Apply by:
-08 Apr 2026
-Organizational Development (OD) Manager
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Manager – Monitoring &amp; Evaluation
-Family Planning Association of India (FPA India)
-Location:
-Maharashtra
-Apply by:
-04 Apr 2026
-Officer – Instructional Design and Technical Supp...
-Room to Read India
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-RFP UNW-IND-2026-00002 for Hiring resource agency...
-UN Women
-Location:
-India
-Apply by:
-23 Mar 2026
 Jobseekers
 Register
 Login
@@ -6165,7 +6137,7 @@
         </is>
       </c>
       <c r="H28" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I28" s="1" t="inlineStr">
         <is>
@@ -6308,6 +6280,36 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+RFP for Data Collection for Foundational Reading ...
+Lords Education and Health Society (LEHS)
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Research Scientist – I (Non Medical)
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Technical Support - III
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Program Lead- Governance and Gender Justice
+Society for Women's Action and Training Initiativ...
+Location:
+Gujarat
+Apply by:
+25 Mar 2026
+Senior Field Officer Certification Management
+Fairtrade India Project - CSM
+Location:
+Andhra Pradesh
+Apply by:
+15 Mar 2026
 Design and Readiness Lead
 SwaTaleem Foundation
 Location:
@@ -6326,36 +6328,6 @@
 Delhi
 Apply by:
 05 Apr 2026
-Director of International Programmes Impact And P...
-Confidential
-Location:
-Telangana
-Apply by:
-08 Apr 2026
-Organizational Development (OD) Manager
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Manager – Monitoring &amp; Evaluation
-Family Planning Association of India (FPA India)
-Location:
-Maharashtra
-Apply by:
-04 Apr 2026
-Officer – Instructional Design and Technical Supp...
-Room to Read India
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-RFP UNW-IND-2026-00002 for Hiring resource agency...
-UN Women
-Location:
-India
-Apply by:
-23 Mar 2026
 Jobseekers
 Register
 Login
@@ -6394,7 +6366,7 @@
         </is>
       </c>
       <c r="H29" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I29" s="1" t="inlineStr">
         <is>
@@ -6531,6 +6503,36 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+RFP for Data Collection for Foundational Reading ...
+Lords Education and Health Society (LEHS)
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Research Scientist – I (Non Medical)
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Technical Support - III
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Program Lead- Governance and Gender Justice
+Society for Women's Action and Training Initiativ...
+Location:
+Gujarat
+Apply by:
+25 Mar 2026
+Senior Field Officer Certification Management
+Fairtrade India Project - CSM
+Location:
+Andhra Pradesh
+Apply by:
+15 Mar 2026
 Design and Readiness Lead
 SwaTaleem Foundation
 Location:
@@ -6549,36 +6551,6 @@
 Delhi
 Apply by:
 05 Apr 2026
-Director of International Programmes Impact And P...
-Confidential
-Location:
-Telangana
-Apply by:
-08 Apr 2026
-Organizational Development (OD) Manager
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Manager – Monitoring &amp; Evaluation
-Family Planning Association of India (FPA India)
-Location:
-Maharashtra
-Apply by:
-04 Apr 2026
-Officer – Instructional Design and Technical Supp...
-Room to Read India
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-RFP UNW-IND-2026-00002 for Hiring resource agency...
-UN Women
-Location:
-India
-Apply by:
-23 Mar 2026
 Jobseekers
 Register
 Login
@@ -6617,7 +6589,7 @@
         </is>
       </c>
       <c r="H30" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I30" s="1" t="inlineStr">
         <is>
@@ -6736,6 +6708,36 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+RFP for Data Collection for Foundational Reading ...
+Lords Education and Health Society (LEHS)
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Research Scientist – I (Non Medical)
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Technical Support - III
+Affordable Quality Health/ACCESS Health Internati...
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Program Lead- Governance and Gender Justice
+Society for Women's Action and Training Initiativ...
+Location:
+Gujarat
+Apply by:
+25 Mar 2026
+Senior Field Officer Certification Management
+Fairtrade India Project - CSM
+Location:
+Andhra Pradesh
+Apply by:
+15 Mar 2026
 Design and Readiness Lead
 SwaTaleem Foundation
 Location:
@@ -6754,36 +6756,6 @@
 Delhi
 Apply by:
 05 Apr 2026
-Director of International Programmes Impact And P...
-Confidential
-Location:
-Telangana
-Apply by:
-08 Apr 2026
-Organizational Development (OD) Manager
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Manager – Monitoring &amp; Evaluation
-Family Planning Association of India (FPA India)
-Location:
-Maharashtra
-Apply by:
-04 Apr 2026
-Officer – Instructional Design and Technical Supp...
-Room to Read India
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-RFP UNW-IND-2026-00002 for Hiring resource agency...
-UN Women
-Location:
-India
-Apply by:
-23 Mar 2026
 Jobseekers
 Register
 Login
@@ -6822,7 +6794,7 @@
         </is>
       </c>
       <c r="H31" s="1" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I31" s="1" t="inlineStr">
         <is>

--- a/all_grants.xlsx
+++ b/all_grants.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I80"/>
+  <dimension ref="A1:I77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -489,13 +489,13 @@
       <c r="B2" s="1" t="inlineStr"/>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>RFP - Onboarding Agency for Revamping Assam LMIS Dashboard</t>
+          <t>RFQ: Construction of New gated check dams, De-siltation, and retrofitting ...</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>PATH | Assam
-International Development - RFP - Onboarding Agency for Revamping Assam LMIS Dashboard, PATH, Assam - DevNetJobsIndia.org
+          <t>WaterAid India | Telangana
+International Development - RFQ: Construction of New gated check dams, De-siltation, and retrofitting of check dam in 6 villages, WaterAid India, Telangana - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
@@ -505,103 +505,20 @@
 Broadcast Resume
 RFPs/Tenders
 Search Jobs
-Events
-Jobseekers:
-Login
-|
-Register
-Jobseekers Login
-Jobseekers Registe ... Read More</t>
+E ... Read More</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>• 3.2. Commercial contracting terms and conditions will be negotiated with the successful supplier at the end of the selection process.
-3.3. By submitting a proposal, the supplier confirms their agreement to abide by the RFP terms and PATH policies, including the
-PATH Code
-of
-Ethics
-a
-nd general practices promoting sustainability, fair trading, health and safety, records management, anti-fraud and corruption, and environmental responsibility.
-3.4. The estimated duration of the contract is 3 months.
-• 4. Solicitation terms and conditions
-4.1.
-Notice of nonbinding solicitation:
-PATH reserves the right to reject any or all bids received in response to this solicitation and is not obligated to accept any proposal.
-4.2.
-Confidentiality:
-Suppliers must treat all information provided by PATH as part of this solicitation as confidential. Unauthorized disclosure of such information may result in PATH seeking appropriate remedies under applicable law.
-4.3.
-Conflict of interest disclosure:
-Suppliers bidding on PATH business (herein referenced as “bidders”) must disclose any actual or potential conflicts of interest to the contact(s) listed in the RFP. Conflicts of interest may exist if a personal relationship with a PATH staff member constitutes a significant financial interest, a board membership, other employment, or ownership or rights in intellectual property that conflict with the supplier’s obligations to PATH. Both suppliers and PATH are safeguarded when actual or perceived conflicts of interest are disclosed. When necessary, PATH will develop a management plan to mitigate potential risks associated with disclosed conflicts of interest.
-4.4.
-Acceptance:
-• A bidder’s submission of a proposal constitutes acceptance of all terms and conditions set forth in the RFP. However, PATH’s acceptance of a proposal does not imply acceptance of its terms and conditions. PATH reserves the right to negotiate the final terms and conditions, as well as the substance of the RFP finalists’ proposals. Additionally, PATH may choose to accept partial components of a proposal if appropriate.
-4.5.
-Right to final negotiations:
-• PATH reserves the right to negotiate the final costs and scope of work and to limit or include third parties in such negotiations at its sole discretion.
-4.6.
-Third-party limitations:
-PATH does not represent, warrant, or act as an agent for any third party as a result of this solicitation. This solicitation does not authorize any third party to bind or commit PATH in any way without express written consent.
-4.7.
-Proposal validity:
-Proposals submitted under this RFP must remain valid for at least 90 days from the submission deadline. The validity period must also be explicitly stated in the proposal.
-4.8.
-Limitation of liability:
-• The terms and conditions outlined in this RFP do not exclude or limit the liability of PATH or the supplier in cases of fraud or other circumstances that result in liability under applicable law.
-4.9.
-Tender costs and liability:
-Bidders are responsible for obtaining all necessary information to prepare their proposal and for covering all costs and expenses incurred during the preparation process. Subject to the “Limitation of liability” section (Section 4.8), bidders acknowledge that by participating in this RFP—including the submission of their proposal—they are not entitled to claim from PATH any costs, expenses, or liabilities incurred during the tender process, regardless of the outcome of their proposal.
-4.10.
-PATH’s variation or termination rights
-: PATH reserves the right to modify or terminate this RFP process with written notice to all suppliers who have submitted proposals. The solicitation process is intended to proceed in accordance with the provisions outlined in this RFP. However, PATH reserves the right to terminate, amend, or modify the process, including time scales or deadlines, with notice to all suppliers who have submitted proposals. Subject to section 4.8, “Limitation of liability,” PATH shall not be held liable for any losses, costs, or expenses resulting from its termination, amendment, or modification to this RFP.
-4.11.
-Joint venture, consortium, or subcontractors:
-The lead supplier submitting a proposal in response to this RFP assumes full responsibility for ensuring compliance with RFP requirements among all members of the joint venture or consortium, including their advisers, subcontractors, and staff.
-4.12.
-Payment and invoicing:
-PATH will process correctly addressed and undisputed invoices within 30 days. Suppliers must ensure that comparable payment terms apply to their downstream parties.
-Advance payment is not preferred
-. If an advance payment is proposed and deviates from industry- or country-standard practices, it must be clearly outlined in the financial proposal submitted to PATH.
-5. Instructions for submission
-5.1.
-PATH contacts:
-All communications regarding this solicitation must be directed to the contacts listed below. Contacting third parties involved in the project, the review panel, or any other party will be considered a conflict of interest and may result in disqualification of the proposal. All required documents must be submitted to the listed contacts by the submission deadline:
-Technical and Financial proposal should be Addressed to: Procurement Officer at
-rfpindia@path.org
-INSTRUCTIONS FOR SUBMITTING THE PROPOSAL:
-FORMAT OF THE PROPOSAL:
-The Bidder should submit the proposal in English. The response to the proposal should be set out in two main parts:
-•
-Part A – Technical Proposal
-•
-Part B – Financial Proposal
-Part A (Technical Proposal) and Part B (Financial Proposal) must be documented and saved separately and efforts to be made for submission in a single email to enable evaluation of Technical Proposal and Financial Proposal independently. Part B (Financial Proposal) MUST BE PASSWORD PROTECTED separately. Please do not include any price information/password to access the Proposal in Part A (Technical Proposal) and/or in any communication (until and unless requested by PATH).
-The subject line of all emails regarding the proposal should read:
-RFP # 2026-016 - Your Company
-Name.
-5.2.
-Confirmation of interest:
-Send a statement acknowledging receipt of this solicitation and your intent to respond (or not) no later than the date specified in the schedule in Section 1. Send the confirmation to the contacts listed in Section 5.1 above.
-5.3.
-Proposal technical content:
-Bidders are advised to provide only the information required. Proposals must be clear, concise, unambiguous, and directly address the stated requirements.
-5.4.
-Selection of shortlist:
-PATH reserves the right to select a shortlist from the bids received. PATH may also interview and discuss specific details with shortlisted candidates.
-5.5.
-Deliberate alteration
-of a PATH requirement as part of your proposal will invalidate the proposal; and for evaluation purposes, the proposal may be deemed to be unresponsive .
-For detailed information, please check the complete version of the RFP attached below.
-• Job Email ID:
-rfpindia(at)path.org
+          <t>• Job Email ID:
+WAIProcurementAP(at)wateraid.org
 Download Attachment:
-Request for Proposal - RFP#2026-016-Onboarding Agency for Revamping Assam LMIS Dashboard.pdf
+Tender Notice-15 check dams-Jalsankalp-19.02.26_compressed.pdf
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
 Apply by:
-07 Mar 2026
+08 Mar 2026
 Access all the jobs and get ahead!
 Subscribe to Value Membership Now!
 Subscribe
@@ -655,13 +572,13 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
 Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
 Project Potential
 Location:
 Bihar
@@ -669,54 +586,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+Manager - Individual Engagement (Acquisition)
+(Value Members only)
+Location:
+Maharashtra
+Apply by:
+10 Mar 2026
+Part Time Accountant
+Sahabhagi Vikash Abhiyan
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Coordinator
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
+Consultant Architects
+(Value Members only)
+Location:
+Chhattisgarh
+Apply by:
+18 Mar 2026
+Community Mobilizer
+Common Man Trust
+Location:
+Delhi, Uttar Pradesh, Haryana
+Apply by:
+25 Mar 2026
+Part-Time Psychology Intern (Telugu Speaking)
+Nayi Disha
+Location:
+Telangana
+Apply by:
+20 Mar 2026
+Field Mobilizer
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
 RFP for Data Collection for Foundational Reading ...
 Lords Education and Health Society (LEHS)
 Location:
 Odisha
 Apply by:
 15 Mar 2026
-Project Research Scientist – I (Non Medical)
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Technical Support - III
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Program Lead- Governance and Gender Justice
-Society for Women's Action and Training Initiativ...
-Location:
-Gujarat
-Apply by:
-25 Mar 2026
-Senior Field Officer Certification Management
-Fairtrade India Project - CSM
-Location:
-Andhra Pradesh
-Apply by:
-15 Mar 2026
-Design and Readiness Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Program Manager – AI Skilling Initiative
-SwaTaleem Foundation
-Location:
-Haryana
-Apply by:
-05 Apr 2026
-Communications Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
 Jobseekers
 Register
 Login
@@ -746,12 +663,12 @@
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>07-03-2026</t>
+          <t>08-03-2026</t>
         </is>
       </c>
       <c r="H2" s="1" t="n">
@@ -759,7 +676,7 @@
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287335</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287784</t>
         </is>
       </c>
     </row>
@@ -772,628 +689,10 @@
       <c r="B3" s="1" t="inlineStr"/>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>RFP- #2026-IN-01- Agency for economic Impact Analysis</t>
+          <t>RFP - Final Evaluation of the Bhoomi Ka Programme</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>PATH | Delhi
-International Development - RFP- #2026-IN-01- Agency for economic Impact Analysis, PATH, Delhi - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Login
-|
-Register
-Jobseekers Login
-Jobseekers Register
-Job ... Read More</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>• Job Email ID:
-rfpindia(at)path.org
-Download Attachment:
-Request for Proposal - RFP#2026-IN-01- Agency for economic Impact Analysis.doc
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-07 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Associate – Finance and Operations
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-RFP for Data Collection for Foundational Reading ...
-Lords Education and Health Society (LEHS)
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Research Scientist – I (Non Medical)
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Technical Support - III
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Program Lead- Governance and Gender Justice
-Society for Women's Action and Training Initiativ...
-Location:
-Gujarat
-Apply by:
-25 Mar 2026
-Senior Field Officer Certification Management
-Fairtrade India Project - CSM
-Location:
-Andhra Pradesh
-Apply by:
-15 Mar 2026
-Design and Readiness Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Program Manager – AI Skilling Initiative
-SwaTaleem Foundation
-Location:
-Haryana
-Apply by:
-05 Apr 2026
-Communications Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>07-03-2026</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287460</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr"/>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>Associate (Programme Management)</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Indian Institute For Human Settlements (Iihs) | Karnataka
-International Development - Associate (Programme Management), Indian Institute For Human Settlements (Iihs), Karnataka - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events ... Read More</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>• IIHS is an equal opportunity employer that encourages women, people with disabilities and those from economically and socially excluded communities with the requisite skills and qualifications to apply for positions.
-• To apply
-If you are interested in exploring this opportunity with us, please fill the online
-application form
-by clicking here. (You can also click on the “
-Apply Now
-” button at the end of the Job Description displayed on the website).
-Contact
-Please write to us at
-hr@iihs.co.in
-if you need any clarifications while filling the online application form.
-• Job Email ID:
-hr(at)iihs.co.in
-Download Attachment:
-Associate-Programme-Management-–-ASSURE-Lighthouse-Projects.pdf
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-07 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Associate – Finance and Operations
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-RFP for Data Collection for Foundational Reading ...
-Lords Education and Health Society (LEHS)
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Research Scientist – I (Non Medical)
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Technical Support - III
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Program Lead- Governance and Gender Justice
-Society for Women's Action and Training Initiativ...
-Location:
-Gujarat
-Apply by:
-25 Mar 2026
-Senior Field Officer Certification Management
-Fairtrade India Project - CSM
-Location:
-Andhra Pradesh
-Apply by:
-15 Mar 2026
-Design and Readiness Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Program Manager – AI Skilling Initiative
-SwaTaleem Foundation
-Location:
-Haryana
-Apply by:
-05 Apr 2026
-Communications Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>07-03-2026</t>
-        </is>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=285747</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr"/>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>RFQ: Construction of New gated check dams, De-siltation, and retrofitting ...</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>WaterAid India | Telangana
-International Development - RFQ: Construction of New gated check dams, De-siltation, and retrofitting of check dam in 6 villages, WaterAid India, Telangana - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-E ... Read More</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>• Job Email ID:
-WAIProcurementAP(at)wateraid.org
-Download Attachment:
-Tender Notice-15 check dams-Jalsankalp-19.02.26_compressed.pdf
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-08 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Associate – Finance and Operations
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-RFP for Data Collection for Foundational Reading ...
-Lords Education and Health Society (LEHS)
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Research Scientist – I (Non Medical)
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Technical Support - III
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Program Lead- Governance and Gender Justice
-Society for Women's Action and Training Initiativ...
-Location:
-Gujarat
-Apply by:
-25 Mar 2026
-Senior Field Officer Certification Management
-Fairtrade India Project - CSM
-Location:
-Andhra Pradesh
-Apply by:
-15 Mar 2026
-Design and Readiness Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Program Manager – AI Skilling Initiative
-SwaTaleem Foundation
-Location:
-Haryana
-Apply by:
-05 Apr 2026
-Communications Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G5" s="1" t="inlineStr">
-        <is>
-          <t>08-03-2026</t>
-        </is>
-      </c>
-      <c r="H5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287784</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr"/>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Final Evaluation of the Bhoomi Ka Programme</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Deutsche Welthungerhilfe | India
 International Development - RFP - Final Evaluation of the Bhoomi Ka Programme, Deutsche Welthungerhilfe, India - DevNetJobsIndia.org
@@ -1414,7 +713,7 @@
 Jobs ... Read More</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>• INTRODUCTION AND CONTEXT
 Country:
@@ -1530,13 +829,13 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
 Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
 Project Potential
 Location:
 Bihar
@@ -1544,54 +843,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+Manager - Individual Engagement (Acquisition)
+(Value Members only)
+Location:
+Maharashtra
+Apply by:
+10 Mar 2026
+Part Time Accountant
+Sahabhagi Vikash Abhiyan
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Coordinator
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
+Consultant Architects
+(Value Members only)
+Location:
+Chhattisgarh
+Apply by:
+18 Mar 2026
+Community Mobilizer
+Common Man Trust
+Location:
+Delhi, Uttar Pradesh, Haryana
+Apply by:
+25 Mar 2026
+Part-Time Psychology Intern (Telugu Speaking)
+Nayi Disha
+Location:
+Telangana
+Apply by:
+20 Mar 2026
+Field Mobilizer
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
 RFP for Data Collection for Foundational Reading ...
 Lords Education and Health Society (LEHS)
 Location:
 Odisha
 Apply by:
 15 Mar 2026
-Project Research Scientist – I (Non Medical)
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Technical Support - III
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Program Lead- Governance and Gender Justice
-Society for Women's Action and Training Initiativ...
-Location:
-Gujarat
-Apply by:
-25 Mar 2026
-Senior Field Officer Certification Management
-Fairtrade India Project - CSM
-Location:
-Andhra Pradesh
-Apply by:
-15 Mar 2026
-Design and Readiness Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Program Manager – AI Skilling Initiative
-SwaTaleem Foundation
-Location:
-Haryana
-Apply by:
-05 Apr 2026
-Communications Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
 Jobseekers
 Register
 Login
@@ -1619,60 +918,107 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F6" s="1" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G6" s="1" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>08-03-2026</t>
         </is>
       </c>
-      <c r="H6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="1" t="inlineStr">
+      <c r="H3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287384</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr"/>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>RFP For Selection of an Implementation Support Agency (Isa) For Capacity B...</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>EAII Advisors Pvt Ltd | Andhra Pradesh
-International Development - RFP For Selection of an Implementation Support Agency (Isa) For Capacity Building Of Community Leaders To Conduct Community Engagement Activities, EAII Advisors Pvt Ltd, Andhra Pradesh - DevNetJobsIndia.org
+      <c r="B4" s="1" t="inlineStr"/>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>RFP - Early-Stage Impact Assessment-CDRI SWP 23-26</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Coalition for Disaster Resilient Infrastructure (CDRI) | India
+International Development - RFP - Early-Stage Impact Assessment-CDRI SWP 23-26, Coalition for Disaster Resilient Infrastructure (CDRI), India - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
-Regis ... Read More</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>• Proposal Requirements
-1. Company Background and Details
-A. Company Profile
-Overview of the firm or firms submitting the bid, including a brief history, information about organizational structure, relevant company financials, location of offices, number of employees, relevant certifications, or any other information that could be pertinent.
-Supplier Response:
-Kindly fill in the column “Bidder Response”. The current inputs are guiding inputs or choices for answers. Kindly fill in accordingly.
-For detailed information, please check the complete version of the RFP attached below.
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs ... Read More</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Climate, Governance</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>09-03-2026</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287093</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr"/>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>RFP - Hiring of an International Audit Firm</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Coalition for Disaster Resilient Infrastructure (CDRI) | India
+International Development - RFP - Hiring of an International Audit Firm, Coalition for Disaster Resilient Infrastructure (CDRI), India - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tender ... Read More</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>• Job Email ID:
+tender.projects(at)cdri.world
 Download Attachment:
-Standalone ISA RFP Technical Evaluation Response Template (1).docx
-Download Attachment:
-Telugu_Standalone ISA RFP Technical Evaluation Response Template.docx
+RFP-Hiring International Audit Firm-20 Feb'26.pdf
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
@@ -1731,13 +1077,13 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
 Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
 Project Potential
 Location:
 Bihar
@@ -1745,54 +1091,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+Manager - Individual Engagement (Acquisition)
+(Value Members only)
+Location:
+Maharashtra
+Apply by:
+10 Mar 2026
+Part Time Accountant
+Sahabhagi Vikash Abhiyan
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Coordinator
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
+Consultant Architects
+(Value Members only)
+Location:
+Chhattisgarh
+Apply by:
+18 Mar 2026
+Community Mobilizer
+Common Man Trust
+Location:
+Delhi, Uttar Pradesh, Haryana
+Apply by:
+25 Mar 2026
+Part-Time Psychology Intern (Telugu Speaking)
+Nayi Disha
+Location:
+Telangana
+Apply by:
+20 Mar 2026
+Field Mobilizer
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
 RFP for Data Collection for Foundational Reading ...
 Lords Education and Health Society (LEHS)
 Location:
 Odisha
 Apply by:
 15 Mar 2026
-Project Research Scientist – I (Non Medical)
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Technical Support - III
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Program Lead- Governance and Gender Justice
-Society for Women's Action and Training Initiativ...
-Location:
-Gujarat
-Apply by:
-25 Mar 2026
-Senior Field Officer Certification Management
-Fairtrade India Project - CSM
-Location:
-Andhra Pradesh
-Apply by:
-15 Mar 2026
-Design and Readiness Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Program Manager – AI Skilling Initiative
-SwaTaleem Foundation
-Location:
-Haryana
-Apply by:
-05 Apr 2026
-Communications Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
 Jobseekers
 Register
 Login
@@ -1820,107 +1166,60 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>Governance, Learning</t>
-        </is>
-      </c>
-      <c r="G7" s="1" t="inlineStr">
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>Climate</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>09-03-2026</t>
         </is>
       </c>
-      <c r="H7" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I7" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=285950</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="H5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287382</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr"/>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Early-Stage Impact Assessment-CDRI SWP 23-26</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Coalition for Disaster Resilient Infrastructure (CDRI) | India
-International Development - RFP - Early-Stage Impact Assessment-CDRI SWP 23-26, Coalition for Disaster Resilient Infrastructure (CDRI), India - DevNetJobsIndia.org
+      <c r="B6" s="1" t="inlineStr"/>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>RFP For Selection of an Implementation Support Agency (Isa) For Capacity B...</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>EAII Advisors Pvt Ltd | Andhra Pradesh
+International Development - RFP For Selection of an Implementation Support Agency (Isa) For Capacity Building Of Community Leaders To Conduct Community Engagement Activities, EAII Advisors Pvt Ltd, Andhra Pradesh - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs ... Read More</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>Climate, Governance</t>
-        </is>
-      </c>
-      <c r="G8" s="1" t="inlineStr">
-        <is>
-          <t>09-03-2026</t>
-        </is>
-      </c>
-      <c r="H8" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I8" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287093</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="inlineStr"/>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Hiring of an International Audit Firm</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Coalition for Disaster Resilient Infrastructure (CDRI) | India
-International Development - RFP - Hiring of an International Audit Firm, Coalition for Disaster Resilient Infrastructure (CDRI), India - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tender ... Read More</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>• Job Email ID:
-tender.projects(at)cdri.world
+Regis ... Read More</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>• Proposal Requirements
+1. Company Background and Details
+A. Company Profile
+Overview of the firm or firms submitting the bid, including a brief history, information about organizational structure, relevant company financials, location of offices, number of employees, relevant certifications, or any other information that could be pertinent.
+Supplier Response:
+Kindly fill in the column “Bidder Response”. The current inputs are guiding inputs or choices for answers. Kindly fill in accordingly.
+For detailed information, please check the complete version of the RFP attached below.
 Download Attachment:
-RFP-Hiring International Audit Firm-20 Feb'26.pdf
+Standalone ISA RFP Technical Evaluation Response Template (1).docx
+Download Attachment:
+Telugu_Standalone ISA RFP Technical Evaluation Response Template.docx
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
@@ -1979,13 +1278,13 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
 Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
 Project Potential
 Location:
 Bihar
@@ -1993,54 +1292,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+Manager - Individual Engagement (Acquisition)
+(Value Members only)
+Location:
+Maharashtra
+Apply by:
+10 Mar 2026
+Part Time Accountant
+Sahabhagi Vikash Abhiyan
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Coordinator
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
+Consultant Architects
+(Value Members only)
+Location:
+Chhattisgarh
+Apply by:
+18 Mar 2026
+Community Mobilizer
+Common Man Trust
+Location:
+Delhi, Uttar Pradesh, Haryana
+Apply by:
+25 Mar 2026
+Part-Time Psychology Intern (Telugu Speaking)
+Nayi Disha
+Location:
+Telangana
+Apply by:
+20 Mar 2026
+Field Mobilizer
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
 RFP for Data Collection for Foundational Reading ...
 Lords Education and Health Society (LEHS)
 Location:
 Odisha
 Apply by:
 15 Mar 2026
-Project Research Scientist – I (Non Medical)
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Technical Support - III
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Program Lead- Governance and Gender Justice
-Society for Women's Action and Training Initiativ...
-Location:
-Gujarat
-Apply by:
-25 Mar 2026
-Senior Field Officer Certification Management
-Fairtrade India Project - CSM
-Location:
-Andhra Pradesh
-Apply by:
-15 Mar 2026
-Design and Readiness Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Program Manager – AI Skilling Initiative
-SwaTaleem Foundation
-Location:
-Haryana
-Apply by:
-05 Apr 2026
-Communications Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
 Jobseekers
 Register
 Login
@@ -2068,38 +1367,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>Climate</t>
-        </is>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>Governance, Learning</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>09-03-2026</t>
         </is>
       </c>
-      <c r="H9" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287382</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="H6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=285950</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr"/>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>RFP For The Contractors To Procure, Build, Install, Supply Chlorine Tablet...</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>EAII Advisors Pvt Ltd | Andhra Pradesh
 International Development - RFP For The Contractors To Procure, Build, Install, Supply Chlorine Tablets, Operate And Maintain Tablet-Based In Line Chlorination Devices, EAII Advisors Pvt Ltd, Andhra Pradesh - DevNetJobsIndia.org
@@ -2110,7 +1409,7 @@
 Ho ... Read More</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>• Proposal Requirements
 1. Company Background and Details
@@ -2181,13 +1480,13 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
 Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
 Project Potential
 Location:
 Bihar
@@ -2195,54 +1494,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+Manager - Individual Engagement (Acquisition)
+(Value Members only)
+Location:
+Maharashtra
+Apply by:
+10 Mar 2026
+Part Time Accountant
+Sahabhagi Vikash Abhiyan
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Coordinator
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
+Consultant Architects
+(Value Members only)
+Location:
+Chhattisgarh
+Apply by:
+18 Mar 2026
+Community Mobilizer
+Common Man Trust
+Location:
+Delhi, Uttar Pradesh, Haryana
+Apply by:
+25 Mar 2026
+Part-Time Psychology Intern (Telugu Speaking)
+Nayi Disha
+Location:
+Telangana
+Apply by:
+20 Mar 2026
+Field Mobilizer
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
 RFP for Data Collection for Foundational Reading ...
 Lords Education and Health Society (LEHS)
 Location:
 Odisha
 Apply by:
 15 Mar 2026
-Project Research Scientist – I (Non Medical)
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Technical Support - III
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Program Lead- Governance and Gender Justice
-Society for Women's Action and Training Initiativ...
-Location:
-Gujarat
-Apply by:
-25 Mar 2026
-Senior Field Officer Certification Management
-Fairtrade India Project - CSM
-Location:
-Andhra Pradesh
-Apply by:
-15 Mar 2026
-Design and Readiness Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Program Manager – AI Skilling Initiative
-SwaTaleem Foundation
-Location:
-Haryana
-Apply by:
-05 Apr 2026
-Communications Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
 Jobseekers
 Register
 Login
@@ -2270,38 +1569,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F10" s="1" t="inlineStr">
+      <c r="F7" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G10" s="1" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>09-03-2026</t>
         </is>
       </c>
-      <c r="H10" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" s="1" t="inlineStr">
+      <c r="H7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=285949</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr"/>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr"/>
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>RFP - for Supply of Skill Lab Items</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>TeamLease Foundation | India
 International Development - RFP - for Supply of Skill Lab Items, TeamLease Foundation, India - DevNetJobsIndia.org
@@ -2323,7 +1622,7 @@
 Jobseeker ... Read More</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>• Technical Bid Submission Link-
 https://forms.gle/V9iy35ddb4kWEb468
@@ -2416,13 +1715,13 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
 Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
 Project Potential
 Location:
 Bihar
@@ -2430,54 +1729,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+Manager - Individual Engagement (Acquisition)
+(Value Members only)
+Location:
+Maharashtra
+Apply by:
+10 Mar 2026
+Part Time Accountant
+Sahabhagi Vikash Abhiyan
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Coordinator
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
+Consultant Architects
+(Value Members only)
+Location:
+Chhattisgarh
+Apply by:
+18 Mar 2026
+Community Mobilizer
+Common Man Trust
+Location:
+Delhi, Uttar Pradesh, Haryana
+Apply by:
+25 Mar 2026
+Part-Time Psychology Intern (Telugu Speaking)
+Nayi Disha
+Location:
+Telangana
+Apply by:
+20 Mar 2026
+Field Mobilizer
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
 RFP for Data Collection for Foundational Reading ...
 Lords Education and Health Society (LEHS)
 Location:
 Odisha
 Apply by:
 15 Mar 2026
-Project Research Scientist – I (Non Medical)
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Technical Support - III
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Program Lead- Governance and Gender Justice
-Society for Women's Action and Training Initiativ...
-Location:
-Gujarat
-Apply by:
-25 Mar 2026
-Senior Field Officer Certification Management
-Fairtrade India Project - CSM
-Location:
-Andhra Pradesh
-Apply by:
-15 Mar 2026
-Design and Readiness Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Program Manager – AI Skilling Initiative
-SwaTaleem Foundation
-Location:
-Haryana
-Apply by:
-05 Apr 2026
-Communications Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
 Jobseekers
 Register
 Login
@@ -2505,44 +1804,44 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F11" s="1" t="inlineStr">
+      <c r="F8" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G11" s="1" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>11-03-2026</t>
         </is>
       </c>
-      <c r="H11" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I11" s="1" t="inlineStr">
+      <c r="H8" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287613</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr"/>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="B9" s="1" t="inlineStr"/>
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>RFP - Study On SC-DMPA In Rajasthan- Clients And Providers Perspectives On...</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Centre For Community Economics And Development Consultants Society- CECOEDECON | Jaipur, Rajasthan
 International Development - RFP - Study On SC-DMPA In Rajasthan- Clients And Providers Perspectives On SC-DMPA In Rajasthan, Centre For Community Economics And Development Consultants Society- CECOEDE ... Read More</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>• Despite India’s achievement of replacement-level fertility, unmet need for contraception—particularly for spacing methods—remains substantial, with modern contraceptive use at 56.4% (2019–21), highlighting persistent gaps in access and choice, especially among vulnerable populations. Expanding the contraceptive method mix through innovative, user-centred approaches is therefore essential to meeting national commitments under FP2030 and the Sustainable Development Goals. In this context, the Government of India’s introduction of subcutaneous DMPA (DMPA-SC) as a self-care option under the National Family Planning Programme in 2023 represents a strategic step toward enhancing women’s autonomy, privacy, and convenience in contraceptive use. Global and national evidence indicates strong feasibility and acceptability of self-administered DMPA-SC among both users and providers; however, successful implementation requires an in-depth understanding of user experiences and health system readiness. This study, to be conducted in Jaipur-1, Jaisalmer and Sawai Madhopur districts of Rajasthan, aims to examine the perspectives &amp; experience of current SC-DMPA users and explore healthcare providers’ views on enabling and generating actionable evidence to inform effective scale-up of SC-DMPA within India’s public health system.
 CECOEDECON, with support from UNFPA, is implementing the roll-out of subcutaneous DMPA (SC-DMPA) in selected pilot districts of Rajasthan in the public health facilities, in collaboration with the Department of Health &amp; Family Welfare, Government of Rajasthan.
@@ -2663,13 +1962,13 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
 Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
 Project Potential
 Location:
 Bihar
@@ -2677,54 +1976,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+Manager - Individual Engagement (Acquisition)
+(Value Members only)
+Location:
+Maharashtra
+Apply by:
+10 Mar 2026
+Part Time Accountant
+Sahabhagi Vikash Abhiyan
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Coordinator
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
+Consultant Architects
+(Value Members only)
+Location:
+Chhattisgarh
+Apply by:
+18 Mar 2026
+Community Mobilizer
+Common Man Trust
+Location:
+Delhi, Uttar Pradesh, Haryana
+Apply by:
+25 Mar 2026
+Part-Time Psychology Intern (Telugu Speaking)
+Nayi Disha
+Location:
+Telangana
+Apply by:
+20 Mar 2026
+Field Mobilizer
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
 RFP for Data Collection for Foundational Reading ...
 Lords Education and Health Society (LEHS)
 Location:
 Odisha
 Apply by:
 15 Mar 2026
-Project Research Scientist – I (Non Medical)
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Technical Support - III
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Program Lead- Governance and Gender Justice
-Society for Women's Action and Training Initiativ...
-Location:
-Gujarat
-Apply by:
-25 Mar 2026
-Senior Field Officer Certification Management
-Fairtrade India Project - CSM
-Location:
-Andhra Pradesh
-Apply by:
-15 Mar 2026
-Design and Readiness Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Program Manager – AI Skilling Initiative
-SwaTaleem Foundation
-Location:
-Haryana
-Apply by:
-05 Apr 2026
-Communications Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
 Jobseekers
 Register
 Login
@@ -2752,38 +2051,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F12" s="1" t="inlineStr">
+      <c r="F9" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G12" s="1" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>11-03-2026</t>
         </is>
       </c>
-      <c r="H12" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I12" s="1" t="inlineStr">
+      <c r="H9" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287322</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr"/>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="B10" s="1" t="inlineStr"/>
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>SOW - Engagement of a Public Relations (PR) Agency on Retainer</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Room to Read India | India
 International Development - SOW - Engagement of a Public Relations (PR) Agency on Retainer, Room to Read India, India - DevNetJobsIndia.org
@@ -2804,7 +2103,7 @@
 Job ... Read More</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>• Scope of Work (SOW)
 Engagement of a Public Relations (PR) Agency on Retainer
@@ -2920,13 +2219,13 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
 Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
 Project Potential
 Location:
 Bihar
@@ -2934,54 +2233,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+Manager - Individual Engagement (Acquisition)
+(Value Members only)
+Location:
+Maharashtra
+Apply by:
+10 Mar 2026
+Part Time Accountant
+Sahabhagi Vikash Abhiyan
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Coordinator
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
+Consultant Architects
+(Value Members only)
+Location:
+Chhattisgarh
+Apply by:
+18 Mar 2026
+Community Mobilizer
+Common Man Trust
+Location:
+Delhi, Uttar Pradesh, Haryana
+Apply by:
+25 Mar 2026
+Part-Time Psychology Intern (Telugu Speaking)
+Nayi Disha
+Location:
+Telangana
+Apply by:
+20 Mar 2026
+Field Mobilizer
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
 RFP for Data Collection for Foundational Reading ...
 Lords Education and Health Society (LEHS)
 Location:
 Odisha
 Apply by:
 15 Mar 2026
-Project Research Scientist – I (Non Medical)
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Technical Support - III
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Program Lead- Governance and Gender Justice
-Society for Women's Action and Training Initiativ...
-Location:
-Gujarat
-Apply by:
-25 Mar 2026
-Senior Field Officer Certification Management
-Fairtrade India Project - CSM
-Location:
-Andhra Pradesh
-Apply by:
-15 Mar 2026
-Design and Readiness Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Program Manager – AI Skilling Initiative
-SwaTaleem Foundation
-Location:
-Haryana
-Apply by:
-05 Apr 2026
-Communications Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
 Jobseekers
 Register
 Login
@@ -3009,38 +2308,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F13" s="1" t="inlineStr">
+      <c r="F10" s="1" t="inlineStr">
         <is>
           <t>Governance, Learning</t>
         </is>
       </c>
-      <c r="G13" s="1" t="inlineStr">
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>12-03-2026</t>
         </is>
       </c>
-      <c r="H13" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="I13" s="1" t="inlineStr">
+      <c r="H10" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287648</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr"/>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr"/>
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>RFP - for Internal Audit</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>India HIV/AIDS Alliance (Alliance India) | Delhi
 International Development - RFP - for Internal Audit, India HIV/AIDS Alliance (Alliance India), Delhi - DevNetJobsIndia.org
@@ -3060,7 +2359,7 @@
 Regist ... Read More</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>• Alliance India reserves the right to reject applications that do not meet eligibility or application submission requirements (as detailed above) without further notice to the applicant. Issuance of this RFP does not constitute an award commitment or a guarantee of business on the part of Alliance India, nor does it commit Alliance India to pay for the costs incurred in submitting the application. Further, Alliance India reserves the right to reject any or all applications received and negotiate separately with an applicant if such action is considered in the best interest of Alliance India/ project.
 iii.
@@ -3133,13 +2432,13 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
 Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
 Project Potential
 Location:
 Bihar
@@ -3147,54 +2446,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+Manager - Individual Engagement (Acquisition)
+(Value Members only)
+Location:
+Maharashtra
+Apply by:
+10 Mar 2026
+Part Time Accountant
+Sahabhagi Vikash Abhiyan
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Coordinator
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
+Consultant Architects
+(Value Members only)
+Location:
+Chhattisgarh
+Apply by:
+18 Mar 2026
+Community Mobilizer
+Common Man Trust
+Location:
+Delhi, Uttar Pradesh, Haryana
+Apply by:
+25 Mar 2026
+Part-Time Psychology Intern (Telugu Speaking)
+Nayi Disha
+Location:
+Telangana
+Apply by:
+20 Mar 2026
+Field Mobilizer
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
 RFP for Data Collection for Foundational Reading ...
 Lords Education and Health Society (LEHS)
 Location:
 Odisha
 Apply by:
 15 Mar 2026
-Project Research Scientist – I (Non Medical)
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Technical Support - III
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Program Lead- Governance and Gender Justice
-Society for Women's Action and Training Initiativ...
-Location:
-Gujarat
-Apply by:
-25 Mar 2026
-Senior Field Officer Certification Management
-Fairtrade India Project - CSM
-Location:
-Andhra Pradesh
-Apply by:
-15 Mar 2026
-Design and Readiness Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Program Manager – AI Skilling Initiative
-SwaTaleem Foundation
-Location:
-Haryana
-Apply by:
-05 Apr 2026
-Communications Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
 Jobseekers
 Register
 Login
@@ -3222,38 +2521,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F14" s="1" t="inlineStr">
+      <c r="F11" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G14" s="1" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>13-03-2026</t>
         </is>
       </c>
-      <c r="H14" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I14" s="1" t="inlineStr">
+      <c r="H11" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287765</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr"/>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="B12" s="1" t="inlineStr"/>
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>Specialist – Financial Management and Compliance</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Financial Management Service Foundation (FMSF) | Uttar Pradesh
 International Development - Specialist – Financial Management and Compliance, Financial Management Service Foundation (FMSF), Uttar Pradesh - DevNetJobsIndia.org
@@ -3267,7 +2566,7 @@
 RFPs/T ... Read More</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>• will play a vital role in a program which seeks to strengthen the internal capacities of non-profit organizations in India across three building blocks of institutional functioning: governance, financial management, and compliance. These areas are deeply interconnected and together determine how effectively an organization operates, delivers programs and meets the expectations of its stakeholders. This position demands expertise in specific areas related to governance, compliance, and financial management, contributing essential guidance and support to strengthen the capabilities of participating organizations.
 Job Responsibilities:
@@ -3366,13 +2665,13 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
 Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
 Project Potential
 Location:
 Bihar
@@ -3380,54 +2679,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+Manager - Individual Engagement (Acquisition)
+(Value Members only)
+Location:
+Maharashtra
+Apply by:
+10 Mar 2026
+Part Time Accountant
+Sahabhagi Vikash Abhiyan
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Coordinator
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
+Consultant Architects
+(Value Members only)
+Location:
+Chhattisgarh
+Apply by:
+18 Mar 2026
+Community Mobilizer
+Common Man Trust
+Location:
+Delhi, Uttar Pradesh, Haryana
+Apply by:
+25 Mar 2026
+Part-Time Psychology Intern (Telugu Speaking)
+Nayi Disha
+Location:
+Telangana
+Apply by:
+20 Mar 2026
+Field Mobilizer
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
 RFP for Data Collection for Foundational Reading ...
 Lords Education and Health Society (LEHS)
 Location:
 Odisha
 Apply by:
 15 Mar 2026
-Project Research Scientist – I (Non Medical)
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Technical Support - III
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Program Lead- Governance and Gender Justice
-Society for Women's Action and Training Initiativ...
-Location:
-Gujarat
-Apply by:
-25 Mar 2026
-Senior Field Officer Certification Management
-Fairtrade India Project - CSM
-Location:
-Andhra Pradesh
-Apply by:
-15 Mar 2026
-Design and Readiness Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Program Manager – AI Skilling Initiative
-SwaTaleem Foundation
-Location:
-Haryana
-Apply by:
-05 Apr 2026
-Communications Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
 Jobseekers
 Register
 Login
@@ -3455,41 +2754,41 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F15" s="1" t="inlineStr">
+      <c r="F12" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G15" s="1" t="inlineStr">
+      <c r="G12" s="1" t="inlineStr">
         <is>
           <t>13-03-2026</t>
         </is>
       </c>
-      <c r="H15" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I15" s="1" t="inlineStr">
+      <c r="H12" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I12" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287015</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr"/>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>ToR - Portfolio-Wide Learning Exercise cum review for the Health Domain</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="B13" s="1" t="inlineStr"/>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>ToR - Livelihoods Strategy Review and Future Direction Roadmap</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>ChildFund India | India
-International Development - ToR - Portfolio-Wide Learning Exercise cum review for the Health Domain, ChildFund India, India - DevNetJobsIndia.org
+International Development - ToR - Livelihoods Strategy Review and Future Direction Roadmap, ChildFund India, India - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
@@ -3503,15 +2802,34 @@
 Jobseekers:
 Login
 |
-Register ... Read More</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>• Job Email ID:
+Register
+Jobseeker ... Read More</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>• To determine the relevance, alignment, and coherence of the Livelihood Program under CSP 2022–2027 with national priorities, donor expectations, and organizational mandate.
+To assess the extent to which planned outputs and outcomes have been achieved and to evaluate the quality and impact of program interventions.
+Identify achievements, innovations, good practices, and enabling factors across Livelihood program interventions.
+Document gaps, challenges, and areas for strengthening
+To examine the sustainability of program outcomes and the institutional readiness of ChildFund India for long-term resilience and growth.
+Facilitate reflection through workshops involving staff, partners, and selected beneficiaries and provide recommendations for strategic direction, scalability, and future program priorities.
+Proposal Submission
+Interested evaluators/agencies are invited to submit:
+Technical proposal outlining approach and methodology
+Team composition and relevant experience
+Financial proposal with a detailed budget
+Sample of previous qualitative evaluation work
+Interested evaluators/agencies are requested to submit their technical and financial proposals to
+centralpurchase2@childfundindia.org
+by 15 March 2026.
+Reference No:- PRA/CFI/DEL/2025-26/053
+ChildFund India reserves the right to modify this ToR based on programmatic and contextual requirements.
+For detailed information, please check the complete version of the advert attached below.
+• Job Email ID:
 centralpurchase2(at)childfundindia.org
 Download Attachment:
-TOR  Health Portfolio_23.2.2026.doc
+ToR Livelihood Portfolio-6.3.2026.doc
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
@@ -3570,13 +2888,13 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
 Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
 Project Potential
 Location:
 Bihar
@@ -3584,54 +2902,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+Manager - Individual Engagement (Acquisition)
+(Value Members only)
+Location:
+Maharashtra
+Apply by:
+10 Mar 2026
+Part Time Accountant
+Sahabhagi Vikash Abhiyan
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Coordinator
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
+Consultant Architects
+(Value Members only)
+Location:
+Chhattisgarh
+Apply by:
+18 Mar 2026
+Community Mobilizer
+Common Man Trust
+Location:
+Delhi, Uttar Pradesh, Haryana
+Apply by:
+25 Mar 2026
+Part-Time Psychology Intern (Telugu Speaking)
+Nayi Disha
+Location:
+Telangana
+Apply by:
+20 Mar 2026
+Field Mobilizer
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
 RFP for Data Collection for Foundational Reading ...
 Lords Education and Health Society (LEHS)
 Location:
 Odisha
 Apply by:
 15 Mar 2026
-Project Research Scientist – I (Non Medical)
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Technical Support - III
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Program Lead- Governance and Gender Justice
-Society for Women's Action and Training Initiativ...
-Location:
-Gujarat
-Apply by:
-25 Mar 2026
-Senior Field Officer Certification Management
-Fairtrade India Project - CSM
-Location:
-Andhra Pradesh
-Apply by:
-15 Mar 2026
-Design and Readiness Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Program Manager – AI Skilling Initiative
-SwaTaleem Foundation
-Location:
-Haryana
-Apply by:
-05 Apr 2026
-Communications Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
 Jobseekers
 Register
 Login
@@ -3659,6 +2977,463 @@
 Recruitment Exchange</t>
         </is>
       </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="G13" s="1" t="inlineStr">
+        <is>
+          <t>15-03-2026</t>
+        </is>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I13" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287910</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr"/>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>ToR - Portfolio-Wide Learning Exercise cum review for the Health Domain</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>ChildFund India | India
+International Development - ToR - Portfolio-Wide Learning Exercise cum review for the Health Domain, ChildFund India, India - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers:
+Login
+|
+Register ... Read More</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>• Job Email ID:
+centralpurchase2(at)childfundindia.org
+Download Attachment:
+TOR  Health Portfolio_23.2.2026.doc
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+15 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+Manager - Individual Engagement (Acquisition)
+(Value Members only)
+Location:
+Maharashtra
+Apply by:
+10 Mar 2026
+Part Time Accountant
+Sahabhagi Vikash Abhiyan
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Coordinator
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
+Consultant Architects
+(Value Members only)
+Location:
+Chhattisgarh
+Apply by:
+18 Mar 2026
+Community Mobilizer
+Common Man Trust
+Location:
+Delhi, Uttar Pradesh, Haryana
+Apply by:
+25 Mar 2026
+Part-Time Psychology Intern (Telugu Speaking)
+Nayi Disha
+Location:
+Telangana
+Apply by:
+20 Mar 2026
+Field Mobilizer
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
+RFP for Data Collection for Foundational Reading ...
+Lords Education and Health Society (LEHS)
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t>Learning, Safety</t>
+        </is>
+      </c>
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t>15-03-2026</t>
+        </is>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I14" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287901</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr"/>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>RFP - for Empanelment of Knowledge Partners for Grooming of students for ...</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>TeamLease Foundation | India
+International Development - RFP - for  Empanelment of Knowledge Partners for Grooming of students for competitive examination (through partner) Super 30 Model, TeamLease Foundation, India - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast ... Read More</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F15" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G15" s="1" t="inlineStr">
+        <is>
+          <t>15-03-2026</t>
+        </is>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I15" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287763</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr"/>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>ToR - Strategic Review and Forward-Looking Education Strategy Development</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>ChildFund India | India
+International Development - ToR - Strategic Review and Forward-Looking Education Strategy Development, ChildFund India, India - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers:
+Login
+|
+Registe ... Read More</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>• Job Email ID:
+centralpurchase2(at)childfundindia.org
+Download Attachment:
+ToR for Education.doc
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+15 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+Manager - Individual Engagement (Acquisition)
+(Value Members only)
+Location:
+Maharashtra
+Apply by:
+10 Mar 2026
+Part Time Accountant
+Sahabhagi Vikash Abhiyan
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Coordinator
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
+Consultant Architects
+(Value Members only)
+Location:
+Chhattisgarh
+Apply by:
+18 Mar 2026
+Community Mobilizer
+Common Man Trust
+Location:
+Delhi, Uttar Pradesh, Haryana
+Apply by:
+25 Mar 2026
+Part-Time Psychology Intern (Telugu Speaking)
+Nayi Disha
+Location:
+Telangana
+Apply by:
+20 Mar 2026
+Field Mobilizer
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
+RFP for Data Collection for Foundational Reading ...
+Lords Education and Health Society (LEHS)
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
           <t>Learning, Safety</t>
@@ -3670,11 +3445,11 @@
         </is>
       </c>
       <c r="H16" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I16" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287901</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287902</t>
         </is>
       </c>
     </row>
@@ -3790,13 +3565,13 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
 Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
 Project Potential
 Location:
 Bihar
@@ -3804,54 +3579,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+Manager - Individual Engagement (Acquisition)
+(Value Members only)
+Location:
+Maharashtra
+Apply by:
+10 Mar 2026
+Part Time Accountant
+Sahabhagi Vikash Abhiyan
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Coordinator
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
+Consultant Architects
+(Value Members only)
+Location:
+Chhattisgarh
+Apply by:
+18 Mar 2026
+Community Mobilizer
+Common Man Trust
+Location:
+Delhi, Uttar Pradesh, Haryana
+Apply by:
+25 Mar 2026
+Part-Time Psychology Intern (Telugu Speaking)
+Nayi Disha
+Location:
+Telangana
+Apply by:
+20 Mar 2026
+Field Mobilizer
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
 RFP for Data Collection for Foundational Reading ...
 Lords Education and Health Society (LEHS)
 Location:
 Odisha
 Apply by:
 15 Mar 2026
-Project Research Scientist – I (Non Medical)
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Technical Support - III
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Program Lead- Governance and Gender Justice
-Society for Women's Action and Training Initiativ...
-Location:
-Gujarat
-Apply by:
-25 Mar 2026
-Senior Field Officer Certification Management
-Fairtrade India Project - CSM
-Location:
-Andhra Pradesh
-Apply by:
-15 Mar 2026
-Design and Readiness Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Program Manager – AI Skilling Initiative
-SwaTaleem Foundation
-Location:
-Haryana
-Apply by:
-05 Apr 2026
-Communications Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
 Jobseekers
 Register
 Login
@@ -3890,7 +3665,7 @@
         </is>
       </c>
       <c r="H17" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I17" s="1" t="inlineStr">
         <is>
@@ -4053,13 +3828,13 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
 Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
 Project Potential
 Location:
 Bihar
@@ -4067,54 +3842,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+Manager - Individual Engagement (Acquisition)
+(Value Members only)
+Location:
+Maharashtra
+Apply by:
+10 Mar 2026
+Part Time Accountant
+Sahabhagi Vikash Abhiyan
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Coordinator
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
+Consultant Architects
+(Value Members only)
+Location:
+Chhattisgarh
+Apply by:
+18 Mar 2026
+Community Mobilizer
+Common Man Trust
+Location:
+Delhi, Uttar Pradesh, Haryana
+Apply by:
+25 Mar 2026
+Part-Time Psychology Intern (Telugu Speaking)
+Nayi Disha
+Location:
+Telangana
+Apply by:
+20 Mar 2026
+Field Mobilizer
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
 RFP for Data Collection for Foundational Reading ...
 Lords Education and Health Society (LEHS)
 Location:
 Odisha
 Apply by:
 15 Mar 2026
-Project Research Scientist – I (Non Medical)
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Technical Support - III
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Program Lead- Governance and Gender Justice
-Society for Women's Action and Training Initiativ...
-Location:
-Gujarat
-Apply by:
-25 Mar 2026
-Senior Field Officer Certification Management
-Fairtrade India Project - CSM
-Location:
-Andhra Pradesh
-Apply by:
-15 Mar 2026
-Design and Readiness Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Program Manager – AI Skilling Initiative
-SwaTaleem Foundation
-Location:
-Haryana
-Apply by:
-05 Apr 2026
-Communications Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
 Jobseekers
 Register
 Login
@@ -4153,7 +3928,7 @@
         </is>
       </c>
       <c r="H18" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I18" s="1" t="inlineStr">
         <is>
@@ -4170,486 +3945,10 @@
       <c r="B19" s="1" t="inlineStr"/>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>ToR - Livelihoods Strategy Review and Future Direction Roadmap</t>
+          <t>RFP - Big IC+ISA RFP - Selection of a Service Provider for Supply, Instal...</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>ChildFund India | India
-International Development - ToR - Livelihoods Strategy Review and Future Direction Roadmap, ChildFund India, India - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Login
-|
-Register
-Jobseeker ... Read More</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>• To determine the relevance, alignment, and coherence of the Livelihood Program under CSP 2022–2027 with national priorities, donor expectations, and organizational mandate.
-To assess the extent to which planned outputs and outcomes have been achieved and to evaluate the quality and impact of program interventions.
-Identify achievements, innovations, good practices, and enabling factors across Livelihood program interventions.
-Document gaps, challenges, and areas for strengthening
-To examine the sustainability of program outcomes and the institutional readiness of ChildFund India for long-term resilience and growth.
-Facilitate reflection through workshops involving staff, partners, and selected beneficiaries and provide recommendations for strategic direction, scalability, and future program priorities.
-Proposal Submission
-Interested evaluators/agencies are invited to submit:
-Technical proposal outlining approach and methodology
-Team composition and relevant experience
-Financial proposal with a detailed budget
-Sample of previous qualitative evaluation work
-Interested evaluators/agencies are requested to submit their technical and financial proposals to
-centralpurchase2@childfundindia.org
-by 15 March 2026.
-Reference No:- PRA/CFI/DEL/2025-26/053
-ChildFund India reserves the right to modify this ToR based on programmatic and contextual requirements.
-For detailed information, please check the complete version of the advert attached below.
-• Job Email ID:
-centralpurchase2(at)childfundindia.org
-Download Attachment:
-ToR Livelihood Portfolio-6.3.2026.doc
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-15 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Associate – Finance and Operations
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-RFP for Data Collection for Foundational Reading ...
-Lords Education and Health Society (LEHS)
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Research Scientist – I (Non Medical)
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Technical Support - III
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Program Lead- Governance and Gender Justice
-Society for Women's Action and Training Initiativ...
-Location:
-Gujarat
-Apply by:
-25 Mar 2026
-Senior Field Officer Certification Management
-Fairtrade India Project - CSM
-Location:
-Andhra Pradesh
-Apply by:
-15 Mar 2026
-Design and Readiness Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Program Manager – AI Skilling Initiative
-SwaTaleem Foundation
-Location:
-Haryana
-Apply by:
-05 Apr 2026
-Communications Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F19" s="1" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="G19" s="1" t="inlineStr">
-        <is>
-          <t>15-03-2026</t>
-        </is>
-      </c>
-      <c r="H19" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="I19" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287910</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B20" s="1" t="inlineStr"/>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>ToR - Strategic Review and Forward-Looking Education Strategy Development</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>ChildFund India | India
-International Development - ToR - Strategic Review and Forward-Looking Education Strategy Development, ChildFund India, India - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Login
-|
-Registe ... Read More</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>• Job Email ID:
-centralpurchase2(at)childfundindia.org
-Download Attachment:
-ToR for Education.doc
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-15 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Associate – Finance and Operations
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-RFP for Data Collection for Foundational Reading ...
-Lords Education and Health Society (LEHS)
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Research Scientist – I (Non Medical)
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Technical Support - III
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Program Lead- Governance and Gender Justice
-Society for Women's Action and Training Initiativ...
-Location:
-Gujarat
-Apply by:
-25 Mar 2026
-Senior Field Officer Certification Management
-Fairtrade India Project - CSM
-Location:
-Andhra Pradesh
-Apply by:
-15 Mar 2026
-Design and Readiness Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Program Manager – AI Skilling Initiative
-SwaTaleem Foundation
-Location:
-Haryana
-Apply by:
-05 Apr 2026
-Communications Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>Learning, Safety</t>
-        </is>
-      </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>15-03-2026</t>
-        </is>
-      </c>
-      <c r="H20" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="I20" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287902</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B21" s="1" t="inlineStr"/>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>RFP - for Empanelment of Knowledge Partners for Grooming of students for ...</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>TeamLease Foundation | India
-International Development - RFP - for  Empanelment of Knowledge Partners for Grooming of students for competitive examination (through partner) Super 30 Model, TeamLease Foundation, India - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast ... Read More</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F21" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G21" s="1" t="inlineStr">
-        <is>
-          <t>15-03-2026</t>
-        </is>
-      </c>
-      <c r="H21" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="I21" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287763</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B22" s="1" t="inlineStr"/>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Big IC+ISA RFP - Selection of a Service Provider for Supply, Instal...</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>EAII Advisors Pvt Ltd | Andhra Pradesh
 International Development - RFP - Big IC+ISA RFP -  Selection of a Service Provider for Supply, Installation and Operation &amp; Maintenance of 150 ILC Devices and Capacity Building., EAII Advisors Pvt Ltd, Andhra Pradesh - DevNetJobsIndia.org
@@ -4658,7 +3957,7 @@
 | ... Read More</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>• 2. Purpose of the RFP:
 2.1  EAII is soliciting bids for:
@@ -4753,13 +4052,13 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
 Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
 Project Potential
 Location:
 Bihar
@@ -4767,54 +4066,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+Manager - Individual Engagement (Acquisition)
+(Value Members only)
+Location:
+Maharashtra
+Apply by:
+10 Mar 2026
+Part Time Accountant
+Sahabhagi Vikash Abhiyan
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Coordinator
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
+Consultant Architects
+(Value Members only)
+Location:
+Chhattisgarh
+Apply by:
+18 Mar 2026
+Community Mobilizer
+Common Man Trust
+Location:
+Delhi, Uttar Pradesh, Haryana
+Apply by:
+25 Mar 2026
+Part-Time Psychology Intern (Telugu Speaking)
+Nayi Disha
+Location:
+Telangana
+Apply by:
+20 Mar 2026
+Field Mobilizer
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
 RFP for Data Collection for Foundational Reading ...
 Lords Education and Health Society (LEHS)
 Location:
 Odisha
 Apply by:
 15 Mar 2026
-Project Research Scientist – I (Non Medical)
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Technical Support - III
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Program Lead- Governance and Gender Justice
-Society for Women's Action and Training Initiativ...
-Location:
-Gujarat
-Apply by:
-25 Mar 2026
-Senior Field Officer Certification Management
-Fairtrade India Project - CSM
-Location:
-Andhra Pradesh
-Apply by:
-15 Mar 2026
-Design and Readiness Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Program Manager – AI Skilling Initiative
-SwaTaleem Foundation
-Location:
-Haryana
-Apply by:
-05 Apr 2026
-Communications Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
 Jobseekers
 Register
 Login
@@ -4842,38 +4141,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F22" s="1" t="inlineStr">
+      <c r="F19" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G22" s="1" t="inlineStr">
+      <c r="G19" s="1" t="inlineStr">
         <is>
           <t>16-03-2026</t>
         </is>
       </c>
-      <c r="H22" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="I22" s="1" t="inlineStr">
+      <c r="H19" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="I19" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287172</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr"/>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="B20" s="1" t="inlineStr"/>
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>Specialist – Communication</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Financial Management Service Foundation (FMSF) | Uttar Pradesh
 International Development - Specialist – Communication, Financial Management Service Foundation (FMSF), Uttar Pradesh - DevNetJobsIndia.org
@@ -4889,7 +4188,7 @@
 Eve ... Read More</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>• Joining FMSF means becoming part of a passionate team dedicated to making a positive impact. We offer competitive compensation, opportunities for professional development, and a supportive work environment where your contributions are valued and recognized. If you are committed to driving positive change, promoting accountability and strengthening the development sector, we encourage you to apply for the position of Specialist – Communication at FMSF.
 • How to Apply:
@@ -4959,13 +4258,13 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
 Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
 Project Potential
 Location:
 Bihar
@@ -4973,54 +4272,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+Manager - Individual Engagement (Acquisition)
+(Value Members only)
+Location:
+Maharashtra
+Apply by:
+10 Mar 2026
+Part Time Accountant
+Sahabhagi Vikash Abhiyan
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Coordinator
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
+Consultant Architects
+(Value Members only)
+Location:
+Chhattisgarh
+Apply by:
+18 Mar 2026
+Community Mobilizer
+Common Man Trust
+Location:
+Delhi, Uttar Pradesh, Haryana
+Apply by:
+25 Mar 2026
+Part-Time Psychology Intern (Telugu Speaking)
+Nayi Disha
+Location:
+Telangana
+Apply by:
+20 Mar 2026
+Field Mobilizer
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
 RFP for Data Collection for Foundational Reading ...
 Lords Education and Health Society (LEHS)
 Location:
 Odisha
 Apply by:
 15 Mar 2026
-Project Research Scientist – I (Non Medical)
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Technical Support - III
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Program Lead- Governance and Gender Justice
-Society for Women's Action and Training Initiativ...
-Location:
-Gujarat
-Apply by:
-25 Mar 2026
-Senior Field Officer Certification Management
-Fairtrade India Project - CSM
-Location:
-Andhra Pradesh
-Apply by:
-15 Mar 2026
-Design and Readiness Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Program Manager – AI Skilling Initiative
-SwaTaleem Foundation
-Location:
-Haryana
-Apply by:
-05 Apr 2026
-Communications Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
 Jobseekers
 Register
 Login
@@ -5048,38 +4347,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F23" s="1" t="inlineStr">
+      <c r="F20" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G23" s="1" t="inlineStr">
+      <c r="G20" s="1" t="inlineStr">
         <is>
           <t>19-03-2026</t>
         </is>
       </c>
-      <c r="H23" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="I23" s="1" t="inlineStr">
+      <c r="H20" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="I20" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287207</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr"/>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="B21" s="1" t="inlineStr"/>
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>RFP - Consultancy for development of descriptive documentation of Ashiyana...</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Prerana | Mumbai, Maharashtra
 International Development - RFP - Consultancy for development of descriptive documentation of Ashiyana Implementation &amp; Practice Framework, and produce a replication-ready, Prerana, Maharashtra - DevNetJobsIndia.org
@@ -5092,7 +4391,7 @@
 Br ... Read More</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>• Submission Details
 Proposals must be submitted by email to:
@@ -5164,13 +4463,13 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
 Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
 Project Potential
 Location:
 Bihar
@@ -5178,54 +4477,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+Manager - Individual Engagement (Acquisition)
+(Value Members only)
+Location:
+Maharashtra
+Apply by:
+10 Mar 2026
+Part Time Accountant
+Sahabhagi Vikash Abhiyan
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Coordinator
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
+Consultant Architects
+(Value Members only)
+Location:
+Chhattisgarh
+Apply by:
+18 Mar 2026
+Community Mobilizer
+Common Man Trust
+Location:
+Delhi, Uttar Pradesh, Haryana
+Apply by:
+25 Mar 2026
+Part-Time Psychology Intern (Telugu Speaking)
+Nayi Disha
+Location:
+Telangana
+Apply by:
+20 Mar 2026
+Field Mobilizer
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
 RFP for Data Collection for Foundational Reading ...
 Lords Education and Health Society (LEHS)
 Location:
 Odisha
 Apply by:
 15 Mar 2026
-Project Research Scientist – I (Non Medical)
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Technical Support - III
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Program Lead- Governance and Gender Justice
-Society for Women's Action and Training Initiativ...
-Location:
-Gujarat
-Apply by:
-25 Mar 2026
-Senior Field Officer Certification Management
-Fairtrade India Project - CSM
-Location:
-Andhra Pradesh
-Apply by:
-15 Mar 2026
-Design and Readiness Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Program Manager – AI Skilling Initiative
-SwaTaleem Foundation
-Location:
-Haryana
-Apply by:
-05 Apr 2026
-Communications Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
 Jobseekers
 Register
 Login
@@ -5253,38 +4552,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F24" s="1" t="inlineStr">
+      <c r="F21" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G24" s="1" t="inlineStr">
+      <c r="G21" s="1" t="inlineStr">
         <is>
           <t>21-03-2026</t>
         </is>
       </c>
-      <c r="H24" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="I24" s="1" t="inlineStr">
+      <c r="H21" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="I21" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287890</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr"/>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="B22" s="1" t="inlineStr"/>
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>Specialist - Grants</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Financial Management Service Foundation (FMSF) | Uttar Pradesh
 International Development - Specialist - Grants, Financial Management Service Foundation (FMSF), Uttar Pradesh - DevNetJobsIndia.org
@@ -5301,7 +4600,7 @@
 Job ... Read More</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>• Joining FMSF means becoming part of a passionate team dedicated to making a positive impact. We offer competitive compensation, opportunities for professional development, and a supportive work environment where your contributions are valued and recognized. If you are committed to driving positive change, promoting accountability and strengthening the development sector, we encourage you to apply for the position of Specialist - Grants at FMSF.
 You’re Resume to be accompanied with:
@@ -5371,13 +4670,13 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
 Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
 Project Potential
 Location:
 Bihar
@@ -5385,54 +4684,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+Manager - Individual Engagement (Acquisition)
+(Value Members only)
+Location:
+Maharashtra
+Apply by:
+10 Mar 2026
+Part Time Accountant
+Sahabhagi Vikash Abhiyan
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Coordinator
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
+Consultant Architects
+(Value Members only)
+Location:
+Chhattisgarh
+Apply by:
+18 Mar 2026
+Community Mobilizer
+Common Man Trust
+Location:
+Delhi, Uttar Pradesh, Haryana
+Apply by:
+25 Mar 2026
+Part-Time Psychology Intern (Telugu Speaking)
+Nayi Disha
+Location:
+Telangana
+Apply by:
+20 Mar 2026
+Field Mobilizer
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
 RFP for Data Collection for Foundational Reading ...
 Lords Education and Health Society (LEHS)
 Location:
 Odisha
 Apply by:
 15 Mar 2026
-Project Research Scientist – I (Non Medical)
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Technical Support - III
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Program Lead- Governance and Gender Justice
-Society for Women's Action and Training Initiativ...
-Location:
-Gujarat
-Apply by:
-25 Mar 2026
-Senior Field Officer Certification Management
-Fairtrade India Project - CSM
-Location:
-Andhra Pradesh
-Apply by:
-15 Mar 2026
-Design and Readiness Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Program Manager – AI Skilling Initiative
-SwaTaleem Foundation
-Location:
-Haryana
-Apply by:
-05 Apr 2026
-Communications Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
 Jobseekers
 Register
 Login
@@ -5460,38 +4759,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F25" s="1" t="inlineStr">
+      <c r="F22" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G25" s="1" t="inlineStr">
+      <c r="G22" s="1" t="inlineStr">
         <is>
           <t>21-03-2026</t>
         </is>
       </c>
-      <c r="H25" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="I25" s="1" t="inlineStr">
+      <c r="H22" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="I22" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287318</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr"/>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="B23" s="1" t="inlineStr"/>
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>EoI – Mobile Medical Units, Ai-Enabled Tb Screening &amp; Supply Of Medical An...</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Ashray Foundation | Korba, Chattisgarh (Delivery Location), Gujarat
 International Development - EoI – Mobile Medical Units, Ai-Enabled Tb Screening &amp; Supply Of Medical And Nutritional Support, Ashray Foundation, Gujarat - DevNetJobsIndia.org
@@ -5504,7 +4803,7 @@
 Broadc ... Read More</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>• Ashray Foundation invites eligible and experienced agencies to submit their Expression of Interest / for the following scope of work:
 Fabrication of Mobile Medical Units (MMUs) – 2 Units
@@ -5579,13 +4878,13 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
 Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
 Project Potential
 Location:
 Bihar
@@ -5593,54 +4892,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+Manager - Individual Engagement (Acquisition)
+(Value Members only)
+Location:
+Maharashtra
+Apply by:
+10 Mar 2026
+Part Time Accountant
+Sahabhagi Vikash Abhiyan
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Coordinator
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
+Consultant Architects
+(Value Members only)
+Location:
+Chhattisgarh
+Apply by:
+18 Mar 2026
+Community Mobilizer
+Common Man Trust
+Location:
+Delhi, Uttar Pradesh, Haryana
+Apply by:
+25 Mar 2026
+Part-Time Psychology Intern (Telugu Speaking)
+Nayi Disha
+Location:
+Telangana
+Apply by:
+20 Mar 2026
+Field Mobilizer
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
 RFP for Data Collection for Foundational Reading ...
 Lords Education and Health Society (LEHS)
 Location:
 Odisha
 Apply by:
 15 Mar 2026
-Project Research Scientist – I (Non Medical)
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Technical Support - III
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Program Lead- Governance and Gender Justice
-Society for Women's Action and Training Initiativ...
-Location:
-Gujarat
-Apply by:
-25 Mar 2026
-Senior Field Officer Certification Management
-Fairtrade India Project - CSM
-Location:
-Andhra Pradesh
-Apply by:
-15 Mar 2026
-Design and Readiness Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Program Manager – AI Skilling Initiative
-SwaTaleem Foundation
-Location:
-Haryana
-Apply by:
-05 Apr 2026
-Communications Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
 Jobseekers
 Register
 Login
@@ -5668,38 +4967,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F26" s="1" t="inlineStr">
+      <c r="F23" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G26" s="1" t="inlineStr">
+      <c r="G23" s="1" t="inlineStr">
         <is>
           <t>24-03-2026</t>
         </is>
       </c>
-      <c r="H26" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="I26" s="1" t="inlineStr">
+      <c r="H23" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="I23" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287319</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr"/>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="B24" s="1" t="inlineStr"/>
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>RFP - End of Program Evaluation Accelerating Access to Safe Water and San...</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Water.org | Bangladesh, Cambodia, India
 International Development - RFP - End of Program Evaluation  Accelerating Access to Safe Water and Sanitation, Financing, Water.org, India - DevNetJobsIndia.org
@@ -5715,7 +5014,7 @@
 Event ... Read More</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>• The evaluation will require the firm to facilitate and coordinate with Water.org staff and partners. The program requires the firm to submit the deliverables outlined in section 2 Scope of Work.
 C.
@@ -5808,13 +5107,13 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
 Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
 Project Potential
 Location:
 Bihar
@@ -5822,54 +5121,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+Manager - Individual Engagement (Acquisition)
+(Value Members only)
+Location:
+Maharashtra
+Apply by:
+10 Mar 2026
+Part Time Accountant
+Sahabhagi Vikash Abhiyan
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Coordinator
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
+Consultant Architects
+(Value Members only)
+Location:
+Chhattisgarh
+Apply by:
+18 Mar 2026
+Community Mobilizer
+Common Man Trust
+Location:
+Delhi, Uttar Pradesh, Haryana
+Apply by:
+25 Mar 2026
+Part-Time Psychology Intern (Telugu Speaking)
+Nayi Disha
+Location:
+Telangana
+Apply by:
+20 Mar 2026
+Field Mobilizer
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
 RFP for Data Collection for Foundational Reading ...
 Lords Education and Health Society (LEHS)
 Location:
 Odisha
 Apply by:
 15 Mar 2026
-Project Research Scientist – I (Non Medical)
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Technical Support - III
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Program Lead- Governance and Gender Justice
-Society for Women's Action and Training Initiativ...
-Location:
-Gujarat
-Apply by:
-25 Mar 2026
-Senior Field Officer Certification Management
-Fairtrade India Project - CSM
-Location:
-Andhra Pradesh
-Apply by:
-15 Mar 2026
-Design and Readiness Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Program Manager – AI Skilling Initiative
-SwaTaleem Foundation
-Location:
-Haryana
-Apply by:
-05 Apr 2026
-Communications Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
 Jobseekers
 Register
 Login
@@ -5897,267 +5196,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F27" s="1" t="inlineStr">
+      <c r="F24" s="1" t="inlineStr">
         <is>
           <t>Governance, Safety</t>
         </is>
       </c>
-      <c r="G27" s="1" t="inlineStr">
+      <c r="G24" s="1" t="inlineStr">
         <is>
           <t>25-03-2026</t>
         </is>
       </c>
-      <c r="H27" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="I27" s="1" t="inlineStr">
+      <c r="H24" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="I24" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287835</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr"/>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>Junior Research Technicians / Senior Project Asso...</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Starshield Security Solution Pvt.Ltd | Uttar Pradesh
-International Development - Junior Research Technicians / Senior Project Associate, Starshield Security Solution Pvt.Ltd, Uttar Pradesh - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search ... Read More</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>• Eligibility Criteria
-Qualification
-:
-Intermediate with 2–3 years of relevant experience
-OR
-Graduate with 1–2 years of relevant experience
-Skills &amp; Experience (Mandatory):
-Experience in agriculture field operations and data collection
-Basic knowledge of MS Office (Word &amp; Excel)
-Experience in rice-wheat cropping system production preferred
-Good coordination and communication skills
-Willingness to travel and work in field conditions
-Knowledge of smart mobile apps for data survey and data recording
-Knowledge on agri machinery
-Community mobilization and Work with Farmers group/FPCs
-The applicants must have a two-wheeler vehicle and license with them
-Key Performance Indicators
-Timely support to demonstrations, trainings, and field activities
-Accurate data collection and documentation
-Proper maintenance of equipment and field sites
-Positive feedback from farmers and stakeholders
-Creation of new service providers
-Application Details
-Interested candidates are requested to fill-out the shared application form and submit their updated CV via email to
-communications@starshieldsolution.com
-with the subject line:
-Application for Junior Research Technician (IRRI Project Deployment)
-.
-Only shortlisted candidates who complete the required documentation will be considered for subsequent stages of selection.
-Selection will be done on a first-come-first-served basis. Applications received up to Thursday each week will be reviewed, and interviews will be conducted in the following week. As soon as we shall finish all recruitment, we will take the advertisement off.
-• Job Email ID:
-communications(at)starshieldsolution.com
-Download Attachment:
-Application Proforma_Junior Research Technicians -  Senior Project Associate.doc
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-30 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Associate – Finance and Operations
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-RFP for Data Collection for Foundational Reading ...
-Lords Education and Health Society (LEHS)
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Research Scientist – I (Non Medical)
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Technical Support - III
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Program Lead- Governance and Gender Justice
-Society for Women's Action and Training Initiativ...
-Location:
-Gujarat
-Apply by:
-25 Mar 2026
-Senior Field Officer Certification Management
-Fairtrade India Project - CSM
-Location:
-Andhra Pradesh
-Apply by:
-15 Mar 2026
-Design and Readiness Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Program Manager – AI Skilling Initiative
-SwaTaleem Foundation
-Location:
-Haryana
-Apply by:
-05 Apr 2026
-Communications Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F28" s="1" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="G28" s="1" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="H28" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="I28" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287635</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B29" s="1" t="inlineStr"/>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="B25" s="1" t="inlineStr"/>
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>Agriculture Research Development Officer / Projec...</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Starshield Security Solution Pvt.Ltd | Uttar Pradesh
 International Development - Agriculture Research Development Officer / Project Scientist III, Starshield Security Solution Pvt.Ltd, Uttar Pradesh - DevNetJobsIndia.org
@@ -6171,7 +5241,7 @@
 RFPs/Tende ... Read More</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>• Eligibility Criteria
 Qualification:
@@ -6266,13 +5336,13 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
 Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
 Project Potential
 Location:
 Bihar
@@ -6280,54 +5350,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+Manager - Individual Engagement (Acquisition)
+(Value Members only)
+Location:
+Maharashtra
+Apply by:
+10 Mar 2026
+Part Time Accountant
+Sahabhagi Vikash Abhiyan
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Coordinator
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
+Consultant Architects
+(Value Members only)
+Location:
+Chhattisgarh
+Apply by:
+18 Mar 2026
+Community Mobilizer
+Common Man Trust
+Location:
+Delhi, Uttar Pradesh, Haryana
+Apply by:
+25 Mar 2026
+Part-Time Psychology Intern (Telugu Speaking)
+Nayi Disha
+Location:
+Telangana
+Apply by:
+20 Mar 2026
+Field Mobilizer
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
 RFP for Data Collection for Foundational Reading ...
 Lords Education and Health Society (LEHS)
 Location:
 Odisha
 Apply by:
 15 Mar 2026
-Project Research Scientist – I (Non Medical)
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Technical Support - III
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Program Lead- Governance and Gender Justice
-Society for Women's Action and Training Initiativ...
-Location:
-Gujarat
-Apply by:
-25 Mar 2026
-Senior Field Officer Certification Management
-Fairtrade India Project - CSM
-Location:
-Andhra Pradesh
-Apply by:
-15 Mar 2026
-Design and Readiness Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Program Manager – AI Skilling Initiative
-SwaTaleem Foundation
-Location:
-Haryana
-Apply by:
-05 Apr 2026
-Communications Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
 Jobseekers
 Register
 Login
@@ -6355,38 +5425,267 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F29" s="1" t="inlineStr">
+      <c r="F25" s="1" t="inlineStr">
         <is>
           <t>Learning, Safety</t>
         </is>
       </c>
-      <c r="G29" s="1" t="inlineStr">
+      <c r="G25" s="1" t="inlineStr">
         <is>
           <t>30-03-2026</t>
         </is>
       </c>
-      <c r="H29" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="I29" s="1" t="inlineStr">
+      <c r="H25" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="I25" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287636</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B30" s="1" t="inlineStr"/>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="B26" s="1" t="inlineStr"/>
+      <c r="C26" s="1" t="inlineStr">
+        <is>
+          <t>Junior Research Technicians / Senior Project Asso...</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Starshield Security Solution Pvt.Ltd | Uttar Pradesh
+International Development - Junior Research Technicians / Senior Project Associate, Starshield Security Solution Pvt.Ltd, Uttar Pradesh - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search ... Read More</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>• Eligibility Criteria
+Qualification
+:
+Intermediate with 2–3 years of relevant experience
+OR
+Graduate with 1–2 years of relevant experience
+Skills &amp; Experience (Mandatory):
+Experience in agriculture field operations and data collection
+Basic knowledge of MS Office (Word &amp; Excel)
+Experience in rice-wheat cropping system production preferred
+Good coordination and communication skills
+Willingness to travel and work in field conditions
+Knowledge of smart mobile apps for data survey and data recording
+Knowledge on agri machinery
+Community mobilization and Work with Farmers group/FPCs
+The applicants must have a two-wheeler vehicle and license with them
+Key Performance Indicators
+Timely support to demonstrations, trainings, and field activities
+Accurate data collection and documentation
+Proper maintenance of equipment and field sites
+Positive feedback from farmers and stakeholders
+Creation of new service providers
+Application Details
+Interested candidates are requested to fill-out the shared application form and submit their updated CV via email to
+communications@starshieldsolution.com
+with the subject line:
+Application for Junior Research Technician (IRRI Project Deployment)
+.
+Only shortlisted candidates who complete the required documentation will be considered for subsequent stages of selection.
+Selection will be done on a first-come-first-served basis. Applications received up to Thursday each week will be reviewed, and interviews will be conducted in the following week. As soon as we shall finish all recruitment, we will take the advertisement off.
+• Job Email ID:
+communications(at)starshieldsolution.com
+Download Attachment:
+Application Proforma_Junior Research Technicians -  Senior Project Associate.doc
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+30 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+Manager - Individual Engagement (Acquisition)
+(Value Members only)
+Location:
+Maharashtra
+Apply by:
+10 Mar 2026
+Part Time Accountant
+Sahabhagi Vikash Abhiyan
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Coordinator
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
+Consultant Architects
+(Value Members only)
+Location:
+Chhattisgarh
+Apply by:
+18 Mar 2026
+Community Mobilizer
+Common Man Trust
+Location:
+Delhi, Uttar Pradesh, Haryana
+Apply by:
+25 Mar 2026
+Part-Time Psychology Intern (Telugu Speaking)
+Nayi Disha
+Location:
+Telangana
+Apply by:
+20 Mar 2026
+Field Mobilizer
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
+RFP for Data Collection for Foundational Reading ...
+Lords Education and Health Society (LEHS)
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F26" s="1" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="G26" s="1" t="inlineStr">
+        <is>
+          <t>30-03-2026</t>
+        </is>
+      </c>
+      <c r="H26" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="I26" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287635</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="inlineStr"/>
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>Sector Experts</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Academy of Management Studies (AMS) | India
 International Development - Sector Experts, Academy of Management Studies (AMS), India - DevNetJobsIndia.org
@@ -6407,7 +5706,7 @@
 Jobseekers Login ... Read More</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>• Eligibility
 Postgraduate degree / Ph.D. in relevant or allied disciplines
@@ -6489,13 +5788,13 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
 Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
 Project Potential
 Location:
 Bihar
@@ -6503,54 +5802,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+Manager - Individual Engagement (Acquisition)
+(Value Members only)
+Location:
+Maharashtra
+Apply by:
+10 Mar 2026
+Part Time Accountant
+Sahabhagi Vikash Abhiyan
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Coordinator
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
+Consultant Architects
+(Value Members only)
+Location:
+Chhattisgarh
+Apply by:
+18 Mar 2026
+Community Mobilizer
+Common Man Trust
+Location:
+Delhi, Uttar Pradesh, Haryana
+Apply by:
+25 Mar 2026
+Part-Time Psychology Intern (Telugu Speaking)
+Nayi Disha
+Location:
+Telangana
+Apply by:
+20 Mar 2026
+Field Mobilizer
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
 RFP for Data Collection for Foundational Reading ...
 Lords Education and Health Society (LEHS)
 Location:
 Odisha
 Apply by:
 15 Mar 2026
-Project Research Scientist – I (Non Medical)
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Technical Support - III
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Program Lead- Governance and Gender Justice
-Society for Women's Action and Training Initiativ...
-Location:
-Gujarat
-Apply by:
-25 Mar 2026
-Senior Field Officer Certification Management
-Fairtrade India Project - CSM
-Location:
-Andhra Pradesh
-Apply by:
-15 Mar 2026
-Design and Readiness Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Program Manager – AI Skilling Initiative
-SwaTaleem Foundation
-Location:
-Haryana
-Apply by:
-05 Apr 2026
-Communications Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
 Jobseekers
 Register
 Login
@@ -6578,38 +5877,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F30" s="1" t="inlineStr">
+      <c r="F27" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G30" s="1" t="inlineStr">
+      <c r="G27" s="1" t="inlineStr">
         <is>
           <t>31-03-2026</t>
         </is>
       </c>
-      <c r="H30" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="I30" s="1" t="inlineStr">
+      <c r="H27" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="I27" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287726</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr"/>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="B28" s="1" t="inlineStr"/>
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>Associate – Finance and Operations</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Financial Management Service Foundation (FMSF) | Uttar Pradesh
 International Development - Associate – Finance and Operations, Financial Management Service Foundation (FMSF), Uttar Pradesh - DevNetJobsIndia.org
@@ -6624,7 +5923,7 @@
 Search ... Read More</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>• Joining FMSF means becoming part of a passionate team dedicated to making a positive impact. We offer competitive compensation, opportunities for professional development, and a supportive work environment where your contributions are valued and recognized. If you are committed to driving positive change, promoting accountability and strengthening the development sector, we encourage you to apply for the position of
 Associate – Finance and Operations
@@ -6694,13 +5993,13 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Associate (Programme Management)
-Indian Institute For Human Settlements (Iihs)
-Location:
-Karnataka
-Apply by:
-07 Mar 2026
 Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
 Project Potential
 Location:
 Bihar
@@ -6708,54 +6007,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
+Manager - Individual Engagement (Acquisition)
+(Value Members only)
+Location:
+Maharashtra
+Apply by:
+10 Mar 2026
+Part Time Accountant
+Sahabhagi Vikash Abhiyan
+Location:
+Odisha
+Apply by:
+15 Mar 2026
+Project Coordinator
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
+Consultant Architects
+(Value Members only)
+Location:
+Chhattisgarh
+Apply by:
+18 Mar 2026
+Community Mobilizer
+Common Man Trust
+Location:
+Delhi, Uttar Pradesh, Haryana
+Apply by:
+25 Mar 2026
+Part-Time Psychology Intern (Telugu Speaking)
+Nayi Disha
+Location:
+Telangana
+Apply by:
+20 Mar 2026
+Field Mobilizer
+Hanuman Prasad Gramin Vikas Seva Samiti
+Location:
+Bihar
+Apply by:
+15 Mar 2026
 RFP for Data Collection for Foundational Reading ...
 Lords Education and Health Society (LEHS)
 Location:
 Odisha
 Apply by:
 15 Mar 2026
-Project Research Scientist – I (Non Medical)
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Technical Support - III
-Affordable Quality Health/ACCESS Health Internati...
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Program Lead- Governance and Gender Justice
-Society for Women's Action and Training Initiativ...
-Location:
-Gujarat
-Apply by:
-25 Mar 2026
-Senior Field Officer Certification Management
-Fairtrade India Project - CSM
-Location:
-Andhra Pradesh
-Apply by:
-15 Mar 2026
-Design and Readiness Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
-Program Manager – AI Skilling Initiative
-SwaTaleem Foundation
-Location:
-Haryana
-Apply by:
-05 Apr 2026
-Communications Lead
-SwaTaleem Foundation
-Location:
-Delhi
-Apply by:
-05 Apr 2026
 Jobseekers
 Register
 Login
@@ -6783,22 +6082,103 @@
 Recruitment Exchange</t>
         </is>
       </c>
+      <c r="F28" s="1" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G28" s="1" t="inlineStr">
+        <is>
+          <t>05-04-2026</t>
+        </is>
+      </c>
+      <c r="H28" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="I28" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287913</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="inlineStr"/>
+      <c r="C29" s="1" t="inlineStr">
+        <is>
+          <t>RFP for Endline Evaluation Study - HSBC GCC Women Entrepreneurship Program - Click here</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr"/>
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="1" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G29" s="1" t="inlineStr"/>
+      <c r="H29" s="1" t="inlineStr"/>
+      <c r="I29" s="1" t="inlineStr">
+        <is>
+          <t>https://www.nasscomfoundation.org/pdf/endline-evaluation-study-hsbc-gcc-women-entrepreneurship-program.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr"/>
+      <c r="C30" s="1" t="inlineStr">
+        <is>
+          <t>Travel &amp; Transportation Services for Trainer Mobility - IBM SkillBuild Bootcamps - Click here</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G30" s="1" t="inlineStr"/>
+      <c r="H30" s="1" t="inlineStr"/>
+      <c r="I30" s="1" t="inlineStr">
+        <is>
+          <t>https://www.nasscomfoundation.org/pdf/travel-and-transportation-services-for-trainer-mobility-ibm-skillbuild-bootcamps.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="inlineStr"/>
+      <c r="C31" s="1" t="inlineStr">
+        <is>
+          <t>Baseline and End-line Evaluation of the HSBC Neurodivergent Digital Annotator Skilling Program - Click here | Click here</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr"/>
+      <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G31" s="1" t="inlineStr">
-        <is>
-          <t>05-04-2026</t>
-        </is>
-      </c>
-      <c r="H31" s="1" t="n">
-        <v>29</v>
-      </c>
+      <c r="G31" s="1" t="inlineStr"/>
+      <c r="H31" s="1" t="inlineStr"/>
       <c r="I31" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287913</t>
+          <t>https://www.nasscomfoundation.org/pdf/baseline-and-end-line-evaluation-of-hsbc-neurodivergent-digital-annotator-skilling-program.pdf</t>
         </is>
       </c>
     </row>
@@ -6811,21 +6191,21 @@
       <c r="B32" s="1" t="inlineStr"/>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>RFP for Endline Evaluation Study - HSBC GCC Women Entrepreneurship Program - Click here</t>
+          <t>RFP for Catering Vendor - IBM Skillbuild Bootcamps - Click here</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G32" s="1" t="inlineStr"/>
       <c r="H32" s="1" t="inlineStr"/>
       <c r="I32" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/endline-evaluation-study-hsbc-gcc-women-entrepreneurship-program.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/rfp-for-catering-vendor-ibm-skillbuild-bootcamps.pdf</t>
         </is>
       </c>
     </row>
@@ -6838,21 +6218,21 @@
       <c r="B33" s="1" t="inlineStr"/>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>Travel &amp; Transportation Services for Trainer Mobility - IBM SkillBuild Bootcamps - Click here</t>
+          <t>Organization-wide Management Information System (MIS) for Nasscom Foundation - Click here</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G33" s="1" t="inlineStr"/>
       <c r="H33" s="1" t="inlineStr"/>
       <c r="I33" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/travel-and-transportation-services-for-trainer-mobility-ibm-skillbuild-bootcamps.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/organization-wide-management-information-system-for-nasscom-foundation.pdf</t>
         </is>
       </c>
     </row>
@@ -6865,7 +6245,7 @@
       <c r="B34" s="1" t="inlineStr"/>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>Baseline and End-line Evaluation of the HSBC Neurodivergent Digital Annotator Skilling Program - Click here | Click here</t>
+          <t>Request for Proposal (RFP) for Social Media Management Services - Click here</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr"/>
@@ -6879,7 +6259,7 @@
       <c r="H34" s="1" t="inlineStr"/>
       <c r="I34" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/baseline-and-end-line-evaluation-of-hsbc-neurodivergent-digital-annotator-skilling-program.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/request-for-proposal-for-social-media-management-services.pdf</t>
         </is>
       </c>
     </row>
@@ -6892,21 +6272,21 @@
       <c r="B35" s="1" t="inlineStr"/>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>RFP for Catering Vendor - IBM Skillbuild Bootcamps - Click here</t>
+          <t>RFP - TechForSociety - Evaluation Study - Click here</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G35" s="1" t="inlineStr"/>
       <c r="H35" s="1" t="inlineStr"/>
       <c r="I35" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/rfp-for-catering-vendor-ibm-skillbuild-bootcamps.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/techforsociety-evaluation-study.pdf</t>
         </is>
       </c>
     </row>
@@ -6919,7 +6299,7 @@
       <c r="B36" s="1" t="inlineStr"/>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>Organization-wide Management Information System (MIS) for Nasscom Foundation - Click here</t>
+          <t>Base-line and End-line evaluation for Digital Literacy Project in 4 States - Click here</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr"/>
@@ -6933,7 +6313,7 @@
       <c r="H36" s="1" t="inlineStr"/>
       <c r="I36" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/organization-wide-management-information-system-for-nasscom-foundation.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/base-line-and-end-line-evaluation-for-digital-literacy-project-in-4-states.pdf</t>
         </is>
       </c>
     </row>
@@ -6946,21 +6326,21 @@
       <c r="B37" s="1" t="inlineStr"/>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>Request for Proposal (RFP) for Social Media Management Services - Click here</t>
+          <t>IP Selection - Scholarship Support to students from Economically Weaker Section pursuing higher education in STEM courses - Click here</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G37" s="1" t="inlineStr"/>
       <c r="H37" s="1" t="inlineStr"/>
       <c r="I37" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/request-for-proposal-for-social-media-management-services.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/scholarship-support-for-economically-weaker-section-students-in-stem-higher-education.pdf</t>
         </is>
       </c>
     </row>
@@ -6973,21 +6353,21 @@
       <c r="B38" s="1" t="inlineStr"/>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>RFP - TechForSociety - Evaluation Study - Click here</t>
+          <t>Digital Upskilling of Farmer Producer Organizations (FPOs) through Technology - Click here</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr"/>
       <c r="H38" s="1" t="inlineStr"/>
       <c r="I38" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/techforsociety-evaluation-study.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/baseline-endline-study-digital-upskilling-fpos-technology.pdf</t>
         </is>
       </c>
     </row>
@@ -7000,21 +6380,21 @@
       <c r="B39" s="1" t="inlineStr"/>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>Base-line and End-line evaluation for Digital Literacy Project in 4 States - Click here</t>
+          <t>Project - Accelerating 100 Women Micro Entrepreneurs of Northeastern States - Click here</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G39" s="1" t="inlineStr"/>
       <c r="H39" s="1" t="inlineStr"/>
       <c r="I39" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/base-line-and-end-line-evaluation-for-digital-literacy-project-in-4-states.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/project-accelerating-100-women-micro-entrepreneurs-of-northeastern-states.pdf</t>
         </is>
       </c>
     </row>
@@ -7027,21 +6407,21 @@
       <c r="B40" s="1" t="inlineStr"/>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>IP Selection - Scholarship Support to students from Economically Weaker Section pursuing higher education in STEM courses - Click here</t>
+          <t>Agency for Developing Training Modules and Conducting Training of Trainers (ToT) for MSMEs on IPR and Financial Management - Click here</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G40" s="1" t="inlineStr"/>
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/scholarship-support-for-economically-weaker-section-students-in-stem-higher-education.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/agency-for-developing-training-modules-and-conducting-ToT-for-MSMEs-on-IPR-and-financial-management.pdf</t>
         </is>
       </c>
     </row>
@@ -7054,7 +6434,7 @@
       <c r="B41" s="1" t="inlineStr"/>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>Digital Upskilling of Farmer Producer Organizations (FPOs) through Technology - Click here</t>
+          <t>RFP for WISE - Women in Innovation, Skills &amp; Entrepreneurship - Click here</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr"/>
@@ -7068,7 +6448,7 @@
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/baseline-endline-study-digital-upskilling-fpos-technology.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/women-in-Innovation-skills-and-entrepreneurship.pdf</t>
         </is>
       </c>
     </row>
@@ -7081,7 +6461,7 @@
       <c r="B42" s="1" t="inlineStr"/>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>Project - Accelerating 100 Women Micro Entrepreneurs of Northeastern States - Click here</t>
+          <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - English  - Click here</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr"/>
@@ -7095,7 +6475,7 @@
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/project-accelerating-100-women-micro-entrepreneurs-of-northeastern-states.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-English.pdf</t>
         </is>
       </c>
     </row>
@@ -7108,21 +6488,21 @@
       <c r="B43" s="1" t="inlineStr"/>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>Agency for Developing Training Modules and Conducting Training of Trainers (ToT) for MSMEs on IPR and Financial Management - Click here</t>
+          <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - Kannada - Click here</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
       <c r="E43" s="2" t="inlineStr"/>
       <c r="F43" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G43" s="1" t="inlineStr"/>
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/agency-for-developing-training-modules-and-conducting-ToT-for-MSMEs-on-IPR-and-financial-management.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-Kannada.pdf</t>
         </is>
       </c>
     </row>
@@ -7135,7 +6515,7 @@
       <c r="B44" s="1" t="inlineStr"/>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>RFP for WISE - Women in Innovation, Skills &amp; Entrepreneurship - Click here</t>
+          <t>RFP - Trainer for Nano Women Entrepreneurs in Karnataka - Click here</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
@@ -7149,7 +6529,7 @@
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/women-in-Innovation-skills-and-entrepreneurship.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/trainer-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
         </is>
       </c>
     </row>
@@ -7162,7 +6542,7 @@
       <c r="B45" s="1" t="inlineStr"/>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - English  - Click here</t>
+          <t>RFP - Training Agency with Content and Trainers for Nano Women Entrepreneurs in Karnataka - Click here</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
@@ -7176,7 +6556,7 @@
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-English.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/training-agency-with-content-and-trainers-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
         </is>
       </c>
     </row>
@@ -7189,21 +6569,21 @@
       <c r="B46" s="1" t="inlineStr"/>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - Kannada - Click here</t>
+          <t>Access to E-Governance and Livelihood in PVTG Communities in Aspirational Blocks - Click here</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G46" s="1" t="inlineStr"/>
       <c r="H46" s="1" t="inlineStr"/>
       <c r="I46" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-Kannada.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/access-to-e-governance-and-livelihood-in-pvtg-communities-in-aspirational-blocks.pdf</t>
         </is>
       </c>
     </row>
@@ -7216,7 +6596,7 @@
       <c r="B47" s="1" t="inlineStr"/>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>RFP - Trainer for Nano Women Entrepreneurs in Karnataka - Click here</t>
+          <t>thingQbator Portal Enhancement and Maintenance Proposal - Click here</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
@@ -7230,74 +6610,94 @@
       <c r="H47" s="1" t="inlineStr"/>
       <c r="I47" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/trainer-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/thingQbator-portal-enhancement-and-maintenance-proposal.pdf</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B48" s="1" t="inlineStr"/>
+          <t>HCL Foundation</t>
+        </is>
+      </c>
+      <c r="B48" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>RFP - Training Agency with Content and Trainers for Nano Women Entrepreneurs in Karnataka - Click here</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards Biodiversity monitoring for Pan-India Afforestation sites</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
       <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G48" s="1" t="inlineStr"/>
+          <t>Climate</t>
+        </is>
+      </c>
+      <c r="G48" s="1" t="inlineStr">
+        <is>
+          <t>10th Feb, 2026</t>
+        </is>
+      </c>
       <c r="H48" s="1" t="inlineStr"/>
       <c r="I48" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/training-agency-with-content-and-trainers-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Biodiversity%20monitoring%20for%20Pan-India%20Afforestation%20sites%202-DSB.pdf</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B49" s="1" t="inlineStr"/>
+          <t>HCL Foundation</t>
+        </is>
+      </c>
+      <c r="B49" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>Access to E-Governance and Livelihood in PVTG Communities in Aspirational Blocks - Click here</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards soil profiling and assessment from the restored and rejuvenated Harit sites.</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
       <c r="E49" s="2" t="inlineStr"/>
       <c r="F49" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G49" s="1" t="inlineStr"/>
+          <t>Climate</t>
+        </is>
+      </c>
+      <c r="G49" s="1" t="inlineStr">
+        <is>
+          <t>10th Feb, 2026</t>
+        </is>
+      </c>
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/access-to-e-governance-and-livelihood-in-pvtg-communities-in-aspirational-blocks.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Soil%20assessment-v1%20RKS-DSB_0.pdf</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B50" s="1" t="inlineStr"/>
+          <t>HCL Foundation</t>
+        </is>
+      </c>
+      <c r="B50" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>thingQbator Portal Enhancement and Maintenance Proposal - Click here</t>
+          <t>HCLFoundation invites proposals from NGOs/CSR implementing agencies for ‘Operating a Social Enterprise Cafe” under the flagship urban development programme - Uday</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
@@ -7307,11 +6707,15 @@
           <t>Learning</t>
         </is>
       </c>
-      <c r="G50" s="1" t="inlineStr"/>
+      <c r="G50" s="1" t="inlineStr">
+        <is>
+          <t>15th Dec, 2025</t>
+        </is>
+      </c>
       <c r="H50" s="1" t="inlineStr"/>
       <c r="I50" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/thingQbator-portal-enhancement-and-maintenance-proposal.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-11/RfP_Social%20Enterprise%20Cafe_UDAY.docx</t>
         </is>
       </c>
     </row>
@@ -7328,25 +6732,25 @@
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards Biodiversity monitoring for Pan-India Afforestation sites</t>
+          <t>Programme Officer/Senior Programme Officer – Environment Education</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
       <c r="E51" s="2" t="inlineStr"/>
       <c r="F51" s="1" t="inlineStr">
         <is>
-          <t>Climate</t>
+          <t>Learning, Climate</t>
         </is>
       </c>
       <c r="G51" s="1" t="inlineStr">
         <is>
-          <t>10th Feb, 2026</t>
+          <t>10th Nov, 2025</t>
         </is>
       </c>
       <c r="H51" s="1" t="inlineStr"/>
       <c r="I51" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Biodiversity%20monitoring%20for%20Pan-India%20Afforestation%20sites%202-DSB.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-10/Harit_POSPO_EEA_Multilocation_Oct%202025.pdf</t>
         </is>
       </c>
     </row>
@@ -7363,25 +6767,25 @@
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards soil profiling and assessment from the restored and rejuvenated Harit sites.</t>
+          <t>HCLFoundation invites applications for the PO/SPO position under its flagship programme Harit by HCLFoundation</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
       <c r="E52" s="2" t="inlineStr"/>
       <c r="F52" s="1" t="inlineStr">
         <is>
-          <t>Climate</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G52" s="1" t="inlineStr">
         <is>
-          <t>10th Feb, 2026</t>
+          <t>31st Oct, 2025</t>
         </is>
       </c>
       <c r="H52" s="1" t="inlineStr"/>
       <c r="I52" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Soil%20assessment-v1%20RKS-DSB_0.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-10/JD_Water%20Conservation_SPO%20V4.pdf</t>
         </is>
       </c>
     </row>
@@ -7398,25 +6802,25 @@
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites proposals from NGOs/CSR implementing agencies for ‘Operating a Social Enterprise Cafe” under the flagship urban development programme - Uday</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit by HCLFoundation, invites RFP from NGOs / CSR organizations working in Water Conservation for the development of Water Structures etc.</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
       <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Learning, Climate</t>
         </is>
       </c>
       <c r="G53" s="1" t="inlineStr">
         <is>
-          <t>15th Dec, 2025</t>
+          <t>21st May, 2025</t>
         </is>
       </c>
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-11/RfP_Social%20Enterprise%20Cafe_UDAY.docx</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/Final_RFP%20for%20water%20structure%20rejuvenation%20.docx</t>
         </is>
       </c>
     </row>
@@ -7433,25 +6837,25 @@
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>Programme Officer/Senior Programme Officer – Environment Education</t>
+          <t>HCLFoundation invites technical application abstracts for the developing technology drive source code model mobile applications and web portals for addressing human-animal interactions under the Animal Welfare thematic of  Harit by HCLFoundation</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
       <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="1" t="inlineStr">
         <is>
-          <t>Learning, Climate</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G54" s="1" t="inlineStr">
         <is>
-          <t>10th Nov, 2025</t>
+          <t>15th May, 2025</t>
         </is>
       </c>
       <c r="H54" s="1" t="inlineStr"/>
       <c r="I54" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-10/Harit_POSPO_EEA_Multilocation_Oct%202025.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_AW%20Tech%20Based%20Source%20Code%20Model_V1%20%281%29.docx</t>
         </is>
       </c>
     </row>
@@ -7468,25 +6872,25 @@
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites applications for the PO/SPO position under its flagship programme Harit by HCLFoundation</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit invites RFP from NGOs/CSR organizations working in the field of environment for project on the restoration of various degraded and natural habitats</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr"/>
       <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Climate</t>
         </is>
       </c>
       <c r="G55" s="1" t="inlineStr">
         <is>
-          <t>31st Oct, 2025</t>
+          <t>15th May, 2025</t>
         </is>
       </c>
       <c r="H55" s="1" t="inlineStr"/>
       <c r="I55" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-10/JD_Water%20Conservation_SPO%20V4.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/Harit_A%20HR_RFP%20.docx</t>
         </is>
       </c>
     </row>
@@ -7503,25 +6907,25 @@
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit by HCLFoundation, invites RFP from NGOs / CSR organizations working in Water Conservation for the development of Water Structures etc.</t>
+          <t>HCLFoundation invites EOI for conducting holistic and comprehensive Impact Assessments of environmental projects supported under Harit by HCLFoundation</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="1" t="inlineStr">
         <is>
-          <t>Learning, Climate</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G56" s="1" t="inlineStr">
         <is>
-          <t>21st May, 2025</t>
+          <t>15th May, 2025</t>
         </is>
       </c>
       <c r="H56" s="1" t="inlineStr"/>
       <c r="I56" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/Final_RFP%20for%20water%20structure%20rejuvenation%20.docx</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_Harit%20Impact%20Assessments.docx</t>
         </is>
       </c>
     </row>
@@ -7538,14 +6942,14 @@
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites technical application abstracts for the developing technology drive source code model mobile applications and web portals for addressing human-animal interactions under the Animal Welfare thematic of  Harit by HCLFoundation</t>
+          <t>HCLFoundation invites technical application abstracts for the conducting technical and highly engaging environment awareness and sustainability workshops under Harit by HCLFoundation</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr"/>
       <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Climate</t>
         </is>
       </c>
       <c r="G57" s="1" t="inlineStr">
@@ -7556,112 +6960,88 @@
       <c r="H57" s="1" t="inlineStr"/>
       <c r="I57" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_AW%20Tech%20Based%20Source%20Code%20Model_V1%20%281%29.docx</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_EEA_Env%20%20Sus%20awareness%20workshops_FY%2025-26%20%281%29.docx</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>HCL Foundation</t>
+          <t>NIUA</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Tender</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit invites RFP from NGOs/CSR organizations working in the field of environment for project on the restoration of various degraded and natural habitats</t>
+          <t>Supply_of_Unskilled_Manpower.pdf</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr"/>
       <c r="E58" s="2" t="inlineStr"/>
-      <c r="F58" s="1" t="inlineStr">
-        <is>
-          <t>Climate</t>
-        </is>
-      </c>
-      <c r="G58" s="1" t="inlineStr">
-        <is>
-          <t>15th May, 2025</t>
-        </is>
-      </c>
+      <c r="F58" s="1" t="inlineStr"/>
+      <c r="G58" s="1" t="inlineStr"/>
       <c r="H58" s="1" t="inlineStr"/>
       <c r="I58" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/Harit_A%20HR_RFP%20.docx</t>
+          <t>https://niua.in/sites/default/files/tenders/Supply_of_Unskilled_Manpower.pdf</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>HCL Foundation</t>
+          <t>NIUA</t>
         </is>
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Tender</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites EOI for conducting holistic and comprehensive Impact Assessments of environmental projects supported under Harit by HCLFoundation</t>
+          <t>Quotation_for_Rate_Contrac_Vehicle_Hiring_for_NCR_or_Outstation..pdf</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr"/>
       <c r="E59" s="2" t="inlineStr"/>
-      <c r="F59" s="1" t="inlineStr">
-        <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G59" s="1" t="inlineStr">
-        <is>
-          <t>15th May, 2025</t>
-        </is>
-      </c>
+      <c r="F59" s="1" t="inlineStr"/>
+      <c r="G59" s="1" t="inlineStr"/>
       <c r="H59" s="1" t="inlineStr"/>
       <c r="I59" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_Harit%20Impact%20Assessments.docx</t>
+          <t>https://niua.in/sites/default/files/tenders/Quotation_for_Rate_Contrac_Vehicle_Hiring_for_NCR_or_Outstation..pdf</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>HCL Foundation</t>
+          <t>NIUA</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Tender</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites technical application abstracts for the conducting technical and highly engaging environment awareness and sustainability workshops under Harit by HCLFoundation</t>
+          <t>Final_RfP_UrbanShift_Preparation_of_Integrated_Green_Mobility_Plan_for_Pune.pdf</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr"/>
       <c r="E60" s="2" t="inlineStr"/>
-      <c r="F60" s="1" t="inlineStr">
-        <is>
-          <t>Climate</t>
-        </is>
-      </c>
-      <c r="G60" s="1" t="inlineStr">
-        <is>
-          <t>15th May, 2025</t>
-        </is>
-      </c>
+      <c r="F60" s="1" t="inlineStr"/>
+      <c r="G60" s="1" t="inlineStr"/>
       <c r="H60" s="1" t="inlineStr"/>
       <c r="I60" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_EEA_Env%20%20Sus%20awareness%20workshops_FY%2025-26%20%281%29.docx</t>
+          <t>https://niua.in/sites/default/files/tenders/Final_RfP_UrbanShift_Preparation_of_Integrated_Green_Mobility_Plan_for_Pune.pdf</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7058,7 @@
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>Supply_of_Unskilled_Manpower.pdf</t>
+          <t>RfP_IGMP_Response to Pre-Bid Queries_200226.pdf</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr"/>
@@ -7688,7 +7068,7 @@
       <c r="H61" s="1" t="inlineStr"/>
       <c r="I61" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Supply_of_Unskilled_Manpower.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/RfP_IGMP_Response%20to%20Pre-Bid%20Queries_200226.pdf</t>
         </is>
       </c>
     </row>
@@ -7705,7 +7085,7 @@
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>Quotation_for_Rate_Contrac_Vehicle_Hiring_for_NCR_or_Outstation..pdf</t>
+          <t>Corrigendum_1_RfP_IGMP.pdf</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr"/>
@@ -7715,7 +7095,7 @@
       <c r="H62" s="1" t="inlineStr"/>
       <c r="I62" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Quotation_for_Rate_Contrac_Vehicle_Hiring_for_NCR_or_Outstation..pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/Corrigendum_1_RfP_IGMP.pdf</t>
         </is>
       </c>
     </row>
@@ -7732,7 +7112,7 @@
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>Final_RfP_UrbanShift_Preparation_of_Integrated_Green_Mobility_Plan_for_Pune.pdf</t>
+          <t>Corrigendum 2_IGMP.pdf</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr"/>
@@ -7742,7 +7122,7 @@
       <c r="H63" s="1" t="inlineStr"/>
       <c r="I63" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Final_RfP_UrbanShift_Preparation_of_Integrated_Green_Mobility_Plan_for_Pune.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/Corrigendum%202_IGMP.pdf</t>
         </is>
       </c>
     </row>
@@ -7759,7 +7139,7 @@
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>RfP_IGMP_Response to Pre-Bid Queries_200226.pdf</t>
+          <t>RFP_Engagement of GIS Expert_SCBP_2026.pdf</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr"/>
@@ -7769,7 +7149,7 @@
       <c r="H64" s="1" t="inlineStr"/>
       <c r="I64" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/RfP_IGMP_Response%20to%20Pre-Bid%20Queries_200226.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/RFP_Engagement%20of%20GIS%20Expert_SCBP_2026.pdf</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7166,7 @@
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>Corrigendum_1_RfP_IGMP.pdf</t>
+          <t>Response_to_Queries_Engagement_of_GIS_Expert_Agency.pdf</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr"/>
@@ -7796,7 +7176,7 @@
       <c r="H65" s="1" t="inlineStr"/>
       <c r="I65" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Corrigendum_1_RfP_IGMP.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/Response_to_Queries_Engagement_of_GIS_Expert_Agency.pdf</t>
         </is>
       </c>
     </row>
@@ -7813,7 +7193,7 @@
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>Corrigendum 2_IGMP.pdf</t>
+          <t>RfP_SRTW.pdf</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
@@ -7823,7 +7203,7 @@
       <c r="H66" s="1" t="inlineStr"/>
       <c r="I66" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Corrigendum%202_IGMP.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/RfP_SRTW.pdf</t>
         </is>
       </c>
     </row>
@@ -7840,7 +7220,7 @@
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>RFP_Engagement of GIS Expert_SCBP_2026.pdf</t>
+          <t>Response to Pre-Bid Queries_SRTW_for Uploading.pdf</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr"/>
@@ -7850,7 +7230,7 @@
       <c r="H67" s="1" t="inlineStr"/>
       <c r="I67" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/RFP_Engagement%20of%20GIS%20Expert_SCBP_2026.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/Response%20to%20Pre-Bid%20Queries_SRTW_for%20Uploading.pdf</t>
         </is>
       </c>
     </row>
@@ -7867,7 +7247,7 @@
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>Response_to_Queries_Engagement_of_GIS_Expert_Agency.pdf</t>
+          <t>EOI_TECHNICAL_ASSISTANCE_UNDER_CITIIS_2.0_PROGRAM_DOMESTIC_POOL_OF_EXPERTS.pdf</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr"/>
@@ -7877,7 +7257,7 @@
       <c r="H68" s="1" t="inlineStr"/>
       <c r="I68" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Response_to_Queries_Engagement_of_GIS_Expert_Agency.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/EOI_TECHNICAL_ASSISTANCE_UNDER_CITIIS_2.0_PROGRAM_DOMESTIC_POOL_OF_EXPERTS.pdf</t>
         </is>
       </c>
     </row>
@@ -7894,7 +7274,7 @@
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>RfP_SRTW.pdf</t>
+          <t>Reply to Pre- Bid Queries - EOI for DE's under CITIIS 2.0.pdf</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr"/>
@@ -7904,7 +7284,7 @@
       <c r="H69" s="1" t="inlineStr"/>
       <c r="I69" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/RfP_SRTW.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/Reply%20to%20Pre-%20Bid%20Queries%20-%20EOI%20for%20DE%27s%20under%20CITIIS%202.0.pdf</t>
         </is>
       </c>
     </row>
@@ -7921,7 +7301,7 @@
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>Response to Pre-Bid Queries_SRTW_for Uploading.pdf</t>
+          <t>GeM-Bidding-8666471.pdf</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr"/>
@@ -7931,7 +7311,7 @@
       <c r="H70" s="1" t="inlineStr"/>
       <c r="I70" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Response%20to%20Pre-Bid%20Queries_SRTW_for%20Uploading.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-8666471.pdf</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7328,7 @@
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>EOI_TECHNICAL_ASSISTANCE_UNDER_CITIIS_2.0_PROGRAM_DOMESTIC_POOL_OF_EXPERTS.pdf</t>
+          <t>corgaudt1.pdf</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr"/>
@@ -7958,7 +7338,7 @@
       <c r="H71" s="1" t="inlineStr"/>
       <c r="I71" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/EOI_TECHNICAL_ASSISTANCE_UNDER_CITIIS_2.0_PROGRAM_DOMESTIC_POOL_OF_EXPERTS.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/corgaudt1.pdf</t>
         </is>
       </c>
     </row>
@@ -7975,7 +7355,7 @@
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>Reply to Pre- Bid Queries - EOI for DE's under CITIIS 2.0.pdf</t>
+          <t>Corrigendum6959493.pdf</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr"/>
@@ -7985,7 +7365,7 @@
       <c r="H72" s="1" t="inlineStr"/>
       <c r="I72" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Reply%20to%20Pre-%20Bid%20Queries%20-%20EOI%20for%20DE%27s%20under%20CITIIS%202.0.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/Corrigendum6959493.pdf</t>
         </is>
       </c>
     </row>
@@ -8002,7 +7382,7 @@
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>GeM-Bidding-8666471.pdf</t>
+          <t>ADDENDUM6959493.pdf</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr"/>
@@ -8012,7 +7392,7 @@
       <c r="H73" s="1" t="inlineStr"/>
       <c r="I73" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-8666471.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/ADDENDUM6959493.pdf</t>
         </is>
       </c>
     </row>
@@ -8029,7 +7409,7 @@
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>corgaudt1.pdf</t>
+          <t>RfP CJ&amp;IP Package 03_UrbanShift.pdf</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr"/>
@@ -8039,7 +7419,7 @@
       <c r="H74" s="1" t="inlineStr"/>
       <c r="I74" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/corgaudt1.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/RfP%20CJ%26IP%20Package%2003_UrbanShift.pdf</t>
         </is>
       </c>
     </row>
@@ -8056,7 +7436,7 @@
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>Corrigendum6959493.pdf</t>
+          <t>Prebid reply Cj&amp;IP package 3_18.12.2025.pdf</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr"/>
@@ -8066,7 +7446,7 @@
       <c r="H75" s="1" t="inlineStr"/>
       <c r="I75" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Corrigendum6959493.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/Prebid%20reply%20Cj%26IP%20package%203_18.12.2025.pdf</t>
         </is>
       </c>
     </row>
@@ -8083,7 +7463,7 @@
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>ADDENDUM6959493.pdf</t>
+          <t>GeM-Bidding-8478801.pdf</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr"/>
@@ -8093,7 +7473,7 @@
       <c r="H76" s="1" t="inlineStr"/>
       <c r="I76" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/ADDENDUM6959493.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-8478801.pdf</t>
         </is>
       </c>
     </row>
@@ -8110,7 +7490,7 @@
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>RfP CJ&amp;IP Package 03_UrbanShift.pdf</t>
+          <t>GeM-Bidding-8476974.pdf</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr"/>
@@ -8120,87 +7500,6 @@
       <c r="H77" s="1" t="inlineStr"/>
       <c r="I77" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/RfP%20CJ%26IP%20Package%2003_UrbanShift.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>Prebid reply Cj&amp;IP package 3_18.12.2025.pdf</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr"/>
-      <c r="E78" s="2" t="inlineStr"/>
-      <c r="F78" s="1" t="inlineStr"/>
-      <c r="G78" s="1" t="inlineStr"/>
-      <c r="H78" s="1" t="inlineStr"/>
-      <c r="I78" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/Prebid%20reply%20Cj%26IP%20package%203_18.12.2025.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>GeM-Bidding-8478801.pdf</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr"/>
-      <c r="E79" s="2" t="inlineStr"/>
-      <c r="F79" s="1" t="inlineStr"/>
-      <c r="G79" s="1" t="inlineStr"/>
-      <c r="H79" s="1" t="inlineStr"/>
-      <c r="I79" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-8478801.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>GeM-Bidding-8476974.pdf</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr"/>
-      <c r="E80" s="2" t="inlineStr"/>
-      <c r="F80" s="1" t="inlineStr"/>
-      <c r="G80" s="1" t="inlineStr"/>
-      <c r="H80" s="1" t="inlineStr"/>
-      <c r="I80" s="1" t="inlineStr">
-        <is>
           <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-8476974.pdf</t>
         </is>
       </c>

--- a/all_grants.xlsx
+++ b/all_grants.xlsx
@@ -489,13 +489,13 @@
       <c r="B2" s="1" t="inlineStr"/>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>RFQ: Construction of New gated check dams, De-siltation, and retrofitting ...</t>
+          <t>RFP - Hiring of an International Audit Firm</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>WaterAid India | Telangana
-International Development - RFQ: Construction of New gated check dams, De-siltation, and retrofitting of check dam in 6 villages, WaterAid India, Telangana - DevNetJobsIndia.org
+          <t>Coalition for Disaster Resilient Infrastructure (CDRI) | India
+International Development - RFP - Hiring of an International Audit Firm, Coalition for Disaster Resilient Infrastructure (CDRI), India - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
@@ -503,27 +503,31 @@
 Home
 Value Membership
 Broadcast Resume
-RFPs/Tenders
-Search Jobs
-E ... Read More</t>
+RFPs/Tender ... Read More</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>• Job Email ID:
-WAIProcurementAP(at)wateraid.org
+tender.projects(at)cdri.world
 Download Attachment:
-Tender Notice-15 check dams-Jalsankalp-19.02.26_compressed.pdf
+RFP-Hiring International Audit Firm-20 Feb'26.pdf
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
 Apply by:
-08 Mar 2026
+09 Mar 2026
 Access all the jobs and get ahead!
 Subscribe to Value Membership Now!
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
 Associate – Finance and Operations
 Financial Management Service Foundation (FMSF)
 Location:
@@ -536,12 +540,6 @@
 Maharashtra
 Apply by:
 03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -586,54 +584,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Manager - Individual Engagement (Acquisition)
-(Value Members only)
+RFQ-Corporate Global Group Health Insurance Cover...
+Coalition for Disaster Resilient Infrastructure (...
+Location:
+India
+Apply by:
+23 Mar 2026
+HR Associate
+Inclusion Economics India Centre (IEIC) at IFMR
+Location:
+Delhi
+Apply by:
+08 Apr 2026
+Short Term Consultant - Workshop Facilitator for ...
+Fairtrade NAPP
+Location:
+Assam
+Apply by:
+31 Mar 2026
+State Manager
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Uttar Pradesh
+Apply by:
+22 Mar 2026
+State Project Officer
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+India
+Apply by:
+22 Mar 2026
+State Program Manager-HIV-CSC-North East
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Assam
+Apply by:
+22 Mar 2026
+Neighbourhood Facilitator – Health &amp; NCDs
+Transform Rural India (TRI)
 Location:
 Maharashtra
 Apply by:
-10 Mar 2026
-Part Time Accountant
-Sahabhagi Vikash Abhiyan
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Coordinator
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-Consultant Architects
-(Value Members only)
-Location:
-Chhattisgarh
-Apply by:
-18 Mar 2026
-Community Mobilizer
-Common Man Trust
-Location:
-Delhi, Uttar Pradesh, Haryana
-Apply by:
-25 Mar 2026
-Part-Time Psychology Intern (Telugu Speaking)
-Nayi Disha
-Location:
-Telangana
-Apply by:
-20 Mar 2026
-Field Mobilizer
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-RFP for Data Collection for Foundational Reading ...
-Lords Education and Health Society (LEHS)
-Location:
-Odisha
-Apply by:
-15 Mar 2026
+30 Mar 2026
+Health Planner – Community Mobilization
+Transform Rural India (TRI)
+Location:
+Maharashtra
+Apply by:
+30 Mar 2026
 Jobseekers
 Register
 Login
@@ -663,12 +661,12 @@
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Climate</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>08-03-2026</t>
+          <t>09-03-2026</t>
         </is>
       </c>
       <c r="H2" s="1" t="n">
@@ -676,7 +674,7 @@
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287784</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287382</t>
         </is>
       </c>
     </row>
@@ -689,98 +687,48 @@
       <c r="B3" s="1" t="inlineStr"/>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>RFP - Final Evaluation of the Bhoomi Ka Programme</t>
+          <t>RFP For Selection of an Implementation Support Agency (Isa) For Capacity B...</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Deutsche Welthungerhilfe | India
-International Development - RFP - Final Evaluation of the Bhoomi Ka Programme, Deutsche Welthungerhilfe, India - DevNetJobsIndia.org
+          <t>EAII Advisors Pvt Ltd | Andhra Pradesh
+International Development - RFP For Selection of an Implementation Support Agency (Isa) For Capacity Building Of Community Leaders To Conduct Community Engagement Activities, EAII Advisors Pvt Ltd, Andhra Pradesh - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Login
-|
-Register
-Jobs ... Read More</t>
+Regis ... Read More</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>• INTRODUCTION AND CONTEXT
-Country:
-India
-Programme Title:
-Bhoomi Ka   –Co-creating Clean, Green and Fair Food Systems
-Programme No. :
-IND 1398
-Programme Holder /   Contracting Authority:
-Welthungerhilfe (WHH)
-Donor(s):
-BMZ
-Programme Period:
-02/11/2022-   30/06/2026
-Geographical   Coverage:
-7 states across India   (across programme supported FPOs, ecopreneurs, and farmer collectives)
-Welthungerhilfe (WHH) is a German, non-profit organisation working in the field of international development cooperation and emergency aid. The organisation is dedicated to achieving food security and addressing the root causes of poverty, and for over 55 years has supported voluntary and civil society partner organisations in rural India. (
-www.welthungerhilfeindia.org
-)
-1.1 About the Project
-Welthungerhilfe and its partners initiated Bhoomi Ka as a multi-stakeholder platform to strengthen agroecological and organic food value chains in India. The programme operates across selected districts in Jharkhand, Odisha, West Bengal, Madhya Pradesh, Rajasthan, Punjab and Uttarakhand, with market linkages developed in nearby urban centres such as Ranchi, Jamshedpur, Bhubaneswar, Kolkata, Indore, Bhopal, Udaipur, Amritsar and Ranikhet.
-The programme works with 100 Farmer Producer Organisations (FPOs) representing around 10,000 smallholder households, and 100 ecopreneurs/SMEs engaged in processing, retail and marketing of organic products. Of these, 20 FPOs and 20 ecopreneurs receive intensive support to develop ‘lighthouse’ agroecological value chains. The Bhoomi Ka platform further connects producers, enterprises, consumers, service providers and policy actors to strengthen an integrated food systems approach.
-1.2 Direct and Indirect Beneficiaries
-DIRECT BENEFICIARIES
-1. 100 Farmer Producer Organisations (FPOs)
-Representing approximately 10,000 smallholder households (~45,000 people)
-Majority from disadvantaged tribal populations
-Cultivating less than 2 hectares on average
-Linked to 2–3 agroecological value chains
-Preferably marketing PGS-certified products
-2. 100 Ecopreneurs / SMEs / Food Start-ups
-Organic processors, retailers, restaurants, organic markets
-Employing 1–3 people on average
-Value-driven enterprises promoting Clean, Green and Fair principles
-3. 20 FPOs and 20 Ecopreneurs (Intensive Support / Lighthouse Value Chains)
-Receiving mentoring, coaching, networking and business development support
-4. 5,000 Bhoomi Ka Platform Users
-Including producers, enterprises, consumer groups, service providers, experts and CSOs
-Total direct reach: Over 6,200 primary actors, including institutional stakeholders.
-INDIRECT BENEFICIARIES
-Approximately 10,000 smallholder households benefitting from strengthened value chains
-Around 10,000 urban consumers accessing organic products
-Up to 1 million consumers reached through campaigns, food festivals, dialogues and awareness initiatives
-Government departments and policy actors benefitting from improved models and policy advocacy
-• Submission Details
-Proposals should be submitted electronically in PDF format to
-shruti.pandey@welthungerhilfe.de
-with CC to
-renita.rajora@welthungerhilfe.de
-Last date for submission
-8 March 2026
-Queries, if any, may be sent to
-shruti.pandey@welthungerhilfe.de
-WHH reserves the right to accept or reject any proposal and to cancel the RFP process at any stage without assigning any reason
-For detailed information, please check the complete version of the RFP attached below
+          <t>• Proposal Requirements
+1. Company Background and Details
+A. Company Profile
+Overview of the firm or firms submitting the bid, including a brief history, information about organizational structure, relevant company financials, location of offices, number of employees, relevant certifications, or any other information that could be pertinent.
+Supplier Response:
+Kindly fill in the column “Bidder Response”. The current inputs are guiding inputs or choices for answers. Kindly fill in accordingly.
+For detailed information, please check the complete version of the RFP attached below.
 Download Attachment:
-TOR_Final Evaluation of Bhoomi Ka  Final SP.pdf
+Standalone ISA RFP Technical Evaluation Response Template (1).docx
+Download Attachment:
+Telugu_Standalone ISA RFP Technical Evaluation Response Template.docx
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
 Apply by:
-08 Mar 2026
+09 Mar 2026
 Access all the jobs and get ahead!
 Subscribe to Value Membership Now!
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
 Associate – Finance and Operations
 Financial Management Service Foundation (FMSF)
 Location:
@@ -793,12 +741,6 @@
 Maharashtra
 Apply by:
 03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -843,54 +785,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Manager - Individual Engagement (Acquisition)
-(Value Members only)
+RFQ-Corporate Global Group Health Insurance Cover...
+Coalition for Disaster Resilient Infrastructure (...
+Location:
+India
+Apply by:
+23 Mar 2026
+HR Associate
+Inclusion Economics India Centre (IEIC) at IFMR
+Location:
+Delhi
+Apply by:
+08 Apr 2026
+Short Term Consultant - Workshop Facilitator for ...
+Fairtrade NAPP
+Location:
+Assam
+Apply by:
+31 Mar 2026
+State Manager
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Uttar Pradesh
+Apply by:
+22 Mar 2026
+State Project Officer
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+India
+Apply by:
+22 Mar 2026
+State Program Manager-HIV-CSC-North East
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Assam
+Apply by:
+22 Mar 2026
+Neighbourhood Facilitator – Health &amp; NCDs
+Transform Rural India (TRI)
 Location:
 Maharashtra
 Apply by:
-10 Mar 2026
-Part Time Accountant
-Sahabhagi Vikash Abhiyan
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Coordinator
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-Consultant Architects
-(Value Members only)
-Location:
-Chhattisgarh
-Apply by:
-18 Mar 2026
-Community Mobilizer
-Common Man Trust
-Location:
-Delhi, Uttar Pradesh, Haryana
-Apply by:
-25 Mar 2026
-Part-Time Psychology Intern (Telugu Speaking)
-Nayi Disha
-Location:
-Telangana
-Apply by:
-20 Mar 2026
-Field Mobilizer
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-RFP for Data Collection for Foundational Reading ...
-Lords Education and Health Society (LEHS)
-Location:
-Odisha
-Apply by:
-15 Mar 2026
+30 Mar 2026
+Health Planner – Community Mobilization
+Transform Rural India (TRI)
+Location:
+Maharashtra
+Apply by:
+30 Mar 2026
 Jobseekers
 Register
 Login
@@ -920,12 +862,12 @@
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Governance, Learning</t>
         </is>
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
-          <t>08-03-2026</t>
+          <t>09-03-2026</t>
         </is>
       </c>
       <c r="H3" s="1" t="n">
@@ -933,7 +875,7 @@
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287384</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=285950</t>
         </is>
       </c>
     </row>
@@ -946,79 +888,33 @@
       <c r="B4" s="1" t="inlineStr"/>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>RFP - Early-Stage Impact Assessment-CDRI SWP 23-26</t>
+          <t>RFP For The Contractors To Procure, Build, Install, Supply Chlorine Tablet...</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Coalition for Disaster Resilient Infrastructure (CDRI) | India
-International Development - RFP - Early-Stage Impact Assessment-CDRI SWP 23-26, Coalition for Disaster Resilient Infrastructure (CDRI), India - DevNetJobsIndia.org
+          <t>EAII Advisors Pvt Ltd | Andhra Pradesh
+International Development - RFP For The Contractors To Procure, Build, Install, Supply Chlorine Tablets, Operate And Maintain Tablet-Based In Line Chlorination Devices, EAII Advisors Pvt Ltd, Andhra Pradesh - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
 Register
-Home
-Value Membership
-Broadcast Resume
-RFPs ... Read More</t>
+Ho ... Read More</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>Climate, Governance</t>
-        </is>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>09-03-2026</t>
-        </is>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287093</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr"/>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Hiring of an International Audit Firm</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Coalition for Disaster Resilient Infrastructure (CDRI) | India
-International Development - RFP - Hiring of an International Audit Firm, Coalition for Disaster Resilient Infrastructure (CDRI), India - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tender ... Read More</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>• Job Email ID:
-tender.projects(at)cdri.world
+          <t>• Proposal Requirements
+1. Company Background and Details
+A. Company Profile
+Overview of the firm or firms submitting the bid, including a brief history, information about organizational structure, relevant company financials, location of offices, number of employees, relevant certifications, or any other information that could be pertinent.
+Supplier Response:
+Kindly fill in the column “Bidder Response”. The current inputs are guiding inputs or choices for answers. Kindly fill in accordingly.
+For detailed information, please check the complete version of the RFP attached below.
 Download Attachment:
-RFP-Hiring International Audit Firm-20 Feb'26.pdf
+Standalone IC RFP Technical Evaluation Response Template.docx
+Download Attachment:
+Telugu_Standalone IC RFP Technical Evaluation Response Template.docx
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
@@ -1029,6 +925,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
 Associate – Finance and Operations
 Financial Management Service Foundation (FMSF)
 Location:
@@ -1041,12 +943,6 @@
 Maharashtra
 Apply by:
 03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -1091,54 +987,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Manager - Individual Engagement (Acquisition)
-(Value Members only)
+RFQ-Corporate Global Group Health Insurance Cover...
+Coalition for Disaster Resilient Infrastructure (...
+Location:
+India
+Apply by:
+23 Mar 2026
+HR Associate
+Inclusion Economics India Centre (IEIC) at IFMR
+Location:
+Delhi
+Apply by:
+08 Apr 2026
+Short Term Consultant - Workshop Facilitator for ...
+Fairtrade NAPP
+Location:
+Assam
+Apply by:
+31 Mar 2026
+State Manager
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Uttar Pradesh
+Apply by:
+22 Mar 2026
+State Project Officer
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+India
+Apply by:
+22 Mar 2026
+State Program Manager-HIV-CSC-North East
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Assam
+Apply by:
+22 Mar 2026
+Neighbourhood Facilitator – Health &amp; NCDs
+Transform Rural India (TRI)
 Location:
 Maharashtra
 Apply by:
-10 Mar 2026
-Part Time Accountant
-Sahabhagi Vikash Abhiyan
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Coordinator
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-Consultant Architects
-(Value Members only)
-Location:
-Chhattisgarh
-Apply by:
-18 Mar 2026
-Community Mobilizer
-Common Man Trust
-Location:
-Delhi, Uttar Pradesh, Haryana
-Apply by:
-25 Mar 2026
-Part-Time Psychology Intern (Telugu Speaking)
-Nayi Disha
-Location:
-Telangana
-Apply by:
-20 Mar 2026
-Field Mobilizer
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-RFP for Data Collection for Foundational Reading ...
-Lords Education and Health Society (LEHS)
-Location:
-Odisha
-Apply by:
-15 Mar 2026
+30 Mar 2026
+Health Planner – Community Mobilization
+Transform Rural India (TRI)
+Location:
+Maharashtra
+Apply by:
+30 Mar 2026
 Jobseekers
 Register
 Login
@@ -1166,441 +1062,88 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>Climate</t>
-        </is>
-      </c>
-      <c r="G5" s="1" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>09-03-2026</t>
         </is>
       </c>
-      <c r="H5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287382</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="H4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=285949</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr"/>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>RFP For Selection of an Implementation Support Agency (Isa) For Capacity B...</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>EAII Advisors Pvt Ltd | Andhra Pradesh
-International Development - RFP For Selection of an Implementation Support Agency (Isa) For Capacity Building Of Community Leaders To Conduct Community Engagement Activities, EAII Advisors Pvt Ltd, Andhra Pradesh - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Regis ... Read More</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>• Proposal Requirements
-1. Company Background and Details
-A. Company Profile
-Overview of the firm or firms submitting the bid, including a brief history, information about organizational structure, relevant company financials, location of offices, number of employees, relevant certifications, or any other information that could be pertinent.
-Supplier Response:
-Kindly fill in the column “Bidder Response”. The current inputs are guiding inputs or choices for answers. Kindly fill in accordingly.
-For detailed information, please check the complete version of the RFP attached below.
-Download Attachment:
-Standalone ISA RFP Technical Evaluation Response Template (1).docx
-Download Attachment:
-Telugu_Standalone ISA RFP Technical Evaluation Response Template.docx
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-09 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Associate – Finance and Operations
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-Manager - Individual Engagement (Acquisition)
-(Value Members only)
-Location:
-Maharashtra
-Apply by:
-10 Mar 2026
-Part Time Accountant
-Sahabhagi Vikash Abhiyan
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Coordinator
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-Consultant Architects
-(Value Members only)
-Location:
-Chhattisgarh
-Apply by:
-18 Mar 2026
-Community Mobilizer
-Common Man Trust
-Location:
-Delhi, Uttar Pradesh, Haryana
-Apply by:
-25 Mar 2026
-Part-Time Psychology Intern (Telugu Speaking)
-Nayi Disha
-Location:
-Telangana
-Apply by:
-20 Mar 2026
-Field Mobilizer
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-RFP for Data Collection for Foundational Reading ...
-Lords Education and Health Society (LEHS)
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>Governance, Learning</t>
-        </is>
-      </c>
-      <c r="G6" s="1" t="inlineStr">
-        <is>
-          <t>09-03-2026</t>
-        </is>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=285950</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr"/>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>RFP For The Contractors To Procure, Build, Install, Supply Chlorine Tablet...</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>EAII Advisors Pvt Ltd | Andhra Pradesh
-International Development - RFP For The Contractors To Procure, Build, Install, Supply Chlorine Tablets, Operate And Maintain Tablet-Based In Line Chlorination Devices, EAII Advisors Pvt Ltd, Andhra Pradesh - DevNetJobsIndia.org
+      <c r="B5" s="1" t="inlineStr"/>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>RFP - Early-Stage Impact Assessment-CDRI SWP 23-26</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Coalition for Disaster Resilient Infrastructure (CDRI) | India
+International Development - RFP - Early-Stage Impact Assessment-CDRI SWP 23-26, Coalition for Disaster Resilient Infrastructure (CDRI), India - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
 Register
-Ho ... Read More</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>• Proposal Requirements
-1. Company Background and Details
-A. Company Profile
-Overview of the firm or firms submitting the bid, including a brief history, information about organizational structure, relevant company financials, location of offices, number of employees, relevant certifications, or any other information that could be pertinent.
-Supplier Response:
-Kindly fill in the column “Bidder Response”. The current inputs are guiding inputs or choices for answers. Kindly fill in accordingly.
-For detailed information, please check the complete version of the RFP attached below.
-Download Attachment:
-Standalone IC RFP Technical Evaluation Response Template.docx
-Download Attachment:
-Telugu_Standalone IC RFP Technical Evaluation Response Template.docx
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-09 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Associate – Finance and Operations
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-Manager - Individual Engagement (Acquisition)
-(Value Members only)
-Location:
-Maharashtra
-Apply by:
-10 Mar 2026
-Part Time Accountant
-Sahabhagi Vikash Abhiyan
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Coordinator
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-Consultant Architects
-(Value Members only)
-Location:
-Chhattisgarh
-Apply by:
-18 Mar 2026
-Community Mobilizer
-Common Man Trust
-Location:
-Delhi, Uttar Pradesh, Haryana
-Apply by:
-25 Mar 2026
-Part-Time Psychology Intern (Telugu Speaking)
-Nayi Disha
-Location:
-Telangana
-Apply by:
-20 Mar 2026
-Field Mobilizer
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-RFP for Data Collection for Foundational Reading ...
-Lords Education and Health Society (LEHS)
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
+Home
+Value Membership
 Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G7" s="1" t="inlineStr">
+RFPs ... Read More</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>Climate, Governance</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>09-03-2026</t>
         </is>
       </c>
-      <c r="H7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=285949</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="H5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287093</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr"/>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="B6" s="1" t="inlineStr"/>
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>RFP - for Supply of Skill Lab Items</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>TeamLease Foundation | India
 International Development - RFP - for Supply of Skill Lab Items, TeamLease Foundation, India - DevNetJobsIndia.org
@@ -1622,7 +1165,7 @@
 Jobseeker ... Read More</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>• Technical Bid Submission Link-
 https://forms.gle/V9iy35ddb4kWEb468
@@ -1667,6 +1210,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
 Associate – Finance and Operations
 Financial Management Service Foundation (FMSF)
 Location:
@@ -1679,12 +1228,6 @@
 Maharashtra
 Apply by:
 03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -1729,54 +1272,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Manager - Individual Engagement (Acquisition)
-(Value Members only)
+RFQ-Corporate Global Group Health Insurance Cover...
+Coalition for Disaster Resilient Infrastructure (...
+Location:
+India
+Apply by:
+23 Mar 2026
+HR Associate
+Inclusion Economics India Centre (IEIC) at IFMR
+Location:
+Delhi
+Apply by:
+08 Apr 2026
+Short Term Consultant - Workshop Facilitator for ...
+Fairtrade NAPP
+Location:
+Assam
+Apply by:
+31 Mar 2026
+State Manager
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Uttar Pradesh
+Apply by:
+22 Mar 2026
+State Project Officer
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+India
+Apply by:
+22 Mar 2026
+State Program Manager-HIV-CSC-North East
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Assam
+Apply by:
+22 Mar 2026
+Neighbourhood Facilitator – Health &amp; NCDs
+Transform Rural India (TRI)
 Location:
 Maharashtra
 Apply by:
-10 Mar 2026
-Part Time Accountant
-Sahabhagi Vikash Abhiyan
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Coordinator
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-Consultant Architects
-(Value Members only)
-Location:
-Chhattisgarh
-Apply by:
-18 Mar 2026
-Community Mobilizer
-Common Man Trust
-Location:
-Delhi, Uttar Pradesh, Haryana
-Apply by:
-25 Mar 2026
-Part-Time Psychology Intern (Telugu Speaking)
-Nayi Disha
-Location:
-Telangana
-Apply by:
-20 Mar 2026
-Field Mobilizer
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-RFP for Data Collection for Foundational Reading ...
-Lords Education and Health Society (LEHS)
-Location:
-Odisha
-Apply by:
-15 Mar 2026
+30 Mar 2026
+Health Planner – Community Mobilization
+Transform Rural India (TRI)
+Location:
+Maharashtra
+Apply by:
+30 Mar 2026
 Jobseekers
 Register
 Login
@@ -1804,285 +1347,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F8" s="1" t="inlineStr">
+      <c r="F6" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G8" s="1" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>11-03-2026</t>
         </is>
       </c>
-      <c r="H8" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="I8" s="1" t="inlineStr">
+      <c r="H6" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287613</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr"/>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Study On SC-DMPA In Rajasthan- Clients And Providers Perspectives On...</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Centre For Community Economics And Development Consultants Society- CECOEDECON | Jaipur, Rajasthan
-International Development - RFP - Study On SC-DMPA In Rajasthan- Clients And Providers Perspectives On SC-DMPA In Rajasthan, Centre For Community Economics And Development Consultants Society- CECOEDE ... Read More</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>• Despite India’s achievement of replacement-level fertility, unmet need for contraception—particularly for spacing methods—remains substantial, with modern contraceptive use at 56.4% (2019–21), highlighting persistent gaps in access and choice, especially among vulnerable populations. Expanding the contraceptive method mix through innovative, user-centred approaches is therefore essential to meeting national commitments under FP2030 and the Sustainable Development Goals. In this context, the Government of India’s introduction of subcutaneous DMPA (DMPA-SC) as a self-care option under the National Family Planning Programme in 2023 represents a strategic step toward enhancing women’s autonomy, privacy, and convenience in contraceptive use. Global and national evidence indicates strong feasibility and acceptability of self-administered DMPA-SC among both users and providers; however, successful implementation requires an in-depth understanding of user experiences and health system readiness. This study, to be conducted in Jaipur-1, Jaisalmer and Sawai Madhopur districts of Rajasthan, aims to examine the perspectives &amp; experience of current SC-DMPA users and explore healthcare providers’ views on enabling and generating actionable evidence to inform effective scale-up of SC-DMPA within India’s public health system.
-CECOEDECON, with support from UNFPA, is implementing the roll-out of subcutaneous DMPA (SC-DMPA) in selected pilot districts of Rajasthan in the public health facilities, in collaboration with the Department of Health &amp; Family Welfare, Government of Rajasthan.
-The selected agency will be required to:
-To assess the experiences and perspectives of SC-DMPA users with a focus on service delivery, follow-up mechanisms, continuation, and future contraceptive intentions related to self-administration.
-To examine the perspectives of healthcare providers (including doctors, nurses, and Community Health Officers trained in the study districts) on client acceptance, readiness, and support requirements for SC-DMPA self-administration. (Total more than 250 doctors and 951 nursing staff and CHOs trained in these districts)
-To identify key barriers and facilitating factors at both client and health-system levels influencing the acceptance, effective use, scalability and Future ready system for scalability of SC-DMPA
-• 2. Scope of Work:
-The agency will be responsible for:
-Finalizing study design and methodology in consultation with stakeholders.
-Developing and pre-testing quantitative and qualitative study tools.
-Securing ethical clearance from a recognized Institutional Review Board (IRB).
-Conducting data collection, including:
-Quantitative interviews with a representative sample of SC-DMPA users
-In-depth interviews with doctors, ANMs.
-Data management, including data entry, cleaning, and analysis.
-Preparation and submission of study reports.
-3. Methodology:
-This study will employ quantitative research techniques on a sample of users of SC-DMPA and qualitative techniques of in-depth interviews with the service providers. A representative sample will be drawn from the list of users of SC-DMPA from the three districts. The health care providers will include Doctors, nurses, Auxiliary Nurse Midwives (ANMs), Nurses and CHOs (Total more than 250 doctors and 951 nursing staff and CHOs trained in these districts)
-Sampling: Probability proportional to size sampling will be adopted using the number of SC-DMPA users in Jaisalmer, Sawai Madhupur and Jaipur-1, as size measure (from approx. 15000 users)
-Quantitative data: Interviews with selected SC-DMPA users.
-Qualitative data: In-depth interviews with healthcare providers.
-4. Deliverables:
-Inception report with finalized study design and tools.
-IRB approval.
-Clean dataset (quantitative and qualitative).
-Analytical reports (interim and final).
-Policy brief with actionable recommendations.
-5. Timeline:
-The assignment is expected to be completed within 5 months following contract signing, as per the following tentative schedule:
-Finalization of study design and tool development: March-
-April 2026
-Ethical clearance: May 2026
-Training of investigators – June 2026
-Data collection: July 2026
-Data analysis and reporting: Mid Aug 2026
-6. Required Qualifications of the Agency:
-Proven experience in conducting large-scale health and family planning research studies.
-Expertise in both quantitative and qualitative research methods.
-Familiarity with contraceptive technology, self-care interventions, and public health systems.
-Experience in working with government health systems and familiarity with Rajasthan’s context will be preferred.
-Demonstrated capacity to ensure ethical compliance and data confidentiality.
-Availability of qualified and experienced research team.
-• 7. Proposal Submission Requirements:
-Interested agencies should submit:
-• Organizational profile with relevant experience.
-Detailed technical proposal maximum of 5 pages outlining understanding of the assignment, methodology, sampling approach, data collection plan, team composition, quality assurance, and ethical considerations.
-Financial proposal (separately in INR).
-https://docs.google.com/spreadsheets/d/1Yqiy8FXJeOrAIv_vXiA_whsUG59WtuvY/edit?usp=sharing&amp;ouid=107933350131648505243&amp;rtpof=true&amp;sd=true
-(Please Download Financial proposal format.)
-Timeline for deliverables.
-CVs of key team members.
-• 8. Evaluation Criteria:
-Proposals will be evaluated based on:
-Technical expertise and relevance of prior experience.
-Soundness of proposed methodology and work plan.
-Qualifications of proposed team.
-Financial competitiveness.
-9.  Contact Information:
-In case of any doubt or query the agency can send mail to cecojobs@gmail.com within 7 days of advertisement of the RFP.
-• Job Email ID:
-cecojobs(at)gmail.com
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-11 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Associate – Finance and Operations
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-Manager - Individual Engagement (Acquisition)
-(Value Members only)
-Location:
-Maharashtra
-Apply by:
-10 Mar 2026
-Part Time Accountant
-Sahabhagi Vikash Abhiyan
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Coordinator
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-Consultant Architects
-(Value Members only)
-Location:
-Chhattisgarh
-Apply by:
-18 Mar 2026
-Community Mobilizer
-Common Man Trust
-Location:
-Delhi, Uttar Pradesh, Haryana
-Apply by:
-25 Mar 2026
-Part-Time Psychology Intern (Telugu Speaking)
-Nayi Disha
-Location:
-Telangana
-Apply by:
-20 Mar 2026
-Field Mobilizer
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-RFP for Data Collection for Foundational Reading ...
-Lords Education and Health Society (LEHS)
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
-          <t>11-03-2026</t>
-        </is>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="I9" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287322</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="inlineStr"/>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>SOW - Engagement of a Public Relations (PR) Agency on Retainer</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Room to Read India | India
 International Development - SOW - Engagement of a Public Relations (PR) Agency on Retainer, Room to Read India, India - DevNetJobsIndia.org
@@ -2103,7 +1399,7 @@
 Job ... Read More</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>• Scope of Work (SOW)
 Engagement of a Public Relations (PR) Agency on Retainer
@@ -2171,6 +1467,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
 Associate – Finance and Operations
 Financial Management Service Foundation (FMSF)
 Location:
@@ -2183,12 +1485,6 @@
 Maharashtra
 Apply by:
 03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -2233,54 +1529,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Manager - Individual Engagement (Acquisition)
-(Value Members only)
+RFQ-Corporate Global Group Health Insurance Cover...
+Coalition for Disaster Resilient Infrastructure (...
+Location:
+India
+Apply by:
+23 Mar 2026
+HR Associate
+Inclusion Economics India Centre (IEIC) at IFMR
+Location:
+Delhi
+Apply by:
+08 Apr 2026
+Short Term Consultant - Workshop Facilitator for ...
+Fairtrade NAPP
+Location:
+Assam
+Apply by:
+31 Mar 2026
+State Manager
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Uttar Pradesh
+Apply by:
+22 Mar 2026
+State Project Officer
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+India
+Apply by:
+22 Mar 2026
+State Program Manager-HIV-CSC-North East
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Assam
+Apply by:
+22 Mar 2026
+Neighbourhood Facilitator – Health &amp; NCDs
+Transform Rural India (TRI)
 Location:
 Maharashtra
 Apply by:
-10 Mar 2026
-Part Time Accountant
-Sahabhagi Vikash Abhiyan
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Coordinator
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-Consultant Architects
-(Value Members only)
-Location:
-Chhattisgarh
-Apply by:
-18 Mar 2026
-Community Mobilizer
-Common Man Trust
-Location:
-Delhi, Uttar Pradesh, Haryana
-Apply by:
-25 Mar 2026
-Part-Time Psychology Intern (Telugu Speaking)
-Nayi Disha
-Location:
-Telangana
-Apply by:
-20 Mar 2026
-Field Mobilizer
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-RFP for Data Collection for Foundational Reading ...
-Lords Education and Health Society (LEHS)
-Location:
-Odisha
-Apply by:
-15 Mar 2026
+30 Mar 2026
+Health Planner – Community Mobilization
+Transform Rural India (TRI)
+Location:
+Maharashtra
+Apply by:
+30 Mar 2026
 Jobseekers
 Register
 Login
@@ -2308,251 +1604,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F10" s="1" t="inlineStr">
+      <c r="F7" s="1" t="inlineStr">
         <is>
           <t>Governance, Learning</t>
         </is>
       </c>
-      <c r="G10" s="1" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>12-03-2026</t>
         </is>
       </c>
-      <c r="H10" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I10" s="1" t="inlineStr">
+      <c r="H7" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287648</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr"/>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>RFP - for Internal Audit</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>India HIV/AIDS Alliance (Alliance India) | Delhi
-International Development - RFP - for Internal Audit, India HIV/AIDS Alliance (Alliance India), Delhi - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Login
-|
-Regist ... Read More</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>• Alliance India reserves the right to reject applications that do not meet eligibility or application submission requirements (as detailed above) without further notice to the applicant. Issuance of this RFP does not constitute an award commitment or a guarantee of business on the part of Alliance India, nor does it commit Alliance India to pay for the costs incurred in submitting the application. Further, Alliance India reserves the right to reject any or all applications received and negotiate separately with an applicant if such action is considered in the best interest of Alliance India/ project.
-iii.
-Queries, Response and Submission
-Queries regarding this RFP will be sent only to procurement@allianceindia.org by March 07, 2026. Alliance India shall collaborate and respond to all meaningful queries from prospective applicants by March 10, 2026. Responses to questions shall be compiled and sent to all the applicants who raised the queries through email only. ALLIANCE INDIA is under no obligation to consider or respond to questions that are not received on time.
-iv.
-• Submission of bids
-The bid has to be submitted in the prescribed format on or before March 13, 2026 by 5 p.m. Indian Standard Time to
-procurement@allianceindia.org
-For the detailed version of the Request for Proposal, please refer to the RFP attached.
-• Job Email ID:
-procurement(at)allianceindia.org
-Download Attachment:
-RFP for Internal Audit - FY 2025-26.doc
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-13 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Associate – Finance and Operations
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-Manager - Individual Engagement (Acquisition)
-(Value Members only)
-Location:
-Maharashtra
-Apply by:
-10 Mar 2026
-Part Time Accountant
-Sahabhagi Vikash Abhiyan
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Coordinator
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-Consultant Architects
-(Value Members only)
-Location:
-Chhattisgarh
-Apply by:
-18 Mar 2026
-Community Mobilizer
-Common Man Trust
-Location:
-Delhi, Uttar Pradesh, Haryana
-Apply by:
-25 Mar 2026
-Part-Time Psychology Intern (Telugu Speaking)
-Nayi Disha
-Location:
-Telangana
-Apply by:
-20 Mar 2026
-Field Mobilizer
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-RFP for Data Collection for Foundational Reading ...
-Lords Education and Health Society (LEHS)
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G11" s="1" t="inlineStr">
-        <is>
-          <t>13-03-2026</t>
-        </is>
-      </c>
-      <c r="H11" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="I11" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287765</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="inlineStr"/>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr"/>
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>Specialist – Financial Management and Compliance</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Financial Management Service Foundation (FMSF) | Uttar Pradesh
 International Development - Specialist – Financial Management and Compliance, Financial Management Service Foundation (FMSF), Uttar Pradesh - DevNetJobsIndia.org
@@ -2566,7 +1649,7 @@
 RFPs/T ... Read More</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>• will play a vital role in a program which seeks to strengthen the internal capacities of non-profit organizations in India across three building blocks of institutional functioning: governance, financial management, and compliance. These areas are deeply interconnected and together determine how effectively an organization operates, delivers programs and meets the expectations of its stakeholders. This position demands expertise in specific areas related to governance, compliance, and financial management, contributing essential guidance and support to strengthen the capabilities of participating organizations.
 Job Responsibilities:
@@ -2617,6 +1700,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
 Associate – Finance and Operations
 Financial Management Service Foundation (FMSF)
 Location:
@@ -2629,12 +1718,6 @@
 Maharashtra
 Apply by:
 03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -2679,54 +1762,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Manager - Individual Engagement (Acquisition)
-(Value Members only)
+RFQ-Corporate Global Group Health Insurance Cover...
+Coalition for Disaster Resilient Infrastructure (...
+Location:
+India
+Apply by:
+23 Mar 2026
+HR Associate
+Inclusion Economics India Centre (IEIC) at IFMR
+Location:
+Delhi
+Apply by:
+08 Apr 2026
+Short Term Consultant - Workshop Facilitator for ...
+Fairtrade NAPP
+Location:
+Assam
+Apply by:
+31 Mar 2026
+State Manager
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Uttar Pradesh
+Apply by:
+22 Mar 2026
+State Project Officer
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+India
+Apply by:
+22 Mar 2026
+State Program Manager-HIV-CSC-North East
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Assam
+Apply by:
+22 Mar 2026
+Neighbourhood Facilitator – Health &amp; NCDs
+Transform Rural India (TRI)
 Location:
 Maharashtra
 Apply by:
-10 Mar 2026
-Part Time Accountant
-Sahabhagi Vikash Abhiyan
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Coordinator
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-Consultant Architects
-(Value Members only)
-Location:
-Chhattisgarh
-Apply by:
-18 Mar 2026
-Community Mobilizer
-Common Man Trust
-Location:
-Delhi, Uttar Pradesh, Haryana
-Apply by:
-25 Mar 2026
-Part-Time Psychology Intern (Telugu Speaking)
-Nayi Disha
-Location:
-Telangana
-Apply by:
-20 Mar 2026
-Field Mobilizer
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-RFP for Data Collection for Foundational Reading ...
-Lords Education and Health Society (LEHS)
-Location:
-Odisha
-Apply by:
-15 Mar 2026
+30 Mar 2026
+Health Planner – Community Mobilization
+Transform Rural India (TRI)
+Location:
+Maharashtra
+Apply by:
+30 Mar 2026
 Jobseekers
 Register
 Login
@@ -2754,41 +1837,41 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F12" s="1" t="inlineStr">
+      <c r="F8" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G12" s="1" t="inlineStr">
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>13-03-2026</t>
         </is>
       </c>
-      <c r="H12" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="I12" s="1" t="inlineStr">
+      <c r="H8" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287015</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr"/>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>ToR - Livelihoods Strategy Review and Future Direction Roadmap</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>ChildFund India | India
-International Development - ToR - Livelihoods Strategy Review and Future Direction Roadmap, ChildFund India, India - DevNetJobsIndia.org
+      <c r="B9" s="1" t="inlineStr"/>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>RFP - for Internal Audit</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>India HIV/AIDS Alliance (Alliance India) | Delhi
+International Development - RFP - for Internal Audit, India HIV/AIDS Alliance (Alliance India), Delhi - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
@@ -2802,44 +1885,40 @@
 Jobseekers:
 Login
 |
-Register
-Jobseeker ... Read More</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>• To determine the relevance, alignment, and coherence of the Livelihood Program under CSP 2022–2027 with national priorities, donor expectations, and organizational mandate.
-To assess the extent to which planned outputs and outcomes have been achieved and to evaluate the quality and impact of program interventions.
-Identify achievements, innovations, good practices, and enabling factors across Livelihood program interventions.
-Document gaps, challenges, and areas for strengthening
-To examine the sustainability of program outcomes and the institutional readiness of ChildFund India for long-term resilience and growth.
-Facilitate reflection through workshops involving staff, partners, and selected beneficiaries and provide recommendations for strategic direction, scalability, and future program priorities.
-Proposal Submission
-Interested evaluators/agencies are invited to submit:
-Technical proposal outlining approach and methodology
-Team composition and relevant experience
-Financial proposal with a detailed budget
-Sample of previous qualitative evaluation work
-Interested evaluators/agencies are requested to submit their technical and financial proposals to
-centralpurchase2@childfundindia.org
-by 15 March 2026.
-Reference No:- PRA/CFI/DEL/2025-26/053
-ChildFund India reserves the right to modify this ToR based on programmatic and contextual requirements.
-For detailed information, please check the complete version of the advert attached below.
+Regist ... Read More</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>• Alliance India reserves the right to reject applications that do not meet eligibility or application submission requirements (as detailed above) without further notice to the applicant. Issuance of this RFP does not constitute an award commitment or a guarantee of business on the part of Alliance India, nor does it commit Alliance India to pay for the costs incurred in submitting the application. Further, Alliance India reserves the right to reject any or all applications received and negotiate separately with an applicant if such action is considered in the best interest of Alliance India/ project.
+iii.
+Queries, Response and Submission
+Queries regarding this RFP will be sent only to procurement@allianceindia.org by March 07, 2026. Alliance India shall collaborate and respond to all meaningful queries from prospective applicants by March 10, 2026. Responses to questions shall be compiled and sent to all the applicants who raised the queries through email only. ALLIANCE INDIA is under no obligation to consider or respond to questions that are not received on time.
+iv.
+• Submission of bids
+The bid has to be submitted in the prescribed format on or before March 13, 2026 by 5 p.m. Indian Standard Time to
+procurement@allianceindia.org
+For the detailed version of the Request for Proposal, please refer to the RFP attached.
 • Job Email ID:
-centralpurchase2(at)childfundindia.org
+procurement(at)allianceindia.org
 Download Attachment:
-ToR Livelihood Portfolio-6.3.2026.doc
+RFP for Internal Audit - FY 2025-26.doc
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
 Apply by:
-15 Mar 2026
+13 Mar 2026
 Access all the jobs and get ahead!
 Subscribe to Value Membership Now!
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
 Associate – Finance and Operations
 Financial Management Service Foundation (FMSF)
 Location:
@@ -2852,12 +1931,6 @@
 Maharashtra
 Apply by:
 03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -2902,54 +1975,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Manager - Individual Engagement (Acquisition)
-(Value Members only)
+RFQ-Corporate Global Group Health Insurance Cover...
+Coalition for Disaster Resilient Infrastructure (...
+Location:
+India
+Apply by:
+23 Mar 2026
+HR Associate
+Inclusion Economics India Centre (IEIC) at IFMR
+Location:
+Delhi
+Apply by:
+08 Apr 2026
+Short Term Consultant - Workshop Facilitator for ...
+Fairtrade NAPP
+Location:
+Assam
+Apply by:
+31 Mar 2026
+State Manager
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Uttar Pradesh
+Apply by:
+22 Mar 2026
+State Project Officer
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+India
+Apply by:
+22 Mar 2026
+State Program Manager-HIV-CSC-North East
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Assam
+Apply by:
+22 Mar 2026
+Neighbourhood Facilitator – Health &amp; NCDs
+Transform Rural India (TRI)
 Location:
 Maharashtra
 Apply by:
-10 Mar 2026
-Part Time Accountant
-Sahabhagi Vikash Abhiyan
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Coordinator
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-Consultant Architects
-(Value Members only)
-Location:
-Chhattisgarh
-Apply by:
-18 Mar 2026
-Community Mobilizer
-Common Man Trust
-Location:
-Delhi, Uttar Pradesh, Haryana
-Apply by:
-25 Mar 2026
-Part-Time Psychology Intern (Telugu Speaking)
-Nayi Disha
-Location:
-Telangana
-Apply by:
-20 Mar 2026
-Field Mobilizer
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-RFP for Data Collection for Foundational Reading ...
-Lords Education and Health Society (LEHS)
-Location:
-Odisha
-Apply by:
-15 Mar 2026
+30 Mar 2026
+Health Planner – Community Mobilization
+Transform Rural India (TRI)
+Location:
+Maharashtra
+Apply by:
+30 Mar 2026
 Jobseekers
 Register
 Login
@@ -2977,715 +2050,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="G13" s="1" t="inlineStr">
-        <is>
-          <t>15-03-2026</t>
-        </is>
-      </c>
-      <c r="H13" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="I13" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287910</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t>13-03-2026</t>
+        </is>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287765</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr"/>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>ToR - Portfolio-Wide Learning Exercise cum review for the Health Domain</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>ChildFund India | India
-International Development - ToR - Portfolio-Wide Learning Exercise cum review for the Health Domain, ChildFund India, India - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Login
-|
-Register ... Read More</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>• Job Email ID:
-centralpurchase2(at)childfundindia.org
-Download Attachment:
-TOR  Health Portfolio_23.2.2026.doc
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-15 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Associate – Finance and Operations
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-Manager - Individual Engagement (Acquisition)
-(Value Members only)
-Location:
-Maharashtra
-Apply by:
-10 Mar 2026
-Part Time Accountant
-Sahabhagi Vikash Abhiyan
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Coordinator
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-Consultant Architects
-(Value Members only)
-Location:
-Chhattisgarh
-Apply by:
-18 Mar 2026
-Community Mobilizer
-Common Man Trust
-Location:
-Delhi, Uttar Pradesh, Haryana
-Apply by:
-25 Mar 2026
-Part-Time Psychology Intern (Telugu Speaking)
-Nayi Disha
-Location:
-Telangana
-Apply by:
-20 Mar 2026
-Field Mobilizer
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-RFP for Data Collection for Foundational Reading ...
-Lords Education and Health Society (LEHS)
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F14" s="1" t="inlineStr">
-        <is>
-          <t>Learning, Safety</t>
-        </is>
-      </c>
-      <c r="G14" s="1" t="inlineStr">
-        <is>
-          <t>15-03-2026</t>
-        </is>
-      </c>
-      <c r="H14" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="I14" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287901</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B15" s="1" t="inlineStr"/>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>RFP - for Empanelment of Knowledge Partners for Grooming of students for ...</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>TeamLease Foundation | India
-International Development - RFP - for  Empanelment of Knowledge Partners for Grooming of students for competitive examination (through partner) Super 30 Model, TeamLease Foundation, India - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast ... Read More</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F15" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G15" s="1" t="inlineStr">
-        <is>
-          <t>15-03-2026</t>
-        </is>
-      </c>
-      <c r="H15" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="I15" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287763</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B16" s="1" t="inlineStr"/>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>ToR - Strategic Review and Forward-Looking Education Strategy Development</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>ChildFund India | India
-International Development - ToR - Strategic Review and Forward-Looking Education Strategy Development, ChildFund India, India - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Login
-|
-Registe ... Read More</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>• Job Email ID:
-centralpurchase2(at)childfundindia.org
-Download Attachment:
-ToR for Education.doc
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-15 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Associate – Finance and Operations
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-Manager - Individual Engagement (Acquisition)
-(Value Members only)
-Location:
-Maharashtra
-Apply by:
-10 Mar 2026
-Part Time Accountant
-Sahabhagi Vikash Abhiyan
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Coordinator
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-Consultant Architects
-(Value Members only)
-Location:
-Chhattisgarh
-Apply by:
-18 Mar 2026
-Community Mobilizer
-Common Man Trust
-Location:
-Delhi, Uttar Pradesh, Haryana
-Apply by:
-25 Mar 2026
-Part-Time Psychology Intern (Telugu Speaking)
-Nayi Disha
-Location:
-Telangana
-Apply by:
-20 Mar 2026
-Field Mobilizer
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-RFP for Data Collection for Foundational Reading ...
-Lords Education and Health Society (LEHS)
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t>Learning, Safety</t>
-        </is>
-      </c>
-      <c r="G16" s="1" t="inlineStr">
-        <is>
-          <t>15-03-2026</t>
-        </is>
-      </c>
-      <c r="H16" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="I16" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287902</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B17" s="1" t="inlineStr"/>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>RFP for Data Collection for Foundational Reading Tool in Odisha</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Lords Education and Health Society (LEHS) | Odisha
-International Development - RFP for Data Collection for Foundational Reading Tool in Odisha, Lords Education and Health Society (LEHS), Odisha - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Se ... Read More</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>• 4. SCOPE OF WORK
-Summary of Activities
-S.No
-Activity   Description
-Timelines
-1
-Data   Collection: students' reading of textual items   (letters/words/non-words/paragraphs) in Odia &amp; English languages for   Grades 1-8.
-Data       Collection should be completed in   April 2026
-Details of the Activity Below:
-Data Collection: Collect audio data of students reading texts in Odia &amp; English from Grade 1-8
-Total Number of Hours to be collected: ~360 hours for the Odia language
-Total Number of Hours to be collected: ~115 hours for the English language
-• Submission Details
-All proposals to this RFP must be received no later than &lt;15th March 2026&gt;
-.
-The proposal should be submitted only through e-mail in PDF format addressed to the Procurement Team at:
-rfp.lehs@wadhwaniai.org
-. The email's subject line must contain the reference number and title of the RFP: Data Collection for Foundational Reading
-Tool in Odisha  (Name of Partner)
-Any proposals received by Wadhwani-AI after the deadline prescribed in the timeline of this document are liable to be rejected.
-For detailed information, please check the complete version of the RFP attached below
-• Job Email ID:
-rfp.lehs(at)wadhwaniai.org
-Download Attachment:
-RFP for Data Collection for Foundational Reading Tool in Odisha.pdf
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-15 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Associate – Finance and Operations
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-Manager - Individual Engagement (Acquisition)
-(Value Members only)
-Location:
-Maharashtra
-Apply by:
-10 Mar 2026
-Part Time Accountant
-Sahabhagi Vikash Abhiyan
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Coordinator
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-Consultant Architects
-(Value Members only)
-Location:
-Chhattisgarh
-Apply by:
-18 Mar 2026
-Community Mobilizer
-Common Man Trust
-Location:
-Delhi, Uttar Pradesh, Haryana
-Apply by:
-25 Mar 2026
-Part-Time Psychology Intern (Telugu Speaking)
-Nayi Disha
-Location:
-Telangana
-Apply by:
-20 Mar 2026
-Field Mobilizer
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-RFP for Data Collection for Foundational Reading ...
-Lords Education and Health Society (LEHS)
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t>Governance, Learning, Safety</t>
-        </is>
-      </c>
-      <c r="G17" s="1" t="inlineStr">
-        <is>
-          <t>15-03-2026</t>
-        </is>
-      </c>
-      <c r="H17" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="I17" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287936</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B18" s="1" t="inlineStr"/>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="B10" s="1" t="inlineStr"/>
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>RFP - External organization/agency to undertake documentation and process ...</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>India Health Action Trust (IHAT) | India
 International Development - RFP - External organization/agency to undertake documentation and process evaluation of the Gen Equal Fellowship Programme, India Health Action Trust (IHAT), India - DevNetJobsIndia.org
@@ -3697,7 +2093,7 @@
 Value Memb ... Read More</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>• 3A. Scope of Work
 Time Period
@@ -3780,6 +2176,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
 Associate – Finance and Operations
 Financial Management Service Foundation (FMSF)
 Location:
@@ -3792,12 +2194,6 @@
 Maharashtra
 Apply by:
 03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -3842,54 +2238,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Manager - Individual Engagement (Acquisition)
-(Value Members only)
+RFQ-Corporate Global Group Health Insurance Cover...
+Coalition for Disaster Resilient Infrastructure (...
+Location:
+India
+Apply by:
+23 Mar 2026
+HR Associate
+Inclusion Economics India Centre (IEIC) at IFMR
+Location:
+Delhi
+Apply by:
+08 Apr 2026
+Short Term Consultant - Workshop Facilitator for ...
+Fairtrade NAPP
+Location:
+Assam
+Apply by:
+31 Mar 2026
+State Manager
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Uttar Pradesh
+Apply by:
+22 Mar 2026
+State Project Officer
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+India
+Apply by:
+22 Mar 2026
+State Program Manager-HIV-CSC-North East
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Assam
+Apply by:
+22 Mar 2026
+Neighbourhood Facilitator – Health &amp; NCDs
+Transform Rural India (TRI)
 Location:
 Maharashtra
 Apply by:
-10 Mar 2026
-Part Time Accountant
-Sahabhagi Vikash Abhiyan
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Coordinator
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-Consultant Architects
-(Value Members only)
-Location:
-Chhattisgarh
-Apply by:
-18 Mar 2026
-Community Mobilizer
-Common Man Trust
-Location:
-Delhi, Uttar Pradesh, Haryana
-Apply by:
-25 Mar 2026
-Part-Time Psychology Intern (Telugu Speaking)
-Nayi Disha
-Location:
-Telangana
-Apply by:
-20 Mar 2026
-Field Mobilizer
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-RFP for Data Collection for Foundational Reading ...
-Lords Education and Health Society (LEHS)
-Location:
-Odisha
-Apply by:
-15 Mar 2026
+30 Mar 2026
+Health Planner – Community Mobilization
+Transform Rural India (TRI)
+Location:
+Maharashtra
+Apply by:
+30 Mar 2026
 Jobseekers
 Register
 Login
@@ -3917,38 +2313,938 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F18" s="1" t="inlineStr">
+      <c r="F10" s="1" t="inlineStr">
         <is>
           <t>Safety</t>
         </is>
       </c>
-      <c r="G18" s="1" t="inlineStr">
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>15-03-2026</t>
         </is>
       </c>
-      <c r="H18" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="I18" s="1" t="inlineStr">
+      <c r="H10" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I10" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287645</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr"/>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr"/>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t>ToR - Livelihoods Strategy Review and Future Direction Roadmap</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>ChildFund India | India
+International Development - ToR - Livelihoods Strategy Review and Future Direction Roadmap, ChildFund India, India - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers:
+Login
+|
+Register
+Jobseeker ... Read More</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>• To determine the relevance, alignment, and coherence of the Livelihood Program under CSP 2022–2027 with national priorities, donor expectations, and organizational mandate.
+To assess the extent to which planned outputs and outcomes have been achieved and to evaluate the quality and impact of program interventions.
+Identify achievements, innovations, good practices, and enabling factors across Livelihood program interventions.
+Document gaps, challenges, and areas for strengthening
+To examine the sustainability of program outcomes and the institutional readiness of ChildFund India for long-term resilience and growth.
+Facilitate reflection through workshops involving staff, partners, and selected beneficiaries and provide recommendations for strategic direction, scalability, and future program priorities.
+Proposal Submission
+Interested evaluators/agencies are invited to submit:
+Technical proposal outlining approach and methodology
+Team composition and relevant experience
+Financial proposal with a detailed budget
+Sample of previous qualitative evaluation work
+Interested evaluators/agencies are requested to submit their technical and financial proposals to
+centralpurchase2@childfundindia.org
+by 15 March 2026.
+Reference No:- PRA/CFI/DEL/2025-26/053
+ChildFund India reserves the right to modify this ToR based on programmatic and contextual requirements.
+For detailed information, please check the complete version of the advert attached below.
+• Job Email ID:
+centralpurchase2(at)childfundindia.org
+Download Attachment:
+ToR Livelihood Portfolio-6.3.2026.doc
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+15 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+RFQ-Corporate Global Group Health Insurance Cover...
+Coalition for Disaster Resilient Infrastructure (...
+Location:
+India
+Apply by:
+23 Mar 2026
+HR Associate
+Inclusion Economics India Centre (IEIC) at IFMR
+Location:
+Delhi
+Apply by:
+08 Apr 2026
+Short Term Consultant - Workshop Facilitator for ...
+Fairtrade NAPP
+Location:
+Assam
+Apply by:
+31 Mar 2026
+State Manager
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Uttar Pradesh
+Apply by:
+22 Mar 2026
+State Project Officer
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+India
+Apply by:
+22 Mar 2026
+State Program Manager-HIV-CSC-North East
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Assam
+Apply by:
+22 Mar 2026
+Neighbourhood Facilitator – Health &amp; NCDs
+Transform Rural India (TRI)
+Location:
+Maharashtra
+Apply by:
+30 Mar 2026
+Health Planner – Community Mobilization
+Transform Rural India (TRI)
+Location:
+Maharashtra
+Apply by:
+30 Mar 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t>15-03-2026</t>
+        </is>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I11" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287910</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr"/>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>ToR - Strategic Review and Forward-Looking Education Strategy Development</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>ChildFund India | India
+International Development - ToR - Strategic Review and Forward-Looking Education Strategy Development, ChildFund India, India - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers:
+Login
+|
+Registe ... Read More</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>• Job Email ID:
+centralpurchase2(at)childfundindia.org
+Download Attachment:
+ToR for Education.doc
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+15 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+RFQ-Corporate Global Group Health Insurance Cover...
+Coalition for Disaster Resilient Infrastructure (...
+Location:
+India
+Apply by:
+23 Mar 2026
+HR Associate
+Inclusion Economics India Centre (IEIC) at IFMR
+Location:
+Delhi
+Apply by:
+08 Apr 2026
+Short Term Consultant - Workshop Facilitator for ...
+Fairtrade NAPP
+Location:
+Assam
+Apply by:
+31 Mar 2026
+State Manager
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Uttar Pradesh
+Apply by:
+22 Mar 2026
+State Project Officer
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+India
+Apply by:
+22 Mar 2026
+State Program Manager-HIV-CSC-North East
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Assam
+Apply by:
+22 Mar 2026
+Neighbourhood Facilitator – Health &amp; NCDs
+Transform Rural India (TRI)
+Location:
+Maharashtra
+Apply by:
+30 Mar 2026
+Health Planner – Community Mobilization
+Transform Rural India (TRI)
+Location:
+Maharashtra
+Apply by:
+30 Mar 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>Learning, Safety</t>
+        </is>
+      </c>
+      <c r="G12" s="1" t="inlineStr">
+        <is>
+          <t>15-03-2026</t>
+        </is>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I12" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287902</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr"/>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>ToR - Portfolio-Wide Learning Exercise cum review for the Health Domain</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>ChildFund India | India
+International Development - ToR - Portfolio-Wide Learning Exercise cum review for the Health Domain, ChildFund India, India - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers:
+Login
+|
+Register ... Read More</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>• Job Email ID:
+centralpurchase2(at)childfundindia.org
+Download Attachment:
+TOR  Health Portfolio_23.2.2026.doc
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+15 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+RFQ-Corporate Global Group Health Insurance Cover...
+Coalition for Disaster Resilient Infrastructure (...
+Location:
+India
+Apply by:
+23 Mar 2026
+HR Associate
+Inclusion Economics India Centre (IEIC) at IFMR
+Location:
+Delhi
+Apply by:
+08 Apr 2026
+Short Term Consultant - Workshop Facilitator for ...
+Fairtrade NAPP
+Location:
+Assam
+Apply by:
+31 Mar 2026
+State Manager
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Uttar Pradesh
+Apply by:
+22 Mar 2026
+State Project Officer
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+India
+Apply by:
+22 Mar 2026
+State Program Manager-HIV-CSC-North East
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Assam
+Apply by:
+22 Mar 2026
+Neighbourhood Facilitator – Health &amp; NCDs
+Transform Rural India (TRI)
+Location:
+Maharashtra
+Apply by:
+30 Mar 2026
+Health Planner – Community Mobilization
+Transform Rural India (TRI)
+Location:
+Maharashtra
+Apply by:
+30 Mar 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>Learning, Safety</t>
+        </is>
+      </c>
+      <c r="G13" s="1" t="inlineStr">
+        <is>
+          <t>15-03-2026</t>
+        </is>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I13" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287901</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr"/>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>RFP - for Empanelment of Knowledge Partners for Grooming of students for ...</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>TeamLease Foundation | India
+International Development - RFP - for  Empanelment of Knowledge Partners for Grooming of students for competitive examination (through partner) Super 30 Model, TeamLease Foundation, India - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast ... Read More</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t>15-03-2026</t>
+        </is>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I14" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287763</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr"/>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>RFP for Data Collection for Foundational Reading Tool in Odisha</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Lords Education and Health Society (LEHS) | Odisha
+International Development - RFP for Data Collection for Foundational Reading Tool in Odisha, Lords Education and Health Society (LEHS), Odisha - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Se ... Read More</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>• 4. SCOPE OF WORK
+Summary of Activities
+S.No
+Activity   Description
+Timelines
+1
+Data   Collection: students' reading of textual items   (letters/words/non-words/paragraphs) in Odia &amp; English languages for   Grades 1-8.
+Data       Collection should be completed in   April 2026
+Details of the Activity Below:
+Data Collection: Collect audio data of students reading texts in Odia &amp; English from Grade 1-8
+Total Number of Hours to be collected: ~360 hours for the Odia language
+Total Number of Hours to be collected: ~115 hours for the English language
+• Submission Details
+All proposals to this RFP must be received no later than &lt;15th March 2026&gt;
+.
+The proposal should be submitted only through e-mail in PDF format addressed to the Procurement Team at:
+rfp.lehs@wadhwaniai.org
+. The email's subject line must contain the reference number and title of the RFP: Data Collection for Foundational Reading
+Tool in Odisha  (Name of Partner)
+Any proposals received by Wadhwani-AI after the deadline prescribed in the timeline of this document are liable to be rejected.
+For detailed information, please check the complete version of the RFP attached below
+• Job Email ID:
+rfp.lehs(at)wadhwaniai.org
+Download Attachment:
+RFP for Data Collection for Foundational Reading Tool in Odisha.pdf
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+15 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+RFQ-Corporate Global Group Health Insurance Cover...
+Coalition for Disaster Resilient Infrastructure (...
+Location:
+India
+Apply by:
+23 Mar 2026
+HR Associate
+Inclusion Economics India Centre (IEIC) at IFMR
+Location:
+Delhi
+Apply by:
+08 Apr 2026
+Short Term Consultant - Workshop Facilitator for ...
+Fairtrade NAPP
+Location:
+Assam
+Apply by:
+31 Mar 2026
+State Manager
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Uttar Pradesh
+Apply by:
+22 Mar 2026
+State Project Officer
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+India
+Apply by:
+22 Mar 2026
+State Program Manager-HIV-CSC-North East
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Assam
+Apply by:
+22 Mar 2026
+Neighbourhood Facilitator – Health &amp; NCDs
+Transform Rural India (TRI)
+Location:
+Maharashtra
+Apply by:
+30 Mar 2026
+Health Planner – Community Mobilization
+Transform Rural India (TRI)
+Location:
+Maharashtra
+Apply by:
+30 Mar 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F15" s="1" t="inlineStr">
+        <is>
+          <t>Governance, Learning, Safety</t>
+        </is>
+      </c>
+      <c r="G15" s="1" t="inlineStr">
+        <is>
+          <t>15-03-2026</t>
+        </is>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I15" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287936</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr"/>
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>RFP - Big IC+ISA RFP - Selection of a Service Provider for Supply, Instal...</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>EAII Advisors Pvt Ltd | Andhra Pradesh
 International Development - RFP - Big IC+ISA RFP -  Selection of a Service Provider for Supply, Installation and Operation &amp; Maintenance of 150 ILC Devices and Capacity Building., EAII Advisors Pvt Ltd, Andhra Pradesh - DevNetJobsIndia.org
@@ -3957,7 +3253,7 @@
 | ... Read More</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>• 2. Purpose of the RFP:
 2.1  EAII is soliciting bids for:
@@ -4004,6 +3300,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
 Associate – Finance and Operations
 Financial Management Service Foundation (FMSF)
 Location:
@@ -4016,12 +3318,6 @@
 Maharashtra
 Apply by:
 03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -4066,54 +3362,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Manager - Individual Engagement (Acquisition)
-(Value Members only)
+RFQ-Corporate Global Group Health Insurance Cover...
+Coalition for Disaster Resilient Infrastructure (...
+Location:
+India
+Apply by:
+23 Mar 2026
+HR Associate
+Inclusion Economics India Centre (IEIC) at IFMR
+Location:
+Delhi
+Apply by:
+08 Apr 2026
+Short Term Consultant - Workshop Facilitator for ...
+Fairtrade NAPP
+Location:
+Assam
+Apply by:
+31 Mar 2026
+State Manager
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Uttar Pradesh
+Apply by:
+22 Mar 2026
+State Project Officer
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+India
+Apply by:
+22 Mar 2026
+State Program Manager-HIV-CSC-North East
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Assam
+Apply by:
+22 Mar 2026
+Neighbourhood Facilitator – Health &amp; NCDs
+Transform Rural India (TRI)
 Location:
 Maharashtra
 Apply by:
-10 Mar 2026
-Part Time Accountant
-Sahabhagi Vikash Abhiyan
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Coordinator
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-Consultant Architects
-(Value Members only)
-Location:
-Chhattisgarh
-Apply by:
-18 Mar 2026
-Community Mobilizer
-Common Man Trust
-Location:
-Delhi, Uttar Pradesh, Haryana
-Apply by:
-25 Mar 2026
-Part-Time Psychology Intern (Telugu Speaking)
-Nayi Disha
-Location:
-Telangana
-Apply by:
-20 Mar 2026
-Field Mobilizer
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-RFP for Data Collection for Foundational Reading ...
-Lords Education and Health Society (LEHS)
-Location:
-Odisha
-Apply by:
-15 Mar 2026
+30 Mar 2026
+Health Planner – Community Mobilization
+Transform Rural India (TRI)
+Location:
+Maharashtra
+Apply by:
+30 Mar 2026
 Jobseekers
 Register
 Login
@@ -4141,38 +3437,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F19" s="1" t="inlineStr">
+      <c r="F16" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G19" s="1" t="inlineStr">
+      <c r="G16" s="1" t="inlineStr">
         <is>
           <t>16-03-2026</t>
         </is>
       </c>
-      <c r="H19" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="I19" s="1" t="inlineStr">
+      <c r="H16" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I16" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287172</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr"/>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="B17" s="1" t="inlineStr"/>
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>Specialist – Communication</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Financial Management Service Foundation (FMSF) | Uttar Pradesh
 International Development - Specialist – Communication, Financial Management Service Foundation (FMSF), Uttar Pradesh - DevNetJobsIndia.org
@@ -4188,7 +3484,7 @@
 Eve ... Read More</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>• Joining FMSF means becoming part of a passionate team dedicated to making a positive impact. We offer competitive compensation, opportunities for professional development, and a supportive work environment where your contributions are valued and recognized. If you are committed to driving positive change, promoting accountability and strengthening the development sector, we encourage you to apply for the position of Specialist – Communication at FMSF.
 • How to Apply:
@@ -4210,6 +3506,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
 Associate – Finance and Operations
 Financial Management Service Foundation (FMSF)
 Location:
@@ -4222,12 +3524,6 @@
 Maharashtra
 Apply by:
 03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -4272,54 +3568,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Manager - Individual Engagement (Acquisition)
-(Value Members only)
+RFQ-Corporate Global Group Health Insurance Cover...
+Coalition for Disaster Resilient Infrastructure (...
+Location:
+India
+Apply by:
+23 Mar 2026
+HR Associate
+Inclusion Economics India Centre (IEIC) at IFMR
+Location:
+Delhi
+Apply by:
+08 Apr 2026
+Short Term Consultant - Workshop Facilitator for ...
+Fairtrade NAPP
+Location:
+Assam
+Apply by:
+31 Mar 2026
+State Manager
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Uttar Pradesh
+Apply by:
+22 Mar 2026
+State Project Officer
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+India
+Apply by:
+22 Mar 2026
+State Program Manager-HIV-CSC-North East
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Assam
+Apply by:
+22 Mar 2026
+Neighbourhood Facilitator – Health &amp; NCDs
+Transform Rural India (TRI)
 Location:
 Maharashtra
 Apply by:
-10 Mar 2026
-Part Time Accountant
-Sahabhagi Vikash Abhiyan
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Coordinator
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-Consultant Architects
-(Value Members only)
-Location:
-Chhattisgarh
-Apply by:
-18 Mar 2026
-Community Mobilizer
-Common Man Trust
-Location:
-Delhi, Uttar Pradesh, Haryana
-Apply by:
-25 Mar 2026
-Part-Time Psychology Intern (Telugu Speaking)
-Nayi Disha
-Location:
-Telangana
-Apply by:
-20 Mar 2026
-Field Mobilizer
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-RFP for Data Collection for Foundational Reading ...
-Lords Education and Health Society (LEHS)
-Location:
-Odisha
-Apply by:
-15 Mar 2026
+30 Mar 2026
+Health Planner – Community Mobilization
+Transform Rural India (TRI)
+Location:
+Maharashtra
+Apply by:
+30 Mar 2026
 Jobseekers
 Register
 Login
@@ -4347,38 +3643,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F20" s="1" t="inlineStr">
+      <c r="F17" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G20" s="1" t="inlineStr">
+      <c r="G17" s="1" t="inlineStr">
         <is>
           <t>19-03-2026</t>
         </is>
       </c>
-      <c r="H20" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="I20" s="1" t="inlineStr">
+      <c r="H17" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="I17" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287207</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr"/>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="B18" s="1" t="inlineStr"/>
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>RFP - Consultancy for development of descriptive documentation of Ashiyana...</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Prerana | Mumbai, Maharashtra
 International Development - RFP - Consultancy for development of descriptive documentation of Ashiyana Implementation &amp; Practice Framework, and produce a replication-ready, Prerana, Maharashtra - DevNetJobsIndia.org
@@ -4391,7 +3687,7 @@
 Br ... Read More</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>• Submission Details
 Proposals must be submitted by email to:
@@ -4415,6 +3711,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
 Associate – Finance and Operations
 Financial Management Service Foundation (FMSF)
 Location:
@@ -4427,12 +3729,6 @@
 Maharashtra
 Apply by:
 03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -4477,54 +3773,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Manager - Individual Engagement (Acquisition)
-(Value Members only)
+RFQ-Corporate Global Group Health Insurance Cover...
+Coalition for Disaster Resilient Infrastructure (...
+Location:
+India
+Apply by:
+23 Mar 2026
+HR Associate
+Inclusion Economics India Centre (IEIC) at IFMR
+Location:
+Delhi
+Apply by:
+08 Apr 2026
+Short Term Consultant - Workshop Facilitator for ...
+Fairtrade NAPP
+Location:
+Assam
+Apply by:
+31 Mar 2026
+State Manager
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Uttar Pradesh
+Apply by:
+22 Mar 2026
+State Project Officer
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+India
+Apply by:
+22 Mar 2026
+State Program Manager-HIV-CSC-North East
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Assam
+Apply by:
+22 Mar 2026
+Neighbourhood Facilitator – Health &amp; NCDs
+Transform Rural India (TRI)
 Location:
 Maharashtra
 Apply by:
-10 Mar 2026
-Part Time Accountant
-Sahabhagi Vikash Abhiyan
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Coordinator
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-Consultant Architects
-(Value Members only)
-Location:
-Chhattisgarh
-Apply by:
-18 Mar 2026
-Community Mobilizer
-Common Man Trust
-Location:
-Delhi, Uttar Pradesh, Haryana
-Apply by:
-25 Mar 2026
-Part-Time Psychology Intern (Telugu Speaking)
-Nayi Disha
-Location:
-Telangana
-Apply by:
-20 Mar 2026
-Field Mobilizer
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-RFP for Data Collection for Foundational Reading ...
-Lords Education and Health Society (LEHS)
-Location:
-Odisha
-Apply by:
-15 Mar 2026
+30 Mar 2026
+Health Planner – Community Mobilization
+Transform Rural India (TRI)
+Location:
+Maharashtra
+Apply by:
+30 Mar 2026
 Jobseekers
 Register
 Login
@@ -4552,38 +3848,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F21" s="1" t="inlineStr">
+      <c r="F18" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G21" s="1" t="inlineStr">
+      <c r="G18" s="1" t="inlineStr">
         <is>
           <t>21-03-2026</t>
         </is>
       </c>
-      <c r="H21" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="I21" s="1" t="inlineStr">
+      <c r="H18" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="I18" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287890</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr"/>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="B19" s="1" t="inlineStr"/>
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>Specialist - Grants</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Financial Management Service Foundation (FMSF) | Uttar Pradesh
 International Development - Specialist - Grants, Financial Management Service Foundation (FMSF), Uttar Pradesh - DevNetJobsIndia.org
@@ -4600,7 +3896,7 @@
 Job ... Read More</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>• Joining FMSF means becoming part of a passionate team dedicated to making a positive impact. We offer competitive compensation, opportunities for professional development, and a supportive work environment where your contributions are valued and recognized. If you are committed to driving positive change, promoting accountability and strengthening the development sector, we encourage you to apply for the position of Specialist - Grants at FMSF.
 You’re Resume to be accompanied with:
@@ -4622,6 +3918,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
 Associate – Finance and Operations
 Financial Management Service Foundation (FMSF)
 Location:
@@ -4634,12 +3936,6 @@
 Maharashtra
 Apply by:
 03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -4684,54 +3980,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Manager - Individual Engagement (Acquisition)
-(Value Members only)
+RFQ-Corporate Global Group Health Insurance Cover...
+Coalition for Disaster Resilient Infrastructure (...
+Location:
+India
+Apply by:
+23 Mar 2026
+HR Associate
+Inclusion Economics India Centre (IEIC) at IFMR
+Location:
+Delhi
+Apply by:
+08 Apr 2026
+Short Term Consultant - Workshop Facilitator for ...
+Fairtrade NAPP
+Location:
+Assam
+Apply by:
+31 Mar 2026
+State Manager
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Uttar Pradesh
+Apply by:
+22 Mar 2026
+State Project Officer
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+India
+Apply by:
+22 Mar 2026
+State Program Manager-HIV-CSC-North East
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Assam
+Apply by:
+22 Mar 2026
+Neighbourhood Facilitator – Health &amp; NCDs
+Transform Rural India (TRI)
 Location:
 Maharashtra
 Apply by:
-10 Mar 2026
-Part Time Accountant
-Sahabhagi Vikash Abhiyan
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Coordinator
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-Consultant Architects
-(Value Members only)
-Location:
-Chhattisgarh
-Apply by:
-18 Mar 2026
-Community Mobilizer
-Common Man Trust
-Location:
-Delhi, Uttar Pradesh, Haryana
-Apply by:
-25 Mar 2026
-Part-Time Psychology Intern (Telugu Speaking)
-Nayi Disha
-Location:
-Telangana
-Apply by:
-20 Mar 2026
-Field Mobilizer
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-RFP for Data Collection for Foundational Reading ...
-Lords Education and Health Society (LEHS)
-Location:
-Odisha
-Apply by:
-15 Mar 2026
+30 Mar 2026
+Health Planner – Community Mobilization
+Transform Rural India (TRI)
+Location:
+Maharashtra
+Apply by:
+30 Mar 2026
 Jobseekers
 Register
 Login
@@ -4759,77 +4055,122 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F22" s="1" t="inlineStr">
+      <c r="F19" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G22" s="1" t="inlineStr">
+      <c r="G19" s="1" t="inlineStr">
         <is>
           <t>21-03-2026</t>
         </is>
       </c>
-      <c r="H22" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="I22" s="1" t="inlineStr">
+      <c r="H19" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="I19" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287318</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr"/>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>EoI – Mobile Medical Units, Ai-Enabled Tb Screening &amp; Supply Of Medical An...</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Ashray Foundation | Korba, Chattisgarh (Delivery Location), Gujarat
-International Development - EoI – Mobile Medical Units, Ai-Enabled Tb Screening &amp; Supply Of Medical And Nutritional Support, Ashray Foundation, Gujarat - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadc ... Read More</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>• Ashray Foundation invites eligible and experienced agencies to submit their Expression of Interest / for the following scope of work:
-Fabrication of Mobile Medical Units (MMUs) – 2 Units
-AI Integration &amp; Medical Equipment for TB screening (Portable X-ray) – 2 Units
-Supply of Hygiene Kits for TB support treatment on a monthly basis.
-Supply of Nutritional Kits
-Supply of Medicines (on actuals)
-Interested agencies are requested to submit their company profile along with the following mandatory documents such as Registration Certificate of the firm, PAN Card, GST Registration Certificate, Udyam Registration Certificate (if available), Bank details (Cancelled Cheque), Relevant work experience in the above-mentioned areas, supported by photographs.
-For agencies applying for the supply of medicines, hygiene kits, and nutritional kits, submission of valid registration required for medical supply
-and statutory licenses and registration required for medical supply,
-necessary approvals are mandatory. The last date for submission of the company profile and required documents is 24 February 2026.
-All documents should be sent via email to:
-tenders@ashrayfoundation.org
-. Note: Incomplete submissions or unclear copies will lead to rejection.
+      <c r="B20" s="1" t="inlineStr"/>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>RFP - Study On SC-DMPA In Rajasthan- Clients And Providers Perspectives On...</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Centre For Community Economics And Development Consultants Society- CECOEDECON | Jaipur, Rajasthan
+International Development - RFP - Study On SC-DMPA In Rajasthan- Clients And Providers Perspectives On SC-DMPA In Rajasthan, Centre For Community Economics And Development Consultants Society- CECOEDE ... Read More</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>• Despite India’s achievement of replacement-level fertility, unmet need for contraception—particularly for spacing methods—remains substantial, with modern contraceptive use at 56.4% (2019–21), highlighting persistent gaps in access and choice, especially among vulnerable populations. Expanding the contraceptive method mix through innovative, user-centred approaches is therefore essential to meeting national commitments under FP2030 and the Sustainable Development Goals. In this context, the Government of India’s introduction of subcutaneous DMPA (DMPA-SC) as a self-care option under the National Family Planning Programme in 2023 represents a strategic step toward enhancing women’s autonomy, privacy, and convenience in contraceptive use. Global and national evidence indicates strong feasibility and acceptability of self-administered DMPA-SC among both users and providers; however, successful implementation requires an in-depth understanding of user experiences and health system readiness. This study, to be conducted in Jaipur-1, Jaisalmer and Sawai Madhopur districts of Rajasthan, aims to examine the perspectives &amp; experience of current SC-DMPA users and explore healthcare providers’ views on enabling and generating actionable evidence to inform effective scale-up of SC-DMPA within India’s public health system.
+CECOEDECON, with support from UNFPA, is implementing the roll-out of subcutaneous DMPA (SC-DMPA) in selected pilot districts of Rajasthan in the public health facilities, in collaboration with the Department of Health &amp; Family Welfare, Government of Rajasthan.
+The selected agency will be required to:
+To assess the experiences and perspectives of SC-DMPA users with a focus on service delivery, follow-up mechanisms, continuation, and future contraceptive intentions related to self-administration.
+To examine the perspectives of healthcare providers (including doctors, nurses, and Community Health Officers trained in the study districts) on client acceptance, readiness, and support requirements for SC-DMPA self-administration. (Total more than 250 doctors and 951 nursing staff and CHOs trained in these districts)
+To identify key barriers and facilitating factors at both client and health-system levels influencing the acceptance, effective use, scalability and Future ready system for scalability of SC-DMPA
+• 2. Scope of Work:
+The agency will be responsible for:
+Finalizing study design and methodology in consultation with stakeholders.
+Developing and pre-testing quantitative and qualitative study tools.
+Securing ethical clearance from a recognized Institutional Review Board (IRB).
+Conducting data collection, including:
+Quantitative interviews with a representative sample of SC-DMPA users
+In-depth interviews with doctors, ANMs.
+Data management, including data entry, cleaning, and analysis.
+Preparation and submission of study reports.
+3. Methodology:
+This study will employ quantitative research techniques on a sample of users of SC-DMPA and qualitative techniques of in-depth interviews with the service providers. A representative sample will be drawn from the list of users of SC-DMPA from the three districts. The health care providers will include Doctors, nurses, Auxiliary Nurse Midwives (ANMs), Nurses and CHOs (Total more than 250 doctors and 951 nursing staff and CHOs trained in these districts)
+Sampling: Probability proportional to size sampling will be adopted using the number of SC-DMPA users in Jaisalmer, Sawai Madhupur and Jaipur-1, as size measure (from approx. 15000 users)
+Quantitative data: Interviews with selected SC-DMPA users.
+Qualitative data: In-depth interviews with healthcare providers.
+4. Deliverables:
+Inception report with finalized study design and tools.
+IRB approval.
+Clean dataset (quantitative and qualitative).
+Analytical reports (interim and final).
+Policy brief with actionable recommendations.
+5. Timeline:
+The assignment is expected to be completed within 5 months following contract signing, as per the following tentative schedule:
+Finalization of study design and tool development: March-
+April 2026
+Ethical clearance: May 2026
+Training of investigators – June 2026
+Data collection: July 2026
+Data analysis and reporting: Mid Aug 2026
+6. Required Qualifications of the Agency:
+Proven experience in conducting large-scale health and family planning research studies.
+Expertise in both quantitative and qualitative research methods.
+Familiarity with contraceptive technology, self-care interventions, and public health systems.
+Experience in working with government health systems and familiarity with Rajasthan’s context will be preferred.
+Demonstrated capacity to ensure ethical compliance and data confidentiality.
+Availability of qualified and experienced research team.
+• 7. Proposal Submission Requirements:
+Interested agencies should submit:
+• Organizational profile with relevant experience.
+Detailed technical proposal maximum of 5 pages outlining understanding of the assignment, methodology, sampling approach, data collection plan, team composition, quality assurance, and ethical considerations.
+Financial proposal (separately in INR).
+https://docs.google.com/spreadsheets/d/1Yqiy8FXJeOrAIv_vXiA_whsUG59WtuvY/edit?usp=sharing&amp;ouid=107933350131648505243&amp;rtpof=true&amp;sd=true
+(Please Download Financial proposal format.)
+Timeline for deliverables.
+CVs of key team members.
+• 8. Evaluation Criteria:
+Proposals will be evaluated based on:
+Technical expertise and relevance of prior experience.
+Soundness of proposed methodology and work plan.
+Qualifications of proposed team.
+Financial competitiveness.
+9.  Contact Information:
+In case of any doubt or query the agency can send mail to cecojobs@gmail.com within 7 days of advertisement of the RFP.
 • Job Email ID:
-tenders(at)ashrayfoundation.org
+cecojobs(at)gmail.com
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
 Apply by:
-24 Mar 2026
+22 Mar 2026
 Access all the jobs and get ahead!
 Subscribe to Value Membership Now!
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
 Associate – Finance and Operations
 Financial Management Service Foundation (FMSF)
 Location:
@@ -4842,12 +4183,6 @@
 Maharashtra
 Apply by:
 03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -4892,54 +4227,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Manager - Individual Engagement (Acquisition)
-(Value Members only)
+RFQ-Corporate Global Group Health Insurance Cover...
+Coalition for Disaster Resilient Infrastructure (...
+Location:
+India
+Apply by:
+23 Mar 2026
+HR Associate
+Inclusion Economics India Centre (IEIC) at IFMR
+Location:
+Delhi
+Apply by:
+08 Apr 2026
+Short Term Consultant - Workshop Facilitator for ...
+Fairtrade NAPP
+Location:
+Assam
+Apply by:
+31 Mar 2026
+State Manager
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Uttar Pradesh
+Apply by:
+22 Mar 2026
+State Project Officer
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+India
+Apply by:
+22 Mar 2026
+State Program Manager-HIV-CSC-North East
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Assam
+Apply by:
+22 Mar 2026
+Neighbourhood Facilitator – Health &amp; NCDs
+Transform Rural India (TRI)
 Location:
 Maharashtra
 Apply by:
-10 Mar 2026
-Part Time Accountant
-Sahabhagi Vikash Abhiyan
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Coordinator
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-Consultant Architects
-(Value Members only)
-Location:
-Chhattisgarh
-Apply by:
-18 Mar 2026
-Community Mobilizer
-Common Man Trust
-Location:
-Delhi, Uttar Pradesh, Haryana
-Apply by:
-25 Mar 2026
-Part-Time Psychology Intern (Telugu Speaking)
-Nayi Disha
-Location:
-Telangana
-Apply by:
-20 Mar 2026
-Field Mobilizer
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-RFP for Data Collection for Foundational Reading ...
-Lords Education and Health Society (LEHS)
-Location:
-Odisha
-Apply by:
-15 Mar 2026
+30 Mar 2026
+Health Planner – Community Mobilization
+Transform Rural India (TRI)
+Location:
+Maharashtra
+Apply by:
+30 Mar 2026
 Jobseekers
 Register
 Login
@@ -4967,38 +4302,524 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F23" s="1" t="inlineStr">
+      <c r="F20" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G23" s="1" t="inlineStr">
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t>22-03-2026</t>
+        </is>
+      </c>
+      <c r="H20" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287322</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr"/>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>RFQ-Corporate Global Group Health Insurance Coverage</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Coalition for Disaster Resilient Infrastructure (CDRI) | India
+International Development - RFQ-Corporate Global Group Health Insurance Coverage, Coalition for Disaster Resilient Infrastructure (CDRI), India - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RF ... Read More</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>• The specific staff details, policy document, along with the claim MIS will only be shared with the interested bidders upon request to the email ID
+:
+tender.projects@cdri.world
+Scope of Services:
+Corporate Global Group Health Insurance
+The insurance provider should provide a
+Corporate Global Health Insurance
+Cover Including but not limited to the following scope (
+Offerors can also include additional benefits
+):
+Estimated group size in the contract period:
+~60
+(Self, Spouse, and Child(ren)
+.
+The staff to be covered under the Global Health Scheme.
+Policy Type
+-
+Global
+Health Insurance with
+worldwide coverage Including USA &amp; Canada
+.
+Age Band-1 day - 90 yrs (Adult 18-90 years and Dependent Child 01 Day-21 Years).
+Sum Insured-
+Family floater Sum Insured equivalent to
+USD 2,50,000 per family
+during the policy period.
+Family Definition
+- Employee + Spouse/partner + Child(ren),
+No capping on children
+. The partner can be of same or other gender.
+OPD Cover-
+OPD cover of equivalent to
+USD 500 per family
+during the policy period.
+Maternity Benefits-
+Natural Birth, C-section and prenatal check-ups, Wellness baby, waiver of the waiting period of nine months for all new entrants.
+In-Patient Benefits
+-Inpatient hospitalization due to injury, illness, Psychiatric Illness and planned surgeries should be covered. Robotic, modern treatments, laser treatments due to injury, illness, or psychiatric illness should be covered up to full entitlement.
+OPD covers should include
+-
+Consultation &amp; Prescribed Drugs and Dressing, Physiotherapy, Psychotherapy counselling, Dental Treatment: Routine Dental Treatment, surgery, cleaning, capping, RTC, Eye treatment: Eye check-up, Power Glasses with frame, Eye surgery, Cataract.
+Annual Deductible &amp; Co-pay on claims-Not Applicable, No Disease-wise sublimit.
+Repatriation of mortal remains cost covered in case of death due to illness, accident or injury.
+Health cover from day one of the policy to all the insured family members.
+Coverage of pre-existing diseases from day one for all staff (existing members and new joiners).
+No waiting period of 30 days should be applied for existing and new joiners.
+First, second, third, and fourth-year exclusion conditions for specific diseases should be waived.
+Pre &amp; and post-hospitalization should be covered for a minimum of 30 days and 60 days, respectively.
+Cashless hospitalization at network hospitals globally.
+Terrorism risk coverage from inception day.
+Coverage of Ambulance charges, Domiciliary Hospitalization.
+All additions and deletions of members shall be done on a pro-rata basis from the respective DOJ/DOL. Midterm Addition / Deletion of Dependents in the event of marriage, divorce, birth, &amp; Death.
+• Terms and Conditions of Proposal(s):
+Proposals must be valid through the effective date of the contract.
+Proposals must indicate any exceptions or deviations from the RFQ Terms of Reference (ToR).
+Any amendments to the terms of reference will be made in writing and agreed upon by both parties.
+The policy period will be from
+09 April 2026 till 08April 2027
+.
+CDRI is under no obligation to award this contract to the offeror offering the lowest rates. Contract awards will be based on price, service reputation, financial stability, and claim turnaround ratio vs the actual settlement. Only proposals that meet all technical and service requirements outlined in this RFQ will be considered for financial evaluation
+CDRI will follow the
+Single-Stage: One-Envelope Bidding Procedure
+to select the agency. The contract is awarded to the bidder whose bid has been determined to be the
+lowest evaluated substantially responsive bid
+.
+CDRI, at its own discretion, can reach out to shortlisted agencies for Best and Final Offer (BAFO).
+Submission of Proposal:
+Interested vendors are requested to submit their proposal in a
+PASSWORD-PROTECTED
+PDF file
+through email to
+tender.projects@cdri.world
+by 23:59 hrs (IST) on 23 March 2026
+.
+Financial Proposal for Global Group Health Insurance:
+Vendors to quote premiums per family unit (floater)
+Include OPD riders and applicable GST clearly
+The proposal should specify the applicable premium structure, relevant taxes, and any add-on or optional coverage separately.
+Note: The PDF must be password-protected. Under no circumstances should the password be shared at the time of submission. It will be requested separately after the RFQ submission deadline has passed.
+Please ensure that your proposal is sent ONLY to the ABOVE-MENTIONED email ID before the closing date &amp; time. Proposals sent/copied to any other email ID (other than above) OR received after the bid closing date &amp; time (mentioned above) will not be entertained.
+• Job Email ID:
+tender.projects(at)cdri.world
+Download Attachment:
+RFQ_Global Group Health Insurance_CDRI_2026-27.pdf
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+23 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+RFQ-Corporate Global Group Health Insurance Cover...
+Coalition for Disaster Resilient Infrastructure (...
+Location:
+India
+Apply by:
+23 Mar 2026
+HR Associate
+Inclusion Economics India Centre (IEIC) at IFMR
+Location:
+Delhi
+Apply by:
+08 Apr 2026
+Short Term Consultant - Workshop Facilitator for ...
+Fairtrade NAPP
+Location:
+Assam
+Apply by:
+31 Mar 2026
+State Manager
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Uttar Pradesh
+Apply by:
+22 Mar 2026
+State Project Officer
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+India
+Apply by:
+22 Mar 2026
+State Program Manager-HIV-CSC-North East
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Assam
+Apply by:
+22 Mar 2026
+Neighbourhood Facilitator – Health &amp; NCDs
+Transform Rural India (TRI)
+Location:
+Maharashtra
+Apply by:
+30 Mar 2026
+Health Planner – Community Mobilization
+Transform Rural India (TRI)
+Location:
+Maharashtra
+Apply by:
+30 Mar 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F21" s="1" t="inlineStr">
+        <is>
+          <t>Climate, Safety</t>
+        </is>
+      </c>
+      <c r="G21" s="1" t="inlineStr">
+        <is>
+          <t>23-03-2026</t>
+        </is>
+      </c>
+      <c r="H21" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="I21" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=288006</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr"/>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>EoI – Mobile Medical Units, Ai-Enabled Tb Screening &amp; Supply Of Medical An...</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Ashray Foundation | Korba, Chattisgarh (Delivery Location), Gujarat
+International Development - EoI – Mobile Medical Units, Ai-Enabled Tb Screening &amp; Supply Of Medical And Nutritional Support, Ashray Foundation, Gujarat - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadc ... Read More</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>• Ashray Foundation invites eligible and experienced agencies to submit their Expression of Interest / for the following scope of work:
+Fabrication of Mobile Medical Units (MMUs) – 2 Units
+AI Integration &amp; Medical Equipment for TB screening (Portable X-ray) – 2 Units
+Supply of Hygiene Kits for TB support treatment on a monthly basis.
+Supply of Nutritional Kits
+Supply of Medicines (on actuals)
+Interested agencies are requested to submit their company profile along with the following mandatory documents such as Registration Certificate of the firm, PAN Card, GST Registration Certificate, Udyam Registration Certificate (if available), Bank details (Cancelled Cheque), Relevant work experience in the above-mentioned areas, supported by photographs.
+For agencies applying for the supply of medicines, hygiene kits, and nutritional kits, submission of valid registration required for medical supply
+and statutory licenses and registration required for medical supply,
+necessary approvals are mandatory. The last date for submission of the company profile and required documents is 24 February 2026.
+All documents should be sent via email to:
+tenders@ashrayfoundation.org
+. Note: Incomplete submissions or unclear copies will lead to rejection.
+• Job Email ID:
+tenders(at)ashrayfoundation.org
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+24 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+RFQ-Corporate Global Group Health Insurance Cover...
+Coalition for Disaster Resilient Infrastructure (...
+Location:
+India
+Apply by:
+23 Mar 2026
+HR Associate
+Inclusion Economics India Centre (IEIC) at IFMR
+Location:
+Delhi
+Apply by:
+08 Apr 2026
+Short Term Consultant - Workshop Facilitator for ...
+Fairtrade NAPP
+Location:
+Assam
+Apply by:
+31 Mar 2026
+State Manager
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Uttar Pradesh
+Apply by:
+22 Mar 2026
+State Project Officer
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+India
+Apply by:
+22 Mar 2026
+State Program Manager-HIV-CSC-North East
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Assam
+Apply by:
+22 Mar 2026
+Neighbourhood Facilitator – Health &amp; NCDs
+Transform Rural India (TRI)
+Location:
+Maharashtra
+Apply by:
+30 Mar 2026
+Health Planner – Community Mobilization
+Transform Rural India (TRI)
+Location:
+Maharashtra
+Apply by:
+30 Mar 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F22" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G22" s="1" t="inlineStr">
         <is>
           <t>24-03-2026</t>
         </is>
       </c>
-      <c r="H23" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="I23" s="1" t="inlineStr">
+      <c r="H22" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="I22" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287319</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr"/>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="B23" s="1" t="inlineStr"/>
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>RFP - End of Program Evaluation Accelerating Access to Safe Water and San...</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Water.org | Bangladesh, Cambodia, India
 International Development - RFP - End of Program Evaluation  Accelerating Access to Safe Water and Sanitation, Financing, Water.org, India - DevNetJobsIndia.org
@@ -5014,7 +4835,7 @@
 Event ... Read More</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>• The evaluation will require the firm to facilitate and coordinate with Water.org staff and partners. The program requires the firm to submit the deliverables outlined in section 2 Scope of Work.
 C.
@@ -5059,6 +4880,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
 Associate – Finance and Operations
 Financial Management Service Foundation (FMSF)
 Location:
@@ -5071,12 +4898,6 @@
 Maharashtra
 Apply by:
 03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -5121,54 +4942,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Manager - Individual Engagement (Acquisition)
-(Value Members only)
+RFQ-Corporate Global Group Health Insurance Cover...
+Coalition for Disaster Resilient Infrastructure (...
+Location:
+India
+Apply by:
+23 Mar 2026
+HR Associate
+Inclusion Economics India Centre (IEIC) at IFMR
+Location:
+Delhi
+Apply by:
+08 Apr 2026
+Short Term Consultant - Workshop Facilitator for ...
+Fairtrade NAPP
+Location:
+Assam
+Apply by:
+31 Mar 2026
+State Manager
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Uttar Pradesh
+Apply by:
+22 Mar 2026
+State Project Officer
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+India
+Apply by:
+22 Mar 2026
+State Program Manager-HIV-CSC-North East
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Assam
+Apply by:
+22 Mar 2026
+Neighbourhood Facilitator – Health &amp; NCDs
+Transform Rural India (TRI)
 Location:
 Maharashtra
 Apply by:
-10 Mar 2026
-Part Time Accountant
-Sahabhagi Vikash Abhiyan
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Coordinator
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-Consultant Architects
-(Value Members only)
-Location:
-Chhattisgarh
-Apply by:
-18 Mar 2026
-Community Mobilizer
-Common Man Trust
-Location:
-Delhi, Uttar Pradesh, Haryana
-Apply by:
-25 Mar 2026
-Part-Time Psychology Intern (Telugu Speaking)
-Nayi Disha
-Location:
-Telangana
-Apply by:
-20 Mar 2026
-Field Mobilizer
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-RFP for Data Collection for Foundational Reading ...
-Lords Education and Health Society (LEHS)
-Location:
-Odisha
-Apply by:
-15 Mar 2026
+30 Mar 2026
+Health Planner – Community Mobilization
+Transform Rural India (TRI)
+Location:
+Maharashtra
+Apply by:
+30 Mar 2026
 Jobseekers
 Register
 Login
@@ -5196,38 +5017,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F24" s="1" t="inlineStr">
+      <c r="F23" s="1" t="inlineStr">
         <is>
           <t>Governance, Safety</t>
         </is>
       </c>
-      <c r="G24" s="1" t="inlineStr">
+      <c r="G23" s="1" t="inlineStr">
         <is>
           <t>25-03-2026</t>
         </is>
       </c>
-      <c r="H24" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="I24" s="1" t="inlineStr">
+      <c r="H23" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="I23" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287835</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr"/>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="B24" s="1" t="inlineStr"/>
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>Agriculture Research Development Officer / Projec...</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Starshield Security Solution Pvt.Ltd | Uttar Pradesh
 International Development - Agriculture Research Development Officer / Project Scientist III, Starshield Security Solution Pvt.Ltd, Uttar Pradesh - DevNetJobsIndia.org
@@ -5241,7 +5062,7 @@
 RFPs/Tende ... Read More</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>• Eligibility Criteria
 Qualification:
@@ -5288,6 +5109,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
 Associate – Finance and Operations
 Financial Management Service Foundation (FMSF)
 Location:
@@ -5300,12 +5127,6 @@
 Maharashtra
 Apply by:
 03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -5350,54 +5171,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Manager - Individual Engagement (Acquisition)
-(Value Members only)
+RFQ-Corporate Global Group Health Insurance Cover...
+Coalition for Disaster Resilient Infrastructure (...
+Location:
+India
+Apply by:
+23 Mar 2026
+HR Associate
+Inclusion Economics India Centre (IEIC) at IFMR
+Location:
+Delhi
+Apply by:
+08 Apr 2026
+Short Term Consultant - Workshop Facilitator for ...
+Fairtrade NAPP
+Location:
+Assam
+Apply by:
+31 Mar 2026
+State Manager
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Uttar Pradesh
+Apply by:
+22 Mar 2026
+State Project Officer
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+India
+Apply by:
+22 Mar 2026
+State Program Manager-HIV-CSC-North East
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Assam
+Apply by:
+22 Mar 2026
+Neighbourhood Facilitator – Health &amp; NCDs
+Transform Rural India (TRI)
 Location:
 Maharashtra
 Apply by:
-10 Mar 2026
-Part Time Accountant
-Sahabhagi Vikash Abhiyan
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Coordinator
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-Consultant Architects
-(Value Members only)
-Location:
-Chhattisgarh
-Apply by:
-18 Mar 2026
-Community Mobilizer
-Common Man Trust
-Location:
-Delhi, Uttar Pradesh, Haryana
-Apply by:
-25 Mar 2026
-Part-Time Psychology Intern (Telugu Speaking)
-Nayi Disha
-Location:
-Telangana
-Apply by:
-20 Mar 2026
-Field Mobilizer
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-RFP for Data Collection for Foundational Reading ...
-Lords Education and Health Society (LEHS)
-Location:
-Odisha
-Apply by:
-15 Mar 2026
+30 Mar 2026
+Health Planner – Community Mobilization
+Transform Rural India (TRI)
+Location:
+Maharashtra
+Apply by:
+30 Mar 2026
 Jobseekers
 Register
 Login
@@ -5425,38 +5246,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F25" s="1" t="inlineStr">
+      <c r="F24" s="1" t="inlineStr">
         <is>
           <t>Learning, Safety</t>
         </is>
       </c>
-      <c r="G25" s="1" t="inlineStr">
+      <c r="G24" s="1" t="inlineStr">
         <is>
           <t>30-03-2026</t>
         </is>
       </c>
-      <c r="H25" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="I25" s="1" t="inlineStr">
+      <c r="H24" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="I24" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287636</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr"/>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="B25" s="1" t="inlineStr"/>
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>Junior Research Technicians / Senior Project Asso...</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Starshield Security Solution Pvt.Ltd | Uttar Pradesh
 International Development - Junior Research Technicians / Senior Project Associate, Starshield Security Solution Pvt.Ltd, Uttar Pradesh - DevNetJobsIndia.org
@@ -5471,7 +5292,7 @@
 Search ... Read More</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>• Eligibility Criteria
 Qualification
@@ -5517,6 +5338,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
 Associate – Finance and Operations
 Financial Management Service Foundation (FMSF)
 Location:
@@ -5529,12 +5356,6 @@
 Maharashtra
 Apply by:
 03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -5579,54 +5400,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Manager - Individual Engagement (Acquisition)
-(Value Members only)
+RFQ-Corporate Global Group Health Insurance Cover...
+Coalition for Disaster Resilient Infrastructure (...
+Location:
+India
+Apply by:
+23 Mar 2026
+HR Associate
+Inclusion Economics India Centre (IEIC) at IFMR
+Location:
+Delhi
+Apply by:
+08 Apr 2026
+Short Term Consultant - Workshop Facilitator for ...
+Fairtrade NAPP
+Location:
+Assam
+Apply by:
+31 Mar 2026
+State Manager
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Uttar Pradesh
+Apply by:
+22 Mar 2026
+State Project Officer
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+India
+Apply by:
+22 Mar 2026
+State Program Manager-HIV-CSC-North East
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Assam
+Apply by:
+22 Mar 2026
+Neighbourhood Facilitator – Health &amp; NCDs
+Transform Rural India (TRI)
 Location:
 Maharashtra
 Apply by:
-10 Mar 2026
-Part Time Accountant
-Sahabhagi Vikash Abhiyan
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Coordinator
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-Consultant Architects
-(Value Members only)
-Location:
-Chhattisgarh
-Apply by:
-18 Mar 2026
-Community Mobilizer
-Common Man Trust
-Location:
-Delhi, Uttar Pradesh, Haryana
-Apply by:
-25 Mar 2026
-Part-Time Psychology Intern (Telugu Speaking)
-Nayi Disha
-Location:
-Telangana
-Apply by:
-20 Mar 2026
-Field Mobilizer
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-RFP for Data Collection for Foundational Reading ...
-Lords Education and Health Society (LEHS)
-Location:
-Odisha
-Apply by:
-15 Mar 2026
+30 Mar 2026
+Health Planner – Community Mobilization
+Transform Rural India (TRI)
+Location:
+Maharashtra
+Apply by:
+30 Mar 2026
 Jobseekers
 Register
 Login
@@ -5654,38 +5475,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F26" s="1" t="inlineStr">
+      <c r="F25" s="1" t="inlineStr">
         <is>
           <t>Safety</t>
         </is>
       </c>
-      <c r="G26" s="1" t="inlineStr">
+      <c r="G25" s="1" t="inlineStr">
         <is>
           <t>30-03-2026</t>
         </is>
       </c>
-      <c r="H26" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="I26" s="1" t="inlineStr">
+      <c r="H25" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="I25" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287635</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr"/>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="B26" s="1" t="inlineStr"/>
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>Sector Experts</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Academy of Management Studies (AMS) | India
 International Development - Sector Experts, Academy of Management Studies (AMS), India - DevNetJobsIndia.org
@@ -5706,7 +5527,7 @@
 Jobseekers Login ... Read More</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>• Eligibility
 Postgraduate degree / Ph.D. in relevant or allied disciplines
@@ -5740,6 +5561,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
 Associate – Finance and Operations
 Financial Management Service Foundation (FMSF)
 Location:
@@ -5752,12 +5579,6 @@
 Maharashtra
 Apply by:
 03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -5802,54 +5623,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Manager - Individual Engagement (Acquisition)
-(Value Members only)
+RFQ-Corporate Global Group Health Insurance Cover...
+Coalition for Disaster Resilient Infrastructure (...
+Location:
+India
+Apply by:
+23 Mar 2026
+HR Associate
+Inclusion Economics India Centre (IEIC) at IFMR
+Location:
+Delhi
+Apply by:
+08 Apr 2026
+Short Term Consultant - Workshop Facilitator for ...
+Fairtrade NAPP
+Location:
+Assam
+Apply by:
+31 Mar 2026
+State Manager
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Uttar Pradesh
+Apply by:
+22 Mar 2026
+State Project Officer
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+India
+Apply by:
+22 Mar 2026
+State Program Manager-HIV-CSC-North East
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Assam
+Apply by:
+22 Mar 2026
+Neighbourhood Facilitator – Health &amp; NCDs
+Transform Rural India (TRI)
 Location:
 Maharashtra
 Apply by:
-10 Mar 2026
-Part Time Accountant
-Sahabhagi Vikash Abhiyan
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Coordinator
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-Consultant Architects
-(Value Members only)
-Location:
-Chhattisgarh
-Apply by:
-18 Mar 2026
-Community Mobilizer
-Common Man Trust
-Location:
-Delhi, Uttar Pradesh, Haryana
-Apply by:
-25 Mar 2026
-Part-Time Psychology Intern (Telugu Speaking)
-Nayi Disha
-Location:
-Telangana
-Apply by:
-20 Mar 2026
-Field Mobilizer
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-RFP for Data Collection for Foundational Reading ...
-Lords Education and Health Society (LEHS)
-Location:
-Odisha
-Apply by:
-15 Mar 2026
+30 Mar 2026
+Health Planner – Community Mobilization
+Transform Rural India (TRI)
+Location:
+Maharashtra
+Apply by:
+30 Mar 2026
 Jobseekers
 Register
 Login
@@ -5877,38 +5698,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F27" s="1" t="inlineStr">
+      <c r="F26" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G27" s="1" t="inlineStr">
+      <c r="G26" s="1" t="inlineStr">
         <is>
           <t>31-03-2026</t>
         </is>
       </c>
-      <c r="H27" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="I27" s="1" t="inlineStr">
+      <c r="H26" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="I26" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287726</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr"/>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="B27" s="1" t="inlineStr"/>
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>Associate – Finance and Operations</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Financial Management Service Foundation (FMSF) | Uttar Pradesh
 International Development - Associate – Finance and Operations, Financial Management Service Foundation (FMSF), Uttar Pradesh - DevNetJobsIndia.org
@@ -5923,7 +5744,7 @@
 Search ... Read More</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>• Joining FMSF means becoming part of a passionate team dedicated to making a positive impact. We offer competitive compensation, opportunities for professional development, and a supportive work environment where your contributions are valued and recognized. If you are committed to driving positive change, promoting accountability and strengthening the development sector, we encourage you to apply for the position of
 Associate – Finance and Operations
@@ -5945,6 +5766,12 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
 Associate – Finance and Operations
 Financial Management Service Foundation (FMSF)
 Location:
@@ -5957,12 +5784,6 @@
 Maharashtra
 Apply by:
 03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -6007,54 +5828,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Manager - Individual Engagement (Acquisition)
-(Value Members only)
+RFQ-Corporate Global Group Health Insurance Cover...
+Coalition for Disaster Resilient Infrastructure (...
+Location:
+India
+Apply by:
+23 Mar 2026
+HR Associate
+Inclusion Economics India Centre (IEIC) at IFMR
+Location:
+Delhi
+Apply by:
+08 Apr 2026
+Short Term Consultant - Workshop Facilitator for ...
+Fairtrade NAPP
+Location:
+Assam
+Apply by:
+31 Mar 2026
+State Manager
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Uttar Pradesh
+Apply by:
+22 Mar 2026
+State Project Officer
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+India
+Apply by:
+22 Mar 2026
+State Program Manager-HIV-CSC-North East
+Hindustan Latex Family Planning Promotion Trust (...
+Location:
+Assam
+Apply by:
+22 Mar 2026
+Neighbourhood Facilitator – Health &amp; NCDs
+Transform Rural India (TRI)
 Location:
 Maharashtra
 Apply by:
-10 Mar 2026
-Part Time Accountant
-Sahabhagi Vikash Abhiyan
-Location:
-Odisha
-Apply by:
-15 Mar 2026
-Project Coordinator
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-Consultant Architects
-(Value Members only)
-Location:
-Chhattisgarh
-Apply by:
-18 Mar 2026
-Community Mobilizer
-Common Man Trust
-Location:
-Delhi, Uttar Pradesh, Haryana
-Apply by:
-25 Mar 2026
-Part-Time Psychology Intern (Telugu Speaking)
-Nayi Disha
-Location:
-Telangana
-Apply by:
-20 Mar 2026
-Field Mobilizer
-Hanuman Prasad Gramin Vikas Seva Samiti
-Location:
-Bihar
-Apply by:
-15 Mar 2026
-RFP for Data Collection for Foundational Reading ...
-Lords Education and Health Society (LEHS)
-Location:
-Odisha
-Apply by:
-15 Mar 2026
+30 Mar 2026
+Health Planner – Community Mobilization
+Transform Rural India (TRI)
+Location:
+Maharashtra
+Apply by:
+30 Mar 2026
 Jobseekers
 Register
 Login
@@ -6082,22 +5903,49 @@
 Recruitment Exchange</t>
         </is>
       </c>
+      <c r="F27" s="1" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G27" s="1" t="inlineStr">
+        <is>
+          <t>05-04-2026</t>
+        </is>
+      </c>
+      <c r="H27" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="I27" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287913</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr"/>
+      <c r="C28" s="1" t="inlineStr">
+        <is>
+          <t>RFP for Endline Evaluation Study - HSBC GCC Women Entrepreneurship Program - Click here</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G28" s="1" t="inlineStr">
-        <is>
-          <t>05-04-2026</t>
-        </is>
-      </c>
-      <c r="H28" s="1" t="n">
-        <v>28</v>
-      </c>
+      <c r="G28" s="1" t="inlineStr"/>
+      <c r="H28" s="1" t="inlineStr"/>
       <c r="I28" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287913</t>
+          <t>https://www.nasscomfoundation.org/pdf/endline-evaluation-study-hsbc-gcc-women-entrepreneurship-program.pdf</t>
         </is>
       </c>
     </row>
@@ -6110,21 +5958,21 @@
       <c r="B29" s="1" t="inlineStr"/>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>RFP for Endline Evaluation Study - HSBC GCC Women Entrepreneurship Program - Click here</t>
+          <t>Travel &amp; Transportation Services for Trainer Mobility - IBM SkillBuild Bootcamps - Click here</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G29" s="1" t="inlineStr"/>
       <c r="H29" s="1" t="inlineStr"/>
       <c r="I29" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/endline-evaluation-study-hsbc-gcc-women-entrepreneurship-program.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/travel-and-transportation-services-for-trainer-mobility-ibm-skillbuild-bootcamps.pdf</t>
         </is>
       </c>
     </row>
@@ -6137,21 +5985,21 @@
       <c r="B30" s="1" t="inlineStr"/>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>Travel &amp; Transportation Services for Trainer Mobility - IBM SkillBuild Bootcamps - Click here</t>
+          <t>Baseline and End-line Evaluation of the HSBC Neurodivergent Digital Annotator Skilling Program - Click here | Click here</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G30" s="1" t="inlineStr"/>
       <c r="H30" s="1" t="inlineStr"/>
       <c r="I30" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/travel-and-transportation-services-for-trainer-mobility-ibm-skillbuild-bootcamps.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/baseline-and-end-line-evaluation-of-hsbc-neurodivergent-digital-annotator-skilling-program.pdf</t>
         </is>
       </c>
     </row>
@@ -6164,21 +6012,21 @@
       <c r="B31" s="1" t="inlineStr"/>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>Baseline and End-line Evaluation of the HSBC Neurodivergent Digital Annotator Skilling Program - Click here | Click here</t>
+          <t>RFP for Catering Vendor - IBM Skillbuild Bootcamps - Click here</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G31" s="1" t="inlineStr"/>
       <c r="H31" s="1" t="inlineStr"/>
       <c r="I31" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/baseline-and-end-line-evaluation-of-hsbc-neurodivergent-digital-annotator-skilling-program.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/rfp-for-catering-vendor-ibm-skillbuild-bootcamps.pdf</t>
         </is>
       </c>
     </row>
@@ -6191,21 +6039,21 @@
       <c r="B32" s="1" t="inlineStr"/>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>RFP for Catering Vendor - IBM Skillbuild Bootcamps - Click here</t>
+          <t>Organization-wide Management Information System (MIS) for Nasscom Foundation - Click here</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G32" s="1" t="inlineStr"/>
       <c r="H32" s="1" t="inlineStr"/>
       <c r="I32" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/rfp-for-catering-vendor-ibm-skillbuild-bootcamps.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/organization-wide-management-information-system-for-nasscom-foundation.pdf</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6066,7 @@
       <c r="B33" s="1" t="inlineStr"/>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>Organization-wide Management Information System (MIS) for Nasscom Foundation - Click here</t>
+          <t>Request for Proposal (RFP) for Social Media Management Services - Click here</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr"/>
@@ -6232,7 +6080,7 @@
       <c r="H33" s="1" t="inlineStr"/>
       <c r="I33" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/organization-wide-management-information-system-for-nasscom-foundation.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/request-for-proposal-for-social-media-management-services.pdf</t>
         </is>
       </c>
     </row>
@@ -6245,7 +6093,7 @@
       <c r="B34" s="1" t="inlineStr"/>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>Request for Proposal (RFP) for Social Media Management Services - Click here</t>
+          <t>RFP - TechForSociety - Evaluation Study - Click here</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr"/>
@@ -6259,7 +6107,7 @@
       <c r="H34" s="1" t="inlineStr"/>
       <c r="I34" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/request-for-proposal-for-social-media-management-services.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/techforsociety-evaluation-study.pdf</t>
         </is>
       </c>
     </row>
@@ -6272,7 +6120,7 @@
       <c r="B35" s="1" t="inlineStr"/>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>RFP - TechForSociety - Evaluation Study - Click here</t>
+          <t>Base-line and End-line evaluation for Digital Literacy Project in 4 States - Click here</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr"/>
@@ -6286,7 +6134,7 @@
       <c r="H35" s="1" t="inlineStr"/>
       <c r="I35" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/techforsociety-evaluation-study.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/base-line-and-end-line-evaluation-for-digital-literacy-project-in-4-states.pdf</t>
         </is>
       </c>
     </row>
@@ -6299,21 +6147,21 @@
       <c r="B36" s="1" t="inlineStr"/>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>Base-line and End-line evaluation for Digital Literacy Project in 4 States - Click here</t>
+          <t>IP Selection - Scholarship Support to students from Economically Weaker Section pursuing higher education in STEM courses - Click here</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G36" s="1" t="inlineStr"/>
       <c r="H36" s="1" t="inlineStr"/>
       <c r="I36" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/base-line-and-end-line-evaluation-for-digital-literacy-project-in-4-states.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/scholarship-support-for-economically-weaker-section-students-in-stem-higher-education.pdf</t>
         </is>
       </c>
     </row>
@@ -6326,7 +6174,7 @@
       <c r="B37" s="1" t="inlineStr"/>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>IP Selection - Scholarship Support to students from Economically Weaker Section pursuing higher education in STEM courses - Click here</t>
+          <t>Digital Upskilling of Farmer Producer Organizations (FPOs) through Technology - Click here</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr"/>
@@ -6340,7 +6188,7 @@
       <c r="H37" s="1" t="inlineStr"/>
       <c r="I37" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/scholarship-support-for-economically-weaker-section-students-in-stem-higher-education.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/baseline-endline-study-digital-upskilling-fpos-technology.pdf</t>
         </is>
       </c>
     </row>
@@ -6353,7 +6201,7 @@
       <c r="B38" s="1" t="inlineStr"/>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>Digital Upskilling of Farmer Producer Organizations (FPOs) through Technology - Click here</t>
+          <t>Project - Accelerating 100 Women Micro Entrepreneurs of Northeastern States - Click here</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr"/>
@@ -6367,7 +6215,7 @@
       <c r="H38" s="1" t="inlineStr"/>
       <c r="I38" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/baseline-endline-study-digital-upskilling-fpos-technology.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/project-accelerating-100-women-micro-entrepreneurs-of-northeastern-states.pdf</t>
         </is>
       </c>
     </row>
@@ -6380,21 +6228,21 @@
       <c r="B39" s="1" t="inlineStr"/>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>Project - Accelerating 100 Women Micro Entrepreneurs of Northeastern States - Click here</t>
+          <t>Agency for Developing Training Modules and Conducting Training of Trainers (ToT) for MSMEs on IPR and Financial Management - Click here</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G39" s="1" t="inlineStr"/>
       <c r="H39" s="1" t="inlineStr"/>
       <c r="I39" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/project-accelerating-100-women-micro-entrepreneurs-of-northeastern-states.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/agency-for-developing-training-modules-and-conducting-ToT-for-MSMEs-on-IPR-and-financial-management.pdf</t>
         </is>
       </c>
     </row>
@@ -6407,21 +6255,21 @@
       <c r="B40" s="1" t="inlineStr"/>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>Agency for Developing Training Modules and Conducting Training of Trainers (ToT) for MSMEs on IPR and Financial Management - Click here</t>
+          <t>RFP for WISE - Women in Innovation, Skills &amp; Entrepreneurship - Click here</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G40" s="1" t="inlineStr"/>
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/agency-for-developing-training-modules-and-conducting-ToT-for-MSMEs-on-IPR-and-financial-management.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/women-in-Innovation-skills-and-entrepreneurship.pdf</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6282,7 @@
       <c r="B41" s="1" t="inlineStr"/>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>RFP for WISE - Women in Innovation, Skills &amp; Entrepreneurship - Click here</t>
+          <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - English  - Click here</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr"/>
@@ -6448,7 +6296,7 @@
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/women-in-Innovation-skills-and-entrepreneurship.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-English.pdf</t>
         </is>
       </c>
     </row>
@@ -6461,7 +6309,7 @@
       <c r="B42" s="1" t="inlineStr"/>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - English  - Click here</t>
+          <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - Kannada - Click here</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr"/>
@@ -6475,7 +6323,7 @@
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-English.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-Kannada.pdf</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6336,7 @@
       <c r="B43" s="1" t="inlineStr"/>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - Kannada - Click here</t>
+          <t>RFP - Trainer for Nano Women Entrepreneurs in Karnataka - Click here</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
@@ -6502,7 +6350,7 @@
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-Kannada.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/trainer-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
         </is>
       </c>
     </row>
@@ -6515,7 +6363,7 @@
       <c r="B44" s="1" t="inlineStr"/>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>RFP - Trainer for Nano Women Entrepreneurs in Karnataka - Click here</t>
+          <t>RFP - Training Agency with Content and Trainers for Nano Women Entrepreneurs in Karnataka - Click here</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
@@ -6529,7 +6377,7 @@
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/trainer-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/training-agency-with-content-and-trainers-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
         </is>
       </c>
     </row>
@@ -6542,21 +6390,21 @@
       <c r="B45" s="1" t="inlineStr"/>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>RFP - Training Agency with Content and Trainers for Nano Women Entrepreneurs in Karnataka - Click here</t>
+          <t>Access to E-Governance and Livelihood in PVTG Communities in Aspirational Blocks - Click here</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
       <c r="E45" s="2" t="inlineStr"/>
       <c r="F45" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G45" s="1" t="inlineStr"/>
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/training-agency-with-content-and-trainers-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/access-to-e-governance-and-livelihood-in-pvtg-communities-in-aspirational-blocks.pdf</t>
         </is>
       </c>
     </row>
@@ -6569,48 +6417,56 @@
       <c r="B46" s="1" t="inlineStr"/>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>Access to E-Governance and Livelihood in PVTG Communities in Aspirational Blocks - Click here</t>
+          <t>thingQbator Portal Enhancement and Maintenance Proposal - Click here</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G46" s="1" t="inlineStr"/>
       <c r="H46" s="1" t="inlineStr"/>
       <c r="I46" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/access-to-e-governance-and-livelihood-in-pvtg-communities-in-aspirational-blocks.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/thingQbator-portal-enhancement-and-maintenance-proposal.pdf</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B47" s="1" t="inlineStr"/>
+          <t>HCL Foundation</t>
+        </is>
+      </c>
+      <c r="B47" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>thingQbator Portal Enhancement and Maintenance Proposal - Click here</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards Biodiversity monitoring for Pan-India Afforestation sites</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
       <c r="E47" s="2" t="inlineStr"/>
       <c r="F47" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G47" s="1" t="inlineStr"/>
+          <t>Climate</t>
+        </is>
+      </c>
+      <c r="G47" s="1" t="inlineStr">
+        <is>
+          <t>10th Feb, 2026</t>
+        </is>
+      </c>
       <c r="H47" s="1" t="inlineStr"/>
       <c r="I47" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/thingQbator-portal-enhancement-and-maintenance-proposal.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Biodiversity%20monitoring%20for%20Pan-India%20Afforestation%20sites%202-DSB.pdf</t>
         </is>
       </c>
     </row>
@@ -6627,7 +6483,7 @@
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards Biodiversity monitoring for Pan-India Afforestation sites</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards soil profiling and assessment from the restored and rejuvenated Harit sites.</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
@@ -6645,7 +6501,7 @@
       <c r="H48" s="1" t="inlineStr"/>
       <c r="I48" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Biodiversity%20monitoring%20for%20Pan-India%20Afforestation%20sites%202-DSB.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Soil%20assessment-v1%20RKS-DSB_0.pdf</t>
         </is>
       </c>
     </row>
@@ -6662,25 +6518,25 @@
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards soil profiling and assessment from the restored and rejuvenated Harit sites.</t>
+          <t>HCLFoundation invites proposals from NGOs/CSR implementing agencies for ‘Operating a Social Enterprise Cafe” under the flagship urban development programme - Uday</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
       <c r="E49" s="2" t="inlineStr"/>
       <c r="F49" s="1" t="inlineStr">
         <is>
-          <t>Climate</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G49" s="1" t="inlineStr">
         <is>
-          <t>10th Feb, 2026</t>
+          <t>15th Dec, 2025</t>
         </is>
       </c>
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Soil%20assessment-v1%20RKS-DSB_0.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-11/RfP_Social%20Enterprise%20Cafe_UDAY.docx</t>
         </is>
       </c>
     </row>
@@ -6697,25 +6553,25 @@
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites proposals from NGOs/CSR implementing agencies for ‘Operating a Social Enterprise Cafe” under the flagship urban development programme - Uday</t>
+          <t>Programme Officer/Senior Programme Officer – Environment Education</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
       <c r="E50" s="2" t="inlineStr"/>
       <c r="F50" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Learning, Climate</t>
         </is>
       </c>
       <c r="G50" s="1" t="inlineStr">
         <is>
-          <t>15th Dec, 2025</t>
+          <t>10th Nov, 2025</t>
         </is>
       </c>
       <c r="H50" s="1" t="inlineStr"/>
       <c r="I50" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-11/RfP_Social%20Enterprise%20Cafe_UDAY.docx</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-10/Harit_POSPO_EEA_Multilocation_Oct%202025.pdf</t>
         </is>
       </c>
     </row>
@@ -6732,25 +6588,25 @@
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>Programme Officer/Senior Programme Officer – Environment Education</t>
+          <t>HCLFoundation invites applications for the PO/SPO position under its flagship programme Harit by HCLFoundation</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
       <c r="E51" s="2" t="inlineStr"/>
       <c r="F51" s="1" t="inlineStr">
         <is>
-          <t>Learning, Climate</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G51" s="1" t="inlineStr">
         <is>
-          <t>10th Nov, 2025</t>
+          <t>31st Oct, 2025</t>
         </is>
       </c>
       <c r="H51" s="1" t="inlineStr"/>
       <c r="I51" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-10/Harit_POSPO_EEA_Multilocation_Oct%202025.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-10/JD_Water%20Conservation_SPO%20V4.pdf</t>
         </is>
       </c>
     </row>
@@ -6767,25 +6623,25 @@
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites applications for the PO/SPO position under its flagship programme Harit by HCLFoundation</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit by HCLFoundation, invites RFP from NGOs / CSR organizations working in Water Conservation for the development of Water Structures etc.</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
       <c r="E52" s="2" t="inlineStr"/>
       <c r="F52" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Learning, Climate</t>
         </is>
       </c>
       <c r="G52" s="1" t="inlineStr">
         <is>
-          <t>31st Oct, 2025</t>
+          <t>21st May, 2025</t>
         </is>
       </c>
       <c r="H52" s="1" t="inlineStr"/>
       <c r="I52" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-10/JD_Water%20Conservation_SPO%20V4.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/Final_RFP%20for%20water%20structure%20rejuvenation%20.docx</t>
         </is>
       </c>
     </row>
@@ -6802,25 +6658,25 @@
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit by HCLFoundation, invites RFP from NGOs / CSR organizations working in Water Conservation for the development of Water Structures etc.</t>
+          <t>HCLFoundation invites technical application abstracts for the developing technology drive source code model mobile applications and web portals for addressing human-animal interactions under the Animal Welfare thematic of  Harit by HCLFoundation</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
       <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="1" t="inlineStr">
         <is>
-          <t>Learning, Climate</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G53" s="1" t="inlineStr">
         <is>
-          <t>21st May, 2025</t>
+          <t>15th May, 2025</t>
         </is>
       </c>
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/Final_RFP%20for%20water%20structure%20rejuvenation%20.docx</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_AW%20Tech%20Based%20Source%20Code%20Model_V1%20%281%29.docx</t>
         </is>
       </c>
     </row>
@@ -6837,14 +6693,14 @@
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites technical application abstracts for the developing technology drive source code model mobile applications and web portals for addressing human-animal interactions under the Animal Welfare thematic of  Harit by HCLFoundation</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit invites RFP from NGOs/CSR organizations working in the field of environment for project on the restoration of various degraded and natural habitats</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
       <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Climate</t>
         </is>
       </c>
       <c r="G54" s="1" t="inlineStr">
@@ -6855,7 +6711,7 @@
       <c r="H54" s="1" t="inlineStr"/>
       <c r="I54" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_AW%20Tech%20Based%20Source%20Code%20Model_V1%20%281%29.docx</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/Harit_A%20HR_RFP%20.docx</t>
         </is>
       </c>
     </row>
@@ -6872,14 +6728,14 @@
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit invites RFP from NGOs/CSR organizations working in the field of environment for project on the restoration of various degraded and natural habitats</t>
+          <t>HCLFoundation invites EOI for conducting holistic and comprehensive Impact Assessments of environmental projects supported under Harit by HCLFoundation</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr"/>
       <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="1" t="inlineStr">
         <is>
-          <t>Climate</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G55" s="1" t="inlineStr">
@@ -6890,7 +6746,7 @@
       <c r="H55" s="1" t="inlineStr"/>
       <c r="I55" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/Harit_A%20HR_RFP%20.docx</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_Harit%20Impact%20Assessments.docx</t>
         </is>
       </c>
     </row>
@@ -6907,14 +6763,14 @@
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites EOI for conducting holistic and comprehensive Impact Assessments of environmental projects supported under Harit by HCLFoundation</t>
+          <t>HCLFoundation invites technical application abstracts for the conducting technical and highly engaging environment awareness and sustainability workshops under Harit by HCLFoundation</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Climate</t>
         </is>
       </c>
       <c r="G56" s="1" t="inlineStr">
@@ -6925,42 +6781,34 @@
       <c r="H56" s="1" t="inlineStr"/>
       <c r="I56" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_Harit%20Impact%20Assessments.docx</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_EEA_Env%20%20Sus%20awareness%20workshops_FY%2025-26%20%281%29.docx</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>HCL Foundation</t>
+          <t>NIUA</t>
         </is>
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Tender</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites technical application abstracts for the conducting technical and highly engaging environment awareness and sustainability workshops under Harit by HCLFoundation</t>
+          <t>Supply_of_Unskilled_Manpower.pdf</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr"/>
       <c r="E57" s="2" t="inlineStr"/>
-      <c r="F57" s="1" t="inlineStr">
-        <is>
-          <t>Climate</t>
-        </is>
-      </c>
-      <c r="G57" s="1" t="inlineStr">
-        <is>
-          <t>15th May, 2025</t>
-        </is>
-      </c>
+      <c r="F57" s="1" t="inlineStr"/>
+      <c r="G57" s="1" t="inlineStr"/>
       <c r="H57" s="1" t="inlineStr"/>
       <c r="I57" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_EEA_Env%20%20Sus%20awareness%20workshops_FY%2025-26%20%281%29.docx</t>
+          <t>https://niua.in/sites/default/files/tenders/Supply_of_Unskilled_Manpower.pdf</t>
         </is>
       </c>
     </row>
@@ -6977,7 +6825,7 @@
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>Supply_of_Unskilled_Manpower.pdf</t>
+          <t>Addendum manpower quotation.pdf</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr"/>
@@ -6987,7 +6835,7 @@
       <c r="H58" s="1" t="inlineStr"/>
       <c r="I58" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Supply_of_Unskilled_Manpower.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/Addendum%20manpower%20quotation.pdf</t>
         </is>
       </c>
     </row>

--- a/all_grants.xlsx
+++ b/all_grants.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -489,661 +489,10 @@
       <c r="B2" s="1" t="inlineStr"/>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>RFP - Hiring of an International Audit Firm</t>
+          <t>RFP - for Supply of Skill Lab Items</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Coalition for Disaster Resilient Infrastructure (CDRI) | India
-International Development - RFP - Hiring of an International Audit Firm, Coalition for Disaster Resilient Infrastructure (CDRI), India - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tender ... Read More</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>• Job Email ID:
-tender.projects(at)cdri.world
-Download Attachment:
-RFP-Hiring International Audit Firm-20 Feb'26.pdf
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-09 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Associate – Finance and Operations
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-RFQ-Corporate Global Group Health Insurance Cover...
-Coalition for Disaster Resilient Infrastructure (...
-Location:
-India
-Apply by:
-23 Mar 2026
-HR Associate
-Inclusion Economics India Centre (IEIC) at IFMR
-Location:
-Delhi
-Apply by:
-08 Apr 2026
-Short Term Consultant - Workshop Facilitator for ...
-Fairtrade NAPP
-Location:
-Assam
-Apply by:
-31 Mar 2026
-State Manager
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-Uttar Pradesh
-Apply by:
-22 Mar 2026
-State Project Officer
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-India
-Apply by:
-22 Mar 2026
-State Program Manager-HIV-CSC-North East
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-Assam
-Apply by:
-22 Mar 2026
-Neighbourhood Facilitator – Health &amp; NCDs
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
-Health Planner – Community Mobilization
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>Climate</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>09-03-2026</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287382</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr"/>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>RFP For Selection of an Implementation Support Agency (Isa) For Capacity B...</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>EAII Advisors Pvt Ltd | Andhra Pradesh
-International Development - RFP For Selection of an Implementation Support Agency (Isa) For Capacity Building Of Community Leaders To Conduct Community Engagement Activities, EAII Advisors Pvt Ltd, Andhra Pradesh - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Regis ... Read More</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>• Proposal Requirements
-1. Company Background and Details
-A. Company Profile
-Overview of the firm or firms submitting the bid, including a brief history, information about organizational structure, relevant company financials, location of offices, number of employees, relevant certifications, or any other information that could be pertinent.
-Supplier Response:
-Kindly fill in the column “Bidder Response”. The current inputs are guiding inputs or choices for answers. Kindly fill in accordingly.
-For detailed information, please check the complete version of the RFP attached below.
-Download Attachment:
-Standalone ISA RFP Technical Evaluation Response Template (1).docx
-Download Attachment:
-Telugu_Standalone ISA RFP Technical Evaluation Response Template.docx
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-09 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Associate – Finance and Operations
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-RFQ-Corporate Global Group Health Insurance Cover...
-Coalition for Disaster Resilient Infrastructure (...
-Location:
-India
-Apply by:
-23 Mar 2026
-HR Associate
-Inclusion Economics India Centre (IEIC) at IFMR
-Location:
-Delhi
-Apply by:
-08 Apr 2026
-Short Term Consultant - Workshop Facilitator for ...
-Fairtrade NAPP
-Location:
-Assam
-Apply by:
-31 Mar 2026
-State Manager
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-Uttar Pradesh
-Apply by:
-22 Mar 2026
-State Project Officer
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-India
-Apply by:
-22 Mar 2026
-State Program Manager-HIV-CSC-North East
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-Assam
-Apply by:
-22 Mar 2026
-Neighbourhood Facilitator – Health &amp; NCDs
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
-Health Planner – Community Mobilization
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Governance, Learning</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>09-03-2026</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=285950</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr"/>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>RFP For The Contractors To Procure, Build, Install, Supply Chlorine Tablet...</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>EAII Advisors Pvt Ltd | Andhra Pradesh
-International Development - RFP For The Contractors To Procure, Build, Install, Supply Chlorine Tablets, Operate And Maintain Tablet-Based In Line Chlorination Devices, EAII Advisors Pvt Ltd, Andhra Pradesh - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Ho ... Read More</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>• Proposal Requirements
-1. Company Background and Details
-A. Company Profile
-Overview of the firm or firms submitting the bid, including a brief history, information about organizational structure, relevant company financials, location of offices, number of employees, relevant certifications, or any other information that could be pertinent.
-Supplier Response:
-Kindly fill in the column “Bidder Response”. The current inputs are guiding inputs or choices for answers. Kindly fill in accordingly.
-For detailed information, please check the complete version of the RFP attached below.
-Download Attachment:
-Standalone IC RFP Technical Evaluation Response Template.docx
-Download Attachment:
-Telugu_Standalone IC RFP Technical Evaluation Response Template.docx
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-09 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Associate – Finance and Operations
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-RFQ-Corporate Global Group Health Insurance Cover...
-Coalition for Disaster Resilient Infrastructure (...
-Location:
-India
-Apply by:
-23 Mar 2026
-HR Associate
-Inclusion Economics India Centre (IEIC) at IFMR
-Location:
-Delhi
-Apply by:
-08 Apr 2026
-Short Term Consultant - Workshop Facilitator for ...
-Fairtrade NAPP
-Location:
-Assam
-Apply by:
-31 Mar 2026
-State Manager
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-Uttar Pradesh
-Apply by:
-22 Mar 2026
-State Project Officer
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-India
-Apply by:
-22 Mar 2026
-State Program Manager-HIV-CSC-North East
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-Assam
-Apply by:
-22 Mar 2026
-Neighbourhood Facilitator – Health &amp; NCDs
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
-Health Planner – Community Mobilization
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>09-03-2026</t>
-        </is>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=285949</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr"/>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Early-Stage Impact Assessment-CDRI SWP 23-26</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Coalition for Disaster Resilient Infrastructure (CDRI) | India
-International Development - RFP - Early-Stage Impact Assessment-CDRI SWP 23-26, Coalition for Disaster Resilient Infrastructure (CDRI), India - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs ... Read More</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>Climate, Governance</t>
-        </is>
-      </c>
-      <c r="G5" s="1" t="inlineStr">
-        <is>
-          <t>09-03-2026</t>
-        </is>
-      </c>
-      <c r="H5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287093</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr"/>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>RFP - for Supply of Skill Lab Items</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>TeamLease Foundation | India
 International Development - RFP - for Supply of Skill Lab Items, TeamLease Foundation, India - DevNetJobsIndia.org
@@ -1165,7 +514,7 @@
 Jobseeker ... Read More</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>• Technical Bid Submission Link-
 https://forms.gle/V9iy35ddb4kWEb468
@@ -1272,54 +621,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFQ-Corporate Global Group Health Insurance Cover...
-Coalition for Disaster Resilient Infrastructure (...
-Location:
-India
-Apply by:
-23 Mar 2026
-HR Associate
-Inclusion Economics India Centre (IEIC) at IFMR
+Sr MEAL Officer, Preconception Nutrition and Care
+Nutrition International
 Location:
 Delhi
 Apply by:
+29 Mar 2026
+Academic Mentor
+Bharti Airtel Foundation
+Location:
+Sikkim, Assam, Jharkhand
+Apply by:
+09 Apr 2026
+Manager – Enterprise Promotion
+Project Concern International India (PCI India)
+Location:
+Bihar
+Apply by:
+13 Mar 2026
+RFP - Design, Development, Deployment and Mainten...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+RFP - Appointment of Agency for SEO Management an...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+Senior Program Manager/Program Manager, Doctors f...
+Lung Care Foundation
+Location:
+Haryana
+Apply by:
 08 Apr 2026
-Short Term Consultant - Workshop Facilitator for ...
-Fairtrade NAPP
-Location:
-Assam
-Apply by:
-31 Mar 2026
-State Manager
-Hindustan Latex Family Planning Promotion Trust (...
+Program Head - MIS And Technology
+Dhwani Foundation
+Location:
+Karnataka
+Apply by:
+08 Apr 2026
+Associate/Specialist-Supply Chain
+India Health Action Trust (IHAT)
 Location:
 Uttar Pradesh
 Apply by:
 22 Mar 2026
-State Project Officer
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-India
-Apply by:
-22 Mar 2026
-State Program Manager-HIV-CSC-North East
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-Assam
-Apply by:
-22 Mar 2026
-Neighbourhood Facilitator – Health &amp; NCDs
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
-Health Planner – Community Mobilization
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
 Jobseekers
 Register
 Login
@@ -1347,38 +696,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F6" s="1" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G6" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>11-03-2026</t>
         </is>
       </c>
-      <c r="H6" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I6" s="1" t="inlineStr">
+      <c r="H2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287613</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr"/>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr"/>
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>SOW - Engagement of a Public Relations (PR) Agency on Retainer</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Room to Read India | India
 International Development - SOW - Engagement of a Public Relations (PR) Agency on Retainer, Room to Read India, India - DevNetJobsIndia.org
@@ -1399,7 +748,7 @@
 Job ... Read More</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>• Scope of Work (SOW)
 Engagement of a Public Relations (PR) Agency on Retainer
@@ -1529,54 +878,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFQ-Corporate Global Group Health Insurance Cover...
-Coalition for Disaster Resilient Infrastructure (...
-Location:
-India
-Apply by:
-23 Mar 2026
-HR Associate
-Inclusion Economics India Centre (IEIC) at IFMR
+Sr MEAL Officer, Preconception Nutrition and Care
+Nutrition International
 Location:
 Delhi
 Apply by:
+29 Mar 2026
+Academic Mentor
+Bharti Airtel Foundation
+Location:
+Sikkim, Assam, Jharkhand
+Apply by:
+09 Apr 2026
+Manager – Enterprise Promotion
+Project Concern International India (PCI India)
+Location:
+Bihar
+Apply by:
+13 Mar 2026
+RFP - Design, Development, Deployment and Mainten...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+RFP - Appointment of Agency for SEO Management an...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+Senior Program Manager/Program Manager, Doctors f...
+Lung Care Foundation
+Location:
+Haryana
+Apply by:
 08 Apr 2026
-Short Term Consultant - Workshop Facilitator for ...
-Fairtrade NAPP
-Location:
-Assam
-Apply by:
-31 Mar 2026
-State Manager
-Hindustan Latex Family Planning Promotion Trust (...
+Program Head - MIS And Technology
+Dhwani Foundation
+Location:
+Karnataka
+Apply by:
+08 Apr 2026
+Associate/Specialist-Supply Chain
+India Health Action Trust (IHAT)
 Location:
 Uttar Pradesh
 Apply by:
 22 Mar 2026
-State Project Officer
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-India
-Apply by:
-22 Mar 2026
-State Program Manager-HIV-CSC-North East
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-Assam
-Apply by:
-22 Mar 2026
-Neighbourhood Facilitator – Health &amp; NCDs
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
-Health Planner – Community Mobilization
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
 Jobseekers
 Register
 Login
@@ -1604,38 +953,251 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F7" s="1" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>Governance, Learning</t>
         </is>
       </c>
-      <c r="G7" s="1" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>12-03-2026</t>
         </is>
       </c>
-      <c r="H7" s="1" t="n">
+      <c r="H3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287648</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr"/>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>RFP - for Internal Audit</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>India HIV/AIDS Alliance (Alliance India) | Delhi
+International Development - RFP - for Internal Audit, India HIV/AIDS Alliance (Alliance India), Delhi - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers:
+Login
+|
+Regist ... Read More</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>• Alliance India reserves the right to reject applications that do not meet eligibility or application submission requirements (as detailed above) without further notice to the applicant. Issuance of this RFP does not constitute an award commitment or a guarantee of business on the part of Alliance India, nor does it commit Alliance India to pay for the costs incurred in submitting the application. Further, Alliance India reserves the right to reject any or all applications received and negotiate separately with an applicant if such action is considered in the best interest of Alliance India/ project.
+iii.
+Queries, Response and Submission
+Queries regarding this RFP will be sent only to procurement@allianceindia.org by March 07, 2026. Alliance India shall collaborate and respond to all meaningful queries from prospective applicants by March 10, 2026. Responses to questions shall be compiled and sent to all the applicants who raised the queries through email only. ALLIANCE INDIA is under no obligation to consider or respond to questions that are not received on time.
+iv.
+• Submission of bids
+The bid has to be submitted in the prescribed format on or before March 13, 2026 by 5 p.m. Indian Standard Time to
+procurement@allianceindia.org
+For the detailed version of the Request for Proposal, please refer to the RFP attached.
+• Job Email ID:
+procurement(at)allianceindia.org
+Download Attachment:
+RFP for Internal Audit - FY 2025-26.doc
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+13 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+Sr MEAL Officer, Preconception Nutrition and Care
+Nutrition International
+Location:
+Delhi
+Apply by:
+29 Mar 2026
+Academic Mentor
+Bharti Airtel Foundation
+Location:
+Sikkim, Assam, Jharkhand
+Apply by:
+09 Apr 2026
+Manager – Enterprise Promotion
+Project Concern International India (PCI India)
+Location:
+Bihar
+Apply by:
+13 Mar 2026
+RFP - Design, Development, Deployment and Mainten...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+RFP - Appointment of Agency for SEO Management an...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+Senior Program Manager/Program Manager, Doctors f...
+Lung Care Foundation
+Location:
+Haryana
+Apply by:
+08 Apr 2026
+Program Head - MIS And Technology
+Dhwani Foundation
+Location:
+Karnataka
+Apply by:
+08 Apr 2026
+Associate/Specialist-Supply Chain
+India Health Action Trust (IHAT)
+Location:
+Uttar Pradesh
+Apply by:
+22 Mar 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>13-03-2026</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I7" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287648</t>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287765</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr"/>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr"/>
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>Specialist – Financial Management and Compliance</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Financial Management Service Foundation (FMSF) | Uttar Pradesh
 International Development - Specialist – Financial Management and Compliance, Financial Management Service Foundation (FMSF), Uttar Pradesh - DevNetJobsIndia.org
@@ -1649,7 +1211,7 @@
 RFPs/T ... Read More</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>• will play a vital role in a program which seeks to strengthen the internal capacities of non-profit organizations in India across three building blocks of institutional functioning: governance, financial management, and compliance. These areas are deeply interconnected and together determine how effectively an organization operates, delivers programs and meets the expectations of its stakeholders. This position demands expertise in specific areas related to governance, compliance, and financial management, contributing essential guidance and support to strengthen the capabilities of participating organizations.
 Job Responsibilities:
@@ -1762,54 +1324,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFQ-Corporate Global Group Health Insurance Cover...
-Coalition for Disaster Resilient Infrastructure (...
-Location:
-India
-Apply by:
-23 Mar 2026
-HR Associate
-Inclusion Economics India Centre (IEIC) at IFMR
+Sr MEAL Officer, Preconception Nutrition and Care
+Nutrition International
 Location:
 Delhi
 Apply by:
+29 Mar 2026
+Academic Mentor
+Bharti Airtel Foundation
+Location:
+Sikkim, Assam, Jharkhand
+Apply by:
+09 Apr 2026
+Manager – Enterprise Promotion
+Project Concern International India (PCI India)
+Location:
+Bihar
+Apply by:
+13 Mar 2026
+RFP - Design, Development, Deployment and Mainten...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+RFP - Appointment of Agency for SEO Management an...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+Senior Program Manager/Program Manager, Doctors f...
+Lung Care Foundation
+Location:
+Haryana
+Apply by:
 08 Apr 2026
-Short Term Consultant - Workshop Facilitator for ...
-Fairtrade NAPP
-Location:
-Assam
-Apply by:
-31 Mar 2026
-State Manager
-Hindustan Latex Family Planning Promotion Trust (...
+Program Head - MIS And Technology
+Dhwani Foundation
+Location:
+Karnataka
+Apply by:
+08 Apr 2026
+Associate/Specialist-Supply Chain
+India Health Action Trust (IHAT)
 Location:
 Uttar Pradesh
 Apply by:
 22 Mar 2026
-State Project Officer
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-India
-Apply by:
-22 Mar 2026
-State Program Manager-HIV-CSC-North East
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-Assam
-Apply by:
-22 Mar 2026
-Neighbourhood Facilitator – Health &amp; NCDs
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
-Health Planner – Community Mobilization
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
 Jobseekers
 Register
 Login
@@ -1837,41 +1399,41 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F8" s="1" t="inlineStr">
+      <c r="F5" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G8" s="1" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>13-03-2026</t>
         </is>
       </c>
-      <c r="H8" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I8" s="1" t="inlineStr">
+      <c r="H5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287015</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr"/>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>RFP - for Internal Audit</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>India HIV/AIDS Alliance (Alliance India) | Delhi
-International Development - RFP - for Internal Audit, India HIV/AIDS Alliance (Alliance India), Delhi - DevNetJobsIndia.org
+      <c r="B6" s="1" t="inlineStr"/>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>ToR - Livelihoods Strategy Review and Future Direction Roadmap</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>ChildFund India | India
+International Development - ToR - Livelihoods Strategy Review and Future Direction Roadmap, ChildFund India, India - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
@@ -1885,29 +1447,39 @@
 Jobseekers:
 Login
 |
-Regist ... Read More</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>• Alliance India reserves the right to reject applications that do not meet eligibility or application submission requirements (as detailed above) without further notice to the applicant. Issuance of this RFP does not constitute an award commitment or a guarantee of business on the part of Alliance India, nor does it commit Alliance India to pay for the costs incurred in submitting the application. Further, Alliance India reserves the right to reject any or all applications received and negotiate separately with an applicant if such action is considered in the best interest of Alliance India/ project.
-iii.
-Queries, Response and Submission
-Queries regarding this RFP will be sent only to procurement@allianceindia.org by March 07, 2026. Alliance India shall collaborate and respond to all meaningful queries from prospective applicants by March 10, 2026. Responses to questions shall be compiled and sent to all the applicants who raised the queries through email only. ALLIANCE INDIA is under no obligation to consider or respond to questions that are not received on time.
-iv.
-• Submission of bids
-The bid has to be submitted in the prescribed format on or before March 13, 2026 by 5 p.m. Indian Standard Time to
-procurement@allianceindia.org
-For the detailed version of the Request for Proposal, please refer to the RFP attached.
+Register
+Jobseeker ... Read More</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>• To determine the relevance, alignment, and coherence of the Livelihood Program under CSP 2022–2027 with national priorities, donor expectations, and organizational mandate.
+To assess the extent to which planned outputs and outcomes have been achieved and to evaluate the quality and impact of program interventions.
+Identify achievements, innovations, good practices, and enabling factors across Livelihood program interventions.
+Document gaps, challenges, and areas for strengthening
+To examine the sustainability of program outcomes and the institutional readiness of ChildFund India for long-term resilience and growth.
+Facilitate reflection through workshops involving staff, partners, and selected beneficiaries and provide recommendations for strategic direction, scalability, and future program priorities.
+Proposal Submission
+Interested evaluators/agencies are invited to submit:
+Technical proposal outlining approach and methodology
+Team composition and relevant experience
+Financial proposal with a detailed budget
+Sample of previous qualitative evaluation work
+Interested evaluators/agencies are requested to submit their technical and financial proposals to
+centralpurchase2@childfundindia.org
+by 15 March 2026.
+Reference No:- PRA/CFI/DEL/2025-26/053
+ChildFund India reserves the right to modify this ToR based on programmatic and contextual requirements.
+For detailed information, please check the complete version of the advert attached below.
 • Job Email ID:
-procurement(at)allianceindia.org
+centralpurchase2(at)childfundindia.org
 Download Attachment:
-RFP for Internal Audit - FY 2025-26.doc
+ToR Livelihood Portfolio-6.3.2026.doc
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
 Apply by:
-13 Mar 2026
+15 Mar 2026
 Access all the jobs and get ahead!
 Subscribe to Value Membership Now!
 Subscribe
@@ -1975,54 +1547,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFQ-Corporate Global Group Health Insurance Cover...
-Coalition for Disaster Resilient Infrastructure (...
-Location:
-India
-Apply by:
-23 Mar 2026
-HR Associate
-Inclusion Economics India Centre (IEIC) at IFMR
+Sr MEAL Officer, Preconception Nutrition and Care
+Nutrition International
 Location:
 Delhi
 Apply by:
+29 Mar 2026
+Academic Mentor
+Bharti Airtel Foundation
+Location:
+Sikkim, Assam, Jharkhand
+Apply by:
+09 Apr 2026
+Manager – Enterprise Promotion
+Project Concern International India (PCI India)
+Location:
+Bihar
+Apply by:
+13 Mar 2026
+RFP - Design, Development, Deployment and Mainten...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+RFP - Appointment of Agency for SEO Management an...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+Senior Program Manager/Program Manager, Doctors f...
+Lung Care Foundation
+Location:
+Haryana
+Apply by:
 08 Apr 2026
-Short Term Consultant - Workshop Facilitator for ...
-Fairtrade NAPP
-Location:
-Assam
-Apply by:
-31 Mar 2026
-State Manager
-Hindustan Latex Family Planning Promotion Trust (...
+Program Head - MIS And Technology
+Dhwani Foundation
+Location:
+Karnataka
+Apply by:
+08 Apr 2026
+Associate/Specialist-Supply Chain
+India Health Action Trust (IHAT)
 Location:
 Uttar Pradesh
 Apply by:
 22 Mar 2026
-State Project Officer
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-India
-Apply by:
-22 Mar 2026
-State Program Manager-HIV-CSC-North East
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-Assam
-Apply by:
-22 Mar 2026
-Neighbourhood Facilitator – Health &amp; NCDs
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
-Health Planner – Community Mobilization
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
 Jobseekers
 Register
 Login
@@ -2050,22 +1622,650 @@
 Recruitment Exchange</t>
         </is>
       </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>15-03-2026</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287910</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>ToR - Strategic Review and Forward-Looking Education Strategy Development</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>ChildFund India | India
+International Development - ToR - Strategic Review and Forward-Looking Education Strategy Development, ChildFund India, India - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers:
+Login
+|
+Registe ... Read More</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>• Job Email ID:
+centralpurchase2(at)childfundindia.org
+Download Attachment:
+ToR for Education.doc
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+15 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+Sr MEAL Officer, Preconception Nutrition and Care
+Nutrition International
+Location:
+Delhi
+Apply by:
+29 Mar 2026
+Academic Mentor
+Bharti Airtel Foundation
+Location:
+Sikkim, Assam, Jharkhand
+Apply by:
+09 Apr 2026
+Manager – Enterprise Promotion
+Project Concern International India (PCI India)
+Location:
+Bihar
+Apply by:
+13 Mar 2026
+RFP - Design, Development, Deployment and Mainten...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+RFP - Appointment of Agency for SEO Management an...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+Senior Program Manager/Program Manager, Doctors f...
+Lung Care Foundation
+Location:
+Haryana
+Apply by:
+08 Apr 2026
+Program Head - MIS And Technology
+Dhwani Foundation
+Location:
+Karnataka
+Apply by:
+08 Apr 2026
+Associate/Specialist-Supply Chain
+India Health Action Trust (IHAT)
+Location:
+Uttar Pradesh
+Apply by:
+22 Mar 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>Learning, Safety</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>15-03-2026</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287902</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr"/>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>RFP for Data Collection for Foundational Reading Tool in Odisha</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Lords Education and Health Society (LEHS) | Odisha
+International Development - RFP for Data Collection for Foundational Reading Tool in Odisha, Lords Education and Health Society (LEHS), Odisha - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Se ... Read More</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>• 4. SCOPE OF WORK
+Summary of Activities
+S.No
+Activity   Description
+Timelines
+1
+Data   Collection: students' reading of textual items   (letters/words/non-words/paragraphs) in Odia &amp; English languages for   Grades 1-8.
+Data       Collection should be completed in   April 2026
+Details of the Activity Below:
+Data Collection: Collect audio data of students reading texts in Odia &amp; English from Grade 1-8
+Total Number of Hours to be collected: ~360 hours for the Odia language
+Total Number of Hours to be collected: ~115 hours for the English language
+• Submission Details
+All proposals to this RFP must be received no later than &lt;15th March 2026&gt;
+.
+The proposal should be submitted only through e-mail in PDF format addressed to the Procurement Team at:
+rfp.lehs@wadhwaniai.org
+. The email's subject line must contain the reference number and title of the RFP: Data Collection for Foundational Reading
+Tool in Odisha  (Name of Partner)
+Any proposals received by Wadhwani-AI after the deadline prescribed in the timeline of this document are liable to be rejected.
+For detailed information, please check the complete version of the RFP attached below
+• Job Email ID:
+rfp.lehs(at)wadhwaniai.org
+Download Attachment:
+RFP for Data Collection for Foundational Reading Tool in Odisha.pdf
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+15 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+Sr MEAL Officer, Preconception Nutrition and Care
+Nutrition International
+Location:
+Delhi
+Apply by:
+29 Mar 2026
+Academic Mentor
+Bharti Airtel Foundation
+Location:
+Sikkim, Assam, Jharkhand
+Apply by:
+09 Apr 2026
+Manager – Enterprise Promotion
+Project Concern International India (PCI India)
+Location:
+Bihar
+Apply by:
+13 Mar 2026
+RFP - Design, Development, Deployment and Mainten...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+RFP - Appointment of Agency for SEO Management an...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+Senior Program Manager/Program Manager, Doctors f...
+Lung Care Foundation
+Location:
+Haryana
+Apply by:
+08 Apr 2026
+Program Head - MIS And Technology
+Dhwani Foundation
+Location:
+Karnataka
+Apply by:
+08 Apr 2026
+Associate/Specialist-Supply Chain
+India Health Action Trust (IHAT)
+Location:
+Uttar Pradesh
+Apply by:
+22 Mar 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>Governance, Learning, Safety</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>15-03-2026</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287936</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr"/>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>ToR - Portfolio-Wide Learning Exercise cum review for the Health Domain</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>ChildFund India | India
+International Development - ToR - Portfolio-Wide Learning Exercise cum review for the Health Domain, ChildFund India, India - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers:
+Login
+|
+Register ... Read More</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>• Job Email ID:
+centralpurchase2(at)childfundindia.org
+Download Attachment:
+TOR  Health Portfolio_23.2.2026.doc
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+15 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+Sr MEAL Officer, Preconception Nutrition and Care
+Nutrition International
+Location:
+Delhi
+Apply by:
+29 Mar 2026
+Academic Mentor
+Bharti Airtel Foundation
+Location:
+Sikkim, Assam, Jharkhand
+Apply by:
+09 Apr 2026
+Manager – Enterprise Promotion
+Project Concern International India (PCI India)
+Location:
+Bihar
+Apply by:
+13 Mar 2026
+RFP - Design, Development, Deployment and Mainten...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+RFP - Appointment of Agency for SEO Management an...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+Senior Program Manager/Program Manager, Doctors f...
+Lung Care Foundation
+Location:
+Haryana
+Apply by:
+08 Apr 2026
+Program Head - MIS And Technology
+Dhwani Foundation
+Location:
+Karnataka
+Apply by:
+08 Apr 2026
+Associate/Specialist-Supply Chain
+India Health Action Trust (IHAT)
+Location:
+Uttar Pradesh
+Apply by:
+22 Mar 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
       <c r="F9" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Learning, Safety</t>
         </is>
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
-          <t>13-03-2026</t>
+          <t>15-03-2026</t>
         </is>
       </c>
       <c r="H9" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I9" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287765</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287901</t>
         </is>
       </c>
     </row>
@@ -2238,54 +2438,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFQ-Corporate Global Group Health Insurance Cover...
-Coalition for Disaster Resilient Infrastructure (...
-Location:
-India
-Apply by:
-23 Mar 2026
-HR Associate
-Inclusion Economics India Centre (IEIC) at IFMR
+Sr MEAL Officer, Preconception Nutrition and Care
+Nutrition International
 Location:
 Delhi
 Apply by:
+29 Mar 2026
+Academic Mentor
+Bharti Airtel Foundation
+Location:
+Sikkim, Assam, Jharkhand
+Apply by:
+09 Apr 2026
+Manager – Enterprise Promotion
+Project Concern International India (PCI India)
+Location:
+Bihar
+Apply by:
+13 Mar 2026
+RFP - Design, Development, Deployment and Mainten...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+RFP - Appointment of Agency for SEO Management an...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+Senior Program Manager/Program Manager, Doctors f...
+Lung Care Foundation
+Location:
+Haryana
+Apply by:
 08 Apr 2026
-Short Term Consultant - Workshop Facilitator for ...
-Fairtrade NAPP
-Location:
-Assam
-Apply by:
-31 Mar 2026
-State Manager
-Hindustan Latex Family Planning Promotion Trust (...
+Program Head - MIS And Technology
+Dhwani Foundation
+Location:
+Karnataka
+Apply by:
+08 Apr 2026
+Associate/Specialist-Supply Chain
+India Health Action Trust (IHAT)
 Location:
 Uttar Pradesh
 Apply by:
 22 Mar 2026
-State Project Officer
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-India
-Apply by:
-22 Mar 2026
-State Program Manager-HIV-CSC-North East
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-Assam
-Apply by:
-22 Mar 2026
-Neighbourhood Facilitator – Health &amp; NCDs
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
-Health Planner – Community Mobilization
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
 Jobseekers
 Register
 Login
@@ -2324,7 +2524,7 @@
         </is>
       </c>
       <c r="H10" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I10" s="1" t="inlineStr">
         <is>
@@ -2341,641 +2541,10 @@
       <c r="B11" s="1" t="inlineStr"/>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>ToR - Livelihoods Strategy Review and Future Direction Roadmap</t>
+          <t>RFP - for Empanelment of Knowledge Partners for Grooming of students for ...</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>ChildFund India | India
-International Development - ToR - Livelihoods Strategy Review and Future Direction Roadmap, ChildFund India, India - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Login
-|
-Register
-Jobseeker ... Read More</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>• To determine the relevance, alignment, and coherence of the Livelihood Program under CSP 2022–2027 with national priorities, donor expectations, and organizational mandate.
-To assess the extent to which planned outputs and outcomes have been achieved and to evaluate the quality and impact of program interventions.
-Identify achievements, innovations, good practices, and enabling factors across Livelihood program interventions.
-Document gaps, challenges, and areas for strengthening
-To examine the sustainability of program outcomes and the institutional readiness of ChildFund India for long-term resilience and growth.
-Facilitate reflection through workshops involving staff, partners, and selected beneficiaries and provide recommendations for strategic direction, scalability, and future program priorities.
-Proposal Submission
-Interested evaluators/agencies are invited to submit:
-Technical proposal outlining approach and methodology
-Team composition and relevant experience
-Financial proposal with a detailed budget
-Sample of previous qualitative evaluation work
-Interested evaluators/agencies are requested to submit their technical and financial proposals to
-centralpurchase2@childfundindia.org
-by 15 March 2026.
-Reference No:- PRA/CFI/DEL/2025-26/053
-ChildFund India reserves the right to modify this ToR based on programmatic and contextual requirements.
-For detailed information, please check the complete version of the advert attached below.
-• Job Email ID:
-centralpurchase2(at)childfundindia.org
-Download Attachment:
-ToR Livelihood Portfolio-6.3.2026.doc
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-15 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Associate – Finance and Operations
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-RFQ-Corporate Global Group Health Insurance Cover...
-Coalition for Disaster Resilient Infrastructure (...
-Location:
-India
-Apply by:
-23 Mar 2026
-HR Associate
-Inclusion Economics India Centre (IEIC) at IFMR
-Location:
-Delhi
-Apply by:
-08 Apr 2026
-Short Term Consultant - Workshop Facilitator for ...
-Fairtrade NAPP
-Location:
-Assam
-Apply by:
-31 Mar 2026
-State Manager
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-Uttar Pradesh
-Apply by:
-22 Mar 2026
-State Project Officer
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-India
-Apply by:
-22 Mar 2026
-State Program Manager-HIV-CSC-North East
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-Assam
-Apply by:
-22 Mar 2026
-Neighbourhood Facilitator – Health &amp; NCDs
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
-Health Planner – Community Mobilization
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="G11" s="1" t="inlineStr">
-        <is>
-          <t>15-03-2026</t>
-        </is>
-      </c>
-      <c r="H11" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I11" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287910</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="inlineStr"/>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>ToR - Strategic Review and Forward-Looking Education Strategy Development</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>ChildFund India | India
-International Development - ToR - Strategic Review and Forward-Looking Education Strategy Development, ChildFund India, India - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Login
-|
-Registe ... Read More</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>• Job Email ID:
-centralpurchase2(at)childfundindia.org
-Download Attachment:
-ToR for Education.doc
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-15 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Associate – Finance and Operations
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-RFQ-Corporate Global Group Health Insurance Cover...
-Coalition for Disaster Resilient Infrastructure (...
-Location:
-India
-Apply by:
-23 Mar 2026
-HR Associate
-Inclusion Economics India Centre (IEIC) at IFMR
-Location:
-Delhi
-Apply by:
-08 Apr 2026
-Short Term Consultant - Workshop Facilitator for ...
-Fairtrade NAPP
-Location:
-Assam
-Apply by:
-31 Mar 2026
-State Manager
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-Uttar Pradesh
-Apply by:
-22 Mar 2026
-State Project Officer
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-India
-Apply by:
-22 Mar 2026
-State Program Manager-HIV-CSC-North East
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-Assam
-Apply by:
-22 Mar 2026
-Neighbourhood Facilitator – Health &amp; NCDs
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
-Health Planner – Community Mobilization
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>Learning, Safety</t>
-        </is>
-      </c>
-      <c r="G12" s="1" t="inlineStr">
-        <is>
-          <t>15-03-2026</t>
-        </is>
-      </c>
-      <c r="H12" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I12" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287902</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="inlineStr"/>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>ToR - Portfolio-Wide Learning Exercise cum review for the Health Domain</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>ChildFund India | India
-International Development - ToR - Portfolio-Wide Learning Exercise cum review for the Health Domain, ChildFund India, India - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Login
-|
-Register ... Read More</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>• Job Email ID:
-centralpurchase2(at)childfundindia.org
-Download Attachment:
-TOR  Health Portfolio_23.2.2026.doc
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-15 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Associate – Finance and Operations
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-RFQ-Corporate Global Group Health Insurance Cover...
-Coalition for Disaster Resilient Infrastructure (...
-Location:
-India
-Apply by:
-23 Mar 2026
-HR Associate
-Inclusion Economics India Centre (IEIC) at IFMR
-Location:
-Delhi
-Apply by:
-08 Apr 2026
-Short Term Consultant - Workshop Facilitator for ...
-Fairtrade NAPP
-Location:
-Assam
-Apply by:
-31 Mar 2026
-State Manager
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-Uttar Pradesh
-Apply by:
-22 Mar 2026
-State Project Officer
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-India
-Apply by:
-22 Mar 2026
-State Program Manager-HIV-CSC-North East
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-Assam
-Apply by:
-22 Mar 2026
-Neighbourhood Facilitator – Health &amp; NCDs
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
-Health Planner – Community Mobilization
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>Learning, Safety</t>
-        </is>
-      </c>
-      <c r="G13" s="1" t="inlineStr">
-        <is>
-          <t>15-03-2026</t>
-        </is>
-      </c>
-      <c r="H13" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I13" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287901</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="inlineStr"/>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>RFP - for Empanelment of Knowledge Partners for Grooming of students for ...</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>TeamLease Foundation | India
 International Development - RFP - for  Empanelment of Knowledge Partners for Grooming of students for competitive examination (through partner) Super 30 Model, TeamLease Foundation, India - DevNetJobsIndia.org
@@ -2988,263 +2557,43 @@
 Broadcast ... Read More</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F14" s="1" t="inlineStr">
+      <c r="F11" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G14" s="1" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>15-03-2026</t>
         </is>
       </c>
-      <c r="H14" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I14" s="1" t="inlineStr">
+      <c r="H11" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287763</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr"/>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>RFP for Data Collection for Foundational Reading Tool in Odisha</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Lords Education and Health Society (LEHS) | Odisha
-International Development - RFP for Data Collection for Foundational Reading Tool in Odisha, Lords Education and Health Society (LEHS), Odisha - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Se ... Read More</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>• 4. SCOPE OF WORK
-Summary of Activities
-S.No
-Activity   Description
-Timelines
-1
-Data   Collection: students' reading of textual items   (letters/words/non-words/paragraphs) in Odia &amp; English languages for   Grades 1-8.
-Data       Collection should be completed in   April 2026
-Details of the Activity Below:
-Data Collection: Collect audio data of students reading texts in Odia &amp; English from Grade 1-8
-Total Number of Hours to be collected: ~360 hours for the Odia language
-Total Number of Hours to be collected: ~115 hours for the English language
-• Submission Details
-All proposals to this RFP must be received no later than &lt;15th March 2026&gt;
-.
-The proposal should be submitted only through e-mail in PDF format addressed to the Procurement Team at:
-rfp.lehs@wadhwaniai.org
-. The email's subject line must contain the reference number and title of the RFP: Data Collection for Foundational Reading
-Tool in Odisha  (Name of Partner)
-Any proposals received by Wadhwani-AI after the deadline prescribed in the timeline of this document are liable to be rejected.
-For detailed information, please check the complete version of the RFP attached below
-• Job Email ID:
-rfp.lehs(at)wadhwaniai.org
-Download Attachment:
-RFP for Data Collection for Foundational Reading Tool in Odisha.pdf
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-15 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Associate – Finance and Operations
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-RFQ-Corporate Global Group Health Insurance Cover...
-Coalition for Disaster Resilient Infrastructure (...
-Location:
-India
-Apply by:
-23 Mar 2026
-HR Associate
-Inclusion Economics India Centre (IEIC) at IFMR
-Location:
-Delhi
-Apply by:
-08 Apr 2026
-Short Term Consultant - Workshop Facilitator for ...
-Fairtrade NAPP
-Location:
-Assam
-Apply by:
-31 Mar 2026
-State Manager
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-Uttar Pradesh
-Apply by:
-22 Mar 2026
-State Project Officer
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-India
-Apply by:
-22 Mar 2026
-State Program Manager-HIV-CSC-North East
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-Assam
-Apply by:
-22 Mar 2026
-Neighbourhood Facilitator – Health &amp; NCDs
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
-Health Planner – Community Mobilization
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F15" s="1" t="inlineStr">
-        <is>
-          <t>Governance, Learning, Safety</t>
-        </is>
-      </c>
-      <c r="G15" s="1" t="inlineStr">
-        <is>
-          <t>15-03-2026</t>
-        </is>
-      </c>
-      <c r="H15" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I15" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287936</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B16" s="1" t="inlineStr"/>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="B12" s="1" t="inlineStr"/>
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>RFP - Big IC+ISA RFP - Selection of a Service Provider for Supply, Instal...</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>EAII Advisors Pvt Ltd | Andhra Pradesh
 International Development - RFP - Big IC+ISA RFP -  Selection of a Service Provider for Supply, Installation and Operation &amp; Maintenance of 150 ILC Devices and Capacity Building., EAII Advisors Pvt Ltd, Andhra Pradesh - DevNetJobsIndia.org
@@ -3253,7 +2602,7 @@
 | ... Read More</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>• 2. Purpose of the RFP:
 2.1  EAII is soliciting bids for:
@@ -3362,54 +2711,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFQ-Corporate Global Group Health Insurance Cover...
-Coalition for Disaster Resilient Infrastructure (...
-Location:
-India
-Apply by:
-23 Mar 2026
-HR Associate
-Inclusion Economics India Centre (IEIC) at IFMR
+Sr MEAL Officer, Preconception Nutrition and Care
+Nutrition International
 Location:
 Delhi
 Apply by:
+29 Mar 2026
+Academic Mentor
+Bharti Airtel Foundation
+Location:
+Sikkim, Assam, Jharkhand
+Apply by:
+09 Apr 2026
+Manager – Enterprise Promotion
+Project Concern International India (PCI India)
+Location:
+Bihar
+Apply by:
+13 Mar 2026
+RFP - Design, Development, Deployment and Mainten...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+RFP - Appointment of Agency for SEO Management an...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+Senior Program Manager/Program Manager, Doctors f...
+Lung Care Foundation
+Location:
+Haryana
+Apply by:
 08 Apr 2026
-Short Term Consultant - Workshop Facilitator for ...
-Fairtrade NAPP
-Location:
-Assam
-Apply by:
-31 Mar 2026
-State Manager
-Hindustan Latex Family Planning Promotion Trust (...
+Program Head - MIS And Technology
+Dhwani Foundation
+Location:
+Karnataka
+Apply by:
+08 Apr 2026
+Associate/Specialist-Supply Chain
+India Health Action Trust (IHAT)
 Location:
 Uttar Pradesh
 Apply by:
 22 Mar 2026
-State Project Officer
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-India
-Apply by:
-22 Mar 2026
-State Program Manager-HIV-CSC-North East
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-Assam
-Apply by:
-22 Mar 2026
-Neighbourhood Facilitator – Health &amp; NCDs
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
-Health Planner – Community Mobilization
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
 Jobseekers
 Register
 Login
@@ -3437,41 +2786,41 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F16" s="1" t="inlineStr">
+      <c r="F12" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G16" s="1" t="inlineStr">
+      <c r="G12" s="1" t="inlineStr">
         <is>
           <t>16-03-2026</t>
         </is>
       </c>
-      <c r="H16" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="I16" s="1" t="inlineStr">
+      <c r="H12" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I12" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287172</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr"/>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>Specialist – Communication</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Financial Management Service Foundation (FMSF) | Uttar Pradesh
-International Development - Specialist – Communication, Financial Management Service Foundation (FMSF), Uttar Pradesh - DevNetJobsIndia.org
+      <c r="B13" s="1" t="inlineStr"/>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>RFP - Design, Development, Deployment and Maintenance of Mobile Applicati...</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>YRGCARE | India
+International Development - RFP - Design, Development, Deployment and Maintenance of  Mobile Application for the Breakfree Platform, YRGCARE, India - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
@@ -3481,21 +2830,23 @@
 Broadcast Resume
 RFPs/Tenders
 Search Jobs
-Eve ... Read More</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>• Joining FMSF means becoming part of a passionate team dedicated to making a positive impact. We offer competitive compensation, opportunities for professional development, and a supportive work environment where your contributions are valued and recognized. If you are committed to driving positive change, promoting accountability and strengthening the development sector, we encourage you to apply for the position of Specialist – Communication at FMSF.
-• How to Apply:
-Apply online by clicking on the link:
-https://www.fmsfindia.org.in/apply-now/specialist-communication1
-You’re Resume to be accompanied with:
-Motivational letter justifying suitability for the position – role fitment based on present &amp; past work experience
-Current/last drawn compensation &amp; expected compensation
-CVs without Motivational Letter will not be considered
-FMSF is an Equal Opportunity Employer.
-Please note that only the shortlisted candidates will be contacted.
+Events
+Jobseekers:
+L ... Read More</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>• This Terms of Reference (ToR) defines the full scope of work, technical requirements, compliance standards, and performance expectations for the agency appointed to design, develop, deploy, and maintain the Breakfree mobile application for both Android and iOS platforms.
+For detailed information visit
+https://www.yrgmerf.org/procurement-notices
+or please check the complete version of the RFP attached below.
+• Job Email ID:
+rfp(at)yrgcare.org
+Download Attachment:
+Mobile Application Development_RFP_002_2026_Evaluation_Grid.pdf
+Download Attachment:
+Mobile Application Development_RFP_002_Mob_App_.pdf
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
@@ -3568,54 +2919,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFQ-Corporate Global Group Health Insurance Cover...
-Coalition for Disaster Resilient Infrastructure (...
-Location:
-India
-Apply by:
-23 Mar 2026
-HR Associate
-Inclusion Economics India Centre (IEIC) at IFMR
+Sr MEAL Officer, Preconception Nutrition and Care
+Nutrition International
 Location:
 Delhi
 Apply by:
+29 Mar 2026
+Academic Mentor
+Bharti Airtel Foundation
+Location:
+Sikkim, Assam, Jharkhand
+Apply by:
+09 Apr 2026
+Manager – Enterprise Promotion
+Project Concern International India (PCI India)
+Location:
+Bihar
+Apply by:
+13 Mar 2026
+RFP - Design, Development, Deployment and Mainten...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+RFP - Appointment of Agency for SEO Management an...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+Senior Program Manager/Program Manager, Doctors f...
+Lung Care Foundation
+Location:
+Haryana
+Apply by:
 08 Apr 2026
-Short Term Consultant - Workshop Facilitator for ...
-Fairtrade NAPP
-Location:
-Assam
-Apply by:
-31 Mar 2026
-State Manager
-Hindustan Latex Family Planning Promotion Trust (...
+Program Head - MIS And Technology
+Dhwani Foundation
+Location:
+Karnataka
+Apply by:
+08 Apr 2026
+Associate/Specialist-Supply Chain
+India Health Action Trust (IHAT)
 Location:
 Uttar Pradesh
 Apply by:
 22 Mar 2026
-State Project Officer
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-India
-Apply by:
-22 Mar 2026
-State Program Manager-HIV-CSC-North East
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-Assam
-Apply by:
-22 Mar 2026
-Neighbourhood Facilitator – Health &amp; NCDs
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
-Health Planner – Community Mobilization
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
 Jobseekers
 Register
 Login
@@ -3643,69 +2994,74 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G17" s="1" t="inlineStr">
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>Learning, Safety</t>
+        </is>
+      </c>
+      <c r="G13" s="1" t="inlineStr">
         <is>
           <t>19-03-2026</t>
         </is>
       </c>
-      <c r="H17" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="I17" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287207</t>
+      <c r="H13" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="I13" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=288064</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B18" s="1" t="inlineStr"/>
-      <c r="C18" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Consultancy for development of descriptive documentation of Ashiyana...</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Prerana | Mumbai, Maharashtra
-International Development - RFP - Consultancy for development of descriptive documentation of Ashiyana Implementation &amp; Practice Framework, and produce a replication-ready, Prerana, Maharashtra - DevNetJobsIndia.org
+      <c r="B14" s="1" t="inlineStr"/>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>RFP - Appointment of Agency for SEO Management and Meta (Facebook / Instag...</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>YRGCARE | India
+International Development - RFP - Appointment of Agency for SEO Management and Meta (Facebook / Instagram) Advertising, YRGCARE, India - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
 Register
 Home
 Value Membership
-Br ... Read More</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>• Submission Details
-Proposals must be submitted by email to:
-rashmi@preranaantitrafficking.org
-Subject line:
-Proposal – Aashiyana Implementation &amp; Practice Framework
-Deadline:
-21-03-26
-For detailed information, please check the complete version of the RFP attached below.
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers:
+Login
+|
+Regist ... Read More</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>• To drive sustained awareness, organic discoverability, and ethical user engagement, NACO/YRGCARE intends to appoint professional agencies to manage two complementary digital outreach functions: Search Engine Optimisation (SEO) and paid social outreach through Meta platforms (Facebook and Instagram). This ToR defines the full scope, expectations, compliance requirements, and monitoring framework for this appointment.
+For detailed information visit
+https://www.yrgmerf.org/procurement-notices
+or please check the complete version of the RFP attached below.
 • Job Email ID:
-rashmi(at)preranaantitrafficking.org
+rfp(at)yrgcare.org
 Download Attachment:
-Aashiyana- Framework Documentation- RFP- v2.doc
+RFP_001_2026_SEO_.pdf
+Download Attachment:
+RFP_001_2026_Evaluation_Grid_SEO.pdf
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
 Apply by:
-21 Mar 2026
+19 Mar 2026
 Access all the jobs and get ahead!
 Subscribe to Value Membership Now!
 Subscribe
@@ -3773,54 +3129,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFQ-Corporate Global Group Health Insurance Cover...
-Coalition for Disaster Resilient Infrastructure (...
-Location:
-India
-Apply by:
-23 Mar 2026
-HR Associate
-Inclusion Economics India Centre (IEIC) at IFMR
+Sr MEAL Officer, Preconception Nutrition and Care
+Nutrition International
 Location:
 Delhi
 Apply by:
+29 Mar 2026
+Academic Mentor
+Bharti Airtel Foundation
+Location:
+Sikkim, Assam, Jharkhand
+Apply by:
+09 Apr 2026
+Manager – Enterprise Promotion
+Project Concern International India (PCI India)
+Location:
+Bihar
+Apply by:
+13 Mar 2026
+RFP - Design, Development, Deployment and Mainten...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+RFP - Appointment of Agency for SEO Management an...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+Senior Program Manager/Program Manager, Doctors f...
+Lung Care Foundation
+Location:
+Haryana
+Apply by:
 08 Apr 2026
-Short Term Consultant - Workshop Facilitator for ...
-Fairtrade NAPP
-Location:
-Assam
-Apply by:
-31 Mar 2026
-State Manager
-Hindustan Latex Family Planning Promotion Trust (...
+Program Head - MIS And Technology
+Dhwani Foundation
+Location:
+Karnataka
+Apply by:
+08 Apr 2026
+Associate/Specialist-Supply Chain
+India Health Action Trust (IHAT)
 Location:
 Uttar Pradesh
 Apply by:
 22 Mar 2026
-State Project Officer
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-India
-Apply by:
-22 Mar 2026
-State Program Manager-HIV-CSC-North East
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-Assam
-Apply by:
-22 Mar 2026
-Neighbourhood Facilitator – Health &amp; NCDs
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
-Health Planner – Community Mobilization
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
 Jobseekers
 Register
 Login
@@ -3848,41 +3204,41 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F18" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G18" s="1" t="inlineStr">
-        <is>
-          <t>21-03-2026</t>
-        </is>
-      </c>
-      <c r="H18" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="I18" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287890</t>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t>19-03-2026</t>
+        </is>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="I14" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=288063</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr"/>
-      <c r="C19" s="1" t="inlineStr">
-        <is>
-          <t>Specialist - Grants</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="B15" s="1" t="inlineStr"/>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>Specialist – Communication</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Financial Management Service Foundation (FMSF) | Uttar Pradesh
-International Development - Specialist - Grants, Financial Management Service Foundation (FMSF), Uttar Pradesh - DevNetJobsIndia.org
+International Development - Specialist – Communication, Financial Management Service Foundation (FMSF), Uttar Pradesh - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
@@ -3892,27 +3248,26 @@
 Broadcast Resume
 RFPs/Tenders
 Search Jobs
-Events
-Job ... Read More</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>• Joining FMSF means becoming part of a passionate team dedicated to making a positive impact. We offer competitive compensation, opportunities for professional development, and a supportive work environment where your contributions are valued and recognized. If you are committed to driving positive change, promoting accountability and strengthening the development sector, we encourage you to apply for the position of Specialist - Grants at FMSF.
+Eve ... Read More</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>• Joining FMSF means becoming part of a passionate team dedicated to making a positive impact. We offer competitive compensation, opportunities for professional development, and a supportive work environment where your contributions are valued and recognized. If you are committed to driving positive change, promoting accountability and strengthening the development sector, we encourage you to apply for the position of Specialist – Communication at FMSF.
+• How to Apply:
+Apply online by clicking on the link:
+https://www.fmsfindia.org.in/apply-now/specialist-communication1
 You’re Resume to be accompanied with:
 Motivational letter justifying suitability for the position – role fitment based on present &amp; past work experience
 Current/last drawn compensation &amp; expected compensation
 CVs without Motivational Letter will not be considered
-• How to Apply:
-Apply online by clicking on the link
-https://www.fmsfindia.org.in/apply-now/specialist-grants
 FMSF is an Equal Opportunity Employer.
 Please note that only the shortlisted candidates will be contacted.
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
 Apply by:
-21 Mar 2026
+19 Mar 2026
 Access all the jobs and get ahead!
 Subscribe to Value Membership Now!
 Subscribe
@@ -3980,54 +3335,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFQ-Corporate Global Group Health Insurance Cover...
-Coalition for Disaster Resilient Infrastructure (...
-Location:
-India
-Apply by:
-23 Mar 2026
-HR Associate
-Inclusion Economics India Centre (IEIC) at IFMR
+Sr MEAL Officer, Preconception Nutrition and Care
+Nutrition International
 Location:
 Delhi
 Apply by:
+29 Mar 2026
+Academic Mentor
+Bharti Airtel Foundation
+Location:
+Sikkim, Assam, Jharkhand
+Apply by:
+09 Apr 2026
+Manager – Enterprise Promotion
+Project Concern International India (PCI India)
+Location:
+Bihar
+Apply by:
+13 Mar 2026
+RFP - Design, Development, Deployment and Mainten...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+RFP - Appointment of Agency for SEO Management an...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+Senior Program Manager/Program Manager, Doctors f...
+Lung Care Foundation
+Location:
+Haryana
+Apply by:
 08 Apr 2026
-Short Term Consultant - Workshop Facilitator for ...
-Fairtrade NAPP
-Location:
-Assam
-Apply by:
-31 Mar 2026
-State Manager
-Hindustan Latex Family Planning Promotion Trust (...
+Program Head - MIS And Technology
+Dhwani Foundation
+Location:
+Karnataka
+Apply by:
+08 Apr 2026
+Associate/Specialist-Supply Chain
+India Health Action Trust (IHAT)
 Location:
 Uttar Pradesh
 Apply by:
 22 Mar 2026
-State Project Officer
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-India
-Apply by:
-22 Mar 2026
-State Program Manager-HIV-CSC-North East
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-Assam
-Apply by:
-22 Mar 2026
-Neighbourhood Facilitator – Health &amp; NCDs
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
-Health Planner – Community Mobilization
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
 Jobseekers
 Register
 Login
@@ -4055,44 +3410,456 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F19" s="1" t="inlineStr">
+      <c r="F15" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G19" s="1" t="inlineStr">
+      <c r="G15" s="1" t="inlineStr">
+        <is>
+          <t>19-03-2026</t>
+        </is>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="I15" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287207</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr"/>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>Specialist - Grants</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Financial Management Service Foundation (FMSF) | Uttar Pradesh
+International Development - Specialist - Grants, Financial Management Service Foundation (FMSF), Uttar Pradesh - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Job ... Read More</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>• Joining FMSF means becoming part of a passionate team dedicated to making a positive impact. We offer competitive compensation, opportunities for professional development, and a supportive work environment where your contributions are valued and recognized. If you are committed to driving positive change, promoting accountability and strengthening the development sector, we encourage you to apply for the position of Specialist - Grants at FMSF.
+You’re Resume to be accompanied with:
+Motivational letter justifying suitability for the position – role fitment based on present &amp; past work experience
+Current/last drawn compensation &amp; expected compensation
+CVs without Motivational Letter will not be considered
+• How to Apply:
+Apply online by clicking on the link
+https://www.fmsfindia.org.in/apply-now/specialist-grants
+FMSF is an Equal Opportunity Employer.
+Please note that only the shortlisted candidates will be contacted.
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+21 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+Sr MEAL Officer, Preconception Nutrition and Care
+Nutrition International
+Location:
+Delhi
+Apply by:
+29 Mar 2026
+Academic Mentor
+Bharti Airtel Foundation
+Location:
+Sikkim, Assam, Jharkhand
+Apply by:
+09 Apr 2026
+Manager – Enterprise Promotion
+Project Concern International India (PCI India)
+Location:
+Bihar
+Apply by:
+13 Mar 2026
+RFP - Design, Development, Deployment and Mainten...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+RFP - Appointment of Agency for SEO Management an...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+Senior Program Manager/Program Manager, Doctors f...
+Lung Care Foundation
+Location:
+Haryana
+Apply by:
+08 Apr 2026
+Program Head - MIS And Technology
+Dhwani Foundation
+Location:
+Karnataka
+Apply by:
+08 Apr 2026
+Associate/Specialist-Supply Chain
+India Health Action Trust (IHAT)
+Location:
+Uttar Pradesh
+Apply by:
+22 Mar 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G16" s="1" t="inlineStr">
         <is>
           <t>21-03-2026</t>
         </is>
       </c>
-      <c r="H19" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="I19" s="1" t="inlineStr">
+      <c r="H16" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="I16" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287318</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr"/>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="B17" s="1" t="inlineStr"/>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>RFP - Consultancy for development of descriptive documentation of Ashiyana...</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Prerana | Mumbai, Maharashtra
+International Development - RFP - Consultancy for development of descriptive documentation of Ashiyana Implementation &amp; Practice Framework, and produce a replication-ready, Prerana, Maharashtra - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Br ... Read More</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>• Submission Details
+Proposals must be submitted by email to:
+rashmi@preranaantitrafficking.org
+Subject line:
+Proposal – Aashiyana Implementation &amp; Practice Framework
+Deadline:
+21-03-26
+For detailed information, please check the complete version of the RFP attached below.
+• Job Email ID:
+rashmi(at)preranaantitrafficking.org
+Download Attachment:
+Aashiyana- Framework Documentation- RFP- v2.doc
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+21 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+Sr MEAL Officer, Preconception Nutrition and Care
+Nutrition International
+Location:
+Delhi
+Apply by:
+29 Mar 2026
+Academic Mentor
+Bharti Airtel Foundation
+Location:
+Sikkim, Assam, Jharkhand
+Apply by:
+09 Apr 2026
+Manager – Enterprise Promotion
+Project Concern International India (PCI India)
+Location:
+Bihar
+Apply by:
+13 Mar 2026
+RFP - Design, Development, Deployment and Mainten...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+RFP - Appointment of Agency for SEO Management an...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+Senior Program Manager/Program Manager, Doctors f...
+Lung Care Foundation
+Location:
+Haryana
+Apply by:
+08 Apr 2026
+Program Head - MIS And Technology
+Dhwani Foundation
+Location:
+Karnataka
+Apply by:
+08 Apr 2026
+Associate/Specialist-Supply Chain
+India Health Action Trust (IHAT)
+Location:
+Uttar Pradesh
+Apply by:
+22 Mar 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G17" s="1" t="inlineStr">
+        <is>
+          <t>21-03-2026</t>
+        </is>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="I17" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287890</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr"/>
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>RFP - Study On SC-DMPA In Rajasthan- Clients And Providers Perspectives On...</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Centre For Community Economics And Development Consultants Society- CECOEDECON | Jaipur, Rajasthan
 International Development - RFP - Study On SC-DMPA In Rajasthan- Clients And Providers Perspectives On SC-DMPA In Rajasthan, Centre For Community Economics And Development Consultants Society- CECOEDE ... Read More</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>• Despite India’s achievement of replacement-level fertility, unmet need for contraception—particularly for spacing methods—remains substantial, with modern contraceptive use at 56.4% (2019–21), highlighting persistent gaps in access and choice, especially among vulnerable populations. Expanding the contraceptive method mix through innovative, user-centred approaches is therefore essential to meeting national commitments under FP2030 and the Sustainable Development Goals. In this context, the Government of India’s introduction of subcutaneous DMPA (DMPA-SC) as a self-care option under the National Family Planning Programme in 2023 represents a strategic step toward enhancing women’s autonomy, privacy, and convenience in contraceptive use. Global and national evidence indicates strong feasibility and acceptability of self-administered DMPA-SC among both users and providers; however, successful implementation requires an in-depth understanding of user experiences and health system readiness. This study, to be conducted in Jaipur-1, Jaisalmer and Sawai Madhopur districts of Rajasthan, aims to examine the perspectives &amp; experience of current SC-DMPA users and explore healthcare providers’ views on enabling and generating actionable evidence to inform effective scale-up of SC-DMPA within India’s public health system.
 CECOEDECON, with support from UNFPA, is implementing the roll-out of subcutaneous DMPA (SC-DMPA) in selected pilot districts of Rajasthan in the public health facilities, in collaboration with the Department of Health &amp; Family Welfare, Government of Rajasthan.
@@ -4227,54 +3994,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFQ-Corporate Global Group Health Insurance Cover...
-Coalition for Disaster Resilient Infrastructure (...
-Location:
-India
-Apply by:
-23 Mar 2026
-HR Associate
-Inclusion Economics India Centre (IEIC) at IFMR
+Sr MEAL Officer, Preconception Nutrition and Care
+Nutrition International
 Location:
 Delhi
 Apply by:
+29 Mar 2026
+Academic Mentor
+Bharti Airtel Foundation
+Location:
+Sikkim, Assam, Jharkhand
+Apply by:
+09 Apr 2026
+Manager – Enterprise Promotion
+Project Concern International India (PCI India)
+Location:
+Bihar
+Apply by:
+13 Mar 2026
+RFP - Design, Development, Deployment and Mainten...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+RFP - Appointment of Agency for SEO Management an...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+Senior Program Manager/Program Manager, Doctors f...
+Lung Care Foundation
+Location:
+Haryana
+Apply by:
 08 Apr 2026
-Short Term Consultant - Workshop Facilitator for ...
-Fairtrade NAPP
-Location:
-Assam
-Apply by:
-31 Mar 2026
-State Manager
-Hindustan Latex Family Planning Promotion Trust (...
+Program Head - MIS And Technology
+Dhwani Foundation
+Location:
+Karnataka
+Apply by:
+08 Apr 2026
+Associate/Specialist-Supply Chain
+India Health Action Trust (IHAT)
 Location:
 Uttar Pradesh
 Apply by:
 22 Mar 2026
-State Project Officer
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-India
-Apply by:
-22 Mar 2026
-State Program Manager-HIV-CSC-North East
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-Assam
-Apply by:
-22 Mar 2026
-Neighbourhood Facilitator – Health &amp; NCDs
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
-Health Planner – Community Mobilization
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
 Jobseekers
 Register
 Login
@@ -4302,38 +4069,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F20" s="1" t="inlineStr">
+      <c r="F18" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G20" s="1" t="inlineStr">
+      <c r="G18" s="1" t="inlineStr">
         <is>
           <t>22-03-2026</t>
         </is>
       </c>
-      <c r="H20" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="I20" s="1" t="inlineStr">
+      <c r="H18" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="I18" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287322</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr"/>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="B19" s="1" t="inlineStr"/>
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>RFQ-Corporate Global Group Health Insurance Coverage</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Coalition for Disaster Resilient Infrastructure (CDRI) | India
 International Development - RFQ-Corporate Global Group Health Insurance Coverage, Coalition for Disaster Resilient Infrastructure (CDRI), India - DevNetJobsIndia.org
@@ -4347,7 +4114,7 @@
 RF ... Read More</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>• The specific staff details, policy document, along with the claim MIS will only be shared with the interested bidders upon request to the email ID
 :
@@ -4505,54 +4272,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFQ-Corporate Global Group Health Insurance Cover...
-Coalition for Disaster Resilient Infrastructure (...
-Location:
-India
-Apply by:
-23 Mar 2026
-HR Associate
-Inclusion Economics India Centre (IEIC) at IFMR
+Sr MEAL Officer, Preconception Nutrition and Care
+Nutrition International
 Location:
 Delhi
 Apply by:
+29 Mar 2026
+Academic Mentor
+Bharti Airtel Foundation
+Location:
+Sikkim, Assam, Jharkhand
+Apply by:
+09 Apr 2026
+Manager – Enterprise Promotion
+Project Concern International India (PCI India)
+Location:
+Bihar
+Apply by:
+13 Mar 2026
+RFP - Design, Development, Deployment and Mainten...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+RFP - Appointment of Agency for SEO Management an...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+Senior Program Manager/Program Manager, Doctors f...
+Lung Care Foundation
+Location:
+Haryana
+Apply by:
 08 Apr 2026
-Short Term Consultant - Workshop Facilitator for ...
-Fairtrade NAPP
-Location:
-Assam
-Apply by:
-31 Mar 2026
-State Manager
-Hindustan Latex Family Planning Promotion Trust (...
+Program Head - MIS And Technology
+Dhwani Foundation
+Location:
+Karnataka
+Apply by:
+08 Apr 2026
+Associate/Specialist-Supply Chain
+India Health Action Trust (IHAT)
 Location:
 Uttar Pradesh
 Apply by:
 22 Mar 2026
-State Project Officer
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-India
-Apply by:
-22 Mar 2026
-State Program Manager-HIV-CSC-North East
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-Assam
-Apply by:
-22 Mar 2026
-Neighbourhood Facilitator – Health &amp; NCDs
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
-Health Planner – Community Mobilization
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
 Jobseekers
 Register
 Login
@@ -4580,38 +4347,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F21" s="1" t="inlineStr">
+      <c r="F19" s="1" t="inlineStr">
         <is>
           <t>Climate, Safety</t>
         </is>
       </c>
-      <c r="G21" s="1" t="inlineStr">
+      <c r="G19" s="1" t="inlineStr">
         <is>
           <t>23-03-2026</t>
         </is>
       </c>
-      <c r="H21" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="I21" s="1" t="inlineStr">
+      <c r="H19" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="I19" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=288006</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr"/>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="B20" s="1" t="inlineStr"/>
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>EoI – Mobile Medical Units, Ai-Enabled Tb Screening &amp; Supply Of Medical An...</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Ashray Foundation | Korba, Chattisgarh (Delivery Location), Gujarat
 International Development - EoI – Mobile Medical Units, Ai-Enabled Tb Screening &amp; Supply Of Medical And Nutritional Support, Ashray Foundation, Gujarat - DevNetJobsIndia.org
@@ -4624,7 +4391,7 @@
 Broadc ... Read More</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>• Ashray Foundation invites eligible and experienced agencies to submit their Expression of Interest / for the following scope of work:
 Fabrication of Mobile Medical Units (MMUs) – 2 Units
@@ -4713,54 +4480,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFQ-Corporate Global Group Health Insurance Cover...
-Coalition for Disaster Resilient Infrastructure (...
-Location:
-India
-Apply by:
-23 Mar 2026
-HR Associate
-Inclusion Economics India Centre (IEIC) at IFMR
+Sr MEAL Officer, Preconception Nutrition and Care
+Nutrition International
 Location:
 Delhi
 Apply by:
+29 Mar 2026
+Academic Mentor
+Bharti Airtel Foundation
+Location:
+Sikkim, Assam, Jharkhand
+Apply by:
+09 Apr 2026
+Manager – Enterprise Promotion
+Project Concern International India (PCI India)
+Location:
+Bihar
+Apply by:
+13 Mar 2026
+RFP - Design, Development, Deployment and Mainten...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+RFP - Appointment of Agency for SEO Management an...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+Senior Program Manager/Program Manager, Doctors f...
+Lung Care Foundation
+Location:
+Haryana
+Apply by:
 08 Apr 2026
-Short Term Consultant - Workshop Facilitator for ...
-Fairtrade NAPP
-Location:
-Assam
-Apply by:
-31 Mar 2026
-State Manager
-Hindustan Latex Family Planning Promotion Trust (...
+Program Head - MIS And Technology
+Dhwani Foundation
+Location:
+Karnataka
+Apply by:
+08 Apr 2026
+Associate/Specialist-Supply Chain
+India Health Action Trust (IHAT)
 Location:
 Uttar Pradesh
 Apply by:
 22 Mar 2026
-State Project Officer
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-India
-Apply by:
-22 Mar 2026
-State Program Manager-HIV-CSC-North East
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-Assam
-Apply by:
-22 Mar 2026
-Neighbourhood Facilitator – Health &amp; NCDs
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
-Health Planner – Community Mobilization
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
 Jobseekers
 Register
 Login
@@ -4788,38 +4555,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F22" s="1" t="inlineStr">
+      <c r="F20" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G22" s="1" t="inlineStr">
+      <c r="G20" s="1" t="inlineStr">
         <is>
           <t>24-03-2026</t>
         </is>
       </c>
-      <c r="H22" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="I22" s="1" t="inlineStr">
+      <c r="H20" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="I20" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287319</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr"/>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="B21" s="1" t="inlineStr"/>
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>RFP - End of Program Evaluation Accelerating Access to Safe Water and San...</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Water.org | Bangladesh, Cambodia, India
 International Development - RFP - End of Program Evaluation  Accelerating Access to Safe Water and Sanitation, Financing, Water.org, India - DevNetJobsIndia.org
@@ -4835,7 +4602,7 @@
 Event ... Read More</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>• The evaluation will require the firm to facilitate and coordinate with Water.org staff and partners. The program requires the firm to submit the deliverables outlined in section 2 Scope of Work.
 C.
@@ -4942,54 +4709,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFQ-Corporate Global Group Health Insurance Cover...
-Coalition for Disaster Resilient Infrastructure (...
-Location:
-India
-Apply by:
-23 Mar 2026
-HR Associate
-Inclusion Economics India Centre (IEIC) at IFMR
+Sr MEAL Officer, Preconception Nutrition and Care
+Nutrition International
 Location:
 Delhi
 Apply by:
+29 Mar 2026
+Academic Mentor
+Bharti Airtel Foundation
+Location:
+Sikkim, Assam, Jharkhand
+Apply by:
+09 Apr 2026
+Manager – Enterprise Promotion
+Project Concern International India (PCI India)
+Location:
+Bihar
+Apply by:
+13 Mar 2026
+RFP - Design, Development, Deployment and Mainten...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+RFP - Appointment of Agency for SEO Management an...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+Senior Program Manager/Program Manager, Doctors f...
+Lung Care Foundation
+Location:
+Haryana
+Apply by:
 08 Apr 2026
-Short Term Consultant - Workshop Facilitator for ...
-Fairtrade NAPP
-Location:
-Assam
-Apply by:
-31 Mar 2026
-State Manager
-Hindustan Latex Family Planning Promotion Trust (...
+Program Head - MIS And Technology
+Dhwani Foundation
+Location:
+Karnataka
+Apply by:
+08 Apr 2026
+Associate/Specialist-Supply Chain
+India Health Action Trust (IHAT)
 Location:
 Uttar Pradesh
 Apply by:
 22 Mar 2026
-State Project Officer
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-India
-Apply by:
-22 Mar 2026
-State Program Manager-HIV-CSC-North East
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-Assam
-Apply by:
-22 Mar 2026
-Neighbourhood Facilitator – Health &amp; NCDs
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
-Health Planner – Community Mobilization
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
 Jobseekers
 Register
 Login
@@ -5017,38 +4784,267 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F23" s="1" t="inlineStr">
+      <c r="F21" s="1" t="inlineStr">
         <is>
           <t>Governance, Safety</t>
         </is>
       </c>
-      <c r="G23" s="1" t="inlineStr">
+      <c r="G21" s="1" t="inlineStr">
         <is>
           <t>25-03-2026</t>
         </is>
       </c>
-      <c r="H23" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="I23" s="1" t="inlineStr">
+      <c r="H21" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="I21" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287835</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr"/>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="B22" s="1" t="inlineStr"/>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>Junior Research Technicians / Senior Project Asso...</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Starshield Security Solution Pvt.Ltd | Uttar Pradesh
+International Development - Junior Research Technicians / Senior Project Associate, Starshield Security Solution Pvt.Ltd, Uttar Pradesh - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search ... Read More</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>• Eligibility Criteria
+Qualification
+:
+Intermediate with 2–3 years of relevant experience
+OR
+Graduate with 1–2 years of relevant experience
+Skills &amp; Experience (Mandatory):
+Experience in agriculture field operations and data collection
+Basic knowledge of MS Office (Word &amp; Excel)
+Experience in rice-wheat cropping system production preferred
+Good coordination and communication skills
+Willingness to travel and work in field conditions
+Knowledge of smart mobile apps for data survey and data recording
+Knowledge on agri machinery
+Community mobilization and Work with Farmers group/FPCs
+The applicants must have a two-wheeler vehicle and license with them
+Key Performance Indicators
+Timely support to demonstrations, trainings, and field activities
+Accurate data collection and documentation
+Proper maintenance of equipment and field sites
+Positive feedback from farmers and stakeholders
+Creation of new service providers
+Application Details
+Interested candidates are requested to fill-out the shared application form and submit their updated CV via email to
+communications@starshieldsolution.com
+with the subject line:
+Application for Junior Research Technician (IRRI Project Deployment)
+.
+Only shortlisted candidates who complete the required documentation will be considered for subsequent stages of selection.
+Selection will be done on a first-come-first-served basis. Applications received up to Thursday each week will be reviewed, and interviews will be conducted in the following week. As soon as we shall finish all recruitment, we will take the advertisement off.
+• Job Email ID:
+communications(at)starshieldsolution.com
+Download Attachment:
+Application Proforma_Junior Research Technicians -  Senior Project Associate.doc
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+30 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Chief Programs Officer for Project Potential
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Program Lead- Finance &amp; Compliance for Project Po...
+Project Potential
+Location:
+Bihar
+Apply by:
+11 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+Sr MEAL Officer, Preconception Nutrition and Care
+Nutrition International
+Location:
+Delhi
+Apply by:
+29 Mar 2026
+Academic Mentor
+Bharti Airtel Foundation
+Location:
+Sikkim, Assam, Jharkhand
+Apply by:
+09 Apr 2026
+Manager – Enterprise Promotion
+Project Concern International India (PCI India)
+Location:
+Bihar
+Apply by:
+13 Mar 2026
+RFP - Design, Development, Deployment and Mainten...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+RFP - Appointment of Agency for SEO Management an...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+Senior Program Manager/Program Manager, Doctors f...
+Lung Care Foundation
+Location:
+Haryana
+Apply by:
+08 Apr 2026
+Program Head - MIS And Technology
+Dhwani Foundation
+Location:
+Karnataka
+Apply by:
+08 Apr 2026
+Associate/Specialist-Supply Chain
+India Health Action Trust (IHAT)
+Location:
+Uttar Pradesh
+Apply by:
+22 Mar 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F22" s="1" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="G22" s="1" t="inlineStr">
+        <is>
+          <t>30-03-2026</t>
+        </is>
+      </c>
+      <c r="H22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="I22" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287635</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr"/>
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>Agriculture Research Development Officer / Projec...</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Starshield Security Solution Pvt.Ltd | Uttar Pradesh
 International Development - Agriculture Research Development Officer / Project Scientist III, Starshield Security Solution Pvt.Ltd, Uttar Pradesh - DevNetJobsIndia.org
@@ -5062,7 +5058,7 @@
 RFPs/Tende ... Read More</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>• Eligibility Criteria
 Qualification:
@@ -5171,54 +5167,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFQ-Corporate Global Group Health Insurance Cover...
-Coalition for Disaster Resilient Infrastructure (...
-Location:
-India
-Apply by:
-23 Mar 2026
-HR Associate
-Inclusion Economics India Centre (IEIC) at IFMR
+Sr MEAL Officer, Preconception Nutrition and Care
+Nutrition International
 Location:
 Delhi
 Apply by:
+29 Mar 2026
+Academic Mentor
+Bharti Airtel Foundation
+Location:
+Sikkim, Assam, Jharkhand
+Apply by:
+09 Apr 2026
+Manager – Enterprise Promotion
+Project Concern International India (PCI India)
+Location:
+Bihar
+Apply by:
+13 Mar 2026
+RFP - Design, Development, Deployment and Mainten...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+RFP - Appointment of Agency for SEO Management an...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+Senior Program Manager/Program Manager, Doctors f...
+Lung Care Foundation
+Location:
+Haryana
+Apply by:
 08 Apr 2026
-Short Term Consultant - Workshop Facilitator for ...
-Fairtrade NAPP
-Location:
-Assam
-Apply by:
-31 Mar 2026
-State Manager
-Hindustan Latex Family Planning Promotion Trust (...
+Program Head - MIS And Technology
+Dhwani Foundation
+Location:
+Karnataka
+Apply by:
+08 Apr 2026
+Associate/Specialist-Supply Chain
+India Health Action Trust (IHAT)
 Location:
 Uttar Pradesh
 Apply by:
 22 Mar 2026
-State Project Officer
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-India
-Apply by:
-22 Mar 2026
-State Program Manager-HIV-CSC-North East
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-Assam
-Apply by:
-22 Mar 2026
-Neighbourhood Facilitator – Health &amp; NCDs
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
-Health Planner – Community Mobilization
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
 Jobseekers
 Register
 Login
@@ -5246,41 +5242,41 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F24" s="1" t="inlineStr">
+      <c r="F23" s="1" t="inlineStr">
         <is>
           <t>Learning, Safety</t>
         </is>
       </c>
-      <c r="G24" s="1" t="inlineStr">
+      <c r="G23" s="1" t="inlineStr">
         <is>
           <t>30-03-2026</t>
         </is>
       </c>
-      <c r="H24" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="I24" s="1" t="inlineStr">
+      <c r="H23" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="I23" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287636</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr"/>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>Junior Research Technicians / Senior Project Asso...</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Starshield Security Solution Pvt.Ltd | Uttar Pradesh
-International Development - Junior Research Technicians / Senior Project Associate, Starshield Security Solution Pvt.Ltd, Uttar Pradesh - DevNetJobsIndia.org
+      <c r="B24" s="1" t="inlineStr"/>
+      <c r="C24" s="1" t="inlineStr">
+        <is>
+          <t>Sector Experts</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Academy of Management Studies (AMS) | India
+International Development - Sector Experts, Academy of Management Studies (AMS), India - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
@@ -5289,50 +5285,44 @@
 Value Membership
 Broadcast Resume
 RFPs/Tenders
-Search ... Read More</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>• Eligibility Criteria
-Qualification
-:
-Intermediate with 2–3 years of relevant experience
-OR
-Graduate with 1–2 years of relevant experience
-Skills &amp; Experience (Mandatory):
-Experience in agriculture field operations and data collection
-Basic knowledge of MS Office (Word &amp; Excel)
-Experience in rice-wheat cropping system production preferred
-Good coordination and communication skills
-Willingness to travel and work in field conditions
-Knowledge of smart mobile apps for data survey and data recording
-Knowledge on agri machinery
-Community mobilization and Work with Farmers group/FPCs
-The applicants must have a two-wheeler vehicle and license with them
-Key Performance Indicators
-Timely support to demonstrations, trainings, and field activities
-Accurate data collection and documentation
-Proper maintenance of equipment and field sites
-Positive feedback from farmers and stakeholders
-Creation of new service providers
-Application Details
-Interested candidates are requested to fill-out the shared application form and submit their updated CV via email to
-communications@starshieldsolution.com
-with the subject line:
-Application for Junior Research Technician (IRRI Project Deployment)
-.
-Only shortlisted candidates who complete the required documentation will be considered for subsequent stages of selection.
-Selection will be done on a first-come-first-served basis. Applications received up to Thursday each week will be reviewed, and interviews will be conducted in the following week. As soon as we shall finish all recruitment, we will take the advertisement off.
+Search Jobs
+Events
+Jobseekers:
+Login
+|
+Register
+Jobseekers Login ... Read More</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>• Eligibility
+Postgraduate degree / Ph.D. in relevant or allied disciplines
+Minimum 5 years of relevant experience
+Experience of working with Government Departments / International Agencies preferred
+Demonstrated experience in research, monitoring &amp; evaluation, or technical advisory role
+Engagement Terms
+Shortlisted Experts shall be empaneled for a duration of 1 year which is extendable based on mutual agreement. Experts shall be engaged in short-term project-based assignments that organization undertakes in relevant sectors. The duration of engagement, project-specific roles and responsibilities, and remuneration will be decided as per project requirements and expertise level.
+• How to Apply
+Interested candidates may mail their detailed CV along with a recent photograph by
+31st March, 2026
+to
+hrd@amsindia.org
+mentioning“
+Sector Experts – Sector Name
+” in the subject line. The applicants must also mention in their emails the following details:
+Area(s) of specialization
+Current status of Employment
+Expected professional fee (daily/monthly)
 • Job Email ID:
-communications(at)starshieldsolution.com
+hrd(at)amsindia.org
 Download Attachment:
-Application Proforma_Junior Research Technicians -  Senior Project Associate.doc
+Empanelment of Experts.pdf
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
 Apply by:
-30 Mar 2026
+31 Mar 2026
 Access all the jobs and get ahead!
 Subscribe to Value Membership Now!
 Subscribe
@@ -5400,54 +5390,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFQ-Corporate Global Group Health Insurance Cover...
-Coalition for Disaster Resilient Infrastructure (...
-Location:
-India
-Apply by:
-23 Mar 2026
-HR Associate
-Inclusion Economics India Centre (IEIC) at IFMR
+Sr MEAL Officer, Preconception Nutrition and Care
+Nutrition International
 Location:
 Delhi
 Apply by:
+29 Mar 2026
+Academic Mentor
+Bharti Airtel Foundation
+Location:
+Sikkim, Assam, Jharkhand
+Apply by:
+09 Apr 2026
+Manager – Enterprise Promotion
+Project Concern International India (PCI India)
+Location:
+Bihar
+Apply by:
+13 Mar 2026
+RFP - Design, Development, Deployment and Mainten...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+RFP - Appointment of Agency for SEO Management an...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+Senior Program Manager/Program Manager, Doctors f...
+Lung Care Foundation
+Location:
+Haryana
+Apply by:
 08 Apr 2026
-Short Term Consultant - Workshop Facilitator for ...
-Fairtrade NAPP
-Location:
-Assam
-Apply by:
-31 Mar 2026
-State Manager
-Hindustan Latex Family Planning Promotion Trust (...
+Program Head - MIS And Technology
+Dhwani Foundation
+Location:
+Karnataka
+Apply by:
+08 Apr 2026
+Associate/Specialist-Supply Chain
+India Health Action Trust (IHAT)
 Location:
 Uttar Pradesh
 Apply by:
 22 Mar 2026
-State Project Officer
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-India
-Apply by:
-22 Mar 2026
-State Program Manager-HIV-CSC-North East
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-Assam
-Apply by:
-22 Mar 2026
-Neighbourhood Facilitator – Health &amp; NCDs
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
-Health Planner – Community Mobilization
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
 Jobseekers
 Register
 Login
@@ -5475,41 +5465,41 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F25" s="1" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="G25" s="1" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="H25" s="1" t="n">
+      <c r="F24" s="1" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G24" s="1" t="inlineStr">
+        <is>
+          <t>31-03-2026</t>
+        </is>
+      </c>
+      <c r="H24" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="I25" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287635</t>
+      <c r="I24" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287726</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr"/>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>Sector Experts</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Academy of Management Studies (AMS) | India
-International Development - Sector Experts, Academy of Management Studies (AMS), India - DevNetJobsIndia.org
+      <c r="B25" s="1" t="inlineStr"/>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>Associate – Finance and Operations</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Financial Management Service Foundation (FMSF) | Uttar Pradesh
+International Development - Associate – Finance and Operations, Financial Management Service Foundation (FMSF), Uttar Pradesh - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
@@ -5518,44 +5508,26 @@
 Value Membership
 Broadcast Resume
 RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Login
-|
-Register
-Jobseekers Login ... Read More</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>• Eligibility
-Postgraduate degree / Ph.D. in relevant or allied disciplines
-Minimum 5 years of relevant experience
-Experience of working with Government Departments / International Agencies preferred
-Demonstrated experience in research, monitoring &amp; evaluation, or technical advisory role
-Engagement Terms
-Shortlisted Experts shall be empaneled for a duration of 1 year which is extendable based on mutual agreement. Experts shall be engaged in short-term project-based assignments that organization undertakes in relevant sectors. The duration of engagement, project-specific roles and responsibilities, and remuneration will be decided as per project requirements and expertise level.
-• How to Apply
-Interested candidates may mail their detailed CV along with a recent photograph by
-31st March, 2026
-to
-hrd@amsindia.org
-mentioning“
-Sector Experts – Sector Name
-” in the subject line. The applicants must also mention in their emails the following details:
-Area(s) of specialization
-Current status of Employment
-Expected professional fee (daily/monthly)
-• Job Email ID:
-hrd(at)amsindia.org
-Download Attachment:
-Empanelment of Experts.pdf
+Search ... Read More</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>• Joining FMSF means becoming part of a passionate team dedicated to making a positive impact. We offer competitive compensation, opportunities for professional development, and a supportive work environment where your contributions are valued and recognized. If you are committed to driving positive change, promoting accountability and strengthening the development sector, we encourage you to apply for the position of
+Associate – Finance and Operations
+at FMSF.
+You’re Resume to be accompanied with:
+Motivational letter justifying suitability for the position – role fitment based on present &amp; past work experience
+Current/last drawn compensation &amp; expected compensation
+CVs without Motivational Letter will not be considered
+FMSF is an Equal Opportunity Employer.
+Please note that only the shortlisted candidates will be contacted
+Apply Here
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
 Apply by:
-31 Mar 2026
+05 Apr 2026
 Access all the jobs and get ahead!
 Subscribe to Value Membership Now!
 Subscribe
@@ -5623,54 +5595,54 @@
 11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-RFQ-Corporate Global Group Health Insurance Cover...
-Coalition for Disaster Resilient Infrastructure (...
-Location:
-India
-Apply by:
-23 Mar 2026
-HR Associate
-Inclusion Economics India Centre (IEIC) at IFMR
+Sr MEAL Officer, Preconception Nutrition and Care
+Nutrition International
 Location:
 Delhi
 Apply by:
+29 Mar 2026
+Academic Mentor
+Bharti Airtel Foundation
+Location:
+Sikkim, Assam, Jharkhand
+Apply by:
+09 Apr 2026
+Manager – Enterprise Promotion
+Project Concern International India (PCI India)
+Location:
+Bihar
+Apply by:
+13 Mar 2026
+RFP - Design, Development, Deployment and Mainten...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+RFP - Appointment of Agency for SEO Management an...
+YRGCARE
+Location:
+India
+Apply by:
+19 Mar 2026
+Senior Program Manager/Program Manager, Doctors f...
+Lung Care Foundation
+Location:
+Haryana
+Apply by:
 08 Apr 2026
-Short Term Consultant - Workshop Facilitator for ...
-Fairtrade NAPP
-Location:
-Assam
-Apply by:
-31 Mar 2026
-State Manager
-Hindustan Latex Family Planning Promotion Trust (...
+Program Head - MIS And Technology
+Dhwani Foundation
+Location:
+Karnataka
+Apply by:
+08 Apr 2026
+Associate/Specialist-Supply Chain
+India Health Action Trust (IHAT)
 Location:
 Uttar Pradesh
 Apply by:
 22 Mar 2026
-State Project Officer
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-India
-Apply by:
-22 Mar 2026
-State Program Manager-HIV-CSC-North East
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-Assam
-Apply by:
-22 Mar 2026
-Neighbourhood Facilitator – Health &amp; NCDs
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
-Health Planner – Community Mobilization
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
 Jobseekers
 Register
 Login
@@ -5698,227 +5670,76 @@
 Recruitment Exchange</t>
         </is>
       </c>
+      <c r="F25" s="1" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G25" s="1" t="inlineStr">
+        <is>
+          <t>05-04-2026</t>
+        </is>
+      </c>
+      <c r="H25" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="I25" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287913</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr"/>
+      <c r="C26" s="1" t="inlineStr">
+        <is>
+          <t>RFP for Endline Evaluation Study - HSBC GCC Women Entrepreneurship Program - Click here</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr"/>
       <c r="F26" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G26" s="1" t="inlineStr">
-        <is>
-          <t>31-03-2026</t>
-        </is>
-      </c>
-      <c r="H26" s="1" t="n">
-        <v>22</v>
-      </c>
+      <c r="G26" s="1" t="inlineStr"/>
+      <c r="H26" s="1" t="inlineStr"/>
       <c r="I26" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287726</t>
+          <t>https://www.nasscomfoundation.org/pdf/endline-evaluation-study-hsbc-gcc-women-entrepreneurship-program.pdf</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>DevNetJobsIndia</t>
+          <t>Nasscom</t>
         </is>
       </c>
       <c r="B27" s="1" t="inlineStr"/>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>Associate – Finance and Operations</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Financial Management Service Foundation (FMSF) | Uttar Pradesh
-International Development - Associate – Finance and Operations, Financial Management Service Foundation (FMSF), Uttar Pradesh - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search ... Read More</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>• Joining FMSF means becoming part of a passionate team dedicated to making a positive impact. We offer competitive compensation, opportunities for professional development, and a supportive work environment where your contributions are valued and recognized. If you are committed to driving positive change, promoting accountability and strengthening the development sector, we encourage you to apply for the position of
-Associate – Finance and Operations
-at FMSF.
-You’re Resume to be accompanied with:
-Motivational letter justifying suitability for the position – role fitment based on present &amp; past work experience
-Current/last drawn compensation &amp; expected compensation
-CVs without Motivational Letter will not be considered
-FMSF is an Equal Opportunity Employer.
-Please note that only the shortlisted candidates will be contacted
-Apply Here
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-05 Apr 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Associate – Finance and Operations
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-RFQ-Corporate Global Group Health Insurance Cover...
-Coalition for Disaster Resilient Infrastructure (...
-Location:
-India
-Apply by:
-23 Mar 2026
-HR Associate
-Inclusion Economics India Centre (IEIC) at IFMR
-Location:
-Delhi
-Apply by:
-08 Apr 2026
-Short Term Consultant - Workshop Facilitator for ...
-Fairtrade NAPP
-Location:
-Assam
-Apply by:
-31 Mar 2026
-State Manager
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-Uttar Pradesh
-Apply by:
-22 Mar 2026
-State Project Officer
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-India
-Apply by:
-22 Mar 2026
-State Program Manager-HIV-CSC-North East
-Hindustan Latex Family Planning Promotion Trust (...
-Location:
-Assam
-Apply by:
-22 Mar 2026
-Neighbourhood Facilitator – Health &amp; NCDs
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
-Health Planner – Community Mobilization
-Transform Rural India (TRI)
-Location:
-Maharashtra
-Apply by:
-30 Mar 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
+          <t>Travel &amp; Transportation Services for Trainer Mobility - IBM SkillBuild Bootcamps - Click here</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr"/>
+      <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G27" s="1" t="inlineStr">
-        <is>
-          <t>05-04-2026</t>
-        </is>
-      </c>
-      <c r="H27" s="1" t="n">
-        <v>27</v>
-      </c>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G27" s="1" t="inlineStr"/>
+      <c r="H27" s="1" t="inlineStr"/>
       <c r="I27" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287913</t>
+          <t>https://www.nasscomfoundation.org/pdf/travel-and-transportation-services-for-trainer-mobility-ibm-skillbuild-bootcamps.pdf</t>
         </is>
       </c>
     </row>
@@ -5931,7 +5752,7 @@
       <c r="B28" s="1" t="inlineStr"/>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>RFP for Endline Evaluation Study - HSBC GCC Women Entrepreneurship Program - Click here</t>
+          <t>Baseline and End-line Evaluation of the HSBC Neurodivergent Digital Annotator Skilling Program - Click here | Click here</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr"/>
@@ -5945,7 +5766,7 @@
       <c r="H28" s="1" t="inlineStr"/>
       <c r="I28" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/endline-evaluation-study-hsbc-gcc-women-entrepreneurship-program.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/baseline-and-end-line-evaluation-of-hsbc-neurodivergent-digital-annotator-skilling-program.pdf</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5779,7 @@
       <c r="B29" s="1" t="inlineStr"/>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>Travel &amp; Transportation Services for Trainer Mobility - IBM SkillBuild Bootcamps - Click here</t>
+          <t>RFP for Catering Vendor - IBM Skillbuild Bootcamps - Click here</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr"/>
@@ -5972,7 +5793,7 @@
       <c r="H29" s="1" t="inlineStr"/>
       <c r="I29" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/travel-and-transportation-services-for-trainer-mobility-ibm-skillbuild-bootcamps.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/rfp-for-catering-vendor-ibm-skillbuild-bootcamps.pdf</t>
         </is>
       </c>
     </row>
@@ -5985,7 +5806,7 @@
       <c r="B30" s="1" t="inlineStr"/>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>Baseline and End-line Evaluation of the HSBC Neurodivergent Digital Annotator Skilling Program - Click here | Click here</t>
+          <t>Organization-wide Management Information System (MIS) for Nasscom Foundation - Click here</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr"/>
@@ -5999,7 +5820,7 @@
       <c r="H30" s="1" t="inlineStr"/>
       <c r="I30" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/baseline-and-end-line-evaluation-of-hsbc-neurodivergent-digital-annotator-skilling-program.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/organization-wide-management-information-system-for-nasscom-foundation.pdf</t>
         </is>
       </c>
     </row>
@@ -6012,21 +5833,21 @@
       <c r="B31" s="1" t="inlineStr"/>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>RFP for Catering Vendor - IBM Skillbuild Bootcamps - Click here</t>
+          <t>Request for Proposal (RFP) for Social Media Management Services - Click here</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G31" s="1" t="inlineStr"/>
       <c r="H31" s="1" t="inlineStr"/>
       <c r="I31" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/rfp-for-catering-vendor-ibm-skillbuild-bootcamps.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/request-for-proposal-for-social-media-management-services.pdf</t>
         </is>
       </c>
     </row>
@@ -6039,7 +5860,7 @@
       <c r="B32" s="1" t="inlineStr"/>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>Organization-wide Management Information System (MIS) for Nasscom Foundation - Click here</t>
+          <t>RFP - TechForSociety - Evaluation Study - Click here</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr"/>
@@ -6053,7 +5874,7 @@
       <c r="H32" s="1" t="inlineStr"/>
       <c r="I32" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/organization-wide-management-information-system-for-nasscom-foundation.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/techforsociety-evaluation-study.pdf</t>
         </is>
       </c>
     </row>
@@ -6066,7 +5887,7 @@
       <c r="B33" s="1" t="inlineStr"/>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>Request for Proposal (RFP) for Social Media Management Services - Click here</t>
+          <t>Base-line and End-line evaluation for Digital Literacy Project in 4 States - Click here</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr"/>
@@ -6080,7 +5901,7 @@
       <c r="H33" s="1" t="inlineStr"/>
       <c r="I33" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/request-for-proposal-for-social-media-management-services.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/base-line-and-end-line-evaluation-for-digital-literacy-project-in-4-states.pdf</t>
         </is>
       </c>
     </row>
@@ -6093,21 +5914,21 @@
       <c r="B34" s="1" t="inlineStr"/>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>RFP - TechForSociety - Evaluation Study - Click here</t>
+          <t>IP Selection - Scholarship Support to students from Economically Weaker Section pursuing higher education in STEM courses - Click here</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G34" s="1" t="inlineStr"/>
       <c r="H34" s="1" t="inlineStr"/>
       <c r="I34" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/techforsociety-evaluation-study.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/scholarship-support-for-economically-weaker-section-students-in-stem-higher-education.pdf</t>
         </is>
       </c>
     </row>
@@ -6120,21 +5941,21 @@
       <c r="B35" s="1" t="inlineStr"/>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>Base-line and End-line evaluation for Digital Literacy Project in 4 States - Click here</t>
+          <t>Digital Upskilling of Farmer Producer Organizations (FPOs) through Technology - Click here</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G35" s="1" t="inlineStr"/>
       <c r="H35" s="1" t="inlineStr"/>
       <c r="I35" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/base-line-and-end-line-evaluation-for-digital-literacy-project-in-4-states.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/baseline-endline-study-digital-upskilling-fpos-technology.pdf</t>
         </is>
       </c>
     </row>
@@ -6147,7 +5968,7 @@
       <c r="B36" s="1" t="inlineStr"/>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>IP Selection - Scholarship Support to students from Economically Weaker Section pursuing higher education in STEM courses - Click here</t>
+          <t>Project - Accelerating 100 Women Micro Entrepreneurs of Northeastern States - Click here</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr"/>
@@ -6161,7 +5982,7 @@
       <c r="H36" s="1" t="inlineStr"/>
       <c r="I36" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/scholarship-support-for-economically-weaker-section-students-in-stem-higher-education.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/project-accelerating-100-women-micro-entrepreneurs-of-northeastern-states.pdf</t>
         </is>
       </c>
     </row>
@@ -6174,21 +5995,21 @@
       <c r="B37" s="1" t="inlineStr"/>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>Digital Upskilling of Farmer Producer Organizations (FPOs) through Technology - Click here</t>
+          <t>Agency for Developing Training Modules and Conducting Training of Trainers (ToT) for MSMEs on IPR and Financial Management - Click here</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G37" s="1" t="inlineStr"/>
       <c r="H37" s="1" t="inlineStr"/>
       <c r="I37" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/baseline-endline-study-digital-upskilling-fpos-technology.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/agency-for-developing-training-modules-and-conducting-ToT-for-MSMEs-on-IPR-and-financial-management.pdf</t>
         </is>
       </c>
     </row>
@@ -6201,7 +6022,7 @@
       <c r="B38" s="1" t="inlineStr"/>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>Project - Accelerating 100 Women Micro Entrepreneurs of Northeastern States - Click here</t>
+          <t>RFP for WISE - Women in Innovation, Skills &amp; Entrepreneurship - Click here</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr"/>
@@ -6215,7 +6036,7 @@
       <c r="H38" s="1" t="inlineStr"/>
       <c r="I38" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/project-accelerating-100-women-micro-entrepreneurs-of-northeastern-states.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/women-in-Innovation-skills-and-entrepreneurship.pdf</t>
         </is>
       </c>
     </row>
@@ -6228,21 +6049,21 @@
       <c r="B39" s="1" t="inlineStr"/>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>Agency for Developing Training Modules and Conducting Training of Trainers (ToT) for MSMEs on IPR and Financial Management - Click here</t>
+          <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - English  - Click here</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G39" s="1" t="inlineStr"/>
       <c r="H39" s="1" t="inlineStr"/>
       <c r="I39" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/agency-for-developing-training-modules-and-conducting-ToT-for-MSMEs-on-IPR-and-financial-management.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-English.pdf</t>
         </is>
       </c>
     </row>
@@ -6255,7 +6076,7 @@
       <c r="B40" s="1" t="inlineStr"/>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>RFP for WISE - Women in Innovation, Skills &amp; Entrepreneurship - Click here</t>
+          <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - Kannada - Click here</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr"/>
@@ -6269,7 +6090,7 @@
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/women-in-Innovation-skills-and-entrepreneurship.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-Kannada.pdf</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6103,7 @@
       <c r="B41" s="1" t="inlineStr"/>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - English  - Click here</t>
+          <t>RFP - Trainer for Nano Women Entrepreneurs in Karnataka - Click here</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr"/>
@@ -6296,7 +6117,7 @@
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-English.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/trainer-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
         </is>
       </c>
     </row>
@@ -6309,7 +6130,7 @@
       <c r="B42" s="1" t="inlineStr"/>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - Kannada - Click here</t>
+          <t>RFP - Training Agency with Content and Trainers for Nano Women Entrepreneurs in Karnataka - Click here</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr"/>
@@ -6323,7 +6144,7 @@
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-Kannada.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/training-agency-with-content-and-trainers-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
         </is>
       </c>
     </row>
@@ -6336,21 +6157,21 @@
       <c r="B43" s="1" t="inlineStr"/>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>RFP - Trainer for Nano Women Entrepreneurs in Karnataka - Click here</t>
+          <t>Access to E-Governance and Livelihood in PVTG Communities in Aspirational Blocks - Click here</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
       <c r="E43" s="2" t="inlineStr"/>
       <c r="F43" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G43" s="1" t="inlineStr"/>
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/trainer-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/access-to-e-governance-and-livelihood-in-pvtg-communities-in-aspirational-blocks.pdf</t>
         </is>
       </c>
     </row>
@@ -6363,7 +6184,7 @@
       <c r="B44" s="1" t="inlineStr"/>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>RFP - Training Agency with Content and Trainers for Nano Women Entrepreneurs in Karnataka - Click here</t>
+          <t>thingQbator Portal Enhancement and Maintenance Proposal - Click here</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
@@ -6377,61 +6198,77 @@
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/training-agency-with-content-and-trainers-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/thingQbator-portal-enhancement-and-maintenance-proposal.pdf</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B45" s="1" t="inlineStr"/>
+          <t>HCL Foundation</t>
+        </is>
+      </c>
+      <c r="B45" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>Access to E-Governance and Livelihood in PVTG Communities in Aspirational Blocks - Click here</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards Biodiversity monitoring for Pan-India Afforestation sites</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
       <c r="E45" s="2" t="inlineStr"/>
       <c r="F45" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G45" s="1" t="inlineStr"/>
+          <t>Climate</t>
+        </is>
+      </c>
+      <c r="G45" s="1" t="inlineStr">
+        <is>
+          <t>10th Feb, 2026</t>
+        </is>
+      </c>
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/access-to-e-governance-and-livelihood-in-pvtg-communities-in-aspirational-blocks.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Biodiversity%20monitoring%20for%20Pan-India%20Afforestation%20sites%202-DSB.pdf</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B46" s="1" t="inlineStr"/>
+          <t>HCL Foundation</t>
+        </is>
+      </c>
+      <c r="B46" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>thingQbator Portal Enhancement and Maintenance Proposal - Click here</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards soil profiling and assessment from the restored and rejuvenated Harit sites.</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G46" s="1" t="inlineStr"/>
+          <t>Climate</t>
+        </is>
+      </c>
+      <c r="G46" s="1" t="inlineStr">
+        <is>
+          <t>10th Feb, 2026</t>
+        </is>
+      </c>
       <c r="H46" s="1" t="inlineStr"/>
       <c r="I46" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/thingQbator-portal-enhancement-and-maintenance-proposal.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Soil%20assessment-v1%20RKS-DSB_0.pdf</t>
         </is>
       </c>
     </row>
@@ -6448,25 +6285,25 @@
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards Biodiversity monitoring for Pan-India Afforestation sites</t>
+          <t>HCLFoundation invites proposals from NGOs/CSR implementing agencies for ‘Operating a Social Enterprise Cafe” under the flagship urban development programme - Uday</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
       <c r="E47" s="2" t="inlineStr"/>
       <c r="F47" s="1" t="inlineStr">
         <is>
-          <t>Climate</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G47" s="1" t="inlineStr">
         <is>
-          <t>10th Feb, 2026</t>
+          <t>15th Dec, 2025</t>
         </is>
       </c>
       <c r="H47" s="1" t="inlineStr"/>
       <c r="I47" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Biodiversity%20monitoring%20for%20Pan-India%20Afforestation%20sites%202-DSB.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-11/RfP_Social%20Enterprise%20Cafe_UDAY.docx</t>
         </is>
       </c>
     </row>
@@ -6483,25 +6320,25 @@
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards soil profiling and assessment from the restored and rejuvenated Harit sites.</t>
+          <t>Programme Officer/Senior Programme Officer – Environment Education</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
       <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="1" t="inlineStr">
         <is>
-          <t>Climate</t>
+          <t>Learning, Climate</t>
         </is>
       </c>
       <c r="G48" s="1" t="inlineStr">
         <is>
-          <t>10th Feb, 2026</t>
+          <t>10th Nov, 2025</t>
         </is>
       </c>
       <c r="H48" s="1" t="inlineStr"/>
       <c r="I48" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Soil%20assessment-v1%20RKS-DSB_0.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-10/Harit_POSPO_EEA_Multilocation_Oct%202025.pdf</t>
         </is>
       </c>
     </row>
@@ -6518,25 +6355,25 @@
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites proposals from NGOs/CSR implementing agencies for ‘Operating a Social Enterprise Cafe” under the flagship urban development programme - Uday</t>
+          <t>HCLFoundation invites applications for the PO/SPO position under its flagship programme Harit by HCLFoundation</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
       <c r="E49" s="2" t="inlineStr"/>
       <c r="F49" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G49" s="1" t="inlineStr">
         <is>
-          <t>15th Dec, 2025</t>
+          <t>31st Oct, 2025</t>
         </is>
       </c>
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-11/RfP_Social%20Enterprise%20Cafe_UDAY.docx</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-10/JD_Water%20Conservation_SPO%20V4.pdf</t>
         </is>
       </c>
     </row>
@@ -6553,7 +6390,7 @@
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>Programme Officer/Senior Programme Officer – Environment Education</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit by HCLFoundation, invites RFP from NGOs / CSR organizations working in Water Conservation for the development of Water Structures etc.</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
@@ -6565,13 +6402,13 @@
       </c>
       <c r="G50" s="1" t="inlineStr">
         <is>
-          <t>10th Nov, 2025</t>
+          <t>21st May, 2025</t>
         </is>
       </c>
       <c r="H50" s="1" t="inlineStr"/>
       <c r="I50" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-10/Harit_POSPO_EEA_Multilocation_Oct%202025.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/Final_RFP%20for%20water%20structure%20rejuvenation%20.docx</t>
         </is>
       </c>
     </row>
@@ -6588,7 +6425,7 @@
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites applications for the PO/SPO position under its flagship programme Harit by HCLFoundation</t>
+          <t>HCLFoundation invites technical application abstracts for the developing technology drive source code model mobile applications and web portals for addressing human-animal interactions under the Animal Welfare thematic of  Harit by HCLFoundation</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
@@ -6600,13 +6437,13 @@
       </c>
       <c r="G51" s="1" t="inlineStr">
         <is>
-          <t>31st Oct, 2025</t>
+          <t>15th May, 2025</t>
         </is>
       </c>
       <c r="H51" s="1" t="inlineStr"/>
       <c r="I51" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-10/JD_Water%20Conservation_SPO%20V4.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_AW%20Tech%20Based%20Source%20Code%20Model_V1%20%281%29.docx</t>
         </is>
       </c>
     </row>
@@ -6623,25 +6460,25 @@
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit by HCLFoundation, invites RFP from NGOs / CSR organizations working in Water Conservation for the development of Water Structures etc.</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit invites RFP from NGOs/CSR organizations working in the field of environment for project on the restoration of various degraded and natural habitats</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
       <c r="E52" s="2" t="inlineStr"/>
       <c r="F52" s="1" t="inlineStr">
         <is>
-          <t>Learning, Climate</t>
+          <t>Climate</t>
         </is>
       </c>
       <c r="G52" s="1" t="inlineStr">
         <is>
-          <t>21st May, 2025</t>
+          <t>15th May, 2025</t>
         </is>
       </c>
       <c r="H52" s="1" t="inlineStr"/>
       <c r="I52" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/Final_RFP%20for%20water%20structure%20rejuvenation%20.docx</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/Harit_A%20HR_RFP%20.docx</t>
         </is>
       </c>
     </row>
@@ -6658,14 +6495,14 @@
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites technical application abstracts for the developing technology drive source code model mobile applications and web portals for addressing human-animal interactions under the Animal Welfare thematic of  Harit by HCLFoundation</t>
+          <t>HCLFoundation invites EOI for conducting holistic and comprehensive Impact Assessments of environmental projects supported under Harit by HCLFoundation</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
       <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G53" s="1" t="inlineStr">
@@ -6676,7 +6513,7 @@
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_AW%20Tech%20Based%20Source%20Code%20Model_V1%20%281%29.docx</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_Harit%20Impact%20Assessments.docx</t>
         </is>
       </c>
     </row>
@@ -6693,7 +6530,7 @@
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit invites RFP from NGOs/CSR organizations working in the field of environment for project on the restoration of various degraded and natural habitats</t>
+          <t>HCLFoundation invites technical application abstracts for the conducting technical and highly engaging environment awareness and sustainability workshops under Harit by HCLFoundation</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
@@ -6711,644 +6548,7 @@
       <c r="H54" s="1" t="inlineStr"/>
       <c r="I54" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/Harit_A%20HR_RFP%20.docx</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>HCL Foundation</t>
-        </is>
-      </c>
-      <c r="B55" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C55" s="1" t="inlineStr">
-        <is>
-          <t>HCLFoundation invites EOI for conducting holistic and comprehensive Impact Assessments of environmental projects supported under Harit by HCLFoundation</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr"/>
-      <c r="E55" s="2" t="inlineStr"/>
-      <c r="F55" s="1" t="inlineStr">
-        <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G55" s="1" t="inlineStr">
-        <is>
-          <t>15th May, 2025</t>
-        </is>
-      </c>
-      <c r="H55" s="1" t="inlineStr"/>
-      <c r="I55" s="1" t="inlineStr">
-        <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_Harit%20Impact%20Assessments.docx</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>HCL Foundation</t>
-        </is>
-      </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>HCLFoundation invites technical application abstracts for the conducting technical and highly engaging environment awareness and sustainability workshops under Harit by HCLFoundation</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr"/>
-      <c r="E56" s="2" t="inlineStr"/>
-      <c r="F56" s="1" t="inlineStr">
-        <is>
-          <t>Climate</t>
-        </is>
-      </c>
-      <c r="G56" s="1" t="inlineStr">
-        <is>
-          <t>15th May, 2025</t>
-        </is>
-      </c>
-      <c r="H56" s="1" t="inlineStr"/>
-      <c r="I56" s="1" t="inlineStr">
-        <is>
           <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_EEA_Env%20%20Sus%20awareness%20workshops_FY%2025-26%20%281%29.docx</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>Supply_of_Unskilled_Manpower.pdf</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr"/>
-      <c r="E57" s="2" t="inlineStr"/>
-      <c r="F57" s="1" t="inlineStr"/>
-      <c r="G57" s="1" t="inlineStr"/>
-      <c r="H57" s="1" t="inlineStr"/>
-      <c r="I57" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/Supply_of_Unskilled_Manpower.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>Addendum manpower quotation.pdf</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr"/>
-      <c r="E58" s="2" t="inlineStr"/>
-      <c r="F58" s="1" t="inlineStr"/>
-      <c r="G58" s="1" t="inlineStr"/>
-      <c r="H58" s="1" t="inlineStr"/>
-      <c r="I58" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/Addendum%20manpower%20quotation.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>Quotation_for_Rate_Contrac_Vehicle_Hiring_for_NCR_or_Outstation..pdf</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr"/>
-      <c r="E59" s="2" t="inlineStr"/>
-      <c r="F59" s="1" t="inlineStr"/>
-      <c r="G59" s="1" t="inlineStr"/>
-      <c r="H59" s="1" t="inlineStr"/>
-      <c r="I59" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/Quotation_for_Rate_Contrac_Vehicle_Hiring_for_NCR_or_Outstation..pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>Final_RfP_UrbanShift_Preparation_of_Integrated_Green_Mobility_Plan_for_Pune.pdf</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr"/>
-      <c r="E60" s="2" t="inlineStr"/>
-      <c r="F60" s="1" t="inlineStr"/>
-      <c r="G60" s="1" t="inlineStr"/>
-      <c r="H60" s="1" t="inlineStr"/>
-      <c r="I60" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/Final_RfP_UrbanShift_Preparation_of_Integrated_Green_Mobility_Plan_for_Pune.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>RfP_IGMP_Response to Pre-Bid Queries_200226.pdf</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr"/>
-      <c r="E61" s="2" t="inlineStr"/>
-      <c r="F61" s="1" t="inlineStr"/>
-      <c r="G61" s="1" t="inlineStr"/>
-      <c r="H61" s="1" t="inlineStr"/>
-      <c r="I61" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/RfP_IGMP_Response%20to%20Pre-Bid%20Queries_200226.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B62" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C62" s="1" t="inlineStr">
-        <is>
-          <t>Corrigendum_1_RfP_IGMP.pdf</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr"/>
-      <c r="E62" s="2" t="inlineStr"/>
-      <c r="F62" s="1" t="inlineStr"/>
-      <c r="G62" s="1" t="inlineStr"/>
-      <c r="H62" s="1" t="inlineStr"/>
-      <c r="I62" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/Corrigendum_1_RfP_IGMP.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B63" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C63" s="1" t="inlineStr">
-        <is>
-          <t>Corrigendum 2_IGMP.pdf</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr"/>
-      <c r="E63" s="2" t="inlineStr"/>
-      <c r="F63" s="1" t="inlineStr"/>
-      <c r="G63" s="1" t="inlineStr"/>
-      <c r="H63" s="1" t="inlineStr"/>
-      <c r="I63" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/Corrigendum%202_IGMP.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>RFP_Engagement of GIS Expert_SCBP_2026.pdf</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr"/>
-      <c r="E64" s="2" t="inlineStr"/>
-      <c r="F64" s="1" t="inlineStr"/>
-      <c r="G64" s="1" t="inlineStr"/>
-      <c r="H64" s="1" t="inlineStr"/>
-      <c r="I64" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/RFP_Engagement%20of%20GIS%20Expert_SCBP_2026.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>Response_to_Queries_Engagement_of_GIS_Expert_Agency.pdf</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr"/>
-      <c r="E65" s="2" t="inlineStr"/>
-      <c r="F65" s="1" t="inlineStr"/>
-      <c r="G65" s="1" t="inlineStr"/>
-      <c r="H65" s="1" t="inlineStr"/>
-      <c r="I65" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/Response_to_Queries_Engagement_of_GIS_Expert_Agency.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>RfP_SRTW.pdf</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr"/>
-      <c r="E66" s="2" t="inlineStr"/>
-      <c r="F66" s="1" t="inlineStr"/>
-      <c r="G66" s="1" t="inlineStr"/>
-      <c r="H66" s="1" t="inlineStr"/>
-      <c r="I66" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/RfP_SRTW.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>Response to Pre-Bid Queries_SRTW_for Uploading.pdf</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr"/>
-      <c r="E67" s="2" t="inlineStr"/>
-      <c r="F67" s="1" t="inlineStr"/>
-      <c r="G67" s="1" t="inlineStr"/>
-      <c r="H67" s="1" t="inlineStr"/>
-      <c r="I67" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/Response%20to%20Pre-Bid%20Queries_SRTW_for%20Uploading.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C68" s="1" t="inlineStr">
-        <is>
-          <t>EOI_TECHNICAL_ASSISTANCE_UNDER_CITIIS_2.0_PROGRAM_DOMESTIC_POOL_OF_EXPERTS.pdf</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr"/>
-      <c r="E68" s="2" t="inlineStr"/>
-      <c r="F68" s="1" t="inlineStr"/>
-      <c r="G68" s="1" t="inlineStr"/>
-      <c r="H68" s="1" t="inlineStr"/>
-      <c r="I68" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/EOI_TECHNICAL_ASSISTANCE_UNDER_CITIIS_2.0_PROGRAM_DOMESTIC_POOL_OF_EXPERTS.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>Reply to Pre- Bid Queries - EOI for DE's under CITIIS 2.0.pdf</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr"/>
-      <c r="E69" s="2" t="inlineStr"/>
-      <c r="F69" s="1" t="inlineStr"/>
-      <c r="G69" s="1" t="inlineStr"/>
-      <c r="H69" s="1" t="inlineStr"/>
-      <c r="I69" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/Reply%20to%20Pre-%20Bid%20Queries%20-%20EOI%20for%20DE%27s%20under%20CITIIS%202.0.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>GeM-Bidding-8666471.pdf</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr"/>
-      <c r="E70" s="2" t="inlineStr"/>
-      <c r="F70" s="1" t="inlineStr"/>
-      <c r="G70" s="1" t="inlineStr"/>
-      <c r="H70" s="1" t="inlineStr"/>
-      <c r="I70" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-8666471.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>corgaudt1.pdf</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr"/>
-      <c r="E71" s="2" t="inlineStr"/>
-      <c r="F71" s="1" t="inlineStr"/>
-      <c r="G71" s="1" t="inlineStr"/>
-      <c r="H71" s="1" t="inlineStr"/>
-      <c r="I71" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/corgaudt1.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>Corrigendum6959493.pdf</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr"/>
-      <c r="E72" s="2" t="inlineStr"/>
-      <c r="F72" s="1" t="inlineStr"/>
-      <c r="G72" s="1" t="inlineStr"/>
-      <c r="H72" s="1" t="inlineStr"/>
-      <c r="I72" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/Corrigendum6959493.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>ADDENDUM6959493.pdf</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr"/>
-      <c r="E73" s="2" t="inlineStr"/>
-      <c r="F73" s="1" t="inlineStr"/>
-      <c r="G73" s="1" t="inlineStr"/>
-      <c r="H73" s="1" t="inlineStr"/>
-      <c r="I73" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/ADDENDUM6959493.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>RfP CJ&amp;IP Package 03_UrbanShift.pdf</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr"/>
-      <c r="E74" s="2" t="inlineStr"/>
-      <c r="F74" s="1" t="inlineStr"/>
-      <c r="G74" s="1" t="inlineStr"/>
-      <c r="H74" s="1" t="inlineStr"/>
-      <c r="I74" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/RfP%20CJ%26IP%20Package%2003_UrbanShift.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>Prebid reply Cj&amp;IP package 3_18.12.2025.pdf</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr"/>
-      <c r="E75" s="2" t="inlineStr"/>
-      <c r="F75" s="1" t="inlineStr"/>
-      <c r="G75" s="1" t="inlineStr"/>
-      <c r="H75" s="1" t="inlineStr"/>
-      <c r="I75" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/Prebid%20reply%20Cj%26IP%20package%203_18.12.2025.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B76" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C76" s="1" t="inlineStr">
-        <is>
-          <t>GeM-Bidding-8478801.pdf</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr"/>
-      <c r="E76" s="2" t="inlineStr"/>
-      <c r="F76" s="1" t="inlineStr"/>
-      <c r="G76" s="1" t="inlineStr"/>
-      <c r="H76" s="1" t="inlineStr"/>
-      <c r="I76" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-8478801.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="1" t="inlineStr">
-        <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>GeM-Bidding-8476974.pdf</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr"/>
-      <c r="E77" s="2" t="inlineStr"/>
-      <c r="F77" s="1" t="inlineStr"/>
-      <c r="G77" s="1" t="inlineStr"/>
-      <c r="H77" s="1" t="inlineStr"/>
-      <c r="I77" s="1" t="inlineStr">
-        <is>
-          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-8476974.pdf</t>
         </is>
       </c>
     </row>

--- a/all_grants.xlsx
+++ b/all_grants.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,6 +559,24 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Unit Head - Proposal Development
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Research Analysts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -571,12 +589,6 @@
 Uttar Pradesh
 Apply by:
 05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -607,68 +619,56 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Sr MEAL Officer, Preconception Nutrition and Care
-Nutrition International
-Location:
-Delhi
-Apply by:
-29 Mar 2026
-Academic Mentor
-Bharti Airtel Foundation
-Location:
-Sikkim, Assam, Jharkhand
-Apply by:
-09 Apr 2026
-Manager – Enterprise Promotion
-Project Concern International India (PCI India)
-Location:
-Bihar
-Apply by:
-13 Mar 2026
-RFP - Design, Development, Deployment and Mainten...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-RFP - Appointment of Agency for SEO Management an...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-Senior Program Manager/Program Manager, Doctors f...
-Lung Care Foundation
-Location:
-Haryana
-Apply by:
-08 Apr 2026
-Program Head - MIS And Technology
-Dhwani Foundation
-Location:
-Karnataka
-Apply by:
-08 Apr 2026
-Associate/Specialist-Supply Chain
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+Assistant Manager (Partnerships and Fundraising)
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Assistant Manager – MIS
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+UN Women National Consultant – GRB Technical Coor...
+UN Women
+Location:
+Delhi
 Apply by:
 22 Mar 2026
+UN Women National Consultant – GRB Expert - MWCD,...
+UN Women
+Location:
+Delhi
+Apply by:
+22 Mar 2026
+Communication Officer
+Association for Stimulating Know How (ASK)
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Program Coordinator
+Sampark Foundation
+Location:
+India
+Apply by:
+10 Apr 2026
+Senior Consultant – Education
+TeamLease Foundation
+Location:
+Delhi
+Apply by:
+10 Apr 2026
+Program Coordinator - Government Relations  &amp; Adv...
+Quest Alliance
+Location:
+Andhra Pradesh
+Apply by:
+10 Apr 2026
 Jobseekers
 Register
 Login
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="H2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
@@ -816,6 +816,24 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Unit Head - Proposal Development
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Research Analysts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -828,12 +846,6 @@
 Uttar Pradesh
 Apply by:
 05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -864,68 +876,56 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Sr MEAL Officer, Preconception Nutrition and Care
-Nutrition International
-Location:
-Delhi
-Apply by:
-29 Mar 2026
-Academic Mentor
-Bharti Airtel Foundation
-Location:
-Sikkim, Assam, Jharkhand
-Apply by:
-09 Apr 2026
-Manager – Enterprise Promotion
-Project Concern International India (PCI India)
-Location:
-Bihar
-Apply by:
-13 Mar 2026
-RFP - Design, Development, Deployment and Mainten...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-RFP - Appointment of Agency for SEO Management an...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-Senior Program Manager/Program Manager, Doctors f...
-Lung Care Foundation
-Location:
-Haryana
-Apply by:
-08 Apr 2026
-Program Head - MIS And Technology
-Dhwani Foundation
-Location:
-Karnataka
-Apply by:
-08 Apr 2026
-Associate/Specialist-Supply Chain
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+Assistant Manager (Partnerships and Fundraising)
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Assistant Manager – MIS
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+UN Women National Consultant – GRB Technical Coor...
+UN Women
+Location:
+Delhi
 Apply by:
 22 Mar 2026
+UN Women National Consultant – GRB Expert - MWCD,...
+UN Women
+Location:
+Delhi
+Apply by:
+22 Mar 2026
+Communication Officer
+Association for Stimulating Know How (ASK)
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Program Coordinator
+Sampark Foundation
+Location:
+India
+Apply by:
+10 Apr 2026
+Senior Consultant – Education
+TeamLease Foundation
+Location:
+Delhi
+Apply by:
+10 Apr 2026
+Program Coordinator - Government Relations  &amp; Adv...
+Quest Alliance
+Location:
+Andhra Pradesh
+Apply by:
+10 Apr 2026
 Jobseekers
 Register
 Login
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="H3" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
@@ -1029,6 +1029,24 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Unit Head - Proposal Development
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Research Analysts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -1041,12 +1059,6 @@
 Uttar Pradesh
 Apply by:
 05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -1077,68 +1089,56 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Sr MEAL Officer, Preconception Nutrition and Care
-Nutrition International
-Location:
-Delhi
-Apply by:
-29 Mar 2026
-Academic Mentor
-Bharti Airtel Foundation
-Location:
-Sikkim, Assam, Jharkhand
-Apply by:
-09 Apr 2026
-Manager – Enterprise Promotion
-Project Concern International India (PCI India)
-Location:
-Bihar
-Apply by:
-13 Mar 2026
-RFP - Design, Development, Deployment and Mainten...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-RFP - Appointment of Agency for SEO Management an...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-Senior Program Manager/Program Manager, Doctors f...
-Lung Care Foundation
-Location:
-Haryana
-Apply by:
-08 Apr 2026
-Program Head - MIS And Technology
-Dhwani Foundation
-Location:
-Karnataka
-Apply by:
-08 Apr 2026
-Associate/Specialist-Supply Chain
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+Assistant Manager (Partnerships and Fundraising)
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Assistant Manager – MIS
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+UN Women National Consultant – GRB Technical Coor...
+UN Women
+Location:
+Delhi
 Apply by:
 22 Mar 2026
+UN Women National Consultant – GRB Expert - MWCD,...
+UN Women
+Location:
+Delhi
+Apply by:
+22 Mar 2026
+Communication Officer
+Association for Stimulating Know How (ASK)
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Program Coordinator
+Sampark Foundation
+Location:
+India
+Apply by:
+10 Apr 2026
+Senior Consultant – Education
+TeamLease Foundation
+Location:
+Delhi
+Apply by:
+10 Apr 2026
+Program Coordinator - Government Relations  &amp; Adv...
+Quest Alliance
+Location:
+Andhra Pradesh
+Apply by:
+10 Apr 2026
 Jobseekers
 Register
 Login
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="H4" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
@@ -1262,6 +1262,24 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Unit Head - Proposal Development
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Research Analysts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -1274,12 +1292,6 @@
 Uttar Pradesh
 Apply by:
 05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -1310,68 +1322,56 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Sr MEAL Officer, Preconception Nutrition and Care
-Nutrition International
-Location:
-Delhi
-Apply by:
-29 Mar 2026
-Academic Mentor
-Bharti Airtel Foundation
-Location:
-Sikkim, Assam, Jharkhand
-Apply by:
-09 Apr 2026
-Manager – Enterprise Promotion
-Project Concern International India (PCI India)
-Location:
-Bihar
-Apply by:
-13 Mar 2026
-RFP - Design, Development, Deployment and Mainten...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-RFP - Appointment of Agency for SEO Management an...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-Senior Program Manager/Program Manager, Doctors f...
-Lung Care Foundation
-Location:
-Haryana
-Apply by:
-08 Apr 2026
-Program Head - MIS And Technology
-Dhwani Foundation
-Location:
-Karnataka
-Apply by:
-08 Apr 2026
-Associate/Specialist-Supply Chain
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+Assistant Manager (Partnerships and Fundraising)
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Assistant Manager – MIS
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+UN Women National Consultant – GRB Technical Coor...
+UN Women
+Location:
+Delhi
 Apply by:
 22 Mar 2026
+UN Women National Consultant – GRB Expert - MWCD,...
+UN Women
+Location:
+Delhi
+Apply by:
+22 Mar 2026
+Communication Officer
+Association for Stimulating Know How (ASK)
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Program Coordinator
+Sampark Foundation
+Location:
+India
+Apply by:
+10 Apr 2026
+Senior Consultant – Education
+TeamLease Foundation
+Location:
+Delhi
+Apply by:
+10 Apr 2026
+Program Coordinator - Government Relations  &amp; Adv...
+Quest Alliance
+Location:
+Andhra Pradesh
+Apply by:
+10 Apr 2026
 Jobseekers
 Register
 Login
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="H5" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5" s="1" t="inlineStr">
         <is>
@@ -1427,13 +1427,13 @@
       <c r="B6" s="1" t="inlineStr"/>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>ToR - Livelihoods Strategy Review and Future Direction Roadmap</t>
+          <t>ToR - Strategic Review and Forward-Looking Education Strategy Development</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t>ChildFund India | India
-International Development - ToR - Livelihoods Strategy Review and Future Direction Roadmap, ChildFund India, India - DevNetJobsIndia.org
+International Development - ToR - Strategic Review and Forward-Looking Education Strategy Development, ChildFund India, India - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
@@ -1447,34 +1447,15 @@
 Jobseekers:
 Login
 |
-Register
-Jobseeker ... Read More</t>
+Registe ... Read More</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>• To determine the relevance, alignment, and coherence of the Livelihood Program under CSP 2022–2027 with national priorities, donor expectations, and organizational mandate.
-To assess the extent to which planned outputs and outcomes have been achieved and to evaluate the quality and impact of program interventions.
-Identify achievements, innovations, good practices, and enabling factors across Livelihood program interventions.
-Document gaps, challenges, and areas for strengthening
-To examine the sustainability of program outcomes and the institutional readiness of ChildFund India for long-term resilience and growth.
-Facilitate reflection through workshops involving staff, partners, and selected beneficiaries and provide recommendations for strategic direction, scalability, and future program priorities.
-Proposal Submission
-Interested evaluators/agencies are invited to submit:
-Technical proposal outlining approach and methodology
-Team composition and relevant experience
-Financial proposal with a detailed budget
-Sample of previous qualitative evaluation work
-Interested evaluators/agencies are requested to submit their technical and financial proposals to
-centralpurchase2@childfundindia.org
-by 15 March 2026.
-Reference No:- PRA/CFI/DEL/2025-26/053
-ChildFund India reserves the right to modify this ToR based on programmatic and contextual requirements.
-For detailed information, please check the complete version of the advert attached below.
-• Job Email ID:
+          <t>• Job Email ID:
 centralpurchase2(at)childfundindia.org
 Download Attachment:
-ToR Livelihood Portfolio-6.3.2026.doc
+ToR for Education.doc
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
@@ -1485,6 +1466,24 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Unit Head - Proposal Development
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Research Analysts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -1497,12 +1496,6 @@
 Uttar Pradesh
 Apply by:
 05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -1533,68 +1526,56 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Sr MEAL Officer, Preconception Nutrition and Care
-Nutrition International
-Location:
-Delhi
-Apply by:
-29 Mar 2026
-Academic Mentor
-Bharti Airtel Foundation
-Location:
-Sikkim, Assam, Jharkhand
-Apply by:
-09 Apr 2026
-Manager – Enterprise Promotion
-Project Concern International India (PCI India)
-Location:
-Bihar
-Apply by:
-13 Mar 2026
-RFP - Design, Development, Deployment and Mainten...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-RFP - Appointment of Agency for SEO Management an...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-Senior Program Manager/Program Manager, Doctors f...
-Lung Care Foundation
-Location:
-Haryana
-Apply by:
-08 Apr 2026
-Program Head - MIS And Technology
-Dhwani Foundation
-Location:
-Karnataka
-Apply by:
-08 Apr 2026
-Associate/Specialist-Supply Chain
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+Assistant Manager (Partnerships and Fundraising)
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Assistant Manager – MIS
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+UN Women National Consultant – GRB Technical Coor...
+UN Women
+Location:
+Delhi
 Apply by:
 22 Mar 2026
+UN Women National Consultant – GRB Expert - MWCD,...
+UN Women
+Location:
+Delhi
+Apply by:
+22 Mar 2026
+Communication Officer
+Association for Stimulating Know How (ASK)
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Program Coordinator
+Sampark Foundation
+Location:
+India
+Apply by:
+10 Apr 2026
+Senior Consultant – Education
+TeamLease Foundation
+Location:
+Delhi
+Apply by:
+10 Apr 2026
+Program Coordinator - Government Relations  &amp; Adv...
+Quest Alliance
+Location:
+Andhra Pradesh
+Apply by:
+10 Apr 2026
 Jobseekers
 Register
 Login
@@ -1624,7 +1605,7 @@
       </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Learning, Safety</t>
         </is>
       </c>
       <c r="G6" s="1" t="inlineStr">
@@ -1633,11 +1614,11 @@
         </is>
       </c>
       <c r="H6" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287910</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287902</t>
         </is>
       </c>
     </row>
@@ -1650,13 +1631,13 @@
       <c r="B7" s="1" t="inlineStr"/>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>ToR - Strategic Review and Forward-Looking Education Strategy Development</t>
+          <t>ToR - Portfolio-Wide Learning Exercise cum review for the Health Domain</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
           <t>ChildFund India | India
-International Development - ToR - Strategic Review and Forward-Looking Education Strategy Development, ChildFund India, India - DevNetJobsIndia.org
+International Development - ToR - Portfolio-Wide Learning Exercise cum review for the Health Domain, ChildFund India, India - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
@@ -1670,7 +1651,7 @@
 Jobseekers:
 Login
 |
-Registe ... Read More</t>
+Register ... Read More</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1678,7 +1659,7 @@
           <t>• Job Email ID:
 centralpurchase2(at)childfundindia.org
 Download Attachment:
-ToR for Education.doc
+TOR  Health Portfolio_23.2.2026.doc
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
@@ -1689,6 +1670,24 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Unit Head - Proposal Development
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Research Analysts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -1701,12 +1700,6 @@
 Uttar Pradesh
 Apply by:
 05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -1737,68 +1730,56 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Sr MEAL Officer, Preconception Nutrition and Care
-Nutrition International
-Location:
-Delhi
-Apply by:
-29 Mar 2026
-Academic Mentor
-Bharti Airtel Foundation
-Location:
-Sikkim, Assam, Jharkhand
-Apply by:
-09 Apr 2026
-Manager – Enterprise Promotion
-Project Concern International India (PCI India)
-Location:
-Bihar
-Apply by:
-13 Mar 2026
-RFP - Design, Development, Deployment and Mainten...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-RFP - Appointment of Agency for SEO Management an...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-Senior Program Manager/Program Manager, Doctors f...
-Lung Care Foundation
-Location:
-Haryana
-Apply by:
-08 Apr 2026
-Program Head - MIS And Technology
-Dhwani Foundation
-Location:
-Karnataka
-Apply by:
-08 Apr 2026
-Associate/Specialist-Supply Chain
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+Assistant Manager (Partnerships and Fundraising)
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Assistant Manager – MIS
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+UN Women National Consultant – GRB Technical Coor...
+UN Women
+Location:
+Delhi
 Apply by:
 22 Mar 2026
+UN Women National Consultant – GRB Expert - MWCD,...
+UN Women
+Location:
+Delhi
+Apply by:
+22 Mar 2026
+Communication Officer
+Association for Stimulating Know How (ASK)
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Program Coordinator
+Sampark Foundation
+Location:
+India
+Apply by:
+10 Apr 2026
+Senior Consultant – Education
+TeamLease Foundation
+Location:
+Delhi
+Apply by:
+10 Apr 2026
+Program Coordinator - Government Relations  &amp; Adv...
+Quest Alliance
+Location:
+Andhra Pradesh
+Apply by:
+10 Apr 2026
 Jobseekers
 Register
 Login
@@ -1837,11 +1818,11 @@
         </is>
       </c>
       <c r="H7" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I7" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287902</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287901</t>
         </is>
       </c>
     </row>
@@ -1909,6 +1890,24 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Unit Head - Proposal Development
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Research Analysts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -1921,12 +1920,6 @@
 Uttar Pradesh
 Apply by:
 05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -1957,68 +1950,56 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Sr MEAL Officer, Preconception Nutrition and Care
-Nutrition International
-Location:
-Delhi
-Apply by:
-29 Mar 2026
-Academic Mentor
-Bharti Airtel Foundation
-Location:
-Sikkim, Assam, Jharkhand
-Apply by:
-09 Apr 2026
-Manager – Enterprise Promotion
-Project Concern International India (PCI India)
-Location:
-Bihar
-Apply by:
-13 Mar 2026
-RFP - Design, Development, Deployment and Mainten...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-RFP - Appointment of Agency for SEO Management an...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-Senior Program Manager/Program Manager, Doctors f...
-Lung Care Foundation
-Location:
-Haryana
-Apply by:
-08 Apr 2026
-Program Head - MIS And Technology
-Dhwani Foundation
-Location:
-Karnataka
-Apply by:
-08 Apr 2026
-Associate/Specialist-Supply Chain
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+Assistant Manager (Partnerships and Fundraising)
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Assistant Manager – MIS
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+UN Women National Consultant – GRB Technical Coor...
+UN Women
+Location:
+Delhi
 Apply by:
 22 Mar 2026
+UN Women National Consultant – GRB Expert - MWCD,...
+UN Women
+Location:
+Delhi
+Apply by:
+22 Mar 2026
+Communication Officer
+Association for Stimulating Know How (ASK)
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Program Coordinator
+Sampark Foundation
+Location:
+India
+Apply by:
+10 Apr 2026
+Senior Consultant – Education
+TeamLease Foundation
+Location:
+Delhi
+Apply by:
+10 Apr 2026
+Program Coordinator - Government Relations  &amp; Adv...
+Quest Alliance
+Location:
+Andhra Pradesh
+Apply by:
+10 Apr 2026
 Jobseekers
 Register
 Login
@@ -2057,7 +2038,7 @@
         </is>
       </c>
       <c r="H8" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I8" s="1" t="inlineStr">
         <is>
@@ -2074,13 +2055,62 @@
       <c r="B9" s="1" t="inlineStr"/>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>ToR - Portfolio-Wide Learning Exercise cum review for the Health Domain</t>
+          <t>RFP - for Empanelment of Knowledge Partners for Grooming of students for ...</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>TeamLease Foundation | India
+International Development - RFP - for  Empanelment of Knowledge Partners for Grooming of students for competitive examination (through partner) Super 30 Model, TeamLease Foundation, India - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast ... Read More</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t>15-03-2026</t>
+        </is>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287763</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr"/>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>ToR - Livelihoods Strategy Review and Future Direction Roadmap</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>ChildFund India | India
-International Development - ToR - Portfolio-Wide Learning Exercise cum review for the Health Domain, ChildFund India, India - DevNetJobsIndia.org
+International Development - ToR - Livelihoods Strategy Review and Future Direction Roadmap, ChildFund India, India - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
@@ -2094,15 +2124,34 @@
 Jobseekers:
 Login
 |
-Register ... Read More</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>• Job Email ID:
+Register
+Jobseeker ... Read More</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>• To determine the relevance, alignment, and coherence of the Livelihood Program under CSP 2022–2027 with national priorities, donor expectations, and organizational mandate.
+To assess the extent to which planned outputs and outcomes have been achieved and to evaluate the quality and impact of program interventions.
+Identify achievements, innovations, good practices, and enabling factors across Livelihood program interventions.
+Document gaps, challenges, and areas for strengthening
+To examine the sustainability of program outcomes and the institutional readiness of ChildFund India for long-term resilience and growth.
+Facilitate reflection through workshops involving staff, partners, and selected beneficiaries and provide recommendations for strategic direction, scalability, and future program priorities.
+Proposal Submission
+Interested evaluators/agencies are invited to submit:
+Technical proposal outlining approach and methodology
+Team composition and relevant experience
+Financial proposal with a detailed budget
+Sample of previous qualitative evaluation work
+Interested evaluators/agencies are requested to submit their technical and financial proposals to
+centralpurchase2@childfundindia.org
+by 15 March 2026.
+Reference No:- PRA/CFI/DEL/2025-26/053
+ChildFund India reserves the right to modify this ToR based on programmatic and contextual requirements.
+For detailed information, please check the complete version of the advert attached below.
+• Job Email ID:
 centralpurchase2(at)childfundindia.org
 Download Attachment:
-TOR  Health Portfolio_23.2.2026.doc
+ToR Livelihood Portfolio-6.3.2026.doc
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
@@ -2113,6 +2162,24 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Unit Head - Proposal Development
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Research Analysts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -2125,12 +2192,6 @@
 Uttar Pradesh
 Apply by:
 05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -2161,68 +2222,56 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Sr MEAL Officer, Preconception Nutrition and Care
-Nutrition International
-Location:
-Delhi
-Apply by:
-29 Mar 2026
-Academic Mentor
-Bharti Airtel Foundation
-Location:
-Sikkim, Assam, Jharkhand
-Apply by:
-09 Apr 2026
-Manager – Enterprise Promotion
-Project Concern International India (PCI India)
-Location:
-Bihar
-Apply by:
-13 Mar 2026
-RFP - Design, Development, Deployment and Mainten...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-RFP - Appointment of Agency for SEO Management an...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-Senior Program Manager/Program Manager, Doctors f...
-Lung Care Foundation
-Location:
-Haryana
-Apply by:
-08 Apr 2026
-Program Head - MIS And Technology
-Dhwani Foundation
-Location:
-Karnataka
-Apply by:
-08 Apr 2026
-Associate/Specialist-Supply Chain
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+Assistant Manager (Partnerships and Fundraising)
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Assistant Manager – MIS
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+UN Women National Consultant – GRB Technical Coor...
+UN Women
+Location:
+Delhi
 Apply by:
 22 Mar 2026
+UN Women National Consultant – GRB Expert - MWCD,...
+UN Women
+Location:
+Delhi
+Apply by:
+22 Mar 2026
+Communication Officer
+Association for Stimulating Know How (ASK)
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Program Coordinator
+Sampark Foundation
+Location:
+India
+Apply by:
+10 Apr 2026
+Senior Consultant – Education
+TeamLease Foundation
+Location:
+Delhi
+Apply by:
+10 Apr 2026
+Program Coordinator - Government Relations  &amp; Adv...
+Quest Alliance
+Location:
+Andhra Pradesh
+Apply by:
+10 Apr 2026
 Jobseekers
 Register
 Login
@@ -2250,38 +2299,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>Learning, Safety</t>
-        </is>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>15-03-2026</t>
         </is>
       </c>
-      <c r="H9" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="I9" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287901</t>
+      <c r="H10" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287910</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr"/>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr"/>
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>RFP - External organization/agency to undertake documentation and process ...</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>India Health Action Trust (IHAT) | India
 International Development - RFP - External organization/agency to undertake documentation and process evaluation of the Gen Equal Fellowship Programme, India Health Action Trust (IHAT), India - DevNetJobsIndia.org
@@ -2293,7 +2342,7 @@
 Value Memb ... Read More</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>• 3A. Scope of Work
 Time Period
@@ -2376,6 +2425,24 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Unit Head - Proposal Development
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Research Analysts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -2388,12 +2455,6 @@
 Uttar Pradesh
 Apply by:
 05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -2424,68 +2485,56 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Sr MEAL Officer, Preconception Nutrition and Care
-Nutrition International
-Location:
-Delhi
-Apply by:
-29 Mar 2026
-Academic Mentor
-Bharti Airtel Foundation
-Location:
-Sikkim, Assam, Jharkhand
-Apply by:
-09 Apr 2026
-Manager – Enterprise Promotion
-Project Concern International India (PCI India)
-Location:
-Bihar
-Apply by:
-13 Mar 2026
-RFP - Design, Development, Deployment and Mainten...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-RFP - Appointment of Agency for SEO Management an...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-Senior Program Manager/Program Manager, Doctors f...
-Lung Care Foundation
-Location:
-Haryana
-Apply by:
-08 Apr 2026
-Program Head - MIS And Technology
-Dhwani Foundation
-Location:
-Karnataka
-Apply by:
-08 Apr 2026
-Associate/Specialist-Supply Chain
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+Assistant Manager (Partnerships and Fundraising)
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Assistant Manager – MIS
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+UN Women National Consultant – GRB Technical Coor...
+UN Women
+Location:
+Delhi
 Apply by:
 22 Mar 2026
+UN Women National Consultant – GRB Expert - MWCD,...
+UN Women
+Location:
+Delhi
+Apply by:
+22 Mar 2026
+Communication Officer
+Association for Stimulating Know How (ASK)
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Program Coordinator
+Sampark Foundation
+Location:
+India
+Apply by:
+10 Apr 2026
+Senior Consultant – Education
+TeamLease Foundation
+Location:
+Delhi
+Apply by:
+10 Apr 2026
+Program Coordinator - Government Relations  &amp; Adv...
+Quest Alliance
+Location:
+Andhra Pradesh
+Apply by:
+10 Apr 2026
 Jobseekers
 Register
 Login
@@ -2513,71 +2562,22 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F10" s="1" t="inlineStr">
+      <c r="F11" s="1" t="inlineStr">
         <is>
           <t>Safety</t>
         </is>
       </c>
-      <c r="G10" s="1" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>15-03-2026</t>
         </is>
       </c>
-      <c r="H10" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="I10" s="1" t="inlineStr">
+      <c r="H11" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287645</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="inlineStr"/>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>RFP - for Empanelment of Knowledge Partners for Grooming of students for ...</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>TeamLease Foundation | India
-International Development - RFP - for  Empanelment of Knowledge Partners for Grooming of students for competitive examination (through partner) Super 30 Model, TeamLease Foundation, India - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast ... Read More</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G11" s="1" t="inlineStr">
-        <is>
-          <t>15-03-2026</t>
-        </is>
-      </c>
-      <c r="H11" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="I11" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287763</t>
         </is>
       </c>
     </row>
@@ -2649,6 +2649,24 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Unit Head - Proposal Development
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Research Analysts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -2661,12 +2679,6 @@
 Uttar Pradesh
 Apply by:
 05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -2697,68 +2709,56 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Sr MEAL Officer, Preconception Nutrition and Care
-Nutrition International
-Location:
-Delhi
-Apply by:
-29 Mar 2026
-Academic Mentor
-Bharti Airtel Foundation
-Location:
-Sikkim, Assam, Jharkhand
-Apply by:
-09 Apr 2026
-Manager – Enterprise Promotion
-Project Concern International India (PCI India)
-Location:
-Bihar
-Apply by:
-13 Mar 2026
-RFP - Design, Development, Deployment and Mainten...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-RFP - Appointment of Agency for SEO Management an...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-Senior Program Manager/Program Manager, Doctors f...
-Lung Care Foundation
-Location:
-Haryana
-Apply by:
-08 Apr 2026
-Program Head - MIS And Technology
-Dhwani Foundation
-Location:
-Karnataka
-Apply by:
-08 Apr 2026
-Associate/Specialist-Supply Chain
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+Assistant Manager (Partnerships and Fundraising)
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Assistant Manager – MIS
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+UN Women National Consultant – GRB Technical Coor...
+UN Women
+Location:
+Delhi
 Apply by:
 22 Mar 2026
+UN Women National Consultant – GRB Expert - MWCD,...
+UN Women
+Location:
+Delhi
+Apply by:
+22 Mar 2026
+Communication Officer
+Association for Stimulating Know How (ASK)
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Program Coordinator
+Sampark Foundation
+Location:
+India
+Apply by:
+10 Apr 2026
+Senior Consultant – Education
+TeamLease Foundation
+Location:
+Delhi
+Apply by:
+10 Apr 2026
+Program Coordinator - Government Relations  &amp; Adv...
+Quest Alliance
+Location:
+Andhra Pradesh
+Apply by:
+10 Apr 2026
 Jobseekers
 Register
 Login
@@ -2797,7 +2797,7 @@
         </is>
       </c>
       <c r="H12" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I12" s="1" t="inlineStr">
         <is>
@@ -2814,13 +2814,13 @@
       <c r="B13" s="1" t="inlineStr"/>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>RFP - Design, Development, Deployment and Maintenance of Mobile Applicati...</t>
+          <t>RFP - Appointment of Agency for SEO Management and Meta (Facebook / Instag...</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
           <t>YRGCARE | India
-International Development - RFP - Design, Development, Deployment and Maintenance of  Mobile Application for the Breakfree Platform, YRGCARE, India - DevNetJobsIndia.org
+International Development - RFP - Appointment of Agency for SEO Management and Meta (Facebook / Instagram) Advertising, YRGCARE, India - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
@@ -2832,21 +2832,23 @@
 Search Jobs
 Events
 Jobseekers:
-L ... Read More</t>
+Login
+|
+Regist ... Read More</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>• This Terms of Reference (ToR) defines the full scope of work, technical requirements, compliance standards, and performance expectations for the agency appointed to design, develop, deploy, and maintain the Breakfree mobile application for both Android and iOS platforms.
+          <t>• To drive sustained awareness, organic discoverability, and ethical user engagement, NACO/YRGCARE intends to appoint professional agencies to manage two complementary digital outreach functions: Search Engine Optimisation (SEO) and paid social outreach through Meta platforms (Facebook and Instagram). This ToR defines the full scope, expectations, compliance requirements, and monitoring framework for this appointment.
 For detailed information visit
 https://www.yrgmerf.org/procurement-notices
 or please check the complete version of the RFP attached below.
 • Job Email ID:
 rfp(at)yrgcare.org
 Download Attachment:
-Mobile Application Development_RFP_002_2026_Evaluation_Grid.pdf
+RFP_001_2026_SEO_.pdf
 Download Attachment:
-Mobile Application Development_RFP_002_Mob_App_.pdf
+RFP_001_2026_Evaluation_Grid_SEO.pdf
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
@@ -2857,6 +2859,24 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Unit Head - Proposal Development
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Research Analysts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -2869,12 +2889,6 @@
 Uttar Pradesh
 Apply by:
 05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -2905,68 +2919,56 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Sr MEAL Officer, Preconception Nutrition and Care
-Nutrition International
-Location:
-Delhi
-Apply by:
-29 Mar 2026
-Academic Mentor
-Bharti Airtel Foundation
-Location:
-Sikkim, Assam, Jharkhand
-Apply by:
-09 Apr 2026
-Manager – Enterprise Promotion
-Project Concern International India (PCI India)
-Location:
-Bihar
-Apply by:
-13 Mar 2026
-RFP - Design, Development, Deployment and Mainten...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-RFP - Appointment of Agency for SEO Management an...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-Senior Program Manager/Program Manager, Doctors f...
-Lung Care Foundation
-Location:
-Haryana
-Apply by:
-08 Apr 2026
-Program Head - MIS And Technology
-Dhwani Foundation
-Location:
-Karnataka
-Apply by:
-08 Apr 2026
-Associate/Specialist-Supply Chain
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+Assistant Manager (Partnerships and Fundraising)
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Assistant Manager – MIS
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+UN Women National Consultant – GRB Technical Coor...
+UN Women
+Location:
+Delhi
 Apply by:
 22 Mar 2026
+UN Women National Consultant – GRB Expert - MWCD,...
+UN Women
+Location:
+Delhi
+Apply by:
+22 Mar 2026
+Communication Officer
+Association for Stimulating Know How (ASK)
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Program Coordinator
+Sampark Foundation
+Location:
+India
+Apply by:
+10 Apr 2026
+Senior Consultant – Education
+TeamLease Foundation
+Location:
+Delhi
+Apply by:
+10 Apr 2026
+Program Coordinator - Government Relations  &amp; Adv...
+Quest Alliance
+Location:
+Andhra Pradesh
+Apply by:
+10 Apr 2026
 Jobseekers
 Register
 Login
@@ -2996,7 +2998,7 @@
       </c>
       <c r="F13" s="1" t="inlineStr">
         <is>
-          <t>Learning, Safety</t>
+          <t>Governance</t>
         </is>
       </c>
       <c r="G13" s="1" t="inlineStr">
@@ -3005,11 +3007,11 @@
         </is>
       </c>
       <c r="H13" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I13" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=288064</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=288063</t>
         </is>
       </c>
     </row>
@@ -3022,13 +3024,13 @@
       <c r="B14" s="1" t="inlineStr"/>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>RFP - Appointment of Agency for SEO Management and Meta (Facebook / Instag...</t>
+          <t>RFP - Design, Development, Deployment and Maintenance of Mobile Applicati...</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
           <t>YRGCARE | India
-International Development - RFP - Appointment of Agency for SEO Management and Meta (Facebook / Instagram) Advertising, YRGCARE, India - DevNetJobsIndia.org
+International Development - RFP - Design, Development, Deployment and Maintenance of  Mobile Application for the Breakfree Platform, YRGCARE, India - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
@@ -3040,23 +3042,21 @@
 Search Jobs
 Events
 Jobseekers:
-Login
-|
-Regist ... Read More</t>
+L ... Read More</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>• To drive sustained awareness, organic discoverability, and ethical user engagement, NACO/YRGCARE intends to appoint professional agencies to manage two complementary digital outreach functions: Search Engine Optimisation (SEO) and paid social outreach through Meta platforms (Facebook and Instagram). This ToR defines the full scope, expectations, compliance requirements, and monitoring framework for this appointment.
+          <t>• This Terms of Reference (ToR) defines the full scope of work, technical requirements, compliance standards, and performance expectations for the agency appointed to design, develop, deploy, and maintain the Breakfree mobile application for both Android and iOS platforms.
 For detailed information visit
 https://www.yrgmerf.org/procurement-notices
 or please check the complete version of the RFP attached below.
 • Job Email ID:
 rfp(at)yrgcare.org
 Download Attachment:
-RFP_001_2026_SEO_.pdf
+Mobile Application Development_RFP_002_2026_Evaluation_Grid.pdf
 Download Attachment:
-RFP_001_2026_Evaluation_Grid_SEO.pdf
+Mobile Application Development_RFP_002_Mob_App_.pdf
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
@@ -3067,6 +3067,24 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Unit Head - Proposal Development
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Research Analysts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -3079,12 +3097,6 @@
 Uttar Pradesh
 Apply by:
 05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -3115,68 +3127,56 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Sr MEAL Officer, Preconception Nutrition and Care
-Nutrition International
-Location:
-Delhi
-Apply by:
-29 Mar 2026
-Academic Mentor
-Bharti Airtel Foundation
-Location:
-Sikkim, Assam, Jharkhand
-Apply by:
-09 Apr 2026
-Manager – Enterprise Promotion
-Project Concern International India (PCI India)
-Location:
-Bihar
-Apply by:
-13 Mar 2026
-RFP - Design, Development, Deployment and Mainten...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-RFP - Appointment of Agency for SEO Management an...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-Senior Program Manager/Program Manager, Doctors f...
-Lung Care Foundation
-Location:
-Haryana
-Apply by:
-08 Apr 2026
-Program Head - MIS And Technology
-Dhwani Foundation
-Location:
-Karnataka
-Apply by:
-08 Apr 2026
-Associate/Specialist-Supply Chain
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+Assistant Manager (Partnerships and Fundraising)
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Assistant Manager – MIS
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+UN Women National Consultant – GRB Technical Coor...
+UN Women
+Location:
+Delhi
 Apply by:
 22 Mar 2026
+UN Women National Consultant – GRB Expert - MWCD,...
+UN Women
+Location:
+Delhi
+Apply by:
+22 Mar 2026
+Communication Officer
+Association for Stimulating Know How (ASK)
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Program Coordinator
+Sampark Foundation
+Location:
+India
+Apply by:
+10 Apr 2026
+Senior Consultant – Education
+TeamLease Foundation
+Location:
+Delhi
+Apply by:
+10 Apr 2026
+Program Coordinator - Government Relations  &amp; Adv...
+Quest Alliance
+Location:
+Andhra Pradesh
+Apply by:
+10 Apr 2026
 Jobseekers
 Register
 Login
@@ -3206,7 +3206,7 @@
       </c>
       <c r="F14" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
+          <t>Learning, Safety</t>
         </is>
       </c>
       <c r="G14" s="1" t="inlineStr">
@@ -3215,11 +3215,11 @@
         </is>
       </c>
       <c r="H14" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I14" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=288063</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=288064</t>
         </is>
       </c>
     </row>
@@ -3273,6 +3273,24 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Unit Head - Proposal Development
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Research Analysts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -3285,12 +3303,6 @@
 Uttar Pradesh
 Apply by:
 05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -3321,68 +3333,56 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Sr MEAL Officer, Preconception Nutrition and Care
-Nutrition International
-Location:
-Delhi
-Apply by:
-29 Mar 2026
-Academic Mentor
-Bharti Airtel Foundation
-Location:
-Sikkim, Assam, Jharkhand
-Apply by:
-09 Apr 2026
-Manager – Enterprise Promotion
-Project Concern International India (PCI India)
-Location:
-Bihar
-Apply by:
-13 Mar 2026
-RFP - Design, Development, Deployment and Mainten...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-RFP - Appointment of Agency for SEO Management an...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-Senior Program Manager/Program Manager, Doctors f...
-Lung Care Foundation
-Location:
-Haryana
-Apply by:
-08 Apr 2026
-Program Head - MIS And Technology
-Dhwani Foundation
-Location:
-Karnataka
-Apply by:
-08 Apr 2026
-Associate/Specialist-Supply Chain
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+Assistant Manager (Partnerships and Fundraising)
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Assistant Manager – MIS
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+UN Women National Consultant – GRB Technical Coor...
+UN Women
+Location:
+Delhi
 Apply by:
 22 Mar 2026
+UN Women National Consultant – GRB Expert - MWCD,...
+UN Women
+Location:
+Delhi
+Apply by:
+22 Mar 2026
+Communication Officer
+Association for Stimulating Know How (ASK)
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Program Coordinator
+Sampark Foundation
+Location:
+India
+Apply by:
+10 Apr 2026
+Senior Consultant – Education
+TeamLease Foundation
+Location:
+Delhi
+Apply by:
+10 Apr 2026
+Program Coordinator - Government Relations  &amp; Adv...
+Quest Alliance
+Location:
+Andhra Pradesh
+Apply by:
+10 Apr 2026
 Jobseekers
 Register
 Login
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="H15" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I15" s="1" t="inlineStr">
         <is>
@@ -3480,6 +3480,24 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Unit Head - Proposal Development
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Research Analysts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -3492,12 +3510,6 @@
 Uttar Pradesh
 Apply by:
 05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -3528,68 +3540,56 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Sr MEAL Officer, Preconception Nutrition and Care
-Nutrition International
-Location:
-Delhi
-Apply by:
-29 Mar 2026
-Academic Mentor
-Bharti Airtel Foundation
-Location:
-Sikkim, Assam, Jharkhand
-Apply by:
-09 Apr 2026
-Manager – Enterprise Promotion
-Project Concern International India (PCI India)
-Location:
-Bihar
-Apply by:
-13 Mar 2026
-RFP - Design, Development, Deployment and Mainten...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-RFP - Appointment of Agency for SEO Management an...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-Senior Program Manager/Program Manager, Doctors f...
-Lung Care Foundation
-Location:
-Haryana
-Apply by:
-08 Apr 2026
-Program Head - MIS And Technology
-Dhwani Foundation
-Location:
-Karnataka
-Apply by:
-08 Apr 2026
-Associate/Specialist-Supply Chain
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+Assistant Manager (Partnerships and Fundraising)
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Assistant Manager – MIS
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+UN Women National Consultant – GRB Technical Coor...
+UN Women
+Location:
+Delhi
 Apply by:
 22 Mar 2026
+UN Women National Consultant – GRB Expert - MWCD,...
+UN Women
+Location:
+Delhi
+Apply by:
+22 Mar 2026
+Communication Officer
+Association for Stimulating Know How (ASK)
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Program Coordinator
+Sampark Foundation
+Location:
+India
+Apply by:
+10 Apr 2026
+Senior Consultant – Education
+TeamLease Foundation
+Location:
+Delhi
+Apply by:
+10 Apr 2026
+Program Coordinator - Government Relations  &amp; Adv...
+Quest Alliance
+Location:
+Andhra Pradesh
+Apply by:
+10 Apr 2026
 Jobseekers
 Register
 Login
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="H16" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I16" s="1" t="inlineStr">
         <is>
@@ -3685,6 +3685,24 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Unit Head - Proposal Development
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Research Analysts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -3697,12 +3715,6 @@
 Uttar Pradesh
 Apply by:
 05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -3733,68 +3745,56 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Sr MEAL Officer, Preconception Nutrition and Care
-Nutrition International
-Location:
-Delhi
-Apply by:
-29 Mar 2026
-Academic Mentor
-Bharti Airtel Foundation
-Location:
-Sikkim, Assam, Jharkhand
-Apply by:
-09 Apr 2026
-Manager – Enterprise Promotion
-Project Concern International India (PCI India)
-Location:
-Bihar
-Apply by:
-13 Mar 2026
-RFP - Design, Development, Deployment and Mainten...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-RFP - Appointment of Agency for SEO Management an...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-Senior Program Manager/Program Manager, Doctors f...
-Lung Care Foundation
-Location:
-Haryana
-Apply by:
-08 Apr 2026
-Program Head - MIS And Technology
-Dhwani Foundation
-Location:
-Karnataka
-Apply by:
-08 Apr 2026
-Associate/Specialist-Supply Chain
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+Assistant Manager (Partnerships and Fundraising)
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Assistant Manager – MIS
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+UN Women National Consultant – GRB Technical Coor...
+UN Women
+Location:
+Delhi
 Apply by:
 22 Mar 2026
+UN Women National Consultant – GRB Expert - MWCD,...
+UN Women
+Location:
+Delhi
+Apply by:
+22 Mar 2026
+Communication Officer
+Association for Stimulating Know How (ASK)
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Program Coordinator
+Sampark Foundation
+Location:
+India
+Apply by:
+10 Apr 2026
+Senior Consultant – Education
+TeamLease Foundation
+Location:
+Delhi
+Apply by:
+10 Apr 2026
+Program Coordinator - Government Relations  &amp; Adv...
+Quest Alliance
+Location:
+Andhra Pradesh
+Apply by:
+10 Apr 2026
 Jobseekers
 Register
 Login
@@ -3833,7 +3833,7 @@
         </is>
       </c>
       <c r="H17" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I17" s="1" t="inlineStr">
         <is>
@@ -3932,6 +3932,24 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Unit Head - Proposal Development
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Research Analysts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -3944,12 +3962,6 @@
 Uttar Pradesh
 Apply by:
 05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -3980,68 +3992,56 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Sr MEAL Officer, Preconception Nutrition and Care
-Nutrition International
-Location:
-Delhi
-Apply by:
-29 Mar 2026
-Academic Mentor
-Bharti Airtel Foundation
-Location:
-Sikkim, Assam, Jharkhand
-Apply by:
-09 Apr 2026
-Manager – Enterprise Promotion
-Project Concern International India (PCI India)
-Location:
-Bihar
-Apply by:
-13 Mar 2026
-RFP - Design, Development, Deployment and Mainten...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-RFP - Appointment of Agency for SEO Management an...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-Senior Program Manager/Program Manager, Doctors f...
-Lung Care Foundation
-Location:
-Haryana
-Apply by:
-08 Apr 2026
-Program Head - MIS And Technology
-Dhwani Foundation
-Location:
-Karnataka
-Apply by:
-08 Apr 2026
-Associate/Specialist-Supply Chain
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+Assistant Manager (Partnerships and Fundraising)
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Assistant Manager – MIS
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+UN Women National Consultant – GRB Technical Coor...
+UN Women
+Location:
+Delhi
 Apply by:
 22 Mar 2026
+UN Women National Consultant – GRB Expert - MWCD,...
+UN Women
+Location:
+Delhi
+Apply by:
+22 Mar 2026
+Communication Officer
+Association for Stimulating Know How (ASK)
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Program Coordinator
+Sampark Foundation
+Location:
+India
+Apply by:
+10 Apr 2026
+Senior Consultant – Education
+TeamLease Foundation
+Location:
+Delhi
+Apply by:
+10 Apr 2026
+Program Coordinator - Government Relations  &amp; Adv...
+Quest Alliance
+Location:
+Andhra Pradesh
+Apply by:
+10 Apr 2026
 Jobseekers
 Register
 Login
@@ -4080,7 +4080,7 @@
         </is>
       </c>
       <c r="H18" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I18" s="1" t="inlineStr">
         <is>
@@ -4097,10 +4097,247 @@
       <c r="B19" s="1" t="inlineStr"/>
       <c r="C19" s="1" t="inlineStr">
         <is>
+          <t>RFP - for hiring of an agency for providing Legal and Compliance Advisory...</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>International Union Against Tuberculosis and Lung Disease (The Union) | India
+International Development - RFP -  for hiring of an agency for providing Legal and Compliance Advisory Services, International Union Against Tuberculosis and Lung Disease (The Union), India - DevNetJobsIndia.org
+Jobseeker ... Read More</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>• 1. PURPOSE OF THE RFP
+1.1 The Union is interested in engaging a firm/ agency to provide comprehensive legal advisory and compliance support to the organisation, ensuring adherence to applicable laws, regulations, donor requirements, and good governance standards relevant to the social impact/ non-profit sector
+1.2 Accordingly, The Union is requesting for proposals from relevant agencies for The Union. This RFP should not be considered as neither as an agreement nor an offer by The Union to the prospective bidders.
+2. GENERAL TERMS OF BIDDING
+2.1. All Bidders are required to submit their Bid in accordance with the terms set forth in this RFP.
+2.2. Notwithstanding anything to the contrary contained in this RFP, the detailed terms specified in the Agreement shall have overriding effect.
+• 2.3. The Union reserves the right to invite fresh bids with or without amendment of the RFP at any stage or to terminate at any time the entire bidding/selection process without any liability or any obligation to any of the Bidders and without assigning any reason whatsoever.
+2.4. The Union will not guarantee any minimum quantity of business under any contract. Also, The Union reserves the right to split the business amongst empanelled agencies keeping in mind the interest of the organisation. The Union reserves the right to enter into contract with multiple service providers/agencies at the same time.
+2.5. The Bidder cannot be an individual or group of individuals. It should only be a registered legal entity. The Bidder should not be a consortium of such entities. The agencies should have PAN, GST registration and registration under applicable laws and should submit copies of the same.
+2.6. A Bidder shall not have a conflict of interest that affects the bidding process. Any Bidder found to have a Conflict of Interest shall be disqualified.
+2.7. Also, the bidder should not have been convicted/charge-sheeted for any criminal offence. Any Entity which has been convicted for any criminal offence shall not be eligible to submit the bid.
+2.8. The e-bids shall be opened at The Union, C-6, Qutub Institutional Area, New Delhi. The RFP document will be advertised on devnetjobsindia.org
+PROPOSAL SUBMISSION:
+Proposals through email are invited from the reputed agency for the aforesaid purpose. The proposal should include the
+"Technical &amp; Financial"
+details.
+Two separate emails are required to be submitted -
+Technical and Financial Proposal.
+The interested service provider must submit their proposals in two separate emails , should clearly state in the subject line - "
+Technical Proposal
+–"
+for hiring of an agency for providing
+Legal and Compliance Advisory Services
+”
+and
+"Financial Proposal -
+for hiring of
+agency for providing Legal and Compliance Advisory Services
+" with all relevant documents as listed in document to
+Procurement.USEA@theunion.org
+latest by
+22
+March 2026
+.
+The Service Provider shall ensure the preparation of Detailed Technical Proposal in accordance with documentation as technical evaluation. The Technical Proposal should not contain any cost information whatsoever.
+The “Financial Proposal” should contain the detailed in accordance with instructions in
+Annexure-A
+to this RFP. Financial Proposal” shall remain password-protected, and such password shall be obtained by procurement committee appointed by The Union after the Technical Qualification of the Proposal submitted by the bidder. Financial Proposal” shall remain password-protected, and such password shall be obtained by procurement committee appointed by The Union after the Technical Qualification of the Proposal submitted by the bidder.
+Proposal validity period will be for
+180 days
+from the date of submission of proposal.
+You can write your queries  / clarifications through email on
+Procurement.USEA@theunion.org
+latest by
+17 March 2026.
+For detailed information, please check the complete version of the RFP attached below.
+• Job Email ID:
+Procurement.USEA(at)theunion.org
+Download Attachment:
+RFP - Legal and Compliance Advisory Services.pdf
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+22 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Unit Head - Proposal Development
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Research Analysts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+Assistant Manager (Partnerships and Fundraising)
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Assistant Manager – MIS
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+UN Women National Consultant – GRB Technical Coor...
+UN Women
+Location:
+Delhi
+Apply by:
+22 Mar 2026
+UN Women National Consultant – GRB Expert - MWCD,...
+UN Women
+Location:
+Delhi
+Apply by:
+22 Mar 2026
+Communication Officer
+Association for Stimulating Know How (ASK)
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Program Coordinator
+Sampark Foundation
+Location:
+India
+Apply by:
+10 Apr 2026
+Senior Consultant – Education
+TeamLease Foundation
+Location:
+Delhi
+Apply by:
+10 Apr 2026
+Program Coordinator - Government Relations  &amp; Adv...
+Quest Alliance
+Location:
+Andhra Pradesh
+Apply by:
+10 Apr 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G19" s="1" t="inlineStr">
+        <is>
+          <t>22-03-2026</t>
+        </is>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="I19" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=288152</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr"/>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
           <t>RFQ-Corporate Global Group Health Insurance Coverage</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Coalition for Disaster Resilient Infrastructure (CDRI) | India
 International Development - RFQ-Corporate Global Group Health Insurance Coverage, Coalition for Disaster Resilient Infrastructure (CDRI), India - DevNetJobsIndia.org
@@ -4114,7 +4351,7 @@
 RF ... Read More</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>• The specific staff details, policy document, along with the claim MIS will only be shared with the interested bidders upon request to the email ID
 :
@@ -4210,6 +4447,24 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Unit Head - Proposal Development
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Research Analysts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -4222,12 +4477,6 @@
 Uttar Pradesh
 Apply by:
 05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -4258,68 +4507,56 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Sr MEAL Officer, Preconception Nutrition and Care
-Nutrition International
-Location:
-Delhi
-Apply by:
-29 Mar 2026
-Academic Mentor
-Bharti Airtel Foundation
-Location:
-Sikkim, Assam, Jharkhand
-Apply by:
-09 Apr 2026
-Manager – Enterprise Promotion
-Project Concern International India (PCI India)
-Location:
-Bihar
-Apply by:
-13 Mar 2026
-RFP - Design, Development, Deployment and Mainten...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-RFP - Appointment of Agency for SEO Management an...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-Senior Program Manager/Program Manager, Doctors f...
-Lung Care Foundation
-Location:
-Haryana
-Apply by:
-08 Apr 2026
-Program Head - MIS And Technology
-Dhwani Foundation
-Location:
-Karnataka
-Apply by:
-08 Apr 2026
-Associate/Specialist-Supply Chain
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+Assistant Manager (Partnerships and Fundraising)
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Assistant Manager – MIS
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+UN Women National Consultant – GRB Technical Coor...
+UN Women
+Location:
+Delhi
 Apply by:
 22 Mar 2026
+UN Women National Consultant – GRB Expert - MWCD,...
+UN Women
+Location:
+Delhi
+Apply by:
+22 Mar 2026
+Communication Officer
+Association for Stimulating Know How (ASK)
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Program Coordinator
+Sampark Foundation
+Location:
+India
+Apply by:
+10 Apr 2026
+Senior Consultant – Education
+TeamLease Foundation
+Location:
+Delhi
+Apply by:
+10 Apr 2026
+Program Coordinator - Government Relations  &amp; Adv...
+Quest Alliance
+Location:
+Andhra Pradesh
+Apply by:
+10 Apr 2026
 Jobseekers
 Register
 Login
@@ -4347,38 +4584,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F19" s="1" t="inlineStr">
+      <c r="F20" s="1" t="inlineStr">
         <is>
           <t>Climate, Safety</t>
         </is>
       </c>
-      <c r="G19" s="1" t="inlineStr">
+      <c r="G20" s="1" t="inlineStr">
         <is>
           <t>23-03-2026</t>
         </is>
       </c>
-      <c r="H19" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="I19" s="1" t="inlineStr">
+      <c r="H20" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="I20" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=288006</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr"/>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="B21" s="1" t="inlineStr"/>
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>EoI – Mobile Medical Units, Ai-Enabled Tb Screening &amp; Supply Of Medical An...</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Ashray Foundation | Korba, Chattisgarh (Delivery Location), Gujarat
 International Development - EoI – Mobile Medical Units, Ai-Enabled Tb Screening &amp; Supply Of Medical And Nutritional Support, Ashray Foundation, Gujarat - DevNetJobsIndia.org
@@ -4391,7 +4628,7 @@
 Broadc ... Read More</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>• Ashray Foundation invites eligible and experienced agencies to submit their Expression of Interest / for the following scope of work:
 Fabrication of Mobile Medical Units (MMUs) – 2 Units
@@ -4418,6 +4655,24 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Unit Head - Proposal Development
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Research Analysts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -4430,12 +4685,6 @@
 Uttar Pradesh
 Apply by:
 05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -4466,68 +4715,56 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Sr MEAL Officer, Preconception Nutrition and Care
-Nutrition International
-Location:
-Delhi
-Apply by:
-29 Mar 2026
-Academic Mentor
-Bharti Airtel Foundation
-Location:
-Sikkim, Assam, Jharkhand
-Apply by:
-09 Apr 2026
-Manager – Enterprise Promotion
-Project Concern International India (PCI India)
-Location:
-Bihar
-Apply by:
-13 Mar 2026
-RFP - Design, Development, Deployment and Mainten...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-RFP - Appointment of Agency for SEO Management an...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-Senior Program Manager/Program Manager, Doctors f...
-Lung Care Foundation
-Location:
-Haryana
-Apply by:
-08 Apr 2026
-Program Head - MIS And Technology
-Dhwani Foundation
-Location:
-Karnataka
-Apply by:
-08 Apr 2026
-Associate/Specialist-Supply Chain
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+Assistant Manager (Partnerships and Fundraising)
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Assistant Manager – MIS
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+UN Women National Consultant – GRB Technical Coor...
+UN Women
+Location:
+Delhi
 Apply by:
 22 Mar 2026
+UN Women National Consultant – GRB Expert - MWCD,...
+UN Women
+Location:
+Delhi
+Apply by:
+22 Mar 2026
+Communication Officer
+Association for Stimulating Know How (ASK)
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Program Coordinator
+Sampark Foundation
+Location:
+India
+Apply by:
+10 Apr 2026
+Senior Consultant – Education
+TeamLease Foundation
+Location:
+Delhi
+Apply by:
+10 Apr 2026
+Program Coordinator - Government Relations  &amp; Adv...
+Quest Alliance
+Location:
+Andhra Pradesh
+Apply by:
+10 Apr 2026
 Jobseekers
 Register
 Login
@@ -4555,38 +4792,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F20" s="1" t="inlineStr">
+      <c r="F21" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G20" s="1" t="inlineStr">
+      <c r="G21" s="1" t="inlineStr">
         <is>
           <t>24-03-2026</t>
         </is>
       </c>
-      <c r="H20" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="I20" s="1" t="inlineStr">
+      <c r="H21" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="I21" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287319</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr"/>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="B22" s="1" t="inlineStr"/>
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>RFP - End of Program Evaluation Accelerating Access to Safe Water and San...</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Water.org | Bangladesh, Cambodia, India
 International Development - RFP - End of Program Evaluation  Accelerating Access to Safe Water and Sanitation, Financing, Water.org, India - DevNetJobsIndia.org
@@ -4602,7 +4839,7 @@
 Event ... Read More</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>• The evaluation will require the firm to facilitate and coordinate with Water.org staff and partners. The program requires the firm to submit the deliverables outlined in section 2 Scope of Work.
 C.
@@ -4636,7 +4873,7 @@
 Download Attachment:
 Water.org Project Budget - template.xls
 Download Attachment:
-Request for proposal_evaluation March 2026.pdf
+Request for proposal_evaluation Updated 10 March 2026.pdf
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
@@ -4647,6 +4884,24 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Unit Head - Proposal Development
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Research Analysts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -4659,12 +4914,6 @@
 Uttar Pradesh
 Apply by:
 05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -4695,68 +4944,56 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Sr MEAL Officer, Preconception Nutrition and Care
-Nutrition International
-Location:
-Delhi
-Apply by:
-29 Mar 2026
-Academic Mentor
-Bharti Airtel Foundation
-Location:
-Sikkim, Assam, Jharkhand
-Apply by:
-09 Apr 2026
-Manager – Enterprise Promotion
-Project Concern International India (PCI India)
-Location:
-Bihar
-Apply by:
-13 Mar 2026
-RFP - Design, Development, Deployment and Mainten...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-RFP - Appointment of Agency for SEO Management an...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-Senior Program Manager/Program Manager, Doctors f...
-Lung Care Foundation
-Location:
-Haryana
-Apply by:
-08 Apr 2026
-Program Head - MIS And Technology
-Dhwani Foundation
-Location:
-Karnataka
-Apply by:
-08 Apr 2026
-Associate/Specialist-Supply Chain
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+Assistant Manager (Partnerships and Fundraising)
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Assistant Manager – MIS
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+UN Women National Consultant – GRB Technical Coor...
+UN Women
+Location:
+Delhi
 Apply by:
 22 Mar 2026
+UN Women National Consultant – GRB Expert - MWCD,...
+UN Women
+Location:
+Delhi
+Apply by:
+22 Mar 2026
+Communication Officer
+Association for Stimulating Know How (ASK)
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Program Coordinator
+Sampark Foundation
+Location:
+India
+Apply by:
+10 Apr 2026
+Senior Consultant – Education
+TeamLease Foundation
+Location:
+Delhi
+Apply by:
+10 Apr 2026
+Program Coordinator - Government Relations  &amp; Adv...
+Quest Alliance
+Location:
+Andhra Pradesh
+Apply by:
+10 Apr 2026
 Jobseekers
 Register
 Login
@@ -4784,38 +5021,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F21" s="1" t="inlineStr">
+      <c r="F22" s="1" t="inlineStr">
         <is>
           <t>Governance, Safety</t>
         </is>
       </c>
-      <c r="G21" s="1" t="inlineStr">
+      <c r="G22" s="1" t="inlineStr">
         <is>
           <t>25-03-2026</t>
         </is>
       </c>
-      <c r="H21" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="I21" s="1" t="inlineStr">
+      <c r="H22" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="I22" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287835</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr"/>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="B23" s="1" t="inlineStr"/>
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>Junior Research Technicians / Senior Project Asso...</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Starshield Security Solution Pvt.Ltd | Uttar Pradesh
 International Development - Junior Research Technicians / Senior Project Associate, Starshield Security Solution Pvt.Ltd, Uttar Pradesh - DevNetJobsIndia.org
@@ -4830,7 +5067,7 @@
 Search ... Read More</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>• Eligibility Criteria
 Qualification
@@ -4876,6 +5113,24 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Unit Head - Proposal Development
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Research Analysts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -4888,12 +5143,6 @@
 Uttar Pradesh
 Apply by:
 05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -4924,68 +5173,56 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Sr MEAL Officer, Preconception Nutrition and Care
-Nutrition International
-Location:
-Delhi
-Apply by:
-29 Mar 2026
-Academic Mentor
-Bharti Airtel Foundation
-Location:
-Sikkim, Assam, Jharkhand
-Apply by:
-09 Apr 2026
-Manager – Enterprise Promotion
-Project Concern International India (PCI India)
-Location:
-Bihar
-Apply by:
-13 Mar 2026
-RFP - Design, Development, Deployment and Mainten...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-RFP - Appointment of Agency for SEO Management an...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-Senior Program Manager/Program Manager, Doctors f...
-Lung Care Foundation
-Location:
-Haryana
-Apply by:
-08 Apr 2026
-Program Head - MIS And Technology
-Dhwani Foundation
-Location:
-Karnataka
-Apply by:
-08 Apr 2026
-Associate/Specialist-Supply Chain
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+Assistant Manager (Partnerships and Fundraising)
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Assistant Manager – MIS
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+UN Women National Consultant – GRB Technical Coor...
+UN Women
+Location:
+Delhi
 Apply by:
 22 Mar 2026
+UN Women National Consultant – GRB Expert - MWCD,...
+UN Women
+Location:
+Delhi
+Apply by:
+22 Mar 2026
+Communication Officer
+Association for Stimulating Know How (ASK)
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Program Coordinator
+Sampark Foundation
+Location:
+India
+Apply by:
+10 Apr 2026
+Senior Consultant – Education
+TeamLease Foundation
+Location:
+Delhi
+Apply by:
+10 Apr 2026
+Program Coordinator - Government Relations  &amp; Adv...
+Quest Alliance
+Location:
+Andhra Pradesh
+Apply by:
+10 Apr 2026
 Jobseekers
 Register
 Login
@@ -5013,38 +5250,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F22" s="1" t="inlineStr">
+      <c r="F23" s="1" t="inlineStr">
         <is>
           <t>Safety</t>
         </is>
       </c>
-      <c r="G22" s="1" t="inlineStr">
+      <c r="G23" s="1" t="inlineStr">
         <is>
           <t>30-03-2026</t>
         </is>
       </c>
-      <c r="H22" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="I22" s="1" t="inlineStr">
+      <c r="H23" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="I23" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287635</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr"/>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="B24" s="1" t="inlineStr"/>
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>Agriculture Research Development Officer / Projec...</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Starshield Security Solution Pvt.Ltd | Uttar Pradesh
 International Development - Agriculture Research Development Officer / Project Scientist III, Starshield Security Solution Pvt.Ltd, Uttar Pradesh - DevNetJobsIndia.org
@@ -5058,7 +5295,7 @@
 RFPs/Tende ... Read More</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>• Eligibility Criteria
 Qualification:
@@ -5105,6 +5342,24 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Unit Head - Proposal Development
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Research Analysts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -5117,12 +5372,6 @@
 Uttar Pradesh
 Apply by:
 05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -5153,68 +5402,56 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Sr MEAL Officer, Preconception Nutrition and Care
-Nutrition International
-Location:
-Delhi
-Apply by:
-29 Mar 2026
-Academic Mentor
-Bharti Airtel Foundation
-Location:
-Sikkim, Assam, Jharkhand
-Apply by:
-09 Apr 2026
-Manager – Enterprise Promotion
-Project Concern International India (PCI India)
-Location:
-Bihar
-Apply by:
-13 Mar 2026
-RFP - Design, Development, Deployment and Mainten...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-RFP - Appointment of Agency for SEO Management an...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-Senior Program Manager/Program Manager, Doctors f...
-Lung Care Foundation
-Location:
-Haryana
-Apply by:
-08 Apr 2026
-Program Head - MIS And Technology
-Dhwani Foundation
-Location:
-Karnataka
-Apply by:
-08 Apr 2026
-Associate/Specialist-Supply Chain
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+Assistant Manager (Partnerships and Fundraising)
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Assistant Manager – MIS
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+UN Women National Consultant – GRB Technical Coor...
+UN Women
+Location:
+Delhi
 Apply by:
 22 Mar 2026
+UN Women National Consultant – GRB Expert - MWCD,...
+UN Women
+Location:
+Delhi
+Apply by:
+22 Mar 2026
+Communication Officer
+Association for Stimulating Know How (ASK)
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Program Coordinator
+Sampark Foundation
+Location:
+India
+Apply by:
+10 Apr 2026
+Senior Consultant – Education
+TeamLease Foundation
+Location:
+Delhi
+Apply by:
+10 Apr 2026
+Program Coordinator - Government Relations  &amp; Adv...
+Quest Alliance
+Location:
+Andhra Pradesh
+Apply by:
+10 Apr 2026
 Jobseekers
 Register
 Login
@@ -5242,38 +5479,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F23" s="1" t="inlineStr">
+      <c r="F24" s="1" t="inlineStr">
         <is>
           <t>Learning, Safety</t>
         </is>
       </c>
-      <c r="G23" s="1" t="inlineStr">
+      <c r="G24" s="1" t="inlineStr">
         <is>
           <t>30-03-2026</t>
         </is>
       </c>
-      <c r="H23" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="I23" s="1" t="inlineStr">
+      <c r="H24" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="I24" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287636</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr"/>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="B25" s="1" t="inlineStr"/>
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>Sector Experts</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Academy of Management Studies (AMS) | India
 International Development - Sector Experts, Academy of Management Studies (AMS), India - DevNetJobsIndia.org
@@ -5294,7 +5531,7 @@
 Jobseekers Login ... Read More</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>• Eligibility
 Postgraduate degree / Ph.D. in relevant or allied disciplines
@@ -5328,6 +5565,24 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Unit Head - Proposal Development
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Research Analysts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -5340,12 +5595,6 @@
 Uttar Pradesh
 Apply by:
 05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -5376,68 +5625,56 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Sr MEAL Officer, Preconception Nutrition and Care
-Nutrition International
-Location:
-Delhi
-Apply by:
-29 Mar 2026
-Academic Mentor
-Bharti Airtel Foundation
-Location:
-Sikkim, Assam, Jharkhand
-Apply by:
-09 Apr 2026
-Manager – Enterprise Promotion
-Project Concern International India (PCI India)
-Location:
-Bihar
-Apply by:
-13 Mar 2026
-RFP - Design, Development, Deployment and Mainten...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-RFP - Appointment of Agency for SEO Management an...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-Senior Program Manager/Program Manager, Doctors f...
-Lung Care Foundation
-Location:
-Haryana
-Apply by:
-08 Apr 2026
-Program Head - MIS And Technology
-Dhwani Foundation
-Location:
-Karnataka
-Apply by:
-08 Apr 2026
-Associate/Specialist-Supply Chain
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+Assistant Manager (Partnerships and Fundraising)
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Assistant Manager – MIS
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+UN Women National Consultant – GRB Technical Coor...
+UN Women
+Location:
+Delhi
 Apply by:
 22 Mar 2026
+UN Women National Consultant – GRB Expert - MWCD,...
+UN Women
+Location:
+Delhi
+Apply by:
+22 Mar 2026
+Communication Officer
+Association for Stimulating Know How (ASK)
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Program Coordinator
+Sampark Foundation
+Location:
+India
+Apply by:
+10 Apr 2026
+Senior Consultant – Education
+TeamLease Foundation
+Location:
+Delhi
+Apply by:
+10 Apr 2026
+Program Coordinator - Government Relations  &amp; Adv...
+Quest Alliance
+Location:
+Andhra Pradesh
+Apply by:
+10 Apr 2026
 Jobseekers
 Register
 Login
@@ -5465,38 +5702,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F24" s="1" t="inlineStr">
+      <c r="F25" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G24" s="1" t="inlineStr">
+      <c r="G25" s="1" t="inlineStr">
         <is>
           <t>31-03-2026</t>
         </is>
       </c>
-      <c r="H24" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="I24" s="1" t="inlineStr">
+      <c r="H25" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="I25" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287726</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr"/>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="B26" s="1" t="inlineStr"/>
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>Associate – Finance and Operations</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Financial Management Service Foundation (FMSF) | Uttar Pradesh
 International Development - Associate – Finance and Operations, Financial Management Service Foundation (FMSF), Uttar Pradesh - DevNetJobsIndia.org
@@ -5511,7 +5748,7 @@
 Search ... Read More</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>• Joining FMSF means becoming part of a passionate team dedicated to making a positive impact. We offer competitive compensation, opportunities for professional development, and a supportive work environment where your contributions are valued and recognized. If you are committed to driving positive change, promoting accountability and strengthening the development sector, we encourage you to apply for the position of
 Associate – Finance and Operations
@@ -5533,6 +5770,24 @@
 Subscribe
 Premium Jobs
 Post your premium jobs here
+Unit Head - Proposal Development
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Research Analysts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
 Sector Experts
 Academy of Management Studies (AMS)
 Location:
@@ -5545,12 +5800,6 @@
 Uttar Pradesh
 Apply by:
 05 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
 Junior Research Technicians / Senior Project Asso...
 Starshield Security Solution Pvt.Ltd
 Location:
@@ -5581,68 +5830,56 @@
 Uttar Pradesh
 Apply by:
 13 Mar 2026
-Chief Programs Officer for Project Potential
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
-Program Lead- Finance &amp; Compliance for Project Po...
-Project Potential
-Location:
-Bihar
-Apply by:
-11 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Sr MEAL Officer, Preconception Nutrition and Care
-Nutrition International
-Location:
-Delhi
-Apply by:
-29 Mar 2026
-Academic Mentor
-Bharti Airtel Foundation
-Location:
-Sikkim, Assam, Jharkhand
-Apply by:
-09 Apr 2026
-Manager – Enterprise Promotion
-Project Concern International India (PCI India)
-Location:
-Bihar
-Apply by:
-13 Mar 2026
-RFP - Design, Development, Deployment and Mainten...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-RFP - Appointment of Agency for SEO Management an...
-YRGCARE
-Location:
-India
-Apply by:
-19 Mar 2026
-Senior Program Manager/Program Manager, Doctors f...
-Lung Care Foundation
-Location:
-Haryana
-Apply by:
-08 Apr 2026
-Program Head - MIS And Technology
-Dhwani Foundation
-Location:
-Karnataka
-Apply by:
-08 Apr 2026
-Associate/Specialist-Supply Chain
-India Health Action Trust (IHAT)
-Location:
-Uttar Pradesh
+Assistant Manager (Partnerships and Fundraising)
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Assistant Manager – MIS
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+UN Women National Consultant – GRB Technical Coor...
+UN Women
+Location:
+Delhi
 Apply by:
 22 Mar 2026
+UN Women National Consultant – GRB Expert - MWCD,...
+UN Women
+Location:
+Delhi
+Apply by:
+22 Mar 2026
+Communication Officer
+Association for Stimulating Know How (ASK)
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Program Coordinator
+Sampark Foundation
+Location:
+India
+Apply by:
+10 Apr 2026
+Senior Consultant – Education
+TeamLease Foundation
+Location:
+Delhi
+Apply by:
+10 Apr 2026
+Program Coordinator - Government Relations  &amp; Adv...
+Quest Alliance
+Location:
+Andhra Pradesh
+Apply by:
+10 Apr 2026
 Jobseekers
 Register
 Login
@@ -5670,332 +5907,867 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F25" s="1" t="inlineStr">
+      <c r="F26" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G25" s="1" t="inlineStr">
+      <c r="G26" s="1" t="inlineStr">
         <is>
           <t>05-04-2026</t>
         </is>
       </c>
-      <c r="H25" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="I25" s="1" t="inlineStr">
+      <c r="H26" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="I26" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287913</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B26" s="1" t="inlineStr"/>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>RFP for Endline Evaluation Study - HSBC GCC Women Entrepreneurship Program - Click here</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr"/>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="1" t="inlineStr">
-        <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G26" s="1" t="inlineStr"/>
-      <c r="H26" s="1" t="inlineStr"/>
-      <c r="I26" s="1" t="inlineStr">
-        <is>
-          <t>https://www.nasscomfoundation.org/pdf/endline-evaluation-study-hsbc-gcc-women-entrepreneurship-program.pdf</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
+          <t>DevNetJobsIndia</t>
         </is>
       </c>
       <c r="B27" s="1" t="inlineStr"/>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>Travel &amp; Transportation Services for Trainer Mobility - IBM SkillBuild Bootcamps - Click here</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr"/>
-      <c r="E27" s="2" t="inlineStr"/>
+          <t>Research Analysts</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Academy of Management Studies (AMS) | India
+International Development - Research Analysts, Academy of Management Studies (AMS), India - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers:
+Login
+|
+Register
+Jobseekers Log ... Read More</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>• Eligibility:
+R
+elevant
+experience
+in a research or consulting firm.
+Research Analyst (Proposal Development Unit):
+Minimum 3 Years
+Research Analyst (Project Execution Unit):
+Minimum 2 years
+Remuneration:
+This is a full-time regular position with an initial probation period of 1 year. Starting remuneration –
+Research Analyst (Proposal Development Unit):
+Rs. 10.8 lakh per annum
+Research Analyst (Project Execution Unit):
+Rs. 9.0 lakh
+per annum
+How
+to
+Apply
+Interested
+candidates
+may
+mail
+their
+detailed
+CV
+along
+with
+a
+recent
+photograph
+by
+11
+th
+April, (Saturday), 2026
+to
+hrd@amsindia.org
+mentioning
+“Research Analysts (Proposal Development Unit)”
+or
+“Research Analysts (Project Execution Unit)”
+in the subject line. The applicants must also mention in their emails the following details:
+Current
+status of
+Employment
+If
+employed,
+their
+current
+salary
+and
+notice
+period
+If
+currently
+not
+employed,
+their
+last
+salary
+drawn
+Only
+shortlisted
+candidates
+shall
+be
+notified
+by
+us.
+• Job Email ID:
+hrd(at)amsindia.org
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+11 Apr 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Unit Head - Proposal Development
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Research Analysts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+Assistant Manager (Partnerships and Fundraising)
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Assistant Manager – MIS
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+UN Women National Consultant – GRB Technical Coor...
+UN Women
+Location:
+Delhi
+Apply by:
+22 Mar 2026
+UN Women National Consultant – GRB Expert - MWCD,...
+UN Women
+Location:
+Delhi
+Apply by:
+22 Mar 2026
+Communication Officer
+Association for Stimulating Know How (ASK)
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Program Coordinator
+Sampark Foundation
+Location:
+India
+Apply by:
+10 Apr 2026
+Senior Consultant – Education
+TeamLease Foundation
+Location:
+Delhi
+Apply by:
+10 Apr 2026
+Program Coordinator - Government Relations  &amp; Adv...
+Quest Alliance
+Location:
+Andhra Pradesh
+Apply by:
+10 Apr 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G27" s="1" t="inlineStr"/>
-      <c r="H27" s="1" t="inlineStr"/>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G27" s="1" t="inlineStr">
+        <is>
+          <t>11-04-2026</t>
+        </is>
+      </c>
+      <c r="H27" s="1" t="n">
+        <v>31</v>
+      </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/travel-and-transportation-services-for-trainer-mobility-ibm-skillbuild-bootcamps.pdf</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=288160</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
+          <t>DevNetJobsIndia</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr"/>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>Baseline and End-line Evaluation of the HSBC Neurodivergent Digital Annotator Skilling Program - Click here | Click here</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr"/>
-      <c r="E28" s="2" t="inlineStr"/>
+          <t>Unit Head - Proposal Development</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Academy of Management Studies (AMS) | India
+International Development - Unit Head - Proposal Development, Academy of Management Studies (AMS), India - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers:
+Login
+|
+Register ... Read More</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>• Understand client requirements and check our eligibility against the criteria given in the bid
+Prepare detailed queries to be raised in the pre-bid meetings
+Participate in the pre-bid meetings and to get proper redressal of the queries
+Work in close coordination with the Proposal Development Team
+Assure quality of proposals being submitted and offer suggestions for enrichment to the team
+Monitor the bid outcomes and scores to identify areas for improvement
+The position requires travelling for client meetings as per need
+Requirements:
+Excellent command over written &amp; verbal English (both grammar and language), to be adjudged through an English Writing Ability Test
+Excellent presentation skills
+Experience in leading cross-functional teams and managing timelines under tight deadlines
+Postgraduate in any discipline, preferably MBA/PGDM, from a reputed institution
+• Eligibility:
+Min. 5 years
+of
+relevant
+work
+experience
+(Proposal Development with a knowledge-based service sector organisation, preferably in a research or consulting firm
+)
+Remuneration:
+This is a full-time regular position with a remuneration of
+Rs. 12.0 lakh per annum
+How
+to
+Apply
+Interested
+candidates
+may
+mail
+their
+detailed
+CV
+along
+with
+a
+recent
+photograph
+by
+11
+th
+April (Saturday), 2026
+to
+hrd@amsindia.org
+mentioning
+“Unit Head – Proposal Development”
+in the subject line. The applicants must also mention in their emails the following details:
+Current
+status of
+Employment
+If
+employed,
+their
+current
+salary
+and
+notice
+period
+If
+currently
+not
+employed,
+their
+last
+salary
+drawn
+Only
+shortlisted
+candidates
+shall
+be
+notified
+by
+us.
+• Job Email ID:
+hrd(at)amsindia.org
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+11 Apr 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Unit Head - Proposal Development
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Research Analysts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+Assistant Manager (Partnerships and Fundraising)
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Assistant Manager – MIS
+Pragya
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+UN Women National Consultant – GRB Technical Coor...
+UN Women
+Location:
+Delhi
+Apply by:
+22 Mar 2026
+UN Women National Consultant – GRB Expert - MWCD,...
+UN Women
+Location:
+Delhi
+Apply by:
+22 Mar 2026
+Communication Officer
+Association for Stimulating Know How (ASK)
+Location:
+Haryana
+Apply by:
+10 Apr 2026
+Program Coordinator
+Sampark Foundation
+Location:
+India
+Apply by:
+10 Apr 2026
+Senior Consultant – Education
+TeamLease Foundation
+Location:
+Delhi
+Apply by:
+10 Apr 2026
+Program Coordinator - Government Relations  &amp; Adv...
+Quest Alliance
+Location:
+Andhra Pradesh
+Apply by:
+10 Apr 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
       <c r="F28" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G28" s="1" t="inlineStr"/>
-      <c r="H28" s="1" t="inlineStr"/>
+          <t>Governance, Learning</t>
+        </is>
+      </c>
+      <c r="G28" s="1" t="inlineStr">
+        <is>
+          <t>11-04-2026</t>
+        </is>
+      </c>
+      <c r="H28" s="1" t="n">
+        <v>31</v>
+      </c>
       <c r="I28" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/baseline-and-end-line-evaluation-of-hsbc-neurodivergent-digital-annotator-skilling-program.pdf</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=288161</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B29" s="1" t="inlineStr"/>
+          <t>HCL Foundation</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>RFP for Catering Vendor - IBM Skillbuild Bootcamps - Click here</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards Biodiversity monitoring for Pan-India Afforestation sites</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G29" s="1" t="inlineStr"/>
+          <t>Climate</t>
+        </is>
+      </c>
+      <c r="G29" s="1" t="inlineStr">
+        <is>
+          <t>10th Feb, 2026</t>
+        </is>
+      </c>
       <c r="H29" s="1" t="inlineStr"/>
       <c r="I29" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/rfp-for-catering-vendor-ibm-skillbuild-bootcamps.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Biodiversity%20monitoring%20for%20Pan-India%20Afforestation%20sites%202-DSB.pdf</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B30" s="1" t="inlineStr"/>
+          <t>HCL Foundation</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>Organization-wide Management Information System (MIS) for Nasscom Foundation - Click here</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards soil profiling and assessment from the restored and rejuvenated Harit sites.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G30" s="1" t="inlineStr"/>
+          <t>Climate</t>
+        </is>
+      </c>
+      <c r="G30" s="1" t="inlineStr">
+        <is>
+          <t>10th Feb, 2026</t>
+        </is>
+      </c>
       <c r="H30" s="1" t="inlineStr"/>
       <c r="I30" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/organization-wide-management-information-system-for-nasscom-foundation.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Soil%20assessment-v1%20RKS-DSB_0.pdf</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B31" s="1" t="inlineStr"/>
+          <t>HCL Foundation</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>Request for Proposal (RFP) for Social Media Management Services - Click here</t>
+          <t>HCLFoundation invites proposals from NGOs/CSR implementing agencies for ‘Operating a Social Enterprise Cafe” under the flagship urban development programme - Uday</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G31" s="1" t="inlineStr"/>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G31" s="1" t="inlineStr">
+        <is>
+          <t>15th Dec, 2025</t>
+        </is>
+      </c>
       <c r="H31" s="1" t="inlineStr"/>
       <c r="I31" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/request-for-proposal-for-social-media-management-services.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-11/RfP_Social%20Enterprise%20Cafe_UDAY.docx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B32" s="1" t="inlineStr"/>
+          <t>HCL Foundation</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>RFP - TechForSociety - Evaluation Study - Click here</t>
+          <t>Programme Officer/Senior Programme Officer – Environment Education</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G32" s="1" t="inlineStr"/>
+          <t>Learning, Climate</t>
+        </is>
+      </c>
+      <c r="G32" s="1" t="inlineStr">
+        <is>
+          <t>10th Nov, 2025</t>
+        </is>
+      </c>
       <c r="H32" s="1" t="inlineStr"/>
       <c r="I32" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/techforsociety-evaluation-study.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-10/Harit_POSPO_EEA_Multilocation_Oct%202025.pdf</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B33" s="1" t="inlineStr"/>
+          <t>HCL Foundation</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>Base-line and End-line evaluation for Digital Literacy Project in 4 States - Click here</t>
+          <t>HCLFoundation invites applications for the PO/SPO position under its flagship programme Harit by HCLFoundation</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="1" t="inlineStr">
         <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G33" s="1" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G33" s="1" t="inlineStr">
+        <is>
+          <t>31st Oct, 2025</t>
+        </is>
+      </c>
       <c r="H33" s="1" t="inlineStr"/>
       <c r="I33" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/base-line-and-end-line-evaluation-for-digital-literacy-project-in-4-states.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-10/JD_Water%20Conservation_SPO%20V4.pdf</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B34" s="1" t="inlineStr"/>
+          <t>HCL Foundation</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>IP Selection - Scholarship Support to students from Economically Weaker Section pursuing higher education in STEM courses - Click here</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit by HCLFoundation, invites RFP from NGOs / CSR organizations working in Water Conservation for the development of Water Structures etc.</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G34" s="1" t="inlineStr"/>
+          <t>Learning, Climate</t>
+        </is>
+      </c>
+      <c r="G34" s="1" t="inlineStr">
+        <is>
+          <t>21st May, 2025</t>
+        </is>
+      </c>
       <c r="H34" s="1" t="inlineStr"/>
       <c r="I34" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/scholarship-support-for-economically-weaker-section-students-in-stem-higher-education.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/Final_RFP%20for%20water%20structure%20rejuvenation%20.docx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B35" s="1" t="inlineStr"/>
+          <t>HCL Foundation</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>Digital Upskilling of Farmer Producer Organizations (FPOs) through Technology - Click here</t>
+          <t>HCLFoundation invites technical application abstracts for the developing technology drive source code model mobile applications and web portals for addressing human-animal interactions under the Animal Welfare thematic of  Harit by HCLFoundation</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G35" s="1" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G35" s="1" t="inlineStr">
+        <is>
+          <t>15th May, 2025</t>
+        </is>
+      </c>
       <c r="H35" s="1" t="inlineStr"/>
       <c r="I35" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/baseline-endline-study-digital-upskilling-fpos-technology.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_AW%20Tech%20Based%20Source%20Code%20Model_V1%20%281%29.docx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="inlineStr"/>
+          <t>HCL Foundation</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>Project - Accelerating 100 Women Micro Entrepreneurs of Northeastern States - Click here</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit invites RFP from NGOs/CSR organizations working in the field of environment for project on the restoration of various degraded and natural habitats</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G36" s="1" t="inlineStr"/>
+          <t>Climate</t>
+        </is>
+      </c>
+      <c r="G36" s="1" t="inlineStr">
+        <is>
+          <t>15th May, 2025</t>
+        </is>
+      </c>
       <c r="H36" s="1" t="inlineStr"/>
       <c r="I36" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/project-accelerating-100-women-micro-entrepreneurs-of-northeastern-states.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/Harit_A%20HR_RFP%20.docx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="inlineStr"/>
+          <t>HCL Foundation</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>Agency for Developing Training Modules and Conducting Training of Trainers (ToT) for MSMEs on IPR and Financial Management - Click here</t>
+          <t>HCLFoundation invites EOI for conducting holistic and comprehensive Impact Assessments of environmental projects supported under Harit by HCLFoundation</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr"/>
@@ -6005,550 +6777,617 @@
           <t>Governance</t>
         </is>
       </c>
-      <c r="G37" s="1" t="inlineStr"/>
+      <c r="G37" s="1" t="inlineStr">
+        <is>
+          <t>15th May, 2025</t>
+        </is>
+      </c>
       <c r="H37" s="1" t="inlineStr"/>
       <c r="I37" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/agency-for-developing-training-modules-and-conducting-ToT-for-MSMEs-on-IPR-and-financial-management.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_Harit%20Impact%20Assessments.docx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B38" s="1" t="inlineStr"/>
+          <t>HCL Foundation</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>RFP for WISE - Women in Innovation, Skills &amp; Entrepreneurship - Click here</t>
+          <t>HCLFoundation invites technical application abstracts for the conducting technical and highly engaging environment awareness and sustainability workshops under Harit by HCLFoundation</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G38" s="1" t="inlineStr"/>
+          <t>Climate</t>
+        </is>
+      </c>
+      <c r="G38" s="1" t="inlineStr">
+        <is>
+          <t>15th May, 2025</t>
+        </is>
+      </c>
       <c r="H38" s="1" t="inlineStr"/>
       <c r="I38" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/women-in-Innovation-skills-and-entrepreneurship.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_EEA_Env%20%20Sus%20awareness%20workshops_FY%2025-26%20%281%29.docx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B39" s="1" t="inlineStr"/>
+          <t>NIUA</t>
+        </is>
+      </c>
+      <c r="B39" s="1" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - English  - Click here</t>
+          <t>Supply_of_Unskilled_Manpower.pdf</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr"/>
-      <c r="F39" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
+      <c r="F39" s="1" t="inlineStr"/>
       <c r="G39" s="1" t="inlineStr"/>
       <c r="H39" s="1" t="inlineStr"/>
       <c r="I39" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-English.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/Supply_of_Unskilled_Manpower.pdf</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B40" s="1" t="inlineStr"/>
+          <t>NIUA</t>
+        </is>
+      </c>
+      <c r="B40" s="1" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - Kannada - Click here</t>
+          <t>Addendum manpower quotation.pdf</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
+      <c r="F40" s="1" t="inlineStr"/>
       <c r="G40" s="1" t="inlineStr"/>
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-Kannada.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/Addendum%20manpower%20quotation.pdf</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B41" s="1" t="inlineStr"/>
+          <t>NIUA</t>
+        </is>
+      </c>
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>RFP - Trainer for Nano Women Entrepreneurs in Karnataka - Click here</t>
+          <t>Quotation_for_Rate_Contrac_Vehicle_Hiring_for_NCR_or_Outstation..pdf</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr"/>
       <c r="E41" s="2" t="inlineStr"/>
-      <c r="F41" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
+      <c r="F41" s="1" t="inlineStr"/>
       <c r="G41" s="1" t="inlineStr"/>
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/trainer-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/Quotation_for_Rate_Contrac_Vehicle_Hiring_for_NCR_or_Outstation..pdf</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B42" s="1" t="inlineStr"/>
+          <t>NIUA</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>RFP - Training Agency with Content and Trainers for Nano Women Entrepreneurs in Karnataka - Click here</t>
+          <t>Final_RfP_UrbanShift_Preparation_of_Integrated_Green_Mobility_Plan_for_Pune.pdf</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
+      <c r="F42" s="1" t="inlineStr"/>
       <c r="G42" s="1" t="inlineStr"/>
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/training-agency-with-content-and-trainers-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/Final_RfP_UrbanShift_Preparation_of_Integrated_Green_Mobility_Plan_for_Pune.pdf</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B43" s="1" t="inlineStr"/>
+          <t>NIUA</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>Access to E-Governance and Livelihood in PVTG Communities in Aspirational Blocks - Click here</t>
+          <t>RfP_IGMP_Response to Pre-Bid Queries_200226.pdf</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
       <c r="E43" s="2" t="inlineStr"/>
-      <c r="F43" s="1" t="inlineStr">
-        <is>
-          <t>Governance</t>
-        </is>
-      </c>
+      <c r="F43" s="1" t="inlineStr"/>
       <c r="G43" s="1" t="inlineStr"/>
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/access-to-e-governance-and-livelihood-in-pvtg-communities-in-aspirational-blocks.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/RfP_IGMP_Response%20to%20Pre-Bid%20Queries_200226.pdf</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>Nasscom</t>
-        </is>
-      </c>
-      <c r="B44" s="1" t="inlineStr"/>
+          <t>NIUA</t>
+        </is>
+      </c>
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>thingQbator Portal Enhancement and Maintenance Proposal - Click here</t>
+          <t>Corrigendum_1_RfP_IGMP.pdf</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
       <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
+      <c r="F44" s="1" t="inlineStr"/>
       <c r="G44" s="1" t="inlineStr"/>
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr">
         <is>
-          <t>https://www.nasscomfoundation.org/pdf/thingQbator-portal-enhancement-and-maintenance-proposal.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/Corrigendum_1_RfP_IGMP.pdf</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>HCL Foundation</t>
+          <t>NIUA</t>
         </is>
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Tender</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards Biodiversity monitoring for Pan-India Afforestation sites</t>
+          <t>Corrigendum 2_IGMP.pdf</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
       <c r="E45" s="2" t="inlineStr"/>
-      <c r="F45" s="1" t="inlineStr">
-        <is>
-          <t>Climate</t>
-        </is>
-      </c>
-      <c r="G45" s="1" t="inlineStr">
-        <is>
-          <t>10th Feb, 2026</t>
-        </is>
-      </c>
+      <c r="F45" s="1" t="inlineStr"/>
+      <c r="G45" s="1" t="inlineStr"/>
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Biodiversity%20monitoring%20for%20Pan-India%20Afforestation%20sites%202-DSB.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/Corrigendum%202_IGMP.pdf</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>HCL Foundation</t>
+          <t>NIUA</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Tender</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards soil profiling and assessment from the restored and rejuvenated Harit sites.</t>
+          <t>RFP_Engagement of GIS Expert_SCBP_2026.pdf</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="2" t="inlineStr"/>
-      <c r="F46" s="1" t="inlineStr">
-        <is>
-          <t>Climate</t>
-        </is>
-      </c>
-      <c r="G46" s="1" t="inlineStr">
-        <is>
-          <t>10th Feb, 2026</t>
-        </is>
-      </c>
+      <c r="F46" s="1" t="inlineStr"/>
+      <c r="G46" s="1" t="inlineStr"/>
       <c r="H46" s="1" t="inlineStr"/>
       <c r="I46" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Soil%20assessment-v1%20RKS-DSB_0.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/RFP_Engagement%20of%20GIS%20Expert_SCBP_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>HCL Foundation</t>
+          <t>NIUA</t>
         </is>
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Tender</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites proposals from NGOs/CSR implementing agencies for ‘Operating a Social Enterprise Cafe” under the flagship urban development programme - Uday</t>
+          <t>Response_to_Queries_Engagement_of_GIS_Expert_Agency.pdf</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
       <c r="E47" s="2" t="inlineStr"/>
-      <c r="F47" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G47" s="1" t="inlineStr">
-        <is>
-          <t>15th Dec, 2025</t>
-        </is>
-      </c>
+      <c r="F47" s="1" t="inlineStr"/>
+      <c r="G47" s="1" t="inlineStr"/>
       <c r="H47" s="1" t="inlineStr"/>
       <c r="I47" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-11/RfP_Social%20Enterprise%20Cafe_UDAY.docx</t>
+          <t>https://niua.in/sites/default/files/tenders/Response_to_Queries_Engagement_of_GIS_Expert_Agency.pdf</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>HCL Foundation</t>
+          <t>NIUA</t>
         </is>
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Tender</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>Programme Officer/Senior Programme Officer – Environment Education</t>
+          <t>RfP_SRTW.pdf</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
       <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="1" t="inlineStr">
-        <is>
-          <t>Learning, Climate</t>
-        </is>
-      </c>
-      <c r="G48" s="1" t="inlineStr">
-        <is>
-          <t>10th Nov, 2025</t>
-        </is>
-      </c>
+      <c r="F48" s="1" t="inlineStr"/>
+      <c r="G48" s="1" t="inlineStr"/>
       <c r="H48" s="1" t="inlineStr"/>
       <c r="I48" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-10/Harit_POSPO_EEA_Multilocation_Oct%202025.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/RfP_SRTW.pdf</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>HCL Foundation</t>
+          <t>NIUA</t>
         </is>
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Tender</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites applications for the PO/SPO position under its flagship programme Harit by HCLFoundation</t>
+          <t>Response to Pre-Bid Queries_SRTW_for Uploading.pdf</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
       <c r="E49" s="2" t="inlineStr"/>
-      <c r="F49" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G49" s="1" t="inlineStr">
-        <is>
-          <t>31st Oct, 2025</t>
-        </is>
-      </c>
+      <c r="F49" s="1" t="inlineStr"/>
+      <c r="G49" s="1" t="inlineStr"/>
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-10/JD_Water%20Conservation_SPO%20V4.pdf</t>
+          <t>https://niua.in/sites/default/files/tenders/Response%20to%20Pre-Bid%20Queries_SRTW_for%20Uploading.pdf</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>HCL Foundation</t>
+          <t>NIUA</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Tender</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit by HCLFoundation, invites RFP from NGOs / CSR organizations working in Water Conservation for the development of Water Structures etc.</t>
+          <t>EOI_TECHNICAL_ASSISTANCE_UNDER_CITIIS_2.0_PROGRAM_DOMESTIC_POOL_OF_EXPERTS.pdf</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
       <c r="E50" s="2" t="inlineStr"/>
-      <c r="F50" s="1" t="inlineStr">
-        <is>
-          <t>Learning, Climate</t>
-        </is>
-      </c>
-      <c r="G50" s="1" t="inlineStr">
-        <is>
-          <t>21st May, 2025</t>
-        </is>
-      </c>
+      <c r="F50" s="1" t="inlineStr"/>
+      <c r="G50" s="1" t="inlineStr"/>
       <c r="H50" s="1" t="inlineStr"/>
       <c r="I50" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/Final_RFP%20for%20water%20structure%20rejuvenation%20.docx</t>
+          <t>https://niua.in/sites/default/files/tenders/EOI_TECHNICAL_ASSISTANCE_UNDER_CITIIS_2.0_PROGRAM_DOMESTIC_POOL_OF_EXPERTS.pdf</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>HCL Foundation</t>
+          <t>NIUA</t>
         </is>
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Tender</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites technical application abstracts for the developing technology drive source code model mobile applications and web portals for addressing human-animal interactions under the Animal Welfare thematic of  Harit by HCLFoundation</t>
+          <t>Reply to Pre- Bid Queries - EOI for DE's under CITIIS 2.0.pdf</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
       <c r="E51" s="2" t="inlineStr"/>
-      <c r="F51" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G51" s="1" t="inlineStr">
-        <is>
-          <t>15th May, 2025</t>
-        </is>
-      </c>
+      <c r="F51" s="1" t="inlineStr"/>
+      <c r="G51" s="1" t="inlineStr"/>
       <c r="H51" s="1" t="inlineStr"/>
       <c r="I51" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_AW%20Tech%20Based%20Source%20Code%20Model_V1%20%281%29.docx</t>
+          <t>https://niua.in/sites/default/files/tenders/Reply%20to%20Pre-%20Bid%20Queries%20-%20EOI%20for%20DE%27s%20under%20CITIIS%202.0.pdf</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>HCL Foundation</t>
+          <t>NIUA</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Tender</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit invites RFP from NGOs/CSR organizations working in the field of environment for project on the restoration of various degraded and natural habitats</t>
+          <t>GeM-Bidding-8666471.pdf</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
       <c r="E52" s="2" t="inlineStr"/>
-      <c r="F52" s="1" t="inlineStr">
-        <is>
-          <t>Climate</t>
-        </is>
-      </c>
-      <c r="G52" s="1" t="inlineStr">
-        <is>
-          <t>15th May, 2025</t>
-        </is>
-      </c>
+      <c r="F52" s="1" t="inlineStr"/>
+      <c r="G52" s="1" t="inlineStr"/>
       <c r="H52" s="1" t="inlineStr"/>
       <c r="I52" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/Harit_A%20HR_RFP%20.docx</t>
+          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-8666471.pdf</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>HCL Foundation</t>
+          <t>NIUA</t>
         </is>
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Tender</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites EOI for conducting holistic and comprehensive Impact Assessments of environmental projects supported under Harit by HCLFoundation</t>
+          <t>corgaudt1.pdf</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
       <c r="E53" s="2" t="inlineStr"/>
-      <c r="F53" s="1" t="inlineStr">
-        <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G53" s="1" t="inlineStr">
-        <is>
-          <t>15th May, 2025</t>
-        </is>
-      </c>
+      <c r="F53" s="1" t="inlineStr"/>
+      <c r="G53" s="1" t="inlineStr"/>
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_Harit%20Impact%20Assessments.docx</t>
+          <t>https://niua.in/sites/default/files/tenders/corgaudt1.pdf</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>HCL Foundation</t>
+          <t>NIUA</t>
         </is>
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Tender</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites technical application abstracts for the conducting technical and highly engaging environment awareness and sustainability workshops under Harit by HCLFoundation</t>
+          <t>Corrigendum6959493.pdf</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
       <c r="E54" s="2" t="inlineStr"/>
-      <c r="F54" s="1" t="inlineStr">
-        <is>
-          <t>Climate</t>
-        </is>
-      </c>
-      <c r="G54" s="1" t="inlineStr">
-        <is>
-          <t>15th May, 2025</t>
-        </is>
-      </c>
+      <c r="F54" s="1" t="inlineStr"/>
+      <c r="G54" s="1" t="inlineStr"/>
       <c r="H54" s="1" t="inlineStr"/>
       <c r="I54" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_EEA_Env%20%20Sus%20awareness%20workshops_FY%2025-26%20%281%29.docx</t>
+          <t>https://niua.in/sites/default/files/tenders/Corrigendum6959493.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>NIUA</t>
+        </is>
+      </c>
+      <c r="B55" s="1" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C55" s="1" t="inlineStr">
+        <is>
+          <t>ADDENDUM6959493.pdf</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr"/>
+      <c r="E55" s="2" t="inlineStr"/>
+      <c r="F55" s="1" t="inlineStr"/>
+      <c r="G55" s="1" t="inlineStr"/>
+      <c r="H55" s="1" t="inlineStr"/>
+      <c r="I55" s="1" t="inlineStr">
+        <is>
+          <t>https://niua.in/sites/default/files/tenders/ADDENDUM6959493.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>NIUA</t>
+        </is>
+      </c>
+      <c r="B56" s="1" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C56" s="1" t="inlineStr">
+        <is>
+          <t>RfP CJ&amp;IP Package 03_UrbanShift.pdf</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr"/>
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="1" t="inlineStr"/>
+      <c r="G56" s="1" t="inlineStr"/>
+      <c r="H56" s="1" t="inlineStr"/>
+      <c r="I56" s="1" t="inlineStr">
+        <is>
+          <t>https://niua.in/sites/default/files/tenders/RfP%20CJ%26IP%20Package%2003_UrbanShift.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>NIUA</t>
+        </is>
+      </c>
+      <c r="B57" s="1" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C57" s="1" t="inlineStr">
+        <is>
+          <t>Prebid reply Cj&amp;IP package 3_18.12.2025.pdf</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr"/>
+      <c r="E57" s="2" t="inlineStr"/>
+      <c r="F57" s="1" t="inlineStr"/>
+      <c r="G57" s="1" t="inlineStr"/>
+      <c r="H57" s="1" t="inlineStr"/>
+      <c r="I57" s="1" t="inlineStr">
+        <is>
+          <t>https://niua.in/sites/default/files/tenders/Prebid%20reply%20Cj%26IP%20package%203_18.12.2025.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>NIUA</t>
+        </is>
+      </c>
+      <c r="B58" s="1" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="inlineStr">
+        <is>
+          <t>GeM-Bidding-8478801.pdf</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr"/>
+      <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="1" t="inlineStr"/>
+      <c r="G58" s="1" t="inlineStr"/>
+      <c r="H58" s="1" t="inlineStr"/>
+      <c r="I58" s="1" t="inlineStr">
+        <is>
+          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-8478801.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>NIUA</t>
+        </is>
+      </c>
+      <c r="B59" s="1" t="inlineStr">
+        <is>
+          <t>Tender</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="inlineStr">
+        <is>
+          <t>GeM-Bidding-8476974.pdf</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr"/>
+      <c r="E59" s="2" t="inlineStr"/>
+      <c r="F59" s="1" t="inlineStr"/>
+      <c r="G59" s="1" t="inlineStr"/>
+      <c r="H59" s="1" t="inlineStr"/>
+      <c r="I59" s="1" t="inlineStr">
+        <is>
+          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-8476974.pdf</t>
         </is>
       </c>
     </row>

--- a/all_grants.xlsx
+++ b/all_grants.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -489,245 +489,10 @@
       <c r="B2" s="1" t="inlineStr"/>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>RFP - for Supply of Skill Lab Items</t>
+          <t>SOW - Engagement of a Public Relations (PR) Agency on Retainer</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>TeamLease Foundation | India
-International Development - RFP - for Supply of Skill Lab Items, TeamLease Foundation, India - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Login
-|
-Register
-Jobseekers Login
-Jobseeker ... Read More</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>• Technical Bid Submission Link-
-https://forms.gle/V9iy35ddb4kWEb468
-• Financial Bid Submission Link-
-https://forms.gle/LozobuuuMh55Ea2G8
-Note
-: Technical bid and financial bid are to be submitted separately in separate links.
-Following points are to be kept in mind while submitting the bids-
-All Bid must contain the complete address of firm, including contact number/ email ID of the person who is authorized to submit the bid under their signatures.
-All bids must be signed on all pages by the bidder. Unsigned bids shall not be entertained/ accepted.
-All pages of the bid being submitted must be signed and sequentially numbered by the bidder irrespective of the nature of content of the documents.
-Bids not submitted as per the specified format and nomenclature or ambiguous in nature will be liable to be rejected.
-• The interested bidders may submit their bid to TLF on or before the date mentioned in this RFP Documents. Any bid received by TLF after the prescribed deadline for submission of bids will be rejected and no further correspondence in this regard will be entertained.
-Financial bid should be prepared as per Annexure II given in the RFP Documents. Same is also to be uploaded in google forms too.
-Bidders shall indicate their rates in clear/ visible figures as well as in words. In case of a mismatch, the rates written in words will prevail.
-• At any time prior to the last date for submission of bids, TLF, may, for any reason, whether at its own initiative or in response to a clarification requested by a prospective bidder, modify the RFP Documents by an amendment and publish the revised version of the RFP.
-The contract panel may consist of maximum three vendors for each item. However, TLF reserves the right to review the performance of the panel of vendors and terminate the contract of such vendors whose performance is not found satisfactory. The decision of TLF will be final in this regard.
-TLF will issue Purchase Order(s) (PO) during the period up to 31-March-2026. as per the required quantities and as per the rates and other terms of the Purchase Order.
-TLF may issue separate Purchase Order(s) PO based on its actual requirements to the Successful Bidder(s) for providing Product(s) and / or Service(s) and there is no minimum or prior commitment for such orders under this RFP.
-The successful bidder will be expected to provide all the necessary support for delivery of the items, warranty and required support during the warranty period.
-Delivery of the Kits specified in this RFP should be by 20
-th
-December 2025 from the PO date
-Successful bidder will ensure delivery, installation and operationalization of all products /components under the contract before acceptance testing / examination, and the Warranty period will commence only on acceptance of the products
-If, during the warranty period, any system as a whole or any subsystem has any failure on two or more occasions in a period of 3 months, it shall be replaced by equivalent new equipment by the Vendor at no cost to TLF
-The successful bidder shall be fully responsible for the manufacturer’s warranty for all equipment, accessories, spare parts etc. against any defects arising from design, material, manufacturing, workmanship, or any act or omission of the manufacturer / vendor or any defect that may develop under normal use of supplied equipment during the warranty period
-In case of any deviations, specific exemption may be sought on case-to-case basis from the respective Departments placing the Service Request
-• Printed terms and conditions of the bidders will not be considered as forming part of their bid. In case terms and conditions as given in the RFP Documents are not acceptable to any bidder, they should clearly specify the deviations in their bids.
-Bids complete in all respects along with supporting documents, must be submitted as per the RFP requirements. No physical document is to be submitted by the bidders.
-NO conditional or partial Bid will be entertained and will be rejected.
-• Parallel Contracts - TLF may also execute parallel contracts with more than one firm on the lowest approved rates on the same terms and conditions. These parallel contracts will be utilized if the original L1 substantially technically qualified bidder is not in a position to supply material as per TLFs requirement within the time frame indicated in the bid.
-For detailed information, please check the complete version of the RFP attached below.
-Download Attachment:
-RFP for procurement Skill Lab Items under RIST Mansi_250226.pdf
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-11 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Unit Head - Proposal Development
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-11 Apr 2026
-Research Analysts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-11 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Associate – Finance and Operations
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-05 Apr 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-Assistant Manager (Partnerships and Fundraising)
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Assistant Manager – MIS
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-UN Women National Consultant – GRB Technical Coor...
-UN Women
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-UN Women National Consultant – GRB Expert - MWCD,...
-UN Women
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-Communication Officer
-Association for Stimulating Know How (ASK)
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Program Coordinator
-Sampark Foundation
-Location:
-India
-Apply by:
-10 Apr 2026
-Senior Consultant – Education
-TeamLease Foundation
-Location:
-Delhi
-Apply by:
-10 Apr 2026
-Program Coordinator - Government Relations  &amp; Adv...
-Quest Alliance
-Location:
-Andhra Pradesh
-Apply by:
-10 Apr 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>11-03-2026</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287613</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr"/>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>SOW - Engagement of a Public Relations (PR) Agency on Retainer</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Room to Read India | India
 International Development - SOW - Engagement of a Public Relations (PR) Agency on Retainer, Room to Read India, India - DevNetJobsIndia.org
@@ -748,7 +513,7 @@
 Job ... Read More</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>• Scope of Work (SOW)
 Engagement of a Public Relations (PR) Agency on Retainer
@@ -878,54 +643,54 @@
 13 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Partnerships and Fundraising)
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Assistant Manager – MIS
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-UN Women National Consultant – GRB Technical Coor...
-UN Women
-Location:
-Delhi
+State Consultant - Communication, Advocacy and Pa...
+UNICEF
+Location:
+Rajasthan
+Apply by:
+23 Mar 2026
+RFP - Hiring agency to implement the organisation...
+Breakthrough
+Location:
+India
 Apply by:
 22 Mar 2026
-UN Women National Consultant – GRB Expert - MWCD,...
-UN Women
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-Communication Officer
-Association for Stimulating Know How (ASK)
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Program Coordinator
-Sampark Foundation
-Location:
-India
-Apply by:
-10 Apr 2026
-Senior Consultant – Education
-TeamLease Foundation
-Location:
-Delhi
-Apply by:
-10 Apr 2026
-Program Coordinator - Government Relations  &amp; Adv...
-Quest Alliance
-Location:
-Andhra Pradesh
-Apply by:
-10 Apr 2026
+Technical Consultant - Hydrogeologists
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+IFP - for Strengthening systems for multi-sectora...
+UNFPA
+Location:
+India
+Apply by:
+17 Apr 2026
+Technical Consultant – Support and facilitate Tra...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant/Firm - Infrastructure Design...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - WASH Infrastructure monito...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - for Short-Term Studies, As...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
 Jobseekers
 Register
 Login
@@ -953,38 +718,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>Governance, Learning</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>12-03-2026</t>
         </is>
       </c>
-      <c r="H3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="H2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287648</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr"/>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr"/>
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>RFP - for Internal Audit</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>India HIV/AIDS Alliance (Alliance India) | Delhi
 International Development - RFP - for Internal Audit, India HIV/AIDS Alliance (Alliance India), Delhi - DevNetJobsIndia.org
@@ -1004,7 +769,7 @@
 Regist ... Read More</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>• Alliance India reserves the right to reject applications that do not meet eligibility or application submission requirements (as detailed above) without further notice to the applicant. Issuance of this RFP does not constitute an award commitment or a guarantee of business on the part of Alliance India, nor does it commit Alliance India to pay for the costs incurred in submitting the application. Further, Alliance India reserves the right to reject any or all applications received and negotiate separately with an applicant if such action is considered in the best interest of Alliance India/ project.
 iii.
@@ -1091,54 +856,54 @@
 13 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Partnerships and Fundraising)
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Assistant Manager – MIS
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-UN Women National Consultant – GRB Technical Coor...
-UN Women
-Location:
-Delhi
+State Consultant - Communication, Advocacy and Pa...
+UNICEF
+Location:
+Rajasthan
+Apply by:
+23 Mar 2026
+RFP - Hiring agency to implement the organisation...
+Breakthrough
+Location:
+India
 Apply by:
 22 Mar 2026
-UN Women National Consultant – GRB Expert - MWCD,...
-UN Women
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-Communication Officer
-Association for Stimulating Know How (ASK)
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Program Coordinator
-Sampark Foundation
-Location:
-India
-Apply by:
-10 Apr 2026
-Senior Consultant – Education
-TeamLease Foundation
-Location:
-Delhi
-Apply by:
-10 Apr 2026
-Program Coordinator - Government Relations  &amp; Adv...
-Quest Alliance
-Location:
-Andhra Pradesh
-Apply by:
-10 Apr 2026
+Technical Consultant - Hydrogeologists
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+IFP - for Strengthening systems for multi-sectora...
+UNFPA
+Location:
+India
+Apply by:
+17 Apr 2026
+Technical Consultant – Support and facilitate Tra...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant/Firm - Infrastructure Design...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - WASH Infrastructure monito...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - for Short-Term Studies, As...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
 Jobseekers
 Register
 Login
@@ -1166,38 +931,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F4" s="1" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G4" s="1" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>13-03-2026</t>
         </is>
       </c>
-      <c r="H4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I4" s="1" t="inlineStr">
+      <c r="H3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287765</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr"/>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr"/>
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>Specialist – Financial Management and Compliance</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Financial Management Service Foundation (FMSF) | Uttar Pradesh
 International Development - Specialist – Financial Management and Compliance, Financial Management Service Foundation (FMSF), Uttar Pradesh - DevNetJobsIndia.org
@@ -1211,7 +976,7 @@
 RFPs/T ... Read More</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>• will play a vital role in a program which seeks to strengthen the internal capacities of non-profit organizations in India across three building blocks of institutional functioning: governance, financial management, and compliance. These areas are deeply interconnected and together determine how effectively an organization operates, delivers programs and meets the expectations of its stakeholders. This position demands expertise in specific areas related to governance, compliance, and financial management, contributing essential guidance and support to strengthen the capabilities of participating organizations.
 Job Responsibilities:
@@ -1324,54 +1089,54 @@
 13 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Partnerships and Fundraising)
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Assistant Manager – MIS
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-UN Women National Consultant – GRB Technical Coor...
-UN Women
-Location:
-Delhi
+State Consultant - Communication, Advocacy and Pa...
+UNICEF
+Location:
+Rajasthan
+Apply by:
+23 Mar 2026
+RFP - Hiring agency to implement the organisation...
+Breakthrough
+Location:
+India
 Apply by:
 22 Mar 2026
-UN Women National Consultant – GRB Expert - MWCD,...
-UN Women
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-Communication Officer
-Association for Stimulating Know How (ASK)
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Program Coordinator
-Sampark Foundation
-Location:
-India
-Apply by:
-10 Apr 2026
-Senior Consultant – Education
-TeamLease Foundation
-Location:
-Delhi
-Apply by:
-10 Apr 2026
-Program Coordinator - Government Relations  &amp; Adv...
-Quest Alliance
-Location:
-Andhra Pradesh
-Apply by:
-10 Apr 2026
+Technical Consultant - Hydrogeologists
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+IFP - for Strengthening systems for multi-sectora...
+UNFPA
+Location:
+India
+Apply by:
+17 Apr 2026
+Technical Consultant – Support and facilitate Tra...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant/Firm - Infrastructure Design...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - WASH Infrastructure monito...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - for Short-Term Studies, As...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
 Jobseekers
 Register
 Login
@@ -1399,41 +1164,41 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F5" s="1" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G5" s="1" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>13-03-2026</t>
         </is>
       </c>
-      <c r="H5" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" s="1" t="inlineStr">
+      <c r="H4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287015</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr"/>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>ToR - Strategic Review and Forward-Looking Education Strategy Development</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>ChildFund India | India
-International Development - ToR - Strategic Review and Forward-Looking Education Strategy Development, ChildFund India, India - DevNetJobsIndia.org
+      <c r="B5" s="1" t="inlineStr"/>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>RFQ - for Developing an animated film</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Institute for Global Development (IGD) | India
+International Development - RFQ - for Developing an animated film, Institute for Global Development (IGD), India - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
@@ -1445,17 +1210,31 @@
 Search Jobs
 Events
 Jobseekers:
-Login
-|
-Registe ... Read More</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>• Job Email ID:
-centralpurchase2(at)childfundindia.org
-Download Attachment:
-ToR for Education.doc
+Login ... Read More</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>• Eligibility Criteria
+IGD
+invites agencies having expertise in developing films for the social sector
+C.
+Deliverables/Outputs
+1.
+Storyboard
+2.
+Final edited 2–3-minute animated film in the required formats (mp4 and mov)
+D.
+PROPOSAL SUBMISSION
+The Agency shall submit Technical and Financial proposals separately for this assignment by
+15
+th
+Mar 2026
+to
+jobs@igdindia.org
+The Agency will provide a detailed cost breakup for each of the activities mentioned above. The costs should be inclusive of all taxes and the out-of-pocket expenses.
+• Job Email ID:
+jobs(at)igdindia.org
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
@@ -1528,54 +1307,54 @@
 13 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Partnerships and Fundraising)
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Assistant Manager – MIS
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-UN Women National Consultant – GRB Technical Coor...
-UN Women
-Location:
-Delhi
+State Consultant - Communication, Advocacy and Pa...
+UNICEF
+Location:
+Rajasthan
+Apply by:
+23 Mar 2026
+RFP - Hiring agency to implement the organisation...
+Breakthrough
+Location:
+India
 Apply by:
 22 Mar 2026
-UN Women National Consultant – GRB Expert - MWCD,...
-UN Women
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-Communication Officer
-Association for Stimulating Know How (ASK)
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Program Coordinator
-Sampark Foundation
-Location:
-India
-Apply by:
-10 Apr 2026
-Senior Consultant – Education
-TeamLease Foundation
-Location:
-Delhi
-Apply by:
-10 Apr 2026
-Program Coordinator - Government Relations  &amp; Adv...
-Quest Alliance
-Location:
-Andhra Pradesh
-Apply by:
-10 Apr 2026
+Technical Consultant - Hydrogeologists
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+IFP - for Strengthening systems for multi-sectora...
+UNFPA
+Location:
+India
+Apply by:
+17 Apr 2026
+Technical Consultant – Support and facilitate Tra...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant/Firm - Infrastructure Design...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - WASH Infrastructure monito...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - for Short-Term Studies, As...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
 Jobseekers
 Register
 Login
@@ -1603,38 +1382,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>Learning, Safety</t>
-        </is>
-      </c>
-      <c r="G6" s="1" t="inlineStr">
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>15-03-2026</t>
         </is>
       </c>
-      <c r="H6" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I6" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287902</t>
+      <c r="H5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=288181</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr"/>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="B6" s="1" t="inlineStr"/>
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>ToR - Portfolio-Wide Learning Exercise cum review for the Health Domain</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>ChildFund India | India
 International Development - ToR - Portfolio-Wide Learning Exercise cum review for the Health Domain, ChildFund India, India - DevNetJobsIndia.org
@@ -1654,7 +1433,7 @@
 Register ... Read More</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>• Job Email ID:
 centralpurchase2(at)childfundindia.org
@@ -1732,54 +1511,54 @@
 13 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Partnerships and Fundraising)
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Assistant Manager – MIS
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-UN Women National Consultant – GRB Technical Coor...
-UN Women
-Location:
-Delhi
+State Consultant - Communication, Advocacy and Pa...
+UNICEF
+Location:
+Rajasthan
+Apply by:
+23 Mar 2026
+RFP - Hiring agency to implement the organisation...
+Breakthrough
+Location:
+India
 Apply by:
 22 Mar 2026
-UN Women National Consultant – GRB Expert - MWCD,...
-UN Women
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-Communication Officer
-Association for Stimulating Know How (ASK)
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Program Coordinator
-Sampark Foundation
-Location:
-India
-Apply by:
-10 Apr 2026
-Senior Consultant – Education
-TeamLease Foundation
-Location:
-Delhi
-Apply by:
-10 Apr 2026
-Program Coordinator - Government Relations  &amp; Adv...
-Quest Alliance
-Location:
-Andhra Pradesh
-Apply by:
-10 Apr 2026
+Technical Consultant - Hydrogeologists
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+IFP - for Strengthening systems for multi-sectora...
+UNFPA
+Location:
+India
+Apply by:
+17 Apr 2026
+Technical Consultant – Support and facilitate Tra...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant/Firm - Infrastructure Design...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - WASH Infrastructure monito...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - for Short-Term Studies, As...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
 Jobseekers
 Register
 Login
@@ -1807,38 +1586,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F7" s="1" t="inlineStr">
+      <c r="F6" s="1" t="inlineStr">
         <is>
           <t>Learning, Safety</t>
         </is>
       </c>
-      <c r="G7" s="1" t="inlineStr">
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>15-03-2026</t>
         </is>
       </c>
-      <c r="H7" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I7" s="1" t="inlineStr">
+      <c r="H6" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287901</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr"/>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>RFP for Data Collection for Foundational Reading Tool in Odisha</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Lords Education and Health Society (LEHS) | Odisha
 International Development - RFP for Data Collection for Foundational Reading Tool in Odisha, Lords Education and Health Society (LEHS), Odisha - DevNetJobsIndia.org
@@ -1853,7 +1632,7 @@
 Se ... Read More</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>• 4. SCOPE OF WORK
 Summary of Activities
@@ -1952,54 +1731,54 @@
 13 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Partnerships and Fundraising)
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Assistant Manager – MIS
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-UN Women National Consultant – GRB Technical Coor...
-UN Women
-Location:
-Delhi
+State Consultant - Communication, Advocacy and Pa...
+UNICEF
+Location:
+Rajasthan
+Apply by:
+23 Mar 2026
+RFP - Hiring agency to implement the organisation...
+Breakthrough
+Location:
+India
 Apply by:
 22 Mar 2026
-UN Women National Consultant – GRB Expert - MWCD,...
-UN Women
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-Communication Officer
-Association for Stimulating Know How (ASK)
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Program Coordinator
-Sampark Foundation
-Location:
-India
-Apply by:
-10 Apr 2026
-Senior Consultant – Education
-TeamLease Foundation
-Location:
-Delhi
-Apply by:
-10 Apr 2026
-Program Coordinator - Government Relations  &amp; Adv...
-Quest Alliance
-Location:
-Andhra Pradesh
-Apply by:
-10 Apr 2026
+Technical Consultant - Hydrogeologists
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+IFP - for Strengthening systems for multi-sectora...
+UNFPA
+Location:
+India
+Apply by:
+17 Apr 2026
+Technical Consultant – Support and facilitate Tra...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant/Firm - Infrastructure Design...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - WASH Infrastructure monito...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - for Short-Term Studies, As...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
 Jobseekers
 Register
 Login
@@ -2027,90 +1806,41 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F8" s="1" t="inlineStr">
+      <c r="F7" s="1" t="inlineStr">
         <is>
           <t>Governance, Learning, Safety</t>
         </is>
       </c>
-      <c r="G8" s="1" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>15-03-2026</t>
         </is>
       </c>
-      <c r="H8" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I8" s="1" t="inlineStr">
+      <c r="H7" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287936</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr"/>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>RFP - for Empanelment of Knowledge Partners for Grooming of students for ...</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>TeamLease Foundation | India
-International Development - RFP - for  Empanelment of Knowledge Partners for Grooming of students for competitive examination (through partner) Super 30 Model, TeamLease Foundation, India - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast ... Read More</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
-          <t>15-03-2026</t>
-        </is>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I9" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287763</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="inlineStr"/>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>ToR - Livelihoods Strategy Review and Future Direction Roadmap</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr"/>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>ToR - Strategic Review and Forward-Looking Education Strategy Development</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>ChildFund India | India
-International Development - ToR - Livelihoods Strategy Review and Future Direction Roadmap, ChildFund India, India - DevNetJobsIndia.org
+International Development - ToR - Strategic Review and Forward-Looking Education Strategy Development, ChildFund India, India - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
@@ -2124,34 +1854,15 @@
 Jobseekers:
 Login
 |
-Register
-Jobseeker ... Read More</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>• To determine the relevance, alignment, and coherence of the Livelihood Program under CSP 2022–2027 with national priorities, donor expectations, and organizational mandate.
-To assess the extent to which planned outputs and outcomes have been achieved and to evaluate the quality and impact of program interventions.
-Identify achievements, innovations, good practices, and enabling factors across Livelihood program interventions.
-Document gaps, challenges, and areas for strengthening
-To examine the sustainability of program outcomes and the institutional readiness of ChildFund India for long-term resilience and growth.
-Facilitate reflection through workshops involving staff, partners, and selected beneficiaries and provide recommendations for strategic direction, scalability, and future program priorities.
-Proposal Submission
-Interested evaluators/agencies are invited to submit:
-Technical proposal outlining approach and methodology
-Team composition and relevant experience
-Financial proposal with a detailed budget
-Sample of previous qualitative evaluation work
-Interested evaluators/agencies are requested to submit their technical and financial proposals to
-centralpurchase2@childfundindia.org
-by 15 March 2026.
-Reference No:- PRA/CFI/DEL/2025-26/053
-ChildFund India reserves the right to modify this ToR based on programmatic and contextual requirements.
-For detailed information, please check the complete version of the advert attached below.
-• Job Email ID:
+Registe ... Read More</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>• Job Email ID:
 centralpurchase2(at)childfundindia.org
 Download Attachment:
-ToR Livelihood Portfolio-6.3.2026.doc
+ToR for Education.doc
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
@@ -2224,54 +1935,54 @@
 13 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Partnerships and Fundraising)
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Assistant Manager – MIS
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-UN Women National Consultant – GRB Technical Coor...
-UN Women
-Location:
-Delhi
+State Consultant - Communication, Advocacy and Pa...
+UNICEF
+Location:
+Rajasthan
+Apply by:
+23 Mar 2026
+RFP - Hiring agency to implement the organisation...
+Breakthrough
+Location:
+India
 Apply by:
 22 Mar 2026
-UN Women National Consultant – GRB Expert - MWCD,...
-UN Women
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-Communication Officer
-Association for Stimulating Know How (ASK)
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Program Coordinator
-Sampark Foundation
-Location:
-India
-Apply by:
-10 Apr 2026
-Senior Consultant – Education
-TeamLease Foundation
-Location:
-Delhi
-Apply by:
-10 Apr 2026
-Program Coordinator - Government Relations  &amp; Adv...
-Quest Alliance
-Location:
-Andhra Pradesh
-Apply by:
-10 Apr 2026
+Technical Consultant - Hydrogeologists
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+IFP - for Strengthening systems for multi-sectora...
+UNFPA
+Location:
+India
+Apply by:
+17 Apr 2026
+Technical Consultant – Support and facilitate Tra...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant/Firm - Infrastructure Design...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - WASH Infrastructure monito...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - for Short-Term Studies, As...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
 Jobseekers
 Register
 Login
@@ -2299,9 +2010,293 @@
 Recruitment Exchange</t>
         </is>
       </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>Learning, Safety</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>15-03-2026</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287902</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr"/>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>RFP - for Supply of Skill Lab Items</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>TeamLease Foundation | India
+International Development - RFP - for Supply of Skill Lab Items, TeamLease Foundation, India - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers:
+Login
+|
+Register
+Jobseekers Login
+Jobseeker ... Read More</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>• Technical Bid Submission Link-
+https://forms.gle/V9iy35ddb4kWEb468
+• Financial Bid Submission Link-
+https://forms.gle/LozobuuuMh55Ea2G8
+Note
+: Technical bid and financial bid are to be submitted separately in separate links.
+Following points are to be kept in mind while submitting the bids-
+All Bid must contain the complete address of firm, including contact number/ email ID of the person who is authorized to submit the bid under their signatures.
+All bids must be signed on all pages by the bidder. Unsigned bids shall not be entertained/ accepted.
+All pages of the bid being submitted must be signed and sequentially numbered by the bidder irrespective of the nature of content of the documents.
+Bids not submitted as per the specified format and nomenclature or ambiguous in nature will be liable to be rejected.
+• The interested bidders may submit their bid to TLF on or before the date mentioned in this RFP Documents. Any bid received by TLF after the prescribed deadline for submission of bids will be rejected and no further correspondence in this regard will be entertained.
+Financial bid should be prepared as per Annexure II given in the RFP Documents. Same is also to be uploaded in google forms too.
+Bidders shall indicate their rates in clear/ visible figures as well as in words. In case of a mismatch, the rates written in words will prevail.
+• At any time prior to the last date for submission of bids, TLF, may, for any reason, whether at its own initiative or in response to a clarification requested by a prospective bidder, modify the RFP Documents by an amendment and publish the revised version of the RFP.
+The contract panel may consist of maximum three vendors for each item. However, TLF reserves the right to review the performance of the panel of vendors and terminate the contract of such vendors whose performance is not found satisfactory. The decision of TLF will be final in this regard.
+TLF will issue Purchase Order(s) (PO) during the period up to 31-March-2026. as per the required quantities and as per the rates and other terms of the Purchase Order.
+TLF may issue separate Purchase Order(s) PO based on its actual requirements to the Successful Bidder(s) for providing Product(s) and / or Service(s) and there is no minimum or prior commitment for such orders under this RFP.
+The successful bidder will be expected to provide all the necessary support for delivery of the items, warranty and required support during the warranty period.
+Delivery of the Kits specified in this RFP should be by 20
+th
+December 2025 from the PO date
+Successful bidder will ensure delivery, installation and operationalization of all products /components under the contract before acceptance testing / examination, and the Warranty period will commence only on acceptance of the products
+If, during the warranty period, any system as a whole or any subsystem has any failure on two or more occasions in a period of 3 months, it shall be replaced by equivalent new equipment by the Vendor at no cost to TLF
+The successful bidder shall be fully responsible for the manufacturer’s warranty for all equipment, accessories, spare parts etc. against any defects arising from design, material, manufacturing, workmanship, or any act or omission of the manufacturer / vendor or any defect that may develop under normal use of supplied equipment during the warranty period
+In case of any deviations, specific exemption may be sought on case-to-case basis from the respective Departments placing the Service Request
+• Printed terms and conditions of the bidders will not be considered as forming part of their bid. In case terms and conditions as given in the RFP Documents are not acceptable to any bidder, they should clearly specify the deviations in their bids.
+Bids complete in all respects along with supporting documents, must be submitted as per the RFP requirements. No physical document is to be submitted by the bidders.
+NO conditional or partial Bid will be entertained and will be rejected.
+• Parallel Contracts - TLF may also execute parallel contracts with more than one firm on the lowest approved rates on the same terms and conditions. These parallel contracts will be utilized if the original L1 substantially technically qualified bidder is not in a position to supply material as per TLFs requirement within the time frame indicated in the bid.
+For detailed information, please check the complete version of the RFP attached below.
+Download Attachment:
+RFP for procurement Skill Lab Items under RIST Mansi_120326.pdf
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+15 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Unit Head - Proposal Development
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Research Analysts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+State Consultant - Communication, Advocacy and Pa...
+UNICEF
+Location:
+Rajasthan
+Apply by:
+23 Mar 2026
+RFP - Hiring agency to implement the organisation...
+Breakthrough
+Location:
+India
+Apply by:
+22 Mar 2026
+Technical Consultant - Hydrogeologists
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+IFP - for Strengthening systems for multi-sectora...
+UNFPA
+Location:
+India
+Apply by:
+17 Apr 2026
+Technical Consultant – Support and facilitate Tra...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant/Firm - Infrastructure Design...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - WASH Infrastructure monito...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - for Short-Term Studies, As...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t>15-03-2026</t>
+        </is>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287613</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr"/>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>RFP - for Empanelment of Knowledge Partners for Grooming of students for ...</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>TeamLease Foundation | India
+International Development - RFP - for  Empanelment of Knowledge Partners for Grooming of students for competitive examination (through partner) Super 30 Model, TeamLease Foundation, India - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast ... Read More</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="F10" s="1" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Learning</t>
         </is>
       </c>
       <c r="G10" s="1" t="inlineStr">
@@ -2310,11 +2305,11 @@
         </is>
       </c>
       <c r="H10" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I10" s="1" t="inlineStr">
         <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287910</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287763</t>
         </is>
       </c>
     </row>
@@ -2487,54 +2482,54 @@
 13 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Partnerships and Fundraising)
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Assistant Manager – MIS
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-UN Women National Consultant – GRB Technical Coor...
-UN Women
-Location:
-Delhi
+State Consultant - Communication, Advocacy and Pa...
+UNICEF
+Location:
+Rajasthan
+Apply by:
+23 Mar 2026
+RFP - Hiring agency to implement the organisation...
+Breakthrough
+Location:
+India
 Apply by:
 22 Mar 2026
-UN Women National Consultant – GRB Expert - MWCD,...
-UN Women
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-Communication Officer
-Association for Stimulating Know How (ASK)
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Program Coordinator
-Sampark Foundation
-Location:
-India
-Apply by:
-10 Apr 2026
-Senior Consultant – Education
-TeamLease Foundation
-Location:
-Delhi
-Apply by:
-10 Apr 2026
-Program Coordinator - Government Relations  &amp; Adv...
-Quest Alliance
-Location:
-Andhra Pradesh
-Apply by:
-10 Apr 2026
+Technical Consultant - Hydrogeologists
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+IFP - for Strengthening systems for multi-sectora...
+UNFPA
+Location:
+India
+Apply by:
+17 Apr 2026
+Technical Consultant – Support and facilitate Tra...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant/Firm - Infrastructure Design...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - WASH Infrastructure monito...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - for Short-Term Studies, As...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
 Jobseekers
 Register
 Login
@@ -2573,7 +2568,7 @@
         </is>
       </c>
       <c r="H11" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I11" s="1" t="inlineStr">
         <is>
@@ -2590,10 +2585,233 @@
       <c r="B12" s="1" t="inlineStr"/>
       <c r="C12" s="1" t="inlineStr">
         <is>
+          <t>ToR - Livelihoods Strategy Review and Future Direction Roadmap</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>ChildFund India | India
+International Development - ToR - Livelihoods Strategy Review and Future Direction Roadmap, ChildFund India, India - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Jobseekers:
+Login
+|
+Register
+Jobseeker ... Read More</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>• To determine the relevance, alignment, and coherence of the Livelihood Program under CSP 2022–2027 with national priorities, donor expectations, and organizational mandate.
+To assess the extent to which planned outputs and outcomes have been achieved and to evaluate the quality and impact of program interventions.
+Identify achievements, innovations, good practices, and enabling factors across Livelihood program interventions.
+Document gaps, challenges, and areas for strengthening
+To examine the sustainability of program outcomes and the institutional readiness of ChildFund India for long-term resilience and growth.
+Facilitate reflection through workshops involving staff, partners, and selected beneficiaries and provide recommendations for strategic direction, scalability, and future program priorities.
+Proposal Submission
+Interested evaluators/agencies are invited to submit:
+Technical proposal outlining approach and methodology
+Team composition and relevant experience
+Financial proposal with a detailed budget
+Sample of previous qualitative evaluation work
+Interested evaluators/agencies are requested to submit their technical and financial proposals to
+centralpurchase2@childfundindia.org
+by 15 March 2026.
+Reference No:- PRA/CFI/DEL/2025-26/053
+ChildFund India reserves the right to modify this ToR based on programmatic and contextual requirements.
+For detailed information, please check the complete version of the advert attached below.
+• Job Email ID:
+centralpurchase2(at)childfundindia.org
+Download Attachment:
+ToR Livelihood Portfolio-6.3.2026.doc
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+15 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Unit Head - Proposal Development
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Research Analysts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+State Consultant - Communication, Advocacy and Pa...
+UNICEF
+Location:
+Rajasthan
+Apply by:
+23 Mar 2026
+RFP - Hiring agency to implement the organisation...
+Breakthrough
+Location:
+India
+Apply by:
+22 Mar 2026
+Technical Consultant - Hydrogeologists
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+IFP - for Strengthening systems for multi-sectora...
+UNFPA
+Location:
+India
+Apply by:
+17 Apr 2026
+Technical Consultant – Support and facilitate Tra...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant/Firm - Infrastructure Design...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - WASH Infrastructure monito...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - for Short-Term Studies, As...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="G12" s="1" t="inlineStr">
+        <is>
+          <t>15-03-2026</t>
+        </is>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287910</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr"/>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
           <t>RFP - Big IC+ISA RFP - Selection of a Service Provider for Supply, Instal...</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>EAII Advisors Pvt Ltd | Andhra Pradesh
 International Development - RFP - Big IC+ISA RFP -  Selection of a Service Provider for Supply, Installation and Operation &amp; Maintenance of 150 ILC Devices and Capacity Building., EAII Advisors Pvt Ltd, Andhra Pradesh - DevNetJobsIndia.org
@@ -2602,7 +2820,7 @@
 | ... Read More</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>• 2. Purpose of the RFP:
 2.1  EAII is soliciting bids for:
@@ -2711,54 +2929,54 @@
 13 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Partnerships and Fundraising)
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Assistant Manager – MIS
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-UN Women National Consultant – GRB Technical Coor...
-UN Women
-Location:
-Delhi
+State Consultant - Communication, Advocacy and Pa...
+UNICEF
+Location:
+Rajasthan
+Apply by:
+23 Mar 2026
+RFP - Hiring agency to implement the organisation...
+Breakthrough
+Location:
+India
 Apply by:
 22 Mar 2026
-UN Women National Consultant – GRB Expert - MWCD,...
-UN Women
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-Communication Officer
-Association for Stimulating Know How (ASK)
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Program Coordinator
-Sampark Foundation
-Location:
-India
-Apply by:
-10 Apr 2026
-Senior Consultant – Education
-TeamLease Foundation
-Location:
-Delhi
-Apply by:
-10 Apr 2026
-Program Coordinator - Government Relations  &amp; Adv...
-Quest Alliance
-Location:
-Andhra Pradesh
-Apply by:
-10 Apr 2026
+Technical Consultant - Hydrogeologists
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+IFP - for Strengthening systems for multi-sectora...
+UNFPA
+Location:
+India
+Apply by:
+17 Apr 2026
+Technical Consultant – Support and facilitate Tra...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant/Firm - Infrastructure Design...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - WASH Infrastructure monito...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - for Short-Term Studies, As...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
 Jobseekers
 Register
 Login
@@ -2786,38 +3004,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F12" s="1" t="inlineStr">
+      <c r="F13" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G12" s="1" t="inlineStr">
+      <c r="G13" s="1" t="inlineStr">
         <is>
           <t>16-03-2026</t>
         </is>
       </c>
-      <c r="H12" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="I12" s="1" t="inlineStr">
+      <c r="H13" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287172</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr"/>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="B14" s="1" t="inlineStr"/>
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>RFP - Appointment of Agency for SEO Management and Meta (Facebook / Instag...</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>YRGCARE | India
 International Development - RFP - Appointment of Agency for SEO Management and Meta (Facebook / Instagram) Advertising, YRGCARE, India - DevNetJobsIndia.org
@@ -2837,7 +3055,7 @@
 Regist ... Read More</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>• To drive sustained awareness, organic discoverability, and ethical user engagement, NACO/YRGCARE intends to appoint professional agencies to manage two complementary digital outreach functions: Search Engine Optimisation (SEO) and paid social outreach through Meta platforms (Facebook and Instagram). This ToR defines the full scope, expectations, compliance requirements, and monitoring framework for this appointment.
 For detailed information visit
@@ -2921,54 +3139,54 @@
 13 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Partnerships and Fundraising)
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Assistant Manager – MIS
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-UN Women National Consultant – GRB Technical Coor...
-UN Women
-Location:
-Delhi
+State Consultant - Communication, Advocacy and Pa...
+UNICEF
+Location:
+Rajasthan
+Apply by:
+23 Mar 2026
+RFP - Hiring agency to implement the organisation...
+Breakthrough
+Location:
+India
 Apply by:
 22 Mar 2026
-UN Women National Consultant – GRB Expert - MWCD,...
-UN Women
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-Communication Officer
-Association for Stimulating Know How (ASK)
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Program Coordinator
-Sampark Foundation
-Location:
-India
-Apply by:
-10 Apr 2026
-Senior Consultant – Education
-TeamLease Foundation
-Location:
-Delhi
-Apply by:
-10 Apr 2026
-Program Coordinator - Government Relations  &amp; Adv...
-Quest Alliance
-Location:
-Andhra Pradesh
-Apply by:
-10 Apr 2026
+Technical Consultant - Hydrogeologists
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+IFP - for Strengthening systems for multi-sectora...
+UNFPA
+Location:
+India
+Apply by:
+17 Apr 2026
+Technical Consultant – Support and facilitate Tra...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant/Firm - Infrastructure Design...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - WASH Infrastructure monito...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - for Short-Term Studies, As...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
 Jobseekers
 Register
 Login
@@ -2996,38 +3214,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F13" s="1" t="inlineStr">
+      <c r="F14" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G13" s="1" t="inlineStr">
+      <c r="G14" s="1" t="inlineStr">
         <is>
           <t>19-03-2026</t>
         </is>
       </c>
-      <c r="H13" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="I13" s="1" t="inlineStr">
+      <c r="H14" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I14" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=288063</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr"/>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="B15" s="1" t="inlineStr"/>
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>RFP - Design, Development, Deployment and Maintenance of Mobile Applicati...</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>YRGCARE | India
 International Development - RFP - Design, Development, Deployment and Maintenance of  Mobile Application for the Breakfree Platform, YRGCARE, India - DevNetJobsIndia.org
@@ -3045,7 +3263,7 @@
 L ... Read More</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>• This Terms of Reference (ToR) defines the full scope of work, technical requirements, compliance standards, and performance expectations for the agency appointed to design, develop, deploy, and maintain the Breakfree mobile application for both Android and iOS platforms.
 For detailed information visit
@@ -3129,54 +3347,54 @@
 13 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Partnerships and Fundraising)
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Assistant Manager – MIS
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-UN Women National Consultant – GRB Technical Coor...
-UN Women
-Location:
-Delhi
+State Consultant - Communication, Advocacy and Pa...
+UNICEF
+Location:
+Rajasthan
+Apply by:
+23 Mar 2026
+RFP - Hiring agency to implement the organisation...
+Breakthrough
+Location:
+India
 Apply by:
 22 Mar 2026
-UN Women National Consultant – GRB Expert - MWCD,...
-UN Women
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-Communication Officer
-Association for Stimulating Know How (ASK)
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Program Coordinator
-Sampark Foundation
-Location:
-India
-Apply by:
-10 Apr 2026
-Senior Consultant – Education
-TeamLease Foundation
-Location:
-Delhi
-Apply by:
-10 Apr 2026
-Program Coordinator - Government Relations  &amp; Adv...
-Quest Alliance
-Location:
-Andhra Pradesh
-Apply by:
-10 Apr 2026
+Technical Consultant - Hydrogeologists
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+IFP - for Strengthening systems for multi-sectora...
+UNFPA
+Location:
+India
+Apply by:
+17 Apr 2026
+Technical Consultant – Support and facilitate Tra...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant/Firm - Infrastructure Design...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - WASH Infrastructure monito...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - for Short-Term Studies, As...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
 Jobseekers
 Register
 Login
@@ -3204,38 +3422,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F14" s="1" t="inlineStr">
+      <c r="F15" s="1" t="inlineStr">
         <is>
           <t>Learning, Safety</t>
         </is>
       </c>
-      <c r="G14" s="1" t="inlineStr">
+      <c r="G15" s="1" t="inlineStr">
         <is>
           <t>19-03-2026</t>
         </is>
       </c>
-      <c r="H14" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="I14" s="1" t="inlineStr">
+      <c r="H15" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I15" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=288064</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr"/>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="B16" s="1" t="inlineStr"/>
+      <c r="C16" s="1" t="inlineStr">
         <is>
           <t>Specialist – Communication</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Financial Management Service Foundation (FMSF) | Uttar Pradesh
 International Development - Specialist – Communication, Financial Management Service Foundation (FMSF), Uttar Pradesh - DevNetJobsIndia.org
@@ -3251,7 +3469,7 @@
 Eve ... Read More</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>• Joining FMSF means becoming part of a passionate team dedicated to making a positive impact. We offer competitive compensation, opportunities for professional development, and a supportive work environment where your contributions are valued and recognized. If you are committed to driving positive change, promoting accountability and strengthening the development sector, we encourage you to apply for the position of Specialist – Communication at FMSF.
 • How to Apply:
@@ -3335,54 +3553,54 @@
 13 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Partnerships and Fundraising)
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Assistant Manager – MIS
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-UN Women National Consultant – GRB Technical Coor...
-UN Women
-Location:
-Delhi
+State Consultant - Communication, Advocacy and Pa...
+UNICEF
+Location:
+Rajasthan
+Apply by:
+23 Mar 2026
+RFP - Hiring agency to implement the organisation...
+Breakthrough
+Location:
+India
 Apply by:
 22 Mar 2026
-UN Women National Consultant – GRB Expert - MWCD,...
-UN Women
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-Communication Officer
-Association for Stimulating Know How (ASK)
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Program Coordinator
-Sampark Foundation
-Location:
-India
-Apply by:
-10 Apr 2026
-Senior Consultant – Education
-TeamLease Foundation
-Location:
-Delhi
-Apply by:
-10 Apr 2026
-Program Coordinator - Government Relations  &amp; Adv...
-Quest Alliance
-Location:
-Andhra Pradesh
-Apply by:
-10 Apr 2026
+Technical Consultant - Hydrogeologists
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+IFP - for Strengthening systems for multi-sectora...
+UNFPA
+Location:
+India
+Apply by:
+17 Apr 2026
+Technical Consultant – Support and facilitate Tra...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant/Firm - Infrastructure Design...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - WASH Infrastructure monito...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - for Short-Term Studies, As...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
 Jobseekers
 Register
 Login
@@ -3410,41 +3628,41 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F15" s="1" t="inlineStr">
+      <c r="F16" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G15" s="1" t="inlineStr">
+      <c r="G16" s="1" t="inlineStr">
         <is>
           <t>19-03-2026</t>
         </is>
       </c>
-      <c r="H15" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="I15" s="1" t="inlineStr">
+      <c r="H16" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I16" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287207</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr"/>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>Specialist - Grants</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Financial Management Service Foundation (FMSF) | Uttar Pradesh
-International Development - Specialist - Grants, Financial Management Service Foundation (FMSF), Uttar Pradesh - DevNetJobsIndia.org
+      <c r="B17" s="1" t="inlineStr"/>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>Technical Consultant/Firm - Infrastructure Design, estimate and cost stand...</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>WaterAid India | India
+International Development - Technical Consultant/Firm - Infrastructure Design, estimate and cost standardisation, WaterAid India, India - DevNetJobsIndia.org
 Jobseekers:
 Login
 |
@@ -3455,26 +3673,19 @@
 RFPs/Tenders
 Search Jobs
 Events
-Job ... Read More</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>• Joining FMSF means becoming part of a passionate team dedicated to making a positive impact. We offer competitive compensation, opportunities for professional development, and a supportive work environment where your contributions are valued and recognized. If you are committed to driving positive change, promoting accountability and strengthening the development sector, we encourage you to apply for the position of Specialist - Grants at FMSF.
-You’re Resume to be accompanied with:
-Motivational letter justifying suitability for the position – role fitment based on present &amp; past work experience
-Current/last drawn compensation &amp; expected compensation
-CVs without Motivational Letter will not be considered
-• How to Apply:
-Apply online by clicking on the link
-https://www.fmsfindia.org.in/apply-now/specialist-grants
-FMSF is an Equal Opportunity Employer.
-Please note that only the shortlisted candidates will be contacted.
+Jobseekers:
+Login ... Read More</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>• Job Email ID:
+waindiahr(at)wateraid.org
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
 Apply by:
-21 Mar 2026
+20 Mar 2026
 Access all the jobs and get ahead!
 Subscribe to Value Membership Now!
 Subscribe
@@ -3542,54 +3753,54 @@
 13 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Partnerships and Fundraising)
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Assistant Manager – MIS
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-UN Women National Consultant – GRB Technical Coor...
-UN Women
-Location:
-Delhi
+State Consultant - Communication, Advocacy and Pa...
+UNICEF
+Location:
+Rajasthan
+Apply by:
+23 Mar 2026
+RFP - Hiring agency to implement the organisation...
+Breakthrough
+Location:
+India
 Apply by:
 22 Mar 2026
-UN Women National Consultant – GRB Expert - MWCD,...
-UN Women
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-Communication Officer
-Association for Stimulating Know How (ASK)
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Program Coordinator
-Sampark Foundation
-Location:
-India
-Apply by:
-10 Apr 2026
-Senior Consultant – Education
-TeamLease Foundation
-Location:
-Delhi
-Apply by:
-10 Apr 2026
-Program Coordinator - Government Relations  &amp; Adv...
-Quest Alliance
-Location:
-Andhra Pradesh
-Apply by:
-10 Apr 2026
+Technical Consultant - Hydrogeologists
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+IFP - for Strengthening systems for multi-sectora...
+UNFPA
+Location:
+India
+Apply by:
+17 Apr 2026
+Technical Consultant – Support and facilitate Tra...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant/Firm - Infrastructure Design...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - WASH Infrastructure monito...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - for Short-Term Studies, As...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
 Jobseekers
 Register
 Login
@@ -3617,38 +3828,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G16" s="1" t="inlineStr">
-        <is>
-          <t>21-03-2026</t>
-        </is>
-      </c>
-      <c r="H16" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="I16" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287318</t>
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>Learning, Safety</t>
+        </is>
+      </c>
+      <c r="G17" s="1" t="inlineStr">
+        <is>
+          <t>20-03-2026</t>
+        </is>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="I17" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=288190</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr"/>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="B18" s="1" t="inlineStr"/>
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>RFP - Consultancy for development of descriptive documentation of Ashiyana...</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Prerana | Mumbai, Maharashtra
 International Development - RFP - Consultancy for development of descriptive documentation of Ashiyana Implementation &amp; Practice Framework, and produce a replication-ready, Prerana, Maharashtra - DevNetJobsIndia.org
@@ -3661,7 +3872,7 @@
 Br ... Read More</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>• Submission Details
 Proposals must be submitted by email to:
@@ -3747,54 +3958,54 @@
 13 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Partnerships and Fundraising)
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Assistant Manager – MIS
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-UN Women National Consultant – GRB Technical Coor...
-UN Women
-Location:
-Delhi
+State Consultant - Communication, Advocacy and Pa...
+UNICEF
+Location:
+Rajasthan
+Apply by:
+23 Mar 2026
+RFP - Hiring agency to implement the organisation...
+Breakthrough
+Location:
+India
 Apply by:
 22 Mar 2026
-UN Women National Consultant – GRB Expert - MWCD,...
-UN Women
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-Communication Officer
-Association for Stimulating Know How (ASK)
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Program Coordinator
-Sampark Foundation
-Location:
-India
-Apply by:
-10 Apr 2026
-Senior Consultant – Education
-TeamLease Foundation
-Location:
-Delhi
-Apply by:
-10 Apr 2026
-Program Coordinator - Government Relations  &amp; Adv...
-Quest Alliance
-Location:
-Andhra Pradesh
-Apply by:
-10 Apr 2026
+Technical Consultant - Hydrogeologists
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+IFP - for Strengthening systems for multi-sectora...
+UNFPA
+Location:
+India
+Apply by:
+17 Apr 2026
+Technical Consultant – Support and facilitate Tra...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant/Firm - Infrastructure Design...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - WASH Infrastructure monito...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - for Short-Term Studies, As...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
 Jobseekers
 Register
 Login
@@ -3822,44 +4033,251 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F17" s="1" t="inlineStr">
+      <c r="F18" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G17" s="1" t="inlineStr">
+      <c r="G18" s="1" t="inlineStr">
         <is>
           <t>21-03-2026</t>
         </is>
       </c>
-      <c r="H17" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="I17" s="1" t="inlineStr">
+      <c r="H18" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="I18" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287890</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B18" s="1" t="inlineStr"/>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="B19" s="1" t="inlineStr"/>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>Specialist - Grants</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Financial Management Service Foundation (FMSF) | Uttar Pradesh
+International Development - Specialist - Grants, Financial Management Service Foundation (FMSF), Uttar Pradesh - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Events
+Job ... Read More</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>• Joining FMSF means becoming part of a passionate team dedicated to making a positive impact. We offer competitive compensation, opportunities for professional development, and a supportive work environment where your contributions are valued and recognized. If you are committed to driving positive change, promoting accountability and strengthening the development sector, we encourage you to apply for the position of Specialist - Grants at FMSF.
+You’re Resume to be accompanied with:
+Motivational letter justifying suitability for the position – role fitment based on present &amp; past work experience
+Current/last drawn compensation &amp; expected compensation
+CVs without Motivational Letter will not be considered
+• How to Apply:
+Apply online by clicking on the link
+https://www.fmsfindia.org.in/apply-now/specialist-grants
+FMSF is an Equal Opportunity Employer.
+Please note that only the shortlisted candidates will be contacted.
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+21 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Unit Head - Proposal Development
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Research Analysts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+State Consultant - Communication, Advocacy and Pa...
+UNICEF
+Location:
+Rajasthan
+Apply by:
+23 Mar 2026
+RFP - Hiring agency to implement the organisation...
+Breakthrough
+Location:
+India
+Apply by:
+22 Mar 2026
+Technical Consultant - Hydrogeologists
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+IFP - for Strengthening systems for multi-sectora...
+UNFPA
+Location:
+India
+Apply by:
+17 Apr 2026
+Technical Consultant – Support and facilitate Tra...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant/Firm - Infrastructure Design...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - WASH Infrastructure monito...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - for Short-Term Studies, As...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G19" s="1" t="inlineStr">
+        <is>
+          <t>21-03-2026</t>
+        </is>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="I19" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287318</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr"/>
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>RFP - Study On SC-DMPA In Rajasthan- Clients And Providers Perspectives On...</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Centre For Community Economics And Development Consultants Society- CECOEDECON | Jaipur, Rajasthan
 International Development - RFP - Study On SC-DMPA In Rajasthan- Clients And Providers Perspectives On SC-DMPA In Rajasthan, Centre For Community Economics And Development Consultants Society- CECOEDE ... Read More</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>• Despite India’s achievement of replacement-level fertility, unmet need for contraception—particularly for spacing methods—remains substantial, with modern contraceptive use at 56.4% (2019–21), highlighting persistent gaps in access and choice, especially among vulnerable populations. Expanding the contraceptive method mix through innovative, user-centred approaches is therefore essential to meeting national commitments under FP2030 and the Sustainable Development Goals. In this context, the Government of India’s introduction of subcutaneous DMPA (DMPA-SC) as a self-care option under the National Family Planning Programme in 2023 represents a strategic step toward enhancing women’s autonomy, privacy, and convenience in contraceptive use. Global and national evidence indicates strong feasibility and acceptability of self-administered DMPA-SC among both users and providers; however, successful implementation requires an in-depth understanding of user experiences and health system readiness. This study, to be conducted in Jaipur-1, Jaisalmer and Sawai Madhopur districts of Rajasthan, aims to examine the perspectives &amp; experience of current SC-DMPA users and explore healthcare providers’ views on enabling and generating actionable evidence to inform effective scale-up of SC-DMPA within India’s public health system.
 CECOEDECON, with support from UNFPA, is implementing the roll-out of subcutaneous DMPA (SC-DMPA) in selected pilot districts of Rajasthan in the public health facilities, in collaboration with the Department of Health &amp; Family Welfare, Government of Rajasthan.
@@ -3994,54 +4412,54 @@
 13 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Partnerships and Fundraising)
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Assistant Manager – MIS
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-UN Women National Consultant – GRB Technical Coor...
-UN Women
-Location:
-Delhi
+State Consultant - Communication, Advocacy and Pa...
+UNICEF
+Location:
+Rajasthan
+Apply by:
+23 Mar 2026
+RFP - Hiring agency to implement the organisation...
+Breakthrough
+Location:
+India
 Apply by:
 22 Mar 2026
-UN Women National Consultant – GRB Expert - MWCD,...
-UN Women
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-Communication Officer
-Association for Stimulating Know How (ASK)
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Program Coordinator
-Sampark Foundation
-Location:
-India
-Apply by:
-10 Apr 2026
-Senior Consultant – Education
-TeamLease Foundation
-Location:
-Delhi
-Apply by:
-10 Apr 2026
-Program Coordinator - Government Relations  &amp; Adv...
-Quest Alliance
-Location:
-Andhra Pradesh
-Apply by:
-10 Apr 2026
+Technical Consultant - Hydrogeologists
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+IFP - for Strengthening systems for multi-sectora...
+UNFPA
+Location:
+India
+Apply by:
+17 Apr 2026
+Technical Consultant – Support and facilitate Tra...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant/Firm - Infrastructure Design...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - WASH Infrastructure monito...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - for Short-Term Studies, As...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
 Jobseekers
 Register
 Login
@@ -4069,45 +4487,45 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F18" s="1" t="inlineStr">
+      <c r="F20" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G18" s="1" t="inlineStr">
+      <c r="G20" s="1" t="inlineStr">
         <is>
           <t>22-03-2026</t>
         </is>
       </c>
-      <c r="H18" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="I18" s="1" t="inlineStr">
+      <c r="H20" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="I20" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287322</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr"/>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="B21" s="1" t="inlineStr"/>
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>RFP - for hiring of an agency for providing Legal and Compliance Advisory...</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>International Union Against Tuberculosis and Lung Disease (The Union) | India
 International Development - RFP -  for hiring of an agency for providing Legal and Compliance Advisory Services, International Union Against Tuberculosis and Lung Disease (The Union), India - DevNetJobsIndia.org
 Jobseeker ... Read More</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>• 1. PURPOSE OF THE RFP
 1.1 The Union is interested in engaging a firm/ agency to provide comprehensive legal advisory and compliance support to the organisation, ensuring adherence to applicable laws, regulations, donor requirements, and good governance standards relevant to the social impact/ non-profit sector
@@ -4231,54 +4649,54 @@
 13 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Partnerships and Fundraising)
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Assistant Manager – MIS
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-UN Women National Consultant – GRB Technical Coor...
-UN Women
-Location:
-Delhi
+State Consultant - Communication, Advocacy and Pa...
+UNICEF
+Location:
+Rajasthan
+Apply by:
+23 Mar 2026
+RFP - Hiring agency to implement the organisation...
+Breakthrough
+Location:
+India
 Apply by:
 22 Mar 2026
-UN Women National Consultant – GRB Expert - MWCD,...
-UN Women
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-Communication Officer
-Association for Stimulating Know How (ASK)
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Program Coordinator
-Sampark Foundation
-Location:
-India
-Apply by:
-10 Apr 2026
-Senior Consultant – Education
-TeamLease Foundation
-Location:
-Delhi
-Apply by:
-10 Apr 2026
-Program Coordinator - Government Relations  &amp; Adv...
-Quest Alliance
-Location:
-Andhra Pradesh
-Apply by:
-10 Apr 2026
+Technical Consultant - Hydrogeologists
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+IFP - for Strengthening systems for multi-sectora...
+UNFPA
+Location:
+India
+Apply by:
+17 Apr 2026
+Technical Consultant – Support and facilitate Tra...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant/Firm - Infrastructure Design...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - WASH Infrastructure monito...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - for Short-Term Studies, As...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
 Jobseekers
 Register
 Login
@@ -4306,38 +4724,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F19" s="1" t="inlineStr">
+      <c r="F21" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G19" s="1" t="inlineStr">
+      <c r="G21" s="1" t="inlineStr">
         <is>
           <t>22-03-2026</t>
         </is>
       </c>
-      <c r="H19" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="I19" s="1" t="inlineStr">
+      <c r="H21" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="I21" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=288152</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr"/>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="B22" s="1" t="inlineStr"/>
+      <c r="C22" s="1" t="inlineStr">
         <is>
           <t>RFQ-Corporate Global Group Health Insurance Coverage</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Coalition for Disaster Resilient Infrastructure (CDRI) | India
 International Development - RFQ-Corporate Global Group Health Insurance Coverage, Coalition for Disaster Resilient Infrastructure (CDRI), India - DevNetJobsIndia.org
@@ -4351,7 +4769,7 @@
 RF ... Read More</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>• The specific staff details, policy document, along with the claim MIS will only be shared with the interested bidders upon request to the email ID
 :
@@ -4509,54 +4927,54 @@
 13 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Partnerships and Fundraising)
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Assistant Manager – MIS
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-UN Women National Consultant – GRB Technical Coor...
-UN Women
-Location:
-Delhi
+State Consultant - Communication, Advocacy and Pa...
+UNICEF
+Location:
+Rajasthan
+Apply by:
+23 Mar 2026
+RFP - Hiring agency to implement the organisation...
+Breakthrough
+Location:
+India
 Apply by:
 22 Mar 2026
-UN Women National Consultant – GRB Expert - MWCD,...
-UN Women
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-Communication Officer
-Association for Stimulating Know How (ASK)
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Program Coordinator
-Sampark Foundation
-Location:
-India
-Apply by:
-10 Apr 2026
-Senior Consultant – Education
-TeamLease Foundation
-Location:
-Delhi
-Apply by:
-10 Apr 2026
-Program Coordinator - Government Relations  &amp; Adv...
-Quest Alliance
-Location:
-Andhra Pradesh
-Apply by:
-10 Apr 2026
+Technical Consultant - Hydrogeologists
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+IFP - for Strengthening systems for multi-sectora...
+UNFPA
+Location:
+India
+Apply by:
+17 Apr 2026
+Technical Consultant – Support and facilitate Tra...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant/Firm - Infrastructure Design...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - WASH Infrastructure monito...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - for Short-Term Studies, As...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
 Jobseekers
 Register
 Login
@@ -4584,38 +5002,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F20" s="1" t="inlineStr">
+      <c r="F22" s="1" t="inlineStr">
         <is>
           <t>Climate, Safety</t>
         </is>
       </c>
-      <c r="G20" s="1" t="inlineStr">
+      <c r="G22" s="1" t="inlineStr">
         <is>
           <t>23-03-2026</t>
         </is>
       </c>
-      <c r="H20" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="I20" s="1" t="inlineStr">
+      <c r="H22" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="I22" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=288006</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr"/>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="B23" s="1" t="inlineStr"/>
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>EoI – Mobile Medical Units, Ai-Enabled Tb Screening &amp; Supply Of Medical An...</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Ashray Foundation | Korba, Chattisgarh (Delivery Location), Gujarat
 International Development - EoI – Mobile Medical Units, Ai-Enabled Tb Screening &amp; Supply Of Medical And Nutritional Support, Ashray Foundation, Gujarat - DevNetJobsIndia.org
@@ -4628,7 +5046,7 @@
 Broadc ... Read More</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>• Ashray Foundation invites eligible and experienced agencies to submit their Expression of Interest / for the following scope of work:
 Fabrication of Mobile Medical Units (MMUs) – 2 Units
@@ -4717,54 +5135,54 @@
 13 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Partnerships and Fundraising)
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Assistant Manager – MIS
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-UN Women National Consultant – GRB Technical Coor...
-UN Women
-Location:
-Delhi
+State Consultant - Communication, Advocacy and Pa...
+UNICEF
+Location:
+Rajasthan
+Apply by:
+23 Mar 2026
+RFP - Hiring agency to implement the organisation...
+Breakthrough
+Location:
+India
 Apply by:
 22 Mar 2026
-UN Women National Consultant – GRB Expert - MWCD,...
-UN Women
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-Communication Officer
-Association for Stimulating Know How (ASK)
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Program Coordinator
-Sampark Foundation
-Location:
-India
-Apply by:
-10 Apr 2026
-Senior Consultant – Education
-TeamLease Foundation
-Location:
-Delhi
-Apply by:
-10 Apr 2026
-Program Coordinator - Government Relations  &amp; Adv...
-Quest Alliance
-Location:
-Andhra Pradesh
-Apply by:
-10 Apr 2026
+Technical Consultant - Hydrogeologists
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+IFP - for Strengthening systems for multi-sectora...
+UNFPA
+Location:
+India
+Apply by:
+17 Apr 2026
+Technical Consultant – Support and facilitate Tra...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant/Firm - Infrastructure Design...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - WASH Infrastructure monito...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - for Short-Term Studies, As...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
 Jobseekers
 Register
 Login
@@ -4792,38 +5210,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F21" s="1" t="inlineStr">
+      <c r="F23" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G21" s="1" t="inlineStr">
+      <c r="G23" s="1" t="inlineStr">
         <is>
           <t>24-03-2026</t>
         </is>
       </c>
-      <c r="H21" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="I21" s="1" t="inlineStr">
+      <c r="H23" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="I23" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287319</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr"/>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="B24" s="1" t="inlineStr"/>
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>RFP - End of Program Evaluation Accelerating Access to Safe Water and San...</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Water.org | Bangladesh, Cambodia, India
 International Development - RFP - End of Program Evaluation  Accelerating Access to Safe Water and Sanitation, Financing, Water.org, India - DevNetJobsIndia.org
@@ -4839,7 +5257,7 @@
 Event ... Read More</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>• The evaluation will require the firm to facilitate and coordinate with Water.org staff and partners. The program requires the firm to submit the deliverables outlined in section 2 Scope of Work.
 C.
@@ -4946,54 +5364,54 @@
 13 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Partnerships and Fundraising)
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Assistant Manager – MIS
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-UN Women National Consultant – GRB Technical Coor...
-UN Women
-Location:
-Delhi
+State Consultant - Communication, Advocacy and Pa...
+UNICEF
+Location:
+Rajasthan
+Apply by:
+23 Mar 2026
+RFP - Hiring agency to implement the organisation...
+Breakthrough
+Location:
+India
 Apply by:
 22 Mar 2026
-UN Women National Consultant – GRB Expert - MWCD,...
-UN Women
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-Communication Officer
-Association for Stimulating Know How (ASK)
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Program Coordinator
-Sampark Foundation
-Location:
-India
-Apply by:
-10 Apr 2026
-Senior Consultant – Education
-TeamLease Foundation
-Location:
-Delhi
-Apply by:
-10 Apr 2026
-Program Coordinator - Government Relations  &amp; Adv...
-Quest Alliance
-Location:
-Andhra Pradesh
-Apply by:
-10 Apr 2026
+Technical Consultant - Hydrogeologists
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+IFP - for Strengthening systems for multi-sectora...
+UNFPA
+Location:
+India
+Apply by:
+17 Apr 2026
+Technical Consultant – Support and facilitate Tra...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant/Firm - Infrastructure Design...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - WASH Infrastructure monito...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - for Short-Term Studies, As...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
 Jobseekers
 Register
 Login
@@ -5021,267 +5439,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F22" s="1" t="inlineStr">
+      <c r="F24" s="1" t="inlineStr">
         <is>
           <t>Governance, Safety</t>
         </is>
       </c>
-      <c r="G22" s="1" t="inlineStr">
+      <c r="G24" s="1" t="inlineStr">
         <is>
           <t>25-03-2026</t>
         </is>
       </c>
-      <c r="H22" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="I22" s="1" t="inlineStr">
+      <c r="H24" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="I24" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287835</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr"/>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>Junior Research Technicians / Senior Project Asso...</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Starshield Security Solution Pvt.Ltd | Uttar Pradesh
-International Development - Junior Research Technicians / Senior Project Associate, Starshield Security Solution Pvt.Ltd, Uttar Pradesh - DevNetJobsIndia.org
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search ... Read More</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>• Eligibility Criteria
-Qualification
-:
-Intermediate with 2–3 years of relevant experience
-OR
-Graduate with 1–2 years of relevant experience
-Skills &amp; Experience (Mandatory):
-Experience in agriculture field operations and data collection
-Basic knowledge of MS Office (Word &amp; Excel)
-Experience in rice-wheat cropping system production preferred
-Good coordination and communication skills
-Willingness to travel and work in field conditions
-Knowledge of smart mobile apps for data survey and data recording
-Knowledge on agri machinery
-Community mobilization and Work with Farmers group/FPCs
-The applicants must have a two-wheeler vehicle and license with them
-Key Performance Indicators
-Timely support to demonstrations, trainings, and field activities
-Accurate data collection and documentation
-Proper maintenance of equipment and field sites
-Positive feedback from farmers and stakeholders
-Creation of new service providers
-Application Details
-Interested candidates are requested to fill-out the shared application form and submit their updated CV via email to
-communications@starshieldsolution.com
-with the subject line:
-Application for Junior Research Technician (IRRI Project Deployment)
-.
-Only shortlisted candidates who complete the required documentation will be considered for subsequent stages of selection.
-Selection will be done on a first-come-first-served basis. Applications received up to Thursday each week will be reviewed, and interviews will be conducted in the following week. As soon as we shall finish all recruitment, we will take the advertisement off.
-• Job Email ID:
-communications(at)starshieldsolution.com
-Download Attachment:
-Application Proforma_Junior Research Technicians -  Senior Project Associate.doc
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-30 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Unit Head - Proposal Development
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-11 Apr 2026
-Research Analysts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-11 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Associate – Finance and Operations
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-05 Apr 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-Latest Jobs
-Post your highlighted jobs here
-Assistant Manager (Partnerships and Fundraising)
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Assistant Manager – MIS
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-UN Women National Consultant – GRB Technical Coor...
-UN Women
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-UN Women National Consultant – GRB Expert - MWCD,...
-UN Women
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-Communication Officer
-Association for Stimulating Know How (ASK)
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Program Coordinator
-Sampark Foundation
-Location:
-India
-Apply by:
-10 Apr 2026
-Senior Consultant – Education
-TeamLease Foundation
-Location:
-Delhi
-Apply by:
-10 Apr 2026
-Program Coordinator - Government Relations  &amp; Adv...
-Quest Alliance
-Location:
-Andhra Pradesh
-Apply by:
-10 Apr 2026
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F23" s="1" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="G23" s="1" t="inlineStr">
-        <is>
-          <t>30-03-2026</t>
-        </is>
-      </c>
-      <c r="H23" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="I23" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287635</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B24" s="1" t="inlineStr"/>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="B25" s="1" t="inlineStr"/>
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>Agriculture Research Development Officer / Projec...</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Starshield Security Solution Pvt.Ltd | Uttar Pradesh
 International Development - Agriculture Research Development Officer / Project Scientist III, Starshield Security Solution Pvt.Ltd, Uttar Pradesh - DevNetJobsIndia.org
@@ -5295,7 +5484,7 @@
 RFPs/Tende ... Read More</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>• Eligibility Criteria
 Qualification:
@@ -5404,54 +5593,54 @@
 13 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Partnerships and Fundraising)
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Assistant Manager – MIS
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-UN Women National Consultant – GRB Technical Coor...
-UN Women
-Location:
-Delhi
+State Consultant - Communication, Advocacy and Pa...
+UNICEF
+Location:
+Rajasthan
+Apply by:
+23 Mar 2026
+RFP - Hiring agency to implement the organisation...
+Breakthrough
+Location:
+India
 Apply by:
 22 Mar 2026
-UN Women National Consultant – GRB Expert - MWCD,...
-UN Women
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-Communication Officer
-Association for Stimulating Know How (ASK)
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Program Coordinator
-Sampark Foundation
-Location:
-India
-Apply by:
-10 Apr 2026
-Senior Consultant – Education
-TeamLease Foundation
-Location:
-Delhi
-Apply by:
-10 Apr 2026
-Program Coordinator - Government Relations  &amp; Adv...
-Quest Alliance
-Location:
-Andhra Pradesh
-Apply by:
-10 Apr 2026
+Technical Consultant - Hydrogeologists
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+IFP - for Strengthening systems for multi-sectora...
+UNFPA
+Location:
+India
+Apply by:
+17 Apr 2026
+Technical Consultant – Support and facilitate Tra...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant/Firm - Infrastructure Design...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - WASH Infrastructure monito...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - for Short-Term Studies, As...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
 Jobseekers
 Register
 Login
@@ -5479,38 +5668,267 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F24" s="1" t="inlineStr">
+      <c r="F25" s="1" t="inlineStr">
         <is>
           <t>Learning, Safety</t>
         </is>
       </c>
-      <c r="G24" s="1" t="inlineStr">
+      <c r="G25" s="1" t="inlineStr">
         <is>
           <t>30-03-2026</t>
         </is>
       </c>
-      <c r="H24" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="I24" s="1" t="inlineStr">
+      <c r="H25" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="I25" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287636</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr"/>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="B26" s="1" t="inlineStr"/>
+      <c r="C26" s="1" t="inlineStr">
+        <is>
+          <t>Junior Research Technicians / Senior Project Asso...</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Starshield Security Solution Pvt.Ltd | Uttar Pradesh
+International Development - Junior Research Technicians / Senior Project Associate, Starshield Security Solution Pvt.Ltd, Uttar Pradesh - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search ... Read More</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>• Eligibility Criteria
+Qualification
+:
+Intermediate with 2–3 years of relevant experience
+OR
+Graduate with 1–2 years of relevant experience
+Skills &amp; Experience (Mandatory):
+Experience in agriculture field operations and data collection
+Basic knowledge of MS Office (Word &amp; Excel)
+Experience in rice-wheat cropping system production preferred
+Good coordination and communication skills
+Willingness to travel and work in field conditions
+Knowledge of smart mobile apps for data survey and data recording
+Knowledge on agri machinery
+Community mobilization and Work with Farmers group/FPCs
+The applicants must have a two-wheeler vehicle and license with them
+Key Performance Indicators
+Timely support to demonstrations, trainings, and field activities
+Accurate data collection and documentation
+Proper maintenance of equipment and field sites
+Positive feedback from farmers and stakeholders
+Creation of new service providers
+Application Details
+Interested candidates are requested to fill-out the shared application form and submit their updated CV via email to
+communications@starshieldsolution.com
+with the subject line:
+Application for Junior Research Technician (IRRI Project Deployment)
+.
+Only shortlisted candidates who complete the required documentation will be considered for subsequent stages of selection.
+Selection will be done on a first-come-first-served basis. Applications received up to Thursday each week will be reviewed, and interviews will be conducted in the following week. As soon as we shall finish all recruitment, we will take the advertisement off.
+• Job Email ID:
+communications(at)starshieldsolution.com
+Download Attachment:
+Application Proforma_Junior Research Technicians -  Senior Project Associate.doc
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+30 Mar 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Unit Head - Proposal Development
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Research Analysts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+State Consultant - Communication, Advocacy and Pa...
+UNICEF
+Location:
+Rajasthan
+Apply by:
+23 Mar 2026
+RFP - Hiring agency to implement the organisation...
+Breakthrough
+Location:
+India
+Apply by:
+22 Mar 2026
+Technical Consultant - Hydrogeologists
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+IFP - for Strengthening systems for multi-sectora...
+UNFPA
+Location:
+India
+Apply by:
+17 Apr 2026
+Technical Consultant – Support and facilitate Tra...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant/Firm - Infrastructure Design...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - WASH Infrastructure monito...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - for Short-Term Studies, As...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
+      <c r="F26" s="1" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="G26" s="1" t="inlineStr">
+        <is>
+          <t>30-03-2026</t>
+        </is>
+      </c>
+      <c r="H26" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="I26" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287635</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="inlineStr"/>
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>Sector Experts</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Academy of Management Studies (AMS) | India
 International Development - Sector Experts, Academy of Management Studies (AMS), India - DevNetJobsIndia.org
@@ -5531,7 +5949,7 @@
 Jobseekers Login ... Read More</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>• Eligibility
 Postgraduate degree / Ph.D. in relevant or allied disciplines
@@ -5627,54 +6045,54 @@
 13 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Partnerships and Fundraising)
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Assistant Manager – MIS
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-UN Women National Consultant – GRB Technical Coor...
-UN Women
-Location:
-Delhi
+State Consultant - Communication, Advocacy and Pa...
+UNICEF
+Location:
+Rajasthan
+Apply by:
+23 Mar 2026
+RFP - Hiring agency to implement the organisation...
+Breakthrough
+Location:
+India
 Apply by:
 22 Mar 2026
-UN Women National Consultant – GRB Expert - MWCD,...
-UN Women
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-Communication Officer
-Association for Stimulating Know How (ASK)
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Program Coordinator
-Sampark Foundation
-Location:
-India
-Apply by:
-10 Apr 2026
-Senior Consultant – Education
-TeamLease Foundation
-Location:
-Delhi
-Apply by:
-10 Apr 2026
-Program Coordinator - Government Relations  &amp; Adv...
-Quest Alliance
-Location:
-Andhra Pradesh
-Apply by:
-10 Apr 2026
+Technical Consultant - Hydrogeologists
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+IFP - for Strengthening systems for multi-sectora...
+UNFPA
+Location:
+India
+Apply by:
+17 Apr 2026
+Technical Consultant – Support and facilitate Tra...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant/Firm - Infrastructure Design...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - WASH Infrastructure monito...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - for Short-Term Studies, As...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
 Jobseekers
 Register
 Login
@@ -5702,38 +6120,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F25" s="1" t="inlineStr">
+      <c r="F27" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G25" s="1" t="inlineStr">
+      <c r="G27" s="1" t="inlineStr">
         <is>
           <t>31-03-2026</t>
         </is>
       </c>
-      <c r="H25" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="I25" s="1" t="inlineStr">
+      <c r="H27" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="I27" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287726</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr"/>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="B28" s="1" t="inlineStr"/>
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>Associate – Finance and Operations</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Financial Management Service Foundation (FMSF) | Uttar Pradesh
 International Development - Associate – Finance and Operations, Financial Management Service Foundation (FMSF), Uttar Pradesh - DevNetJobsIndia.org
@@ -5748,7 +6166,7 @@
 Search ... Read More</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>• Joining FMSF means becoming part of a passionate team dedicated to making a positive impact. We offer competitive compensation, opportunities for professional development, and a supportive work environment where your contributions are valued and recognized. If you are committed to driving positive change, promoting accountability and strengthening the development sector, we encourage you to apply for the position of
 Associate – Finance and Operations
@@ -5832,54 +6250,54 @@
 13 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Partnerships and Fundraising)
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Assistant Manager – MIS
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-UN Women National Consultant – GRB Technical Coor...
-UN Women
-Location:
-Delhi
+State Consultant - Communication, Advocacy and Pa...
+UNICEF
+Location:
+Rajasthan
+Apply by:
+23 Mar 2026
+RFP - Hiring agency to implement the organisation...
+Breakthrough
+Location:
+India
 Apply by:
 22 Mar 2026
-UN Women National Consultant – GRB Expert - MWCD,...
-UN Women
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-Communication Officer
-Association for Stimulating Know How (ASK)
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Program Coordinator
-Sampark Foundation
-Location:
-India
-Apply by:
-10 Apr 2026
-Senior Consultant – Education
-TeamLease Foundation
-Location:
-Delhi
-Apply by:
-10 Apr 2026
-Program Coordinator - Government Relations  &amp; Adv...
-Quest Alliance
-Location:
-Andhra Pradesh
-Apply by:
-10 Apr 2026
+Technical Consultant - Hydrogeologists
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+IFP - for Strengthening systems for multi-sectora...
+UNFPA
+Location:
+India
+Apply by:
+17 Apr 2026
+Technical Consultant – Support and facilitate Tra...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant/Firm - Infrastructure Design...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - WASH Infrastructure monito...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - for Short-Term Studies, As...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
 Jobseekers
 Register
 Login
@@ -5907,38 +6325,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F26" s="1" t="inlineStr">
+      <c r="F28" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G26" s="1" t="inlineStr">
+      <c r="G28" s="1" t="inlineStr">
         <is>
           <t>05-04-2026</t>
         </is>
       </c>
-      <c r="H26" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="I26" s="1" t="inlineStr">
+      <c r="H28" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="I28" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287913</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr"/>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="B29" s="1" t="inlineStr"/>
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>Research Analysts</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Academy of Management Studies (AMS) | India
 International Development - Research Analysts, Academy of Management Studies (AMS), India - DevNetJobsIndia.org
@@ -5959,7 +6377,7 @@
 Jobseekers Log ... Read More</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>• Eligibility:
 R
@@ -6104,54 +6522,54 @@
 13 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Partnerships and Fundraising)
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Assistant Manager – MIS
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-UN Women National Consultant – GRB Technical Coor...
-UN Women
-Location:
-Delhi
+State Consultant - Communication, Advocacy and Pa...
+UNICEF
+Location:
+Rajasthan
+Apply by:
+23 Mar 2026
+RFP - Hiring agency to implement the organisation...
+Breakthrough
+Location:
+India
 Apply by:
 22 Mar 2026
-UN Women National Consultant – GRB Expert - MWCD,...
-UN Women
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-Communication Officer
-Association for Stimulating Know How (ASK)
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Program Coordinator
-Sampark Foundation
-Location:
-India
-Apply by:
-10 Apr 2026
-Senior Consultant – Education
-TeamLease Foundation
-Location:
-Delhi
-Apply by:
-10 Apr 2026
-Program Coordinator - Government Relations  &amp; Adv...
-Quest Alliance
-Location:
-Andhra Pradesh
-Apply by:
-10 Apr 2026
+Technical Consultant - Hydrogeologists
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+IFP - for Strengthening systems for multi-sectora...
+UNFPA
+Location:
+India
+Apply by:
+17 Apr 2026
+Technical Consultant – Support and facilitate Tra...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant/Firm - Infrastructure Design...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - WASH Infrastructure monito...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - for Short-Term Studies, As...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
 Jobseekers
 Register
 Login
@@ -6179,38 +6597,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F27" s="1" t="inlineStr">
+      <c r="F29" s="1" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="G27" s="1" t="inlineStr">
+      <c r="G29" s="1" t="inlineStr">
         <is>
           <t>11-04-2026</t>
         </is>
       </c>
-      <c r="H27" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="I27" s="1" t="inlineStr">
+      <c r="H29" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="I29" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=288160</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr"/>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="B30" s="1" t="inlineStr"/>
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>Unit Head - Proposal Development</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Academy of Management Studies (AMS) | India
 International Development - Unit Head - Proposal Development, Academy of Management Studies (AMS), India - DevNetJobsIndia.org
@@ -6230,7 +6648,7 @@
 Register ... Read More</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>• Understand client requirements and check our eligibility against the criteria given in the bid
 Prepare detailed queries to be raised in the pre-bid meetings
@@ -6380,54 +6798,54 @@
 13 Mar 2026
 Latest Jobs
 Post your highlighted jobs here
-Assistant Manager (Partnerships and Fundraising)
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Assistant Manager – MIS
-Pragya
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-UN Women National Consultant – GRB Technical Coor...
-UN Women
-Location:
-Delhi
+State Consultant - Communication, Advocacy and Pa...
+UNICEF
+Location:
+Rajasthan
+Apply by:
+23 Mar 2026
+RFP - Hiring agency to implement the organisation...
+Breakthrough
+Location:
+India
 Apply by:
 22 Mar 2026
-UN Women National Consultant – GRB Expert - MWCD,...
-UN Women
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-Communication Officer
-Association for Stimulating Know How (ASK)
-Location:
-Haryana
-Apply by:
-10 Apr 2026
-Program Coordinator
-Sampark Foundation
-Location:
-India
-Apply by:
-10 Apr 2026
-Senior Consultant – Education
-TeamLease Foundation
-Location:
-Delhi
-Apply by:
-10 Apr 2026
-Program Coordinator - Government Relations  &amp; Adv...
-Quest Alliance
-Location:
-Andhra Pradesh
-Apply by:
-10 Apr 2026
+Technical Consultant - Hydrogeologists
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+IFP - for Strengthening systems for multi-sectora...
+UNFPA
+Location:
+India
+Apply by:
+17 Apr 2026
+Technical Consultant – Support and facilitate Tra...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant/Firm - Infrastructure Design...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - WASH Infrastructure monito...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - for Short-Term Studies, As...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
 Jobseekers
 Register
 Login
@@ -6455,319 +6873,370 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F28" s="1" t="inlineStr">
+      <c r="F30" s="1" t="inlineStr">
         <is>
           <t>Governance, Learning</t>
         </is>
       </c>
-      <c r="G28" s="1" t="inlineStr">
+      <c r="G30" s="1" t="inlineStr">
         <is>
           <t>11-04-2026</t>
         </is>
       </c>
-      <c r="H28" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="I28" s="1" t="inlineStr">
+      <c r="H30" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="I30" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=288161</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>HCL Foundation</t>
-        </is>
-      </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards Biodiversity monitoring for Pan-India Afforestation sites</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr"/>
-      <c r="E29" s="2" t="inlineStr"/>
-      <c r="F29" s="1" t="inlineStr">
-        <is>
-          <t>Climate</t>
-        </is>
-      </c>
-      <c r="G29" s="1" t="inlineStr">
-        <is>
-          <t>10th Feb, 2026</t>
-        </is>
-      </c>
-      <c r="H29" s="1" t="inlineStr"/>
-      <c r="I29" s="1" t="inlineStr">
-        <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Biodiversity%20monitoring%20for%20Pan-India%20Afforestation%20sites%202-DSB.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>HCL Foundation</t>
-        </is>
-      </c>
-      <c r="B30" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards soil profiling and assessment from the restored and rejuvenated Harit sites.</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr"/>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="1" t="inlineStr">
-        <is>
-          <t>Climate</t>
-        </is>
-      </c>
-      <c r="G30" s="1" t="inlineStr">
-        <is>
-          <t>10th Feb, 2026</t>
-        </is>
-      </c>
-      <c r="H30" s="1" t="inlineStr"/>
-      <c r="I30" s="1" t="inlineStr">
-        <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Soil%20assessment-v1%20RKS-DSB_0.pdf</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>HCL Foundation</t>
-        </is>
-      </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>DevNetJobsIndia</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="inlineStr"/>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites proposals from NGOs/CSR implementing agencies for ‘Operating a Social Enterprise Cafe” under the flagship urban development programme - Uday</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr"/>
-      <c r="E31" s="2" t="inlineStr"/>
+          <t>IFP - for Strengthening systems for multi-sectoral response to Gender-Base...</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>UNFPA | India
+International Development - IFP - for Strengthening systems for multi-sectoral response to Gender-Based Violence (GBV), through model one-stop centres, UNFPA, India - DevNetJobsIndia.org
+Jobseekers:
+Login
+|
+Register
+Home
+Value Membership
+Broadcast Resume
+RFPs/Tenders
+Search Jobs
+Event ... Read More</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>• Applicants are not required to build in budgets for Workstream D (Infrastructure upgrades) at this stage. The budgets for this workstream will be determined based on actual costs, after the agency selection process has been completed and the partnership has been finalized.
+For detailed information, please check the complete version of the IFP attached below.
+Download Attachment:
+UNFPA_CP10_IFP_2026_024.pdf
+View Similar Jobs:
+Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
+Subscribe
+Apply by:
+17 Apr 2026
+Access all the jobs and get ahead!
+Subscribe to Value Membership Now!
+Subscribe
+Premium Jobs
+Post your premium jobs here
+Unit Head - Proposal Development
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Research Analysts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+11 Apr 2026
+Lead-Finance &amp; Compliance
+Marathwada Navnirman Lokayat (Manavlok)
+Location:
+Maharashtra
+Apply by:
+03 Apr 2026
+Sector Experts
+Academy of Management Studies (AMS)
+Location:
+India
+Apply by:
+31 Mar 2026
+Associate – Finance and Operations
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+05 Apr 2026
+Junior Research Technicians / Senior Project Asso...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Agriculture Research Development Officer / Projec...
+Starshield Security Solution Pvt.Ltd
+Location:
+Uttar Pradesh
+Apply by:
+30 Mar 2026
+Specialist - Grants
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+21 Mar 2026
+Specialist – Communication
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+19 Mar 2026
+Specialist – Financial Management and Compliance
+Financial Management Service Foundation (FMSF)
+Location:
+Uttar Pradesh
+Apply by:
+13 Mar 2026
+Latest Jobs
+Post your highlighted jobs here
+State Consultant - Communication, Advocacy and Pa...
+UNICEF
+Location:
+Rajasthan
+Apply by:
+23 Mar 2026
+RFP - Hiring agency to implement the organisation...
+Breakthrough
+Location:
+India
+Apply by:
+22 Mar 2026
+Technical Consultant - Hydrogeologists
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+IFP - for Strengthening systems for multi-sectora...
+UNFPA
+Location:
+India
+Apply by:
+17 Apr 2026
+Technical Consultant – Support and facilitate Tra...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant/Firm - Infrastructure Design...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - WASH Infrastructure monito...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Technical Consultant - for Short-Term Studies, As...
+WaterAid India
+Location:
+India
+Apply by:
+20 Mar 2026
+Jobseekers
+Register
+Login
+Subscribe to Value Membership
+Broadcast Resume
+Contact Us
+Recruiters
+Recruiters Zone
+Post a Free Job
+Post a Highlighted Job (With Logo)
+Post a Highlighted Job (Without Logo)
+Post a Premium Job
+More Job Posting Options
+Rates
+Contact Us
+Advertisers
+Networks
+Advertise Your Banner
+Submit Events &amp; Notices
+© 2025 M-Power Jobs. All rights reserved.
+Disclaimer
+Privacy Policy
+Terms &amp; Conditions
+Powered by
+Recruitment Exchange</t>
+        </is>
+      </c>
       <c r="F31" s="1" t="inlineStr">
         <is>
-          <t>Learning</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="G31" s="1" t="inlineStr">
         <is>
-          <t>15th Dec, 2025</t>
-        </is>
-      </c>
-      <c r="H31" s="1" t="inlineStr"/>
+          <t>17-04-2026</t>
+        </is>
+      </c>
+      <c r="H31" s="1" t="n">
+        <v>36</v>
+      </c>
       <c r="I31" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-11/RfP_Social%20Enterprise%20Cafe_UDAY.docx</t>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=288192</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>HCL Foundation</t>
-        </is>
-      </c>
-      <c r="B32" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr"/>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>Programme Officer/Senior Programme Officer – Environment Education</t>
+          <t>RFP for Endline Evaluation Study - HSBC GCC Women Entrepreneurship Program - Click here</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="1" t="inlineStr">
         <is>
-          <t>Learning, Climate</t>
-        </is>
-      </c>
-      <c r="G32" s="1" t="inlineStr">
-        <is>
-          <t>10th Nov, 2025</t>
-        </is>
-      </c>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G32" s="1" t="inlineStr"/>
       <c r="H32" s="1" t="inlineStr"/>
       <c r="I32" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-10/Harit_POSPO_EEA_Multilocation_Oct%202025.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/endline-evaluation-study-hsbc-gcc-women-entrepreneurship-program.pdf</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>HCL Foundation</t>
-        </is>
-      </c>
-      <c r="B33" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="inlineStr"/>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites applications for the PO/SPO position under its flagship programme Harit by HCLFoundation</t>
+          <t>Travel &amp; Transportation Services for Trainer Mobility - IBM SkillBuild Bootcamps - Click here</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr"/>
       <c r="F33" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G33" s="1" t="inlineStr">
-        <is>
-          <t>31st Oct, 2025</t>
-        </is>
-      </c>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G33" s="1" t="inlineStr"/>
       <c r="H33" s="1" t="inlineStr"/>
       <c r="I33" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-10/JD_Water%20Conservation_SPO%20V4.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/travel-and-transportation-services-for-trainer-mobility-ibm-skillbuild-bootcamps.pdf</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>HCL Foundation</t>
-        </is>
-      </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="inlineStr"/>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit by HCLFoundation, invites RFP from NGOs / CSR organizations working in Water Conservation for the development of Water Structures etc.</t>
+          <t>Baseline and End-line Evaluation of the HSBC Neurodivergent Digital Annotator Skilling Program - Click here | Click here</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="1" t="inlineStr">
         <is>
-          <t>Learning, Climate</t>
-        </is>
-      </c>
-      <c r="G34" s="1" t="inlineStr">
-        <is>
-          <t>21st May, 2025</t>
-        </is>
-      </c>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G34" s="1" t="inlineStr"/>
       <c r="H34" s="1" t="inlineStr"/>
       <c r="I34" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/Final_RFP%20for%20water%20structure%20rejuvenation%20.docx</t>
+          <t>https://www.nasscomfoundation.org/pdf/baseline-and-end-line-evaluation-of-hsbc-neurodivergent-digital-annotator-skilling-program.pdf</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>HCL Foundation</t>
-        </is>
-      </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="inlineStr"/>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites technical application abstracts for the developing technology drive source code model mobile applications and web portals for addressing human-animal interactions under the Animal Welfare thematic of  Harit by HCLFoundation</t>
+          <t>RFP for Catering Vendor - IBM Skillbuild Bootcamps - Click here</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="1" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G35" s="1" t="inlineStr">
-        <is>
-          <t>15th May, 2025</t>
-        </is>
-      </c>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G35" s="1" t="inlineStr"/>
       <c r="H35" s="1" t="inlineStr"/>
       <c r="I35" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_AW%20Tech%20Based%20Source%20Code%20Model_V1%20%281%29.docx</t>
+          <t>https://www.nasscomfoundation.org/pdf/rfp-for-catering-vendor-ibm-skillbuild-bootcamps.pdf</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>HCL Foundation</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="inlineStr"/>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation, under its Environment flagship programme Harit invites RFP from NGOs/CSR organizations working in the field of environment for project on the restoration of various degraded and natural habitats</t>
+          <t>Organization-wide Management Information System (MIS) for Nasscom Foundation - Click here</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="1" t="inlineStr">
         <is>
-          <t>Climate</t>
-        </is>
-      </c>
-      <c r="G36" s="1" t="inlineStr">
-        <is>
-          <t>15th May, 2025</t>
-        </is>
-      </c>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G36" s="1" t="inlineStr"/>
       <c r="H36" s="1" t="inlineStr"/>
       <c r="I36" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/Harit_A%20HR_RFP%20.docx</t>
+          <t>https://www.nasscomfoundation.org/pdf/organization-wide-management-information-system-for-nasscom-foundation.pdf</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>HCL Foundation</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="inlineStr"/>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites EOI for conducting holistic and comprehensive Impact Assessments of environmental projects supported under Harit by HCLFoundation</t>
+          <t>Request for Proposal (RFP) for Social Media Management Services - Click here</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr"/>
@@ -6777,617 +7246,712 @@
           <t>Governance</t>
         </is>
       </c>
-      <c r="G37" s="1" t="inlineStr">
-        <is>
-          <t>15th May, 2025</t>
-        </is>
-      </c>
+      <c r="G37" s="1" t="inlineStr"/>
       <c r="H37" s="1" t="inlineStr"/>
       <c r="I37" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_Harit%20Impact%20Assessments.docx</t>
+          <t>https://www.nasscomfoundation.org/pdf/request-for-proposal-for-social-media-management-services.pdf</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>HCL Foundation</t>
-        </is>
-      </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="inlineStr"/>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>HCLFoundation invites technical application abstracts for the conducting technical and highly engaging environment awareness and sustainability workshops under Harit by HCLFoundation</t>
+          <t>RFP - TechForSociety - Evaluation Study - Click here</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>Climate</t>
-        </is>
-      </c>
-      <c r="G38" s="1" t="inlineStr">
-        <is>
-          <t>15th May, 2025</t>
-        </is>
-      </c>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G38" s="1" t="inlineStr"/>
       <c r="H38" s="1" t="inlineStr"/>
       <c r="I38" s="1" t="inlineStr">
         <is>
-          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_EEA_Env%20%20Sus%20awareness%20workshops_FY%2025-26%20%281%29.docx</t>
+          <t>https://www.nasscomfoundation.org/pdf/techforsociety-evaluation-study.pdf</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B39" s="1" t="inlineStr"/>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>Supply_of_Unskilled_Manpower.pdf</t>
+          <t>Base-line and End-line evaluation for Digital Literacy Project in 4 States - Click here</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr"/>
-      <c r="F39" s="1" t="inlineStr"/>
+      <c r="F39" s="1" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
       <c r="G39" s="1" t="inlineStr"/>
       <c r="H39" s="1" t="inlineStr"/>
       <c r="I39" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Supply_of_Unskilled_Manpower.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/base-line-and-end-line-evaluation-for-digital-literacy-project-in-4-states.pdf</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B40" s="1" t="inlineStr"/>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>Addendum manpower quotation.pdf</t>
+          <t>IP Selection - Scholarship Support to students from Economically Weaker Section pursuing higher education in STEM courses - Click here</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="1" t="inlineStr"/>
+      <c r="F40" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
       <c r="G40" s="1" t="inlineStr"/>
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Addendum%20manpower%20quotation.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/scholarship-support-for-economically-weaker-section-students-in-stem-higher-education.pdf</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B41" s="1" t="inlineStr"/>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>Quotation_for_Rate_Contrac_Vehicle_Hiring_for_NCR_or_Outstation..pdf</t>
+          <t>Digital Upskilling of Farmer Producer Organizations (FPOs) through Technology - Click here</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr"/>
       <c r="E41" s="2" t="inlineStr"/>
-      <c r="F41" s="1" t="inlineStr"/>
+      <c r="F41" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
       <c r="G41" s="1" t="inlineStr"/>
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Quotation_for_Rate_Contrac_Vehicle_Hiring_for_NCR_or_Outstation..pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/baseline-endline-study-digital-upskilling-fpos-technology.pdf</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="inlineStr"/>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>Final_RfP_UrbanShift_Preparation_of_Integrated_Green_Mobility_Plan_for_Pune.pdf</t>
+          <t>Project - Accelerating 100 Women Micro Entrepreneurs of Northeastern States - Click here</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr"/>
-      <c r="F42" s="1" t="inlineStr"/>
+      <c r="F42" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
       <c r="G42" s="1" t="inlineStr"/>
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Final_RfP_UrbanShift_Preparation_of_Integrated_Green_Mobility_Plan_for_Pune.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/project-accelerating-100-women-micro-entrepreneurs-of-northeastern-states.pdf</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="inlineStr"/>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>RfP_IGMP_Response to Pre-Bid Queries_200226.pdf</t>
+          <t>Agency for Developing Training Modules and Conducting Training of Trainers (ToT) for MSMEs on IPR and Financial Management - Click here</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
       <c r="E43" s="2" t="inlineStr"/>
-      <c r="F43" s="1" t="inlineStr"/>
+      <c r="F43" s="1" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
       <c r="G43" s="1" t="inlineStr"/>
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/RfP_IGMP_Response%20to%20Pre-Bid%20Queries_200226.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/agency-for-developing-training-modules-and-conducting-ToT-for-MSMEs-on-IPR-and-financial-management.pdf</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B44" s="1" t="inlineStr"/>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>Corrigendum_1_RfP_IGMP.pdf</t>
+          <t>RFP for WISE - Women in Innovation, Skills &amp; Entrepreneurship - Click here</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
       <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="1" t="inlineStr"/>
+      <c r="F44" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
       <c r="G44" s="1" t="inlineStr"/>
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Corrigendum_1_RfP_IGMP.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/women-in-Innovation-skills-and-entrepreneurship.pdf</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B45" s="1" t="inlineStr"/>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>Corrigendum 2_IGMP.pdf</t>
+          <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - English  - Click here</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
       <c r="E45" s="2" t="inlineStr"/>
-      <c r="F45" s="1" t="inlineStr"/>
+      <c r="F45" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
       <c r="G45" s="1" t="inlineStr"/>
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Corrigendum%202_IGMP.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-English.pdf</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B46" s="1" t="inlineStr"/>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>RFP_Engagement of GIS Expert_SCBP_2026.pdf</t>
+          <t>Women Entrepreneurs Digital Upskilling Project - ATR Program In collaboration with Women Entrepreneurship Platform (WEP), NITI Aayog &amp; Nasscom Foundation - Kannada - Click here</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="2" t="inlineStr"/>
-      <c r="F46" s="1" t="inlineStr"/>
+      <c r="F46" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
       <c r="G46" s="1" t="inlineStr"/>
       <c r="H46" s="1" t="inlineStr"/>
       <c r="I46" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/RFP_Engagement%20of%20GIS%20Expert_SCBP_2026.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/WEP-NI-ATR-RFA-Kannada.pdf</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B47" s="1" t="inlineStr"/>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>Response_to_Queries_Engagement_of_GIS_Expert_Agency.pdf</t>
+          <t>RFP - Trainer for Nano Women Entrepreneurs in Karnataka - Click here</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
       <c r="E47" s="2" t="inlineStr"/>
-      <c r="F47" s="1" t="inlineStr"/>
+      <c r="F47" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
       <c r="G47" s="1" t="inlineStr"/>
       <c r="H47" s="1" t="inlineStr"/>
       <c r="I47" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Response_to_Queries_Engagement_of_GIS_Expert_Agency.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/trainer-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B48" s="1" t="inlineStr"/>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>RfP_SRTW.pdf</t>
+          <t>RFP - Training Agency with Content and Trainers for Nano Women Entrepreneurs in Karnataka - Click here</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
       <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="1" t="inlineStr"/>
+      <c r="F48" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
       <c r="G48" s="1" t="inlineStr"/>
       <c r="H48" s="1" t="inlineStr"/>
       <c r="I48" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/RfP_SRTW.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/training-agency-with-content-and-trainers-for-nano-women-entrepreneurs-in-karnataka.pdf</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B49" s="1" t="inlineStr"/>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>Response to Pre-Bid Queries_SRTW_for Uploading.pdf</t>
+          <t>Access to E-Governance and Livelihood in PVTG Communities in Aspirational Blocks - Click here</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
       <c r="E49" s="2" t="inlineStr"/>
-      <c r="F49" s="1" t="inlineStr"/>
+      <c r="F49" s="1" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
       <c r="G49" s="1" t="inlineStr"/>
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Response%20to%20Pre-Bid%20Queries_SRTW_for%20Uploading.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/access-to-e-governance-and-livelihood-in-pvtg-communities-in-aspirational-blocks.pdf</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>NIUA</t>
-        </is>
-      </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>Tender</t>
-        </is>
-      </c>
+          <t>Nasscom</t>
+        </is>
+      </c>
+      <c r="B50" s="1" t="inlineStr"/>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>EOI_TECHNICAL_ASSISTANCE_UNDER_CITIIS_2.0_PROGRAM_DOMESTIC_POOL_OF_EXPERTS.pdf</t>
+          <t>thingQbator Portal Enhancement and Maintenance Proposal - Click here</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
       <c r="E50" s="2" t="inlineStr"/>
-      <c r="F50" s="1" t="inlineStr"/>
+      <c r="F50" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
       <c r="G50" s="1" t="inlineStr"/>
       <c r="H50" s="1" t="inlineStr"/>
       <c r="I50" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/EOI_TECHNICAL_ASSISTANCE_UNDER_CITIIS_2.0_PROGRAM_DOMESTIC_POOL_OF_EXPERTS.pdf</t>
+          <t>https://www.nasscomfoundation.org/pdf/thingQbator-portal-enhancement-and-maintenance-proposal.pdf</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>NIUA</t>
+          <t>HCL Foundation</t>
         </is>
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>Tender</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>Reply to Pre- Bid Queries - EOI for DE's under CITIIS 2.0.pdf</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards Biodiversity monitoring for Pan-India Afforestation sites</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
       <c r="E51" s="2" t="inlineStr"/>
-      <c r="F51" s="1" t="inlineStr"/>
-      <c r="G51" s="1" t="inlineStr"/>
+      <c r="F51" s="1" t="inlineStr">
+        <is>
+          <t>Climate</t>
+        </is>
+      </c>
+      <c r="G51" s="1" t="inlineStr">
+        <is>
+          <t>10th Feb, 2026</t>
+        </is>
+      </c>
       <c r="H51" s="1" t="inlineStr"/>
       <c r="I51" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Reply%20to%20Pre-%20Bid%20Queries%20-%20EOI%20for%20DE%27s%20under%20CITIIS%202.0.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Biodiversity%20monitoring%20for%20Pan-India%20Afforestation%20sites%202-DSB.pdf</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>NIUA</t>
+          <t>HCL Foundation</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>Tender</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>GeM-Bidding-8666471.pdf</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit, invites RFP from NGOs / CSR organizations/ agencies / Institutions working towards soil profiling and assessment from the restored and rejuvenated Harit sites.</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
       <c r="E52" s="2" t="inlineStr"/>
-      <c r="F52" s="1" t="inlineStr"/>
-      <c r="G52" s="1" t="inlineStr"/>
+      <c r="F52" s="1" t="inlineStr">
+        <is>
+          <t>Climate</t>
+        </is>
+      </c>
+      <c r="G52" s="1" t="inlineStr">
+        <is>
+          <t>10th Feb, 2026</t>
+        </is>
+      </c>
       <c r="H52" s="1" t="inlineStr"/>
       <c r="I52" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-8666471.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2026-01/RFP_Soil%20assessment-v1%20RKS-DSB_0.pdf</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>NIUA</t>
+          <t>HCL Foundation</t>
         </is>
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>Tender</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>corgaudt1.pdf</t>
+          <t>HCLFoundation invites proposals from NGOs/CSR implementing agencies for ‘Operating a Social Enterprise Cafe” under the flagship urban development programme - Uday</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
       <c r="E53" s="2" t="inlineStr"/>
-      <c r="F53" s="1" t="inlineStr"/>
-      <c r="G53" s="1" t="inlineStr"/>
+      <c r="F53" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G53" s="1" t="inlineStr">
+        <is>
+          <t>15th Dec, 2025</t>
+        </is>
+      </c>
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/corgaudt1.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-11/RfP_Social%20Enterprise%20Cafe_UDAY.docx</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>NIUA</t>
+          <t>HCL Foundation</t>
         </is>
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>Tender</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>Corrigendum6959493.pdf</t>
+          <t>Programme Officer/Senior Programme Officer – Environment Education</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
       <c r="E54" s="2" t="inlineStr"/>
-      <c r="F54" s="1" t="inlineStr"/>
-      <c r="G54" s="1" t="inlineStr"/>
+      <c r="F54" s="1" t="inlineStr">
+        <is>
+          <t>Learning, Climate</t>
+        </is>
+      </c>
+      <c r="G54" s="1" t="inlineStr">
+        <is>
+          <t>10th Nov, 2025</t>
+        </is>
+      </c>
       <c r="H54" s="1" t="inlineStr"/>
       <c r="I54" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Corrigendum6959493.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-10/Harit_POSPO_EEA_Multilocation_Oct%202025.pdf</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>NIUA</t>
+          <t>HCL Foundation</t>
         </is>
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>Tender</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>ADDENDUM6959493.pdf</t>
+          <t>HCLFoundation invites applications for the PO/SPO position under its flagship programme Harit by HCLFoundation</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr"/>
       <c r="E55" s="2" t="inlineStr"/>
-      <c r="F55" s="1" t="inlineStr"/>
-      <c r="G55" s="1" t="inlineStr"/>
+      <c r="F55" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G55" s="1" t="inlineStr">
+        <is>
+          <t>31st Oct, 2025</t>
+        </is>
+      </c>
       <c r="H55" s="1" t="inlineStr"/>
       <c r="I55" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/ADDENDUM6959493.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-10/JD_Water%20Conservation_SPO%20V4.pdf</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>NIUA</t>
+          <t>HCL Foundation</t>
         </is>
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>Tender</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>RfP CJ&amp;IP Package 03_UrbanShift.pdf</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit by HCLFoundation, invites RFP from NGOs / CSR organizations working in Water Conservation for the development of Water Structures etc.</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
       <c r="E56" s="2" t="inlineStr"/>
-      <c r="F56" s="1" t="inlineStr"/>
-      <c r="G56" s="1" t="inlineStr"/>
+      <c r="F56" s="1" t="inlineStr">
+        <is>
+          <t>Learning, Climate</t>
+        </is>
+      </c>
+      <c r="G56" s="1" t="inlineStr">
+        <is>
+          <t>21st May, 2025</t>
+        </is>
+      </c>
       <c r="H56" s="1" t="inlineStr"/>
       <c r="I56" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/RfP%20CJ%26IP%20Package%2003_UrbanShift.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/Final_RFP%20for%20water%20structure%20rejuvenation%20.docx</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>NIUA</t>
+          <t>HCL Foundation</t>
         </is>
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>Tender</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>Prebid reply Cj&amp;IP package 3_18.12.2025.pdf</t>
+          <t>HCLFoundation invites technical application abstracts for the developing technology drive source code model mobile applications and web portals for addressing human-animal interactions under the Animal Welfare thematic of  Harit by HCLFoundation</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr"/>
       <c r="E57" s="2" t="inlineStr"/>
-      <c r="F57" s="1" t="inlineStr"/>
-      <c r="G57" s="1" t="inlineStr"/>
+      <c r="F57" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G57" s="1" t="inlineStr">
+        <is>
+          <t>15th May, 2025</t>
+        </is>
+      </c>
       <c r="H57" s="1" t="inlineStr"/>
       <c r="I57" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/Prebid%20reply%20Cj%26IP%20package%203_18.12.2025.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_AW%20Tech%20Based%20Source%20Code%20Model_V1%20%281%29.docx</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>NIUA</t>
+          <t>HCL Foundation</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>Tender</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>GeM-Bidding-8478801.pdf</t>
+          <t>HCLFoundation, under its Environment flagship programme Harit invites RFP from NGOs/CSR organizations working in the field of environment for project on the restoration of various degraded and natural habitats</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr"/>
       <c r="E58" s="2" t="inlineStr"/>
-      <c r="F58" s="1" t="inlineStr"/>
-      <c r="G58" s="1" t="inlineStr"/>
+      <c r="F58" s="1" t="inlineStr">
+        <is>
+          <t>Climate</t>
+        </is>
+      </c>
+      <c r="G58" s="1" t="inlineStr">
+        <is>
+          <t>15th May, 2025</t>
+        </is>
+      </c>
       <c r="H58" s="1" t="inlineStr"/>
       <c r="I58" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-8478801.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/Harit_A%20HR_RFP%20.docx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>NIUA</t>
+          <t>HCL Foundation</t>
         </is>
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>Tender</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>GeM-Bidding-8476974.pdf</t>
+          <t>HCLFoundation invites EOI for conducting holistic and comprehensive Impact Assessments of environmental projects supported under Harit by HCLFoundation</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr"/>
       <c r="E59" s="2" t="inlineStr"/>
-      <c r="F59" s="1" t="inlineStr"/>
-      <c r="G59" s="1" t="inlineStr"/>
+      <c r="F59" s="1" t="inlineStr">
+        <is>
+          <t>Governance</t>
+        </is>
+      </c>
+      <c r="G59" s="1" t="inlineStr">
+        <is>
+          <t>15th May, 2025</t>
+        </is>
+      </c>
       <c r="H59" s="1" t="inlineStr"/>
       <c r="I59" s="1" t="inlineStr">
         <is>
-          <t>https://niua.in/sites/default/files/tenders/GeM-Bidding-8476974.pdf</t>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_Harit%20Impact%20Assessments.docx</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>HCL Foundation</t>
+        </is>
+      </c>
+      <c r="B60" s="1" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="inlineStr">
+        <is>
+          <t>HCLFoundation invites technical application abstracts for the conducting technical and highly engaging environment awareness and sustainability workshops under Harit by HCLFoundation</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr"/>
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="1" t="inlineStr">
+        <is>
+          <t>Climate</t>
+        </is>
+      </c>
+      <c r="G60" s="1" t="inlineStr">
+        <is>
+          <t>15th May, 2025</t>
+        </is>
+      </c>
+      <c r="H60" s="1" t="inlineStr"/>
+      <c r="I60" s="1" t="inlineStr">
+        <is>
+          <t>https://www.hclfoundation.org/sites/default/files/2025-04/EoI_EEA_Env%20%20Sus%20awareness%20workshops_FY%2025-26%20%281%29.docx</t>
         </is>
       </c>
     </row>

--- a/all_grants.xlsx
+++ b/all_grants.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -489,227 +489,10 @@
       <c r="B2" s="1" t="inlineStr"/>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>RFP - for Internal Audit</t>
+          <t>RFP - for Supply of Skill Lab Items</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>India HIV/AIDS Alliance (Alliance India) | Delhi
-RFP - for Internal Audit, India HIV/AIDS Alliance (Alliance India)() | DevNetJobsIndia
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Login
-|
-Register
-Jobseekers Login
-Jobseekers Regist ... Read More</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>• Alliance India reserves the right to reject applications that do not meet eligibility or application submission requirements (as detailed above) without further notice to the applicant. Issuance of this RFP does not constitute an award commitment or a guarantee of business on the part of Alliance India, nor does it commit Alliance India to pay for the costs incurred in submitting the application. Further, Alliance India reserves the right to reject any or all applications received and negotiate separately with an applicant if such action is considered in the best interest of Alliance India/ project.
-iii.
-Queries, Response and Submission
-Queries regarding this RFP will be sent only to procurement@allianceindia.org by March 07, 2026. Alliance India shall collaborate and respond to all meaningful queries from prospective applicants by March 10, 2026. Responses to questions shall be compiled and sent to all the applicants who raised the queries through email only. ALLIANCE INDIA is under no obligation to consider or respond to questions that are not received on time.
-iv.
-• Submission of bids
-The bid has to be submitted in the prescribed format on or before March 13, 2026 by 5 p.m. Indian Standard Time to
-procurement@allianceindia.org
-For the detailed version of the Request for Proposal, please refer to the RFP attached.
-• Job Email ID:
-procurement(at)allianceindia.org
-Download Attachment:
-RFP for Internal Audit - FY 2025-26.doc
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-13 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Associate – Finance and Operations
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-05 Apr 2026
-Unit Head - Proposal Development
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-11 Apr 2026
-Research Analysts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-11 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-View more featured non-profit jobs
-Latest NGO Jobs
-Post your highlighted jobs here
-Coordinator- Business Development &amp; Partnerships
-Karl Kubel Foundation For Child And Family
-Location:
-Tamil Nadu
-Apply by:
-29 Mar 2026
-Executive Assistant / Team Assistant
-National Council Of Applied Economic Research (NC...
-Location:
-Delhi
-Apply by:
-25 Mar 2026
-RFP - for Outcome Evaluation : Enhancing Foundati...
-Language and Learning Foundation (LLF)
-Location:
-Haryana
-Apply by:
-21 Mar 2026
-Resource Person
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-India
-Apply by:
-10 Apr 2026
-Manager - Business Development
-Foundation For Development Initiative (FDI)
-Location:
-Delhi
-Apply by:
-12 Apr 2026
-Consultant/ Jr. Officer – Business Development Su...
-Pathfinder Impact Solutions Private Limited
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-State Consultant-Child Protection CPSS
-UNICEF
-Location:
-Gujarat
-Apply by:
-22 Mar 2026
-RFP -  for  Baseline Study of Goat- Sheep based L...
-Urmul Setu Sansthan
-Location:
-Rajasthan
-Apply by:
-31 Mar 2026
-View all the latest non-profit jobs
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>13-03-2026</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287765</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr"/>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>RFP - for Supply of Skill Lab Items</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>TeamLease Foundation | India
 RFP - for Supply of Skill Lab Items, TeamLease Foundation() | DevNetJobsIndia
@@ -734,7 +517,7 @@
 RFP - for S ... Read More</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>• Technical Bid Submission Link-
 https://forms.gle/V9iy35ddb4kWEb468
@@ -833,63 +616,57 @@
 Uttar Pradesh
 Apply by:
 19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Coordinator- Business Development &amp; Partnerships
-Karl Kubel Foundation For Child And Family
-Location:
-Tamil Nadu
-Apply by:
-29 Mar 2026
-Executive Assistant / Team Assistant
-National Council Of Applied Economic Research (NC...
+Research Intern
+DAI Research and Advisory Services
 Location:
 Delhi
 Apply by:
-25 Mar 2026
-RFP - for Outcome Evaluation : Enhancing Foundati...
-Language and Learning Foundation (LLF)
-Location:
-Haryana
-Apply by:
-21 Mar 2026
-Resource Person
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-India
-Apply by:
-10 Apr 2026
-Manager - Business Development
-Foundation For Development Initiative (FDI)
+22 Mar 2026
+Content Writer and Facilitator
+Vedan Trust
+Location:
+Karnataka
+Apply by:
+13 Apr 2026
+Digital Content Developer
+Vedan Trust
+Location:
+Karnataka
+Apply by:
+13 Apr 2026
+CSR Project Co-Ordinator
+Youth For Seva
 Location:
 Delhi
 Apply by:
-12 Apr 2026
-Consultant/ Jr. Officer – Business Development Su...
-Pathfinder Impact Solutions Private Limited
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-State Consultant-Child Protection CPSS
-UNICEF
-Location:
-Gujarat
-Apply by:
-22 Mar 2026
-RFP -  for  Baseline Study of Goat- Sheep based L...
-Urmul Setu Sansthan
-Location:
-Rajasthan
+13 Apr 2026
+Marketing Officer
+Anchalik Samrudhi Sadhana Anusthan (Assa)
+Location:
+Odisha
 Apply by:
 31 Mar 2026
+Project Coordinator
+Gyan Seva Bharti Sansthan (GSBS)
+Location:
+Bihar
+Apply by:
+23 Mar 2026
+Financial &amp; Entitlement Linkages (FEL)
+Gyan Seva Bharti Sansthan (GSBS)
+Location:
+Bihar
+Apply by:
+23 Mar 2026
+Supervisors
+Gyan Seva Bharti Sansthan (GSBS)
+Location:
+Bihar
+Apply by:
+23 Mar 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -918,41 +695,41 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>15-03-2026</t>
         </is>
       </c>
-      <c r="H3" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="H2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287613</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr"/>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>ToR - Strategic Review and Forward-Looking Education Strategy Development</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr"/>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>ToR - Livelihoods Strategy Review and Future Direction Roadmap</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>ChildFund India | India
-ToR - Strategic Review and Forward-Looking Education Strategy Development, ChildFund India() | DevNetJobsIndia
+ToR - Livelihoods Strategy Review and Future Direction Roadmap, ChildFund India() | DevNetJobsIndia
 Jobseekers:
 Login
 |
@@ -968,15 +745,35 @@
 |
 Register
 Jobseekers Login
-Jobseekers Registe ... Read More</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>• Job Email ID:
+Jobseekers Register
+Job ID:
+2 ... Read More</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>• To determine the relevance, alignment, and coherence of the Livelihood Program under CSP 2022–2027 with national priorities, donor expectations, and organizational mandate.
+To assess the extent to which planned outputs and outcomes have been achieved and to evaluate the quality and impact of program interventions.
+Identify achievements, innovations, good practices, and enabling factors across Livelihood program interventions.
+Document gaps, challenges, and areas for strengthening
+To examine the sustainability of program outcomes and the institutional readiness of ChildFund India for long-term resilience and growth.
+Facilitate reflection through workshops involving staff, partners, and selected beneficiaries and provide recommendations for strategic direction, scalability, and future program priorities.
+Proposal Submission
+Interested evaluators/agencies are invited to submit:
+Technical proposal outlining approach and methodology
+Team composition and relevant experience
+Financial proposal with a detailed budget
+Sample of previous qualitative evaluation work
+Interested evaluators/agencies are requested to submit their technical and financial proposals to
+centralpurchase2@childfundindia.org
+by 15 March 2026.
+Reference No:- PRA/CFI/DEL/2025-26/053
+ChildFund India reserves the right to modify this ToR based on programmatic and contextual requirements.
+For detailed information, please check the complete version of the advert attached below.
+• Job Email ID:
 centralpurchase2(at)childfundindia.org
 Download Attachment:
-ToR for Education.doc
+ToR Livelihood Portfolio-6.3.2026.doc
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
@@ -1041,63 +838,57 @@
 Uttar Pradesh
 Apply by:
 19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Coordinator- Business Development &amp; Partnerships
-Karl Kubel Foundation For Child And Family
-Location:
-Tamil Nadu
-Apply by:
-29 Mar 2026
-Executive Assistant / Team Assistant
-National Council Of Applied Economic Research (NC...
+Research Intern
+DAI Research and Advisory Services
 Location:
 Delhi
 Apply by:
-25 Mar 2026
-RFP - for Outcome Evaluation : Enhancing Foundati...
-Language and Learning Foundation (LLF)
-Location:
-Haryana
-Apply by:
-21 Mar 2026
-Resource Person
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-India
-Apply by:
-10 Apr 2026
-Manager - Business Development
-Foundation For Development Initiative (FDI)
+22 Mar 2026
+Content Writer and Facilitator
+Vedan Trust
+Location:
+Karnataka
+Apply by:
+13 Apr 2026
+Digital Content Developer
+Vedan Trust
+Location:
+Karnataka
+Apply by:
+13 Apr 2026
+CSR Project Co-Ordinator
+Youth For Seva
 Location:
 Delhi
 Apply by:
-12 Apr 2026
-Consultant/ Jr. Officer – Business Development Su...
-Pathfinder Impact Solutions Private Limited
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-State Consultant-Child Protection CPSS
-UNICEF
-Location:
-Gujarat
-Apply by:
-22 Mar 2026
-RFP -  for  Baseline Study of Goat- Sheep based L...
-Urmul Setu Sansthan
-Location:
-Rajasthan
+13 Apr 2026
+Marketing Officer
+Anchalik Samrudhi Sadhana Anusthan (Assa)
+Location:
+Odisha
 Apply by:
 31 Mar 2026
+Project Coordinator
+Gyan Seva Bharti Sansthan (GSBS)
+Location:
+Bihar
+Apply by:
+23 Mar 2026
+Financial &amp; Entitlement Linkages (FEL)
+Gyan Seva Bharti Sansthan (GSBS)
+Location:
+Bihar
+Apply by:
+23 Mar 2026
+Supervisors
+Gyan Seva Bharti Sansthan (GSBS)
+Location:
+Bihar
+Apply by:
+23 Mar 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -1126,41 +917,41 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>Learning, Safety</t>
-        </is>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>15-03-2026</t>
         </is>
       </c>
-      <c r="H4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I4" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287902</t>
+      <c r="H3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287910</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr"/>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>ToR - Livelihoods Strategy Review and Future Direction Roadmap</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr"/>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>ToR - Strategic Review and Forward-Looking Education Strategy Development</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>ChildFund India | India
-ToR - Livelihoods Strategy Review and Future Direction Roadmap, ChildFund India() | DevNetJobsIndia
+ToR - Strategic Review and Forward-Looking Education Strategy Development, ChildFund India() | DevNetJobsIndia
 Jobseekers:
 Login
 |
@@ -1176,35 +967,15 @@
 |
 Register
 Jobseekers Login
-Jobseekers Register
-Job ID:
-2 ... Read More</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>• To determine the relevance, alignment, and coherence of the Livelihood Program under CSP 2022–2027 with national priorities, donor expectations, and organizational mandate.
-To assess the extent to which planned outputs and outcomes have been achieved and to evaluate the quality and impact of program interventions.
-Identify achievements, innovations, good practices, and enabling factors across Livelihood program interventions.
-Document gaps, challenges, and areas for strengthening
-To examine the sustainability of program outcomes and the institutional readiness of ChildFund India for long-term resilience and growth.
-Facilitate reflection through workshops involving staff, partners, and selected beneficiaries and provide recommendations for strategic direction, scalability, and future program priorities.
-Proposal Submission
-Interested evaluators/agencies are invited to submit:
-Technical proposal outlining approach and methodology
-Team composition and relevant experience
-Financial proposal with a detailed budget
-Sample of previous qualitative evaluation work
-Interested evaluators/agencies are requested to submit their technical and financial proposals to
-centralpurchase2@childfundindia.org
-by 15 March 2026.
-Reference No:- PRA/CFI/DEL/2025-26/053
-ChildFund India reserves the right to modify this ToR based on programmatic and contextual requirements.
-For detailed information, please check the complete version of the advert attached below.
-• Job Email ID:
+Jobseekers Registe ... Read More</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>• Job Email ID:
 centralpurchase2(at)childfundindia.org
 Download Attachment:
-ToR Livelihood Portfolio-6.3.2026.doc
+ToR for Education.doc
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
@@ -1269,63 +1040,57 @@
 Uttar Pradesh
 Apply by:
 19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Coordinator- Business Development &amp; Partnerships
-Karl Kubel Foundation For Child And Family
-Location:
-Tamil Nadu
-Apply by:
-29 Mar 2026
-Executive Assistant / Team Assistant
-National Council Of Applied Economic Research (NC...
+Research Intern
+DAI Research and Advisory Services
 Location:
 Delhi
 Apply by:
-25 Mar 2026
-RFP - for Outcome Evaluation : Enhancing Foundati...
-Language and Learning Foundation (LLF)
-Location:
-Haryana
-Apply by:
-21 Mar 2026
-Resource Person
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-India
-Apply by:
-10 Apr 2026
-Manager - Business Development
-Foundation For Development Initiative (FDI)
+22 Mar 2026
+Content Writer and Facilitator
+Vedan Trust
+Location:
+Karnataka
+Apply by:
+13 Apr 2026
+Digital Content Developer
+Vedan Trust
+Location:
+Karnataka
+Apply by:
+13 Apr 2026
+CSR Project Co-Ordinator
+Youth For Seva
 Location:
 Delhi
 Apply by:
-12 Apr 2026
-Consultant/ Jr. Officer – Business Development Su...
-Pathfinder Impact Solutions Private Limited
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-State Consultant-Child Protection CPSS
-UNICEF
-Location:
-Gujarat
-Apply by:
-22 Mar 2026
-RFP -  for  Baseline Study of Goat- Sheep based L...
-Urmul Setu Sansthan
-Location:
-Rajasthan
+13 Apr 2026
+Marketing Officer
+Anchalik Samrudhi Sadhana Anusthan (Assa)
+Location:
+Odisha
 Apply by:
 31 Mar 2026
+Project Coordinator
+Gyan Seva Bharti Sansthan (GSBS)
+Location:
+Bihar
+Apply by:
+23 Mar 2026
+Financial &amp; Entitlement Linkages (FEL)
+Gyan Seva Bharti Sansthan (GSBS)
+Location:
+Bihar
+Apply by:
+23 Mar 2026
+Supervisors
+Gyan Seva Bharti Sansthan (GSBS)
+Location:
+Bihar
+Apply by:
+23 Mar 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -1354,41 +1119,41 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>Safety</t>
-        </is>
-      </c>
-      <c r="G5" s="1" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Learning, Safety</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>15-03-2026</t>
         </is>
       </c>
-      <c r="H5" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287910</t>
+      <c r="H4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287902</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr"/>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>ToR - Portfolio-Wide Learning Exercise cum review for the Health Domain</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>ChildFund India | India
-ToR - Portfolio-Wide Learning Exercise cum review for the Health Domain, ChildFund India() | DevNetJobsIndia
+      <c r="B5" s="1" t="inlineStr"/>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>RFQ - for Developing an animated film</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Institute for Global Development (IGD) | India
+RFQ - for Developing an animated film, Institute for Global Development (IGD)() | DevNetJobsIndia
 Jobseekers:
 Login
 |
@@ -1404,15 +1169,31 @@
 |
 Register
 Jobseekers Login
-Jobseekers Register ... Read More</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>• Job Email ID:
-centralpurchase2(at)childfundindia.org
-Download Attachment:
-TOR  Health Portfolio_23.2.2026.doc
+Jobseeke ... Read More</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>• Eligibility Criteria
+IGD
+invites agencies having expertise in developing films for the social sector
+C.
+Deliverables/Outputs
+1.
+Storyboard
+2.
+Final edited 2–3-minute animated film in the required formats (mp4 and mov)
+D.
+PROPOSAL SUBMISSION
+The Agency shall submit Technical and Financial proposals separately for this assignment by
+15
+th
+Mar 2026
+to
+jobs@igdindia.org
+The Agency will provide a detailed cost breakup for each of the activities mentioned above. The costs should be inclusive of all taxes and the out-of-pocket expenses.
+• Job Email ID:
+jobs(at)igdindia.org
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
@@ -1477,63 +1258,57 @@
 Uttar Pradesh
 Apply by:
 19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Coordinator- Business Development &amp; Partnerships
-Karl Kubel Foundation For Child And Family
-Location:
-Tamil Nadu
-Apply by:
-29 Mar 2026
-Executive Assistant / Team Assistant
-National Council Of Applied Economic Research (NC...
+Research Intern
+DAI Research and Advisory Services
 Location:
 Delhi
 Apply by:
-25 Mar 2026
-RFP - for Outcome Evaluation : Enhancing Foundati...
-Language and Learning Foundation (LLF)
-Location:
-Haryana
-Apply by:
-21 Mar 2026
-Resource Person
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-India
-Apply by:
-10 Apr 2026
-Manager - Business Development
-Foundation For Development Initiative (FDI)
+22 Mar 2026
+Content Writer and Facilitator
+Vedan Trust
+Location:
+Karnataka
+Apply by:
+13 Apr 2026
+Digital Content Developer
+Vedan Trust
+Location:
+Karnataka
+Apply by:
+13 Apr 2026
+CSR Project Co-Ordinator
+Youth For Seva
 Location:
 Delhi
 Apply by:
-12 Apr 2026
-Consultant/ Jr. Officer – Business Development Su...
-Pathfinder Impact Solutions Private Limited
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-State Consultant-Child Protection CPSS
-UNICEF
-Location:
-Gujarat
-Apply by:
-22 Mar 2026
-RFP -  for  Baseline Study of Goat- Sheep based L...
-Urmul Setu Sansthan
-Location:
-Rajasthan
+13 Apr 2026
+Marketing Officer
+Anchalik Samrudhi Sadhana Anusthan (Assa)
+Location:
+Odisha
 Apply by:
 31 Mar 2026
+Project Coordinator
+Gyan Seva Bharti Sansthan (GSBS)
+Location:
+Bihar
+Apply by:
+23 Mar 2026
+Financial &amp; Entitlement Linkages (FEL)
+Gyan Seva Bharti Sansthan (GSBS)
+Location:
+Bihar
+Apply by:
+23 Mar 2026
+Supervisors
+Gyan Seva Bharti Sansthan (GSBS)
+Location:
+Bihar
+Apply by:
+23 Mar 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -1562,41 +1337,41 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>Learning, Safety</t>
-        </is>
-      </c>
-      <c r="G6" s="1" t="inlineStr">
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>Learning</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>15-03-2026</t>
         </is>
       </c>
-      <c r="H6" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I6" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287901</t>
+      <c r="H5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=288181</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr"/>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>RFP for Data Collection for Foundational Reading Tool in Odisha</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Lords Education and Health Society (LEHS) | Odisha
-RFP for Data Collection for Foundational Reading Tool in Odisha, Lords Education and Health Society (LEHS)() | DevNetJobsIndia
+      <c r="B6" s="1" t="inlineStr"/>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>ToR - Portfolio-Wide Learning Exercise cum review for the Health Domain</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>ChildFund India | India
+ToR - Portfolio-Wide Learning Exercise cum review for the Health Domain, ChildFund India() | DevNetJobsIndia
 Jobseekers:
 Login
 |
@@ -1610,36 +1385,17 @@
 Jobseekers:
 Login
 |
-R ... Read More</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>• 4. SCOPE OF WORK
-Summary of Activities
-S.No
-Activity   Description
-Timelines
-1
-Data   Collection: students' reading of textual items   (letters/words/non-words/paragraphs) in Odia &amp; English languages for   Grades 1-8.
-Data       Collection should be completed in   April 2026
-Details of the Activity Below:
-Data Collection: Collect audio data of students reading texts in Odia &amp; English from Grade 1-8
-Total Number of Hours to be collected: ~360 hours for the Odia language
-Total Number of Hours to be collected: ~115 hours for the English language
-• Submission Details
-All proposals to this RFP must be received no later than &lt;15th March 2026&gt;
-.
-The proposal should be submitted only through e-mail in PDF format addressed to the Procurement Team at:
-rfp.lehs@wadhwaniai.org
-. The email's subject line must contain the reference number and title of the RFP: Data Collection for Foundational Reading
-Tool in Odisha  (Name of Partner)
-Any proposals received by Wadhwani-AI after the deadline prescribed in the timeline of this document are liable to be rejected.
-For detailed information, please check the complete version of the RFP attached below
-• Job Email ID:
-rfp.lehs(at)wadhwaniai.org
+Register
+Jobseekers Login
+Jobseekers Register ... Read More</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>• Job Email ID:
+centralpurchase2(at)childfundindia.org
 Download Attachment:
-RFP for Data Collection for Foundational Reading Tool in Odisha.pdf
+TOR  Health Portfolio_23.2.2026.doc
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
@@ -1704,63 +1460,57 @@
 Uttar Pradesh
 Apply by:
 19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Coordinator- Business Development &amp; Partnerships
-Karl Kubel Foundation For Child And Family
-Location:
-Tamil Nadu
-Apply by:
-29 Mar 2026
-Executive Assistant / Team Assistant
-National Council Of Applied Economic Research (NC...
+Research Intern
+DAI Research and Advisory Services
 Location:
 Delhi
 Apply by:
-25 Mar 2026
-RFP - for Outcome Evaluation : Enhancing Foundati...
-Language and Learning Foundation (LLF)
-Location:
-Haryana
-Apply by:
-21 Mar 2026
-Resource Person
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-India
-Apply by:
-10 Apr 2026
-Manager - Business Development
-Foundation For Development Initiative (FDI)
+22 Mar 2026
+Content Writer and Facilitator
+Vedan Trust
+Location:
+Karnataka
+Apply by:
+13 Apr 2026
+Digital Content Developer
+Vedan Trust
+Location:
+Karnataka
+Apply by:
+13 Apr 2026
+CSR Project Co-Ordinator
+Youth For Seva
 Location:
 Delhi
 Apply by:
-12 Apr 2026
-Consultant/ Jr. Officer – Business Development Su...
-Pathfinder Impact Solutions Private Limited
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-State Consultant-Child Protection CPSS
-UNICEF
-Location:
-Gujarat
-Apply by:
-22 Mar 2026
-RFP -  for  Baseline Study of Goat- Sheep based L...
-Urmul Setu Sansthan
-Location:
-Rajasthan
+13 Apr 2026
+Marketing Officer
+Anchalik Samrudhi Sadhana Anusthan (Assa)
+Location:
+Odisha
 Apply by:
 31 Mar 2026
+Project Coordinator
+Gyan Seva Bharti Sansthan (GSBS)
+Location:
+Bihar
+Apply by:
+23 Mar 2026
+Financial &amp; Entitlement Linkages (FEL)
+Gyan Seva Bharti Sansthan (GSBS)
+Location:
+Bihar
+Apply by:
+23 Mar 2026
+Supervisors
+Gyan Seva Bharti Sansthan (GSBS)
+Location:
+Bihar
+Apply by:
+23 Mar 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -1789,38 +1539,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>Governance, Learning, Safety</t>
-        </is>
-      </c>
-      <c r="G7" s="1" t="inlineStr">
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>Learning, Safety</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>15-03-2026</t>
         </is>
       </c>
-      <c r="H7" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I7" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287936</t>
+      <c r="H6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287901</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr"/>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>RFP - External organization/agency to undertake documentation and process ...</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>India Health Action Trust (IHAT) | India
 RFP - External organization/agency to undertake documentation and process evaluation of the Gen Equal Fellowship Programme, India Health Action Trust (IHAT)() | DevNetJobsIndia
@@ -1834,7 +1584,7 @@
 RFPs/Tenders ... Read More</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>• 3A. Scope of Work
 Time Period
@@ -1971,63 +1721,57 @@
 Uttar Pradesh
 Apply by:
 19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Coordinator- Business Development &amp; Partnerships
-Karl Kubel Foundation For Child And Family
-Location:
-Tamil Nadu
-Apply by:
-29 Mar 2026
-Executive Assistant / Team Assistant
-National Council Of Applied Economic Research (NC...
+Research Intern
+DAI Research and Advisory Services
 Location:
 Delhi
 Apply by:
-25 Mar 2026
-RFP - for Outcome Evaluation : Enhancing Foundati...
-Language and Learning Foundation (LLF)
-Location:
-Haryana
-Apply by:
-21 Mar 2026
-Resource Person
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-India
-Apply by:
-10 Apr 2026
-Manager - Business Development
-Foundation For Development Initiative (FDI)
+22 Mar 2026
+Content Writer and Facilitator
+Vedan Trust
+Location:
+Karnataka
+Apply by:
+13 Apr 2026
+Digital Content Developer
+Vedan Trust
+Location:
+Karnataka
+Apply by:
+13 Apr 2026
+CSR Project Co-Ordinator
+Youth For Seva
 Location:
 Delhi
 Apply by:
-12 Apr 2026
-Consultant/ Jr. Officer – Business Development Su...
-Pathfinder Impact Solutions Private Limited
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-State Consultant-Child Protection CPSS
-UNICEF
-Location:
-Gujarat
-Apply by:
-22 Mar 2026
-RFP -  for  Baseline Study of Goat- Sheep based L...
-Urmul Setu Sansthan
-Location:
-Rajasthan
+13 Apr 2026
+Marketing Officer
+Anchalik Samrudhi Sadhana Anusthan (Assa)
+Location:
+Odisha
 Apply by:
 31 Mar 2026
+Project Coordinator
+Gyan Seva Bharti Sansthan (GSBS)
+Location:
+Bihar
+Apply by:
+23 Mar 2026
+Financial &amp; Entitlement Linkages (FEL)
+Gyan Seva Bharti Sansthan (GSBS)
+Location:
+Bihar
+Apply by:
+23 Mar 2026
+Supervisors
+Gyan Seva Bharti Sansthan (GSBS)
+Location:
+Bihar
+Apply by:
+23 Mar 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -2056,41 +1800,41 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F8" s="1" t="inlineStr">
+      <c r="F7" s="1" t="inlineStr">
         <is>
           <t>Safety</t>
         </is>
       </c>
-      <c r="G8" s="1" t="inlineStr">
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>15-03-2026</t>
         </is>
       </c>
-      <c r="H8" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I8" s="1" t="inlineStr">
+      <c r="H7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287645</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr"/>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>RFQ - for Developing an animated film</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Institute for Global Development (IGD) | India
-RFQ - for Developing an animated film, Institute for Global Development (IGD)() | DevNetJobsIndia
+      <c r="B8" s="1" t="inlineStr"/>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>RFP for Data Collection for Foundational Reading Tool in Odisha</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Lords Education and Health Society (LEHS) | Odisha
+RFP for Data Collection for Foundational Reading Tool in Odisha, Lords Education and Health Society (LEHS)() | DevNetJobsIndia
 Jobseekers:
 Login
 |
@@ -2104,33 +1848,36 @@
 Jobseekers:
 Login
 |
-Register
-Jobseekers Login
-Jobseeke ... Read More</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>• Eligibility Criteria
-IGD
-invites agencies having expertise in developing films for the social sector
-C.
-Deliverables/Outputs
-1.
-Storyboard
-2.
-Final edited 2–3-minute animated film in the required formats (mp4 and mov)
-D.
-PROPOSAL SUBMISSION
-The Agency shall submit Technical and Financial proposals separately for this assignment by
-15
-th
-Mar 2026
-to
-jobs@igdindia.org
-The Agency will provide a detailed cost breakup for each of the activities mentioned above. The costs should be inclusive of all taxes and the out-of-pocket expenses.
+R ... Read More</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>• 4. SCOPE OF WORK
+Summary of Activities
+S.No
+Activity   Description
+Timelines
+1
+Data   Collection: students' reading of textual items   (letters/words/non-words/paragraphs) in Odia &amp; English languages for   Grades 1-8.
+Data       Collection should be completed in   April 2026
+Details of the Activity Below:
+Data Collection: Collect audio data of students reading texts in Odia &amp; English from Grade 1-8
+Total Number of Hours to be collected: ~360 hours for the Odia language
+Total Number of Hours to be collected: ~115 hours for the English language
+• Submission Details
+All proposals to this RFP must be received no later than &lt;15th March 2026&gt;
+.
+The proposal should be submitted only through e-mail in PDF format addressed to the Procurement Team at:
+rfp.lehs@wadhwaniai.org
+. The email's subject line must contain the reference number and title of the RFP: Data Collection for Foundational Reading
+Tool in Odisha  (Name of Partner)
+Any proposals received by Wadhwani-AI after the deadline prescribed in the timeline of this document are liable to be rejected.
+For detailed information, please check the complete version of the RFP attached below
 • Job Email ID:
-jobs(at)igdindia.org
+rfp.lehs(at)wadhwaniai.org
+Download Attachment:
+RFP for Data Collection for Foundational Reading Tool in Odisha.pdf
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
@@ -2195,63 +1942,57 @@
 Uttar Pradesh
 Apply by:
 19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Coordinator- Business Development &amp; Partnerships
-Karl Kubel Foundation For Child And Family
-Location:
-Tamil Nadu
-Apply by:
-29 Mar 2026
-Executive Assistant / Team Assistant
-National Council Of Applied Economic Research (NC...
+Research Intern
+DAI Research and Advisory Services
 Location:
 Delhi
 Apply by:
-25 Mar 2026
-RFP - for Outcome Evaluation : Enhancing Foundati...
-Language and Learning Foundation (LLF)
-Location:
-Haryana
-Apply by:
-21 Mar 2026
-Resource Person
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-India
-Apply by:
-10 Apr 2026
-Manager - Business Development
-Foundation For Development Initiative (FDI)
+22 Mar 2026
+Content Writer and Facilitator
+Vedan Trust
+Location:
+Karnataka
+Apply by:
+13 Apr 2026
+Digital Content Developer
+Vedan Trust
+Location:
+Karnataka
+Apply by:
+13 Apr 2026
+CSR Project Co-Ordinator
+Youth For Seva
 Location:
 Delhi
 Apply by:
-12 Apr 2026
-Consultant/ Jr. Officer – Business Development Su...
-Pathfinder Impact Solutions Private Limited
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-State Consultant-Child Protection CPSS
-UNICEF
-Location:
-Gujarat
-Apply by:
-22 Mar 2026
-RFP -  for  Baseline Study of Goat- Sheep based L...
-Urmul Setu Sansthan
-Location:
-Rajasthan
+13 Apr 2026
+Marketing Officer
+Anchalik Samrudhi Sadhana Anusthan (Assa)
+Location:
+Odisha
 Apply by:
 31 Mar 2026
+Project Coordinator
+Gyan Seva Bharti Sansthan (GSBS)
+Location:
+Bihar
+Apply by:
+23 Mar 2026
+Financial &amp; Entitlement Linkages (FEL)
+Gyan Seva Bharti Sansthan (GSBS)
+Location:
+Bihar
+Apply by:
+23 Mar 2026
+Supervisors
+Gyan Seva Bharti Sansthan (GSBS)
+Location:
+Bihar
+Apply by:
+23 Mar 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -2280,38 +2021,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>Learning</t>
-        </is>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>Governance, Learning, Safety</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
         <is>
           <t>15-03-2026</t>
         </is>
       </c>
-      <c r="H9" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=288181</t>
+      <c r="H8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
+          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287936</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr"/>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="B9" s="1" t="inlineStr"/>
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>RFP - for Empanelment of Knowledge Partners for Grooming of students for ...</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>TeamLease Foundation | India
 RFP - for  Empanelment of Knowledge Partners for Grooming of students for competitive examination (through partner) Super 30 Model, TeamLease Foundation() | DevNetJobsIndia
@@ -2327,43 +2068,43 @@
 Even ... Read More</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F10" s="1" t="inlineStr">
+      <c r="F9" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G10" s="1" t="inlineStr">
+      <c r="G9" s="1" t="inlineStr">
         <is>
           <t>15-03-2026</t>
         </is>
       </c>
-      <c r="H10" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" s="1" t="inlineStr">
+      <c r="H9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287763</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr"/>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="B10" s="1" t="inlineStr"/>
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>RFP - Big IC+ISA RFP - Selection of a Service Provider for Supply, Instal...</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>EAII Advisors Pvt Ltd | Andhra Pradesh
 RFP - Big IC+ISA RFP -  Selection of a Service Provider for Supply, Installation and Operation &amp; Maintenance of 150 ILC Devices and Capacity Building., EAII Advisors Pvt Ltd() | DevNetJobsIndia
@@ -2376,7 +2117,7 @@
 Broadcast Resum ... Read More</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>• 2. Purpose of the RFP:
 2.1  EAII is soliciting bids for:
@@ -2477,63 +2218,57 @@
 Uttar Pradesh
 Apply by:
 19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Coordinator- Business Development &amp; Partnerships
-Karl Kubel Foundation For Child And Family
-Location:
-Tamil Nadu
-Apply by:
-29 Mar 2026
-Executive Assistant / Team Assistant
-National Council Of Applied Economic Research (NC...
+Research Intern
+DAI Research and Advisory Services
 Location:
 Delhi
 Apply by:
-25 Mar 2026
-RFP - for Outcome Evaluation : Enhancing Foundati...
-Language and Learning Foundation (LLF)
-Location:
-Haryana
-Apply by:
-21 Mar 2026
-Resource Person
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-India
-Apply by:
-10 Apr 2026
-Manager - Business Development
-Foundation For Development Initiative (FDI)
+22 Mar 2026
+Content Writer and Facilitator
+Vedan Trust
+Location:
+Karnataka
+Apply by:
+13 Apr 2026
+Digital Content Developer
+Vedan Trust
+Location:
+Karnataka
+Apply by:
+13 Apr 2026
+CSR Project Co-Ordinator
+Youth For Seva
 Location:
 Delhi
 Apply by:
-12 Apr 2026
-Consultant/ Jr. Officer – Business Development Su...
-Pathfinder Impact Solutions Private Limited
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-State Consultant-Child Protection CPSS
-UNICEF
-Location:
-Gujarat
-Apply by:
-22 Mar 2026
-RFP -  for  Baseline Study of Goat- Sheep based L...
-Urmul Setu Sansthan
-Location:
-Rajasthan
+13 Apr 2026
+Marketing Officer
+Anchalik Samrudhi Sadhana Anusthan (Assa)
+Location:
+Odisha
 Apply by:
 31 Mar 2026
+Project Coordinator
+Gyan Seva Bharti Sansthan (GSBS)
+Location:
+Bihar
+Apply by:
+23 Mar 2026
+Financial &amp; Entitlement Linkages (FEL)
+Gyan Seva Bharti Sansthan (GSBS)
+Location:
+Bihar
+Apply by:
+23 Mar 2026
+Supervisors
+Gyan Seva Bharti Sansthan (GSBS)
+Location:
+Bihar
+Apply by:
+23 Mar 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -2562,466 +2297,38 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F11" s="1" t="inlineStr">
+      <c r="F10" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G11" s="1" t="inlineStr">
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>16-03-2026</t>
         </is>
       </c>
-      <c r="H11" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="I11" s="1" t="inlineStr">
+      <c r="H10" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=287172</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr"/>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Design, Development, Deployment and Maintenance of Mobile Applicati...</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>YRGCARE | India
-RFP - Design, Development, Deployment and Maintenance of  Mobile Application for the Breakfree Platform, YRGCARE() | DevNetJobsIndia
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Login
-|
-Register
-Jobseekers Login
-Jobs ... Read More</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>• This Terms of Reference (ToR) defines the full scope of work, technical requirements, compliance standards, and performance expectations for the agency appointed to design, develop, deploy, and maintain the Breakfree mobile application for both Android and iOS platforms.
-For detailed information visit
-https://www.yrgmerf.org/procurement-notices
-or please check the complete version of the RFP attached below.
-• Job Email ID:
-rfp(at)yrgcare.org
-Download Attachment:
-Mobile Application Development_RFP_002_2026_Evaluation_Grid.pdf
-Download Attachment:
-Mobile Application Development_RFP_002_Mob_App_.pdf
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-19 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Associate – Finance and Operations
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-05 Apr 2026
-Unit Head - Proposal Development
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-11 Apr 2026
-Research Analysts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-11 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-View more featured non-profit jobs
-Latest NGO Jobs
-Post your highlighted jobs here
-Coordinator- Business Development &amp; Partnerships
-Karl Kubel Foundation For Child And Family
-Location:
-Tamil Nadu
-Apply by:
-29 Mar 2026
-Executive Assistant / Team Assistant
-National Council Of Applied Economic Research (NC...
-Location:
-Delhi
-Apply by:
-25 Mar 2026
-RFP - for Outcome Evaluation : Enhancing Foundati...
-Language and Learning Foundation (LLF)
-Location:
-Haryana
-Apply by:
-21 Mar 2026
-Resource Person
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-India
-Apply by:
-10 Apr 2026
-Manager - Business Development
-Foundation For Development Initiative (FDI)
-Location:
-Delhi
-Apply by:
-12 Apr 2026
-Consultant/ Jr. Officer – Business Development Su...
-Pathfinder Impact Solutions Private Limited
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-State Consultant-Child Protection CPSS
-UNICEF
-Location:
-Gujarat
-Apply by:
-22 Mar 2026
-RFP -  for  Baseline Study of Goat- Sheep based L...
-Urmul Setu Sansthan
-Location:
-Rajasthan
-Apply by:
-31 Mar 2026
-View all the latest non-profit jobs
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>Learning, Safety</t>
-        </is>
-      </c>
-      <c r="G12" s="1" t="inlineStr">
-        <is>
-          <t>19-03-2026</t>
-        </is>
-      </c>
-      <c r="H12" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I12" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=288064</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="inlineStr"/>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>RFP - Appointment of Agency for SEO Management and Meta (Facebook / Instag...</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>YRGCARE | India
-RFP - Appointment of Agency for SEO Management and Meta (Facebook / Instagram) Advertising, YRGCARE() | DevNetJobsIndia
-Jobseekers:
-Login
-|
-Register
-Home
-Value Membership
-Broadcast Resume
-RFPs/Tenders
-Search Jobs
-Events
-Jobseekers:
-Login
-|
-Register
-Jobseekers Login
-Jobseekers Regist ... Read More</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>• To drive sustained awareness, organic discoverability, and ethical user engagement, NACO/YRGCARE intends to appoint professional agencies to manage two complementary digital outreach functions: Search Engine Optimisation (SEO) and paid social outreach through Meta platforms (Facebook and Instagram). This ToR defines the full scope, expectations, compliance requirements, and monitoring framework for this appointment.
-For detailed information visit
-https://www.yrgmerf.org/procurement-notices
-or please check the complete version of the RFP attached below.
-• Job Email ID:
-rfp(at)yrgcare.org
-Download Attachment:
-RFP_001_2026_SEO_.pdf
-Download Attachment:
-RFP_001_2026_Evaluation_Grid_SEO.pdf
-View Similar Jobs:
-Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
-Subscribe
-Apply by:
-19 Mar 2026
-Access all the jobs and get ahead!
-Subscribe to Value Membership Now!
-Subscribe
-Premium Jobs
-Post your premium jobs here
-Associate – Finance and Operations
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-05 Apr 2026
-Unit Head - Proposal Development
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-11 Apr 2026
-Research Analysts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-11 Apr 2026
-Lead-Finance &amp; Compliance
-Marathwada Navnirman Lokayat (Manavlok)
-Location:
-Maharashtra
-Apply by:
-03 Apr 2026
-Sector Experts
-Academy of Management Studies (AMS)
-Location:
-India
-Apply by:
-31 Mar 2026
-Junior Research Technicians / Senior Project Asso...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Agriculture Research Development Officer / Projec...
-Starshield Security Solution Pvt.Ltd
-Location:
-Uttar Pradesh
-Apply by:
-30 Mar 2026
-Specialist - Grants
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-21 Mar 2026
-Specialist – Communication
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
-View more featured non-profit jobs
-Latest NGO Jobs
-Post your highlighted jobs here
-Coordinator- Business Development &amp; Partnerships
-Karl Kubel Foundation For Child And Family
-Location:
-Tamil Nadu
-Apply by:
-29 Mar 2026
-Executive Assistant / Team Assistant
-National Council Of Applied Economic Research (NC...
-Location:
-Delhi
-Apply by:
-25 Mar 2026
-RFP - for Outcome Evaluation : Enhancing Foundati...
-Language and Learning Foundation (LLF)
-Location:
-Haryana
-Apply by:
-21 Mar 2026
-Resource Person
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-India
-Apply by:
-10 Apr 2026
-Manager - Business Development
-Foundation For Development Initiative (FDI)
-Location:
-Delhi
-Apply by:
-12 Apr 2026
-Consultant/ Jr. Officer – Business Development Su...
-Pathfinder Impact Solutions Private Limited
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-State Consultant-Child Protection CPSS
-UNICEF
-Location:
-Gujarat
-Apply by:
-22 Mar 2026
-RFP -  for  Baseline Study of Goat- Sheep based L...
-Urmul Setu Sansthan
-Location:
-Rajasthan
-Apply by:
-31 Mar 2026
-View all the latest non-profit jobs
-Jobseekers
-Register
-Login
-Subscribe to Value Membership
-Broadcast Resume
-Contact Us
-Recruiters
-Recruiters Zone
-Post a Free Job
-Post a Highlighted Job (With Logo)
-Post a Highlighted Job (Without Logo)
-Post a Premium Job
-More Job Posting Options
-Rates
-Contact Us
-Advertisers
-Networks
-Advertise Your Banner
-Submit Events &amp; Notices
-© 2025 M-Power Jobs. All rights reserved.
-Disclaimer
-Privacy Policy
-Terms &amp; Conditions
-Powered by
-Recruitment Exchange</t>
-        </is>
-      </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>Governance</t>
-        </is>
-      </c>
-      <c r="G13" s="1" t="inlineStr">
-        <is>
-          <t>19-03-2026</t>
-        </is>
-      </c>
-      <c r="H13" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I13" s="1" t="inlineStr">
-        <is>
-          <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=288063</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>DevNetJobsIndia</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="inlineStr"/>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr"/>
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>RFP - Establishment and Development of Farmer Business School in Laxmipur,...</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>PRASTUTEE &amp; WORD - Heifer International | Koraput, Odisha
 RFP - Establishment and Development of Farmer Business School in Laxmipur, Nandapur, Pottangi and Semiliguda blocks of Koraput, PRASTUTEE &amp; WORD - Heifer International(Koraput) | DevNetJobsIndia
@@ -3033,7 +2340,7 @@
 Value Member ... Read More</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>• Scope of work
 We invite vendors having expertise in this sector to quote their price as per the details and share in the email provided here. The vendor will complete supply of all materials for ten FBS at designated locations in Laxmipur, Nandapur, Pottangi and Semiliguda blocks of Koraput district by 31
@@ -3241,63 +2548,57 @@
 Uttar Pradesh
 Apply by:
 19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Coordinator- Business Development &amp; Partnerships
-Karl Kubel Foundation For Child And Family
-Location:
-Tamil Nadu
-Apply by:
-29 Mar 2026
-Executive Assistant / Team Assistant
-National Council Of Applied Economic Research (NC...
+Research Intern
+DAI Research and Advisory Services
 Location:
 Delhi
 Apply by:
-25 Mar 2026
-RFP - for Outcome Evaluation : Enhancing Foundati...
-Language and Learning Foundation (LLF)
-Location:
-Haryana
-Apply by:
-21 Mar 2026
-Resource Person
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-India
-Apply by:
-10 Apr 2026
-Manager - Business Development
-Foundation For Development Initiative (FDI)
+22 Mar 2026
+Content Writer and Facilitator
+Vedan Trust
+Location:
+Karnataka
+Apply by:
+13 Apr 2026
+Digital Content Developer
+Vedan Trust
+Location:
+Karnataka
+Apply by:
+13 Apr 2026
+CSR Project Co-Ordinator
+Youth For Seva
 Location:
 Delhi
 Apply by:
-12 Apr 2026
-Consultant/ Jr. Officer – Business Development Su...
-Pathfinder Impact Solutions Private Limited
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-State Consultant-Child Protection CPSS
-UNICEF
-Location:
-Gujarat
-Apply by:
-22 Mar 2026
-RFP -  for  Baseline Study of Goat- Sheep based L...
-Urmul Setu Sansthan
-Location:
-Rajasthan
+13 Apr 2026
+Marketing Officer
+Anchalik Samrudhi Sadhana Anusthan (Assa)
+Location:
+Odisha
 Apply by:
 31 Mar 2026
+Project Coordinator
+Gyan Seva Bharti Sansthan (GSBS)
+Location:
+Bihar
+Apply by:
+23 Mar 2026
+Financial &amp; Entitlement Linkages (FEL)
+Gyan Seva Bharti Sansthan (GSBS)
+Location:
+Bihar
+Apply by:
+23 Mar 2026
+Supervisors
+Gyan Seva Bharti Sansthan (GSBS)
+Location:
+Bihar
+Apply by:
+23 Mar 2026
 View all the latest non-profit jobs
 Jobseekers
 Register
@@ -3326,41 +2627,41 @@
 Recruitment Exchange</t>
         </is>
       </c>
-      <c r="F14" s="1" t="inlineStr">
+      <c r="F11" s="1" t="inlineStr">
         <is>
           <t>Learning</t>
         </is>
       </c>
-      <c r="G14" s="1" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>19-03-2026</t>
         </is>
       </c>
-      <c r="H14" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I14" s="1" t="inlineStr">
+      <c r="H11" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" s="1" t="inlineStr">
         <is>
           <t>https://www.devnetjobsindia.org/JobDescription.aspx?Job_Id=288228</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>DevNetJobsIndia</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr"/>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>Technical Consultant/Firm - Infrastructure Design, estimate and cost stand...</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>WaterAid India | India
-Technical Consultant/Firm - Infrastructure Design, estimate and cost standardisation, WaterAid India() | DevNetJobsIndia
+      <c r="B12" s="1" t="inlineStr"/>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>RFP - Design, Development, Deployment and Maintenance of Mobile Applicati...</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>YRGCARE | India
+RFP - Design, Development, Deployment and Maintenance of  Mobile Application for the Breakfree Platform, YRGCARE() | DevNetJobsIndia
 Jobseekers:
 Login
 |
@@ -3376,18 +2677,26 @@
 |
 Register
 Jobseekers Login
-Jobseeker ... Read More</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>• Job Email ID:
-waindiahr(at)wateraid.org
+Jobs ... Read More</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>• This Terms of Reference (ToR) defines the full scope of work, technical requirements, compliance standards, and performance expectations for the agency appointed to design, develop, deploy, and maintain the Breakfree mobile application for both Android and iOS platforms.
+For detailed information visit
+https://www.yrgmerf.org/procurement-notices
+or please check the complete version of the RFP attached below.
+• Job Email ID:
+rfp(at)yrgcare.org
+Download Attachment:
+Mobile Application Development_RFP_002_2026_Evaluation_Grid.pdf
+Download Attachment:
+Mobile Application Development_RFP_002_Mob_App_.pdf
 View Similar Jobs:
 Was this job of interest to you? Subscribe to Value Membership to get access to similar jobs and hundreds of other member-only jobs.
 Subscribe
 Apply by:
-20 Mar 2026
+19 Mar 2026
 Access all the jobs and get ahead!
 Subscribe to Value Membership Now!
 Subscribe
@@ -3447,63 +2756,57 @@
 Uttar Pradesh
 Apply by:
 19 Mar 2026
-Specialist – Financial Management and Compliance
-Financial Management Service Foundation (FMSF)
-Location:
-Uttar Pradesh
-Apply by:
-13 Mar 2026
 View more featured non-profit jobs
 Latest NGO Jobs
 Post your highlighted jobs here
-Coordinator- Business Development &amp; Partnerships
-Karl Kubel Foundation For Child And Family
-Location:
-Tamil Nadu
-Apply by:
-29 Mar 2026
-Executive Assistant / Team Assistant
-National Council Of Applied Economic Research (NC...
+Research Intern
+DAI Research and Advisory Services
 Location:
 Delhi
 Apply by:
-25 Mar 2026
-RFP - for Outcome Evaluation : Enhancing Foundati...
-Language and Learning Foundation (LLF)
-Location:
-Haryana
-Apply by:
-21 Mar 2026
-Resource Person
-Bharat Rural Livelihoods Foundation (BRLF)
-Location:
-India
-Apply by:
-10 Apr 2026
-Manager - Business Development
-Foundation For Development Initiative (FDI)
+22 Mar 2026
+Content Writer and Facilitator
+Vedan Trust
+Location:
+Karnataka
+Apply by:
+13 Apr 2026
+Digital Content Developer
+Vedan Trust
+Location:
+Karnataka
+Apply by:
+13 Apr 2026
+CSR Project Co-Ordinator
+Youth For Seva
 Location:
 Delhi
 Apply by:
-12 Apr 2026
-Consultant/ Jr. Officer – Business Development Su...
-Pathfinder Impact Solutions Private Limited
-Location:
-Delhi
-Apply by:
-22 Mar 2026
-State Consultant-Child Protection CPSS
-UNICEF
-Location:
-Gujarat
-Apply by:
-22 Mar 2026
-RFP -  for  Baseline Study of Goat- Sheep based L...
-Urmul Setu Sansthan
-Location:
-Rajasthan
+13 Apr 2026
+Marketing Officer
+Anchalik Samrudhi Sadhana Anusthan (Assa)
+Location:
+Odisha
 Apply by:
 31 Mar 2026
+Project Coordinator
+Gyan Seva Bharti Sansthan (GSBS)
+Location:
+Bihar
+Apply by:
+23 Mar 2026
+Financial &amp; Entitlement Linkages (FEL)
+Gyan Seva Bharti Sansthan (GSBS)
+Locat